--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -448,11 +448,11 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -585,16 +585,36 @@
       <c r="L2" s="2" t="n">
         <v>19.99</v>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Ladderup Finance Ltd. Upper Circuit Streak: Day 2 Price and Data - Univest</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Ashoka Metcast Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Ladderup Finance Ltd. Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Ashoka Metcast Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Ladderup Finance Limited – NSE:LADDERUP - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -602,48 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AWFIS.NS</t>
+          <t>STLSTRINF.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Awfis Space Solutions Limited</t>
+          <t>Steel Strips Infrastructures Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>248.5</v>
+        <v>19.19000053405762</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>299.4500122070312</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>244.1000061035156</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>293.2000122070312</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>249.6000061035156</v>
+        <v>17.67000007629395</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>293.2000122070312</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>23943415</v>
+        <v>12925</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+        <v>19.98</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>STLSTRINF Stock Price and Chart — NSE:STLSTRINF - TradingView</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Steel Strips Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Steel Strips Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,48 +691,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>VGL.NS</t>
+          <t>ASHOKAMET.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>VARVEE GLOBAL LIMITED</t>
+          <t>Ashoka Metcast Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>57.95999908447266</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>69.33000183105469</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>54.61999893188477</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.81999969482422</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>57.77999877929688</v>
+        <v>14.34000015258789</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>66.81999969482422</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2056788</v>
+        <v>1455188</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+        <v>19.94</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Ashoka Metcast (NSE:ASHOKAMET) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Ashoka Metcast (NSE:ASHOKAMET) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Ashoka Metcast sells 2.48M Mena Mani Industries shares in open market - scanx.trade</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -700,48 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AMDIND.NS</t>
+          <t>AWFIS.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Limited</t>
+          <t>Awfis Space Solutions Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>56.31999969482422</v>
+        <v>248.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65.19999694824219</v>
+        <v>299.4500122070312</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>55.5099983215332</v>
+        <v>244.1000061035156</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>64.02999877929688</v>
+        <v>293.2000122070312</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>56.04000091552734</v>
+        <v>249.6000061035156</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64.02999877929688</v>
+        <v>293.2000122070312</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>483363</v>
+        <v>23945553</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14.26</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+        <v>17.47</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Awfis Space Solutions share price jumps nearly 20% despite weak Sensex, Nifty 50; what should investors do now? - Livemint</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>AWFIS Space Solutions Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>AWFIS Space Solutions Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Awfis Space Solutions Share Price: Buy or Sell - Univest</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>₹524: That's What Analysts Think Awfis Space Solutions Limited (NSE:AWFIS) Is Worth After Its Latest Results - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -749,48 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AHCL.NS</t>
+          <t>RAYMOND.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Limited</t>
+          <t>Raymond Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17.72999954223633</v>
+        <v>853.8499755859375</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20</v>
+        <v>1024.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17.54000091552734</v>
+        <v>835.0499877929688</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>1002.799987792969</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>17.54000091552734</v>
+        <v>853.8499755859375</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>1002.799987792969</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>150744012</v>
+        <v>16245056</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+        <v>17.44</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Raymond shares to remain in focus as aerospace arm wins orders - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Raymond shares to remain in focus as aerospace arm wins orders - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Raymond shares jump 20% to hit all-time high after three days of consecutive gains; further growth tailwinds ahead? - upstox.com</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Raymond surges 20% on huge volume; here's why stock rose 66% in 11 days - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Small-cap multibagger stock: 135% return in YTD | Defence subsidiary wins ₹33 crore aerospace order - Livemint</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -798,48 +890,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TRACXN.NS</t>
+          <t>FILATEX.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tracxn Technologies Limited</t>
+          <t>Filatex India Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>28.59000015258789</v>
+        <v>76</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>32.38999938964844</v>
+        <v>90.90000152587891</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>28.43000030517578</v>
+        <v>74.26999664306641</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>31.89999961853027</v>
+        <v>87.41000366210938</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>28.61000061035156</v>
+        <v>76.25</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31.89999961853027</v>
+        <v>87.41000366210938</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1039487</v>
+        <v>38898608</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+        <v>14.64</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Be Sure To Check Out Filatex India Limited (NSE:FILATEX) Before It Goes Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Filatex Fashions publishes 32nd AGM notice in newspapers - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Filatex India Share Price: price action and fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Filatex Fashions publishes 32nd AGM notice in newspapers - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Filatex India Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -847,40 +959,48 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SMSPHARMA.NS</t>
+          <t>AMDIND.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SMS Pharmaceuticals Limited</t>
+          <t>AMD Industries Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>417.8500061035156</v>
+        <v>56.31999969482422</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>469</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>414.5499877929688</v>
+        <v>55.5099983215332</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>463.4500122070312</v>
+        <v>64.02999877929688</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>417.4500122070312</v>
+        <v>56.04000091552734</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>463.4500122070312</v>
+        <v>64.02999877929688</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>10400042</v>
+        <v>484603</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+        <v>14.26</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>AMD Industries Share Price rises 12.01%: valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>AMD Industries Share Price rises 12.01%: valuation view - Univest</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -888,7 +1008,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -896,48 +1016,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RACLGEAR.NS</t>
+          <t>SHERVANI.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>RACL Geartech Limited</t>
+          <t>Shervani Industrial Syndicate Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1586</v>
+        <v>326</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1856</v>
+        <v>360</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1551</v>
+        <v>309</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1756.699951171875</v>
+        <v>348.8500061035156</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1588.199951171875</v>
+        <v>311</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1756.699951171875</v>
+        <v>348.8500061035156</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1142822</v>
+        <v>3811</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+        <v>12.17</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate FY26 Results - investywise.com</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Shervani Industrial sets Sep 18 record date for FY26 dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Ltd. Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Ltd. (SHERVANI) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -945,48 +1085,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>HLEGLAS.NS</t>
+          <t>AHCL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>HLE Glascoat Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>367.8500061035156</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>404.3500061035156</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>363</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>404.3500061035156</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>367.6000061035156</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>404.3500061035156</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>870030</v>
+        <v>150749037</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
+        <v>11.57</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>AHCL Stock Price and Chart — NSE:AHCL - TradingView</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>ANLON HEALTHCARE LIMITED Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>ANLON HEALTHCARE LIMITED Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -994,48 +1150,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ANMOL.NS</t>
+          <t>SMSPHARMA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Anmol India Limited</t>
+          <t>SMS Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>15</v>
+        <v>417.8500061035156</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>469</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15</v>
+        <v>414.5499877929688</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>463.4500122070312</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15.34000015258789</v>
+        <v>417.4500122070312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>463.4500122070312</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1521669</v>
+        <v>10401534</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+        <v>11.02</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>SMS Pharmaceuticals Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Here's Why We Think SMS Pharmaceuticals (NSE:SMSPHARMA) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>SMS Pharmaceuticals Share Price Rise: Sector and Peer View - Univest</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SMS Pharmaceuticals Share Price: Fresh 52-Week High Update - Univest</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Here's Why We Think SMS Pharmaceuticals (NSE:SMSPHARMA) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1043,48 +1219,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE.NS</t>
+          <t>DHOOTTRANS.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited</t>
+          <t>Dhoot Transmission Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>431</v>
+        <v>1552</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>511.7999877929688</v>
+        <v>1728.699951171875</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>428.2000122070312</v>
+        <v>1531.5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>478.5</v>
+        <v>1728.699951171875</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>435.7999877929688</v>
+        <v>1571.599975585938</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>478.5</v>
+        <v>1728.699951171875</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>10360670</v>
+        <v>5862704</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>DHOOT TRANSMISSION LTD Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>DHOOT TRANSMISSION LTD Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>5,271,308 Equity Shares of Dhoot Transmission Limited are subject to a Lock-Up Agreement Ending on 11-SEP-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1092,48 +1288,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>MONEYBOXX.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>Moneyboxx Finance Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>49.9900016784668</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>58.9900016784668</v>
+        <v>40.86000061035156</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>48.4900016784668</v>
+        <v>36</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>54.29999923706055</v>
+        <v>40.86000061035156</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>49.91999816894531</v>
+        <v>37.15000152587891</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>54.29999923706055</v>
+        <v>40.86000061035156</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>11274239</v>
+        <v>182568</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+        <v>9.99</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance Ltd Locks at Lower Circuit With 20.0% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1141,48 +1357,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ELANTAS.NS</t>
+          <t>ANMOL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Elantas Beck India Limited</t>
+          <t>Anmol India Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13397</v>
+        <v>15</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>14769</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>13162</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>14513</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13397</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14513</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>23980</v>
+        <v>1521669</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>ANMOL INDIA LIMITED Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Above All Moving Averages and Now at Upper Circuit: Anmol India Ltd Gains 9.0% in a Single Session - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Above All Moving Averages and Now at Upper Circuit: Anmol India Ltd Gains 9.0% in a Single Session - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1190,48 +1426,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>MOBIKWIK.NS</t>
+          <t>QUADFUTURE.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>One Mobikwik Systems Limited</t>
+          <t>Quadrant Future Tek Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>194.4199981689453</v>
+        <v>431</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>220.2200012207031</v>
+        <v>511.7999877929688</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>193.2100067138672</v>
+        <v>428.2000122070312</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>209.6999969482422</v>
+        <v>478.5</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>194.6799926757812</v>
+        <v>435.7999877929688</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>209.6999969482422</v>
+        <v>478.5</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>18103148</v>
+        <v>10362562</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>QUADRANT FUTURE TEK LTD Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>QUADRANT FUTURE TEK LTD Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1239,48 +1491,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BBOX.NS</t>
+          <t>PRIMO.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Black Box Limited</t>
+          <t>Primo Chemicals Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>741</v>
+        <v>21.43000030517578</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>808.4000244140625</v>
+        <v>24.67000007629395</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>740</v>
+        <v>21.43000030517578</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>800.7999877929688</v>
+        <v>23.70999908447266</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>744.8499755859375</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>800.7999877929688</v>
+        <v>23.70999908447266</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1663663</v>
+        <v>1605579</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+        <v>9.26</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Primo Chemicals Share Price rises 11.03% on market update - Univest</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>David Einhorn Bets on Bottled Water, Another Hedge Fund Manager Says ‘Solid Financial Picture’ For Stock - TradingView</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>David Einhorn Bets on Bottled Water, Another Hedge Fund Manager Says ‘Solid Financial Picture’ For Stock - TradingView</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Primo Chemicals (PRIMO.NS) Climbs 2.31% to ₹21.28; Resistance at ₹22.34 in Focus - SMA Signal - siam.in</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Primo Brands: Strong Q2 Confirms Bullish Thesis (NYSE:PRMB) - Seeking Alpha</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1288,48 +1560,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>PWL.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Physicswallah Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>125.5</v>
+        <v>49.9900016784668</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>137.1199951171875</v>
+        <v>58.9900016784668</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>125.370002746582</v>
+        <v>48.4900016784668</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>136.1000061035156</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>126.7300033569336</v>
+        <v>49.91999816894531</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>136.1000061035156</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>41158432</v>
+        <v>11275075</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+        <v>8.77</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>UGARSUGAR Share Price | Ugar Sugar Works Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>UGARSUGAR Share Price | Ugar Sugar Works Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Ugar (UGARSUGAR.NS) Earnings Update: The Report Provides a New Financial Snapshot in the Reported Period; Trading Response: Shares Finish 4.05% Down in the Latest Reading - Financial Data - siam.in</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1337,40 +1629,48 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK.NS</t>
+          <t>PWL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK LIMITED</t>
+          <t>Physicswallah Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>575</v>
+        <v>125.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>634.4000244140625</v>
+        <v>137.1199951171875</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>575</v>
+        <v>125.370002746582</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>628.1500244140625</v>
+        <v>136.1000061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>585.9000244140625</v>
+        <v>126.7300033569336</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>628.1500244140625</v>
+        <v>136.1000061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4432007</v>
+        <v>41161986</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+        <v>7.39</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Earnings Update: Physicswallah Limited (NSE:PWL) Just Reported Its First-Quarter Results And Analysts Are Updating Their Forecasts - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Earnings Update: Physicswallah Limited (NSE:PWL) Just Reported Its First-Quarter Results And Analysts Are Updating Their Forecasts - simplywall.st</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -1378,7 +1678,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1386,48 +1686,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSIND.NS</t>
+          <t>AIIL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Kirloskar Industries Limited</t>
+          <t>Authum Investment &amp; Infrastructure Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3575</v>
+        <v>508</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4055</v>
+        <v>558</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>3562.300048828125</v>
+        <v>503</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>3828.300048828125</v>
+        <v>544.3499755859375</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3576.800048828125</v>
+        <v>512.2999877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3828.300048828125</v>
+        <v>544.3499755859375</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>639315</v>
+        <v>5994616</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+        <v>6.26</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>AIIL Share Price Today: price rise, fundamentals and sector - Univest</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>AIIL Share Price Today: price rise, fundamentals and sector - Univest</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Authum Investment Share Price Decline and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Authum Investment &amp; Infrastructure Share Price rises 4.95% - Univest</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Authum Investment Invests ₹101.6 Cr in ISARC Rights Issue - investywise.com</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1435,48 +1755,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>TEXMOPIPES.NS</t>
+          <t>RRECL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Texmo Pipes and Products Limited</t>
+          <t>RDB Real Estate Constructions Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>56.25</v>
+        <v>126</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>62.9900016784668</v>
+        <v>138.6000061035156</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>55.5</v>
+        <v>125.5800018310547</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.08000183105469</v>
+        <v>133.8000030517578</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>56.43999862670898</v>
+        <v>126</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>60.08000183105469</v>
+        <v>133.8000030517578</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1131516</v>
+        <v>883</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+        <v>6.19</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>RRECL Stock Price and Chart — NSE:RRECL - TradingView</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>RDB Real Estate Constructions Share Price Today Down 9.14% - Univest</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>RDB Real Estate Constructions Ltd. (RRECL) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1484,43 +1824,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RRECL.NS</t>
+          <t>TANAA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions Limited</t>
+          <t>Taneja Aerospace &amp; Aviation Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>126</v>
+        <v>246.5500030517578</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>138.6000061035156</v>
+        <v>269.8500061035156</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>125.5800018310547</v>
+        <v>238</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>133.8000030517578</v>
+        <v>266.9500122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>126</v>
+        <v>251.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>133.8000030517578</v>
+        <v>266.9500122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>883</v>
+        <v>50644</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+        <v>6.14</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>TANAA Stock Price and Chart — NSE:TANAA - TradingView</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Taneja Aerospace &amp; Aviation Ltd. (TANAA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis of Taneja Aerospace &amp; Aviation Ltd. (NSE:TANAA) - TradingView</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1539,20 +1899,20 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1645,7 +2005,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1653,48 +2013,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SRGHFL.NS</t>
+          <t>SUNSHINE.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Limited</t>
+          <t>Sunshine Pictures Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>156</v>
+        <v>512.4000244140625</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>156</v>
+        <v>524.9500122070312</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>156</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>156</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>195</v>
+        <v>509.7000122070312</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>156</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>11736</v>
+        <v>3900142</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-20</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+        <v>-19.99</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>SUNSHINE PICTURES LIMITED Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sunshine Metals (ASX:SHN) in Focus: Could This ASX Resources Stock Be One to Watch in September 2026? - Kalkine</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>SUNSHINE Share Price Today - SUNSHINE PICTURES LIMITED Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Sunshine Metals (ASX:SHN) in Focus: Could This ASX Resources Stock Be One to Watch in September 2026? - Kalkine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -1702,48 +2082,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SREEL.NS</t>
+          <t>CSM.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Limited</t>
+          <t>CSM Technologies Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>365</v>
+        <v>101.1500015258789</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>365.7999877929688</v>
+        <v>101.1500015258789</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>333.2699890136719</v>
+        <v>76.26000213623047</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>333.2699890136719</v>
+        <v>83.44000244140625</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>370.2999877929688</v>
+        <v>94.95999908447266</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>333.2699890136719</v>
+        <v>83.44000244140625</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>129115</v>
+        <v>2772772</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+        <v>-12.13</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>CSM TECHNOLOGIES LIMITED Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>CSM Share Price Today Falls: P/E, P/B and Sector Context - Univest</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Understanding Momentum Shifts in (CSM) - Stock Traders Daily</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1751,48 +2151,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MEDICAPQ.NS</t>
+          <t>KOTIC.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Medi Caps Limited</t>
+          <t>Kothari Industrial Corporation Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34.59000015258789</v>
+        <v>148.7599945068359</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>36.20000076293945</v>
+        <v>148.7599945068359</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>31.70000076293945</v>
+        <v>130.5500030517578</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>31.70000076293945</v>
+        <v>133.8200073242188</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>35.22000122070312</v>
+        <v>151.2100067138672</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>31.70000076293945</v>
+        <v>133.8200073242188</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>64727</v>
+        <v>122378</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.99</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+        <v>-11.5</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What's fuelling the rally? - TradingView</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Kothari Industrial Share Price Today: Fundamental Check - Univest</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Kothari Industrial Corporation (KOTIC.NS) Slips 1.23% to ₹134.79; Support at ₹128.05 in Focus - Bullish Sentiment - siam.in</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Kothari Industrial Corporation Share Price rises 10.14% - Univest</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Kothari Industrial Share Price Today: Fundamental Check - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1800,48 +2220,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CSLFINANCE.NS</t>
+          <t>SREEL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>CSL Finance Limited</t>
+          <t>Sreeleathers Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>234.5399932861328</v>
+        <v>365</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>234.5399932861328</v>
+        <v>365.7999877929688</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>217.1199951171875</v>
+        <v>333.2699890136719</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>220.9799957275391</v>
+        <v>333.2699890136719</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>241.0399932861328</v>
+        <v>370.2999877929688</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>220.9799957275391</v>
+        <v>333.2699890136719</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>149274</v>
+        <v>129115</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-8.32</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+        <v>-10</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Sreeleathers Share Price Fall: Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sreeleathers Daily Chart Outlook - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Sreeleathers Daily Chart Outlook - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Sreeleathers Limited Declares Interim Dividend of ₹1 Per Share for FY 2025-26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Sreeleathers Share Price rises 20%: price, fundamentals - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1849,48 +2289,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>THAKDEV.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Limited</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>130.6499938964844</v>
+        <v>13.75</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>139.8000030517578</v>
+        <v>13.75</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>125.3499984741211</v>
+        <v>13.75</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>128.1499938964844</v>
+        <v>13.75</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>138.9900054931641</v>
+        <v>15.27000045776367</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>128.1499938964844</v>
+        <v>13.75</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>660</v>
+        <v>370055</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Share Price update: price action and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Atal Realtech 20.00% Fall: Chart Analysis - Kalkine India</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1898,48 +2358,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SSDL.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Limited</t>
+          <t>Cochin Shipyard Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>71</v>
+        <v>1510</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>72.69999694824219</v>
+        <v>1510</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61.36999893188477</v>
+        <v>1372</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.59000015258789</v>
+        <v>1381</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>67.83999633789062</v>
+        <v>1520.400024414062</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62.59000015258789</v>
+        <v>1381</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>557556</v>
+        <v>6390480</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-7.74</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+        <v>-9.17</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard Ltd (COCHINSHIP) Share Price - Business Today</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard Seals BRICS-Stage Joint Venture With Drydocks World Dubai - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard Seals BRICS-Stage Joint Venture With Drydocks World Dubai - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard Share Price Today, August 24, 2026: COCHINSHIP Closes at ₹1,514 on NSE - The Eastern Herald</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Cochin Shipyard shares crash nearly 9% - Is it opportunity to buy? Should you take fresh entry? Expert suggests this - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1947,48 +2427,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>IOLCP.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>IOL Chemicals and Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>195</v>
+        <v>210.5099945068359</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>195</v>
+        <v>210.9499969482422</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>176.5</v>
+        <v>192</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>180.6900024414062</v>
+        <v>194.3099975585938</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>195.25</v>
+        <v>211.4299926757812</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>180.6900024414062</v>
+        <v>194.3099975585938</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>7308</v>
+        <v>5129124</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.46</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+        <v>-8.1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>IOL Chemicals and Pharmaceuticals Share Price - Live NSE: IOLCP Stock Price &amp; Chart - upstox.com</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>IOL Chemicals And Pharmaceuticals (IOLCP) Share Price Falls 8.19% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>IOLCP Share Price today near 52-week high, price action - Univest</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>IOL Chemicals (IOLCP.NS) Holds Steady Near ₹194 as Pharma-Chemical Play Consolidates - MFI Overbought - siam.in</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>IOL Chemicals Share Price Today after fresh 52-week high - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1996,48 +2496,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>AARON.NS</t>
+          <t>SSDL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Aaron Industries Limited</t>
+          <t>Saraswati Saree Depot Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>137</v>
+        <v>72.69999694824219</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>121.1600036621094</v>
+        <v>61.36999893188477</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>126.9400024414062</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>136.9499969482422</v>
+        <v>67.83999633789062</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>126.9400024414062</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>34703</v>
+        <v>560099</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-7.31</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+        <v>-7.74</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Saraswati Saree Depot SSDL Fresh High Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Saraswati Saree Depot SSDL Fresh High Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Saraswati Saree Depot Jun 2026 Earnings: Revenue at ₹147.59 crore and EPS of ₹1.67 as Stock Slips 4.7% - siam.in</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Saraswati Saree Depot Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Saraswati Saree Depot Share Price today: price action view - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2045,48 +2565,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE.NS</t>
+          <t>ARVEE.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
+          <t>Arvee Laboratories (India) Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>72.41000366210938</v>
+        <v>195</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>73.80000305175781</v>
+        <v>195</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>68.19999694824219</v>
+        <v>176.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>69.33000183105469</v>
+        <v>180.6900024414062</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>74.76999664306641</v>
+        <v>195.25</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>69.33000183105469</v>
+        <v>180.6900024414062</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1319873</v>
+        <v>7318</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-7.28</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+        <v>-7.46</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Arvee Laboratories (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Volume Gainers on September 8, 2026 at 4:00 PM - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Arvee (ARVEE.NS) Outlook: Ends Lower by 1.98% at ₹165.00; Technical View: ₹156.75 and ₹173.25 Define the Nearby Reference Levels in Latest Trading - OBV Divergence - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2094,48 +2634,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>KENNAMET.NS</t>
+          <t>SUVIDHAA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Kennametal India Limited</t>
+          <t>Suvidhaa Infoserve Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5000</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5000</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4660</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>4682.39990234375</v>
+        <v>2.25</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5027.89990234375</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4682.39990234375</v>
+        <v>2.25</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>70321</v>
+        <v>184883</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-6.87</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
+        <v>-6.64</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Suvidhaa (SUVIDHAA.NS) Earnings Snapshot: The Company Reports Its Latest Available Figures in the Latest Reading; Market Reaction: The Stock Records a 1.26% Increase on the Day - Guidance Update - siam.in</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Suvidhaa Infoserve Sets September 30 Virtual AGM, Closes Books for FY 2025-26 Decisions - TipRanks</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Suvidhaa Infoserve Sets September 30 Virtual AGM, Closes Books for FY 2025-26 Decisions - TipRanks</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2143,48 +2695,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SUVIDHAA.NS</t>
+          <t>AVROIND.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve Limited</t>
+          <t>AVRO INDIA LIMITED</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.470000028610229</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2.470000028610229</v>
+        <v>8.430000305175781</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2.190000057220459</v>
+        <v>7.71999979019165</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.25</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2.410000085830688</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.25</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>184883</v>
+        <v>891730</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+        <v>-6.35</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Avro India Share Price - Live NSE: AVROIND Stock Price &amp; Chart - upstox.com</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Avro India Share Price - Live NSE: AVROIND Stock Price &amp; Chart - upstox.com</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>AVRO India Slips 2.9% to ₹9.03: Support Zone in Focus - Investment Factor - siam.in</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Avro India Ltd. Share Price Today Falls; Valuation View - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2192,48 +2764,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GODREJPROP.NS</t>
+          <t>BIOFILCHEM.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Godrej Properties Limited</t>
+          <t>Biofil Chemicals &amp; Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1855</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1855</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1719</v>
+        <v>32.36000061035156</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1748</v>
+        <v>34.5099983215332</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1872</v>
+        <v>36.79000091552734</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1748</v>
+        <v>34.5099983215332</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2683753</v>
+        <v>173376</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.62</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
+        <v>-6.2</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Biofil (BIOFILCHEM.NS) Technicals: Moves 0.87% Lower to ₹32.06 at the Close; Next Test: the ₹30.46 to ₹33.66 Range Remains in Focus in Latest Trading - Fibonacci Time Zone - siam.in</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2241,48 +2825,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PODDARMENT.NS</t>
+          <t>GOACARBON.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Poddar Pigments Limited</t>
+          <t>Goa Carbon Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>295.1000061035156</v>
+        <v>434.7000122070312</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>298.9500122070312</v>
+        <v>457</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>275.0499877929688</v>
+        <v>408.9500122070312</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>279.8500061035156</v>
+        <v>413.3999938964844</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>299.3999938964844</v>
+        <v>440.25</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>279.8500061035156</v>
+        <v>413.3999938964844</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>12804</v>
+        <v>164355</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-6.53</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+        <v>-6.1</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Goa (GOACARBON.NS) Price: Finishes 0.67% Up at ₹359.85 at the Close; the Supplied Trading Band Runs From ₹341.86 to ₹377.84 - Range Breakout - siam.in</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Goa Carbon 20% Move: Key Chart Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Goa (GOACARBON.NS) Financial Results: The Company Publishes Its Latest Results under the Current Snapshot; Market Response: The Stock Gains 1.63% in the Latest Reading - Earnings Recovery Stocks - siam.in</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Goa Carbon 20% Move: Key Chart Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Goa Carbon Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2290,48 +2894,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>AVROIND.NS</t>
+          <t>CREATIVEYE.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>AVRO INDIA LIMITED</t>
+          <t>Creative Eye Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8.399999618530273</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>8.430000305175781</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>7.71999979019165</v>
+        <v>5.260000228881836</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>7.809999942779541</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8.340000152587891</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.809999942779541</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>890191</v>
+        <v>81227</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-6.35</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
+        <v>-5.77</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Creative (CREATIVEYE.NS) Results Versus Estimates: The Latest Report Adds New Financial Reference Points under the Current Snapshot; Price Reaction: The Stock Loses 0.81% at the Close - Balance Sheet Strength - siam.in</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Creative (CREATIVEYE.NS) Range: Retreats 0.81% to ₹6.15 in Latest Trading; Range Check: Traders Can Monitor the ₹5.84-₹6.46 Range in the Latest Reading - BPI Bull Correction - siam.in</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Creative (CREATIVEYE.NS) Range: Retreats 0.81% to ₹6.15 in Latest Trading; Range Check: Traders Can Monitor the ₹5.84-₹6.46 Range in the Latest Reading - BPI Bull Correction - siam.in</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Martin (MMLP) Latest: Closes Nearly Flat at $2.33 in the Available Record; Range Check: the Price Remains Bounded by the Supplied Support and Resistance on the Day - Rectangle Pattern - vinanet.vn</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2339,48 +2959,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CREATIVEYE.NS</t>
+          <t>MVGJL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Creative Eye Limited</t>
+          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5.989999771118164</v>
+        <v>208.6999969482422</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>5.989999771118164</v>
+        <v>208.6999969482422</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5.260000228881836</v>
+        <v>195.6000061035156</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>5.71999979019165</v>
+        <v>197.3699951171875</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6.070000171661377</v>
+        <v>208.7799987792969</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.71999979019165</v>
+        <v>197.3699951171875</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>81217</v>
+        <v>332881</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.77</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+        <v>-5.47</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>MANOJ VAIBHAV GEM N JEW L Share Price - Live NSE: MVGJL Stock Price &amp; Chart - upstox.com</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - TradingView</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Here's Why Manoj Vaibhav Gems 'N' Jewellers (NSE:MVGJL) Has Caught The Eye Of Investors - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Manoj Vaibhav Gems (MVGJL.NS) Gains 4.6% to ₹179.9: Jewelry Stock Rebounds Toward Key Resistance - Bollinger Squeeze - siam.in</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Manoj (MVGJL.NS) Financial Update: The Company Lists Its Latest Available Figures in the Current Update; Shares Move 1.33% Up in the Latest Reading - Surprise Factor Analysis - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2388,48 +3028,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>HEIDELBERG.NS</t>
+          <t>SVGLOBAL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>HeidelbergCement India Limited</t>
+          <t>S V Global Mill Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>150.9499969482422</v>
+        <v>140.6900024414062</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>150.9499969482422</v>
+        <v>140.6900024414062</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>147.8000030517578</v>
+        <v>126.5500030517578</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>149.8000030517578</v>
+        <v>133.3500061035156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>158.7899932861328</v>
+        <v>140.8000030517578</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>149.8000030517578</v>
+        <v>133.3500061035156</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>313598</v>
+        <v>1859</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.66</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+        <v>-5.29</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Fall and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>S V Global Mill Ltd (SVGLOBAL) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price falls 10.07% | Price analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2437,48 +3097,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>REGENCERAM.NS</t>
+          <t>SECMARK.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Regency Ceramics Limited</t>
+          <t>SecMark Consultancy Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>34.65999984741211</v>
+        <v>148</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>37.5</v>
+        <v>148</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>33.20000076293945</v>
+        <v>138</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>34.09999847412109</v>
+        <v>141.3099975585938</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.04999923706055</v>
+        <v>149.1600036621094</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>34.09999847412109</v>
+        <v>141.3099975585938</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4604</v>
+        <v>2320</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+        <v>-5.26</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Secmark Consultancy Share Price rises 8.39% today - Univest</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Secmark Consultancy Share Price rises 8.39% today - Univest</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>SecMark Consultancy schedules 15th AGM for September 30, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Secmark Consultancy Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Secmark Consultancy Share Price news: Rs 137 and valuation - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2486,48 +3166,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER.NS</t>
+          <t>GUJENERGY.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Skipper Limited</t>
+          <t>GUJARAT ENERGY LIMITED</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>581</v>
+        <v>247.9400024414062</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>581</v>
+        <v>249.2100067138672</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>541.3499755859375</v>
+        <v>240.3600006103516</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>551.5499877929688</v>
+        <v>241.5899963378906</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>583</v>
+        <v>254.8000030517578</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>551.5499877929688</v>
+        <v>241.5899963378906</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2162749</v>
+        <v>1808646</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.39</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+        <v>-5.18</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Energy (NSE:GUJENERGY) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Energy Limited Appoints Dhirubhai Shah &amp; Co. LLP as Statutory Auditors - psuconnect.in</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Gas Share Price Up 2.36%: Price, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Gas Share Price falls to yearly low | Price action - Univest</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Gas Ltd. Share Price Today: 3.43% Fall Analyzed - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2535,48 +3235,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SECMARK.NS</t>
+          <t>GYFTR.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>SecMark Consultancy Limited</t>
+          <t>Gyftr Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>141.3099975585938</v>
+        <v>175.7299957275391</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>149.1600036621094</v>
+        <v>185.3200073242188</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>141.3099975585938</v>
+        <v>175.7299957275391</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2320</v>
+        <v>47421</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.26</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+        <v>-5.17</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>LKP Finance Limited Announces Postal Ballot Results with 99.49% Shareholder Approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>LKP Finance Limited Announces Postal Ballot Results with 99.49% Shareholder Approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Gyftr schedules 42nd AGM for September 29, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Gyftr: कंपनी ने कमाए **₹21.8 करोड़**, क्या है 29 सितंबर की एजीएम (AGM) का एजेंडा? - Whalesbook</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>PNB Partners With GYFTR For Credit Card Offers, Customers To Get Shopping, Food And Travel Benefits - freepressjournal.in</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:12:10 IST</t>
+          <t>2026-09-14 13:30:20 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2584,43 +3304,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>MYSORPETRO.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>Mysore Petro Chemicals Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>43.40000152587891</v>
+        <v>147.7799987792969</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45.4900016784668</v>
+        <v>147.7799987792969</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>41.16999816894531</v>
+        <v>141.1000061035156</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>41.16999816894531</v>
+        <v>141.1000061035156</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43.43000030517578</v>
+        <v>148.5200042724609</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>41.16999816894531</v>
+        <v>141.1000061035156</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>20199028</v>
+        <v>3988</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Ltd. (MYSORPETRO) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals: Denies Undisclosed Material Events Amidst Share Price Movement - investywise.com</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>OPTIFIN Stock Price and Chart — NSE:OPTIFIN - TradingView</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Ltd. (MYSORPETRO) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>MYSORPETRO.NSE - Stocktwits</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,60 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>LADDERUP.NS</t>
+          <t>ASHOKAMET.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Limited</t>
+          <t>Ashoka Metcast Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>73</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>74.30999755859375</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>73</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>74.30999755859375</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>61.93000030517578</v>
+        <v>14.34000015258789</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>74.30999755859375</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>59231</v>
+        <v>1455188</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.99</v>
+        <v>19.94</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Ltd. Upper Circuit Streak: Day 2 Price and Data - Univest</t>
+          <t>Here's Why We Think Ashoka Metcast (NSE:ASHOKAMET) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Here's Why We Think Ashoka Metcast (NSE:ASHOKAMET) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Ashoka Metcast Ltd leads gainers in 'B' group - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Total common shares outstanding of Ladderup Finance Limited – NSE:LADDERUP - TradingView</t>
-        </is>
-      </c>
+          <t>Ashoka Metcast sells 2.48M Mena Mani Industries shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +614,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>STLSTRINF.NS</t>
+          <t>AWFIS.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Steel Strips Infrastructures Limited</t>
+          <t>Awfis Space Solutions Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.19000053405762</v>
+        <v>248.5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>21.20000076293945</v>
+        <v>299.4500122070312</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>18.70000076293945</v>
+        <v>244.1000061035156</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>21.20000076293945</v>
+        <v>293.2000122070312</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>17.67000007629395</v>
+        <v>249.6000061035156</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21.20000076293945</v>
+        <v>293.2000122070312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>12925</v>
+        <v>23945553</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.98</v>
+        <v>17.47</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>STLSTRINF Stock Price and Chart — NSE:STLSTRINF - TradingView</t>
+          <t>Awfis Space Solutions share price jumps nearly 20% despite weak Sensex, Nifty 50; what should investors do now? - Livemint</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Steel Strips Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>AWFIS Space Solutions Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>AWFIS Space Solutions Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Steel Strips Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Awfis Space Solutions Share Price: Buy or Sell - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Fundamental and Financial Data - Stocktwits</t>
+          <t>₹524: That's What Analysts Think Awfis Space Solutions Limited (NSE:AWFIS) Is Worth After Its Latest Results - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,60 +683,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ASHOKAMET.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast Limited</t>
+          <t>Pine Labs Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14.53999996185303</v>
+        <v>171</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17.20000076293945</v>
+        <v>206.3800048828125</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>170.9600067138672</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>17.20000076293945</v>
+        <v>202.1699981689453</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14.34000015258789</v>
+        <v>173.1699981689453</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.20000076293945</v>
+        <v>202.1699981689453</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1455188</v>
+        <v>276696049</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>19.94</v>
+        <v>16.75</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Ashoka Metcast (NSE:ASHOKAMET) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>PINELABS Stock Price and Chart — NSE:PINELABS - TradingView</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Ashoka Metcast (NSE:ASHOKAMET) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>PINELABS Stock Price and Chart — NSE:PINELABS - TradingView</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast sells 2.48M Mena Mani Industries shares in open market - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Pine Labs share price jumps 13%: Fintech stock rises sharply as trading volume explodes - Livemint</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Pine Labs Share Price Today Up 2.43%: Fundamental Check - Univest</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Pine (PINELABS.NS) Chart: Loses 1.77% to Close at ₹156.91 for the Current Session; Market Levels: ₹149.06 and ₹164.76 Define the Nearby Reference Levels in Latest Trading - Sign of Strength - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +752,60 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AWFIS.NS</t>
+          <t>AMDIND.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Awfis Space Solutions Limited</t>
+          <t>AMD Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>248.5</v>
+        <v>56.31999969482422</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>299.4500122070312</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>244.1000061035156</v>
+        <v>55.5099983215332</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>293.2000122070312</v>
+        <v>64.02999877929688</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>249.6000061035156</v>
+        <v>56.04000091552734</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>293.2000122070312</v>
+        <v>64.02999877929688</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>23945553</v>
+        <v>484603</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>17.47</v>
+        <v>14.26</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Awfis Space Solutions share price jumps nearly 20% despite weak Sensex, Nifty 50; what should investors do now? - Livemint</t>
+          <t>AMD Industries Stock: Momentum Above 50-Day SMA - Kalkine India</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>AWFIS Space Solutions Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
+          <t>AMD Industries Stock: Momentum Above 50-Day SMA - Kalkine India</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>AWFIS Space Solutions Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Awfis Space Solutions Share Price: Buy or Sell - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>₹524: That's What Analysts Think Awfis Space Solutions Limited (NSE:AWFIS) Is Worth After Its Latest Results - simplywall.st</t>
-        </is>
-      </c>
+          <t>AMD Industries Share Price rises 12.01%: valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,68 +813,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND.NS</t>
+          <t>AHCL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Raymond Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>853.8499755859375</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1024.5</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>835.0499877929688</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1002.799987792969</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>853.8499755859375</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1002.799987792969</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>16245056</v>
+        <v>150749037</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>17.44</v>
+        <v>11.57</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Raymond shares to remain in focus as aerospace arm wins orders - Moneycontrol.com</t>
+          <t>AHCL Stock Price and Chart — NSE:AHCL - TradingView</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Raymond shares to remain in focus as aerospace arm wins orders - Moneycontrol.com</t>
+          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Raymond shares jump 20% to hit all-time high after three days of consecutive gains; further growth tailwinds ahead? - upstox.com</t>
+          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Raymond surges 20% on huge volume; here's why stock rose 66% in 11 days - Business Standard</t>
+          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Small-cap multibagger stock: 135% return in YTD | Defence subsidiary wins ₹33 crore aerospace order - Livemint</t>
+          <t>AHCL.NS Q2 2026 Earnings: Revenue Jumps 42.96% YoY to ₹171.97 Cr, Stock Slips 2.33% - Earnings Momentum Score - siam.in</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -890,68 +882,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>FILATEX.NS</t>
+          <t>TRACXN.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Limited</t>
+          <t>Tracxn Technologies Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>76</v>
+        <v>28.59000015258789</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>90.90000152587891</v>
+        <v>32.38999938964844</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>74.26999664306641</v>
+        <v>28.43000030517578</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>87.41000366210938</v>
+        <v>31.89999961853027</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>76.25</v>
+        <v>28.61000061035156</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>87.41000366210938</v>
+        <v>31.89999961853027</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>38898608</v>
+        <v>1039887</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>14.64</v>
+        <v>11.5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Filatex India Limited (NSE:FILATEX) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Tracxn Technologies Share Price today: key stock update - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions publishes 32nd AGM notice in newspapers - scanx.trade</t>
+          <t>Tracxn Technologies Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Share Price: price action and fundamentals - Univest</t>
+          <t>Tracxn narrows FY26 loss, eyes FY27 growth with AI - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions publishes 32nd AGM notice in newspapers - scanx.trade</t>
+          <t>Tracxn Technologies Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Tracxn (TRACXN.NS) Watch: Rises 0.64% to ₹29.76 for the Current Session; Technical Setup: Traders Can Monitor the ₹28.27-₹31.25 Range in the Available Record - Growth ETF - siam.in</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -959,56 +951,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AMDIND.NS</t>
+          <t>DIGJAMLMTD.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Limited</t>
+          <t>Digjam Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>56.31999969482422</v>
+        <v>64.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>65.19999694824219</v>
+        <v>73.19000244140625</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>55.5099983215332</v>
+        <v>61.84000015258789</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>64.02999877929688</v>
+        <v>68.41999816894531</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>56.04000091552734</v>
+        <v>61.84000015258789</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>64.02999877929688</v>
+        <v>68.41999816894531</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>484603</v>
+        <v>1282661</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>14.26</v>
+        <v>10.64</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Share Price rises 12.01%: valuation view - Univest</t>
+          <t>Digjam Share Price rises 14.59%: price action - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Share Price rises 12.01%: valuation view - Univest</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Digjam Share Price rises 14.59%: price action - Univest</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Digjam Ltd Gains 2.11% to ₹51.73: Textile Stock Holds Above Key Support - Turnaround Stocks - siam.in</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Digjam (DIGJAMLMTD.NS) Stock: Retreats 0.27% to ₹51.50; the Supplied Trading Band Runs From ₹48.92 to ₹54.08 - Sector ETF Flow - siam.in</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Digjam Limited: స్కీమ్ ఆఫ్ అరేంజ్మెంట్‌పై NCLT కీలక ఆదేశాలు.. అక్టోబర్ 28న తదుపరి విచారణ - Whalesbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1016,68 +1020,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SHERVANI.NS</t>
+          <t>HLEGLAS.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate Limited</t>
+          <t>HLE Glascoat Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>326</v>
+        <v>367.8500061035156</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>360</v>
+        <v>404.3500061035156</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>309</v>
+        <v>363</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>348.8500061035156</v>
+        <v>404.3500061035156</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>311</v>
+        <v>367.6000061035156</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>348.8500061035156</v>
+        <v>404.3500061035156</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3811</v>
+        <v>870661</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>12.17</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>HLE Glascoat Share Price rise: price action and P/E view - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate FY26 Results - investywise.com</t>
+          <t>HLE Glascoat promoter Nilesh Patel gifts 10% stake to son Aalap - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial sets Sep 18 record date for FY26 dividend - scanx.trade</t>
+          <t>HLE (HLEGLAS.NS) Latest Quarter: The Company Releases Its Current Earnings Data in the Latest Reading; Share Move: Shares Fall 0.28% at the Close - Margin Expansion Trends - siam.in</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>HLE (HLEGLAS.NS) EPS and Revenue: The Latest Financial Metrics Are Now Available in the Reported Period; Market Reaction: The Stock Records a 1.74% Decrease in the Latest Reading - Consensus Forecast Report - siam.in</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Shervani Industrial Syndicate Ltd. (SHERVANI) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
+          <t>HLE Glascoat Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1085,64 +1089,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AHCL.NS</t>
+          <t>ANMOL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Limited</t>
+          <t>Anmol India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17.72999954223633</v>
+        <v>15</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>20</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>17.54000091552734</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17.54000091552734</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>150749037</v>
+        <v>1521669</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>11.57</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>AHCL Stock Price and Chart — NSE:AHCL - TradingView</t>
+          <t>ANMOL INDIA LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>ANLON HEALTHCARE LIMITED Share Price - upstox.com</t>
+          <t>Above All Moving Averages and Now at Upper Circuit: Anmol India Ltd Gains 9.0% in a Single Session - MarketsMojo</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ANLON HEALTHCARE LIMITED Share Price - upstox.com</t>
+          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Above All Moving Averages and Now at Upper Circuit: Anmol India Ltd Gains 9.0% in a Single Session - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1150,68 +1158,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SMSPHARMA.NS</t>
+          <t>DAVANGERE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>SMS Pharmaceuticals Limited</t>
+          <t>Davangere Sugar Company Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>417.8500061035156</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>469</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>414.5499877929688</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>463.4500122070312</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>417.4500122070312</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>463.4500122070312</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>10401534</v>
+        <v>36081250</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>11.02</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SMS Pharmaceuticals Share Price - upstox.com</t>
+          <t>Davangere Sugar FY26 net profit falls to ₹850.66 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think SMS Pharmaceuticals (NSE:SMSPHARMA) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Davangere Sugar schedules 55th AGM for September 12, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>SMS Pharmaceuticals Share Price Rise: Sector and Peer View - Univest</t>
+          <t>Sugar stock under ₹10 jumps 6% despite sideways trend in Indian stock market | Here's why - Livemint</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>SMS Pharmaceuticals Share Price: Fresh 52-Week High Update - Univest</t>
+          <t>Davangere Sugar Share Price Today: Price Rise and Valuation - Univest</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think SMS Pharmaceuticals (NSE:SMSPHARMA) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Davangere Sugar Slips 1.5% to ₹1.93, Holds Above Key Support (DAVANGERE.NS) - Ichimoku TK Cross - siam.in</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1219,68 +1227,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DHOOTTRANS.NS</t>
+          <t>QUADFUTURE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Limited</t>
+          <t>Quadrant Future Tek Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1552</v>
+        <v>431</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1728.699951171875</v>
+        <v>511.7999877929688</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1531.5</v>
+        <v>428.2000122070312</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1728.699951171875</v>
+        <v>478.5</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1571.599975585938</v>
+        <v>435.7999877929688</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1728.699951171875</v>
+        <v>478.5</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>5862704</v>
+        <v>10362562</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>DHOOT TRANSMISSION LTD Share Price - upstox.com</t>
+          <t>QUADRANT FUTURE TEK LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>DHOOT TRANSMISSION LTD Share Price - upstox.com</t>
+          <t>QUADRANT FUTURE TEK LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,271,308 Equity Shares of Dhoot Transmission Limited are subject to a Lock-Up Agreement Ending on 11-SEP-2026. - marketscreener.com</t>
+          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>DHOOTTRANS Share Price Today - DHOOT TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1288,68 +1292,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX.NS</t>
+          <t>NAGREEKCAP.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Limited</t>
+          <t>Nagreeka Capital &amp; Infrastructure Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>36</v>
+        <v>22.97999954223633</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>40.86000061035156</v>
+        <v>25.14999961853027</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>36</v>
+        <v>22.30999946594238</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>40.86000061035156</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37.15000152587891</v>
+        <v>22.8700008392334</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>40.86000061035156</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>182568</v>
+        <v>17663</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>9.99</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Nagreeka Capital &amp; Infrastructure (NAGREEKCAP.NS) Gains 1.86% – Key Levels to Watch - Price Target - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Nagreeka Capital &amp; Infrastructure Slips 1.84% to ₹22.38: Key Support and Resistance Levels in Focus - MFI Overbought - siam.in</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Investors Aren't Entirely Convinced By Nagreeka Capital &amp; Infrastructure Ltd.'s (NSE:NAGREEKCAP) Earnings - simplywall.st</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Nagreeka Capital &amp; Infrastructure Slips 1.84% to ₹22.38: Key Support and Resistance Levels in Focus - MFI Overbought - siam.in</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd Locks at Lower Circuit With 20.0% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo</t>
+          <t>Nagreeka Capital &amp; Infrastructure Limited (NAGREEKCAP.NS) Q2 2025 Earnings: Positive EPS in a Revenue Decline Quarter - Operating Margin Analysis - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1357,68 +1361,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ANMOL.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Anmol India Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15</v>
+        <v>49.9900016784668</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>58.9900016784668</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>48.4900016784668</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15.34000015258789</v>
+        <v>49.91999816894531</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1521669</v>
+        <v>11275075</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>ANMOL INDIA LIMITED Share Price - upstox.com</t>
+          <t>UGARSUGAR Share Price | Ugar Sugar Works Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Above All Moving Averages and Now at Upper Circuit: Anmol India Ltd Gains 9.0% in a Single Session - MarketsMojo</t>
+          <t>UGARSUGAR Share Price | Ugar Sugar Works Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Above All Moving Averages and Now at Upper Circuit: Anmol India Ltd Gains 9.0% in a Single Session - MarketsMojo</t>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+          <t>Ugar (UGARSUGAR.NS) Earnings Update: The Report Provides a New Financial Snapshot in the Reported Period; Trading Response: Shares Finish 4.05% Down in the Latest Reading - Financial Data - siam.in</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,64 +1430,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE.NS</t>
+          <t>BLACKBUCK.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited</t>
+          <t>BLACKBUCK LIMITED</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>431</v>
+        <v>575</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>511.7999877929688</v>
+        <v>634.4000244140625</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>428.2000122070312</v>
+        <v>575</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>478.5</v>
+        <v>628.1500244140625</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>435.7999877929688</v>
+        <v>585.9000244140625</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>478.5</v>
+        <v>628.1500244140625</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>10362562</v>
+        <v>4433382</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>7.21</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price - upstox.com</t>
+          <t>Sunil Singhania's Abakkus acquires 1.48% stake in BlackBuck; Jamna Auto promoters sell 5% shares - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price - upstox.com</t>
+          <t>Accel India Sells 1.48% BlackBuck Stake For Rs 155.5 Cr; Abakkus Snaps Up Shares - BW Disrupt</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
+          <t>BLACKBUCK LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Accel India Sells 1.48% BlackBuck Stake For Rs 155.5 Cr; Abakkus Snaps Up Shares - BW Disrupt</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>BLACKBUCK Share Price News: Fundamentals and Sector Gap - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1491,68 +1499,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PRIMO.NS</t>
+          <t>KIRLOSIND.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals Limited</t>
+          <t>Kirloskar Industries Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21.43000030517578</v>
+        <v>3575</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>24.67000007629395</v>
+        <v>4055</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>21.43000030517578</v>
+        <v>3562.300048828125</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>23.70999908447266</v>
+        <v>3828.300048828125</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.70000076293945</v>
+        <v>3576.800048828125</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>23.70999908447266</v>
+        <v>3828.300048828125</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1605579</v>
+        <v>639315</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.26</v>
+        <v>7.03</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals Share Price rises 11.03% on market update - Univest</t>
+          <t>KIRLOSIND Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>David Einhorn Bets on Bottled Water, Another Hedge Fund Manager Says ‘Solid Financial Picture’ For Stock - TradingView</t>
+          <t>Kirloskar Industries files FY26 BRSR with reduced energy use - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>David Einhorn Bets on Bottled Water, Another Hedge Fund Manager Says ‘Solid Financial Picture’ For Stock - TradingView</t>
+          <t>Kirloskar Industries Share Price rises 13.14%: analysis - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals (PRIMO.NS) Climbs 2.31% to ₹21.28; Resistance at ₹22.34 in Focus - SMA Signal - siam.in</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Primo Brands: Strong Q2 Confirms Bullish Thesis (NYSE:PRMB) - Seeking Alpha</t>
-        </is>
-      </c>
+          <t>Kirloskar Industries files FY26 BRSR with reduced energy use - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1560,68 +1564,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>TEXMOPIPES.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>Texmo Pipes and Products Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>49.9900016784668</v>
+        <v>56.25</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>58.9900016784668</v>
+        <v>62.9900016784668</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>48.4900016784668</v>
+        <v>55.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.29999923706055</v>
+        <v>60.08000183105469</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>49.91999816894531</v>
+        <v>56.43999862670898</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>54.29999923706055</v>
+        <v>60.08000183105469</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>11275075</v>
+        <v>1133568</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8.77</v>
+        <v>6.45</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price | Ugar Sugar Works Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>Texmo Pipes &amp; Products Ltd (TEXMOPIPES): Signals to Track - Kalkine India</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price | Ugar Sugar Works Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>Texmo Pipes Wins Strong Shareholder Backing for FY26 Accounts at 18th AGM - TipRanks</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+          <t>TEXMO PIPES Share Price - Upstox</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Ugar (UGARSUGAR.NS) Earnings Update: The Report Provides a New Financial Snapshot in the Reported Period; Trading Response: Shares Finish 4.05% Down in the Latest Reading - Financial Data - siam.in</t>
+          <t>Texmo Pipes Share Price rise: valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - Univest</t>
+          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1629,56 +1633,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PWL.NS</t>
+          <t>AIIL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Physicswallah Limited</t>
+          <t>Authum Investment &amp; Infrastructure Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>125.5</v>
+        <v>508</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>137.1199951171875</v>
+        <v>558</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>125.370002746582</v>
+        <v>503</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>136.1000061035156</v>
+        <v>544.3499755859375</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>126.7300033569336</v>
+        <v>512.2999877929688</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>136.1000061035156</v>
+        <v>544.3499755859375</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>41161986</v>
+        <v>5994616</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.39</v>
+        <v>6.26</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Earnings Update: Physicswallah Limited (NSE:PWL) Just Reported Its First-Quarter Results And Analysts Are Updating Their Forecasts - simplywall.st</t>
+          <t>AIIL Share Price Today: price rise, fundamentals and sector - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Earnings Update: Physicswallah Limited (NSE:PWL) Just Reported Its First-Quarter Results And Analysts Are Updating Their Forecasts - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>AIIL Share Price Today: price rise, fundamentals and sector - Univest</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Authum Investment Share Price Decline and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Authum Investment &amp; Infrastructure Share Price rises 4.95% - Univest</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Authum Investment Invests ₹101.6 Cr in ISARC Rights Issue - InvestyWise</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1686,68 +1702,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AIIL.NS</t>
+          <t>ORIENTTECH.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Authum Investment &amp; Infrastructure Limited</t>
+          <t>Orient Technologies Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>508</v>
+        <v>237.1799926757812</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>558</v>
+        <v>274.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>503</v>
+        <v>233.6999969482422</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>544.3499755859375</v>
+        <v>249.6399993896484</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>512.2999877929688</v>
+        <v>235.3600006103516</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>544.3499755859375</v>
+        <v>249.6399993896484</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>5994616</v>
+        <v>8430139</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6.26</v>
+        <v>6.07</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>AIIL Share Price Today: price rise, fundamentals and sector - Univest</t>
+          <t>ORIENT TECHNOLOGIES LTD Share Price - Live NSE: ORIENTTECH Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>AIIL Share Price Today: price rise, fundamentals and sector - Univest</t>
+          <t>ORIENT TECHNOLOGIES LTD Share Price - Live NSE: ORIENTTECH Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Authum Investment Share Price Decline and Stock Analysis - Univest</t>
+          <t>Orient Technologies Share Price Today: market cap, valuation - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Authum Investment &amp; Infrastructure Share Price rises 4.95% - Univest</t>
+          <t>Orient (ORIENTTECH.NS) Quarterly Results: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Reaction: Shares Move Lower 0.35% in Latest Trading - Next Quarter Guidance - siam.in</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Authum Investment Invests ₹101.6 Cr in ISARC Rights Issue - investywise.com</t>
+          <t>Orient (ORIENTTECH.NS) Today: Climbs 0.27% to ₹244.30 in the Latest Session; Level Watch: Support at ₹232.09 and Resistance at ₹256.52 Frame the Range in the Current Update - Delta Hedging - siam.in</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1755,68 +1771,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RRECL.NS</t>
+          <t>SOLARA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions Limited</t>
+          <t>Solara Active Pharma Sciences Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>126</v>
+        <v>707.2000122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>138.6000061035156</v>
+        <v>759.5499877929688</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>125.5800018310547</v>
+        <v>697.4000244140625</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>133.8000030517578</v>
+        <v>749.1500244140625</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>126</v>
+        <v>707.25</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>133.8000030517578</v>
+        <v>749.1500244140625</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>883</v>
+        <v>1159874</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6.19</v>
+        <v>5.92</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>RRECL Stock Price and Chart — NSE:RRECL - TradingView</t>
+          <t>Solara 52 Week High Streak With Sector and Peer Context - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
+          <t>Solara 52 Week High Streak With Sector and Peer Context - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions Share Price Today Down 9.14% - Univest</t>
+          <t>Solara Active Pharma Sciences Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions Ltd. (RRECL) Fundamental and Financial Data - Stocktwits</t>
+          <t>Solara Active Pharma Sciences Ltd. (SOLARA) Share Price hits fresh 52-week high as stock trades at Rs 738.8 - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
+          <t>Solara Active Pharma Sciences Share Price today after rise - Univest</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1824,61 +1840,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TANAA.NS</t>
+          <t>RPEL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Limited</t>
+          <t>Raghav Productivity Enhancers Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>246.5500030517578</v>
+        <v>1773.5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>269.8500061035156</v>
+        <v>1854.099975585938</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>238</v>
+        <v>1725.900024414062</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>266.9500122070312</v>
+        <v>1845.199951171875</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>251.5</v>
+        <v>1743.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>266.9500122070312</v>
+        <v>1845.199951171875</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>50644</v>
+        <v>171393</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6.14</v>
+        <v>5.83</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>TANAA Stock Price and Chart — NSE:TANAA - TradingView</t>
+          <t>Raghav Productivity Enhancers Ltd Share Price - Business Today</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+          <t>Raghav Productivity Enhancers Ltd Share Price - Business Today</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+          <t>With EPS Growth And More, Raghav Productivity Enhancers (NSE:RPEL) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Ltd. (TANAA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>Raghav Productivity Enhancers Share Price at 52-Week High - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Taneja Aerospace &amp; Aviation Ltd. (NSE:TANAA) - TradingView</t>
+          <t>RPEL to set up 3.5 lakh MTPA silica ramming mass manufacturing facility in Odisha - Business Standard</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1922,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2005,7 +2021,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2013,68 +2029,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE.NS</t>
+          <t>SRGHFL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Limited</t>
+          <t>SRG Housing Finance Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>512.4000244140625</v>
+        <v>156</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>524.9500122070312</v>
+        <v>156</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>156</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>156</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>509.7000122070312</v>
+        <v>195</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>156</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3900142</v>
+        <v>11743</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-19.99</v>
+        <v>-20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE PICTURES LIMITED Share Price - upstox.com</t>
+          <t>Improved Earnings Required Before SRG Housing Finance Limited (NSE:SRGHFL) Shares Find Their Feet - simplywall.st</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Metals (ASX:SHN) in Focus: Could This ASX Resources Stock Be One to Watch in September 2026? - Kalkine</t>
+          <t>SRG Housing Finance Mar 2026 Earnings: EPS at ₹5.89, Stock Gains Amid Steady Performance - Earnings Surprise Score - vinanet.vn</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+          <t>SRG Housing Finance Mar 2026 Earnings: EPS at ₹5.89, Stock Gains Amid Steady Performance - Earnings Surprise Score - vinanet.vn</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE Share Price Today - SUNSHINE PICTURES LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>SRGHFL Stock Price and Chart — NSE:SRGHFL - TradingView</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Metals (ASX:SHN) in Focus: Could This ASX Resources Stock Be One to Watch in September 2026? - Kalkine</t>
+          <t>SRG Housing Finance Mar 2026 Earnings: EPS of ₹5.89 Reported; Stock Declines 2.7% - Earnings Surprise Score - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2082,68 +2098,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CSM.NS</t>
+          <t>SUNSHINE.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Limited</t>
+          <t>Sunshine Pictures Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>101.1500015258789</v>
+        <v>512.4000244140625</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>101.1500015258789</v>
+        <v>524.9500122070312</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>76.26000213623047</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>83.44000244140625</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>94.95999908447266</v>
+        <v>509.7000122070312</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>83.44000244140625</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2772772</v>
+        <v>3900142</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-12.13</v>
+        <v>-19.99</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>CSM TECHNOLOGIES LIMITED Share Price - upstox.com</t>
+          <t>SUNSHINE PICTURES LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
+          <t>Sunshine Metals (ASX:SHN) in Focus: Could This ASX Resources Stock Be One to Watch in September 2026? - Kalkine</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
           <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>CSM Share Price Today Falls: P/E, P/B and Sector Context - Univest</t>
-        </is>
-      </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+          <t>SUNSHINE Share Price Today - SUNSHINE PICTURES LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Understanding Momentum Shifts in (CSM) - Stock Traders Daily</t>
+          <t>Sunshine Pictures IPO Listing: Shares List at 9.97% Premium on NSE, Fall Short of Grey-Market Hopes - India Infoline</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2185,34 +2201,34 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>Kothari Industrial Corporation Stock Falls Below SMA - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Kothari Industrial Corporation Stock Falls Below SMA - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What's fuelling the rally? - TradingView</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial Share Price Today: Fundamental Check - Univest</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Kothari Industrial Corporation (KOTIC.NS) Slips 1.23% to ₹134.79; Support at ₹128.05 in Focus - Bullish Sentiment - siam.in</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Kothari Industrial Corporation Share Price rises 10.14% - Univest</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial Share Price Today: Fundamental Check - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2220,68 +2236,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SREEL.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Limited</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>365</v>
+        <v>13.75</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>365.7999877929688</v>
+        <v>13.75</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>333.2699890136719</v>
+        <v>13.75</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>333.2699890136719</v>
+        <v>13.75</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>370.2999877929688</v>
+        <v>15.27000045776367</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>333.2699890136719</v>
+        <v>13.75</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>129115</v>
+        <v>370055</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-10</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Share Price Fall: Price, Valuation, Sector View - Univest</t>
+          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Daily Chart Outlook - Kalkine India</t>
+          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Daily Chart Outlook - Kalkine India</t>
+          <t>Atal Realtech Share Price Fall Streak With Fresh Weakness - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Limited Declares Interim Dividend of ₹1 Per Share for FY 2025-26 - scanx.trade</t>
+          <t>Atal Realtech Lower Circuit: Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Share Price rises 20%: price, fundamentals - Univest</t>
+          <t>Atal Realtech Share Price update: price action and valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2289,68 +2305,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Limited</t>
+          <t>Cochin Shipyard Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13.75</v>
+        <v>1510</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>13.75</v>
+        <v>1510</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>13.75</v>
+        <v>1372</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>13.75</v>
+        <v>1381</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15.27000045776367</v>
+        <v>1520.400024414062</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13.75</v>
+        <v>1381</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>370055</v>
+        <v>6390480</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-9.949999999999999</v>
+        <v>-9.17</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
+          <t>Cochin Shipyard Ltd (COCHINSHIP) Share Price - Business Today</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
+          <t>Cochin Shipyard Seals BRICS-Stage Joint Venture With Drydocks World Dubai - The Globe and Mail</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price update: price action and valuation - Univest</t>
+          <t>Cochin Shipyard Seals BRICS-Stage Joint Venture With Drydocks World Dubai - The Globe and Mail</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Ltd. (ATALREAL) Share Price Trades Within 2% of 52-Week High - Univest</t>
+          <t>Cochin Shipyard Share Price Today, August 24, 2026: COCHINSHIP Closes at ₹1,514 on NSE - The Eastern Herald</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech 20.00% Fall: Chart Analysis - Kalkine India</t>
+          <t>Cochin Shipyard shares crash nearly 9% - Is it opportunity to buy? Should you take fresh entry? Expert suggests this - TradingView</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2358,68 +2374,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>SSDL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Limited</t>
+          <t>Saraswati Saree Depot Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1510</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1510</v>
+        <v>72.69999694824219</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1372</v>
+        <v>61.36999893188477</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1381</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1520.400024414062</v>
+        <v>67.83999633789062</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1381</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>6390480</v>
+        <v>560099</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-9.17</v>
+        <v>-7.74</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Ltd (COCHINSHIP) Share Price - Business Today</t>
+          <t>Saraswati Saree Depot Stock Price Reversal Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Seals BRICS-Stage Joint Venture With Drydocks World Dubai - The Globe and Mail</t>
+          <t>Saraswati Saree Depot Stock Price Reversal Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Seals BRICS-Stage Joint Venture With Drydocks World Dubai - The Globe and Mail</t>
+          <t>Saraswati Saree Depot Jun 2026 Earnings: Revenue at ₹147.59 crore and EPS of ₹1.67 as Stock Slips 4.7% - siam.in</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Share Price Today, August 24, 2026: COCHINSHIP Closes at ₹1,514 on NSE - The Eastern Herald</t>
+          <t>Saraswati Saree Depot Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard shares crash nearly 9% - Is it opportunity to buy? Should you take fresh entry? Expert suggests this - TradingView</t>
+          <t>Saraswati Saree Depot Share Price today: price action view - Univest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2427,68 +2443,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>IOLCP.NS</t>
+          <t>ARVEE.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals and Pharmaceuticals Limited</t>
+          <t>Arvee Laboratories (India) Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>210.5099945068359</v>
+        <v>195</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>210.9499969482422</v>
+        <v>195</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>192</v>
+        <v>176.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>194.3099975585938</v>
+        <v>180.6900024414062</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>211.4299926757812</v>
+        <v>195.25</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>194.3099975585938</v>
+        <v>180.6900024414062</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>5129124</v>
+        <v>7318</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-8.1</v>
+        <v>-7.46</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals and Pharmaceuticals Share Price - Live NSE: IOLCP Stock Price &amp; Chart - upstox.com</t>
+          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals And Pharmaceuticals (IOLCP) Share Price Falls 8.19% Today - Univest</t>
+          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>IOLCP Share Price today near 52-week high, price action - Univest</t>
+          <t>Arvee Laboratories (India) Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals (IOLCP.NS) Holds Steady Near ₹194 as Pharma-Chemical Play Consolidates - MFI Overbought - siam.in</t>
+          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals Share Price Today after fresh 52-week high - Univest</t>
+          <t>Arvee Laboratories (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2496,68 +2512,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SSDL.NS</t>
+          <t>AARON.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Limited</t>
+          <t>Aaron Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>72.69999694824219</v>
+        <v>137</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>61.36999893188477</v>
+        <v>121.1600036621094</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.59000015258789</v>
+        <v>126.9400024414062</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>67.83999633789062</v>
+        <v>136.9499969482422</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>62.59000015258789</v>
+        <v>126.9400024414062</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>560099</v>
+        <v>34810</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-7.74</v>
+        <v>-7.31</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot SSDL Fresh High Analysis - Kalkine India</t>
+          <t>Aaron Industries confirms Aug 14 dividend record date for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot SSDL Fresh High Analysis - Kalkine India</t>
+          <t>‘It Worked Out the Way That It Should Of’ – Aaron Gordon Shares Mindset Heading to 2026-27 Season, Comments on Exit of Beloved Teammate - Yahoo Sports</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Jun 2026 Earnings: Revenue at ₹147.59 crore and EPS of ₹1.67 as Stock Slips 4.7% - siam.in</t>
+          <t>Box CEO Aaron Levie sells $513,660 in company stock - Investing.com India</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Aaron Industries Share Price Falls 8.36%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Share Price today: price action view - Univest</t>
+          <t>‘It Worked Out the Way That It Should Of’ – Aaron Gordon Shares Mindset Heading to 2026-27 Season, Comments on Exit of Beloved Teammate - Yahoo Sports</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2565,68 +2581,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>KENNAMET.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>Kennametal India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>195</v>
+        <v>5000</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>195</v>
+        <v>5000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>176.5</v>
+        <v>4660</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>180.6900024414062</v>
+        <v>4682.39990234375</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>195.25</v>
+        <v>5027.89990234375</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>180.6900024414062</v>
+        <v>4682.39990234375</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>7318</v>
+        <v>70326</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-7.46</v>
+        <v>-6.87</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
+          <t>Kennametal (KENNAMET.NS) Financial Update: The Company Releases Its Current Earnings Data for This Review; Share Move: Shares Move 8.34% Up for the Current Session - Product Revenue Analysis - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
+          <t>Kennametal India Share Price Today: Price Fall Analysis - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>Kennametal (KENNAMET.NS) Earnings Reading: The Report Provides a New Financial Snapshot in the Latest Reading; Trading Move: Shares Rise 3.25% in the Latest Session - Pre-Earnings Setup - siam.in</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Volume Gainers on September 8, 2026 at 4:00 PM - HDFC Sky</t>
+          <t>Kennametal India Share Price today: price and valuation - Univest</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Arvee (ARVEE.NS) Outlook: Ends Lower by 1.98% at ₹165.00; Technical View: ₹156.75 and ₹173.25 Define the Nearby Reference Levels in Latest Trading - OBV Divergence - siam.in</t>
+          <t>Kennametal India Share Price Today: Price Fall Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2678,16 +2694,20 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>Suvidhaa Infoserve submits FY26 annual report, loss narrows 39% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>Suvidhaa Infoserve Sets September 30 Virtual AGM, Closes Books for FY 2025-26 Decisions - TipRanks</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2695,68 +2715,60 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AVROIND.NS</t>
+          <t>BIOFILCHEM.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>AVRO INDIA LIMITED</t>
+          <t>Biofil Chemicals &amp; Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8.399999618530273</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.430000305175781</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7.71999979019165</v>
+        <v>32.36000061035156</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>7.809999942779541</v>
+        <v>34.5099983215332</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8.340000152587891</v>
+        <v>36.79000091552734</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7.809999942779541</v>
+        <v>34.5099983215332</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>891730</v>
+        <v>173376</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.35</v>
+        <v>-6.2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Avro India Share Price - Live NSE: AVROIND Stock Price &amp; Chart - upstox.com</t>
+          <t>Biofil (BIOFILCHEM.NS) Technicals: Moves 0.87% Lower to ₹32.06 at the Close; Next Test: the ₹30.46 to ₹33.66 Range Remains in Focus in Latest Trading - Fibonacci Time Zone - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Avro India Share Price - Live NSE: AVROIND Stock Price &amp; Chart - upstox.com</t>
+          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>AVRO India Slips 2.9% to ₹9.03: Support Zone in Focus - Investment Factor - siam.in</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Avro India Ltd. Share Price Today Falls; Valuation View - Univest</t>
-        </is>
-      </c>
+          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2764,60 +2776,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BIOFILCHEM.NS</t>
+          <t>GOACARBON.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals Limited</t>
+          <t>Goa Carbon Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37.79999923706055</v>
+        <v>434.7000122070312</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>37.79999923706055</v>
+        <v>457</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>32.36000061035156</v>
+        <v>408.9500122070312</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>34.5099983215332</v>
+        <v>413.3999938964844</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.79000091552734</v>
+        <v>440.25</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>34.5099983215332</v>
+        <v>413.3999938964844</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>173376</v>
+        <v>164355</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.2</v>
+        <v>-6.1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
+          <t>Goa Carbon 20% Move: Key Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
+          <t>Goa Carbon FY26 Results: Income rises 36%, loss widens to ₹48.2 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Biofil (BIOFILCHEM.NS) Technicals: Moves 0.87% Lower to ₹32.06 at the Close; Next Test: the ₹30.46 to ₹33.66 Range Remains in Focus in Latest Trading - Fibonacci Time Zone - siam.in</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Goa (GOACARBON.NS) Price: Finishes 0.67% Up at ₹359.85 at the Close; the Supplied Trading Band Runs From ₹341.86 to ₹377.84 - Range Breakout - siam.in</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Goa (GOACARBON.NS) Financial Results: The Company Publishes Its Latest Results under the Current Snapshot; Market Response: The Stock Gains 1.63% in the Latest Reading - Earnings Recovery Stocks - siam.in</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Goa Carbon Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2825,68 +2845,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>GOACARBON.NS</t>
+          <t>IVC.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Goa Carbon Limited</t>
+          <t>IL&amp;FS Investment Managers Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>434.7000122070312</v>
+        <v>9.569999694824219</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>457</v>
+        <v>9.569999694824219</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>408.9500122070312</v>
+        <v>9.050000190734863</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>413.3999938964844</v>
+        <v>9.109999656677246</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>440.25</v>
+        <v>9.680000305175781</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>413.3999938964844</v>
+        <v>9.109999656677246</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>164355</v>
+        <v>1429459</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-6.1</v>
+        <v>-5.89</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Goa (GOACARBON.NS) Price: Finishes 0.67% Up at ₹359.85 at the Close; the Supplied Trading Band Runs From ₹341.86 to ₹377.84 - Range Breakout - siam.in</t>
+          <t>IL&amp;FS discloses no new encumbrance on IIML shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Goa Carbon 20% Move: Key Chart Analysis - Kalkine India</t>
+          <t>Texmaco Rail bags Rs 78-cr order from IVC Logistics - Business Standard</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Goa (GOACARBON.NS) Financial Results: The Company Publishes Its Latest Results under the Current Snapshot; Market Response: The Stock Gains 1.63% in the Latest Reading - Earnings Recovery Stocks - siam.in</t>
+          <t>IL&amp;FS Investment Managers Limited (IVC.NS) Q2 2025 Earnings: Revenue Declines 44% YoY but EPS Remains Positive at ₹0.42 - Earnings Revision Upgrade - vinanet.vn</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Goa Carbon 20% Move: Key Chart Analysis - Kalkine India</t>
+          <t>Texmaco Rail bags Rs 78-cr order from IVC Logistics - Business Standard</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Goa Carbon Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Texmaco Rail bags ₹62 crore wagon order from IVC Logistics - ET Infra</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2928,7 +2948,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Creative (CREATIVEYE.NS) Results Versus Estimates: The Latest Report Adds New Financial Reference Points under the Current Snapshot; Price Reaction: The Stock Loses 0.81% at the Close - Balance Sheet Strength - siam.in</t>
+          <t>Creative (CREATIVEYE.NS) Results Versus Estimates: The Latest Report Adds New Financial Reference Points under the Current Snapshot; Price Reaction: The Stock Loses 0.81% at the Close - Management Guidance Update - siam.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2951,7 +2971,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2959,68 +2979,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MVGJL.NS</t>
+          <t>HEIDELBERG.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
+          <t>HeidelbergCement India Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>208.6999969482422</v>
+        <v>150.9499969482422</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>208.6999969482422</v>
+        <v>150.9499969482422</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>195.6000061035156</v>
+        <v>147.8000030517578</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>197.3699951171875</v>
+        <v>149.8000030517578</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>208.7799987792969</v>
+        <v>158.7899932861328</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>197.3699951171875</v>
+        <v>149.8000030517578</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>332881</v>
+        <v>314126</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.47</v>
+        <v>-5.66</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>MANOJ VAIBHAV GEM N JEW L Share Price - Live NSE: MVGJL Stock Price &amp; Chart - upstox.com</t>
+          <t>Heidelberg Materials stock edges lower as analysts stay positive - ad-hoc-news.de</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - TradingView</t>
+          <t>Heidelberg Materials stock edges lower as analysts stay positive - ad-hoc-news.de</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Manoj Vaibhav Gems 'N' Jewellers (NSE:MVGJL) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>Heidelberg Cement India Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Manoj Vaibhav Gems (MVGJL.NS) Gains 4.6% to ₹179.9: Jewelry Stock Rebounds Toward Key Resistance - Bollinger Squeeze - siam.in</t>
+          <t>HeidelbergCement (HEIDELBERG.NS) Shares: Posts a 0.89% Gain to ₹160.40 in the Current Update; Level Watch: the Supplied Trading Band Runs From ₹152.38 to ₹168.42 in the Available Record - Earnings Beat Stocks - siam.in</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Manoj (MVGJL.NS) Financial Update: The Company Lists Its Latest Available Figures in the Current Update; Shares Move 1.33% Up in the Latest Reading - Surprise Factor Analysis - siam.in</t>
+          <t>Heidelberg Materials Tokenized Stock (xStock) price today, HEI.DEx to USD live price, marketcap and chart - CoinMarketCap</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3028,68 +3048,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SVGLOBAL.NS</t>
+          <t>MVGJL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Limited</t>
+          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>140.6900024414062</v>
+        <v>208.6999969482422</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>140.6900024414062</v>
+        <v>208.6999969482422</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>126.5500030517578</v>
+        <v>195.6000061035156</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>133.3500061035156</v>
+        <v>197.3699951171875</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>140.8000030517578</v>
+        <v>208.7799987792969</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>133.3500061035156</v>
+        <v>197.3699951171875</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1859</v>
+        <v>332881</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.29</v>
+        <v>-5.47</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
+          <t>MANOJ VAIBHAV GEM N JEW L Share Price - Live NSE: MVGJL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
+          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - TradingView</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Ltd. Share Price Fall and Stock Analysis - Univest</t>
+          <t>Here's Why Manoj Vaibhav Gems 'N' Jewellers (NSE:MVGJL) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Ltd (SVGLOBAL) Fundamental and Financial Data - Stocktwits</t>
+          <t>Manoj Vaibhav Gems (MVGJL.NS) Gains 4.6% to ₹179.9: Jewelry Stock Rebounds Toward Key Resistance - Bollinger Squeeze - siam.in</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Share Price falls 10.07% | Price analysis - Univest</t>
+          <t>Manoj (MVGJL.NS) Financial Update: The Company Lists Its Latest Available Figures in the Current Update; Shares Move 1.33% Up in the Latest Reading - Surprise Factor Analysis - siam.in</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3097,68 +3117,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SECMARK.NS</t>
+          <t>JAYAGROGN.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SecMark Consultancy Limited</t>
+          <t>Jayant Agro Organics Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>148</v>
+        <v>257</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>148</v>
+        <v>257</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>138</v>
+        <v>239.0899963378906</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>141.3099975585938</v>
+        <v>244.1300048828125</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>149.1600036621094</v>
+        <v>258.1799926757812</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>141.3099975585938</v>
+        <v>244.1300048828125</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2320</v>
+        <v>47854</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.26</v>
+        <v>-5.44</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Secmark Consultancy Share Price rises 8.39% today - Univest</t>
+          <t>Jayant Agro-Organics Share Price news after intraday gain - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Secmark Consultancy Share Price rises 8.39% today - Univest</t>
+          <t>Jayant Agro-Organics Approves FY26 Accounts and Dividend at Virtual AGM - TipRanks</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>SecMark Consultancy schedules 15th AGM for September 30, 2026 - scanx.trade</t>
+          <t>Jayant (JAYAGROGN.NS) Closing Review: Rises 0.30% to ₹221.08 in Latest Trading; Support and Resistance: the Supplied Trading Band Runs From ₹210.03 to ₹232.13 in the Latest Reading - ETF Liquidity - siam.in</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Secmark Consultancy Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Jayant (JAYAGROGN.NS) Quarterly Figures: Available Data Shows the Latest Reported Performance in Latest Trading; Trading Response: The Market Price Advances 0.44% in the Latest Session - Analyst Drop Coverage - siam.in</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Secmark Consultancy Share Price news: Rs 137 and valuation - Univest</t>
+          <t>how Fair Value analysis spotted 72% gain in Jayant Agro-Organics - Investing.com India</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3166,68 +3186,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>GUJENERGY.NS</t>
+          <t>SECMARK.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>GUJARAT ENERGY LIMITED</t>
+          <t>SecMark Consultancy Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>247.9400024414062</v>
+        <v>148</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>249.2100067138672</v>
+        <v>148</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>240.3600006103516</v>
+        <v>138</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>241.5899963378906</v>
+        <v>141.3099975585938</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>254.8000030517578</v>
+        <v>149.1600036621094</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>241.5899963378906</v>
+        <v>141.3099975585938</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1808646</v>
+        <v>2320</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.18</v>
+        <v>-5.26</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Energy (NSE:GUJENERGY) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
+          <t>Secmark Consultancy Share Price rises 8.39% today - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Energy Limited Appoints Dhirubhai Shah &amp; Co. LLP as Statutory Auditors - psuconnect.in</t>
+          <t>Secmark Consultancy Share Price rises 8.39% today - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Gas Share Price Up 2.36%: Price, Valuation View - Univest</t>
+          <t>SecMark Consultancy schedules 15th AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Gas Share Price falls to yearly low | Price action - Univest</t>
+          <t>Secmark Consultancy Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Gas Ltd. Share Price Today: 3.43% Fall Analyzed - Univest</t>
+          <t>Secmark Consultancy Share Price news: Rs 137 and valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3235,68 +3255,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>GYFTR.NS</t>
+          <t>INDOTHAI.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Gyftr Limited</t>
+          <t>Indo Thai Securities Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>189</v>
+        <v>43.40000152587891</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>189</v>
+        <v>45.4900016784668</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>175</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>175.7299957275391</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>185.3200073242188</v>
+        <v>43.43000030517578</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>175.7299957275391</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>47421</v>
+        <v>20200138</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.17</v>
+        <v>-5.2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>LKP Finance Limited Announces Postal Ballot Results with 99.49% Shareholder Approval - scanx.trade</t>
+          <t>Indo (INDOTHAI.NS) Quarterly Figures: Available Data Shows the Latest Reported Performance at the Close; After Results: The Stock Ends Down 4.99% - CEO Earnings Statement - siam.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>LKP Finance Limited Announces Postal Ballot Results with 99.49% Shareholder Approval - scanx.trade</t>
+          <t>Indo Thai Securities Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Gyftr schedules 42nd AGM for September 29, 2026 - scanx.trade</t>
+          <t>Indo Thai Securities Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Gyftr: कंपनी ने कमाए **₹21.8 करोड़**, क्या है 29 सितंबर की एजीएम (AGM) का एजेंडा? - Whalesbook</t>
+          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>PNB Partners With GYFTR For Credit Card Offers, Customers To Get Shopping, Food And Travel Benefits - freepressjournal.in</t>
+          <t>Indo Thai Securities schedules NCLT hearing for demerger scheme on September 24 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:30:20 IST</t>
+          <t>2026-09-14 22:01:11 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3304,61 +3324,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO.NS</t>
+          <t>GUJENERGY.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Limited</t>
+          <t>GUJARAT ENERGY LIMITED</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>147.7799987792969</v>
+        <v>247.9400024414062</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>147.7799987792969</v>
+        <v>249.2100067138672</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>141.1000061035156</v>
+        <v>240.3600006103516</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>141.1000061035156</v>
+        <v>241.5899963378906</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>148.5200042724609</v>
+        <v>254.8000030517578</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>141.1000061035156</v>
+        <v>241.5899963378906</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3988</v>
+        <v>1808646</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5</v>
+        <v>-5.18</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Ltd. (MYSORPETRO) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Gujarat Gas Share Price - Live NSE: GUJENERGY Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals: Denies Undisclosed Material Events Amidst Share Price Movement - investywise.com</t>
+          <t>Gujarat Gas fixes July 2 record date for GTL share allotment - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>OPTIFIN Stock Price and Chart — NSE:OPTIFIN - TradingView</t>
+          <t>Gujarat Gas fixes July 2 record date for GTL share allotment - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Ltd. (MYSORPETRO) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>Gujarat Energy (NSE:GUJENERGY) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO.NSE - Stocktwits</t>
+          <t>Gujarat Gas Share Price Up 2.36%: Price, Valuation View - Univest</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,60 +553,64 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ASHOKAMET.NS</t>
+          <t>ZYDUSWELL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.53999996185303</v>
+        <v>549.3499755859375</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>17.20000076293945</v>
+        <v>558.4500122070312</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>547.4500122070312</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>17.20000076293945</v>
+        <v>547.75</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14.34000015258789</v>
+        <v/>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17.20000076293945</v>
+        <v>547.75</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1455188</v>
+        <v>126424</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.94</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Ashoka Metcast (NSE:ASHOKAMET) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Zydus Wellness Share Price - Live NSE: ZYDUSWELL Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Ashoka Metcast (NSE:ASHOKAMET) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Zydus Wellness Share Price - Live NSE: ZYDUSWELL Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast sells 2.48M Mena Mani Industries shares in open market - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
+          <t>Zydus Wellness (ZYDUSWELL.NS) Slips 2.65% to ₹496.65: Approaching Key Support Levels - Institutional Flow Picks - siam.in</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Zydus Wellness Limited Announces Appointment of Kapil Sharma as Chief Revenue Officer (India and Indian Subcontinent), Effective September 1, 2026 - marketscreener.com</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -614,68 +618,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AWFIS.NS</t>
+          <t>AARTECH.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Awfis Space Solutions Limited</t>
+          <t>Aartech Solonics Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>248.5</v>
+        <v>52.2400016784668</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>299.4500122070312</v>
+        <v>52.25</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>244.1000061035156</v>
+        <v>50.5099983215332</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>293.2000122070312</v>
+        <v>51</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>249.6000061035156</v>
+        <v/>
       </c>
       <c r="J3" s="2" t="n">
-        <v>293.2000122070312</v>
+        <v>51</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>23945553</v>
+        <v>24726</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>17.47</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Awfis Space Solutions share price jumps nearly 20% despite weak Sensex, Nifty 50; what should investors do now? - Livemint</t>
+          <t>Aartech Solonics Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>AWFIS Space Solutions Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
+          <t>Aartech Solonics Ltd (AARTECH): Growth Meets a Cash-Flow Question - Kalkine India</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>AWFIS Space Solutions Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo</t>
+          <t>Aartech Solonics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Awfis Space Solutions Share Price: Buy or Sell - Univest</t>
+          <t>Aartech Solonics Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - valueresearchonline.com</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>₹524: That's What Analysts Think Awfis Space Solutions Limited (NSE:AWFIS) Is Worth After Its Latest Results - simplywall.st</t>
+          <t>Aartech Solonics Ltd. Peer Comparison – Compare with Others - valueresearchonline.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +687,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>AARTISURF.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs Limited</t>
+          <t>Aarti Surfactants Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>171</v>
+        <v>506.8999938964844</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>206.3800048828125</v>
+        <v>515</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>170.9600067138672</v>
+        <v>506.8999938964844</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>202.1699981689453</v>
+        <v>510.2000122070312</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>173.1699981689453</v>
+        <v/>
       </c>
       <c r="J4" s="2" t="n">
-        <v>202.1699981689453</v>
+        <v>510.2000122070312</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>276696049</v>
+        <v>10271</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>PINELABS Stock Price and Chart — NSE:PINELABS - TradingView</t>
+          <t>Aarti Surfactants Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>PINELABS Stock Price and Chart — NSE:PINELABS - TradingView</t>
+          <t>Aarti Surfactants Discloses Resignation of Independent Director Nisha B. Shah - TipRanks</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs share price jumps 13%: Fintech stock rises sharply as trading volume explodes - Livemint</t>
+          <t>Aarti Surfactants incorporates US subsidiary Precision Ingredients Inc - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs Share Price Today Up 2.43%: Fundamental Check - Univest</t>
+          <t>Aarti Surfactants declares ₹1 per share final dividend for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Pine (PINELABS.NS) Chart: Loses 1.77% to Close at ₹156.91 for the Current Session; Market Levels: ₹149.06 and ₹164.76 Define the Nearby Reference Levels in Latest Trading - Sign of Strength - siam.in</t>
+          <t>Aarti Surfactants sets up wholly owned U.S. subsidiary to expand global reach - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,60 +756,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AMDIND.NS</t>
+          <t>ABINFRA.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Limited</t>
+          <t>A B Infrabuild Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>56.31999969482422</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65.19999694824219</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>55.5099983215332</v>
+        <v>11.0600004196167</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>64.02999877929688</v>
+        <v>11.28999996185303</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>56.04000091552734</v>
+        <v/>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64.02999877929688</v>
+        <v>11.28999996185303</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>484603</v>
+        <v>60400</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14.26</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Stock: Momentum Above 50-Day SMA - Kalkine India</t>
+          <t>AB Infrabuild Ltd. Share Price News: Price Action Check - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Stock: Momentum Above 50-Day SMA - Kalkine India</t>
+          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Share Price rises 12.01%: valuation view - Univest</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t>AB Infrabuild Ltd. Share Price News: Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -813,68 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AHCL.NS</t>
+          <t>ACCURACY.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Limited</t>
+          <t>Accuracy Shipping Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17.72999954223633</v>
+        <v>4.170000076293945</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17.54000091552734</v>
+        <v>4.170000076293945</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>17.54000091552734</v>
+        <v/>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>150749037</v>
+        <v>73822</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>11.57</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>AHCL Stock Price and Chart — NSE:AHCL - TradingView</t>
+          <t>Cardiff University research shows retailers can dramatically improve stock accuracy and sales by ‘counting smarter’ - Cardiff University</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
+          <t>Top Santa Clara, CA Auto Body Repair Specialist Shares Why Interior and Mechanical Accuracy Matters as Much as Exterior Work - FinancialContent</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
+          <t>A fingerprint drug test produced no false positives. Intelligent Bio Solutions expects an FDA filing in September. - Stock Titan</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
+          <t>Dirty Data Kills Trades: Why Stock DB Accuracy Is the Most Underrated Problem in Financial Technology - nerdbot</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>AHCL.NS Q2 2026 Earnings: Revenue Jumps 42.96% YoY to ₹171.97 Cr, Stock Slips 2.33% - Earnings Momentum Score - siam.in</t>
+          <t>Top Santa Clara, CA Auto Body Repair Specialist Shares Why Interior and Mechanical Accuracy Matters as Much as Exterior Work - FinancialContent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -882,68 +890,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TRACXN.NS</t>
+          <t>AKSHOPTFBR.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tracxn Technologies Limited</t>
+          <t>Aksh Optifibre Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>28.59000015258789</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>32.38999938964844</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>28.43000030517578</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>31.89999961853027</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>28.61000061035156</v>
+        <v/>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31.89999961853027</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1039887</v>
+        <v>281506</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Tracxn Technologies Share Price today: key stock update - Univest</t>
+          <t>Aksh Optifibre narrows FY26 loss, auditors flag unrecognised liabilities - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Tracxn Technologies Ltd is Rated Strong Sell - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Tracxn narrows FY26 loss, eyes FY27 growth with AI - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Tracxn Technologies Ltd is Rated Strong Sell - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Tracxn (TRACXN.NS) Watch: Rises 0.64% to ₹29.76 for the Current Session; Technical Setup: Traders Can Monitor the ₹28.27-₹31.25 Range in the Available Record - Growth ETF - siam.in</t>
-        </is>
-      </c>
+          <t>Aksh Optifibre narrows FY26 loss, auditors flag unrecognised liabilities - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -951,68 +947,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD.NS</t>
+          <t>ALPHAGEO.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Digjam Limited</t>
+          <t>Alphageo (India) Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>64.5</v>
+        <v>307</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>73.19000244140625</v>
+        <v>319.7999877929688</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.84000015258789</v>
+        <v>298.0499877929688</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>68.41999816894531</v>
+        <v>300</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>61.84000015258789</v>
+        <v/>
       </c>
       <c r="J8" s="2" t="n">
-        <v>68.41999816894531</v>
+        <v>300</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1282661</v>
+        <v>6210</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10.64</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Digjam Share Price rises 14.59%: price action - Univest</t>
+          <t>We Wouldn't Be Too Quick To Buy Alphageo (India) Limited (NSE:ALPHAGEO) Before It Goes Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Digjam Share Price rises 14.59%: price action - Univest</t>
+          <t>Alphageo (India) Ltd Downgraded to Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Digjam Ltd Gains 2.11% to ₹51.73: Textile Stock Holds Above Key Support - Turnaround Stocks - siam.in</t>
+          <t>Alphageo (India) Ltd Downgraded to Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Digjam (DIGJAMLMTD.NS) Stock: Retreats 0.27% to ₹51.50; the Supplied Trading Band Runs From ₹48.92 to ₹54.08 - Sector ETF Flow - siam.in</t>
+          <t>Alphageo (India) Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Digjam Limited: స్కీమ్ ఆఫ్ అరేంజ్మెంట్‌పై NCLT కీలక ఆదేశాలు.. అక్టోబర్ 28న తదుపరి విచారణ - Whalesbook</t>
+          <t>Alphageo India Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1020,68 +1016,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HLEGLAS.NS</t>
+          <t>AMBALALSA.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>HLE Glascoat Limited</t>
+          <t>Ambalal Sarabhai Enterprises Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>367.8500061035156</v>
+        <v>40.5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>404.3500061035156</v>
+        <v>40.97999954223633</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>363</v>
+        <v>39.25</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>404.3500061035156</v>
+        <v>39.75</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>367.6000061035156</v>
+        <v/>
       </c>
       <c r="J9" s="2" t="n">
-        <v>404.3500061035156</v>
+        <v>39.75</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>870661</v>
+        <v>18037</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>HLE Glascoat Share Price rise: price action and P/E view - Univest</t>
+          <t>Ambalal (AMBALALSA.NS) Financial Results: The Company Reports Its Latest Available Figures under the Current Snapshot; Market Reaction: Shares Move Lower 2.71% in the Latest Reading - Earnings Beat Alert - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>HLE Glascoat promoter Nilesh Patel gifts 10% stake to son Aalap - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>HLE (HLEGLAS.NS) Latest Quarter: The Company Releases Its Current Earnings Data in the Latest Reading; Share Move: Shares Fall 0.28% at the Close - Margin Expansion Trends - siam.in</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>HLE (HLEGLAS.NS) EPS and Revenue: The Latest Financial Metrics Are Now Available in the Reported Period; Market Reaction: The Stock Records a 1.74% Decrease in the Latest Reading - Consensus Forecast Report - siam.in</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>HLE Glascoat Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
-        </is>
-      </c>
+          <t>Ambalal (AMBALALSA.NS) Financial Results: The Company Reports Its Latest Available Figures under the Current Snapshot; Market Reaction: Shares Move Lower 2.71% in the Latest Reading - Earnings Beat Alert - siam.in</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1089,68 +1073,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ANMOL.NS</t>
+          <t>APTECHT.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Anmol India Limited</t>
+          <t>Aptech Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>86.11000061035156</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.34000015258789</v>
+        <v/>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16.8700008392334</v>
+        <v>86.11000061035156</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1521669</v>
+        <v>40301</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>ANMOL INDIA LIMITED Share Price - Upstox</t>
+          <t>Aptech Ltd Share Price Today,, APTECHT Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Above All Moving Averages and Now at Upper Circuit: Anmol India Ltd Gains 9.0% in a Single Session - MarketsMojo</t>
+          <t>Aptech Ltd Share Price Today,, APTECHT Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
+          <t>Aptech Limited submits FY26 sustainability report detailing ESG metrics - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Above All Moving Averages and Now at Upper Circuit: Anmol India Ltd Gains 9.0% in a Single Session - MarketsMojo</t>
+          <t>Aptech files FY26 annual report with BSE, NSE - scanx.trade</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+          <t>ONEGLOBAL Stock Price and Chart — NSE:ONEGLOBAL - tradingview.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1158,68 +1142,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DAVANGERE.NS</t>
+          <t>YASHO.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar Company Limited</t>
+          <t>Yasho Industries Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.950000047683716</v>
+        <v>4260</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.099999904632568</v>
+        <v>4286.89990234375</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1.899999976158142</v>
+        <v>3921</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2.099999904632568</v>
+        <v>3934.10009765625</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.909999966621399</v>
+        <v/>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.099999904632568</v>
+        <v>3934.10009765625</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>36081250</v>
+        <v>38529</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar FY26 net profit falls to ₹850.66 lakh - scanx.trade</t>
+          <t>Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar schedules 55th AGM for September 12, 2026 - scanx.trade</t>
+          <t>Yasho Industries doubles FY27 capex to ₹250 crore on strong demand - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Sugar stock under ₹10 jumps 6% despite sideways trend in Indian stock market | Here's why - Livemint</t>
+          <t>Yasho Industries Ltd. Stock News - valueresearchonline.com</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar Share Price Today: Price Rise and Valuation - Univest</t>
+          <t>Yasho Industries seeks ₹1,250 crore borrowing limit hike via postal ballot - scanx.trade</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar Slips 1.5% to ₹1.93, Holds Above Key Support (DAVANGERE.NS) - Ichimoku TK Cross - siam.in</t>
+          <t>Yasho Industries Upgraded to Buy on Strong Financials and Bullish Technicals - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1227,64 +1211,60 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE.NS</t>
+          <t>XTGLOBAL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited</t>
+          <t>Xtglobal Infotech Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>431</v>
+        <v>29.54999923706055</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>511.7999877929688</v>
+        <v>31.79999923706055</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>428.2000122070312</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>478.5</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>435.7999877929688</v>
+        <v/>
       </c>
       <c r="J12" s="2" t="n">
-        <v>478.5</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>10362562</v>
+        <v>74999</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price - Upstox</t>
+          <t>XTGLOBAL.NS Q2 2026 Earnings: Revenue Surges 57.48% YoY to ₹368.72 Crore; Stock Declines 3.92% - Pretax Income Report - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price - Upstox</t>
+          <t>XTGlobal Infotech Board Declares Interim Dividend and Confirms Key Reappointments - TipRanks</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
-        </is>
-      </c>
+          <t>XTGlobal Infotech Board Declares Interim Dividend and Confirms Key Reappointments - TipRanks</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1292,68 +1272,56 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NAGREEKCAP.NS</t>
+          <t>XPROINDIA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure Limited</t>
+          <t>Xpro India Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>22.97999954223633</v>
+        <v>1294.699951171875</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>25.14999961853027</v>
+        <v>1295</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>22.30999946594238</v>
+        <v>1263.099975585938</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>24.89999961853027</v>
+        <v>1276.900024414062</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.8700008392334</v>
+        <v/>
       </c>
       <c r="J13" s="2" t="n">
-        <v>24.89999961853027</v>
+        <v>1276.900024414062</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>17663</v>
+        <v>32026</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure (NAGREEKCAP.NS) Gains 1.86% – Key Levels to Watch - Price Target - siam.in</t>
+          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure Slips 1.84% to ₹22.38: Key Support and Resistance Levels in Focus - MFI Overbought - siam.in</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Investors Aren't Entirely Convinced By Nagreeka Capital &amp; Infrastructure Ltd.'s (NSE:NAGREEKCAP) Earnings - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Nagreeka Capital &amp; Infrastructure Slips 1.84% to ₹22.38: Key Support and Resistance Levels in Focus - MFI Overbought - siam.in</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Nagreeka Capital &amp; Infrastructure Limited (NAGREEKCAP.NS) Q2 2025 Earnings: Positive EPS in a Revenue Decline Quarter - Operating Margin Analysis - vinanet.vn</t>
-        </is>
-      </c>
+          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1361,68 +1329,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>XELPMOC.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>Xelpmoc Design And Tech Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>49.9900016784668</v>
+        <v>77.5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>58.9900016784668</v>
+        <v>78.15000152587891</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>48.4900016784668</v>
+        <v>76.25</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>54.29999923706055</v>
+        <v>77</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>49.91999816894531</v>
+        <v/>
       </c>
       <c r="J14" s="2" t="n">
-        <v>54.29999923706055</v>
+        <v>77</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>11275075</v>
+        <v>6433</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.77</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price | Ugar Sugar Works Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>Xelpmoc FY26 revenue falls 4.1% to ₹37.4 million - scanx.trade</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price | Ugar Sugar Works Ltd. Stock Analysis &amp; Recommendation - MarketsMojo</t>
+          <t>Xelpmoc Design and Tech Ltd (NSE: XELPMOC): AI Services Watch - Kalkine India</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
+          <t>Xelpmoc (XELPMOC.NS) Financial Update: The Report Provides a New Financial Snapshot; Trading Move: Shares Close 8.61% Higher in Latest Trading - Earnings Per Share - siam.in</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
+          <t>Xelpmoc Design &amp; Tech approves ₹14.58 crore sale of Woovly India stake - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Ugar (UGARSUGAR.NS) Earnings Update: The Report Provides a New Financial Snapshot in the Reported Period; Trading Response: Shares Finish 4.05% Down in the Latest Reading - Financial Data - siam.in</t>
+          <t>Xelpmoc Design and Tech Publishes Q1 FY2026 Unaudited Results and Confirms SEBI-Compliant Disclosure - The Globe and Mail</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1430,68 +1398,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK.NS</t>
+          <t>WSTCSTPAPR.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK LIMITED</t>
+          <t>West Coast Paper Mills Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>634.4000244140625</v>
+        <v>734</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>575</v>
+        <v>706.2000122070312</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>628.1500244140625</v>
+        <v>712.7000122070312</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>585.9000244140625</v>
+        <v/>
       </c>
       <c r="J15" s="2" t="n">
-        <v>628.1500244140625</v>
+        <v>712.7000122070312</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>4433382</v>
+        <v>214791</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>7.21</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Sunil Singhania's Abakkus acquires 1.48% stake in BlackBuck; Jamna Auto promoters sell 5% shares - Moneycontrol.com</t>
+          <t>West (WSTCSTPAPR.NS) Chart: Closes 0.12% Lower at ₹605.40 in Latest Trading; the Current Price Sits Inside the Supplied Technical Range for the Current Session - Technical Analysis Picks - siam.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Accel India Sells 1.48% BlackBuck Stake For Rs 155.5 Cr; Abakkus Snaps Up Shares - BW Disrupt</t>
+          <t>West Coast Paper Mills 52 Week High Streak Extends Again - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK LIMITED Share Price - Upstox</t>
+          <t>West Coast Paper Mills Share Price: fresh 52-week high at Rs - Univest</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Accel India Sells 1.48% BlackBuck Stake For Rs 155.5 Cr; Abakkus Snaps Up Shares - BW Disrupt</t>
+          <t>West (WSTCSTPAPR.NS) Snapshot: Moves 3.45% Up to ₹636.25 for the Current Session; Price Setup: Support at ₹604.44 and Resistance at ₹668.06 Frame the Range - Triple Bottom - siam.in</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK Share Price News: Fundamentals and Sector Gap - Univest</t>
+          <t>West Coast Paper Mills Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1499,64 +1467,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSIND.NS</t>
+          <t>WSI.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Kirloskar Industries Limited</t>
+          <t>W S Industries (I) Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3575</v>
+        <v>60.20000076293945</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4055</v>
+        <v>62.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3562.300048828125</v>
+        <v>59</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3828.300048828125</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3576.800048828125</v>
+        <v/>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3828.300048828125</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>639315</v>
+        <v>51055</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7.03</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSIND Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>Industries (WSI.NS) Reported Quarter: The Report Provides a New Financial Snapshot for the Current Session; Reported Share Move: Shares Finish 0.91% Up at the Close - Operating Income Trends - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Kirloskar Industries files FY26 BRSR with reduced energy use - scanx.trade</t>
+          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Kirloskar Industries Share Price rises 13.14%: analysis - Univest</t>
+          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Kirloskar Industries files FY26 BRSR with reduced energy use - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>WestStar Industrial (ASX: WSI) Surges 60.71%: What’s Driving the Small-Cap Stock Higher? - Kalkine</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Weststar Industrial Ltd (ASX: WSI) Share Price, WSI Stock News, WSI Share Price &amp; Updates - kalkine.ca</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1564,68 +1536,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TEXMOPIPES.NS</t>
+          <t>WPIL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Texmo Pipes and Products Limited</t>
+          <t>WPIL Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>56.25</v>
+        <v>435.25</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>62.9900016784668</v>
+        <v>440.3999938964844</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>55.5</v>
+        <v>431.0499877929688</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.08000183105469</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>56.43999862670898</v>
+        <v/>
       </c>
       <c r="J17" s="2" t="n">
-        <v>60.08000183105469</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1133568</v>
+        <v>19772</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Texmo Pipes &amp; Products Ltd (TEXMOPIPES): Signals to Track - Kalkine India</t>
+          <t>1:10 Stock Split: Record Date In 3 Days On 12 July; Buy Mukul Agarwal Portfolio Stock? - Goodreturns</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Texmo Pipes Wins Strong Shareholder Backing for FY26 Accounts at 18th AGM - TipRanks</t>
+          <t>1:10 Stock Split: Record Date In 3 Days On 12 July; Buy Mukul Agarwal Portfolio Stock? - Goodreturns</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>TEXMO PIPES Share Price - Upstox</t>
+          <t>WPIL Ltd. Stock News - valueresearchonline.com</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Texmo Pipes Share Price rise: valuation and sector view - Univest</t>
+          <t>WPIL (WPIL.NS) Financial Update: The Latest Report Adds New Financial Reference Points for This Review; Post-Report: Shares Finish 1.33% Lower on the Day - Earnings Acceleration Picks - siam.in</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
+          <t>WPIL Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1633,68 +1605,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>AIIL.NS</t>
+          <t>WORTHPERI.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Authum Investment &amp; Infrastructure Limited</t>
+          <t>Worth Peripherals Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>508</v>
+        <v>144.3600006103516</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>558</v>
+        <v>147.9799957275391</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>503</v>
+        <v>143</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>544.3499755859375</v>
+        <v>147.9799957275391</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>512.2999877929688</v>
+        <v/>
       </c>
       <c r="J18" s="2" t="n">
-        <v>544.3499755859375</v>
+        <v>147.9799957275391</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5994616</v>
+        <v>1591</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>AIIL Share Price Today: price rise, fundamentals and sector - Univest</t>
+          <t>Worth Peripherals confirms no promoter encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>AIIL Share Price Today: price rise, fundamentals and sector - Univest</t>
+          <t>Worth Peripherals confirms no promoter encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Authum Investment Share Price Decline and Stock Analysis - Univest</t>
+          <t>Worth Peripherals Share Price Drops; Price Fall Analysis - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Authum Investment &amp; Infrastructure Share Price rises 4.95% - Univest</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Authum Investment Invests ₹101.6 Cr in ISARC Rights Issue - InvestyWise</t>
-        </is>
-      </c>
+          <t>Worth Peripherals recommends ₹1 per share final dividend for FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1702,68 +1670,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ORIENTTECH.NS</t>
+          <t>WOCKPHARMA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Orient Technologies Limited</t>
+          <t>Wockhardt Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>237.1799926757812</v>
+        <v>2190</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>274.5</v>
+        <v>2193.800048828125</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>233.6999969482422</v>
+        <v>2090.10009765625</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>249.6399993896484</v>
+        <v>2106.10009765625</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>235.3600006103516</v>
+        <v/>
       </c>
       <c r="J19" s="2" t="n">
-        <v>249.6399993896484</v>
+        <v>2106.10009765625</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>8430139</v>
+        <v>566354</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>ORIENT TECHNOLOGIES LTD Share Price - Live NSE: ORIENTTECH Stock Price &amp; Chart - Upstox</t>
+          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>ORIENT TECHNOLOGIES LTD Share Price - Live NSE: ORIENTTECH Stock Price &amp; Chart - Upstox</t>
+          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Orient Technologies Share Price Today: market cap, valuation - Univest</t>
+          <t>Wockhardt Ltd. Share Price Rise Streak: valuation and sector - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Orient (ORIENTTECH.NS) Quarterly Results: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Reaction: Shares Move Lower 0.35% in Latest Trading - Next Quarter Guidance - siam.in</t>
+          <t>Wockhardt Share Price Today: 3.57% Rise, Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Orient (ORIENTTECH.NS) Today: Climbs 0.27% to ₹244.30 in the Latest Session; Level Watch: Support at ₹232.09 and Resistance at ₹256.52 Frame the Range in the Current Update - Delta Hedging - siam.in</t>
+          <t>Wockhardt Ltd Share Price Rise: Price Action and Valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1771,68 +1739,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SOLARA.NS</t>
+          <t>WINDLAS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Limited</t>
+          <t>Windlas Biotech Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>707.2000122070312</v>
+        <v>1137</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>759.5499877929688</v>
+        <v>1144</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>697.4000244140625</v>
+        <v>1102.050048828125</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>749.1500244140625</v>
+        <v>1103.75</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>707.25</v>
+        <v/>
       </c>
       <c r="J20" s="2" t="n">
-        <v>749.1500244140625</v>
+        <v>1103.75</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1159874</v>
+        <v>47283</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5.92</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Solara 52 Week High Streak With Sector and Peer Context - Univest</t>
+          <t>Windlas Biotech Q1FY27 revenue hits record ₹248 crore, up 18% - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Solara 52 Week High Streak With Sector and Peer Context - Univest</t>
+          <t>Windlas Biotech Q1FY27 revenue hits record ₹248 crore, up 18% - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. Stock News - Value Research</t>
+          <t>Volume shocker stocks: Why share price of EMS, Expleo Solutions, Windlas Biotech, AKI India, Heritage Foods are up today - tradingview.com</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Solara Active Pharma Sciences Ltd. (SOLARA) Share Price hits fresh 52-week high as stock trades at Rs 738.8 - Univest</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Solara Active Pharma Sciences Share Price today after rise - Univest</t>
-        </is>
-      </c>
+          <t>Windlas Biotech Restores Operations After Labour Unrest - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1840,61 +1804,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RPEL.NS</t>
+          <t>WHIRLPOOL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Limited</t>
+          <t>Whirlpool of India Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1773.5</v>
+        <v>770.9500122070312</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1854.099975585938</v>
+        <v>771.2000122070312</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1725.900024414062</v>
+        <v>754.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1845.199951171875</v>
+        <v>754.9000244140625</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1743.5</v>
+        <v/>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1845.199951171875</v>
+        <v>754.9000244140625</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>171393</v>
+        <v>91939</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Ltd Share Price - Business Today</t>
+          <t>Whirlpool (WHR) Stock Could Be A Bargain Based On Cash Flow Recovery - simplywall.st</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Ltd Share Price - Business Today</t>
+          <t>Whirlpool (WHR) Stock Could Be A Bargain Based On Cash Flow Recovery - simplywall.st</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Raghav Productivity Enhancers (NSE:RPEL) Makes An Interesting Case - simplywall.st</t>
+          <t>Whirlpool stock hits 52-week low at 35.37 USD - Investing.com</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Share Price at 52-Week High - Univest</t>
+          <t>Whirlpool Stock Plunges 7% as Massive Debt Load Fuels Investor Concerns - TIKR.com</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>RPEL to set up 3.5 lakh MTPA silica ramming mass manufacturing facility in Odisha - Business Standard</t>
+          <t>Whirlpool continues bruising Wall Street run, sets second low in a row - Moody on the Market</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1879,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2021,7 +1985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2029,68 +1993,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SRGHFL.NS</t>
+          <t>SPELS.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Limited</t>
+          <t>SPEL Semiconductor Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>156</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>156</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>156</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>156</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>195</v>
+        <v>145.6499938964844</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>156</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>11743</v>
+        <v>13606</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Improved Earnings Required Before SRG Housing Finance Limited (NSE:SRGHFL) Shares Find Their Feet - simplywall.st</t>
+          <t>SPELS Stock Price and Chart — NSE:SPELS - tradingview.com</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Mar 2026 Earnings: EPS at ₹5.89, Stock Gains Amid Steady Performance - Earnings Surprise Score - vinanet.vn</t>
+          <t>SPEL Semiconductor Ltd. (SPELS) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Mar 2026 Earnings: EPS at ₹5.89, Stock Gains Amid Steady Performance - Earnings Surprise Score - vinanet.vn</t>
+          <t>Technical Analysis of SPEL Semiconductor Limited (NSE:SPELS) - tradingview.com</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>SRGHFL Stock Price and Chart — NSE:SRGHFL - TradingView</t>
+          <t>SPEL Semiconductor Ltd. (SPELS) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Mar 2026 Earnings: EPS of ₹5.89 Reported; Stock Declines 2.7% - Earnings Surprise Score - vinanet.vn</t>
+          <t>SPEL Semiconductor Ltd. (SPELS) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2098,68 +2062,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE.NS</t>
+          <t>LASA.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Limited</t>
+          <t>Lasa Supergenerics Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>512.4000244140625</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>524.9500122070312</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>509.7000122070312</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3900142</v>
+        <v>16158</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-19.99</v>
+        <v>-4.91</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE PICTURES LIMITED Share Price - Upstox</t>
+          <t>Lasa Supergenerics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Metals (ASX:SHN) in Focus: Could This ASX Resources Stock Be One to Watch in September 2026? - Kalkine</t>
+          <t>Lasa Supergenerics appoints Janardan Savala as executive director - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Lasa (LASA.NS) Latest: Posts a 1.57% Gain to ₹7.10 on the Day; Next Test: the Supplied Trading Band Runs From ₹6.74 to ₹7.46 in the Available Record - Pre-Earnings Momentum - siam.in</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE Share Price Today - SUNSHINE PICTURES LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Lasa Supergenerics appoints Janardan Savala as executive director - scanx.trade</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPO Listing: Shares List at 9.97% Premium on NSE, Fall Short of Grey-Market Hopes - India Infoline</t>
+          <t>Lasa Supergenerics accepts Ganesh Potdar resignation as WTD - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2167,68 +2131,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KOTIC.NS</t>
+          <t>WHBRADY.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial Corporation Limited</t>
+          <t>WH Brady &amp; Company Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>148.7599945068359</v>
+        <v>481.2999877929688</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>148.7599945068359</v>
+        <v>481.2999877929688</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>130.5500030517578</v>
+        <v>477</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>133.8200073242188</v>
+        <v>477</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>151.2100067138672</v>
+        <v>480.5</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>133.8200073242188</v>
+        <v>477</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>122378</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-11.5</v>
+        <v>-0.73</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial Corporation Stock Falls Below SMA - Kalkine India</t>
+          <t>W.H. Brady &amp; Co. Ltd. (WHBRADY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial Corporation Stock Falls Below SMA - Kalkine India</t>
+          <t>W.H. Brady &amp; Co. Ltd. (WHBRADY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What's fuelling the rally? - TradingView</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial Corporation (KOTIC.NS) Slips 1.23% to ₹134.79; Support at ₹128.05 in Focus - Bullish Sentiment - siam.in</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial Corporation Share Price rises 10.14% - Univest</t>
-        </is>
-      </c>
+          <t>W.H. Brady &amp; Co. Ltd. (WHBRADY) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2236,68 +2192,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>ZENITHSTL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Limited</t>
+          <t>Zenith Steel Pipes &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.75</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>13.75</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.75</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>13.75</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15.27000045776367</v>
+        <v/>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.75</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>370055</v>
+        <v>40936</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
+          <t>Zenith Steel Pipes Holds Above ₹5 Support; Resistance at ₹5.61 in Focus - Supply Zone - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
+          <t>Zenith Steel Pipes Sets Virtual AGM for September 30, 2026 - TipRanks</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price Fall Streak With Fresh Weakness - Univest</t>
+          <t>Zenith (ZENITHSTL.NS) EPS and Revenue: The Report Supplies Updated Headline Figures for This Review; Market Reaction: Shares Move 1.46% Down in the Latest Session - Fiscal Year Earnings - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Lower Circuit: Chart Analysis - Kalkine India</t>
+          <t>Zenith (ZENITHSTL.NS) Earnings Update: The Company Reports Its Latest Available Figures; Shares Finish 0.37% Up - Financial Summary - siam.in</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price update: price action and valuation - Univest</t>
+          <t>Zenith Steel Pipes Sets Virtual AGM for September 30, 2026 - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2305,68 +2261,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>ZENITHEXPO.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Limited</t>
+          <t>Zenith Exports Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1510</v>
+        <v>207.0500030517578</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1510</v>
+        <v>207.0500030517578</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1372</v>
+        <v>194.75</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1381</v>
+        <v>196.0599975585938</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1520.400024414062</v>
+        <v/>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1381</v>
+        <v>196.0599975585938</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6390480</v>
+        <v>158</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-9.17</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Ltd (COCHINSHIP) Share Price - Business Today</t>
+          <t>Etsy (ETSY) Shares: Ends Down by 0.22% at $81.03 for the Current Session; Next Test: $76.98 and $85.08 Define the Nearby Reference Levels under the Current Snapshot - Aggressive Growth Picks - siam.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Seals BRICS-Stage Joint Venture With Drydocks World Dubai - The Globe and Mail</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Cochin Shipyard Seals BRICS-Stage Joint Venture With Drydocks World Dubai - The Globe and Mail</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Cochin Shipyard Share Price Today, August 24, 2026: COCHINSHIP Closes at ₹1,514 on NSE - The Eastern Herald</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Cochin Shipyard shares crash nearly 9% - Is it opportunity to buy? Should you take fresh entry? Expert suggests this - TradingView</t>
-        </is>
-      </c>
+          <t>Etsy (ETSY) Shares: Ends Down by 0.22% at $81.03 for the Current Session; Next Test: $76.98 and $85.08 Define the Nearby Reference Levels under the Current Snapshot - Aggressive Growth Picks - siam.in</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2374,68 +2318,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SSDL.NS</t>
+          <t>ZEEMEDIA.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Limited</t>
+          <t>Zee Media Corporation Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>71</v>
+        <v>7.5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>72.69999694824219</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61.36999893188477</v>
+        <v>7.309999942779541</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.59000015258789</v>
+        <v>7.329999923706055</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>67.83999633789062</v>
+        <v/>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62.59000015258789</v>
+        <v>7.329999923706055</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>560099</v>
+        <v>926306</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-7.74</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Stock Price Reversal Analysis - Kalkine India</t>
+          <t>Acacia Partners holds 5.51% in Zee Media after warrant conversion - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Stock Price Reversal Analysis - Kalkine India</t>
+          <t>Acacia Partners holds 5.51% in Zee Media after warrant conversion - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Jun 2026 Earnings: Revenue at ₹147.59 crore and EPS of ₹1.67 as Stock Slips 4.7% - siam.in</t>
+          <t>Zee (ZEEMEDIA.NS) Quarter in Focus: Available Data Shows the Latest Reported Performance for This Review; Market Response: Shares Finish 0.21% Lower in the Latest Reading - Earnings Beat Streak - siam.in</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Zee Media Corporation files FY26 business responsibility report with exchanges - scanx.trade</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Share Price today: price action view - Univest</t>
+          <t>Zee Business. . Zee Media : Q1 के दमदार नतीजों के क्या रहे ट्रिगर्स? देखिए Zee Media के CEO, रक्तिम दास से खास बातचीत Watch Full Interview : https://youtu.be/gFQ3lrHMS6k?si=XNZxfntGAX_9zwkg #StockMarket #ZeeMedia #anilsi - facebook.com</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2443,68 +2387,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>ZEEL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>Zee Entertainment Enterprises Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>195</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>176.5</v>
+        <v>78.26999664306641</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>180.6900024414062</v>
+        <v>78.34999847412109</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>195.25</v>
+        <v/>
       </c>
       <c r="J8" s="2" t="n">
-        <v>180.6900024414062</v>
+        <v>78.34999847412109</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>7318</v>
+        <v>8062161</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.46</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
+          <t>ZEEL tanks 15% as Chandra's insolvency resolution plan faces fresh hurdle - Business Standard</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
+          <t>ZEE Entertainment shares fell 6% today; here's why - Business Today</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Ltd is Rated Sell - MarketsMojo</t>
+          <t>ZEE Entertainment shares fell 6% today; here's why - Business Today</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
+          <t>ZEEL shares dip after promoter group gets Rs 660 crore warrant allotment - Indian Television Dot Com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>Zee Entertainment Enterprises Ltd. (ZEEL) Share Price Rises 6.4% Today - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2512,68 +2456,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>AARON.NS</t>
+          <t>YUKEN.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Aaron Industries Limited</t>
+          <t>Yuken India Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>137</v>
+        <v>1124</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>137</v>
+        <v>1124</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>121.1600036621094</v>
+        <v>1046</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>126.9400024414062</v>
+        <v>1050.050048828125</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>136.9499969482422</v>
+        <v/>
       </c>
       <c r="J9" s="2" t="n">
-        <v>126.9400024414062</v>
+        <v>1050.050048828125</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>34810</v>
+        <v>20270</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-7.31</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Aaron Industries confirms Aug 14 dividend record date for FY26 - scanx.trade</t>
+          <t>Yuken India Ltd. Stock News - valueresearchonline.com</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>‘It Worked Out the Way That It Should Of’ – Aaron Gordon Shares Mindset Heading to 2026-27 Season, Comments on Exit of Beloved Teammate - Yahoo Sports</t>
+          <t>Yuken India Limited Announces Redesignation of Yoshitake Tanaka from Non-Executive - Non-Independent Director to Executive Director Designated as Whole-Time Director, Effective October 1, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Box CEO Aaron Levie sells $513,660 in company stock - Investing.com India</t>
+          <t>Yuken India publishes 50th AGM notice for September 10, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Aaron Industries Share Price Falls 8.36%: Stock Analysis - Univest</t>
+          <t>Yuken India Ltd. Share Price Jumps; Fundamentals Checked - Univest</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>‘It Worked Out the Way That It Should Of’ – Aaron Gordon Shares Mindset Heading to 2026-27 Season, Comments on Exit of Beloved Teammate - Yahoo Sports</t>
+          <t>Yuken India Consolidated June 2026 Net Sales at Rs 134.33 crore, up 28.48% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2581,68 +2525,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KENNAMET.NS</t>
+          <t>YESBANK.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kennametal India Limited</t>
+          <t>Yes Bank Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>5000</v>
+        <v>23.68000030517578</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5000</v>
+        <v>23.89999961853027</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4660</v>
+        <v>22.98999977111816</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4682.39990234375</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5027.89990234375</v>
+        <v/>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4682.39990234375</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>70326</v>
+        <v>68264402</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-6.87</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Kennametal (KENNAMET.NS) Financial Update: The Company Releases Its Current Earnings Data for This Review; Share Move: Shares Move 8.34% Up for the Current Session - Product Revenue Analysis - siam.in</t>
+          <t>YESBANK Share Price News: today’s gain and sector context - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Kennametal India Share Price Today: Price Fall Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Kennametal (KENNAMET.NS) Earnings Reading: The Report Provides a New Financial Snapshot in the Latest Reading; Trading Move: Shares Rise 3.25% in the Latest Session - Pre-Earnings Setup - siam.in</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Kennametal India Share Price today: price and valuation - Univest</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Kennametal India Share Price Today: Price Fall Analysis - Univest</t>
-        </is>
-      </c>
+          <t>YESBANK Share Price News: today’s gain and sector context - Univest</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2650,64 +2582,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SUVIDHAA.NS</t>
+          <t>YATHARTH.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve Limited</t>
+          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.470000028610229</v>
+        <v>1000</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.470000028610229</v>
+        <v>1024</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2.190000057220459</v>
+        <v>977.7999877929688</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2.25</v>
+        <v>990.4000244140625</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2.410000085830688</v>
+        <v/>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.25</v>
+        <v>990.4000244140625</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>184883</v>
+        <v>503515</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-6.64</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa (SUVIDHAA.NS) Earnings Snapshot: The Company Reports Its Latest Available Figures in the Latest Reading; Market Reaction: The Stock Records a 1.26% Increase on the Day - Guidance Update - siam.in</t>
+          <t>Yatharth Hospital board to discuss growth plans and fund raising on Sep 17 - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve Sets September 30 Virtual AGM, Closes Books for FY 2025-26 Decisions - TipRanks</t>
+          <t>Yatharth Hospital board to discuss growth plans and fund raising on Sep 17 - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve submits FY26 annual report, loss narrows 39% - scanx.trade</t>
+          <t>Yatharth Hospital shares jump 5% as Aster, Advent likely eye controlling stake - The Economic Times</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve Sets September 30 Virtual AGM, Closes Books for FY 2025-26 Decisions - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Aster, Advent eye controlling stake in Yatharth Hospital, says report; shares rise 4.5% - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Yatharth Hospital gains 6% to new high as Aster, Advent eye majority stake - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2715,60 +2651,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>BIOFILCHEM.NS</t>
+          <t>YASHO.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals Limited</t>
+          <t>Yasho Industries Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>37.79999923706055</v>
+        <v>4260</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>37.79999923706055</v>
+        <v>4286.89990234375</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>32.36000061035156</v>
+        <v>3921</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>34.5099983215332</v>
+        <v>3934.10009765625</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.79000091552734</v>
+        <v/>
       </c>
       <c r="J12" s="2" t="n">
-        <v>34.5099983215332</v>
+        <v>3934.10009765625</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>173376</v>
+        <v>38529</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Biofil (BIOFILCHEM.NS) Technicals: Moves 0.87% Lower to ₹32.06 at the Close; Next Test: the ₹30.46 to ₹33.66 Range Remains in Focus in Latest Trading - Fibonacci Time Zone - siam.in</t>
+          <t>Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
+          <t>Yasho Industries doubles FY27 capex to ₹250 crore on strong demand - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Yasho Industries Ltd. Stock News - valueresearchonline.com</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries seeks ₹1,250 crore borrowing limit hike via postal ballot - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Yasho Industries Upgraded to Buy on Strong Financials and Bullish Technicals - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2776,68 +2720,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GOACARBON.NS</t>
+          <t>XTGLOBAL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Goa Carbon Limited</t>
+          <t>Xtglobal Infotech Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>434.7000122070312</v>
+        <v>29.54999923706055</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>457</v>
+        <v>31.79999923706055</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>408.9500122070312</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>413.3999938964844</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>440.25</v>
+        <v/>
       </c>
       <c r="J13" s="2" t="n">
-        <v>413.3999938964844</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>164355</v>
+        <v>74999</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Goa Carbon 20% Move: Key Chart Analysis - Kalkine India</t>
+          <t>XTGLOBAL.NS Q2 2026 Earnings: Revenue Surges 57.48% YoY to ₹368.72 Crore; Stock Declines 3.92% - Pretax Income Report - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Goa Carbon FY26 Results: Income rises 36%, loss widens to ₹48.2 crore - scanx.trade</t>
+          <t>XTGlobal Infotech Board Declares Interim Dividend and Confirms Key Reappointments - TipRanks</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Goa (GOACARBON.NS) Price: Finishes 0.67% Up at ₹359.85 at the Close; the Supplied Trading Band Runs From ₹341.86 to ₹377.84 - Range Breakout - siam.in</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Goa (GOACARBON.NS) Financial Results: The Company Publishes Its Latest Results under the Current Snapshot; Market Response: The Stock Gains 1.63% in the Latest Reading - Earnings Recovery Stocks - siam.in</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Goa Carbon Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
-        </is>
-      </c>
+          <t>XTGlobal Infotech Board Declares Interim Dividend and Confirms Key Reappointments - TipRanks</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2845,68 +2781,56 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IVC.NS</t>
+          <t>XPROINDIA.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>IL&amp;FS Investment Managers Limited</t>
+          <t>Xpro India Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9.569999694824219</v>
+        <v>1294.699951171875</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>9.569999694824219</v>
+        <v>1295</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9.050000190734863</v>
+        <v>1263.099975585938</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>9.109999656677246</v>
+        <v>1276.900024414062</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>9.680000305175781</v>
+        <v/>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.109999656677246</v>
+        <v>1276.900024414062</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1429459</v>
+        <v>32026</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.89</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IL&amp;FS discloses no new encumbrance on IIML shares in FY26 - scanx.trade</t>
+          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Texmaco Rail bags Rs 78-cr order from IVC Logistics - Business Standard</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>IL&amp;FS Investment Managers Limited (IVC.NS) Q2 2025 Earnings: Revenue Declines 44% YoY but EPS Remains Positive at ₹0.42 - Earnings Revision Upgrade - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Texmaco Rail bags Rs 78-cr order from IVC Logistics - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Texmaco Rail bags ₹62 crore wagon order from IVC Logistics - ET Infra</t>
-        </is>
-      </c>
+          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2914,64 +2838,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CREATIVEYE.NS</t>
+          <t>XELPMOC.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Creative Eye Limited</t>
+          <t>Xelpmoc Design And Tech Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5.989999771118164</v>
+        <v>77.5</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5.989999771118164</v>
+        <v>78.15000152587891</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5.260000228881836</v>
+        <v>76.25</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>5.71999979019165</v>
+        <v>77</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6.070000171661377</v>
+        <v/>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5.71999979019165</v>
+        <v>77</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>81227</v>
+        <v>6433</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5.77</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Creative (CREATIVEYE.NS) Results Versus Estimates: The Latest Report Adds New Financial Reference Points under the Current Snapshot; Price Reaction: The Stock Loses 0.81% at the Close - Management Guidance Update - siam.in</t>
+          <t>Xelpmoc FY26 revenue falls 4.1% to ₹37.4 million - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Creative (CREATIVEYE.NS) Range: Retreats 0.81% to ₹6.15 in Latest Trading; Range Check: Traders Can Monitor the ₹5.84-₹6.46 Range in the Latest Reading - BPI Bull Correction - siam.in</t>
+          <t>Xelpmoc Design and Tech Ltd (NSE: XELPMOC): AI Services Watch - Kalkine India</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Creative (CREATIVEYE.NS) Range: Retreats 0.81% to ₹6.15 in Latest Trading; Range Check: Traders Can Monitor the ₹5.84-₹6.46 Range in the Latest Reading - BPI Bull Correction - siam.in</t>
+          <t>Xelpmoc (XELPMOC.NS) Financial Update: The Report Provides a New Financial Snapshot; Trading Move: Shares Close 8.61% Higher in Latest Trading - Earnings Per Share - siam.in</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Martin (MMLP) Latest: Closes Nearly Flat at $2.33 in the Available Record; Range Check: the Price Remains Bounded by the Supplied Support and Resistance on the Day - Rectangle Pattern - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Xelpmoc Design &amp; Tech approves ₹14.58 crore sale of Woovly India stake - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Xelpmoc Design and Tech Publishes Q1 FY2026 Unaudited Results and Confirms SEBI-Compliant Disclosure - The Globe and Mail</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2979,68 +2907,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>HEIDELBERG.NS</t>
+          <t>WSTCSTPAPR.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>HeidelbergCement India Limited</t>
+          <t>West Coast Paper Mills Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>150.9499969482422</v>
+        <v>713</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>150.9499969482422</v>
+        <v>734</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>147.8000030517578</v>
+        <v>706.2000122070312</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>149.8000030517578</v>
+        <v>712.7000122070312</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>158.7899932861328</v>
+        <v/>
       </c>
       <c r="J16" s="2" t="n">
-        <v>149.8000030517578</v>
+        <v>712.7000122070312</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>314126</v>
+        <v>214791</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.66</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials stock edges lower as analysts stay positive - ad-hoc-news.de</t>
+          <t>West (WSTCSTPAPR.NS) Chart: Closes 0.12% Lower at ₹605.40 in Latest Trading; the Current Price Sits Inside the Supplied Technical Range for the Current Session - Technical Analysis Picks - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials stock edges lower as analysts stay positive - ad-hoc-news.de</t>
+          <t>West Coast Paper Mills 52 Week High Streak Extends Again - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Cement India Ltd. Stock News - Value Research</t>
+          <t>West Coast Paper Mills Share Price: fresh 52-week high at Rs - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>HeidelbergCement (HEIDELBERG.NS) Shares: Posts a 0.89% Gain to ₹160.40 in the Current Update; Level Watch: the Supplied Trading Band Runs From ₹152.38 to ₹168.42 in the Available Record - Earnings Beat Stocks - siam.in</t>
+          <t>West (WSTCSTPAPR.NS) Snapshot: Moves 3.45% Up to ₹636.25 for the Current Session; Price Setup: Support at ₹604.44 and Resistance at ₹668.06 Frame the Range - Triple Bottom - siam.in</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials Tokenized Stock (xStock) price today, HEI.DEx to USD live price, marketcap and chart - CoinMarketCap</t>
+          <t>West Coast Paper Mills Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3048,68 +2976,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MVGJL.NS</t>
+          <t>WSI.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
+          <t>W S Industries (I) Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>208.6999969482422</v>
+        <v>60.20000076293945</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>208.6999969482422</v>
+        <v>62.5</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>195.6000061035156</v>
+        <v>59</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>197.3699951171875</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>208.7799987792969</v>
+        <v/>
       </c>
       <c r="J17" s="2" t="n">
-        <v>197.3699951171875</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>332881</v>
+        <v>51055</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.47</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>MANOJ VAIBHAV GEM N JEW L Share Price - Live NSE: MVGJL Stock Price &amp; Chart - Upstox</t>
+          <t>Industries (WSI.NS) Reported Quarter: The Report Provides a New Financial Snapshot for the Current Session; Reported Share Move: Shares Finish 0.91% Up at the Close - Operating Income Trends - siam.in</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - TradingView</t>
+          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Manoj Vaibhav Gems 'N' Jewellers (NSE:MVGJL) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Manoj Vaibhav Gems (MVGJL.NS) Gains 4.6% to ₹179.9: Jewelry Stock Rebounds Toward Key Resistance - Bollinger Squeeze - siam.in</t>
+          <t>WestStar Industrial (ASX: WSI) Surges 60.71%: What’s Driving the Small-Cap Stock Higher? - Kalkine</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Manoj (MVGJL.NS) Financial Update: The Company Lists Its Latest Available Figures in the Current Update; Shares Move 1.33% Up in the Latest Reading - Surprise Factor Analysis - siam.in</t>
+          <t>Weststar Industrial Ltd (ASX: WSI) Share Price, WSI Stock News, WSI Share Price &amp; Updates - kalkine.ca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3117,68 +3045,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>JAYAGROGN.NS</t>
+          <t>WPIL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Jayant Agro Organics Limited</t>
+          <t>WPIL Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>257</v>
+        <v>435.25</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>257</v>
+        <v>440.3999938964844</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>239.0899963378906</v>
+        <v>431.0499877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>244.1300048828125</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>258.1799926757812</v>
+        <v/>
       </c>
       <c r="J18" s="2" t="n">
-        <v>244.1300048828125</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>47854</v>
+        <v>19772</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.44</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Share Price news after intraday gain - Univest</t>
+          <t>1:10 Stock Split: Record Date In 3 Days On 12 July; Buy Mukul Agarwal Portfolio Stock? - Goodreturns</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Approves FY26 Accounts and Dividend at Virtual AGM - TipRanks</t>
+          <t>1:10 Stock Split: Record Date In 3 Days On 12 July; Buy Mukul Agarwal Portfolio Stock? - Goodreturns</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Jayant (JAYAGROGN.NS) Closing Review: Rises 0.30% to ₹221.08 in Latest Trading; Support and Resistance: the Supplied Trading Band Runs From ₹210.03 to ₹232.13 in the Latest Reading - ETF Liquidity - siam.in</t>
+          <t>WPIL Ltd. Stock News - valueresearchonline.com</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Jayant (JAYAGROGN.NS) Quarterly Figures: Available Data Shows the Latest Reported Performance in Latest Trading; Trading Response: The Market Price Advances 0.44% in the Latest Session - Analyst Drop Coverage - siam.in</t>
+          <t>WPIL (WPIL.NS) Financial Update: The Latest Report Adds New Financial Reference Points for This Review; Post-Report: Shares Finish 1.33% Lower on the Day - Earnings Acceleration Picks - siam.in</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>how Fair Value analysis spotted 72% gain in Jayant Agro-Organics - Investing.com India</t>
+          <t>WPIL Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3186,68 +3114,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SECMARK.NS</t>
+          <t>WORTHPERI.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SecMark Consultancy Limited</t>
+          <t>Worth Peripherals Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>148</v>
+        <v>144.3600006103516</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>148</v>
+        <v>147.9799957275391</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>141.3099975585938</v>
+        <v>147.9799957275391</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>149.1600036621094</v>
+        <v/>
       </c>
       <c r="J19" s="2" t="n">
-        <v>141.3099975585938</v>
+        <v>147.9799957275391</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2320</v>
+        <v>1591</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.26</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Secmark Consultancy Share Price rises 8.39% today - Univest</t>
+          <t>Worth Peripherals confirms no promoter encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Secmark Consultancy Share Price rises 8.39% today - Univest</t>
+          <t>Worth Peripherals confirms no promoter encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>SecMark Consultancy schedules 15th AGM for September 30, 2026 - scanx.trade</t>
+          <t>Worth Peripherals Share Price Drops; Price Fall Analysis - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Secmark Consultancy Ltd leads losers in 'B' group - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Secmark Consultancy Share Price news: Rs 137 and valuation - Univest</t>
-        </is>
-      </c>
+          <t>Worth Peripherals recommends ₹1 per share final dividend for FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3255,68 +3179,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>WOCKPHARMA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>Wockhardt Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>43.40000152587891</v>
+        <v>2190</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45.4900016784668</v>
+        <v>2193.800048828125</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>41.16999816894531</v>
+        <v>2090.10009765625</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>41.16999816894531</v>
+        <v>2106.10009765625</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>43.43000030517578</v>
+        <v/>
       </c>
       <c r="J20" s="2" t="n">
-        <v>41.16999816894531</v>
+        <v>2106.10009765625</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>20200138</v>
+        <v>566354</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Indo (INDOTHAI.NS) Quarterly Figures: Available Data Shows the Latest Reported Performance at the Close; After Results: The Stock Ends Down 4.99% - CEO Earnings Statement - siam.in</t>
+          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Wockhardt Ltd. Share Price Rise Streak: valuation and sector - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Wockhardt Share Price Today: 3.57% Rise, Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities schedules NCLT hearing for demerger scheme on September 24 - scanx.trade</t>
+          <t>Wockhardt Ltd Share Price Rise: Price Action and Valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 22:01:11 IST</t>
+          <t>2026-09-15 13:25:39 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3324,63 +3248,51 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>GUJENERGY.NS</t>
+          <t>CALSOFT.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>GUJARAT ENERGY LIMITED</t>
+          <t>California Software Company Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>247.9400024414062</v>
+        <v>39.90000152587891</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>249.2100067138672</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>240.3600006103516</v>
+        <v>36.81000137329102</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>241.5899963378906</v>
+        <v>36.9900016784668</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>254.8000030517578</v>
+        <v/>
       </c>
       <c r="J21" s="2" t="n">
-        <v>241.5899963378906</v>
+        <v>36.9900016784668</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1808646</v>
+        <v>371103</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.18</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Gas Share Price - Live NSE: GUJENERGY Stock Price &amp; Chart - Upstox</t>
+          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Gas fixes July 2 record date for GTL share allotment - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Gas fixes July 2 record date for GTL share allotment - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Energy (NSE:GUJENERGY) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Gas Share Price Up 2.36%: Price, Valuation View - Univest</t>
-        </is>
-      </c>
+          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,56 +553,56 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL.NS</t>
+          <t>KANCOTEA.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Kanco Tea &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>549.3499755859375</v>
+        <v>52.31000137329102</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>558.4500122070312</v>
+        <v>56.97999954223633</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>547.4500122070312</v>
+        <v>52.31000137329102</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>547.75</v>
+        <v>56.79999923706055</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v/>
+        <v>52.29000091552734</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>547.75</v>
+        <v>56.79999923706055</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>126424</v>
+        <v>1088</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness Share Price - Live NSE: ZYDUSWELL Stock Price &amp; Chart - upstox.com</t>
+          <t>Diluted shares outstanding of Kanco Tea &amp; Industries Ltd. – NSE:KANCOTEA - TradingView</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness Share Price - Live NSE: ZYDUSWELL Stock Price &amp; Chart - upstox.com</t>
+          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness (ZYDUSWELL.NS) Slips 2.65% to ₹496.65: Approaching Key Support Levels - Institutional Flow Picks - siam.in</t>
+          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited Announces Appointment of Kapil Sharma as Chief Revenue Officer (India and Indian Subcontinent), Effective September 1, 2026 - marketscreener.com</t>
+          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -610,7 +610,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -618,68 +618,64 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AARTECH.NS</t>
+          <t>NTPCGREEN.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Aartech Solonics Limited</t>
+          <t>NTPC Green Energy Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>52.2400016784668</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52.25</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>50.5099983215332</v>
+        <v>85.75</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>51</v>
+        <v>85.86000061035156</v>
       </c>
       <c r="I3" s="2" t="n">
         <v/>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51</v>
+        <v>85.86000061035156</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>24726</v>
+        <v>2072032</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Aartech Solonics Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>NTPC (NTPCGREEN.NS) Session: Loses 0.28% to Close at ₹91.62 in Latest Trading - siam.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Aartech Solonics Ltd (AARTECH): Growth Meets a Cash-Flow Question - Kalkine India</t>
+          <t>NTPC Green shares jump over 3% as it commissions 100 MW power at IRPL plant - Business Upturn</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Aartech Solonics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
+          <t>NTPC (NTPCGREEN.NS) Today: Rises 0.33% to ₹92.00 in Latest Trading; Chart View: Support at ₹87.40 and Resistance at ₹96.60 Frame the Range in the Available Record - Mean Reversion Trade - siam.in</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Aartech Solonics Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - valueresearchonline.com</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Aartech Solonics Ltd. Peer Comparison – Compare with Others - valueresearchonline.com</t>
-        </is>
-      </c>
+          <t>NTPC Green shares jump over 3% as it commissions 100 MW power at IRPL plant - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -687,68 +683,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AARTISURF.NS</t>
+          <t>NTPC.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Aarti Surfactants Limited</t>
+          <t>NTPC Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>506.8999938964844</v>
+        <v>333</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>515</v>
+        <v>333.2999877929688</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>506.8999938964844</v>
+        <v>326.3999938964844</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>510.2000122070312</v>
+        <v>329.5</v>
       </c>
       <c r="I4" s="2" t="n">
         <v/>
       </c>
       <c r="J4" s="2" t="n">
-        <v>510.2000122070312</v>
+        <v>329.5</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>10271</v>
+        <v>8431808</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Aarti Surfactants Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
+          <t>BHEL Board Approves Rs 65 Cr Investment In NTPC Joint Venture - TradingView</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Aarti Surfactants Discloses Resignation of Independent Director Nisha B. Shah - TipRanks</t>
+          <t>BHEL Board Approves Rs 65 Cr Investment In NTPC Joint Venture - TradingView</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Aarti Surfactants incorporates US subsidiary Precision Ingredients Inc - scanx.trade</t>
+          <t>BHEL approves ₹65 crore further investment in NTPC joint venture NBPPL - Livemint</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Aarti Surfactants declares ₹1 per share final dividend for FY26 - scanx.trade</t>
+          <t>NTPC Share Price Today (NTPC) | Live Chart, News &amp; Stock Market - TechGraph</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Aarti Surfactants sets up wholly owned U.S. subsidiary to expand global reach - TipRanks</t>
+          <t>Suzlon Energy vs NTPC Green vs NHPC: Wind, Solar or Hydro? Which Energy Stock Deserves Spot In Your Portfolio? - Goodreturns</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -756,64 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ABINFRA.NS</t>
+          <t>NSLNISP.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild Limited</t>
+          <t>NMDC Steel Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11.34000015258789</v>
+        <v>43.68000030517578</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>11.39999961853027</v>
+        <v>43.68999862670898</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>11.0600004196167</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>11.28999996185303</v>
+        <v>41.45000076293945</v>
       </c>
       <c r="I5" s="2" t="n">
         <v/>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11.28999996185303</v>
+        <v>41.45000076293945</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>60400</v>
+        <v>3741115</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>AB Infrabuild Ltd. Share Price News: Price Action Check - Univest</t>
+          <t>NMDC Steel Share Price - Upstox</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
+          <t>NMDC Steel Share Price - Upstox</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>AB Infrabuild Ltd. Share Price News: Price Rise Analysis - Univest</t>
+          <t>NMDC Steel Share Price Today: Market Cap, P/E, Peer View - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>A B Infrabuild schedules AGM and announces book closure - Business Upturn</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>NMDC Steel Share Price falls 5.42%: price action review - Univest</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>NMDC Steel: Clarifies Stock Price Spurt Amidst Financial Results &amp; Rating Upgrade - InvestyWise</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,68 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ACCURACY.NS</t>
+          <t>NSIL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Accuracy Shipping Limited</t>
+          <t>Nalwa Sons Investments Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.170000076293945</v>
+        <v>5623</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>4.389999866485596</v>
+        <v>5623</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4.170000076293945</v>
+        <v>5400</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4.300000190734863</v>
+        <v>5409.5</v>
       </c>
       <c r="I6" s="2" t="n">
         <v/>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.300000190734863</v>
+        <v>5409.5</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>73822</v>
+        <v>1651</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Cardiff University research shows retailers can dramatically improve stock accuracy and sales by ‘counting smarter’ - Cardiff University</t>
+          <t>Nalwa Sons Investments Holds Gains: Stock Climbs 0.68% to ₹5,721.5 Amid Rangebound Trade - Bear Pennant - siam.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Top Santa Clara, CA Auto Body Repair Specialist Shares Why Interior and Mechanical Accuracy Matters as Much as Exterior Work - FinancialContent</t>
+          <t>Nalwa Sons Investments Holds Gains: Stock Climbs 0.68% to ₹5,721.5 Amid Rangebound Trade - Bear Pennant - siam.in</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>A fingerprint drug test produced no false positives. Intelligent Bio Solutions expects an FDA filing in September. - Stock Titan</t>
+          <t>Nalwa (NSIL.NS): Moves 0.73% Lower to ₹5,682.50; Levels: Traders Can Monitor the ₹5,398.38-₹5,966.62 Range under the Current Snapshot - Channel Projection - siam.in</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Dirty Data Kills Trades: Why Stock DB Accuracy Is the Most Underrated Problem in Financial Technology - nerdbot</t>
+          <t>APOORVA Stock Price and Chart — NSE:APOORVA - TradingView</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Top Santa Clara, CA Auto Body Repair Specialist Shares Why Interior and Mechanical Accuracy Matters as Much as Exterior Work - FinancialContent</t>
+          <t>NSIL Q2 2026 Earnings: Revenue Slides 18% to ₹906.8 Million, EPS at ₹106.13 - Dividend Increase Stocks - siam.in</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -890,56 +890,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AKSHOPTFBR.NS</t>
+          <t>NRBBEARING.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Aksh Optifibre Limited</t>
+          <t>NRB Bearing Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8.600000381469727</v>
+        <v>516</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8.890000343322754</v>
+        <v>516.7999877929688</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8.350000381469727</v>
+        <v>478</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>8.350000381469727</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="I7" s="2" t="n">
         <v/>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.350000381469727</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>281506</v>
+        <v>504747</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Aksh Optifibre narrows FY26 loss, auditors flag unrecognised liabilities - scanx.trade</t>
+          <t>NRB Bearings Ltd. (NRBBEARING) Share Price Trades Within 2% of 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Aksh Optifibre narrows FY26 loss, auditors flag unrecognised liabilities - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Granules India promoter offloads shares worth Rs 1,509 crore; Morgan Stanley picks stake in Lotus Developers - TradingView</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>NRB Bearings Share Price Today: Market Cap and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>NRB Bearings 52 Week High Streak: Second Straight Session - Univest</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Granules India promoter offloads shares worth Rs 1,509 crore; Morgan Stanley picks stake in Lotus Developers - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -947,68 +959,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ALPHAGEO.NS</t>
+          <t>NRAIL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Alphageo (India) Limited</t>
+          <t>N R Agarwal Industries Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>307</v>
+        <v>638</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>319.7999877929688</v>
+        <v>685</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>298.0499877929688</v>
+        <v>631</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>300</v>
+        <v>638.8499755859375</v>
       </c>
       <c r="I8" s="2" t="n">
         <v/>
       </c>
       <c r="J8" s="2" t="n">
-        <v>300</v>
+        <v>638.8499755859375</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>6210</v>
+        <v>113595</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>We Wouldn't Be Too Quick To Buy Alphageo (India) Limited (NSE:ALPHAGEO) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Alphageo (India) Ltd Downgraded to Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Alphageo (India) Ltd Downgraded to Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+          <t>NR Agarwal Industries Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Alphageo (India) Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
+          <t>N R Agarwal Industries appoints Manoj Chauhan as Chief Marketing Officer - scanx.trade</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Alphageo India Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>NR Agarwal Industries Share Price today: key market update - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1016,56 +1028,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>AMBALALSA.NS</t>
+          <t>NPST.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ambalal Sarabhai Enterprises Limited</t>
+          <t>Network People Services Technologies Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>40.5</v>
+        <v>1698.900024414062</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>40.97999954223633</v>
+        <v>1700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>39.25</v>
+        <v>1630</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>39.75</v>
+        <v>1639.5</v>
       </c>
       <c r="I9" s="2" t="n">
         <v/>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39.75</v>
+        <v>1639.5</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>18037</v>
+        <v>27585</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Ambalal (AMBALALSA.NS) Financial Results: The Company Reports Its Latest Available Figures under the Current Snapshot; Market Reaction: Shares Move Lower 2.71% in the Latest Reading - Earnings Beat Alert - siam.in</t>
+          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Ambalal (AMBALALSA.NS) Financial Results: The Company Reports Its Latest Available Figures under the Current Snapshot; Market Reaction: Shares Move Lower 2.71% in the Latest Reading - Earnings Beat Alert - siam.in</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>NPST wins Best Digital Banking Platform at Global Fintech Awards 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>NPST Confirms AGM Notice Dispatch and Annual Report Access for Shareholders - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1073,68 +1097,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>APTECHT.NS</t>
+          <t>NORTHARC.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Aptech Limited</t>
+          <t>Northern Arc Capital Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>90</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>90</v>
+        <v>308.2000122070312</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>86</v>
+        <v>292</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>86.11000061035156</v>
+        <v>294.2000122070312</v>
       </c>
       <c r="I10" s="2" t="n">
         <v/>
       </c>
       <c r="J10" s="2" t="n">
-        <v>86.11000061035156</v>
+        <v>294.2000122070312</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>40301</v>
+        <v>1045892</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Aptech Ltd Share Price Today,, APTECHT Share Price NSE, BSE - Business Today</t>
+          <t>Northern ARC Capital Share Price: 8.39% rise, valuation - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Aptech Ltd Share Price Today,, APTECHT Share Price NSE, BSE - Business Today</t>
+          <t>Northern Arc Capital Q1 FY27 Net Profit Jumps 41% YoY to Record ₹114 Cr - Trade Brains</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Aptech Limited submits FY26 sustainability report detailing ESG metrics - scanx.trade</t>
+          <t>Refex Industries promoter pledges 20.9 lakh shares for collateral - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Aptech files FY26 annual report with BSE, NSE - scanx.trade</t>
+          <t>News by CNBC TV18 on TradingView, 2026-08-31 — cnbctv:acd04171b094b:0 - TradingView</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>ONEGLOBAL Stock Price and Chart — NSE:ONEGLOBAL - tradingview.com</t>
+          <t>Northern Arc Capital Q1 FY27 Net Profit Jumps 41% YoY to Record ₹114 Cr - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1142,68 +1166,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>YASHO.NS</t>
+          <t>NORBTEAEXP.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Limited</t>
+          <t>Norben Tea &amp; Exports Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4260</v>
+        <v>65.90000152587891</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4286.89990234375</v>
+        <v>67.38999938964844</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3921</v>
+        <v>64.5</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>3934.10009765625</v>
+        <v>64.5</v>
       </c>
       <c r="I11" s="2" t="n">
         <v/>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3934.10009765625</v>
+        <v>64.5</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>38529</v>
+        <v>1569</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com</t>
+          <t>Norben Tea &amp; Exports Holds Near ₹65.29 as Stock Trades Within Key Range - Zero Gamma Level - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries doubles FY27 capex to ₹250 crore on strong demand - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Yasho Industries Ltd. Stock News - valueresearchonline.com</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Yasho Industries seeks ₹1,250 crore borrowing limit hike via postal ballot - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Yasho Industries Upgraded to Buy on Strong Financials and Bullish Technicals - MarketsMojo</t>
-        </is>
-      </c>
+          <t>Norben Tea &amp; Exports Holds Near ₹65.29 as Stock Trades Within Key Range - Zero Gamma Level - siam.in</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1211,60 +1223,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>XTGLOBAL.NS</t>
+          <t>NLCINDIA.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Xtglobal Infotech Limited</t>
+          <t>NLC India Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>29.54999923706055</v>
+        <v>264.4500122070312</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>31.79999923706055</v>
+        <v>266.3999938964844</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>29.29999923706055</v>
+        <v>256.2999877929688</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>29.70000076293945</v>
+        <v>261.0499877929688</v>
       </c>
       <c r="I12" s="2" t="n">
         <v/>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29.70000076293945</v>
+        <v>261.0499877929688</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>74999</v>
+        <v>1336337</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>XTGLOBAL.NS Q2 2026 Earnings: Revenue Surges 57.48% YoY to ₹368.72 Crore; Stock Declines 3.92% - Pretax Income Report - siam.in</t>
+          <t>NLC India Share Price - Live NSE: NLCINDIA Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>XTGlobal Infotech Board Declares Interim Dividend and Confirms Key Reappointments - TipRanks</t>
+          <t>NLC India Share Price - Live NSE: NLCINDIA Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>XTGlobal Infotech Board Declares Interim Dividend and Confirms Key Reappointments - TipRanks</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>NLC India Share Price Falls 3.89%: Price, Sector Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>NLC India Files Consolidated Sustainability Report for FY 2025-26 - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>NLC (NLCINDIA.NS) Levels: Records a 1.30% Increase to ₹273.30; Technical View - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1272,56 +1292,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>XPROINDIA.NS</t>
+          <t>NKIND.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Xpro India Limited</t>
+          <t>NK Industries Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1294.699951171875</v>
+        <v>55.09999847412109</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1295</v>
+        <v>59.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1263.099975585938</v>
+        <v>55</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1276.900024414062</v>
+        <v>55.52000045776367</v>
       </c>
       <c r="I13" s="2" t="n">
         <v/>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1276.900024414062</v>
+        <v>55.52000045776367</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>32026</v>
+        <v>1139</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
+          <t>NK Industries Stock Near Key Technical Levels - kalkine.co.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t>NK Industries Stock Near Key Technical Levels - kalkine.co.in</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Spire (SRJN) Q2 2026 Earnings: EPS Comes in Above Forecast in the Current Update; After Results - Vinanet</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1329,68 +1357,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>XELPMOC.NS</t>
+          <t>NIVABUPA.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc Design And Tech Limited</t>
+          <t>Niva Bupa Health Insurance Company Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>77.5</v>
+        <v>79.91999816894531</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>78.15000152587891</v>
+        <v>83.90000152587891</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>76.25</v>
+        <v>79.62999725341797</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>77</v>
+        <v>81.5</v>
       </c>
       <c r="I14" s="2" t="n">
         <v/>
       </c>
       <c r="J14" s="2" t="n">
-        <v>77</v>
+        <v>81.5</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>6433</v>
+        <v>1415602</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc FY26 revenue falls 4.1% to ₹37.4 million - scanx.trade</t>
+          <t>NIVABUPA Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc Design and Tech Ltd (NSE: XELPMOC): AI Services Watch - Kalkine India</t>
+          <t>Earnings call transcript: Niva Bupa posts stronger q1 2027 profit, shares edge up - Investing.com</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc (XELPMOC.NS) Financial Update: The Report Provides a New Financial Snapshot; Trading Move: Shares Close 8.61% Higher in Latest Trading - Earnings Per Share - siam.in</t>
+          <t>Here's Why We Think Niva Bupa Health Insurance (NSE:NIVABUPA) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc Design &amp; Tech approves ₹14.58 crore sale of Woovly India stake - scanx.trade</t>
+          <t>IRDAI Approves Transfer of 14.62 Crore Equity Shares by Fettle Tone LLP in Niva Bupa Health Insurance - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc Design and Tech Publishes Q1 FY2026 Unaudited Results and Confirms SEBI-Compliant Disclosure - The Globe and Mail</t>
+          <t>Potential Upside For Niva Bupa Health Insurance Company Limited (NSE:NIVABUPA) Not Without Risk - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1398,68 +1426,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>WSTCSTPAPR.NS</t>
+          <t>NEXTMEDIA.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>West Coast Paper Mills Limited</t>
+          <t>Next Mediaworks Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>713</v>
+        <v>3.809999942779541</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>734</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>706.2000122070312</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>712.7000122070312</v>
+        <v>3.829999923706055</v>
       </c>
       <c r="I15" s="2" t="n">
         <v/>
       </c>
       <c r="J15" s="2" t="n">
-        <v>712.7000122070312</v>
+        <v>3.829999923706055</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>214791</v>
+        <v>15210</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>West (WSTCSTPAPR.NS) Chart: Closes 0.12% Lower at ₹605.40 in Latest Trading; the Current Price Sits Inside the Supplied Technical Range for the Current Session - Technical Analysis Picks - siam.in</t>
+          <t>Next Mediaworks Q1FY26 loss narrows to ₹88 lakh as going concern risk persists - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>West Coast Paper Mills 52 Week High Streak Extends Again - Univest</t>
+          <t>Next Mediaworks Q1FY26 loss narrows to ₹88 lakh as going concern risk persists - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>West Coast Paper Mills Share Price: fresh 52-week high at Rs - Univest</t>
+          <t>Next (NEXTMEDIA.NS) Latest Quarter: The Latest Report Adds New Financial Reference Points in the Latest Reading; Post-Report: The Stock Gains 1.29% in the Latest Session - Earnings Outlook Update - siam.in</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>West (WSTCSTPAPR.NS) Snapshot: Moves 3.45% Up to ₹636.25 for the Current Session; Price Setup: Support at ₹604.44 and Resistance at ₹668.06 Frame the Range - Triple Bottom - siam.in</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>West Coast Paper Mills Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
+          <t>Next Mediaworks dispatches FY26 annual report via weblink for unregistered shareholders - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1467,68 +1491,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>WSI.NS</t>
+          <t>NITCO.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>W S Industries (I) Limited</t>
+          <t>Nitco Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>60.20000076293945</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>62.5</v>
+        <v>94.02999877929688</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>59</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.54999923706055</v>
+        <v>88.23999786376953</v>
       </c>
       <c r="I16" s="2" t="n">
         <v/>
       </c>
       <c r="J16" s="2" t="n">
-        <v>59.54999923706055</v>
+        <v>88.23999786376953</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>51055</v>
+        <v>463772</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Industries (WSI.NS) Reported Quarter: The Report Provides a New Financial Snapshot for the Current Session; Reported Share Move: Shares Finish 0.91% Up at the Close - Operating Income Trends - siam.in</t>
+          <t>Nitco shares rally nearly 14% on entering MoU with HOABL for joint development of Alibaug land; key details to know - Upstox</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
+          <t>Nitco Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
+          <t>Nitco shares jump nearly 14% on Alibaug land deal with HOABL; up to ₹1,500 crore payout expected - CNBC TV18</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>WestStar Industrial (ASX: WSI) Surges 60.71%: What’s Driving the Small-Cap Stock Higher? - Kalkine</t>
+          <t>Nitco Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Weststar Industrial Ltd (ASX: WSI) Share Price, WSI Stock News, WSI Share Price &amp; Updates - kalkine.ca</t>
+          <t>Nitco Ltd. (NITCO) Share Price Rises 8.25% Today to Rs 104.30 - Univest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1536,68 +1560,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>WPIL.NS</t>
+          <t>NIRAJ.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>WPIL Limited</t>
+          <t>Niraj Cement Structurals Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>435.25</v>
+        <v>27.02000045776367</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>440.3999938964844</v>
+        <v>28.70000076293945</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>431.0499877929688</v>
+        <v>27.02000045776367</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>437.5499877929688</v>
+        <v>27.57999992370605</v>
       </c>
       <c r="I17" s="2" t="n">
         <v/>
       </c>
       <c r="J17" s="2" t="n">
-        <v>437.5499877929688</v>
+        <v>27.57999992370605</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>19772</v>
+        <v>19209</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1:10 Stock Split: Record Date In 3 Days On 12 July; Buy Mukul Agarwal Portfolio Stock? - Goodreturns</t>
+          <t>Gulshankumar Chopra acquires 49.82% stake in Niraj Cement Structurals - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1:10 Stock Split: Record Date In 3 Days On 12 July; Buy Mukul Agarwal Portfolio Stock? - Goodreturns</t>
+          <t>Niraj Gemawat raises NINtec Systems stake to 18.44% - scanx.trade</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>WPIL Ltd. Stock News - valueresearchonline.com</t>
+          <t>Niraj Gemawat raises NINtec Systems stake to 18.44% - scanx.trade</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>WPIL (WPIL.NS) Financial Update: The Latest Report Adds New Financial Reference Points for This Review; Post-Report: Shares Finish 1.33% Lower on the Day - Earnings Acceleration Picks - siam.in</t>
+          <t>Niraj (NIRAJISPAT.NS) Price Update: Ends Down by 3.00% at ₹205.65 for the Current Session - siam.in</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>WPIL Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
+          <t>Niraj Cement Structurals incorporates Niraj Group Foundation for CSR - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1605,64 +1629,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>WORTHPERI.NS</t>
+          <t>NINSYS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals Limited</t>
+          <t>NINtec Systems Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>144.3600006103516</v>
+        <v>725</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>147.9799957275391</v>
+        <v>725</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>143</v>
+        <v>700.0499877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>147.9799957275391</v>
+        <v>710.75</v>
       </c>
       <c r="I18" s="2" t="n">
         <v/>
       </c>
       <c r="J18" s="2" t="n">
-        <v>147.9799957275391</v>
+        <v>710.75</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1591</v>
+        <v>3821</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals confirms no promoter encumbrance in FY26 - scanx.trade</t>
+          <t>NINTEC SYSTEMS LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals confirms no promoter encumbrance in FY26 - scanx.trade</t>
+          <t>NINTEC SYSTEMS LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals Share Price Drops; Price Fall Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Worth Peripherals recommends ₹1 per share final dividend for FY26 - scanx.trade</t>
-        </is>
-      </c>
+          <t>NINtec (NINSYS.NS) Financial Update: The Report Provides a New Financial Snapshot under the Current Snapshot; After Results: Shares Finish 1.42% Down for the Current Session - Earnings Yield Analysis - siam.in</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1670,68 +1690,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>WOCKPHARMA.NS</t>
+          <t>NILKAMAL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Limited</t>
+          <t>Nilkamal Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2190</v>
+        <v>2050.800048828125</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2193.800048828125</v>
+        <v>2069.89990234375</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2090.10009765625</v>
+        <v>1989</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2106.10009765625</v>
+        <v>2017.900024414062</v>
       </c>
       <c r="I19" s="2" t="n">
         <v/>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2106.10009765625</v>
+        <v>2017.900024414062</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>566354</v>
+        <v>19595</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - upstox.com</t>
+          <t>Nilkamal FY26 revenue rises 14% to ₹3,686 crore - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - upstox.com</t>
+          <t>Nilkamal FY26 revenue rises 14% to ₹3,686 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Ltd. Share Price Rise Streak: valuation and sector - Univest</t>
+          <t>Nilkamal Ltd. Share Price: Technicals Near 52-Week High - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Share Price Today: 3.57% Rise, Stock Analysis - Univest</t>
+          <t>Nilkamal (NILKAMAL.NS) Results at a Glance: The Latest Financial Metrics Are Now Available in Latest Trading; Stock Move: Shares Fall 1.32% in the Latest Session - EPS Miss Report - siam.in</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Ltd Share Price Rise: Price Action and Valuation - Univest</t>
+          <t>Nilkamal Share Price at Fresh 52-Week High; Valuation View - Univest</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1739,64 +1759,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WINDLAS.NS</t>
+          <t>NILE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Limited</t>
+          <t>Nile Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1137</v>
+        <v>1440</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1144</v>
+        <v>1488</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1102.050048828125</v>
+        <v>1430</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1103.75</v>
+        <v>1431.900024414062</v>
       </c>
       <c r="I20" s="2" t="n">
         <v/>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1103.75</v>
+        <v>1431.900024414062</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>47283</v>
+        <v>1971</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Q1FY27 revenue hits record ₹248 crore, up 18% - scanx.trade</t>
+          <t>Nile Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Q1FY27 revenue hits record ₹248 crore, up 18% - scanx.trade</t>
+          <t>Stratford reports first human case of West Nile virus, officials say - CTPost</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Volume shocker stocks: Why share price of EMS, Expleo Solutions, Windlas Biotech, AKI India, Heritage Foods are up today - tradingview.com</t>
+          <t>Nile Limited (NILE): Lead Recycling Compounder in Focus - kalkine.co.in</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Restores Operations After Labour Unrest - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Expert shares best defense against West Nile is preventing mosquito bites altogether - wcnc.com</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Stratford reports first human case of West Nile virus, officials say - CTPost</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1804,63 +1828,55 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>WHIRLPOOL.NS</t>
+          <t>NILASPACES.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool of India Limited</t>
+          <t>Nila Spaces Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>770.9500122070312</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>771.2000122070312</v>
+        <v>12.5600004196167</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>754.5</v>
+        <v>12</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>754.9000244140625</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="I21" s="2" t="n">
         <v/>
       </c>
       <c r="J21" s="2" t="n">
-        <v>754.9000244140625</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>91939</v>
+        <v>1058182</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool (WHR) Stock Could Be A Bargain Based On Cash Flow Recovery - simplywall.st</t>
+          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool (WHR) Stock Could Be A Bargain Based On Cash Flow Recovery - simplywall.st</t>
+          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool stock hits 52-week low at 35.37 USD - Investing.com</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Whirlpool Stock Plunges 7% as Massive Debt Load Fuels Investor Concerns - TIKR.com</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Whirlpool continues bruising Wall Street run, sets second low in a row - Moody on the Market</t>
-        </is>
-      </c>
+          <t>Nila Spaces promoter Kiran B Vadodaria sells 737,197 shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1879,14 +1895,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -1985,7 +2001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1993,68 +2009,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SPELS.NS</t>
+          <t>LASA.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SPEL Semiconductor Limited</t>
+          <t>Lasa Supergenerics Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>138.3699951171875</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>138.3699951171875</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>138.3699951171875</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>138.3699951171875</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>145.6499938964844</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>138.3699951171875</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>13606</v>
+        <v>18314</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-5</v>
+        <v>-4.91</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>SPELS Stock Price and Chart — NSE:SPELS - tradingview.com</t>
+          <t>Lasa Supergenerics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>SPEL Semiconductor Ltd. (SPELS) Fundamental and Financial Data - Stocktwits</t>
+          <t>Lasa Supergenerics appoints Janardan Savala as executive director - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of SPEL Semiconductor Limited (NSE:SPELS) - tradingview.com</t>
+          <t>Lasa (LASA.NS) Latest: Posts a 1.57% Gain to ₹7.10 on the Day; Next Test: the Supplied Trading Band Runs From ₹6.74 to ₹7.46 in the Available Record - Pre-Earnings Momentum - siam.in</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>SPEL Semiconductor Ltd. (SPELS) Fundamental and Financial Data - Stocktwits</t>
+          <t>Lasa Supergenerics appoints Janardan Savala as executive director - scanx.trade</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>SPEL Semiconductor Ltd. (SPELS) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>Lasa Supergenerics accepts Ganesh Potdar resignation as WTD - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2062,68 +2078,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>LASA.NS</t>
+          <t>CENTEXT.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics Limited</t>
+          <t>Century Extrusions Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>21.95000076293945</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>21.95000076293945</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>19.79999923706055</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6.519999980926514</v>
+        <v>20.36000061035156</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>16158</v>
+        <v>888517</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-4.91</v>
+        <v>-1.87</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
+          <t>Century Extrusions (NSE:CENTEXT): Why Was the Rights Issue Letter of Offer Revised? - kalkine.co.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics appoints Janardan Savala as executive director - scanx.trade</t>
+          <t>Century Extrusions (NSE:CENTEXT): Why Was the Rights Issue Letter of Offer Revised? - kalkine.co.in</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Lasa (LASA.NS) Latest: Posts a 1.57% Gain to ₹7.10 on the Day; Next Test: the Supplied Trading Band Runs From ₹6.74 to ₹7.46 in the Available Record - Pre-Earnings Momentum - siam.in</t>
+          <t>Century (CENTEXT.NS) Update: Finishes 0.23% Lower at ₹22.13; the Current Price Sits Inside the Supplied Technical Range in the Latest Reading - Swing Entry Signals - siam.in</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics appoints Janardan Savala as executive director - scanx.trade</t>
+          <t>Cogent (CCOI) Latest: Slides 3.42% to $10.01 for the Current Session; Next Test - Vinanet</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics accepts Ganesh Potdar resignation as WTD - scanx.trade</t>
+          <t>Century Extrusions reports FY26 net profit of ₹1,057 lakh - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2131,60 +2147,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>WHBRADY.NS</t>
+          <t>PANORAMA.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>WH Brady &amp; Company Limited</t>
+          <t>Panorama Studios International Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>481.2999877929688</v>
+        <v>55.40000152587891</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>481.2999877929688</v>
+        <v>56.18000030517578</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>477</v>
+        <v>50.34999847412109</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>477</v>
+        <v>51.91999816894531</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>480.5</v>
+        <v/>
       </c>
       <c r="J4" s="2" t="n">
-        <v>477</v>
+        <v>51.91999816894531</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>20</v>
+        <v>572747</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>W.H. Brady &amp; Co. Ltd. (WHBRADY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Panorama Studios sets AGM for Sept 30, seeks ₹1,500 crore borrowing limit - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>W.H. Brady &amp; Co. Ltd. (WHBRADY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Panorama Studios sets AGM for Sept 30, seeks ₹1,500 crore borrowing limit - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>W.H. Brady &amp; Co. Ltd. (WHBRADY) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Panorama Studios Share Price rises 13.84% with valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Panorama Studios International Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Panorama Studios International Ltd is Rated Hold - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2192,68 +2216,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ZENITHSTL.NS</t>
+          <t>OBEROIRLTY.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Zenith Steel Pipes &amp; Industries Limited</t>
+          <t>Oberoi Realty Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.949999809265137</v>
+        <v>1746</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5.949999809265137</v>
+        <v>1749.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5.699999809265137</v>
+        <v>1668.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5.840000152587891</v>
+        <v>1668.5</v>
       </c>
       <c r="I5" s="2" t="n">
         <v/>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.840000152587891</v>
+        <v>1668.5</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>40936</v>
+        <v>362396</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Zenith Steel Pipes Holds Above ₹5 Support; Resistance at ₹5.61 in Focus - Supply Zone - siam.in</t>
+          <t>Oberoi Realty Share Price - Live NSE: OBEROIRLTY Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Zenith Steel Pipes Sets Virtual AGM for September 30, 2026 - TipRanks</t>
+          <t>Oberoi Realty Share Price - Live NSE: OBEROIRLTY Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Zenith (ZENITHSTL.NS) EPS and Revenue: The Report Supplies Updated Headline Figures for This Review; Market Reaction: Shares Move 1.46% Down in the Latest Session - Fiscal Year Earnings - siam.in</t>
+          <t>Oberoi (OBEROIRLTY.NS) Results Review: Available Data Shows the Latest Reported Performance for This Review; Trading Response: Shares Move Lower 0.98% in the Current Update - Post-Earnings Reaction - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Zenith (ZENITHSTL.NS) Earnings Update: The Company Reports Its Latest Available Figures; Shares Finish 0.37% Up - Financial Summary - siam.in</t>
+          <t>Oberoi Realty Ltd. Share Price Update With Peer Analysis - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Zenith Steel Pipes Sets Virtual AGM for September 30, 2026 - TipRanks</t>
+          <t>Oberoi Realty (OBEROIRLTY) Share Price Falls 2.25% Today: Price Action, Valuation and Realty Sector Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2261,56 +2285,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ZENITHEXPO.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Zenith Exports Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>207.0500030517578</v>
+        <v>345.3999938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>207.0500030517578</v>
+        <v>346.1499938964844</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>194.75</v>
+        <v>336.2000122070312</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>196.0599975585938</v>
+        <v>336.2000122070312</v>
       </c>
       <c r="I6" s="2" t="n">
         <v/>
       </c>
       <c r="J6" s="2" t="n">
-        <v>196.0599975585938</v>
+        <v>336.2000122070312</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>158</v>
+        <v>2338415</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Etsy (ETSY) Shares: Ends Down by 0.22% at $81.03 for the Current Session; Next Test: $76.98 and $85.08 Define the Nearby Reference Levels under the Current Snapshot - Aggressive Growth Picks - siam.in</t>
+          <t>Nykaa Q2 FY27 Results Preview - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Etsy (ETSY) Shares: Ends Down by 0.22% at $81.03 for the Current Session; Next Test: $76.98 and $85.08 Define the Nearby Reference Levels under the Current Snapshot - Aggressive Growth Picks - siam.in</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Nykaa Q2 FY27 Results Preview - Univest</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Top stock picks: Kalyan Jewellers, Nykaa, Adani Ports among 6 trades recommended by experts - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Nykaa officials to attend investor meets in London from June 22 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>FSN E-Commerce Ventures Nykaa Shares Rise Over 2% Today - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2318,68 +2354,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ZEEMEDIA.NS</t>
+          <t>NUCLEUS.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Zee Media Corporation Limited</t>
+          <t>Nucleus Software Exports Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7.5</v>
+        <v>691.4000244140625</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>7.559999942779541</v>
+        <v>707.5499877929688</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>7.309999942779541</v>
+        <v>691.4000244140625</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7.329999923706055</v>
+        <v>696.4000244140625</v>
       </c>
       <c r="I7" s="2" t="n">
         <v/>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.329999923706055</v>
+        <v>696.4000244140625</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>926306</v>
+        <v>20850</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Acacia Partners holds 5.51% in Zee Media after warrant conversion - scanx.trade</t>
+          <t>Nucleus Software proposes buying 1.14 lakh shares for employee RSU scheme - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Acacia Partners holds 5.51% in Zee Media after warrant conversion - scanx.trade</t>
+          <t>Nucleus Software order book jumps 19% to ₹1,244 crore in Q1FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Zee (ZEEMEDIA.NS) Quarter in Focus: Available Data Shows the Latest Reported Performance for This Review; Market Response: Shares Finish 0.21% Lower in the Latest Reading - Earnings Beat Streak - siam.in</t>
+          <t>Nucleus Software board approves insider trading code amendments - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Zee Media Corporation files FY26 business responsibility report with exchanges - scanx.trade</t>
+          <t>Nucleus Software Q2 2026 Earnings: EPS at ₹44.35 on ₹876.03 Crore Revenue; NSE Stock Gains 0.96% - Earnings Miss Streak - siam.in</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Zee Business. . Zee Media : Q1 के दमदार नतीजों के क्या रहे ट्रिगर्स? देखिए Zee Media के CEO, रक्तिम दास से खास बातचीत Watch Full Interview : https://youtu.be/gFQ3lrHMS6k?si=XNZxfntGAX_9zwkg #StockMarket #ZeeMedia #anilsi - facebook.com</t>
+          <t>Nucleus Software order book jumps 19% to ₹1,244 crore in Q1FY27 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2387,68 +2423,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ZEEL.NS</t>
+          <t>NTPCGREEN.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Zee Entertainment Enterprises Limited</t>
+          <t>NTPC Green Energy Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>80</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>80.29000091552734</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>78.26999664306641</v>
+        <v>85.75</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>78.34999847412109</v>
+        <v>85.86000061035156</v>
       </c>
       <c r="I8" s="2" t="n">
         <v/>
       </c>
       <c r="J8" s="2" t="n">
-        <v>78.34999847412109</v>
+        <v>85.86000061035156</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>8062161</v>
+        <v>2072032</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ZEEL tanks 15% as Chandra's insolvency resolution plan faces fresh hurdle - Business Standard</t>
+          <t>NTPC (NTPCGREEN.NS) Session: Loses 0.28% to Close at ₹91.62 in Latest Trading - siam.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ZEE Entertainment shares fell 6% today; here's why - Business Today</t>
+          <t>NTPC Green shares jump over 3% as it commissions 100 MW power at IRPL plant - Business Upturn</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ZEE Entertainment shares fell 6% today; here's why - Business Today</t>
+          <t>NTPC (NTPCGREEN.NS) Today: Rises 0.33% to ₹92.00 in Latest Trading; Chart View: Support at ₹87.40 and Resistance at ₹96.60 Frame the Range in the Available Record - Mean Reversion Trade - siam.in</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>ZEEL shares dip after promoter group gets Rs 660 crore warrant allotment - Indian Television Dot Com</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Zee Entertainment Enterprises Ltd. (ZEEL) Share Price Rises 6.4% Today - Univest</t>
-        </is>
-      </c>
+          <t>NTPC Green shares jump over 3% as it commissions 100 MW power at IRPL plant - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2456,68 +2488,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>YUKEN.NS</t>
+          <t>NILE.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Yuken India Limited</t>
+          <t>Nile Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1124</v>
+        <v>1440</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1124</v>
+        <v>1488</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1046</v>
+        <v>1430</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1050.050048828125</v>
+        <v>1431.900024414062</v>
       </c>
       <c r="I9" s="2" t="n">
         <v/>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1050.050048828125</v>
+        <v>1431.900024414062</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>20270</v>
+        <v>1971</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Yuken India Ltd. Stock News - valueresearchonline.com</t>
+          <t>Nile Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Yuken India Limited Announces Redesignation of Yoshitake Tanaka from Non-Executive - Non-Independent Director to Executive Director Designated as Whole-Time Director, Effective October 1, 2026 - marketscreener.com</t>
+          <t>Stratford reports first human case of West Nile virus, officials say - CTPost</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Yuken India publishes 50th AGM notice for September 10, 2026 - scanx.trade</t>
+          <t>Nile Limited (NILE): Lead Recycling Compounder in Focus - kalkine.co.in</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Yuken India Ltd. Share Price Jumps; Fundamentals Checked - Univest</t>
+          <t>Expert shares best defense against West Nile is preventing mosquito bites altogether - wcnc.com</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Yuken India Consolidated June 2026 Net Sales at Rs 134.33 crore, up 28.48% Y-o-Y - Moneycontrol.com</t>
+          <t>Stratford reports first human case of West Nile virus, officials say - CTPost</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2525,56 +2557,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>YESBANK.NS</t>
+          <t>NILASPACES.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Yes Bank Limited</t>
+          <t>Nila Spaces Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>23.68000030517578</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>23.89999961853027</v>
+        <v>12.5600004196167</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>22.98999977111816</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>23.35000038146973</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="I10" s="2" t="n">
         <v/>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23.35000038146973</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>68264402</v>
+        <v>1058182</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>YESBANK Share Price News: today’s gain and sector context - Univest</t>
+          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>YESBANK Share Price News: today’s gain and sector context - Univest</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
+          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Nila Spaces promoter Kiran B Vadodaria sells 737,197 shares - scanx.trade</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2582,68 +2618,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH.NS</t>
+          <t>NSIL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
+          <t>Nalwa Sons Investments Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1000</v>
+        <v>5623</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1024</v>
+        <v>5623</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>977.7999877929688</v>
+        <v>5400</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>990.4000244140625</v>
+        <v>5409.5</v>
       </c>
       <c r="I11" s="2" t="n">
         <v/>
       </c>
       <c r="J11" s="2" t="n">
-        <v>990.4000244140625</v>
+        <v>5409.5</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>503515</v>
+        <v>1651</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Yatharth Hospital board to discuss growth plans and fund raising on Sep 17 - scanx.trade</t>
+          <t>Nalwa Sons Investments Holds Gains: Stock Climbs 0.68% to ₹5,721.5 Amid Rangebound Trade - Bear Pennant - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Yatharth Hospital board to discuss growth plans and fund raising on Sep 17 - scanx.trade</t>
+          <t>Nalwa Sons Investments Holds Gains: Stock Climbs 0.68% to ₹5,721.5 Amid Rangebound Trade - Bear Pennant - siam.in</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Yatharth Hospital shares jump 5% as Aster, Advent likely eye controlling stake - The Economic Times</t>
+          <t>Nalwa (NSIL.NS): Moves 0.73% Lower to ₹5,682.50; Levels: Traders Can Monitor the ₹5,398.38-₹5,966.62 Range under the Current Snapshot - Channel Projection - siam.in</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Aster, Advent eye controlling stake in Yatharth Hospital, says report; shares rise 4.5% - Moneycontrol.com</t>
+          <t>APOORVA Stock Price and Chart — NSE:APOORVA - TradingView</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Yatharth Hospital gains 6% to new high as Aster, Advent eye majority stake - Business Standard</t>
+          <t>NSIL Q2 2026 Earnings: Revenue Slides 18% to ₹906.8 Million, EPS at ₹106.13 - Dividend Increase Stocks - siam.in</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2651,68 +2687,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>YASHO.NS</t>
+          <t>NRBBEARING.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Limited</t>
+          <t>NRB Bearing Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4260</v>
+        <v>516</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>4286.89990234375</v>
+        <v>516.7999877929688</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>3921</v>
+        <v>478</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3934.10009765625</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="I12" s="2" t="n">
         <v/>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3934.10009765625</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>38529</v>
+        <v>504747</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com</t>
+          <t>NRB Bearings Ltd. (NRBBEARING) Share Price Trades Within 2% of 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries doubles FY27 capex to ₹250 crore on strong demand - scanx.trade</t>
+          <t>Granules India promoter offloads shares worth Rs 1,509 crore; Morgan Stanley picks stake in Lotus Developers - TradingView</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Ltd. Stock News - valueresearchonline.com</t>
+          <t>NRB Bearings Share Price Today: Market Cap and Valuation - Univest</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries seeks ₹1,250 crore borrowing limit hike via postal ballot - scanx.trade</t>
+          <t>NRB Bearings 52 Week High Streak: Second Straight Session - Univest</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Yasho Industries Upgraded to Buy on Strong Financials and Bullish Technicals - MarketsMojo</t>
+          <t>Granules India promoter offloads shares worth Rs 1,509 crore; Morgan Stanley picks stake in Lotus Developers - TradingView</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2720,60 +2756,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>XTGLOBAL.NS</t>
+          <t>NRAIL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Xtglobal Infotech Limited</t>
+          <t>N R Agarwal Industries Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29.54999923706055</v>
+        <v>638</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>31.79999923706055</v>
+        <v>685</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>29.29999923706055</v>
+        <v>631</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>29.70000076293945</v>
+        <v>638.8499755859375</v>
       </c>
       <c r="I13" s="2" t="n">
         <v/>
       </c>
       <c r="J13" s="2" t="n">
-        <v>29.70000076293945</v>
+        <v>638.8499755859375</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>74999</v>
+        <v>113595</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>XTGLOBAL.NS Q2 2026 Earnings: Revenue Surges 57.48% YoY to ₹368.72 Crore; Stock Declines 3.92% - Pretax Income Report - siam.in</t>
+          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>XTGlobal Infotech Board Declares Interim Dividend and Confirms Key Reappointments - TipRanks</t>
+          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>XTGlobal Infotech Board Declares Interim Dividend and Confirms Key Reappointments - TipRanks</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>NR Agarwal Industries Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>N R Agarwal Industries appoints Manoj Chauhan as Chief Marketing Officer - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>NR Agarwal Industries Share Price today: key market update - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2781,56 +2825,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>XPROINDIA.NS</t>
+          <t>NPST.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Xpro India Limited</t>
+          <t>Network People Services Technologies Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1294.699951171875</v>
+        <v>1698.900024414062</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1295</v>
+        <v>1700</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1263.099975585938</v>
+        <v>1630</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1276.900024414062</v>
+        <v>1639.5</v>
       </c>
       <c r="I14" s="2" t="n">
         <v/>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1276.900024414062</v>
+        <v>1639.5</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>32026</v>
+        <v>27585</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
+          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>NPST wins Best Digital Banking Platform at Global Fintech Awards 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>NPST Confirms AGM Notice Dispatch and Annual Report Access for Shareholders - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2838,68 +2894,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>XELPMOC.NS</t>
+          <t>NORTHARC.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc Design And Tech Limited</t>
+          <t>Northern Arc Capital Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>77.5</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>78.15000152587891</v>
+        <v>308.2000122070312</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>76.25</v>
+        <v>292</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>77</v>
+        <v>294.2000122070312</v>
       </c>
       <c r="I15" s="2" t="n">
         <v/>
       </c>
       <c r="J15" s="2" t="n">
-        <v>77</v>
+        <v>294.2000122070312</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>6433</v>
+        <v>1045892</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc FY26 revenue falls 4.1% to ₹37.4 million - scanx.trade</t>
+          <t>Northern ARC Capital Share Price: 8.39% rise, valuation - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc Design and Tech Ltd (NSE: XELPMOC): AI Services Watch - Kalkine India</t>
+          <t>Northern Arc Capital Q1 FY27 Net Profit Jumps 41% YoY to Record ₹114 Cr - Trade Brains</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc (XELPMOC.NS) Financial Update: The Report Provides a New Financial Snapshot; Trading Move: Shares Close 8.61% Higher in Latest Trading - Earnings Per Share - siam.in</t>
+          <t>Refex Industries promoter pledges 20.9 lakh shares for collateral - scanx.trade</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc Design &amp; Tech approves ₹14.58 crore sale of Woovly India stake - scanx.trade</t>
+          <t>News by CNBC TV18 on TradingView, 2026-08-31 — cnbctv:acd04171b094b:0 - TradingView</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Xelpmoc Design and Tech Publishes Q1 FY2026 Unaudited Results and Confirms SEBI-Compliant Disclosure - The Globe and Mail</t>
+          <t>Northern Arc Capital Q1 FY27 Net Profit Jumps 41% YoY to Record ₹114 Cr - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2907,68 +2963,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>WSTCSTPAPR.NS</t>
+          <t>NORBTEAEXP.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>West Coast Paper Mills Limited</t>
+          <t>Norben Tea &amp; Exports Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>713</v>
+        <v>65.90000152587891</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>734</v>
+        <v>67.38999938964844</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>706.2000122070312</v>
+        <v>64.5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>712.7000122070312</v>
+        <v>64.5</v>
       </c>
       <c r="I16" s="2" t="n">
         <v/>
       </c>
       <c r="J16" s="2" t="n">
-        <v>712.7000122070312</v>
+        <v>64.5</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>214791</v>
+        <v>1569</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>West (WSTCSTPAPR.NS) Chart: Closes 0.12% Lower at ₹605.40 in Latest Trading; the Current Price Sits Inside the Supplied Technical Range for the Current Session - Technical Analysis Picks - siam.in</t>
+          <t>Norben Tea &amp; Exports Holds Near ₹65.29 as Stock Trades Within Key Range - Zero Gamma Level - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>West Coast Paper Mills 52 Week High Streak Extends Again - Univest</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>West Coast Paper Mills Share Price: fresh 52-week high at Rs - Univest</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>West (WSTCSTPAPR.NS) Snapshot: Moves 3.45% Up to ₹636.25 for the Current Session; Price Setup: Support at ₹604.44 and Resistance at ₹668.06 Frame the Range - Triple Bottom - siam.in</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>West Coast Paper Mills Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
+          <t>Norben Tea &amp; Exports Holds Near ₹65.29 as Stock Trades Within Key Range - Zero Gamma Level - siam.in</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2976,68 +3020,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>WSI.NS</t>
+          <t>PANSARI.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>W S Industries (I) Limited</t>
+          <t>Pansari Developers Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>60.20000076293945</v>
+        <v>281.5</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>62.5</v>
+        <v>299</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>59</v>
+        <v>275</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.54999923706055</v>
+        <v>282.1499938964844</v>
       </c>
       <c r="I17" s="2" t="n">
         <v/>
       </c>
       <c r="J17" s="2" t="n">
-        <v>59.54999923706055</v>
+        <v>282.1499938964844</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>51055</v>
+        <v>312</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Industries (WSI.NS) Reported Quarter: The Report Provides a New Financial Snapshot for the Current Session; Reported Share Move: Shares Finish 0.91% Up at the Close - Operating Income Trends - siam.in</t>
+          <t>Pansari Developers Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
+          <t>Pansari Developers Publishes Notice for 30th AGM in Kolkata Dailies - TipRanks</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
+          <t>Pansari Developers (PANSARI.NS) Declines 2.53% to ₹296.1; Support at ₹281.3 in Focus - McClellan Oscillator - siam.in</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>WestStar Industrial (ASX: WSI) Surges 60.71%: What’s Driving the Small-Cap Stock Higher? - Kalkine</t>
+          <t>Pansari Developers Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Weststar Industrial Ltd (ASX: WSI) Share Price, WSI Stock News, WSI Share Price &amp; Updates - kalkine.ca</t>
+          <t>Pansari Developers Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3045,68 +3089,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>WPIL.NS</t>
+          <t>ODIGMA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>WPIL Limited</t>
+          <t>Odigma Consultancy Solutions Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>435.25</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>440.3999938964844</v>
+        <v>22.44000053405762</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>431.0499877929688</v>
+        <v>21.5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>437.5499877929688</v>
+        <v>22.09000015258789</v>
       </c>
       <c r="I18" s="2" t="n">
         <v/>
       </c>
       <c r="J18" s="2" t="n">
-        <v>437.5499877929688</v>
+        <v>22.09000015258789</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>19772</v>
+        <v>9536</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1:10 Stock Split: Record Date In 3 Days On 12 July; Buy Mukul Agarwal Portfolio Stock? - Goodreturns</t>
+          <t>Odigma Consultancy shareholders approve FY26 financials, re-appoint Vishal Mehta - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1:10 Stock Split: Record Date In 3 Days On 12 July; Buy Mukul Agarwal Portfolio Stock? - Goodreturns</t>
+          <t>Odigma Consultancy shareholders approve FY26 financials, re-appoint Vishal Mehta - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>WPIL Ltd. Stock News - valueresearchonline.com</t>
+          <t>Odigma Consultancy Solutions Gains 3.25% to ₹23.16, Approaches Key Resistance at ₹24.32 - Sentiment Shift - siam.in</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>WPIL (WPIL.NS) Financial Update: The Latest Report Adds New Financial Reference Points for This Review; Post-Report: Shares Finish 1.33% Lower on the Day - Earnings Acceleration Picks - siam.in</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>WPIL Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
-        </is>
-      </c>
+          <t>Odigma (ODIGMA.NS) Results Breakdown: The Company Publishes Its Latest Results in the Current Update; Trading Response: Shares Move 1.12% Up at the Close - Healthcare Earnings Report - siam.in</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3114,64 +3154,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>WORTHPERI.NS</t>
+          <t>NIVABUPA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals Limited</t>
+          <t>Niva Bupa Health Insurance Company Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>144.3600006103516</v>
+        <v>79.91999816894531</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>147.9799957275391</v>
+        <v>83.90000152587891</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>143</v>
+        <v>79.62999725341797</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>147.9799957275391</v>
+        <v>81.5</v>
       </c>
       <c r="I19" s="2" t="n">
         <v/>
       </c>
       <c r="J19" s="2" t="n">
-        <v>147.9799957275391</v>
+        <v>81.5</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1591</v>
+        <v>1415602</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals confirms no promoter encumbrance in FY26 - scanx.trade</t>
+          <t>NIVABUPA Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals confirms no promoter encumbrance in FY26 - scanx.trade</t>
+          <t>Earnings call transcript: Niva Bupa posts stronger q1 2027 profit, shares edge up - Investing.com</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals Share Price Drops; Price Fall Analysis - Univest</t>
+          <t>Here's Why We Think Niva Bupa Health Insurance (NSE:NIVABUPA) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Worth Peripherals recommends ₹1 per share final dividend for FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>IRDAI Approves Transfer of 14.62 Crore Equity Shares by Fettle Tone LLP in Niva Bupa Health Insurance - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Potential Upside For Niva Bupa Health Insurance Company Limited (NSE:NIVABUPA) Not Without Risk - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3179,68 +3223,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WOCKPHARMA.NS</t>
+          <t>NITTAGELA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Limited</t>
+          <t>Nitta Gelatin India Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2190</v>
+        <v>1625.400024414062</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2193.800048828125</v>
+        <v>1807</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2090.10009765625</v>
+        <v>1602.199951171875</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2106.10009765625</v>
+        <v>1693</v>
       </c>
       <c r="I20" s="2" t="n">
         <v/>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2106.10009765625</v>
+        <v>1693</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>566354</v>
+        <v>14080</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - upstox.com</t>
+          <t>Nitta Gelatin India (NITTAGELA.NS) Eases 0.76% to ₹1,654.40 as Stock Tests Mid-Range Support - Dynamic Hedging - siam.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Wockhardt Share Price - Live NSE: WOCKPHARMA Stock Price &amp; Chart - upstox.com</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Wockhardt Ltd. Share Price Rise Streak: valuation and sector - Univest</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Wockhardt Share Price Today: 3.57% Rise, Stock Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Wockhardt Ltd Share Price Rise: Price Action and Valuation - Univest</t>
-        </is>
-      </c>
+          <t>Nitta Gelatin India (NITTAGELA.NS) Eases 0.76% to ₹1,654.40 as Stock Tests Mid-Range Support - Dynamic Hedging - siam.in</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:25:39 IST</t>
+          <t>2026-09-15 20:44:28 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3248,51 +3280,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT.NS</t>
+          <t>NITCO.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>California Software Company Limited</t>
+          <t>Nitco Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>39.90000152587891</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>40.20000076293945</v>
+        <v>94.02999877929688</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>36.81000137329102</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>36.9900016784668</v>
+        <v>88.23999786376953</v>
       </c>
       <c r="I21" s="2" t="n">
         <v/>
       </c>
       <c r="J21" s="2" t="n">
-        <v>36.9900016784668</v>
+        <v>88.23999786376953</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>371103</v>
+        <v>463772</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>Nitco shares rally nearly 14% on entering MoU with HOABL for joint development of Alibaug land; key details to know - Upstox</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Nitco Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Nitco shares jump nearly 14% on Alibaug land deal with HOABL; up to ₹1,500 crore payout expected - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Nitco Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Nitco Ltd. (NITCO) Share Price Rises 8.25% Today to Rs 104.30 - Univest</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,64 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KANCOTEA.NS</t>
+          <t>CSM.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Limited</t>
+          <t>CSM Technologies Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>52.31000137329102</v>
+        <v>91.98999786376953</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>56.97999954223633</v>
+        <v>103.4499969482422</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>52.31000137329102</v>
+        <v>88.68000030517578</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>56.79999923706055</v>
+        <v>98.73000335693359</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>52.29000091552734</v>
+        <v>89.84999847412109</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>56.79999923706055</v>
+        <v>98.73000335693359</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1088</v>
+        <v>2318647</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Kanco Tea &amp; Industries Ltd. – NSE:KANCOTEA - TradingView</t>
+          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) Fundamental and Financial Data - Stocktwits</t>
+          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>CSM Share Price Today Falls: P/E, P/B and Sector Context - Univest</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>How (CSM) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -618,64 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NTPCGREEN.NS</t>
+          <t>SUNSHINE.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NTPC Green Energy Limited</t>
+          <t>Sunshine Pictures Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>86.94000244140625</v>
+        <v>350.1499938964844</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>87.01999664306641</v>
+        <v>367.2999877929688</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>85.75</v>
+        <v>332.3500061035156</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>85.86000061035156</v>
+        <v>363.8500061035156</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v/>
+        <v>333.9500122070312</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>85.86000061035156</v>
+        <v>363.8500061035156</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2072032</v>
+        <v>2691567</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>NTPC (NTPCGREEN.NS) Session: Loses 0.28% to Close at ₹91.62 in Latest Trading - siam.in</t>
+          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>NTPC Green shares jump over 3% as it commissions 100 MW power at IRPL plant - Business Upturn</t>
+          <t>Nature's Sunshine (NATR) awards CFO 75,433 stock units vesting over three years - Stock Titan</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>NTPC (NTPCGREEN.NS) Today: Rises 0.33% to ₹92.00 in Latest Trading; Chart View: Support at ₹87.40 and Resistance at ₹96.60 Frame the Range in the Available Record - Mean Reversion Trade - siam.in</t>
+          <t>Sunshine Pictures IPO Listing: Shares List at 9.97% Premium on NSE, Fall Short of Grey-Market Hopes - India Infoline</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>NTPC Green shares jump over 3% as it commissions 100 MW power at IRPL plant - Business Upturn</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Average basic shares outstanding of CHERISH SUNSHINE INTL LTD. – OTC:CHSIF - tradingview.com</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Sunshine Pictures shares list at 10% premium over IPO price - The Economic Times</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NTPC.NS</t>
+          <t>KOPRAN.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NTPC Limited</t>
+          <t>Kopran Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>333</v>
+        <v>251.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>333.2999877929688</v>
+        <v>274.7799987792969</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>326.3999938964844</v>
+        <v>237.7799987792969</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>329.5</v>
+        <v>269.7099914550781</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v/>
+        <v>249.8999938964844</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>329.5</v>
+        <v>269.7099914550781</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>8431808</v>
+        <v>6882018</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>7.93</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>BHEL Board Approves Rs 65 Cr Investment In NTPC Joint Venture - TradingView</t>
+          <t>Kopran Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>BHEL Board Approves Rs 65 Cr Investment In NTPC Joint Venture - TradingView</t>
+          <t>Kopran Q2 FY27 Preview: What to Watch Before Results - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>BHEL approves ₹65 crore further investment in NTPC joint venture NBPPL - Livemint</t>
+          <t>Kopran Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>NTPC Share Price Today (NTPC) | Live Chart, News &amp; Stock Market - TechGraph</t>
+          <t>Kopran Q2 FY27 Preview: What to Watch Before Results - Univest</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Suzlon Energy vs NTPC Green vs NHPC: Wind, Solar or Hydro? Which Energy Stock Deserves Spot In Your Portfolio? - Goodreturns</t>
+          <t>Kopran Ltd. Share Price News With Healthcare Sector View - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>NSLNISP.NS</t>
+          <t>IOLCP.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NMDC Steel Limited</t>
+          <t>IOL Chemicals and Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>43.68000030517578</v>
+        <v>182</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43.68999862670898</v>
+        <v>194.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>41.34999847412109</v>
+        <v>173.5500030517578</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>41.45000076293945</v>
+        <v>192.9799957275391</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v/>
+        <v>179.5200042724609</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41.45000076293945</v>
+        <v>192.9799957275391</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3741115</v>
+        <v>6267284</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>NMDC Steel Share Price - Upstox</t>
+          <t>IOL Chemicals and Pharmaceuticals Share Price - Live NSE: IOLCP Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>NMDC Steel Share Price - Upstox</t>
+          <t>IOL Chemicals and Pharmaceuticals Share Price - Live NSE: IOLCP Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>NMDC Steel Share Price Today: Market Cap, P/E, Peer View - Univest</t>
+          <t>IOL Chemicals Share Price Today after fresh 52-week high - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>NMDC Steel Share Price falls 5.42%: price action review - Univest</t>
+          <t>IOL Chemicals (IOLCP.NS) Holds Steady Near ₹194 as Pharma-Chemical Play Consolidates - MFI Overbought - siam.in</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>NMDC Steel: Clarifies Stock Price Spurt Amidst Financial Results &amp; Rating Upgrade - InvestyWise</t>
+          <t>IOLCP Share Price today near 52-week high, price action - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,68 +829,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NSIL.NS</t>
+          <t>MOREPENLAB.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Nalwa Sons Investments Limited</t>
+          <t>Morepen Laboratories Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5623</v>
+        <v>106.4499969482422</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5623</v>
+        <v>114.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5400</v>
+        <v>97.04000091552734</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5409.5</v>
+        <v>113.0400009155273</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v/>
+        <v>106.2200012207031</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5409.5</v>
+        <v>113.0400009155273</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1651</v>
+        <v>30425551</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Nalwa Sons Investments Holds Gains: Stock Climbs 0.68% to ₹5,721.5 Amid Rangebound Trade - Bear Pennant - siam.in</t>
+          <t>We Ran A Stock Scan For Earnings Growth And Morepen Laboratories (NSE:MOREPENLAB) Passed With Ease - simplywall.st</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Nalwa Sons Investments Holds Gains: Stock Climbs 0.68% to ₹5,721.5 Amid Rangebound Trade - Bear Pennant - siam.in</t>
+          <t>We Ran A Stock Scan For Earnings Growth And Morepen Laboratories (NSE:MOREPENLAB) Passed With Ease - simplywall.st</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Nalwa (NSIL.NS): Moves 0.73% Lower to ₹5,682.50; Levels: Traders Can Monitor the ₹5,398.38-₹5,966.62 Range under the Current Snapshot - Channel Projection - siam.in</t>
+          <t>Morepen Laboratories (MOREPENLAB) Share Price Falls 6.25% Today; Valuation and Sector Context in Focus - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>APOORVA Stock Price and Chart — NSE:APOORVA - TradingView</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>NSIL Q2 2026 Earnings: Revenue Slides 18% to ₹906.8 Million, EPS at ₹106.13 - Dividend Increase Stocks - siam.in</t>
-        </is>
-      </c>
+          <t>Morepen Laboratories Share Price today after yearly high - Univest</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -890,68 +894,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NRBBEARING.NS</t>
+          <t>CSBBANK.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>NRB Bearing Limited</t>
+          <t>CSB Bank Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>516</v>
+        <v>297.8999938964844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>516.7999877929688</v>
+        <v>324</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>478</v>
+        <v>297.7999877929688</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>314.2999877929688</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v/>
+        <v>296.3500061035156</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>314.2999877929688</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>504747</v>
+        <v>4793309</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>NRB Bearings Ltd. (NRBBEARING) Share Price Trades Within 2% of 52-Week High - Univest</t>
+          <t>CSB Bank Falls 2.58% to ₹312.85: Support at ₹297.21 Holds the Key for CSBBANK.NS - Channel Projection - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Granules India promoter offloads shares worth Rs 1,509 crore; Morgan Stanley picks stake in Lotus Developers - TradingView</t>
+          <t>RBI gives ICICI Bank (NYSE: IBN) unit one year to acquire stakes in four lenders - Stock Titan</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>NRB Bearings Share Price Today: Market Cap and Valuation - Univest</t>
+          <t>CSB Bank Ltd. Share Price: 52-Week Low and Valuation View - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>NRB Bearings 52 Week High Streak: Second Straight Session - Univest</t>
+          <t>CSB (CSBBANK.NS) Financial Update: The Latest Report Adds New Financial Reference Points in the Current Update; Post-Report: The Share Price Moves Only Slightly in Latest Trading - Earnings Growth Analysis - siam.in</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Granules India promoter offloads shares worth Rs 1,509 crore; Morgan Stanley picks stake in Lotus Developers - TradingView</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-08 — cnbctv:53b6c3a40094b:0 - tradingview.com</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -959,68 +963,56 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>NRAIL.NS</t>
+          <t>ZEELEARN.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries Limited</t>
+          <t>Zee Learn Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>638</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>685</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>631</v>
+        <v>6.559999942779541</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>638.8499755859375</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v/>
+        <v>6.630000114440918</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>638.8499755859375</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>113595</v>
+        <v>196334</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
+          <t>5 Education Stocks India 2026: Strong Future Roadmaps - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>NR Agarwal Industries Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>N R Agarwal Industries appoints Manoj Chauhan as Chief Marketing Officer - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>NR Agarwal Industries Share Price today: key market update - Univest</t>
-        </is>
-      </c>
+          <t>5 Education Stocks India 2026: Strong Future Roadmaps - Univest</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1028,68 +1020,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>NPST.NS</t>
+          <t>MVGJL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Network People Services Technologies Limited</t>
+          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1698.900024414062</v>
+        <v>196.0399932861328</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1700</v>
+        <v>209.8999938964844</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1630</v>
+        <v>185.1499938964844</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1639.5</v>
+        <v>207.3999938964844</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v/>
+        <v>196.0500030517578</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1639.5</v>
+        <v>207.3999938964844</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>27585</v>
+        <v>554417</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
+          <t>Manoj Vaibhav Gems (MVGJL.NS) Gains 4.6% to ₹179.9: Jewelry Stock Rebounds Toward Key Resistance - Bollinger Squeeze - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - tradingview.com</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>NPST wins Best Digital Banking Platform at Global Fintech Awards 2026 - scanx.trade</t>
+          <t>Here's Why Manoj Vaibhav Gems 'N' Jewellers (NSE:MVGJL) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+          <t>Manoj (MVGJL.NS) Financial Update: The Company Lists Its Latest Available Figures in the Current Update; Shares Move 1.33% Up in the Latest Reading - Surprise Factor Analysis - siam.in</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>NPST Confirms AGM Notice Dispatch and Annual Report Access for Shareholders - TipRanks</t>
+          <t>Manoj Vaibhav Gems (MVGJL) Surges 7.5% to ₹162.37: Bulls Test Key Resistance Zone - Strangle Setup - siam.in</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1097,68 +1089,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>NORTHARC.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Northern Arc Capital Limited</t>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>525.9500122070312</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>308.2000122070312</v>
+        <v>550.6500244140625</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>292</v>
+        <v>505.1000061035156</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>294.2000122070312</v>
+        <v>550.6500244140625</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v/>
+        <v>524.4500122070312</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>294.2000122070312</v>
+        <v>550.6500244140625</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1045892</v>
+        <v>1078848</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Northern ARC Capital Share Price: 8.39% rise, valuation - Univest</t>
+          <t>GRT Jewellers files TBZ open offer at ₹249.61; tendering opens Oct 26 - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Northern Arc Capital Q1 FY27 Net Profit Jumps 41% YoY to Record ₹114 Cr - Trade Brains</t>
+          <t>GRT Jewellers files TBZ open offer at ₹249.61; tendering opens Oct 26 - scanx.trade</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Refex Industries promoter pledges 20.9 lakh shares for collateral - scanx.trade</t>
+          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-31 — cnbctv:acd04171b094b:0 - TradingView</t>
+          <t>TBZ shares extend rally as GRT Jewellers deal sparks growth optimism - BusinessLine</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Northern Arc Capital Q1 FY27 Net Profit Jumps 41% YoY to Record ₹114 Cr - Trade Brains</t>
+          <t>Tribhovandas Bhimji Zaveri share price today: TBZ stock on fire again - What's driving the bull run? - Livemint</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1166,56 +1158,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NORBTEAEXP.NS</t>
+          <t>AARNAV.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Norben Tea &amp; Exports Limited</t>
+          <t>Aarnav Fashions Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>65.90000152587891</v>
+        <v>29.79999923706055</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>67.38999938964844</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>64.5</v>
+        <v>28.31999969482422</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.5</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v/>
+        <v>29.79000091552734</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>64.5</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1569</v>
+        <v>14023</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Norben Tea &amp; Exports Holds Near ₹65.29 as Stock Trades Within Key Range - Zero Gamma Level - siam.in</t>
+          <t>Aarnav Fashions Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Norben Tea &amp; Exports Holds Near ₹65.29 as Stock Trades Within Key Range - Zero Gamma Level - siam.in</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Aarnav Fashions AGM on Sep 30 to adopt FY26 accounts - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price: Buy or Sell - Univest</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>AARNAV Jun 2026 Earnings: Steady Profitability with ₹0.4 EPS on ₹86.53 Crore Revenue; Stock Gains 0.9% - siam.in</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions AGM on Sep 30 to adopt FY26 accounts - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1223,68 +1227,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>NLCINDIA.NS</t>
+          <t>QPOWER.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NLC India Limited</t>
+          <t>Quality Power Electrical Equipments Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>264.4500122070312</v>
+        <v>1344</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>266.3999938964844</v>
+        <v>1422.900024414062</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>256.2999877929688</v>
+        <v>1291.699951171875</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>261.0499877929688</v>
+        <v>1418</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v/>
+        <v>1355.199951171875</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>261.0499877929688</v>
+        <v>1418</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1336337</v>
+        <v>436126</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>NLC India Share Price - Live NSE: NLCINDIA Stock Price &amp; Chart - Upstox</t>
+          <t>QPOWER Share Price Today: price rise, PE and peer check - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>NLC India Share Price - Live NSE: NLCINDIA Stock Price &amp; Chart - Upstox</t>
+          <t>QPOWER Q2 2026 Earnings: Revenue Surges 183% YoY to ₹935.98 Crore Even as Stock Slips - Cash Flow Report - siam.in</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>NLC India Share Price Falls 3.89%: Price, Sector Analysis - Univest</t>
+          <t>QPOWER Share Price rise with Rs 10,145.95 Cr market cap - Univest</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NLC India Files Consolidated Sustainability Report for FY 2025-26 - The Globe and Mail</t>
+          <t>QPOWER Q2 2026 Earnings: Revenue Surges 183% YoY to ₹935.98 Crore Even as Stock Slips - Cash Flow Report - siam.in</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>NLC (NLCINDIA.NS) Levels: Records a 1.30% Increase to ₹273.30; Technical View - siam.in</t>
+          <t>QUALITY POWER ELEC EQUP L (QPOWER) Share Price hits fresh 52-week high on 4.41% rise - Univest</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1292,64 +1296,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NKIND.NS</t>
+          <t>TATVA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited</t>
+          <t>Tatva Chintan Pharma Chem Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>55.09999847412109</v>
+        <v>1560</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>59.5</v>
+        <v>1637.800048828125</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>55</v>
+        <v>1520</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.52000045776367</v>
+        <v>1618.5</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v/>
+        <v>1547.300048828125</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>55.52000045776367</v>
+        <v>1618.5</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1139</v>
+        <v>75667</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Stock Near Key Technical Levels - kalkine.co.in</t>
+          <t>Tatva Chintan Promoters Declare No Share Encumbrance for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Stock Near Key Technical Levels - kalkine.co.in</t>
+          <t>Tatva Chintan Pharma Chem Ltd Downgraded to Hold Amid Mixed Technical and Valuation Signals - MarketsMojo</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>International (IGIC) Latest Quarter: EPS Misses Its Estimate in Latest Trading; After Earnings: Shares Finish 2.35% Higher - Earnings Call Highlights - Vinanet</t>
+          <t>Tatva Chintan Pharma Chem Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Spire (SRJN) Q2 2026 Earnings: EPS Comes in Above Forecast in the Current Update; After Results - Vinanet</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Tatva Chintan Pharma Chem Ltd Downgraded to Hold Amid Mixed Technical and Valuation Signals - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Tatva Chintan FY26 Net Profit Surges to ₹420.54 Mn - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1357,68 +1365,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>NIVABUPA.NS</t>
+          <t>CMSINFO.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Niva Bupa Health Insurance Company Limited</t>
+          <t>CMS Info Systems Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>79.91999816894531</v>
+        <v>235.0800018310547</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>83.90000152587891</v>
+        <v>239</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>79.62999725341797</v>
+        <v>227.8000030517578</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>81.5</v>
+        <v>232.8099975585938</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v/>
+        <v>222.9100036621094</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>81.5</v>
+        <v>232.8099975585938</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1415602</v>
+        <v>4620116</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>NIVABUPA Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>CMS Info Systems Ltd. Share Price Today Hits One-Year Low - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Niva Bupa posts stronger q1 2027 profit, shares edge up - Investing.com</t>
+          <t>CMS Info Systems Ltd. Share Price Today at New One-Year Low - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Niva Bupa Health Insurance (NSE:NIVABUPA) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>CMS Info Systems Share Price: fresh 52-week low explained - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>IRDAI Approves Transfer of 14.62 Crore Equity Shares by Fettle Tone LLP in Niva Bupa Health Insurance - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Potential Upside For Niva Bupa Health Insurance Company Limited (NSE:NIVABUPA) Not Without Risk - simplywall.st</t>
-        </is>
-      </c>
+          <t>CMS Info Systems Ltd. Share Price Today at New One-Year Low - Univest</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,64 +1430,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>NEXTMEDIA.NS</t>
+          <t>FILATEX.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Next Mediaworks Limited</t>
+          <t>Filatex India Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3.809999942779541</v>
+        <v>81</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3.960000038146973</v>
+        <v>86.75</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3.779999971389771</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>3.829999923706055</v>
+        <v>85.87000274658203</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v/>
+        <v>82.41000366210938</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.829999923706055</v>
+        <v>85.87000274658203</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>15210</v>
+        <v>3309321</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Next Mediaworks Q1FY26 loss narrows to ₹88 lakh as going concern risk persists - scanx.trade</t>
+          <t>BSE Filatex India Stock: Elliott Wave Points TP 134 - Moneymunch</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Next Mediaworks Q1FY26 loss narrows to ₹88 lakh as going concern risk persists - scanx.trade</t>
+          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Next (NEXTMEDIA.NS) Latest Quarter: The Latest Report Adds New Financial Reference Points in the Latest Reading; Post-Report: The Stock Gains 1.29% in the Latest Session - Earnings Outlook Update - siam.in</t>
+          <t>Filatex India Stock Near Recent High Zone - Kalkine India</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Next Mediaworks dispatches FY26 annual report via weblink for unregistered shareholders - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Filatex India Share Price: price action and fundamentals - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1491,68 +1499,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NITCO.NS</t>
+          <t>EMPOWER.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Nitco Limited</t>
+          <t>Empower India Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>93.31999969482422</v>
+        <v>2.430000066757202</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>94.02999877929688</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>87.15000152587891</v>
+        <v>2.430000066757202</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>88.23999786376953</v>
+        <v>2.480000019073486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v/>
+        <v>2.380000114440918</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>88.23999786376953</v>
+        <v>2.480000019073486</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>463772</v>
+        <v>26139606</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Nitco shares rally nearly 14% on entering MoU with HOABL for joint development of Alibaug land; key details to know - Upstox</t>
+          <t>Penny stock under ₹10: Up 100% in six months | IT stock hits 5% upper circuit in five straight sessions - Livemint</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Nitco Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Penny stock under ₹10: Up 100% in six months | IT stock hits 5% upper circuit in five straight sessions - Livemint</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Nitco shares jump nearly 14% on Alibaug land deal with HOABL; up to ₹1,500 crore payout expected - CNBC TV18</t>
+          <t>NET Power Closes Acquisition of 123 MW Power Generation Rights From EMPower; Shares Rise - marketscreener.com</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Nitco Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>A West Texas project plans 10 gas engines totaling 123 megawatts - Stock Titan</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Nitco Ltd. (NITCO) Share Price Rises 8.25% Today to Rs 104.30 - Univest</t>
+          <t>AI penny stock under ₹10 hits 5% upper circuit as IndiaAI Mission boosts infrastructure demand - Livemint</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1560,68 +1568,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>NIRAJ.NS</t>
+          <t>INDOCO.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Niraj Cement Structurals Limited</t>
+          <t>Indoco Remedies Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>27.02000045776367</v>
+        <v>241.3899993896484</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>28.70000076293945</v>
+        <v>255.3000030517578</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>27.02000045776367</v>
+        <v>235</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>27.57999992370605</v>
+        <v>251.5</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v/>
+        <v>241.3899993896484</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27.57999992370605</v>
+        <v>251.5</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>19209</v>
+        <v>465021</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Gulshankumar Chopra acquires 49.82% stake in Niraj Cement Structurals - scanx.trade</t>
+          <t>Indoco Remedies Share Price Drops; Technicals in Focus - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Niraj Gemawat raises NINtec Systems stake to 18.44% - scanx.trade</t>
+          <t>Indoco Remedies Share Price Drops; Technicals in Focus - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Niraj Gemawat raises NINtec Systems stake to 18.44% - scanx.trade</t>
+          <t>Indoco Remedies shares jump 18% as UK medicines regulator clears Goa plant - CNBC TV18 - LinkedIn</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Niraj (NIRAJISPAT.NS) Price Update: Ends Down by 3.00% at ₹205.65 for the Current Session - siam.in</t>
+          <t>Indoco Remedies Shares Surge After UK Regulator Clears Goa Plant - Equitypandit</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Niraj Cement Structurals incorporates Niraj Group Foundation for CSR - scanx.trade</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-10 — cnbctv:f7742802d094b:0 - tradingview.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1629,60 +1637,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NINSYS.NS</t>
+          <t>SBCL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>NINtec Systems Limited</t>
+          <t>Shivalik Bimetal Controls Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>725</v>
+        <v>1020</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>725</v>
+        <v>1070.900024414062</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>700.0499877929688</v>
+        <v>957.0999755859375</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>710.75</v>
+        <v>1062.199951171875</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v/>
+        <v>1020.200012207031</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>710.75</v>
+        <v>1062.199951171875</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3821</v>
+        <v>472078</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>NINTEC SYSTEMS LIMITED Share Price - Upstox</t>
+          <t>Sirmaur Hospitality Acquires 67,500 Shares in Shivalik Bimetal Controls Through Open Market - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>NINTEC SYSTEMS LIMITED Share Price - Upstox</t>
+          <t>Sirmaur Hospitality Acquires 67,500 Shares in Shivalik Bimetal Controls Through Open Market - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>NINtec (NINSYS.NS) Financial Update: The Report Provides a New Financial Snapshot under the Current Snapshot; After Results: Shares Finish 1.42% Down for the Current Session - Earnings Yield Analysis - siam.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t>Read This Before Considering Shivalik Bimetal Controls Limited (NSE:SBCL) For Its Upcoming ₹2.00 Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Shivalik Bimetal Controls Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1690,68 +1702,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>NILKAMAL.NS</t>
+          <t>SAMHI.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Nilkamal Limited</t>
+          <t>Samhi Hotels Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2050.800048828125</v>
+        <v>152.0500030517578</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2069.89990234375</v>
+        <v>164</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1989</v>
+        <v>149</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2017.900024414062</v>
+        <v>158.9700012207031</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v/>
+        <v>152.7299957275391</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2017.900024414062</v>
+        <v>158.9700012207031</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>19595</v>
+        <v>3929028</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Nilkamal FY26 revenue rises 14% to ₹3,686 crore - scanx.trade</t>
+          <t>Samhi Hotels shareholders approve ₹750 crore raise despite institutional dissent - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Nilkamal FY26 revenue rises 14% to ₹3,686 crore - scanx.trade</t>
+          <t>Samhi Hotels shareholders approve ₹750 crore raise despite institutional dissent - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Nilkamal Ltd. Share Price: Technicals Near 52-Week High - Univest</t>
+          <t>Samhi Hotels (SAMHI.NS) Edges Lower by 1.05% to ₹151.45; Key Support at ₹143.88 Holds Focus - Defined Outcome ETF - siam.in</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Nilkamal (NILKAMAL.NS) Results at a Glance: The Latest Financial Metrics Are Now Available in Latest Trading; Stock Move: Shares Fall 1.32% in the Latest Session - EPS Miss Report - siam.in</t>
+          <t>Samhi Hotels Ltd Downgraded to Strong Sell Amid Technical and Fundamental Concerns - MarketsMojo</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Nilkamal Share Price at Fresh 52-Week High; Valuation View - Univest</t>
+          <t>FMR LLC raises stake in Samhi Hotels to 5.06% via open market buys - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1759,68 +1771,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NILE.NS</t>
+          <t>KAVDEFENCE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Nile Limited</t>
+          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1440</v>
+        <v>74.72000122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1488</v>
+        <v>79.90000152587891</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1430</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1431.900024414062</v>
+        <v>78</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v/>
+        <v>75.16999816894531</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1431.900024414062</v>
+        <v>78</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1971</v>
+        <v>989678</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Nile Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Kavveri Defence Slides 1.4% to ₹57.02: Stock Holds Key Support Amid Defence Sector Retracement - AAII Bullish - siam.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Stratford reports first human case of West Nile virus, officials say - CTPost</t>
+          <t>Kavveri Defence Share Price Today: Sector and Peer View - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Nile Limited (NILE): Lead Recycling Compounder in Focus - kalkine.co.in</t>
+          <t>Kavveri Defence Share Price Today: Sector and Peer View - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Expert shares best defense against West Nile is preventing mosquito bites altogether - wcnc.com</t>
+          <t>Where Does Kavveri Defence &amp; Wireless Technologies Limited (NSE: KAVDEFENCE) Stand After Its 17.33% Advance? - Kalkine India</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Stratford reports first human case of West Nile virus, officials say - CTPost</t>
+          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1828,54 +1840,58 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>NILASPACES.NS</t>
+          <t>PARAGMILK.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces Limited</t>
+          <t>Parag Milk Foods Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>12.27999973297119</v>
+        <v>252</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>12.5600004196167</v>
+        <v>261.6499938964844</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>12</v>
+        <v>246.3000030517578</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>12.22999954223633</v>
+        <v>261.3500061035156</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v/>
+        <v>252.1499938964844</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12.22999954223633</v>
+        <v>261.3500061035156</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1058182</v>
+        <v>1128190</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
+          <t>Parag Milk Foods Ltd. (PARAGMILK) Share Price Rises 8.79% Today - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
+          <t>Parag Milk Foods Publishes AGM, E-Voting Notice Ahead of September Meeting - TipRanks</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces promoter Kiran B Vadodaria sells 737,197 shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
+          <t>Parag Milk Foods Share Price Today: Rs 256.5 after rise - Univest</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Parag Milk Foods Publishes AGM, E-Voting Notice Ahead of September Meeting - TipRanks</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1895,14 +1911,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2001,7 +2017,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2009,68 +2025,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>LASA.NS</t>
+          <t>PNCINFRA.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics Limited</t>
+          <t>PNC Infratech Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>132</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>133.2899932861328</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>116.4000015258789</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>128.3999938964844</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6.519999980926514</v>
+        <v>140.3200073242188</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>128.3999938964844</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>18314</v>
+        <v>14556667</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-4.91</v>
+        <v>-8.49</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>PNC Infratech shares tumble 20% to hit 52-week low; here's why - Business Today</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics appoints Janardan Savala as executive director - scanx.trade</t>
+          <t>NHAI extends debarment to PNC Infratech; stock hits 52-week low - tradingview.com</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Lasa (LASA.NS) Latest: Posts a 1.57% Gain to ₹7.10 on the Day; Next Test: the Supplied Trading Band Runs From ₹6.74 to ₹7.46 in the Available Record - Pre-Earnings Momentum - siam.in</t>
+          <t>PNC Infratech (NSE: PNCINFRA) Faces NHAI Debarment Extension - Kalkine India</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics appoints Janardan Savala as executive director - scanx.trade</t>
+          <t>NHAI extends debarment to PNC Infratech; stock hits 52-week low - tradingview.com</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics accepts Ganesh Potdar resignation as WTD - scanx.trade</t>
+          <t>PNC Infratech shares hit 20% lower circuit as NHAI extends Awadh Expressway debarment to company; all you need to know - upstox.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2078,68 +2094,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CENTEXT.NS</t>
+          <t>HTEL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>21.95000076293945</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>21.95000076293945</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>19.79999923706055</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>19.97999954223633</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20.36000061035156</v>
+        <v>81.31999969482422</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>19.97999954223633</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>888517</v>
+        <v>3054221</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-1.87</v>
+        <v>-8.24</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions (NSE:CENTEXT): Why Was the Rights Issue Letter of Offer Revised? - kalkine.co.in</t>
+          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions (NSE:CENTEXT): Why Was the Rights Issue Letter of Offer Revised? - kalkine.co.in</t>
+          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Century (CENTEXT.NS) Update: Finishes 0.23% Lower at ₹22.13; the Current Price Sits Inside the Supplied Technical Range in the Latest Reading - Swing Entry Signals - siam.in</t>
+          <t>Free float of Hy-Tech Engineers Limited – NSE:HTEL - tradingview.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Cogent (CCOI) Latest: Slides 3.42% to $10.01 for the Current Session; Next Test - Vinanet</t>
+          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Century Extrusions reports FY26 net profit of ₹1,057 lakh - scanx.trade</t>
+          <t>Hy-Tech Engineers Ltd. (HTEL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2147,68 +2163,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PANORAMA.NS</t>
+          <t>YATRA.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios International Limited</t>
+          <t>Yatra Online Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>55.40000152587891</v>
+        <v>107.4899978637695</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>56.18000030517578</v>
+        <v>108.9800033569336</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>50.34999847412109</v>
+        <v>102.2200012207031</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>51.91999816894531</v>
+        <v>102.3000030517578</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v/>
+        <v>107.9599990844727</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>51.91999816894531</v>
+        <v>102.3000030517578</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>572747</v>
+        <v>867226</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>-5.24</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios sets AGM for Sept 30, seeks ₹1,500 crore borrowing limit - scanx.trade</t>
+          <t>Yatra Online schedules 20th AGM for September 15 via video conference - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios sets AGM for Sept 30, seeks ₹1,500 crore borrowing limit - scanx.trade</t>
+          <t>New bidder for Yatra Online (YTRA) makes cash offer with broad conditions attached - Stock Titan</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios Share Price rises 13.84% with valuation - Univest</t>
+          <t>New bidder for Yatra Online (YTRA) makes cash offer with broad conditions attached - Stock Titan</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios International Ltd. Stock News - Value Research</t>
+          <t>Kailash Mansarovar Yatra Experience: Mumbai-Based Senior Journalist Preeti Sompura Shares Her Divine and Life-Changing Spiritual Journey - Hello Mumbai News</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios International Ltd is Rated Hold - MarketsMojo</t>
+          <t>Yatra Online submits revised annual report for FY26 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2216,68 +2232,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>OBEROIRLTY.NS</t>
+          <t>CYIENTDLM.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Oberoi Realty Limited</t>
+          <t>Cyient DLM Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1746</v>
+        <v>882.4000244140625</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1749.5</v>
+        <v>884.6500244140625</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1668.5</v>
+        <v>811.9500122070312</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1668.5</v>
+        <v>837.2000122070312</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v/>
+        <v>882.7000122070312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1668.5</v>
+        <v>837.2000122070312</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>362396</v>
+        <v>593406</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-5.15</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Oberoi Realty Share Price - Live NSE: OBEROIRLTY Stock Price &amp; Chart - Upstox</t>
+          <t>Cyient DLM Share Price: fresh 52-week high, fundamentals - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Oberoi Realty Share Price - Live NSE: OBEROIRLTY Stock Price &amp; Chart - Upstox</t>
+          <t>Cyient DLM Share Price: fresh 52-week high and valuation - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Oberoi (OBEROIRLTY.NS) Results Review: Available Data Shows the Latest Reported Performance for This Review; Trading Response: Shares Move Lower 0.98% in the Current Update - Post-Earnings Reaction - siam.in</t>
+          <t>Cyient DLM Share Price: fresh 52-week high and valuation - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Oberoi Realty Ltd. Share Price Update With Peer Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Oberoi Realty (OBEROIRLTY) Share Price Falls 2.25% Today: Price Action, Valuation and Realty Sector Analysis - Univest</t>
-        </is>
-      </c>
+          <t>Cyient DLM to host analyst meet with Kotak MF on August 21 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2285,68 +2297,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NYKAA.NS</t>
+          <t>STLTECH.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Limited</t>
+          <t>Sterlite Technologies Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>345.3999938964844</v>
+        <v>809.9500122070312</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>346.1499938964844</v>
+        <v>839</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>336.2000122070312</v>
+        <v>809.9500122070312</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>336.2000122070312</v>
+        <v>809.9500122070312</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v/>
+        <v>852.5499877929688</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>336.2000122070312</v>
+        <v>809.9500122070312</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2338415</v>
+        <v>1793505</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Nykaa Q2 FY27 Results Preview - Univest</t>
+          <t>Ankit Agarwal confirms no encumbrance on Sterlite Technologies shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Nykaa Q2 FY27 Results Preview - Univest</t>
+          <t>Ankit Agarwal confirms no encumbrance on Sterlite Technologies shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Top stock picks: Kalyan Jewellers, Nykaa, Adani Ports among 6 trades recommended by experts - CNBC TV18</t>
+          <t>STLTECH Q2 2026 Earnings: Revenue Surges 19.3% YoY to ₹4,663 Crore; Stock Gains 4% - Energy Earnings Report - siam.in</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Nykaa officials to attend investor meets in London from June 22 - scanx.trade</t>
+          <t>Sterlite (STLTECH.NS) Move: Adds 1.75% to Close at ₹662.75 in the Latest Session; Range View: Price Remains Between ₹629.61 Support and ₹695.89 Resistance for the Current Session - Impulse Wave - siam.in</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Nykaa Shares Rise Over 2% Today - Moneycontrol.com</t>
+          <t>Sterlite Technologies shares: Over 740% returns in 2026 so far; stock hits 52-week high | What's next for investors? - tradingview.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2354,68 +2366,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NUCLEUS.NS</t>
+          <t>RADHIKAJWE.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Nucleus Software Exports Limited</t>
+          <t>Radhika Jeweltech Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>691.4000244140625</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>707.5499877929688</v>
+        <v>74.69999694824219</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>691.4000244140625</v>
+        <v>71.69999694824219</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>696.4000244140625</v>
+        <v>71.69999694824219</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v/>
+        <v>75.47000122070312</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>696.4000244140625</v>
+        <v>71.69999694824219</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>20850</v>
+        <v>76996</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Nucleus Software proposes buying 1.14 lakh shares for employee RSU scheme - scanx.trade</t>
+          <t>Radhika Jeweltech Dips 2.6% to ₹68.5: Support and Resistance Levels in Spotlight - Wave Equality - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Nucleus Software order book jumps 19% to ₹1,244 crore in Q1FY27 - scanx.trade</t>
+          <t>Does Radhika Jeweltech (NSE:RADHIKAJWE) Deserve A Spot On Your Watchlist? - webull.com</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Nucleus Software board approves insider trading code amendments - scanx.trade</t>
+          <t>Does Radhika Jeweltech (NSE:RADHIKAJWE) Deserve A Spot On Your Watchlist? - webull.com</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Nucleus Software Q2 2026 Earnings: EPS at ₹44.35 on ₹876.03 Crore Revenue; NSE Stock Gains 0.96% - Earnings Miss Streak - siam.in</t>
+          <t>Does Radhika Jeweltech (NSE:RADHIKAJWE) Deserve A Spot On Your Watchlist? - simplywall.st</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Nucleus Software order book jumps 19% to ₹1,244 crore in Q1FY27 - scanx.trade</t>
+          <t>Radhika Jeweltech Files Tenth Annual Report for FY 2025-26 With Stock Exchanges - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2423,56 +2435,56 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>NTPCGREEN.NS</t>
+          <t>KESORAMIND.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NTPC Green Energy Limited</t>
+          <t>Kesoram Industries Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>86.94000244140625</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>87.01999664306641</v>
+        <v>12.34000015258789</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>85.75</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>85.86000061035156</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v/>
+        <v>12.60000038146973</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>85.86000061035156</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2072032</v>
+        <v>502687</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>NTPC (NTPCGREEN.NS) Session: Loses 0.28% to Close at ₹91.62 in Latest Trading - siam.in</t>
+          <t>Kesoram Industries: Frontier Warehousing Acquires 42.8% Stake via Off-Market Transfer - Whalesbook</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>NTPC Green shares jump over 3% as it commissions 100 MW power at IRPL plant - Business Upturn</t>
+          <t>Kesoram Industries: Frontier Warehousing Acquires 42.8% Stake via Off-Market Transfer - Whalesbook</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>NTPC (NTPCGREEN.NS) Today: Rises 0.33% to ₹92.00 in Latest Trading; Chart View: Support at ₹87.40 and Resistance at ₹96.60 Frame the Range in the Available Record - Mean Reversion Trade - siam.in</t>
+          <t>Kesoram Industries: Frontier Warehousing का बड़ा दांव, खरीदी **42.8%** हिस्सेदारी - Whalesbook</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>NTPC Green shares jump over 3% as it commissions 100 MW power at IRPL plant - Business Upturn</t>
+          <t>Kesoram Industries માં મોટા ફેરફાર: Frontier Warehousing એ **42.8%** હિસ્સો ખરીદ્યો - Whalesbook</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -2480,7 +2492,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2488,68 +2500,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>NILE.NS</t>
+          <t>UEL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Nile Limited</t>
+          <t>Ujaas Energy Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1440</v>
+        <v>214</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1488</v>
+        <v>214</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1430</v>
+        <v>204.7700042724609</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1431.900024414062</v>
+        <v>204.7700042724609</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v/>
+        <v>215.5399932861328</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1431.900024414062</v>
+        <v>204.7700042724609</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1971</v>
+        <v>16253</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Nile Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Ujaas Energy NSE:UEL Price Movement Clarification Sep 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Stratford reports first human case of West Nile virus, officials say - CTPost</t>
+          <t>Ujaas Energy Ltd. Lower Circuit Streak: Day 2 Price and Data - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Nile Limited (NILE): Lead Recycling Compounder in Focus - kalkine.co.in</t>
+          <t>Ujaas (UEL.NS) Earnings Update: The Company Publishes Its Latest Results in Latest Trading; The Market Price Declines 5.00% for the Current Session - Earnings Revision Report - siam.in</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Expert shares best defense against West Nile is preventing mosquito bites altogether - wcnc.com</t>
+          <t>Ujaas Energy Ltd. Lower Circuit Streak: Day 2 Price and Data - Univest</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Stratford reports first human case of West Nile virus, officials say - CTPost</t>
+          <t>Luxembourg's Social Partners Strike Wage Deal — Pay Indexation Pushed to Spring 2027 - ad-hoc-news.de</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2557,60 +2569,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>NILASPACES.NS</t>
+          <t>DIGJAMLMTD.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces Limited</t>
+          <t>Digjam Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12.27999973297119</v>
+        <v>62.04000091552734</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>12.5600004196167</v>
+        <v>62.04999923706055</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>12</v>
+        <v>61.75</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>12.22999954223633</v>
+        <v>61.75</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12.22999954223633</v>
+        <v>61.75</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1058182</v>
+        <v>4206</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
+          <t>Digjam Share Price rises 14.59%: price action - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
+          <t>Digjam Share Price rises 14.59%: price action - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces promoter Kiran B Vadodaria sells 737,197 shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
+          <t>Digjam Ltd Gains 2.11% to ₹51.73: Textile Stock Holds Above Key Support - Turnaround Stocks - siam.in</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Digjam Limited: స్కీమ్ ఆఫ్ అరేంజ్మెంట్‌పై NCLT కీలక ఆదేశాలు.. అక్టోబర్ 28న తదుపరి విచారణ - Whalesbook</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2618,68 +2634,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NSIL.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Nalwa Sons Investments Limited</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5623</v>
+        <v>60.20000076293945</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5623</v>
+        <v>60.79000091552734</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5400</v>
+        <v>58.5099983215332</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5409.5</v>
+        <v>58.5099983215332</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v/>
+        <v>61.58000183105469</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5409.5</v>
+        <v>58.5099983215332</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1651</v>
+        <v>279339</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>-4.99</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Nalwa Sons Investments Holds Gains: Stock Climbs 0.68% to ₹5,721.5 Amid Rangebound Trade - Bear Pennant - siam.in</t>
+          <t>PVP Ventures Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Nalwa Sons Investments Holds Gains: Stock Climbs 0.68% to ₹5,721.5 Amid Rangebound Trade - Bear Pennant - siam.in</t>
+          <t>PVP Ventures Secures Shareholder Approval on All AGM Resolutions - TipRanks</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Nalwa (NSIL.NS): Moves 0.73% Lower to ₹5,682.50; Levels: Traders Can Monitor the ₹5,398.38-₹5,966.62 Range under the Current Snapshot - Channel Projection - siam.in</t>
+          <t>143% Return In One Month: Multibagger Smallcap Stock Hits 5% Upper Circuit In Trade. Here's Why - NDTV Profit</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>APOORVA Stock Price and Chart — NSE:APOORVA - TradingView</t>
+          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>NSIL Q2 2026 Earnings: Revenue Slides 18% to ₹906.8 Million, EPS at ₹106.13 - Dividend Increase Stocks - siam.in</t>
+          <t>PVP (PVP.NS) Results Versus Estimates: The Company Lists Its Latest Available Figures on the Day; Price Move: Shares Move 5.10% Higher at the Close - Next Quarter Guidance - siam.in</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2687,68 +2703,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>NRBBEARING.NS</t>
+          <t>MOLBIO.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NRB Bearing Limited</t>
+          <t>Molbio Diagnostics Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>516</v>
+        <v>1385</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>516.7999877929688</v>
+        <v>1437.599975585938</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>478</v>
+        <v>1196.199951171875</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>1289.599975585938</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v/>
+        <v>1356.800048828125</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>1289.599975585938</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>504747</v>
+        <v>6666766</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>-4.95</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>NRB Bearings Ltd. (NRBBEARING) Share Price Trades Within 2% of 52-Week High - Univest</t>
+          <t>Recently listed Molbio Diagnostics share price falls 9%: Healthcare stock loses 18.5% in 2 days after blockbuster rally - Livemint</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Granules India promoter offloads shares worth Rs 1,509 crore; Morgan Stanley picks stake in Lotus Developers - TradingView</t>
+          <t>Molbio Diagnostics drops 8.8% to ₹1,229.65 still 50%+ above IPO - NewsBytes</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>NRB Bearings Share Price Today: Market Cap and Valuation - Univest</t>
+          <t>Molbio Diagnostics Q1FY27 net profit up 523% to ₹52.7 crore on deferred exports - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NRB Bearings 52 Week High Streak: Second Straight Session - Univest</t>
+          <t>Molbio Diagnostics shares surge over 50% in just 3 days! What is driving the rally? - tradingview.com</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Granules India promoter offloads shares worth Rs 1,509 crore; Morgan Stanley picks stake in Lotus Developers - TradingView</t>
+          <t>Molbio Diagnostics shares surge 35% in two sessions; here’s why the healthcare stock hit record high on Sept 10 - upstox.com</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2756,68 +2772,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NRAIL.NS</t>
+          <t>ASHOKAMET.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries Limited</t>
+          <t>Ashoka Metcast Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>638</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>685</v>
+        <v>15.18000030517578</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>631</v>
+        <v>14.10999965667725</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>638.8499755859375</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v/>
+        <v>15.14000034332275</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>638.8499755859375</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>113595</v>
+        <v>110616</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>-4.62</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
+          <t>Ashoka Metcast Hits Fresh High: Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
+          <t>Ashoka Metcast Hits Fresh High: Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>NR Agarwal Industries Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Ashoka Metcast sells 2.48M Mena Mani Industries shares in open market - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries appoints Manoj Chauhan as Chief Marketing Officer - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>NR Agarwal Industries Share Price today: key market update - Univest</t>
-        </is>
-      </c>
+          <t>Ashoka Metcast Publishes FY26 Audited Financial Results Ad Under Regulation 47 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2825,68 +2837,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>NPST.NS</t>
+          <t>STEELCAS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Network People Services Technologies Limited</t>
+          <t>Steelcast Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1698.900024414062</v>
+        <v>309</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1700</v>
+        <v>314.6499938964844</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1630</v>
+        <v>297.6000061035156</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1639.5</v>
+        <v>299</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v/>
+        <v>312.75</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1639.5</v>
+        <v>299</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>27585</v>
+        <v>121415</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
+          <t>Steelcast Limited (STEELCAS.NS) Edges Higher: Can It Sustain Momentum? - Put Flow Alert - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+          <t>Steelcast Limited (STEELCAS.NS) Edges Higher: Can It Sustain Momentum? - Put Flow Alert - siam.in</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>NPST wins Best Digital Banking Platform at Global Fintech Awards 2026 - scanx.trade</t>
+          <t>Steelcast Limited (STEELCAS.NS) Gains Momentum: Key Levels and Volume Insights - NAAIM Leverage - Vinanet</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+          <t>STEELCAS Stock Price and Chart — NSE:STEELCAS - tradingview.com</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>NPST Confirms AGM Notice Dispatch and Annual Report Access for Shareholders - TipRanks</t>
+          <t>Steelcast Share Price - upstox.com</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2894,68 +2906,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>NORTHARC.NS</t>
+          <t>LOTUSDEV.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Northern Arc Capital Limited</t>
+          <t>Sri Lotus Developers and Realty Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>209.5099945068359</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>308.2000122070312</v>
+        <v>211.9799957275391</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>292</v>
+        <v>202.8699951171875</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>294.2000122070312</v>
+        <v>204.2599945068359</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v/>
+        <v>213.5399932861328</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>294.2000122070312</v>
+        <v>204.2599945068359</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1045892</v>
+        <v>665269</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>-4.35</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Northern ARC Capital Share Price: 8.39% rise, valuation - Univest</t>
+          <t>LOTUSDEV-BE 52 Week High Streak After Second Straight Peak - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Northern Arc Capital Q1 FY27 Net Profit Jumps 41% YoY to Record ₹114 Cr - Trade Brains</t>
+          <t>Sri Lotus Developers Plans Investor Meetings at Mumbai Conference - TipRanks</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Refex Industries promoter pledges 20.9 lakh shares for collateral - scanx.trade</t>
+          <t>Sri (LOTUSDEV.NS) Results Versus Estimates: Available Data Shows the Latest Reported Performance; Market Reaction: The Stock Records a 1.99% Increase in the Current Update - Profit Recovery Report - siam.in</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-31 — cnbctv:acd04171b094b:0 - TradingView</t>
+          <t>SRI LOTUS DEVLPRS N RTY L (LOTUSDEV-BE) Share Price hits fresh 52-week high on 10 September 2026 - Univest</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Northern Arc Capital Q1 FY27 Net Profit Jumps 41% YoY to Record ₹114 Cr - Trade Brains</t>
+          <t>Sri Lotus Developers receives GST DRC-07 order for FY20-21, 21-22, 23-24 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2963,56 +2975,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NORBTEAEXP.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Norben Tea &amp; Exports Limited</t>
+          <t>Pine Labs Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>65.90000152587891</v>
+        <v>198</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>67.38999938964844</v>
+        <v>198</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>64.5</v>
+        <v>175.3000030517578</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>64.5</v>
+        <v>185.4900054931641</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v/>
+        <v>193.8000030517578</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>64.5</v>
+        <v>185.4900054931641</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1569</v>
+        <v>85272142</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>-4.29</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Norben Tea &amp; Exports Holds Near ₹65.29 as Stock Trades Within Key Range - Zero Gamma Level - siam.in</t>
+          <t>Pine Labs share price jumps 13%: Fintech stock rises sharply as trading volume explodes - Livemint</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Norben Tea &amp; Exports Holds Near ₹65.29 as Stock Trades Within Key Range - Zero Gamma Level - siam.in</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>PINE LABS (PINELABS) Share Price Falls 3.93% Today: What the Decline Shows - Univest</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Pine Labs Share Price Today Up 2.43%: Fundamental Check - Univest</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Pine (PINELABS.NS) Chart: Loses 1.77% to Close at ₹156.91 for the Current Session; Market Levels: ₹149.06 and ₹164.76 Define the Nearby Reference Levels in Latest Trading - Sign of Strength - siam.in</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Pine Labs sends FY26 annual report weblink to shareholders - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3020,68 +3044,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>PANSARI.NS</t>
+          <t>AQYLON.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Pansari Developers Limited</t>
+          <t>Aqylon Nexus Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>281.5</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>299</v>
+        <v>20.54999923706055</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>275</v>
+        <v>19.79000091552734</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>282.1499938964844</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v/>
+        <v>20.70999908447266</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>282.1499938964844</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>312</v>
+        <v>404599</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>-4.15</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Pansari Developers Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>Leading Leasing sells 1.47 cr Aqylon Nexus shares - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Pansari Developers Publishes Notice for 30th AGM in Kolkata Dailies - TipRanks</t>
+          <t>Aqylon Nexus Standalone June 2026 Net Sales at Rs 8.47 crore, up 24294.81% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Pansari Developers (PANSARI.NS) Declines 2.53% to ₹296.1; Support at ₹281.3 in Focus - McClellan Oscillator - siam.in</t>
+          <t>AQYLON Stock Price and Chart — NSE:AQYLON - tradingview.com</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Pansari Developers Share Price Target 2027 to 2030: Analyst Outlook - Univest</t>
+          <t>Why Is Aqylon Nexus Share Price Falling: Key Reasons and Investor Analysis 2026 - Univest</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Pansari Developers Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Aqylon Nexus Standalone June 2026 Net Sales at Rs 8.47 crore, up 24294.81% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3089,64 +3113,56 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ODIGMA.NS</t>
+          <t>NECLIFE.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Odigma Consultancy Solutions Limited</t>
+          <t>Nectar Lifesciences Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>22.1200008392334</v>
+        <v>11.40999984741211</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>22.44000053405762</v>
+        <v>11.68000030517578</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>21.5</v>
+        <v>10.82999992370605</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>22.09000015258789</v>
+        <v>10.93000030517578</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v/>
+        <v>11.39999961853027</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22.09000015258789</v>
+        <v>10.93000030517578</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>9536</v>
+        <v>155205</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>-4.12</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Odigma Consultancy shareholders approve FY26 financials, re-appoint Vishal Mehta - scanx.trade</t>
+          <t>Nectar Lifesciences Rises 2.09%: NECLIFE Stock Holds Near ₹11.23 on NSE - Dealer Positioning - siam.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Odigma Consultancy shareholders approve FY26 financials, re-appoint Vishal Mehta - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Odigma Consultancy Solutions Gains 3.25% to ₹23.16, Approaches Key Resistance at ₹24.32 - Sentiment Shift - siam.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Odigma (ODIGMA.NS) Results Breakdown: The Company Publishes Its Latest Results in the Current Update; Trading Response: Shares Move 1.12% Up at the Close - Healthcare Earnings Report - siam.in</t>
-        </is>
-      </c>
+          <t>Nectar Lifesciences Rises 2.09%: NECLIFE Stock Holds Near ₹11.23 on NSE - Dealer Positioning - siam.in</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3154,68 +3170,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>NIVABUPA.NS</t>
+          <t>CARTRADE.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Niva Bupa Health Insurance Company Limited</t>
+          <t>Cartrade Tech Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>79.91999816894531</v>
+        <v>3037</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>83.90000152587891</v>
+        <v>3064.89990234375</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>79.62999725341797</v>
+        <v>2856.699951171875</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>81.5</v>
+        <v>2896.10009765625</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v/>
+        <v>3017.10009765625</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>81.5</v>
+        <v>2896.10009765625</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1415602</v>
+        <v>306503</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>-4.01</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>NIVABUPA Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>CarTrade Tech Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Niva Bupa posts stronger q1 2027 profit, shares edge up - Investing.com</t>
+          <t>Cartrade Tech Ltd is Rated Hold - MarketsMojo</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Niva Bupa Health Insurance (NSE:NIVABUPA) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>CarTrade Tech Share Price Today: 5.08% Fall, Valuation Check - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>IRDAI Approves Transfer of 14.62 Crore Equity Shares by Fettle Tone LLP in Niva Bupa Health Insurance - scanx.trade</t>
+          <t>Do CarTrade Tech's (NSE:CARTRADE) Earnings Warrant Your Attention? - simplywall.st</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Potential Upside For Niva Bupa Health Insurance Company Limited (NSE:NIVABUPA) Not Without Risk - simplywall.st</t>
+          <t>CarTrade Tech shares jump to the highest level of 2026 after gaining 14% in two sessions - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3223,56 +3239,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NITTAGELA.NS</t>
+          <t>SUMEETINDS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Nitta Gelatin India Limited</t>
+          <t>Sumeet Industries Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1625.400024414062</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1807</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1602.199951171875</v>
+        <v>9.729999542236328</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1693</v>
+        <v>9.840000152587891</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v/>
+        <v>10.23999977111816</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1693</v>
+        <v>9.840000152587891</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>14080</v>
+        <v>1426378</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>-3.91</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Nitta Gelatin India (NITTAGELA.NS) Eases 0.76% to ₹1,654.40 as Stock Tests Mid-Range Support - Dynamic Hedging - siam.in</t>
+          <t>Sumeet Industries AGM Notice 2026: NSE:SUMEETINDS Filing - Kalkine India</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Nitta Gelatin India (NITTAGELA.NS) Eases 0.76% to ₹1,654.40 as Stock Tests Mid-Range Support - Dynamic Hedging - siam.in</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+          <t>Sumeet Industries Addresses NSE Queries and Defers Rights Issue Decision - TipRanks</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Sumeet Industries submits Q1FY27 earnings call audio recording - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Sumeet Industries Addresses NSE Queries and Defers Rights Issue Decision - TipRanks</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:44:28 IST</t>
+          <t>2026-09-16 13:19:18 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3280,61 +3304,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>NITCO.NS</t>
+          <t>UTTAMSUGAR.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Nitco Limited</t>
+          <t>Uttam Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>93.31999969482422</v>
+        <v>257</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>94.02999877929688</v>
+        <v>258.3500061035156</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>87.15000152587891</v>
+        <v>244.1000061035156</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>88.23999786376953</v>
+        <v>246.6999969482422</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v/>
+        <v>256.6499938964844</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>88.23999786376953</v>
+        <v>246.6999969482422</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>463772</v>
+        <v>156066</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>-3.88</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Nitco shares rally nearly 14% on entering MoU with HOABL for joint development of Alibaug land; key details to know - Upstox</t>
+          <t>Uttam Sugar Mills Share Price - upstox.com</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Nitco Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Uttam Sugar Mills Share Price Fall: Price Action Review - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Nitco shares jump nearly 14% on Alibaug land deal with HOABL; up to ₹1,500 crore payout expected - CNBC TV18</t>
+          <t>Uttam Sugar Mills Share Price Fall: Price Action Review - Univest</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Nitco Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Uttam Sugar Mills Limited (NSE:UTTAMSUGAR) Passed Our Checks, And It's About To Pay A ₹2.50 Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Nitco Ltd. (NITCO) Share Price Rises 8.25% Today to Rs 104.30 - Univest</t>
+          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CSM.NS</t>
+          <t>QUINT.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Limited</t>
+          <t>Quint Digital Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>91.98999786376953</v>
+        <v>57.88000106811523</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>103.4499969482422</v>
+        <v>57.88000106811523</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>88.68000030517578</v>
+        <v>57.88000106811523</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>98.73000335693359</v>
+        <v>57.88000106811523</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>89.84999847412109</v>
+        <v>48.2400016784668</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>98.73000335693359</v>
+        <v>57.88000106811523</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2318647</v>
+        <v>41492</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>19.98</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
+          <t>Quint Digital Share Price near 52-week high, valuation view - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
+          <t>Quint Digital Share Price near 52-week high, valuation view - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Quint Digital Share Price Today Near Yearly High | QUINT - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>CSM Share Price Today Falls: P/E, P/B and Sector Context - Univest</t>
+          <t>Quint Digital Stock Enters New Momentum Phase - Kalkine India</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>How (CSM) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
+          <t>Quint Digital board approves related party loans and asset pledges - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE.NS</t>
+          <t>VTMLTD.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Limited</t>
+          <t>VTM Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>350.1499938964844</v>
+        <v>40</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>367.2999877929688</v>
+        <v>50.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>332.3500061035156</v>
+        <v>39.15000152587891</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>363.8500061035156</v>
+        <v>48.83000183105469</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>333.9500122070312</v>
+        <v>42.16999816894531</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>363.8500061035156</v>
+        <v>48.83000183105469</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2691567</v>
+        <v>388201</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>15.79</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+          <t>VTM Ltd. Share Price rises 13.42%: valuation view - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Nature's Sunshine (NATR) awards CFO 75,433 stock units vesting over three years - Stock Titan</t>
+          <t>VTM Ltd. Share Price rises 13.42%: valuation view - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures IPO Listing: Shares List at 9.97% Premium on NSE, Fall Short of Grey-Market Hopes - India Infoline</t>
+          <t>VTMLTD Stock Price and Chart — NSE:VTMLTD - TradingView</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of CHERISH SUNSHINE INTL LTD. – OTC:CHSIF - tradingview.com</t>
+          <t>VTM Share Price Fall: Technicals, Valuation, Sector - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures shares list at 10% premium over IPO price - The Economic Times</t>
+          <t>VTM Ltd. (VTMLTD) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KOPRAN.NS</t>
+          <t>ATAM.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kopran Limited</t>
+          <t>Atam Valves Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>251.5</v>
+        <v>53.70000076293945</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>274.7799987792969</v>
+        <v>65</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>237.7799987792969</v>
+        <v>52.91999816894531</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>269.7099914550781</v>
+        <v>62.15000152587891</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>249.8999938964844</v>
+        <v>54.66999816894531</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>269.7099914550781</v>
+        <v>62.15000152587891</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>6882018</v>
+        <v>168135</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7.93</v>
+        <v>13.68</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Kopran Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Atam Valves Limited Receives API Spec Q1 Certification From American Petroleum Institute - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Kopran Q2 FY27 Preview: What to Watch Before Results - Univest</t>
+          <t>Dividend record date alert: Last chance to buy today for cash reward; Hindustan Copper, Bajaj Steel, VST Tillers, others - TradingView</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Kopran Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Atam Valves Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Kopran Q2 FY27 Preview: What to Watch Before Results - Univest</t>
+          <t>Atam Valves Q2 Results FY27: Date and Expectations - Univest</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Kopran Ltd. Share Price News With Healthcare Sector View - Univest</t>
+          <t>Atam Valves (NSE: ATAM): Catalysts and Risks - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IOLCP.NS</t>
+          <t>NPST.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals and Pharmaceuticals Limited</t>
+          <t>Network People Services Technologies Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>182</v>
+        <v>1730</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>194.5</v>
+        <v>1934</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>173.5500030517578</v>
+        <v>1673.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>192.9799957275391</v>
+        <v>1834.599975585938</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>179.5200042724609</v>
+        <v>1639.5</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>192.9799957275391</v>
+        <v>1834.599975585938</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>6267284</v>
+        <v>3027973</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7.5</v>
+        <v>11.9</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals and Pharmaceuticals Share Price - Live NSE: IOLCP Stock Price &amp; Chart - upstox.com</t>
+          <t>NPST Share Price rises 10.36%: price action and analysis - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals and Pharmaceuticals Share Price - Live NSE: IOLCP Stock Price &amp; Chart - upstox.com</t>
+          <t>Multibagger small cap stock Network People Services share price surges 18% today: Here's what is driving the rally - TradingView</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals Share Price Today after fresh 52-week high - Univest</t>
+          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals (IOLCP.NS) Holds Steady Near ₹194 as Pharma-Chemical Play Consolidates - MFI Overbought - siam.in</t>
+          <t>NPST wins Best Digital Banking Platform at Global Fintech Awards 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>IOLCP Share Price today near 52-week high, price action - Univest</t>
+          <t>Multibagger small cap stock Network People Services share price surges 18% today: Here's what is driving the rally - TradingView</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,64 +829,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MOREPENLAB.NS</t>
+          <t>CSBBANK.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Morepen Laboratories Limited</t>
+          <t>CSB Bank Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>106.4499969482422</v>
+        <v>297.8999938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>114.5</v>
+        <v>337</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>97.04000091552734</v>
+        <v>297.7999877929688</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>113.0400009155273</v>
+        <v>328.75</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>106.2200012207031</v>
+        <v>296.3500061035156</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>113.0400009155273</v>
+        <v>328.75</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>30425551</v>
+        <v>8547664</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6.42</v>
+        <v>10.93</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And Morepen Laboratories (NSE:MOREPENLAB) Passed With Ease - simplywall.st</t>
+          <t>CSB Bank Falls 2.58% to ₹312.85: Support at ₹297.21 Holds the Key for CSBBANK.NS - Channel Projection - siam.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And Morepen Laboratories (NSE:MOREPENLAB) Passed With Ease - simplywall.st</t>
+          <t>RBI gives ICICI Bank (NYSE: IBN) unit one year to acquire stakes in four lenders - Stock Titan</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Morepen Laboratories (MOREPENLAB) Share Price Falls 6.25% Today; Valuation and Sector Context in Focus - Univest</t>
+          <t>CSB Bank Ltd. Share Price: 52-Week Low and Valuation View - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Morepen Laboratories Share Price today after yearly high - Univest</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>CSB (CSBBANK.NS) Financial Update: The Latest Report Adds New Financial Reference Points in the Current Update; Post-Report: The Share Price Moves Only Slightly in Latest Trading - Earnings Growth Analysis - siam.in</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-09-08 — cnbctv:53b6c3a40094b:0 - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -894,68 +898,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK.NS</t>
+          <t>ANTELOPUS.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>CSB Bank Limited</t>
+          <t>Antelopus Selan Energy Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>297.8999938964844</v>
+        <v>1071.050048828125</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>324</v>
+        <v>1214.449951171875</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>297.7999877929688</v>
+        <v>996.0999755859375</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>314.2999877929688</v>
+        <v>1170.949951171875</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>296.3500061035156</v>
+        <v>1057.800048828125</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>314.2999877929688</v>
+        <v>1170.949951171875</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4793309</v>
+        <v>4318807</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6.06</v>
+        <v>10.7</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CSB Bank Falls 2.58% to ₹312.85: Support at ₹297.21 Holds the Key for CSBBANK.NS - Channel Projection - siam.in</t>
+          <t>Antelopus Selan Energy ESOP Allotment 22,138 Shares September 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>RBI gives ICICI Bank (NYSE: IBN) unit one year to acquire stakes in four lenders - Stock Titan</t>
+          <t>Antelopus Selan Energy ESOP Allotment 22,138 Shares September 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>CSB Bank Ltd. Share Price: 52-Week Low and Valuation View - Univest</t>
+          <t>Antelopus Selan Energy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>CSB (CSBBANK.NS) Financial Update: The Latest Report Adds New Financial Reference Points in the Current Update; Post-Report: The Share Price Moves Only Slightly in Latest Trading - Earnings Growth Analysis - siam.in</t>
+          <t>176% return in 2026 so far! Antelopus Selan Energy falls 3% after massive rally | What’s spooking investors? - Livemint</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-09-08 — cnbctv:53b6c3a40094b:0 - tradingview.com</t>
+          <t>Antelopus Selan Energy shares rally 20% to 52-week high; what investors need to know - Upstox</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -963,56 +967,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ZEELEARN.NS</t>
+          <t>KMCSHIL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Zee Learn Limited</t>
+          <t>K M C Speciality Hospitals (India) Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.739999771118164</v>
+        <v>133.4600067138672</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>7.239999771118164</v>
+        <v>154</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6.559999942779541</v>
+        <v>128.4799957275391</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>7.03000020980835</v>
+        <v>146.9299926757812</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6.630000114440918</v>
+        <v>132.8000030517578</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.03000020980835</v>
+        <v>146.9299926757812</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>196334</v>
+        <v>9088405</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.03</v>
+        <v>10.64</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5 Education Stocks India 2026: Strong Future Roadmaps - Univest</t>
+          <t>KMCSHIL Stock Price and Chart — NSE:KMCSHIL - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5 Education Stocks India 2026: Strong Future Roadmaps - Univest</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>KMC Speciality Hospitals Share Price: Price Action and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>KMC Speciality Hospitals (India) Limited Trade Ideas — NSE:KMCSHIL - TradingView</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>KMC Speciality Hospitals Share Price: price rise, valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>KMC Speciality Hospitals (India) Ltd (KMCSHIL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1020,68 +1036,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MVGJL.NS</t>
+          <t>FOSECOIND.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
+          <t>Foseco India Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>196.0399932861328</v>
+        <v>6224.5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>209.8999938964844</v>
+        <v>7040</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>185.1499938964844</v>
+        <v>6141</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>207.3999938964844</v>
+        <v>6846.5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>196.0500030517578</v>
+        <v>6223.5</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>207.3999938964844</v>
+        <v>6846.5</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>554417</v>
+        <v>178656</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5.79</v>
+        <v>10.01</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Manoj Vaibhav Gems (MVGJL.NS) Gains 4.6% to ₹179.9: Jewelry Stock Rebounds Toward Key Resistance - Bollinger Squeeze - siam.in</t>
+          <t>Foseco India Share Price Hits 52-Week High on Market Update - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - tradingview.com</t>
+          <t>Foseco India Share Price Hits 52-Week High on Market Update - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Manoj Vaibhav Gems 'N' Jewellers (NSE:MVGJL) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>Morganite Crucible sells entire 7.84% stake in Foseco India - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Manoj (MVGJL.NS) Financial Update: The Company Lists Its Latest Available Figures in the Current Update; Shares Move 1.33% Up in the Latest Reading - Surprise Factor Analysis - siam.in</t>
+          <t>Foseco India provides web-link for FY25 annual report - scanx.trade</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Manoj Vaibhav Gems (MVGJL) Surges 7.5% to ₹162.37: Bulls Test Key Resistance Zone - Strangle Setup - siam.in</t>
+          <t>Foseco India schedules physical analyst meet with SBI Mutual Fund - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1089,68 +1105,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>MONEYBOXX.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>Moneyboxx Finance Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>525.9500122070312</v>
+        <v>49.43000030517578</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>550.6500244140625</v>
+        <v>49.43000030517578</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>505.1000061035156</v>
+        <v>49.43000030517578</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>550.6500244140625</v>
+        <v>49.43000030517578</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>524.4500122070312</v>
+        <v>44.93999862670898</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>550.6500244140625</v>
+        <v>49.43000030517578</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1078848</v>
+        <v>16118</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5</v>
+        <v>9.99</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>GRT Jewellers files TBZ open offer at ₹249.61; tendering opens Oct 26 - scanx.trade</t>
+          <t>Moneyboxx Finance Share Price Rises 9.99% on Valuation View - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>GRT Jewellers files TBZ open offer at ₹249.61; tendering opens Oct 26 - scanx.trade</t>
+          <t>Moneyboxx Finance Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
+          <t>Moneyboxx Finance Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>TBZ shares extend rally as GRT Jewellers deal sparks growth optimism - BusinessLine</t>
+          <t>Moneyboxx Finance Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri share price today: TBZ stock on fire again - What's driving the bull run? - Livemint</t>
+          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1158,68 +1174,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>AARNAV.NS</t>
+          <t>RRECL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Limited</t>
+          <t>RDB Real Estate Constructions Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>29.79999923706055</v>
+        <v>124</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>136</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>28.31999969482422</v>
+        <v>124</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>135.5700073242188</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>29.79000091552734</v>
+        <v>123.6999969482422</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31.27000045776367</v>
+        <v>135.5700073242188</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>14023</v>
+        <v>707</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4.97</v>
+        <v>9.6</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>RRECL Stock Price and Chart — NSE:RRECL - TradingView</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions AGM on Sep 30 to adopt FY26 accounts - scanx.trade</t>
+          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Share Price: Buy or Sell - Univest</t>
+          <t>RDB Real Estate Constructions Share Price Today Down 9.14% - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>AARNAV Jun 2026 Earnings: Steady Profitability with ₹0.4 EPS on ₹86.53 Crore Revenue; Stock Gains 0.9% - siam.in</t>
+          <t>RDB Real Estate Constructions Ltd. (RRECL) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions AGM on Sep 30 to adopt FY26 accounts - scanx.trade</t>
+          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1227,68 +1243,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>QPOWER.NS</t>
+          <t>SUNSHINE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Quality Power Electrical Equipments Limited</t>
+          <t>Sunshine Pictures Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1344</v>
+        <v>350.1499938964844</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1422.900024414062</v>
+        <v>367.2999877929688</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1291.699951171875</v>
+        <v>332.3500061035156</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1418</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1355.199951171875</v>
+        <v>333.9500122070312</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1418</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>436126</v>
+        <v>3703580</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4.63</v>
+        <v>8.91</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>QPOWER Share Price Today: price rise, PE and peer check - Univest</t>
+          <t>SUNSHINE Share Price Rises 9.05%: Price Action, Valuation - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>QPOWER Q2 2026 Earnings: Revenue Surges 183% YoY to ₹935.98 Crore Even as Stock Slips - Cash Flow Report - siam.in</t>
+          <t>An oral drug candidate suppressed lung virus in infected mice - Stock Titan</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>QPOWER Share Price rise with Rs 10,145.95 Cr market cap - Univest</t>
+          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>QPOWER Q2 2026 Earnings: Revenue Surges 183% YoY to ₹935.98 Crore Even as Stock Slips - Cash Flow Report - siam.in</t>
+          <t>An oral drug candidate suppressed lung virus in infected mice - Stock Titan</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>QUALITY POWER ELEC EQUP L (QPOWER) Share Price hits fresh 52-week high on 4.41% rise - Univest</t>
+          <t>Average basic shares outstanding of CHERISH SUNSHINE INTL LTD. – OTC:CHSIF - TradingView</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1296,68 +1312,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>TATVA.NS</t>
+          <t>MEDICAMEQ.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tatva Chintan Pharma Chem Limited</t>
+          <t>Medicamen Biotech Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1560</v>
+        <v>315.3500061035156</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1637.800048828125</v>
+        <v>354.3999938964844</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1520</v>
+        <v>290.5499877929688</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1618.5</v>
+        <v>345.5</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1547.300048828125</v>
+        <v>318.2000122070312</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1618.5</v>
+        <v>345.5</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>75667</v>
+        <v>248990</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>4.6</v>
+        <v>8.58</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Tatva Chintan Promoters Declare No Share Encumbrance for FY26 - scanx.trade</t>
+          <t>Medicamen Biotech Gains 5%: Stock Approaches Key Resistance at ₹274.54 - Keltner Channel - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Tatva Chintan Pharma Chem Ltd Downgraded to Hold Amid Mixed Technical and Valuation Signals - MarketsMojo</t>
+          <t>Shivalik Rasayan holds 40.46% stake in Medicamen Biotech - scanx.trade</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Tatva Chintan Pharma Chem Ltd. Stock News - Value Research</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Tatva Chintan Pharma Chem Ltd Downgraded to Hold Amid Mixed Technical and Valuation Signals - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Tatva Chintan FY26 Net Profit Surges to ₹420.54 Mn - scanx.trade</t>
-        </is>
-      </c>
+          <t>Shivalik Rasayan holds 40.46% stake in Medicamen Biotech - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1365,64 +1373,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO.NS</t>
+          <t>IOLCP.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CMS Info Systems Limited</t>
+          <t>IOL Chemicals and Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>235.0800018310547</v>
+        <v>182</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>239</v>
+        <v>197.8999938964844</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>227.8000030517578</v>
+        <v>173.5500030517578</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>232.8099975585938</v>
+        <v>194.5700073242188</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>222.9100036621094</v>
+        <v>179.5200042724609</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>232.8099975585938</v>
+        <v>194.5700073242188</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4620116</v>
+        <v>8623017</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4.44</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>CMS Info Systems Ltd. Share Price Today Hits One-Year Low - Univest</t>
+          <t>IOL Chemicals Share Price Today after fresh 52-week high - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>CMS Info Systems Ltd. Share Price Today at New One-Year Low - Univest</t>
+          <t>IOL Chemicals Stock Falls After Recent Rise - Kalkine India</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>CMS Info Systems Share Price: fresh 52-week low explained - Univest</t>
+          <t>IOL Chemicals (IOLCP.NS) Holds Steady Near ₹194 as Pharma-Chemical Play Consolidates - MFI Overbought - siam.in</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>CMS Info Systems Ltd. Share Price Today at New One-Year Low - Univest</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>IOLCP Share Price today near 52-week high, price action - Univest</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>IOLCP Share Price today at 52-week high; sector context - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1430,68 +1442,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>FILATEX.NS</t>
+          <t>EMUDHRA.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Limited</t>
+          <t>eMudhra Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>81</v>
+        <v>625</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>86.75</v>
+        <v>677</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>80.30000305175781</v>
+        <v>600.3499755859375</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>85.87000274658203</v>
+        <v>642.2999877929688</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>82.41000366210938</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>85.87000274658203</v>
+        <v>642.2999877929688</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3309321</v>
+        <v>30254742</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4.2</v>
+        <v>8.34</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>BSE Filatex India Stock: Elliott Wave Points TP 134 - Moneymunch</t>
+          <t>eMudhra share price jumps 12% today, extends gains for second session | What's behind the rally? - Livemint</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+          <t>eMudhra says LEI deal could lift Trust Services growth; 25% margins sustainable - cnbctv18.com</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Stock Near Recent High Zone - Kalkine India</t>
+          <t>eMudhra shares zoom nearly 37% in two days; here's the trigger - BusinessToday - IndiaIPO</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions Ltd Locks at Upper Circuit With 5.56% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+          <t>eMudhra says LEI deal could lift Trust Services growth; 25% margins sustainable - cnbctv18.com</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Share Price: price action and fundamentals - Univest</t>
+          <t>eMudhra Shares Surge as Momentum Strengthens - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1499,68 +1511,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER.NS</t>
+          <t>INDTERRAIN.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Empower India Limited</t>
+          <t>Indian Terrain Fashions Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.430000066757202</v>
+        <v>28.89999961853027</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.490000009536743</v>
+        <v>33.61000061035156</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2.430000066757202</v>
+        <v>28.36000061035156</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2.480000019073486</v>
+        <v>30.29000091552734</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2.380000114440918</v>
+        <v>28.01000022888184</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.480000019073486</v>
+        <v>30.29000091552734</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>26139606</v>
+        <v>251131</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.2</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Penny stock under ₹10: Up 100% in six months | IT stock hits 5% upper circuit in five straight sessions - Livemint</t>
+          <t>Indian Terrain Fashions Share Price today after 19.47% rise - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Penny stock under ₹10: Up 100% in six months | IT stock hits 5% upper circuit in five straight sessions - Livemint</t>
+          <t>Indian Terrain Fashions Share Price today after 19.47% rise - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>NET Power Closes Acquisition of 123 MW Power Generation Rights From EMPower; Shares Rise - marketscreener.com</t>
+          <t>Indian (INDTERRAIN.NS) Market: Declines 0.79% to ₹30.05 at the Close; Market Levels: ₹28.55 and ₹31.55 Define the Nearby Reference Levels under the Current Snapshot - Covered Call ETF - siam.in</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>A West Texas project plans 10 gas engines totaling 123 megawatts - Stock Titan</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>AI penny stock under ₹10 hits 5% upper circuit as IndiaAI Mission boosts infrastructure demand - Livemint</t>
-        </is>
-      </c>
+          <t>Indian (INDTERRAIN.NS) Update: Ends Lower by 0.92% at ₹30.27 at the Close; Range View: Traders Can Monitor the ₹28.76-₹31.78 Range on the Day - Sell Signal Alerts - siam.in</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1568,68 +1576,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>INDOCO.NS</t>
+          <t>KANPRPLA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Indoco Remedies Limited</t>
+          <t>Kanpur Plastipack Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>241.3899993896484</v>
+        <v>247.5</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>255.3000030517578</v>
+        <v>270</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>235</v>
+        <v>243.1499938964844</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>251.5</v>
+        <v>265.8500061035156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>241.3899993896484</v>
+        <v>246</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>251.5</v>
+        <v>265.8500061035156</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>465021</v>
+        <v>27577</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.19</v>
+        <v>8.07</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Indoco Remedies Share Price Drops; Technicals in Focus - Univest</t>
+          <t>Kanpur Plastipack Files Minutes of 55th AGM with Stock Exchanges - The Globe and Mail</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Indoco Remedies Share Price Drops; Technicals in Focus - Univest</t>
+          <t>Kanpur Plastipack Files Minutes of 55th AGM with Stock Exchanges - The Globe and Mail</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Indoco Remedies shares jump 18% as UK medicines regulator clears Goa plant - CNBC TV18 - LinkedIn</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Indoco Remedies Shares Surge After UK Regulator Clears Goa Plant - Equitypandit</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>News by CNBC TV18 on TradingView, 2026-09-10 — cnbctv:f7742802d094b:0 - tradingview.com</t>
-        </is>
-      </c>
+          <t>Kanpur (KANPRPLA.NS) Financial Update: Available Data Shows the Latest Reported Performance under the Current Snapshot; Closing Reaction: The Share Price Sheds 4.13% in the Latest Reading - Earnings Trend Analysis - siam.in</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1637,64 +1637,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SBCL.NS</t>
+          <t>MOREPENLAB.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Bimetal Controls Limited</t>
+          <t>Morepen Laboratories Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1020</v>
+        <v>106.4499969482422</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1070.900024414062</v>
+        <v>116</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>957.0999755859375</v>
+        <v>97.04000091552734</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1062.199951171875</v>
+        <v>114.7300033569336</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1020.200012207031</v>
+        <v>106.2200012207031</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1062.199951171875</v>
+        <v>114.7300033569336</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>472078</v>
+        <v>39395018</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.12</v>
+        <v>8.01</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Sirmaur Hospitality Acquires 67,500 Shares in Shivalik Bimetal Controls Through Open Market - scanx.trade</t>
+          <t>We Ran A Stock Scan For Earnings Growth And Morepen Laboratories (NSE:MOREPENLAB) Passed With Ease - simplywall.st</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sirmaur Hospitality Acquires 67,500 Shares in Shivalik Bimetal Controls Through Open Market - scanx.trade</t>
+          <t>Morepen Laboratories Share Price rises 5.65%; valuation view - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Read This Before Considering Shivalik Bimetal Controls Limited (NSE:SBCL) For Its Upcoming ₹2.00 Dividend - simplywall.st</t>
+          <t>Morepen Laboratories (MOREPENLAB) Share Price Falls 6.25% Today; Valuation and Sector Context in Focus - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Bimetal Controls Share Price Hits 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Morepen Laboratories Share Price rises 5.65%; valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Morepen Laboratories Share Price today after yearly high - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1702,68 +1706,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SAMHI.NS</t>
+          <t>KRYSTAL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Samhi Hotels Limited</t>
+          <t>Krystal Integrated Services Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>152.0500030517578</v>
+        <v>611.9500122070312</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>164</v>
+        <v>668.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>149</v>
+        <v>600.25</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>158.9700012207031</v>
+        <v>655.5999755859375</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>152.7299957275391</v>
+        <v>607.7999877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>158.9700012207031</v>
+        <v>655.5999755859375</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3929028</v>
+        <v>174509</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.09</v>
+        <v>7.86</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Samhi Hotels shareholders approve ₹750 crore raise despite institutional dissent - scanx.trade</t>
+          <t>Krystal Q4 FY26 Earnings: 20%+ Growth Guided, Citelum Acquisition Completed - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Samhi Hotels shareholders approve ₹750 crore raise despite institutional dissent - scanx.trade</t>
+          <t>Krystal Q4 FY26 Earnings: 20%+ Growth Guided, Citelum Acquisition Completed - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Samhi Hotels (SAMHI.NS) Edges Lower by 1.05% to ₹151.45; Key Support at ₹143.88 Holds Focus - Defined Outcome ETF - siam.in</t>
+          <t>Krystal Integrated Services Limited (NSE:KRYSTAL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Samhi Hotels Ltd Downgraded to Strong Sell Amid Technical and Fundamental Concerns - MarketsMojo</t>
+          <t>Krystal Integrated Services Gains 3.29%: Stock Approaches Key Resistance at ₹679.72 - Ichimoku Kumo Twist - siam.in</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>FMR LLC raises stake in Samhi Hotels to 5.06% via open market buys - scanx.trade</t>
+          <t>Krystal Stock Gains 13.4% in a Month: What Is Driving the Rally? - TradingView</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1771,68 +1775,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE.NS</t>
+          <t>PATANJALI.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
+          <t>Patanjali Foods Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>74.72000122070312</v>
+        <v>339.0499877929688</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>79.90000152587891</v>
+        <v>367.3999938964844</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>70.11000061035156</v>
+        <v>337.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>75.16999816894531</v>
+        <v>338.5499877929688</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>989678</v>
+        <v>27861262</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3.76</v>
+        <v>7.81</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence Slides 1.4% to ₹57.02: Stock Holds Key Support Amid Defence Sector Retracement - AAII Bullish - siam.in</t>
+          <t>Patanjali Foods: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence Share Price Today: Sector and Peer View - Univest</t>
+          <t>Patanjali Foods: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence Share Price Today: Sector and Peer View - Univest</t>
+          <t>Tata Chemicals, 3M India, Patanjali Foods shares spurt amid spike in volumes; check full list - Upstox</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Where Does Kavveri Defence &amp; Wireless Technologies Limited (NSE: KAVDEFENCE) Stand After Its 17.33% Advance? - Kalkine India</t>
+          <t>Patanjali Foods share price rises 5% today. What is driving the rally in the FMCG stock? - Livemint</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
+          <t>FMCG Stocks Surge: Nestle India, ITC, HUL, Patanjali Foods Shares Jump Over 3% - NDTV Profit</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1840,58 +1844,54 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PARAGMILK.NS</t>
+          <t>ISHANCH.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Parag Milk Foods Limited</t>
+          <t>Ishan Dyes and Chemicals Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>252</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>261.6499938964844</v>
+        <v>48.90000152587891</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>246.3000030517578</v>
+        <v>43.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>261.3500061035156</v>
+        <v>47.11999893188477</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>252.1499938964844</v>
+        <v>43.72999954223633</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>261.3500061035156</v>
+        <v>47.11999893188477</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1128190</v>
+        <v>32446</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>3.65</v>
+        <v>7.75</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Parag Milk Foods Ltd. (PARAGMILK) Share Price Rises 8.79% Today - Univest</t>
+          <t>Ishan Dyes and Chemicals Share Price Today After 11.7% Rise - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Parag Milk Foods Publishes AGM, E-Voting Notice Ahead of September Meeting - TipRanks</t>
+          <t>Ishan Dyes and Chemicals Share Price Today: key metrics - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Parag Milk Foods Share Price Today: Rs 256.5 after rise - Univest</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Parag Milk Foods Publishes AGM, E-Voting Notice Ahead of September Meeting - TipRanks</t>
-        </is>
-      </c>
+          <t>Ishan Dyes and Chemicals Share Price Today: key metrics - Univest</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1911,14 +1911,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2017,7 +2017,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2025,68 +2025,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA.NS</t>
+          <t>SRGHFL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PNC Infratech Limited</t>
+          <t>SRG Housing Finance Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>132</v>
+        <v>126.4000015258789</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>133.2899932861328</v>
+        <v>138.1999969482422</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>116.4000015258789</v>
+        <v>126.4000015258789</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>128.3999938964844</v>
+        <v>126.4000015258789</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>140.3200073242188</v>
+        <v>140.3999938964844</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>128.3999938964844</v>
+        <v>126.4000015258789</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>14556667</v>
+        <v>350176</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-8.49</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>PNC Infratech shares tumble 20% to hit 52-week low; here's why - Business Today</t>
+          <t>SRG Housing Finance (SRGHFL) Share Price Falls 9.95% Today - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>NHAI extends debarment to PNC Infratech; stock hits 52-week low - tradingview.com</t>
+          <t>SRG Housing Finance (SRGHFL) Share Price Falls 9.95% Today - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>PNC Infratech (NSE: PNCINFRA) Faces NHAI Debarment Extension - Kalkine India</t>
+          <t>SRG Housing Finance Daily Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>NHAI extends debarment to PNC Infratech; stock hits 52-week low - tradingview.com</t>
+          <t>SRG Housing Finance Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>PNC Infratech shares hit 20% lower circuit as NHAI extends Awadh Expressway debarment to company; all you need to know - upstox.com</t>
+          <t>SRG Housing Finance Faces Sharp Breakdown - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2094,68 +2094,60 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HTEL.NS</t>
+          <t>UMESLTD.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Usha Martin Education &amp; Solutions Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>78.40000152587891</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>78.40000152587891</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>71.79000091552734</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>74.62000274658203</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>81.31999969482422</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>74.62000274658203</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3054221</v>
+        <v>363161</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.24</v>
+        <v>-9.93</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Usha (UMESLTD.NS) Quarterly Update: Available Data Shows the Latest Reported Performance in Latest Trading; Market Follow-Through: The Stock Loses 2.33% on the Day - Profit Cycle Analysis - siam.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Usha Martin Education &amp; Solutions Sets Date for 29th AGM and Closes Share Transfer Books - TipRanks</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Free float of Hy-Tech Engineers Limited – NSE:HTEL - tradingview.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Hy-Tech Engineers Ltd. (HTEL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
+          <t>Usha Martin Education &amp; Solutions Sets Date for 29th AGM and Closes Share Transfer Books - TipRanks</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2163,68 +2155,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>YATRA.NS</t>
+          <t>GRAVISSHO.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Yatra Online Limited</t>
+          <t>Graviss Hospitality Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>107.4899978637695</v>
+        <v>49</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>108.9800033569336</v>
+        <v>49.90000152587891</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>102.2200012207031</v>
+        <v>42.27999877929688</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>102.3000030517578</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>107.9599990844727</v>
+        <v>46.97000122070312</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>102.3000030517578</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>867226</v>
+        <v>94415</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-5.24</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Yatra Online schedules 20th AGM for September 15 via video conference - scanx.trade</t>
+          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>New bidder for Yatra Online (YTRA) makes cash offer with broad conditions attached - Stock Titan</t>
+          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>New bidder for Yatra Online (YTRA) makes cash offer with broad conditions attached - Stock Titan</t>
+          <t>Graviss Hospitality Share Price: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Kailash Mansarovar Yatra Experience: Mumbai-Based Senior Journalist Preeti Sompura Shares Her Divine and Life-Changing Spiritual Journey - Hello Mumbai News</t>
+          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Yatra Online submits revised annual report for FY26 - scanx.trade</t>
+          <t>Graviss Hospitality Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2232,64 +2224,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM.NS</t>
+          <t>LAMBODHARA.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Limited</t>
+          <t>Lambodhara Textiles Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>882.4000244140625</v>
+        <v>128.6499938964844</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>884.6500244140625</v>
+        <v>130.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>811.9500122070312</v>
+        <v>116.5999984741211</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>837.2000122070312</v>
+        <v>117.7600021362305</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>882.7000122070312</v>
+        <v>130.3300018310547</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>837.2000122070312</v>
+        <v>117.7600021362305</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>593406</v>
+        <v>98400</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-5.15</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Share Price: fresh 52-week high, fundamentals - Univest</t>
+          <t>Lambodhara Textiles Share Price Fall: Price Analysis - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Share Price: fresh 52-week high and valuation - Univest</t>
+          <t>Lambodhara Textiles Share Price Today: Price Fall Analysis - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Share Price: fresh 52-week high and valuation - Univest</t>
+          <t>Lambodhara (LAMBODHARA.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points for the Current Session; Investor Response: The Stock Gains 0.68% in Latest Trading - Earnings Surprise Stocks - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM to host analyst meet with Kotak MF on August 21 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Lambodhara Textiles Share Price Today: 8.85% Price Rise - Univest</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Lambodhara (LAMBODHARA.NS) Earnings Reading: The Company Releases Its Current Earnings Data on the Day; Trading Move: Shares Finish 19.99% Up for the Current Session - Earnings Outlook Update - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2297,68 +2293,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>STLTECH.NS</t>
+          <t>LADDERUP.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sterlite Technologies Limited</t>
+          <t>Ladderup Finance Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>809.9500122070312</v>
+        <v>66.80000305175781</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>839</v>
+        <v>66.80000305175781</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>809.9500122070312</v>
+        <v>60.20000076293945</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>809.9500122070312</v>
+        <v>60.93999862670898</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>852.5499877929688</v>
+        <v>66.87999725341797</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>809.9500122070312</v>
+        <v>60.93999862670898</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1793505</v>
+        <v>9998</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-5</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Ankit Agarwal confirms no encumbrance on Sterlite Technologies shares in FY26 - scanx.trade</t>
+          <t>Pranav Constructions Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Ankit Agarwal confirms no encumbrance on Sterlite Technologies shares in FY26 - scanx.trade</t>
+          <t>Pranav Constructions Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>STLTECH Q2 2026 Earnings: Revenue Surges 19.3% YoY to ₹4,663 Crore; Stock Gains 4% - Energy Earnings Report - siam.in</t>
+          <t>Ladderup Finance Ltd. Upper Circuit Streak: Day 2 Price and Data - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Sterlite (STLTECH.NS) Move: Adds 1.75% to Close at ₹662.75 in the Latest Session; Range View: Price Remains Between ₹629.61 Support and ₹695.89 Resistance for the Current Session - Impulse Wave - siam.in</t>
+          <t>Ladderup Finance releases FY26 annual report, sets Sep 24 AGM date - scanx.trade</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Sterlite Technologies shares: Over 740% returns in 2026 so far; stock hits 52-week high | What's next for investors? - tradingview.com</t>
+          <t>Ladderup Finance Ltd Upgraded to Hold on Improved Technicals and Valuation - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2366,68 +2362,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>RADHIKAJWE.NS</t>
+          <t>NOVARTIND.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Radhika Jeweltech Limited</t>
+          <t>Novartis India Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>72</v>
+        <v>2164</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>74.69999694824219</v>
+        <v>2178.10009765625</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>71.69999694824219</v>
+        <v>1980</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>71.69999694824219</v>
+        <v>1995.5</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>75.47000122070312</v>
+        <v>2188</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>71.69999694824219</v>
+        <v>1995.5</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>76996</v>
+        <v>122475</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Radhika Jeweltech Dips 2.6% to ₹68.5: Support and Resistance Levels in Spotlight - Wave Equality - siam.in</t>
+          <t>Novartis India Share Price Today: 6.19% Fall, Key Metrics - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Does Radhika Jeweltech (NSE:RADHIKAJWE) Deserve A Spot On Your Watchlist? - webull.com</t>
+          <t>Novartis India Share Price Today: 6.19% Fall, Key Metrics - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Does Radhika Jeweltech (NSE:RADHIKAJWE) Deserve A Spot On Your Watchlist? - webull.com</t>
+          <t>Novartis India Receives Detailed Public Statement for ₹552.49 Crore Open Offer - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Does Radhika Jeweltech (NSE:RADHIKAJWE) Deserve A Spot On Your Watchlist? - simplywall.st</t>
+          <t>Novartis (NOVARTIND.NS) Financial Update: The Company Lists Its Latest Available Figures; Stock Move: Shares Close 1.06% Lower - Earnings Whisper Number - siam.in</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Radhika Jeweltech Files Tenth Annual Report for FY 2025-26 With Stock Exchanges - TipRanks</t>
+          <t>Novartis India Share Price: fresh 52-week high, valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2435,64 +2431,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KESORAMIND.NS</t>
+          <t>HTEL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kesoram Industries Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12.10000038146973</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>12.34000015258789</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>11.97000026702881</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>11.97000026702881</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>12.60000038146973</v>
+        <v>81.31999969482422</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.97000026702881</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>502687</v>
+        <v>3850262</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5</v>
+        <v>-8.74</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Kesoram Industries: Frontier Warehousing Acquires 42.8% Stake via Off-Market Transfer - Whalesbook</t>
+          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Kesoram Industries: Frontier Warehousing Acquires 42.8% Stake via Off-Market Transfer - Whalesbook</t>
+          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Kesoram Industries: Frontier Warehousing का बड़ा दांव, खरीदी **42.8%** हिस्सेदारी - Whalesbook</t>
+          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Kesoram Industries માં મોટા ફેરફાર: Frontier Warehousing એ **42.8%** હિસ્સો ખરીદ્યો - Whalesbook</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Free float of Hy-Tech Engineers Limited – NSE:HTEL - TradingView</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Hy-Tech Engineers IPO subscribed 131.68 times so far on Day 4: Check allotment date and steps - Upstox</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2500,68 +2500,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>UEL.NS</t>
+          <t>AMDIND.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Limited</t>
+          <t>AMD Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>214</v>
+        <v>68.5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>214</v>
+        <v>72.37000274658203</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>204.7700042724609</v>
+        <v>62.20000076293945</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>204.7700042724609</v>
+        <v>63.65999984741211</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>215.5399932861328</v>
+        <v>69.63999938964844</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>204.7700042724609</v>
+        <v>63.65999984741211</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>16253</v>
+        <v>423728</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5</v>
+        <v>-8.59</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy NSE:UEL Price Movement Clarification Sep 2026 - Kalkine India</t>
+          <t>AMD Industries Stock: Momentum Above 50-Day SMA - Kalkine India</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Ltd. Lower Circuit Streak: Day 2 Price and Data - Univest</t>
+          <t>AMD Industries Stock: Momentum Above 50-Day SMA - Kalkine India</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ujaas (UEL.NS) Earnings Update: The Company Publishes Its Latest Results in Latest Trading; The Market Price Declines 5.00% for the Current Session - Earnings Revision Report - siam.in</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Ujaas Energy Ltd. Lower Circuit Streak: Day 2 Price and Data - Univest</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Luxembourg's Social Partners Strike Wage Deal — Pay Indexation Pushed to Spring 2027 - ad-hoc-news.de</t>
-        </is>
-      </c>
+          <t>AMD Industries Share Price rises 12.01%: valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2569,64 +2561,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD.NS</t>
+          <t>PKTEA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Digjam Limited</t>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>62.04000091552734</v>
+        <v>1020</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>62.04999923706055</v>
+        <v>1020</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>61.75</v>
+        <v>922.2000122070312</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.75</v>
+        <v>936.9500122070312</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>65</v>
+        <v>1024.599975585938</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>61.75</v>
+        <v>936.9500122070312</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>4206</v>
+        <v>5051</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Digjam Share Price rises 14.59%: price action - Univest</t>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Digjam Share Price rises 14.59%: price action - Univest</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Digjam Ltd Gains 2.11% to ₹51.73: Textile Stock Holds Above Key Support - Turnaround Stocks - siam.in</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Digjam Limited: స్కీమ్ ఆఫ్ అరేంజ్మెంట్‌పై NCLT కీలక ఆదేశాలు.. అక్టోబర్ 28న తదుపరి విచారణ - Whalesbook</t>
-        </is>
-      </c>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2634,68 +2618,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>FREDUN.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Limited</t>
+          <t>Fredun Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>60.20000076293945</v>
+        <v>1322.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>60.79000091552734</v>
+        <v>1345.800048828125</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>58.5099983215332</v>
+        <v>1195.199951171875</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.5099983215332</v>
+        <v>1221.599975585938</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>61.58000183105469</v>
+        <v>1327.900024414062</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>58.5099983215332</v>
+        <v>1221.599975585938</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>279339</v>
+        <v>306694</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.99</v>
+        <v>-8.01</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Fredun Pharmaceuticals allots 1.1 Cr bonus shares in 2:1 ratio - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Secures Shareholder Approval on All AGM Resolutions - TipRanks</t>
+          <t>Furlicks Goes from 6 to 22 SKUs: Fredun Pharmaceuticals Ltd. Accelerates Pet Wellness Expansion - NewsX</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>143% Return In One Month: Multibagger Smallcap Stock Hits 5% Upper Circuit In Trade. Here's Why - NDTV Profit</t>
+          <t>Fredun Pharmaceuticals expands Furlicks pet brand from 6 to 22 SKUs - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Share Price Today With Price and Valuation View - Univest</t>
+          <t>Fredun Pharma acquires Wellbeing Nutrition's pet wellness brand - VCCircle</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>PVP (PVP.NS) Results Versus Estimates: The Company Lists Its Latest Available Figures on the Day; Price Move: Shares Move 5.10% Higher at the Close - Next Quarter Guidance - siam.in</t>
+          <t>Fredun Pharma FY26 net profit rises 60%; announces 2:1 bonus - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2703,68 +2687,60 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO.NS</t>
+          <t>OSWALSEEDS.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Limited</t>
+          <t>ShreeOswal Seeds And Chemicals Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1385</v>
+        <v>16.47999954223633</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1437.599975585938</v>
+        <v>16.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1196.199951171875</v>
+        <v>14.51000022888184</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1289.599975585938</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1356.800048828125</v>
+        <v>15.82999992370605</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1289.599975585938</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>6666766</v>
+        <v>530991</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.95</v>
+        <v>-7.77</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Recently listed Molbio Diagnostics share price falls 9%: Healthcare stock loses 18.5% in 2 days after blockbuster rally - Livemint</t>
+          <t>Shree Oswal Seeds and Chemicals Share Price Analysis - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics drops 8.8% to ₹1,229.65 still 50%+ above IPO - NewsBytes</t>
+          <t>Shree Oswal Seeds and Chemicals Share Price Analysis - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Q1FY27 net profit up 523% to ₹52.7 crore on deferred exports - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Molbio Diagnostics shares surge over 50% in just 3 days! What is driving the rally? - tradingview.com</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Molbio Diagnostics shares surge 35% in two sessions; here’s why the healthcare stock hit record high on Sept 10 - upstox.com</t>
-        </is>
-      </c>
+          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2772,64 +2748,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ASHOKAMET.NS</t>
+          <t>GKB.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast Limited</t>
+          <t>GKB Ophthalmics Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>15.14999961853027</v>
+        <v>65.80000305175781</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>15.18000030517578</v>
+        <v>66.12000274658203</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>14.10999965667725</v>
+        <v>62.20000076293945</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>14.4399995803833</v>
+        <v>62.36999893188477</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.14000034332275</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14.4399995803833</v>
+        <v>62.36999893188477</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>110616</v>
+        <v>916</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.62</v>
+        <v>-7.49</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast Hits Fresh High: Chart Analysis - Kalkine India</t>
+          <t>GKB Stock Price and Chart — NSE:GKB - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast Hits Fresh High: Chart Analysis - Kalkine India</t>
+          <t>GKB Ophthalmics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast sells 2.48M Mena Mani Industries shares in open market - scanx.trade</t>
+          <t>GKB Ophthalmics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Ashoka Metcast Publishes FY26 Audited Financial Results Ad Under Regulation 47 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>GKB Ophthalmics shareholders unanimously approve all seven AGM resolutions - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>GKB Ophthalmics Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2837,68 +2817,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STEELCAS.NS</t>
+          <t>NAVKARCORP.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Steelcast Limited</t>
+          <t>Navkar Corporation Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>309</v>
+        <v>91.88999938964844</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>314.6499938964844</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>297.6000061035156</v>
+        <v>84.80000305175781</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>299</v>
+        <v>85.55999755859375</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>312.75</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>299</v>
+        <v>85.55999755859375</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>121415</v>
+        <v>1882658</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.4</v>
+        <v>-6.57</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Steelcast Limited (STEELCAS.NS) Edges Higher: Can It Sustain Momentum? - Put Flow Alert - siam.in</t>
+          <t>Navkar (NAVKARCORP.NS) Results Check: The Report Supplies Updated Headline Figures in the Reported Period; Market Move: Shares Finish 0.22% Up in the Current Update - Performance Review - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Steelcast Limited (STEELCAS.NS) Edges Higher: Can It Sustain Momentum? - Put Flow Alert - siam.in</t>
+          <t>Navkar Corporation to participate in investor meet on Sep 2 - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Steelcast Limited (STEELCAS.NS) Gains Momentum: Key Levels and Volume Insights - NAAIM Leverage - Vinanet</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>STEELCAS Stock Price and Chart — NSE:STEELCAS - tradingview.com</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Steelcast Share Price - upstox.com</t>
-        </is>
-      </c>
+          <t>Navkar Corporation to participate in investor meet on Sep 2 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2906,68 +2878,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV.NS</t>
+          <t>WSI.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sri Lotus Developers and Realty Limited</t>
+          <t>W S Industries (I) Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>209.5099945068359</v>
+        <v>60.59999847412109</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>211.9799957275391</v>
+        <v>61.45000076293945</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>202.8699951171875</v>
+        <v>54.0099983215332</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>204.2599945068359</v>
+        <v>56.04000091552734</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>213.5399932861328</v>
+        <v>59.91999816894531</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>204.2599945068359</v>
+        <v>56.04000091552734</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>665269</v>
+        <v>169308</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.35</v>
+        <v>-6.48</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV-BE 52 Week High Streak After Second Straight Peak - Univest</t>
+          <t>Industries (WSI.NS) Reported Quarter: The Report Provides a New Financial Snapshot for the Current Session; Reported Share Move: Shares Finish 0.91% Up at the Close - Operating Income Trends - siam.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Sri Lotus Developers Plans Investor Meetings at Mumbai Conference - TipRanks</t>
+          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Sri (LOTUSDEV.NS) Results Versus Estimates: Available Data Shows the Latest Reported Performance; Market Reaction: The Stock Records a 1.99% Increase in the Current Update - Profit Recovery Report - siam.in</t>
+          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>SRI LOTUS DEVLPRS N RTY L (LOTUSDEV-BE) Share Price hits fresh 52-week high on 10 September 2026 - Univest</t>
+          <t>WestStar Industrial (ASX: WSI) Surges 60.71%: What’s Driving the Small-Cap Stock Higher? - Kalkine</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Sri Lotus Developers receives GST DRC-07 order for FY20-21, 21-22, 23-24 - scanx.trade</t>
+          <t>Weststar Industrial Ltd (ASX: WSI) Share Price, WSI Stock News, WSI Share Price &amp; Updates - kalkine.ca</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2975,68 +2947,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>KNAGRI.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs Limited</t>
+          <t>KN Agri Resources Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>198</v>
+        <v>194.9499969482422</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>198</v>
+        <v>196.6000061035156</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>175.3000030517578</v>
+        <v>163.5500030517578</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>185.4900054931641</v>
+        <v>180.25</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>193.8000030517578</v>
+        <v>192.5200042724609</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>185.4900054931641</v>
+        <v>180.25</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>85272142</v>
+        <v>9108</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.29</v>
+        <v>-6.37</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs share price jumps 13%: Fintech stock rises sharply as trading volume explodes - Livemint</t>
+          <t>KN (KNAGRI.NS) Results Breakdown: The Latest Report Adds New Financial Reference Points at the Close; Price Move - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>PINE LABS (PINELABS) Share Price Falls 3.93% Today: What the Decline Shows - Univest</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Pine Labs Share Price Today Up 2.43%: Fundamental Check - Univest</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Pine (PINELABS.NS) Chart: Loses 1.77% to Close at ₹156.91 for the Current Session; Market Levels: ₹149.06 and ₹164.76 Define the Nearby Reference Levels in Latest Trading - Sign of Strength - siam.in</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Pine Labs sends FY26 annual report weblink to shareholders - scanx.trade</t>
-        </is>
-      </c>
+          <t>KN (KNAGRI.NS) Results Breakdown: The Latest Report Adds New Financial Reference Points at the Close; Price Move - siam.in</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3044,68 +3004,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AQYLON.NS</t>
+          <t>SIL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus Limited</t>
+          <t>Standard Industries Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>20.39999961853027</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>20.54999923706055</v>
+        <v>18</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>19.79000091552734</v>
+        <v>16.31999969482422</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>19.85000038146973</v>
+        <v>16.52000045776367</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.70999908447266</v>
+        <v>17.60000038146973</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>19.85000038146973</v>
+        <v>16.52000045776367</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>404599</v>
+        <v>80645</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.15</v>
+        <v>-6.14</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Leading Leasing sells 1.47 cr Aqylon Nexus shares - scanx.trade</t>
+          <t>How (SIL) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus Standalone June 2026 Net Sales at Rs 8.47 crore, up 24294.81% Y-o-Y - Moneycontrol.com</t>
+          <t>How (SIL) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>AQYLON Stock Price and Chart — NSE:AQYLON - tradingview.com</t>
+          <t>Aishwarya Rai Bachchan celebrates Rakhi with brother Aditya, Aaradhya and family, SIL shares rare pic - FM Bharat</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Why Is Aqylon Nexus Share Price Falling: Key Reasons and Investor Analysis 2026 - Univest</t>
+          <t>(SIL) Risk-Controlled Trading Report (SIL:CA) - Stock Traders Daily</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus Standalone June 2026 Net Sales at Rs 8.47 crore, up 24294.81% Y-o-Y - Moneycontrol.com</t>
+          <t>Aishwarya Rai Bachchan celebrates Rakhi with brother Aditya, Aaradhya and family, SIL shares rare pic - Social News XYZ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3113,56 +3073,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NECLIFE.NS</t>
+          <t>CEWATER.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences Limited</t>
+          <t>Concord Enviro Systems Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11.40999984741211</v>
+        <v>278</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>11.68000030517578</v>
+        <v>278</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>10.82999992370605</v>
+        <v>256.3999938964844</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>10.93000030517578</v>
+        <v>259.3500061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11.39999961853027</v>
+        <v>276.1499938964844</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10.93000030517578</v>
+        <v>259.3500061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>155205</v>
+        <v>95411</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.12</v>
+        <v>-6.08</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences Rises 2.09%: NECLIFE Stock Holds Near ₹11.23 on NSE - Dealer Positioning - siam.in</t>
+          <t>Investors Aren't Entirely Convinced By Concord Enviro Systems Limited's (NSE:CEWATER) Earnings - simplywall.st</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Nectar Lifesciences Rises 2.09%: NECLIFE Stock Holds Near ₹11.23 on NSE - Dealer Positioning - siam.in</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Concord Enviro Stock Rallies 9% After Subsidiary Bags ₹16 Cr Industrial ZLD Order - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>CONCORD ENVIRO SYSTEMS L Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Concord Enviro Systems Limited Announces Equity Shareholders Meeting for Scheme of Arrangement Approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Declining Stock and Decent Financials: Is The Market Wrong About Concord Enviro Systems Limited (NSE:CEWATER)? - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3170,68 +3142,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE.NS</t>
+          <t>KHAITANLTD.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Cartrade Tech Limited</t>
+          <t>Khaitan (India) Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3037</v>
+        <v>159</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>3064.89990234375</v>
+        <v>159</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2856.699951171875</v>
+        <v>145</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2896.10009765625</v>
+        <v>149.3699951171875</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3017.10009765625</v>
+        <v>158.9400024414062</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2896.10009765625</v>
+        <v>149.3699951171875</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>306503</v>
+        <v>3814</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.01</v>
+        <v>-6.02</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>CarTrade Tech Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Khaitan (India) Rises 1% to ₹162.41; Range Between ₹154.29 and ₹170.53 Defines Near-Term Path — KHAITANLTD.NS - Volume Breakout Ideas - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Cartrade Tech Ltd is Rated Hold - MarketsMojo</t>
+          <t>Khaitan India accepts resignation of company secretary Chandranath Banerjee - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>CarTrade Tech Share Price Today: 5.08% Fall, Valuation Check - Univest</t>
+          <t>Khaitan India schedules 89th AGM for September 25, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Do CarTrade Tech's (NSE:CARTRADE) Earnings Warrant Your Attention? - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>CarTrade Tech shares jump to the highest level of 2026 after gaining 14% in two sessions - CNBC TV18</t>
-        </is>
-      </c>
+          <t>Khaitan India accepts resignation of company secretary Chandranath Banerjee - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3239,64 +3207,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>MUKKA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries Limited</t>
+          <t>Mukka Proteins Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10.18000030517578</v>
+        <v>31.10000038146973</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>10.18000030517578</v>
+        <v>31.30999946594238</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>9.729999542236328</v>
+        <v>29.26000022888184</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.840000152587891</v>
+        <v>29.53000068664551</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10.23999977111816</v>
+        <v>31.38999938964844</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9.840000152587891</v>
+        <v>29.53000068664551</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1426378</v>
+        <v>1355101</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.91</v>
+        <v>-5.93</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries AGM Notice 2026: NSE:SUMEETINDS Filing - Kalkine India</t>
+          <t>Mukka Proteins Ltd Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries Addresses NSE Queries and Defers Rights Issue Decision - TipRanks</t>
+          <t>Mukka Proteins to host virtual investor meet with ADD Capital - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries submits Q1FY27 earnings call audio recording - scanx.trade</t>
+          <t>Mukka Proteins Completes 100% Acquisition of Haris Marine Products Subsidiary - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries Addresses NSE Queries and Defers Rights Issue Decision - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Mukka Proteins Share Price Gains as MUKKA Trades Higher - Univest</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Mukka Proteins to host virtual investor meet with ADD Capital - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:19:18 IST</t>
+          <t>2026-09-16 20:39:40 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3304,63 +3276,51 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR.NS</t>
+          <t>GTECJAINX.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Limited</t>
+          <t>G-TEC JAINX EDUCATION LIMITED</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>257</v>
+        <v>28.29999923706055</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>258.3500061035156</v>
+        <v>29</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>244.1000061035156</v>
+        <v>27.11000061035156</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>246.6999969482422</v>
+        <v>27.61000061035156</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>256.6499938964844</v>
+        <v>29.30999946594238</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>246.6999969482422</v>
+        <v>27.61000061035156</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>156066</v>
+        <v>5433</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.88</v>
+        <v>-5.8</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price - upstox.com</t>
+          <t>G-TEC (GTECJAINX.NS): Records a 3.85% Decrease to ₹28.50; Support at ₹27.07 and Resistance at ₹29.93 Frame the Range in the Current Update - Low Volume Node - siam.in</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price Fall: Price Action Review - Univest</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Uttam Sugar Mills Share Price Fall: Price Action Review - Univest</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Uttam Sugar Mills Limited (NSE:UTTAMSUGAR) Passed Our Checks, And It's About To Pay A ₹2.50 Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Uttam Sugar Mills Share Price Jumps; Technicals in Focus - Univest</t>
-        </is>
-      </c>
+          <t>G-TEC (GTECJAINX.NS): Records a 3.85% Decrease to ₹28.50; Support at ₹27.07 and Resistance at ₹29.93 Frame the Range in the Current Update - Low Volume Node - siam.in</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>QUINT.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Limited</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>57.88000106811523</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>57.88000106811523</v>
+        <v>15.88000011444092</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>57.88000106811523</v>
+        <v>14.43000030517578</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>57.88000106811523</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>48.2400016784668</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>57.88000106811523</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>41492</v>
+        <v>7301628</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.98</v>
+        <v>9.9</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Share Price near 52-week high, valuation view - Univest</t>
+          <t>Atal Realtech Share Price Today: Price Fall and Valuation - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Share Price near 52-week high, valuation view - Univest</t>
+          <t>Atal Realtech Share Price Today: Price Fall and Valuation - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Share Price Today Near Yearly High | QUINT - Univest</t>
+          <t>Atal Realtech Share Price and Daily Chart View - Kalkine India</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Stock Enters New Momentum Phase - Kalkine India</t>
+          <t>Atal Realtech Share Price Fall Streak With Fresh Weakness - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital board approves related party loans and asset pledges - scanx.trade</t>
+          <t>Atal Realtech NSE:ATALREAL Board Meeting Outcome September 2026 - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>VTMLTD.NS</t>
+          <t>MOTISONS.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>VTM Limited</t>
+          <t>Motisons Jewellers Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>40</v>
+        <v>16.3700008392334</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>50.5</v>
+        <v>18.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>39.15000152587891</v>
+        <v>16.20000076293945</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>48.83000183105469</v>
+        <v>18.02000045776367</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>42.16999816894531</v>
+        <v>16.6200008392334</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>48.83000183105469</v>
+        <v>18.02000045776367</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>388201</v>
+        <v>195683084</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>15.79</v>
+        <v>8.42</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>VTM Ltd. Share Price rises 13.42%: valuation view - Univest</t>
+          <t>Motisons Jewellers to consider redemption of 50 lakh preference shares - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>VTM Ltd. Share Price rises 13.42%: valuation view - Univest</t>
+          <t>Motisons Jewellers to consider redemption of 50 lakh preference shares - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>VTMLTD Stock Price and Chart — NSE:VTMLTD - TradingView</t>
+          <t>Motisons Jewellers Share Price Today: Price Rise Review - Univest</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>VTM Share Price Fall: Technicals, Valuation, Sector - Univest</t>
+          <t>Motisons Jewellers Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>VTM Ltd. (VTMLTD) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>Motisons (MOTISONS.NS) Range: Finishes 1.03% Down at ₹16.29 at the Close; Market Levels: Traders Can Monitor the ₹15.48-₹17.10 Range under the Current Snapshot - Buyback Factor - siam.in</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ATAM.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Limited</t>
+          <t>Syrma SGS Technology Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>53.70000076293945</v>
+        <v>1513.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>65</v>
+        <v>1658</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>52.91999816894531</v>
+        <v>1513.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>62.15000152587891</v>
+        <v>1638</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>54.66999816894531</v>
+        <v>1511.199951171875</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>62.15000152587891</v>
+        <v>1638</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>168135</v>
+        <v>7953634</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>13.68</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Limited Receives API Spec Q1 Certification From American Petroleum Institute - scanx.trade</t>
+          <t>Syrma SGS Technology soars 9%, up 125% in 2026; what's driving EMS stock? - Business Standard</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Dividend record date alert: Last chance to buy today for cash reward; Hindustan Copper, Bajaj Steel, VST Tillers, others - TradingView</t>
+          <t>SEMICON India 2026: Syrma SGS, Dixon Tech, Kaynes Technology, Moschip Technologies shares rise up to 10% - Business Today</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Syrma SGS, Kaynes Tech, Dixon Shares Rally: Semiconductor Stocks In Focus As SEMICON India Begins - NDTV Profit</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves Q2 Results FY27: Date and Expectations - Univest</t>
+          <t>SEMICON India 2026: Syrma SGS, Dixon Tech, Kaynes Technology, Moschip Technologies shares rise up to 10% - Business Today</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Atam Valves (NSE: ATAM): Catalysts and Risks - Kalkine India</t>
+          <t>SEMICON India 2026: Syrma, Tata Tech, Tata Elxsi, MosChip shares jump up to 10%; here is why - Upstox</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>NPST.NS</t>
+          <t>AEROENTER.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Network People Services Technologies Limited</t>
+          <t>Aeroflex Enterprises Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1730</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1934</v>
+        <v>123.3899993896484</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1673.5</v>
+        <v>112.1999969482422</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1834.599975585938</v>
+        <v>122.6800003051758</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1639.5</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1834.599975585938</v>
+        <v>122.6800003051758</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3027973</v>
+        <v>1290618</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>11.9</v>
+        <v>8.23</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>NPST Share Price rises 10.36%: price action and analysis - Univest</t>
+          <t>Sat Industries Share Price up 8.25%: fundamentals and peers - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Multibagger small cap stock Network People Services share price surges 18% today: Here's what is driving the rally - TradingView</t>
+          <t>Sat Industries Share Price up 8.25%: fundamentals and peers - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
+          <t>Aeroflex Enterprises Share Price and Technical View - Kalkine India</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>NPST wins Best Digital Banking Platform at Global Fintech Awards 2026 - scanx.trade</t>
+          <t>Sat Industries Ltd. Share Price News and Price Action Today - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Multibagger small cap stock Network People Services share price surges 18% today: Here's what is driving the rally - TradingView</t>
+          <t>Sat Industries Share Price Rises 8.5%: Market Cap, Valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,68 +829,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK.NS</t>
+          <t>AHCL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CSB Bank Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>297.8999938964844</v>
+        <v>19.70000076293945</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>337</v>
+        <v>21.79000091552734</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>297.7999877929688</v>
+        <v>19.70000076293945</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>328.75</v>
+        <v>21.54000091552734</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>296.3500061035156</v>
+        <v>20.04000091552734</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>328.75</v>
+        <v>21.54000091552734</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>8547664</v>
+        <v>30345125</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>10.93</v>
+        <v>7.49</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>CSB Bank Falls 2.58% to ₹312.85: Support at ₹297.21 Holds the Key for CSBBANK.NS - Channel Projection - siam.in</t>
+          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>RBI gives ICICI Bank (NYSE: IBN) unit one year to acquire stakes in four lenders - Stock Titan</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>CSB Bank Ltd. Share Price: 52-Week Low and Valuation View - Univest</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>CSB (CSBBANK.NS) Financial Update: The Latest Report Adds New Financial Reference Points in the Current Update; Post-Report: The Share Price Moves Only Slightly in Latest Trading - Earnings Growth Analysis - siam.in</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>News by CNBC TV18 on TradingView, 2026-09-08 — cnbctv:53b6c3a40094b:0 - TradingView</t>
-        </is>
-      </c>
+          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -898,68 +886,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ANTELOPUS.NS</t>
+          <t>RATNAVEER.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy Limited</t>
+          <t>Ratnaveer Precision Engineering Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1071.050048828125</v>
+        <v>287.75</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1214.449951171875</v>
+        <v>322</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>996.0999755859375</v>
+        <v>284.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1170.949951171875</v>
+        <v>307.3999938964844</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1057.800048828125</v>
+        <v>286.75</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1170.949951171875</v>
+        <v>307.3999938964844</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4318807</v>
+        <v>16595283</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10.7</v>
+        <v>7.2</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy ESOP Allotment 22,138 Shares September 2026 - Kalkine India</t>
+          <t>Press Release Distribution India - Business Wire India</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy ESOP Allotment 22,138 Shares September 2026 - Kalkine India</t>
+          <t>Ratnaveer Precision Engineering Publishes Rights Issue Allotment Details in Newspapers - TipRanks</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Ratnaveer Precision Engineering approves capital increase and director appointment - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>176% return in 2026 so far! Antelopus Selan Energy falls 3% after massive rally | What’s spooking investors? - Livemint</t>
+          <t>Ratnaveer Precision Engineering Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy shares rally 20% to 52-week high; what investors need to know - Upstox</t>
+          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -967,68 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KMCSHIL.NS</t>
+          <t>SUNSHINE.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>K M C Speciality Hospitals (India) Limited</t>
+          <t>Sunshine Pictures Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>133.4600067138672</v>
+        <v>365</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>154</v>
+        <v>395.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>128.4799957275391</v>
+        <v>350</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>146.9299926757812</v>
+        <v>389.3500061035156</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>132.8000030517578</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>146.9299926757812</v>
+        <v>389.3500061035156</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>9088405</v>
+        <v>1922166</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10.64</v>
+        <v>7.05</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>KMCSHIL Stock Price and Chart — NSE:KMCSHIL - TradingView</t>
+          <t>SUNSHINE Share Price Rises 9.05%: Price Action, Valuation - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals Share Price: Price Action and Peers - Univest</t>
+          <t>Sunshine Biopharma Authorizes Reverse Stock Split of Up to 1-for-20 - Minichart</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals (India) Limited Trade Ideas — NSE:KMCSHIL - TradingView</t>
+          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals Share Price: price rise, valuation - Univest</t>
+          <t>An oral drug candidate suppressed lung virus in infected mice - Stock Titan</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals (India) Ltd (KMCSHIL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>SUNSHINE PICTURES LIMITED Share Price - Live NSE: SUNSHINE Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1036,68 +1024,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>FOSECOIND.NS</t>
+          <t>HBLENGINE.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Foseco India Limited</t>
+          <t>HBL Engineering Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6224.5</v>
+        <v>710.7999877929688</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7040</v>
+        <v>754.5499877929688</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6141</v>
+        <v>707.7000122070312</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6846.5</v>
+        <v>753.1500244140625</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6223.5</v>
+        <v>704.6500244140625</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6846.5</v>
+        <v>753.1500244140625</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>178656</v>
+        <v>5649210</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10.01</v>
+        <v>6.88</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Foseco India Share Price Hits 52-Week High on Market Update - Univest</t>
+          <t>Should You Buy HBL Engineering Limited (NSE:HBLENGINE) For Its Upcoming Dividend? - simplywall.st</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Foseco India Share Price Hits 52-Week High on Market Update - Univest</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Morganite Crucible sells entire 7.84% stake in Foseco India - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Foseco India provides web-link for FY25 annual report - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Foseco India schedules physical analyst meet with SBI Mutual Fund - scanx.trade</t>
-        </is>
-      </c>
+          <t>Should You Buy HBL Engineering Limited (NSE:HBLENGINE) For Its Upcoming Dividend? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1105,68 +1081,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX.NS</t>
+          <t>KMCSHIL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Limited</t>
+          <t>K M C Speciality Hospitals (India) Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>49.43000030517578</v>
+        <v>146.9199981689453</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>49.43000030517578</v>
+        <v>160.3899993896484</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>49.43000030517578</v>
+        <v>144.4700012207031</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>49.43000030517578</v>
+        <v>156.5599975585938</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>44.93999862670898</v>
+        <v>146.9299926757812</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>49.43000030517578</v>
+        <v>156.5599975585938</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>16118</v>
+        <v>4766322</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.99</v>
+        <v>6.55</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Share Price Rises 9.99% on Valuation View - Univest</t>
+          <t>KMC Speciality Hospitals Share Price: price rise, valuation - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>KMC Speciality Hospitals Share Price: Price Action and Peers - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>KMC Speciality Hospitals (India) Ltd (KMCSHIL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>KMC Speciality Hospitals Share Price: Price Action and Peers - Univest</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
+          <t>KMC Speciality Hospitals Share Price today near 52-week peak - Univest</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1174,68 +1150,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RRECL.NS</t>
+          <t>QUADFUTURE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions Limited</t>
+          <t>Quadrant Future Tek Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>124</v>
+        <v>490</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>136</v>
+        <v>534.3499755859375</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>124</v>
+        <v>484</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>135.5700073242188</v>
+        <v>523</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>123.6999969482422</v>
+        <v>491.9500122070312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>135.5700073242188</v>
+        <v>523</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>707</v>
+        <v>1681591</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.6</v>
+        <v>6.31</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>RRECL Stock Price and Chart — NSE:RRECL - TradingView</t>
+          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
+          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions Share Price Today Down 9.14% - Univest</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>RDB Real Estate Constructions Ltd. (RRECL) Fundamental and Financial Data - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
-        </is>
-      </c>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1243,46 +1211,46 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE.NS</t>
+          <t>CSM.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Limited</t>
+          <t>CSM Technologies Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>350.1499938964844</v>
+        <v>98.90000152587891</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>367.2999877929688</v>
+        <v>103.5999984741211</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>332.3500061035156</v>
+        <v>96.31999969482422</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>363.7000122070312</v>
+        <v>101.7799987792969</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>333.9500122070312</v>
+        <v>96.22000122070312</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>363.7000122070312</v>
+        <v>101.7799987792969</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3703580</v>
+        <v>1345357</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.91</v>
+        <v>5.78</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE Share Price Rises 9.05%: Price Action, Valuation - Univest</t>
+          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>An oral drug candidate suppressed lung virus in infected mice - Stock Titan</t>
+          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1292,19 +1260,19 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>An oral drug candidate suppressed lung virus in infected mice - Stock Titan</t>
+          <t>How (CSM) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of CHERISH SUNSHINE INTL LTD. – OTC:CHSIF - TradingView</t>
+          <t>CSM Share Price Today Falls: P/E, P/B and Sector Context - Univest</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1312,60 +1280,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MEDICAMEQ.NS</t>
+          <t>ARIS.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Medicamen Biotech Limited</t>
+          <t>Arisinfra Solutions Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>315.3500061035156</v>
+        <v>116.5400009155273</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>354.3999938964844</v>
+        <v>124.8000030517578</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>290.5499877929688</v>
+        <v>116.5400009155273</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>345.5</v>
+        <v>123.2399978637695</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>318.2000122070312</v>
+        <v>116.5299987792969</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>345.5</v>
+        <v>123.2399978637695</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>248990</v>
+        <v>1695350</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.58</v>
+        <v>5.76</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Medicamen Biotech Gains 5%: Stock Approaches Key Resistance at ₹274.54 - Keltner Channel - siam.in</t>
+          <t>Aris Mining Corp (ARIS) Shares Fall 3.6% -- What GF Score of 69 Tells Investors - GuruFocus</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Rasayan holds 40.46% stake in Medicamen Biotech - scanx.trade</t>
+          <t>When the Price of (ARIS.WT.A) Talks, People Listen (ARIS.WT.A:CA) - Stock Traders Daily</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Rasayan holds 40.46% stake in Medicamen Biotech - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Aris Mining (TSX:ARIS) Stock Looks Fairly Valued After A Very Large Run - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>When the Price of (ARIS.WT.A) Talks, People Listen (ARIS.WT.A:CA) - Stock Traders Daily</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Aris Mining Corporation (ARIS) Stock Price | Live Quotes &amp; Charts | NYSE - StocksToTrade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1373,68 +1349,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IOLCP.NS</t>
+          <t>LXCHEM.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals and Pharmaceuticals Limited</t>
+          <t>Laxmi Organic Industries Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>182</v>
+        <v>170.3500061035156</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>197.8999938964844</v>
+        <v>183.8999938964844</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>173.5500030517578</v>
+        <v>170.3500061035156</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>194.5700073242188</v>
+        <v>181.2400054931641</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>179.5200042724609</v>
+        <v>171.7299957275391</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>194.5700073242188</v>
+        <v>181.2400054931641</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>8623017</v>
+        <v>2087931</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>5.54</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals Share Price Today after fresh 52-week high - Univest</t>
+          <t>Laxmi (LXCHEM.NS) Earnings Numbers in Focus: The Company Reports Its Latest Available Figures; Market Read: Shares Finish 0.07% Lower - ROA Comparison - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals Stock Falls After Recent Rise - Kalkine India</t>
+          <t>Laxmi Organic Industries Limited Announces the Resignation of Dr. Rajan Venkatesh as Chief Executive Officer, Effective November 13, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>IOL Chemicals (IOLCP.NS) Holds Steady Near ₹194 as Pharma-Chemical Play Consolidates - MFI Overbought - siam.in</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>IOLCP Share Price today near 52-week high, price action - Univest</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>IOLCP Share Price today at 52-week high; sector context - Univest</t>
-        </is>
-      </c>
+          <t>Laxmi Organic Industries Limited Announces the Resignation of Dr. Rajan Venkatesh as Chief Executive Officer, Effective November 13, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1442,68 +1410,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA.NS</t>
+          <t>AEROFLEX.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>eMudhra Limited</t>
+          <t>Aeroflex Industries Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>625</v>
+        <v>483.1000061035156</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>677</v>
+        <v>512.0999755859375</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>600.3499755859375</v>
+        <v>483.1000061035156</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>642.2999877929688</v>
+        <v>507.5</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>592.8499755859375</v>
+        <v>481.1000061035156</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>642.2999877929688</v>
+        <v>507.5</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>30254742</v>
+        <v>1648601</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>8.34</v>
+        <v>5.49</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>eMudhra share price jumps 12% today, extends gains for second session | What's behind the rally? - Livemint</t>
+          <t>Aeroflex Industries Share Price today: key market update - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>eMudhra says LEI deal could lift Trust Services growth; 25% margins sustainable - cnbctv18.com</t>
+          <t>Aeroflex Industries Share Price today: key market update - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>eMudhra shares zoom nearly 37% in two days; here's the trigger - BusinessToday - IndiaIPO</t>
+          <t>Aeroflex Industries Ltd Hits Intraday Low Amid Price Pressure on 15 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>eMudhra says LEI deal could lift Trust Services growth; 25% margins sustainable - cnbctv18.com</t>
+          <t>Aeroflex Enterprises Share Price and Technical View - Kalkine India</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>eMudhra Shares Surge as Momentum Strengthens - Kalkine India</t>
+          <t>Aeroflex Industries Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1511,64 +1479,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>INDTERRAIN.NS</t>
+          <t>HDFCLIFE.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Indian Terrain Fashions Limited</t>
+          <t>HDFC Life Insurance Company Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>28.89999961853027</v>
+        <v>532.9000244140625</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>33.61000061035156</v>
+        <v>560.5499877929688</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.36000061035156</v>
+        <v>529.9500122070312</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>30.29000091552734</v>
+        <v>558.4500122070312</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.01000022888184</v>
+        <v>530.2000122070312</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30.29000091552734</v>
+        <v>558.4500122070312</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>251131</v>
+        <v>5741713</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>5.33</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Indian Terrain Fashions Share Price today after 19.47% rise - Univest</t>
+          <t>HDFCLIFE Outlook for the Week - Equitypandit</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Indian Terrain Fashions Share Price today after 19.47% rise - Univest</t>
+          <t>HDFC Life share price rises on IRDAI commission cut report - Business Upturn</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Indian (INDTERRAIN.NS) Market: Declines 0.79% to ₹30.05 at the Close; Market Levels: ₹28.55 and ₹31.55 Define the Nearby Reference Levels under the Current Snapshot - Covered Call ETF - siam.in</t>
+          <t>HDFC Life Share Price Today (HDFCLIFE) | Live Chart, News &amp; Stock Market - TechGraph</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Indian (INDTERRAIN.NS) Update: Ends Lower by 0.92% at ₹30.27 at the Close; Range View: Traders Can Monitor the ₹28.76-₹31.78 Range on the Day - Sell Signal Alerts - siam.in</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>HDFC (HDFCLIFE.NS) Results Versus Estimates: The Company Publishes Its Latest Results in the Latest Reading; Latest Reaction: Shares Move 1.13% Lower in the Current Update - Strong Earnings Momentum - siam.in</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>HDFC Life Share Price Today: Fall, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1576,60 +1548,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>ICICIPRULI.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Limited</t>
+          <t>ICICI Prudential Life Insurance Company Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>247.5</v>
+        <v>470</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>270</v>
+        <v>496.8999938964844</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>243.1499938964844</v>
+        <v>468.75</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>265.8500061035156</v>
+        <v>494.8999938964844</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>246</v>
+        <v>470</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>265.8500061035156</v>
+        <v>494.8999938964844</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>27577</v>
+        <v>1918837</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8.07</v>
+        <v>5.3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Files Minutes of 55th AGM with Stock Exchanges - The Globe and Mail</t>
+          <t>ICICIPRULI 52 Week Low Streak: Decline, valuation, peers - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Files Minutes of 55th AGM with Stock Exchanges - The Globe and Mail</t>
+          <t>ICICI Prudential Life Insurance Share Price rises 2.06% - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Kanpur (KANPRPLA.NS) Financial Update: Available Data Shows the Latest Reported Performance under the Current Snapshot; Closing Reaction: The Share Price Sheds 4.13% in the Latest Reading - Earnings Trend Analysis - siam.in</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>ICICI Prudential Life ESOP Allotment of 184,265 Shares - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>ICICIPRULI Outlook for the Week - Equitypandit</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Life Insurance Company Ltd. (ICICIPRULI) Share Price Hits Fresh 52-Week Low - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1637,68 +1617,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MOREPENLAB.NS</t>
+          <t>REFEX.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Morepen Laboratories Limited</t>
+          <t>Refex Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>106.4499969482422</v>
+        <v>259.3999938964844</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>116</v>
+        <v>277</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>97.04000091552734</v>
+        <v>259.3999938964844</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>114.7300033569336</v>
+        <v>274.6000061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>106.2200012207031</v>
+        <v>260.8999938964844</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>114.7300033569336</v>
+        <v>274.6000061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>39395018</v>
+        <v>371806</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8.01</v>
+        <v>5.25</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And Morepen Laboratories (NSE:MOREPENLAB) Passed With Ease - simplywall.st</t>
+          <t>Refex Industries promoter pledges additional shares for personal use - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Morepen Laboratories Share Price rises 5.65%; valuation view - Univest</t>
+          <t>Refex Industries to host investor meet at Anand Rathi summit - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Morepen Laboratories (MOREPENLAB) Share Price Falls 6.25% Today; Valuation and Sector Context in Focus - Univest</t>
+          <t>Refex promoter pledges 35 lakh shares for margin funding - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Morepen Laboratories Share Price rises 5.65%; valuation view - Univest</t>
+          <t>Refex Industries (REFEX.NS) Gains 2.36%: Stock Approaches Key Resistance Zone Near ₹311.69 - Analyst Upgrade Stocks - siam.in</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Morepen Laboratories Share Price today after yearly high - Univest</t>
+          <t>Stocks to watch: Hindustan Copper, TCS, Refex Industries, Lenskart, Suzlon - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1706,68 +1686,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>KRYSTAL.NS</t>
+          <t>MOSCHIP.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Krystal Integrated Services Limited</t>
+          <t>Moschip Technologies Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>611.9500122070312</v>
+        <v>200</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>668.5</v>
+        <v>212.8000030517578</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>600.25</v>
+        <v>200</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>655.5999755859375</v>
+        <v>209.4100036621094</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>607.7999877929688</v>
+        <v>199.1600036621094</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>655.5999755859375</v>
+        <v>209.4100036621094</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>174509</v>
+        <v>3833688</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.86</v>
+        <v>5.15</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Krystal Q4 FY26 Earnings: 20%+ Growth Guided, Citelum Acquisition Completed - scanx.trade</t>
+          <t>SEMICON India 2026: Syrma, Tata Tech, Tata Elxsi, MosChip shares jump up to 10%; here is why - Upstox</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Krystal Q4 FY26 Earnings: 20%+ Growth Guided, Citelum Acquisition Completed - scanx.trade</t>
+          <t>SEMICON India 2026: Syrma SGS, Dixon Tech, Kaynes Technology, Moschip Technologies shares rise up to 10% - Business Today</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Krystal Integrated Services Limited (NSE:KRYSTAL) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+          <t>SEMICON India 2026: Syrma SGS, Dixon Tech, Kaynes Technology, Moschip Technologies shares rise up to 10% - Business Today</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Krystal Integrated Services Gains 3.29%: Stock Approaches Key Resistance at ₹679.72 - Ichimoku Kumo Twist - siam.in</t>
+          <t>Moschip Technologies Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Krystal Stock Gains 13.4% in a Month: What Is Driving the Rally? - TradingView</t>
+          <t>Moschip Technologies Slips 2.23% to ₹206.69 — Testing the Middle of Its Recent Range - Gap and Go - siam.in</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1775,68 +1755,60 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>PATANJALI.NS</t>
+          <t>SEJALLTD.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Patanjali Foods Limited</t>
+          <t>Sejal Glass Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>339.0499877929688</v>
+        <v>681.7000122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>367.3999938964844</v>
+        <v>681.7000122070312</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>337.5</v>
+        <v>663</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>365</v>
+        <v>681.7000122070312</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>338.5499877929688</v>
+        <v>649.25</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>365</v>
+        <v>681.7000122070312</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>27861262</v>
+        <v>11601</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.81</v>
+        <v>5</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Patanjali Foods: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>Sejal (SEJALLTD.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points under the Current Snapshot; After Results: Shares Finish 0.16% Up for the Current Session - Revenue Guidance Update - siam.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Patanjali Foods: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>Sejal Glass Jun 2026 Earnings: Positive EPS of ₹0.35 on Revenue of ₹36.43 Crore; Stock Slips Marginally - Low Estimate Range - siam.in</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals, 3M India, Patanjali Foods shares spurt amid spike in volumes; check full list - Upstox</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Patanjali Foods share price rises 5% today. What is driving the rally in the FMCG stock? - Livemint</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>FMCG Stocks Surge: Nestle India, ITC, HUL, Patanjali Foods Shares Jump Over 3% - NDTV Profit</t>
-        </is>
-      </c>
+          <t>Sejal Glass Jun 2026 Earnings: Positive EPS of ₹0.35 on Revenue of ₹36.43 Crore; Stock Slips Marginally - Low Estimate Range - siam.in</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1844,54 +1816,58 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ISHANCH.NS</t>
+          <t>BODALCHEM.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Limited</t>
+          <t>Bodal Chemicals Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>44.70000076293945</v>
+        <v>173</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>48.90000152587891</v>
+        <v>182.1300048828125</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>43.5</v>
+        <v>173</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>47.11999893188477</v>
+        <v>182.1300048828125</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43.72999954223633</v>
+        <v>173.4600067138672</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>47.11999893188477</v>
+        <v>182.1300048828125</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>32446</v>
+        <v>2309741</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7.75</v>
+        <v>5</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Share Price Today After 11.7% Rise - Univest</t>
+          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Share Price Today: key metrics - Univest</t>
+          <t>Bodal Chemicals Share Price rise: fundamentals and peers - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Share Price Today: key metrics - Univest</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
+          <t>Bodal Chemicals Share Price news with valuation context - Univest</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Bodal Chemicals Share Price rise: fundamentals and peers - Univest</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1918,7 +1894,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2017,7 +1993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2025,68 +2001,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SRGHFL.NS</t>
+          <t>SIGACHI.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Limited</t>
+          <t>Sigachi Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>126.4000015258789</v>
+        <v>27.57999992370605</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>138.1999969482422</v>
+        <v>31.23999977111816</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>126.4000015258789</v>
+        <v>27.57999992370605</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>126.4000015258789</v>
+        <v>28.93000030517578</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>140.3999938964844</v>
+        <v>31.15999984741211</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>126.4000015258789</v>
+        <v>28.93000030517578</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>350176</v>
+        <v>9338652</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-9.970000000000001</v>
+        <v>-7.16</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance (SRGHFL) Share Price Falls 9.95% Today - Univest</t>
+          <t>Sigachi Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance (SRGHFL) Share Price Falls 9.95% Today - Univest</t>
+          <t>Sigachi Industries Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Daily Chart Analysis - Kalkine India</t>
+          <t>Sigachi Industries Share Price Today: key stock analysis - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Sigachi Industries Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Faces Sharp Breakdown - Kalkine India</t>
+          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2094,60 +2070,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UMESLTD.NS</t>
+          <t>LALITHAA.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Limited</t>
+          <t>Lalithaa Jewellery Mart Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.900000095367432</v>
+        <v>295</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.900000095367432</v>
+        <v>299.7000122070312</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.079999923706055</v>
+        <v>290.3999938964844</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4.079999923706055</v>
+        <v>290.3999938964844</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4.53000020980835</v>
+        <v>305.6499938964844</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.079999923706055</v>
+        <v>290.3999938964844</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>363161</v>
+        <v>4985001</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.93</v>
+        <v>-4.99</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Usha (UMESLTD.NS) Quarterly Update: Available Data Shows the Latest Reported Performance in Latest Trading; Market Follow-Through: The Stock Loses 2.33% on the Day - Profit Cycle Analysis - siam.in</t>
+          <t>Lalithaa Jewellery Shares Hit 5% Lower Circuit After Weak Q1 Results; Here's What Investors Should Know - Trade Brains</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Sets Date for 29th AGM and Closes Share Transfer Books - TipRanks</t>
+          <t>Lalithaa Jewellery Q1FY27 net profit falls 40% QoQ to ₹208 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Usha Martin Education &amp; Solutions Sets Date for 29th AGM and Closes Share Transfer Books - TipRanks</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Lalithaa Jewellery Mart Ltd. Share Price Live Today - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Lalithaa Jewellery Q1FY27 net profit falls 40% QoQ to ₹208 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Stocks to Watch Today: HDFC Bank, Lalithaa Jewellery, Horizon Industrial Parks, Solar Industries,... - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2155,68 +2139,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GRAVISSHO.NS</t>
+          <t>GLFL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Limited</t>
+          <t>Gujarat Lease Financing Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>49</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>49.90000152587891</v>
+        <v>5.440000057220459</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>42.27999877929688</v>
+        <v>5.090000152587891</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>42.36999893188477</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46.97000122070312</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>42.36999893188477</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>94415</v>
+        <v>3278</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.789999999999999</v>
+        <v>-4.67</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
+          <t>Gujarat Lease Financing Slips 2.19% to ₹5.8: Stock Hovers Near Crucial Support Zone - Dividend Stock Picks - siam.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
+          <t>Gujarat Lease Financing Limited (NSE:GLFL): Understanding Its Operati - Kalkine India</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Share Price: price action and valuation - Univest</t>
+          <t>Gujarat Lease Financing Limited (NSE:GLFL): Understanding Its Operati - Kalkine India</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Graviss Hospitality Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
-        </is>
-      </c>
+          <t>Competent Automobiles Company Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2224,68 +2204,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>LAMBODHARA.NS</t>
+          <t>TNPL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Limited</t>
+          <t>Tamil Nadu Newsprint &amp; Papers Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>128.6499938964844</v>
+        <v>147.25</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>130.5</v>
+        <v>151</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>116.5999984741211</v>
+        <v>145.1499938964844</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>117.7600021362305</v>
+        <v>145.1699981689453</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>130.3300018310547</v>
+        <v>152.0899963378906</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>117.7600021362305</v>
+        <v>145.1699981689453</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>98400</v>
+        <v>249532</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-9.640000000000001</v>
+        <v>-4.55</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Share Price Fall: Price Analysis - Univest</t>
+          <t>TNPL shareholders approve R Kannan and N Venkatesh as directors - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Share Price Today: Price Fall Analysis - Univest</t>
+          <t>TNPL shareholders approve R Kannan and N Venkatesh as directors - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara (LAMBODHARA.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points for the Current Session; Investor Response: The Stock Gains 0.68% in Latest Trading - Earnings Surprise Stocks - siam.in</t>
+          <t>Tamil Nadu Newsprint and Papers (NSE:TNPL) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Share Price Today: 8.85% Price Rise - Univest</t>
+          <t>Paper PSU Stock: TNPL Growth Analysis 2026 - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara (LAMBODHARA.NS) Earnings Reading: The Company Releases Its Current Earnings Data on the Day; Trading Move: Shares Finish 19.99% Up for the Current Session - Earnings Outlook Update - siam.in</t>
+          <t>TNPL files business responsibility and sustainability report for FY26 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2293,68 +2273,60 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>LADDERUP.NS</t>
+          <t>JETFREIGHT.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Limited</t>
+          <t>Jet Freight Logistics Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>66.80000305175781</v>
+        <v>19.98999977111816</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>66.80000305175781</v>
+        <v>20.17000007629395</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>60.20000076293945</v>
+        <v>16.51000022888184</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>60.93999862670898</v>
+        <v>19.01000022888184</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>66.87999725341797</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>60.93999862670898</v>
+        <v>19.01000022888184</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>9998</v>
+        <v>582225</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-8.880000000000001</v>
+        <v>-4.47</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Pranav Constructions Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Jet (JETFREIGHT.NS) EPS and Revenue: The Company Reports Its Latest Available Figures in the Available Record; Share Move: Shares Move Higher 0.76% in the Latest Reading - EPS Guidance Update - siam.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Pranav Constructions Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Jet Freight Logistics sets Sept 23 AGM; seeks approval for ₹250 crore borrowing limit - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Ltd. Upper Circuit Streak: Day 2 Price and Data - Univest</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Ladderup Finance releases FY26 annual report, sets Sep 24 AGM date - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Ladderup Finance Ltd Upgraded to Hold on Improved Technicals and Valuation - MarketsMojo</t>
-        </is>
-      </c>
+          <t>Jet Freight Logistics sets Sept 23 AGM; seeks approval for ₹250 crore borrowing limit - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2362,68 +2334,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NOVARTIND.NS</t>
+          <t>SHIVALIK.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Limited</t>
+          <t>Shivalik Rasayan Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2164</v>
+        <v>389.1499938964844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2178.10009765625</v>
+        <v>399.8500061035156</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1980</v>
+        <v>373.5499877929688</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1995.5</v>
+        <v>374.7000122070312</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2188</v>
+        <v>389.1499938964844</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1995.5</v>
+        <v>374.7000122070312</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>122475</v>
+        <v>80073</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-8.800000000000001</v>
+        <v>-3.71</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price Today: 6.19% Fall, Key Metrics - Univest</t>
+          <t>Shivalik Rasayan surges 62% in two months after Fair Value signal - Investing.com India</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price Today: 6.19% Fall, Key Metrics - Univest</t>
+          <t>Shivalik Rasayan surges 62% in two months after Fair Value signal - Investing.com India</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Receives Detailed Public Statement for ₹552.49 Crore Open Offer - scanx.trade</t>
+          <t>Shivalik Rasayan Share Price: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Novartis (NOVARTIND.NS) Financial Update: The Company Lists Its Latest Available Figures; Stock Move: Shares Close 1.06% Lower - Earnings Whisper Number - siam.in</t>
+          <t>Shivalik Rasayan seeks approval for ₹33 crore preferential share and warrant issue - scanx.trade</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price: fresh 52-week high, valuation - Univest</t>
+          <t>Shivalik Rasayan Ltd. Stock News - Value Research</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2431,68 +2403,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>HTEL.NS</t>
+          <t>ALOKINDS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Alok Industries Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>78.40000152587891</v>
+        <v>7.489999771118164</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>78.40000152587891</v>
+        <v>7.579999923706055</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>71.79000091552734</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>74.20999908447266</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>81.31999969482422</v>
+        <v>7.480000019073486</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>74.20999908447266</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3850262</v>
+        <v>22914578</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-8.74</v>
+        <v>-3.21</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Alok Industries Ltd Share Price Today,, ALOKINDS Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>RIL-backed stock hits fresh 52-week low; shares plunge nearly 56% YTD - Business Today</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
+          <t>Mukesh Ambani's RIL-backed textile stock crash 21% in just 5 days - What's behind the plunge? Explained - TradingView</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Free float of Hy-Tech Engineers Limited – NSE:HTEL - TradingView</t>
+          <t>Alok Industries Share Price: price action and fundamentals - Univest</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPO subscribed 131.68 times so far on Day 4: Check allotment date and steps - Upstox</t>
+          <t>Alok Industries Share Price: fresh 52-week low, analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2500,60 +2472,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>AMDIND.NS</t>
+          <t>POLICYBZR.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Limited</t>
+          <t>PB Fintech Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>68.5</v>
+        <v>1839</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>72.37000274658203</v>
+        <v>1845</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>62.20000076293945</v>
+        <v>1718.099975585938</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.65999984741211</v>
+        <v>1772.599975585938</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>69.63999938964844</v>
+        <v>1827.099975585938</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>63.65999984741211</v>
+        <v>1772.599975585938</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>423728</v>
+        <v>4933749</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-8.59</v>
+        <v>-2.98</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Stock: Momentum Above 50-Day SMA - Kalkine India</t>
+          <t>PB (POLICYBZR.NS) Momentum: Finishes 2.75% Up at ₹1,847.70 in the Latest Session; Price Levels - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Stock: Momentum Above 50-Day SMA - Kalkine India</t>
+          <t>Raja Venkatraman recommends three stocks for 17 September - livemint.com</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>AMD Industries Share Price rises 12.01%: valuation view - Univest</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>PB Fintech Share Price Today: 2.93% Rise, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>PB Fintech Share Price Fall: Technicals, Valuation, Peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Raja Venkatraman recommends three stocks for 17 September - livemint.com</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2561,56 +2541,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PKTEA.NS</t>
+          <t>HTEL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1020</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1020</v>
+        <v>76.69999694824219</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>922.2000122070312</v>
+        <v>68.22000122070312</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>936.9500122070312</v>
+        <v>72.01000213623047</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1024.599975585938</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>936.9500122070312</v>
+        <v>72.01000213623047</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5051</v>
+        <v>2852418</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-8.550000000000001</v>
+        <v>-2.96</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Free float of Hy-Tech Engineers Limited – NSE:HTEL - TradingView</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Hy-Tech Engineers IPO subscribed 131.68 times so far on Day 4: Check allotment date and steps - Upstox</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2618,68 +2610,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>FREDUN.NS</t>
+          <t>SUMEETINDS.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Fredun Pharmaceuticals Limited</t>
+          <t>Sumeet Industries Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1322.5</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1345.800048828125</v>
+        <v>9.979999542236328</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1195.199951171875</v>
+        <v>9.310000419616699</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1221.599975585938</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1327.900024414062</v>
+        <v>9.729999542236328</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1221.599975585938</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>306694</v>
+        <v>1207925</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-8.01</v>
+        <v>-2.88</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Fredun Pharmaceuticals allots 1.1 Cr bonus shares in 2:1 ratio - scanx.trade</t>
+          <t>Sumeet Industries AGM Notice 2026: NSE:SUMEETINDS Filing - Kalkine India</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Furlicks Goes from 6 to 22 SKUs: Fredun Pharmaceuticals Ltd. Accelerates Pet Wellness Expansion - NewsX</t>
+          <t>Sumeet Industries Addresses NSE Queries and Defers Rights Issue Decision - TipRanks</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Fredun Pharmaceuticals expands Furlicks pet brand from 6 to 22 SKUs - scanx.trade</t>
+          <t>Sumeet Industries submits Q1FY27 earnings call audio recording - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Fredun Pharma acquires Wellbeing Nutrition's pet wellness brand - VCCircle</t>
+          <t>Sumeet Industries announces ₹199.75 Cr rights issue to fund expansion - scanx.trade</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Fredun Pharma FY26 net profit rises 60%; announces 2:1 bonus - scanx.trade</t>
+          <t>Sumeet Industries Addresses NSE Queries and Defers Rights Issue Decision - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2687,60 +2679,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS.NS</t>
+          <t>KRN.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal Seeds And Chemicals Limited</t>
+          <t>KRN Heat Exchanger and Refrigeration Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16.47999954223633</v>
+        <v>1430</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>16.5</v>
+        <v>1453</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>14.51000022888184</v>
+        <v>1386</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>14.60000038146973</v>
+        <v>1400.699951171875</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.82999992370605</v>
+        <v>1438.300048828125</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14.60000038146973</v>
+        <v>1400.699951171875</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>530991</v>
+        <v>502213</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-7.77</v>
+        <v>-2.61</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Shree Oswal Seeds and Chemicals Share Price Analysis - Univest</t>
+          <t>Paytm, KRN Heat Exchanger, Ather Energy, Vishal Mega Mart: Expert shares key entry levels, targets - BusinessToday - indiaipo.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Shree Oswal Seeds and Chemicals Share Price Analysis - Univest</t>
+          <t>Paytm, KRN Heat Exchanger, Ather Energy, Vishal Mega Mart: Expert shares key entry levels, targets - BusinessToday - indiaipo.in</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>KRN Share Price Fall: Technical Setup and Sector Context - Univest</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>KRN Heat Exchanger and Refrigeration Ltd leads losers in 'A' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>KRN Heat Exchanger and Refrigeration Bull Case vs Bear Case for 2026 - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2748,68 +2748,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GKB.NS</t>
+          <t>AQYLON.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>GKB Ophthalmics Limited</t>
+          <t>Aqylon Nexus Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>65.80000305175781</v>
+        <v>20.45000076293945</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>66.12000274658203</v>
+        <v>20.45000076293945</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>62.20000076293945</v>
+        <v>19.13999938964844</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.36999893188477</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>67.41999816894531</v>
+        <v>19.70999908447266</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>62.36999893188477</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>916</v>
+        <v>304802</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-7.49</v>
+        <v>-2.59</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>GKB Stock Price and Chart — NSE:GKB - TradingView</t>
+          <t>Aqylon Nexus promoter Kurjibhai Rupareliya sells 1.36% stake in open market - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>GKB Ophthalmics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Aqylon Nexus promoter Kurjibhai Rupareliya sells 1.36% stake in open market - scanx.trade</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>GKB Ophthalmics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>GKB Ophthalmics shareholders unanimously approve all seven AGM resolutions - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>GKB Ophthalmics Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
-        </is>
-      </c>
+          <t>Aqylon Nexus Promoter Sells 34.47 Lakh Shares - whalesbook.com</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2817,60 +2809,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>NAVKARCORP.NS</t>
+          <t>MVELECTRO.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Navkar Corporation Limited</t>
+          <t>MV Electrosystems Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>91.88999938964844</v>
+        <v>822.2999877929688</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>92.06999969482422</v>
+        <v>828.2000122070312</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>84.80000305175781</v>
+        <v>788.7999877929688</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>85.55999755859375</v>
+        <v>798.5499877929688</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>91.58000183105469</v>
+        <v>819.0499877929688</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>85.55999755859375</v>
+        <v>798.5499877929688</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1882658</v>
+        <v>697879</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-6.57</v>
+        <v>-2.5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Navkar (NAVKARCORP.NS) Results Check: The Report Supplies Updated Headline Figures in the Reported Period; Market Move: Shares Finish 0.22% Up in the Current Update - Performance Review - siam.in</t>
+          <t>MV Electrosystems Share Price Falls 8.25%: Full Analysis - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Navkar Corporation to participate in investor meet on Sep 2 - scanx.trade</t>
+          <t>Newly listed MV Electrosystems shares soar 10%: Stock jumps from Rs.425 IPO price to Rs.848 - what's driving the rally? - TradingView</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Navkar Corporation to participate in investor meet on Sep 2 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
+          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Newly listed MV Electrosystems shares soar 10%: Stock jumps from Rs.425 IPO price to Rs.848 - what's driving the rally? - TradingView</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2878,68 +2874,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>WSI.NS</t>
+          <t>MEESHO.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>W S Industries (I) Limited</t>
+          <t>Meesho Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>60.59999847412109</v>
+        <v>213</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>61.45000076293945</v>
+        <v>213.0700073242188</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>54.0099983215332</v>
+        <v>207.9199981689453</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.04000091552734</v>
+        <v>207.9799957275391</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>59.91999816894531</v>
+        <v>213.2599945068359</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>56.04000091552734</v>
+        <v>207.9799957275391</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>169308</v>
+        <v>3970259</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-6.48</v>
+        <v>-2.48</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Industries (WSI.NS) Reported Quarter: The Report Provides a New Financial Snapshot for the Current Session; Reported Share Move: Shares Finish 0.91% Up at the Close - Operating Income Trends - siam.in</t>
+          <t>Meesho Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
+          <t>Meesho - Volume Shocker: MFs added 1 crore+ shares to 8 stocks in August '26; rally up to 30% - The Economic Times</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>WSI withdraws director appointment from 63rd AGM agenda - scanx.trade</t>
+          <t>Meesho promoter confirms no encumbrance on shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>WestStar Industrial (ASX: WSI) Surges 60.71%: What’s Driving the Small-Cap Stock Higher? - Kalkine</t>
+          <t>SoftBank sells $186M Meesho stake in block deal - Dealroom</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Weststar Industrial Ltd (ASX: WSI) Share Price, WSI Stock News, WSI Share Price &amp; Updates - kalkine.ca</t>
+          <t>CAM Advises JP Morgan On Sale Of Meesho Limited's Equity Shares - LawBeat</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2947,56 +2943,60 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KNAGRI.NS</t>
+          <t>KWIL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>KN Agri Resources Limited</t>
+          <t>Kwality Wall's (India) Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>194.9499969482422</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>196.6000061035156</v>
+        <v>41.79000091552734</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>163.5500030517578</v>
+        <v>40.25</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>180.25</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>192.5200042724609</v>
+        <v>41.31999969482422</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>180.25</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>9108</v>
+        <v>5862240</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-6.37</v>
+        <v>-2.47</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>KN (KNAGRI.NS) Results Breakdown: The Latest Report Adds New Financial Reference Points at the Close; Price Move - siam.in</t>
+          <t>Kwality (KWIL.NS) Results Review: The Report Supplies Updated Headline Figures in Latest Trading; Share Response: The Stock Ends Down 2.96% in the Available Record - Revenue Per Share - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>KN (KNAGRI.NS) Results Breakdown: The Latest Report Adds New Financial Reference Points at the Close; Price Move - siam.in</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
+          <t>Kwality (KWIL.NS) Results Review: The Report Supplies Updated Headline Figures in Latest Trading; Share Response: The Stock Ends Down 2.96% in the Available Record - Revenue Per Share - siam.in</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Most Active Equities, August 21, 2026 at 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3004,68 +3004,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SIL.NS</t>
+          <t>AFCONS.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Standard Industries Limited</t>
+          <t>Afcons Infrastructure Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>17.70000076293945</v>
+        <v>256.6000061035156</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>18</v>
+        <v>258.7000122070312</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>16.31999969482422</v>
+        <v>243.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>16.52000045776367</v>
+        <v>252.1499938964844</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>17.60000038146973</v>
+        <v>258.3999938964844</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>16.52000045776367</v>
+        <v>252.1499938964844</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>80645</v>
+        <v>2072763</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-6.14</v>
+        <v>-2.42</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>How (SIL) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
+          <t>AFCONS INFRASTRUCTURE LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>How (SIL) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
+          <t>Nifty Smallcap 100 extends fall for 5th day; Afcons, FSL skid up to 14% - Business Standard</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Aishwarya Rai Bachchan celebrates Rakhi with brother Aditya, Aaradhya and family, SIL shares rare pic - FM Bharat</t>
+          <t>Shapoorji Pallonji Group stocks zoom 20% as RBI asks Tata Sons to list - Business Standard</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>(SIL) Risk-Controlled Trading Report (SIL:CA) - Stock Traders Daily</t>
+          <t>Afcons Infra stock surges on Tata Sons listing hopes. Is a re-rating on the cards? - livemint.com</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Aishwarya Rai Bachchan celebrates Rakhi with brother Aditya, Aaradhya and family, SIL shares rare pic - Social News XYZ</t>
+          <t>Afcons Infrastructure Share Price rises 12.68%: analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3073,68 +3073,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CEWATER.NS</t>
+          <t>BATLIBOI.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Concord Enviro Systems Limited</t>
+          <t>Batliboi Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>278</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>278</v>
+        <v>83.94000244140625</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>256.3999938964844</v>
+        <v>78.11000061035156</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>259.3500061035156</v>
+        <v>80.15000152587891</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>276.1499938964844</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>259.3500061035156</v>
+        <v>80.15000152587891</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>95411</v>
+        <v>67396</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-6.08</v>
+        <v>-2.38</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Investors Aren't Entirely Convinced By Concord Enviro Systems Limited's (NSE:CEWATER) Earnings - simplywall.st</t>
+          <t>Batliboi Ltd. Share Price Today: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Concord Enviro Stock Rallies 9% After Subsidiary Bags ₹16 Cr Industrial ZLD Order - Trade Brains</t>
+          <t>Vedanta Iron &amp; Steel seeks approval for ESOP 2026, related party transactions - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>CONCORD ENVIRO SYSTEMS L Share Price - Upstox</t>
+          <t>Batliboi (BATLIBOI.NS) Quarterly Figures: The Company Publishes Its Latest Results in the Latest Reading; After Results: Shares Move Higher 0.54% in the Latest Reading - Earnings Call Highlights - siam.in</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Concord Enviro Systems Limited Announces Equity Shareholders Meeting for Scheme of Arrangement Approval - scanx.trade</t>
+          <t>Batliboi signs MOU to sell part of Surat land and buildings - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Declining Stock and Decent Financials: Is The Market Wrong About Concord Enviro Systems Limited (NSE:CEWATER)? - simplywall.st</t>
+          <t>Batliboi Consolidated June 2026 Net Sales at Rs 125.29 crore, up 80.15% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3142,56 +3142,56 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>KHAITANLTD.NS</t>
+          <t>PKTEA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Khaitan (India) Limited</t>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>159</v>
+        <v>931.9500122070312</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>159</v>
+        <v>936.9500122070312</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>145</v>
+        <v>900.0499877929688</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>149.3699951171875</v>
+        <v>915</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>158.9400024414062</v>
+        <v>936.9500122070312</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>149.3699951171875</v>
+        <v>915</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3814</v>
+        <v>1646</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-6.02</v>
+        <v>-2.34</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Khaitan (India) Rises 1% to ₹162.41; Range Between ₹154.29 and ₹170.53 Defines Near-Term Path — KHAITANLTD.NS - Volume Breakout Ideas - siam.in</t>
+          <t>PKTEA Share Price Fall: Price Action, Valuation and Sector - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Khaitan India accepts resignation of company secretary Chandranath Banerjee - scanx.trade</t>
+          <t>PKTEA Share Price Fall: Price Action, Valuation and Sector - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Khaitan India schedules 89th AGM for September 25, 2026 - scanx.trade</t>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Khaitan India accepts resignation of company secretary Chandranath Banerjee - scanx.trade</t>
+          <t>Peria Karamalai Tea PKTEA Record Date FY26 Dividend AGM - Kalkine India</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3207,68 +3207,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MUKKA.NS</t>
+          <t>OIL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins Limited</t>
+          <t>Oil India Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.10000038146973</v>
+        <v>485</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>31.30999946594238</v>
+        <v>491</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>29.26000022888184</v>
+        <v>477</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>29.53000068664551</v>
+        <v>477.1000061035156</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>31.38999938964844</v>
+        <v>487.6000061035156</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>29.53000068664551</v>
+        <v>477.1000061035156</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1355101</v>
+        <v>573096</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.93</v>
+        <v>-2.15</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins Ltd Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>Indian shares rise on bargain buying, Fed, oil cap gains - Reuters</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins to host virtual investor meet with ADD Capital - scanx.trade</t>
+          <t>European shares rise as oil slips, yields stall By Reuters - Investing.com</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins Completes 100% Acquisition of Haris Marine Products Subsidiary - scanx.trade</t>
+          <t>Oil (USCrude) Price Forecast for Today, Tomorrow, Next Week, and Next 30 Days - LiteFinance</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins Share Price Gains as MUKKA Trades Higher - Univest</t>
+          <t>European shares rise as oil slips, yields stall By Reuters - Investing.com</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins to host virtual investor meet with ADD Capital - scanx.trade</t>
+          <t>Indian shares rise on bargain buying, Fed, oil cap gains - TradingView</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:39:40 IST</t>
+          <t>2026-09-17 13:23:03 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3276,51 +3276,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>GTECJAINX.NS</t>
+          <t>GUJENERGY.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>G-TEC JAINX EDUCATION LIMITED</t>
+          <t>GUJARAT ENERGY LIMITED</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>28.29999923706055</v>
+        <v>244.3999938964844</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>29</v>
+        <v>245.4499969482422</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>27.11000061035156</v>
+        <v>237.6100006103516</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>27.61000061035156</v>
+        <v>239.0500030517578</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>29.30999946594238</v>
+        <v>244.2400054931641</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>27.61000061035156</v>
+        <v>239.0500030517578</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5433</v>
+        <v>668547</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.8</v>
+        <v>-2.12</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>G-TEC (GTECJAINX.NS): Records a 3.85% Decrease to ₹28.50; Support at ₹27.07 and Resistance at ₹29.93 Frame the Range in the Current Update - Low Volume Node - siam.in</t>
+          <t>Gujarat Gas Share Price Up 2.36%: Price, Valuation View - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>G-TEC (GTECJAINX.NS): Records a 3.85% Decrease to ₹28.50; Support at ₹27.07 and Resistance at ₹29.93 Frame the Range in the Current Update - Low Volume Node - siam.in</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Gujarat Energy Limited Appoints Dhirubhai Shah &amp; Co. LLP as Statutory Auditors - PSU Connect</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Energy schedules 14th AGM for September 29, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Energy EVP Yogiraj Navathe retires on August 29 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Energy Limited Appoints Dhirubhai Shah &amp; Co. LLP as Statutory Auditors - PSU Connect</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>ASTAR.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Limited</t>
+          <t>Asian Star Company Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.44999980926514</v>
+        <v>598</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.88000011444092</v>
+        <v>672.7999877929688</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14.43000030517578</v>
+        <v>597.9500122070312</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>15.86999988555908</v>
+        <v>672.7999877929688</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14.4399995803833</v>
+        <v>560.7000122070312</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15.86999988555908</v>
+        <v>672.7999877929688</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7301628</v>
+        <v>1394</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>9.9</v>
+        <v>19.99</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price Today: Price Fall and Valuation - Univest</t>
+          <t>Astar Fi Opens Public Beta for Onchain Personal Finance Manager - TradingView</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price Today: Price Fall and Valuation - Univest</t>
+          <t>7 Stocks That Hit 20% Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price and Daily Chart View - Kalkine India</t>
+          <t>Asian Star Company Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price Fall Streak With Fresh Weakness - Univest</t>
+          <t>Asian (ASTAR.NS) Quarter in Focus: The Company Publishes Its Latest Results; After Results: The Market Price Moves 1.60% Higher in Latest Trading - Low Estimate Range - siam.in</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech NSE:ATALREAL Board Meeting Outcome September 2026 - Kalkine India</t>
+          <t>Digital Assets: From Cryptocurrencies to Meme Coins - Page 134 - Yellow.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,64 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MOTISONS.NS</t>
+          <t>SBGLP.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers Limited</t>
+          <t>Suratwwala Business Group Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16.3700008392334</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>18.5</v>
+        <v>25.78000068664551</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>16.20000076293945</v>
+        <v>22.98999977111816</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>18.02000045776367</v>
+        <v>25.78000068664551</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16.6200008392334</v>
+        <v>21.48999977111816</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18.02000045776367</v>
+        <v>25.78000068664551</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>195683084</v>
+        <v>684802</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>8.42</v>
+        <v>19.96</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers to consider redemption of 50 lakh preference shares - scanx.trade</t>
+          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers to consider redemption of 50 lakh preference shares - scanx.trade</t>
+          <t>SBGLP Technical Setup After Recent Decline - Kalkine India</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers Share Price Today: Price Rise Review - Univest</t>
+          <t>Suratwwala Business Group Share Price Today: 11.04% Gain - Univest</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Motisons (MOTISONS.NS) Range: Finishes 1.03% Down at ₹16.29 at the Close; Market Levels: Traders Can Monitor the ₹15.48-₹17.10 Range under the Current Snapshot - Buyback Factor - siam.in</t>
-        </is>
-      </c>
+          <t>SBGLP Technical Setup After Recent Decline - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +687,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>OPTIFIN.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Limited</t>
+          <t>Optimus Finance Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1513.5</v>
+        <v>13.02000045776367</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1658</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1513.5</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1638</v>
+        <v>15.13000011444092</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1511.199951171875</v>
+        <v>13.28999996185303</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1638</v>
+        <v>15.13000011444092</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>7953634</v>
+        <v>64843</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>13.84</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology soars 9%, up 125% in 2026; what's driving EMS stock? - Business Standard</t>
+          <t>Optimus Finance appoints Kheradia as director, new auditor - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>SEMICON India 2026: Syrma SGS, Dixon Tech, Kaynes Technology, Moschip Technologies shares rise up to 10% - Business Today</t>
+          <t>Optimus Finance appoints Kheradia as director, new auditor - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS, Kaynes Tech, Dixon Shares Rally: Semiconductor Stocks In Focus As SEMICON India Begins - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>SEMICON India 2026: Syrma SGS, Dixon Tech, Kaynes Technology, Moschip Technologies shares rise up to 10% - Business Today</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>SEMICON India 2026: Syrma, Tata Tech, Tata Elxsi, MosChip shares jump up to 10%; here is why - Upstox</t>
-        </is>
-      </c>
+          <t>Optimus Finance Ltd. (OPTIFIN) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +748,56 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AEROENTER.NS</t>
+          <t>KNAGRI.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Enterprises Limited</t>
+          <t>KN Agri Resources Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>113.3499984741211</v>
+        <v>180.0800018310547</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>123.3899993896484</v>
+        <v>205</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>112.1999969482422</v>
+        <v>180.0800018310547</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>122.6800003051758</v>
+        <v>202.2400054931641</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>113.3499984741211</v>
+        <v>180.25</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>122.6800003051758</v>
+        <v>202.2400054931641</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1290618</v>
+        <v>17508</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>8.23</v>
+        <v>12.2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Sat Industries Share Price up 8.25%: fundamentals and peers - Univest</t>
+          <t>KN (KNAGRI.NS) Results Breakdown: The Latest Report Adds New Financial Reference Points at the Close; Price Move: The Share Price Sheds 1.44% for the Current Session - Buyback Announcement Report - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Sat Industries Share Price up 8.25%: fundamentals and peers - Univest</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Aeroflex Enterprises Share Price and Technical View - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Sat Industries Ltd. Share Price News and Price Action Today - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Sat Industries Share Price Rises 8.5%: Market Cap, Valuation - Univest</t>
-        </is>
-      </c>
+          <t>KN (KNAGRI.NS) Results Breakdown: The Latest Report Adds New Financial Reference Points at the Close; Price Move: The Share Price Sheds 1.44% for the Current Session - Buyback Announcement Report - siam.in</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,56 +805,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AHCL.NS</t>
+          <t>TEGA.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Limited</t>
+          <t>Tega Industries Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.70000076293945</v>
+        <v>1699.099975585938</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>21.79000091552734</v>
+        <v>1944</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19.70000076293945</v>
+        <v>1699</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>21.54000091552734</v>
+        <v>1920</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.04000091552734</v>
+        <v>1717.099975585938</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21.54000091552734</v>
+        <v>1920</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>30345125</v>
+        <v>3909408</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>7.49</v>
+        <v>11.82</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
+          <t>Tega Industries Share Price rises 5.01%: valuation, peers - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Tega Industries Share Price rises 5.01%: valuation, peers - Univest</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Tega Industries Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Tega Industries Limited (NSE:TEGA) Stock Goes Ex-Dividend In Just Three Days - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Tega Industries sets ₹1,994 per share price for preferential equity issue - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,68 +874,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER.NS</t>
+          <t>SHAREINDIA.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Limited</t>
+          <t>Share India Securities Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>287.75</v>
+        <v>199</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>322</v>
+        <v>219.9499969482422</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>284.75</v>
+        <v>196.1999969482422</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>307.3999938964844</v>
+        <v>218.4400024414062</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>286.75</v>
+        <v>196.0500030517578</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>307.3999938964844</v>
+        <v>218.4400024414062</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>16595283</v>
+        <v>28920933</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>7.2</v>
+        <v>11.42</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Press Release Distribution India - Business Wire India</t>
+          <t>Share India Securities Share Price Today: Key Price Rise - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Publishes Rights Issue Allotment Details in Newspapers - TipRanks</t>
+          <t>Share India Securities Share Price Near Peak, Sector View - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering approves capital increase and director appointment - scanx.trade</t>
+          <t>Share India Securities Ltd. (SHAREINDIA): Share India Securities Share Price hits fresh 52-week high at Rs 207.15 - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Share India Securities jumps 12% to 52-week high, up 24% in just 2 sessions- What is driving the stock price? - TradingView</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Board Approves 1.25 Crore Shares Rights Issue At ₹264 Totaling ₹330 Crore - Sahi</t>
+          <t>Share India Securities Share Price Near Peak, Sector View - Univest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,68 +943,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE.NS</t>
+          <t>RMC.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Limited</t>
+          <t>RMC Switchgears Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>365</v>
+        <v>207.3500061035156</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>395.5</v>
+        <v>239.8999938964844</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>350</v>
+        <v>206.4100036621094</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>389.3500061035156</v>
+        <v>229.1600036621094</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>363.7000122070312</v>
+        <v>206.4100036621094</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>389.3500061035156</v>
+        <v>229.1600036621094</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1922166</v>
+        <v>171578</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>7.05</v>
+        <v>11.02</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE Share Price Rises 9.05%: Price Action, Valuation - Univest</t>
+          <t>RMC Switchgears Receives ₹14.98 Crore Solar Pump Order From MSEDCL; Shares Fall 2.88% - HDFC Sky</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Biopharma Authorizes Reverse Stock Split of Up to 1-for-20 - Minichart</t>
+          <t>RMC Switchgears appoints Tarun Kumar Sharma as COO effective Sep 16 - scanx.trade</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+          <t>RMC Switchgears Applies for NSE Mainboard Migration After BSE Approval - scanx.trade</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>An oral drug candidate suppressed lung virus in infected mice - Stock Titan</t>
+          <t>RMC Switchgears Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE PICTURES LIMITED Share Price - Live NSE: SUNSHINE Stock Price &amp; Chart - Upstox</t>
+          <t>RMC Switchgears appoints Tarun Kumar Sharma as COO effective Sep 16 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1024,56 +1012,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HBLENGINE.NS</t>
+          <t>TREL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>HBL Engineering Limited</t>
+          <t>Transindia Real Estate Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>710.7999877929688</v>
+        <v>27.03000068664551</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>754.5499877929688</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>707.7000122070312</v>
+        <v>26.52000045776367</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>753.1500244140625</v>
+        <v>29.77000045776367</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>704.6500244140625</v>
+        <v>27.03000068664551</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>753.1500244140625</v>
+        <v>29.77000045776367</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>5649210</v>
+        <v>725801</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6.88</v>
+        <v>10.14</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Should You Buy HBL Engineering Limited (NSE:HBLENGINE) For Its Upcoming Dividend? - simplywall.st</t>
+          <t>TREL Share Price Today: rise, valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Should You Buy HBL Engineering Limited (NSE:HBLENGINE) For Its Upcoming Dividend? - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>TREL Share Price Today: rise, valuation and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Transindia Real Estate completes acquisition of 48.28% stake in Comptech Solutions for ₹24 cr - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Should You Think About Buying Trelleborg AB (publ) (STO:TREL B) Now? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Trelleborg steps up share buybacks to refine capital structure - The Globe and Mail</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1081,68 +1081,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KMCSHIL.NS</t>
+          <t>VENUSPIPES.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>K M C Speciality Hospitals (India) Limited</t>
+          <t>Venus Pipes &amp; Tubes Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>146.9199981689453</v>
+        <v>1954</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>160.3899993896484</v>
+        <v>2160</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>144.4700012207031</v>
+        <v>1941.199951171875</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>156.5599975585938</v>
+        <v>2131.699951171875</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>146.9299926757812</v>
+        <v>1938.099975585938</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>156.5599975585938</v>
+        <v>2131.699951171875</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>4766322</v>
+        <v>1292804</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.55</v>
+        <v>9.99</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals Share Price: price rise, valuation - Univest</t>
+          <t>If EPS Growth Is Important To You, Venus Pipes and Tubes (NSE:VENUSPIPES) Presents An Opportunity - simplywall.st</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals Share Price: Price Action and Peers - Univest</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-17 — cnbctv:df8bdb20b094b:0 - TradingView</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals (India) Ltd (KMCSHIL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>Venus Pipes &amp; Tubes Share Price live: latest stock news - Univest</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals Share Price: Price Action and Peers - Univest</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-17 — cnbctv:df8bdb20b094b:0 - TradingView</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>KMC Speciality Hospitals Share Price today near 52-week peak - Univest</t>
+          <t>Venus Pipes &amp; Tubes Share Price: Price Action at Yearly High - Univest</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1150,60 +1150,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE.NS</t>
+          <t>QUINT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited</t>
+          <t>Quint Digital Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>490</v>
+        <v>63.65999984741211</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>534.3499755859375</v>
+        <v>63.65999984741211</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>484</v>
+        <v>63.65999984741211</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>523</v>
+        <v>63.65999984741211</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>491.9500122070312</v>
+        <v>57.88000106811523</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>523</v>
+        <v>63.65999984741211</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1681591</v>
+        <v>216505</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.31</v>
+        <v>9.99</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
+          <t>Quint Digital Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
+          <t>Quint Digital Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Quint Digital CCPS and warrants begin BSE trading on Sep 18 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Quint Digital Share Price Today Near Yearly High | QUINT - Univest</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Quint Digital Stock Enters New Momentum Phase - Kalkine India</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1211,68 +1219,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CSM.NS</t>
+          <t>TTL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Limited</t>
+          <t>T T Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>98.90000152587891</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>103.5999984741211</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>96.31999969482422</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>101.7799987792969</v>
+        <v>7.070000171661377</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>96.22000122070312</v>
+        <v>6.429999828338623</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>101.7799987792969</v>
+        <v>7.070000171661377</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1345357</v>
+        <v>626276</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.78</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
+          <t>T T Brands acquires 98,101 shares; promoter stake rises to 35.06% - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
+          <t>T T Limited Promoter Group Raises Stake Through Open-Market Share Purchase - TipRanks</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+          <t>TTL Enterprises Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>How (CSM) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
+          <t>TTL Enterprises board approves Ardent Ventures promoter reclassification - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>CSM Share Price Today Falls: P/E, P/B and Sector Context - Univest</t>
+          <t>TTL Enterprises approves AGM, appoints new statutory auditor - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1280,68 +1288,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ARIS.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Arisinfra Solutions Limited</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>116.5400009155273</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>124.8000030517578</v>
+        <v>15.88000011444092</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>116.5400009155273</v>
+        <v>14.43000030517578</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>123.2399978637695</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>116.5299987792969</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>123.2399978637695</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1695350</v>
+        <v>11327698</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.76</v>
+        <v>9.9</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Aris Mining Corp (ARIS) Shares Fall 3.6% -- What GF Score of 69 Tells Investors - GuruFocus</t>
+          <t>Atal Realtech Share Price News: Rs 15.69 After 8.73% Gain - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>When the Price of (ARIS.WT.A) Talks, People Listen (ARIS.WT.A:CA) - Stock Traders Daily</t>
+          <t>Atal Realtech Share Price News: Rs 15.69 After 8.73% Gain - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Aris Mining (TSX:ARIS) Stock Looks Fairly Valued After A Very Large Run - Yahoo Finance</t>
+          <t>Atal Realtech Share Price Today: Price Fall and Valuation - Univest</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>When the Price of (ARIS.WT.A) Talks, People Listen (ARIS.WT.A:CA) - Stock Traders Daily</t>
+          <t>Atal Realtech Share Price and Daily Chart View - Kalkine India</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Aris Mining Corporation (ARIS) Stock Price | Live Quotes &amp; Charts | NYSE - StocksToTrade</t>
+          <t>Atal Realtech NSE:ATALREAL Board Meeting Outcome September 2026 - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1349,60 +1357,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM.NS</t>
+          <t>GEEKAYWIRE.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Organic Industries Limited</t>
+          <t>Geekay Wires Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>170.3500061035156</v>
+        <v>31.20000076293945</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>183.8999938964844</v>
+        <v>34</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>170.3500061035156</v>
+        <v>30.40999984741211</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>181.2400054931641</v>
+        <v>33.45999908447266</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>171.7299957275391</v>
+        <v>30.55999946594238</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>181.2400054931641</v>
+        <v>33.45999908447266</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2087931</v>
+        <v>955396</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.54</v>
+        <v>9.49</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Laxmi (LXCHEM.NS) Earnings Numbers in Focus: The Company Reports Its Latest Available Figures; Market Read: Shares Finish 0.07% Lower - ROA Comparison - siam.in</t>
+          <t>Geekay Wires Limited (GEEKAYWIRE.NS) Slips 1.57%: Testing Support Levels Amid Market Headwinds - PCR Divergence - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Organic Industries Limited Announces the Resignation of Dr. Rajan Venkatesh as Chief Executive Officer, Effective November 13, 2026 - marketscreener.com</t>
+          <t>Geekay Wires Q1 Results: Net profit falls 20% YoY to ₹5.77 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Organic Industries Limited Announces the Resignation of Dr. Rajan Venkatesh as Chief Executive Officer, Effective November 13, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Geekay Wires Falls 50% Post Stock Split; Trades Ex-Split at ₹34 - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Geekay Wires Q1 Results: Net profit falls 20% YoY to ₹5.77 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Geekay Wires Limited (NSE:GEEKAYWIRE) Screens Well But There Might Be A Catch - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1410,68 +1426,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>AEROFLEX.NS</t>
+          <t>AHCL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>483.1000061035156</v>
+        <v>19.70000076293945</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>512.0999755859375</v>
+        <v>22.36000061035156</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>483.1000061035156</v>
+        <v>19.70000076293945</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>507.5</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>481.1000061035156</v>
+        <v>20.04000091552734</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>507.5</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1648601</v>
+        <v>49724010</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5.49</v>
+        <v>8.98</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Share Price today: key market update - Univest</t>
+          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Share Price today: key market update - Univest</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Aeroflex Industries Ltd Hits Intraday Low Amid Price Pressure on 15 Sep 2026 - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Aeroflex Enterprises Share Price and Technical View - Kalkine India</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Aeroflex Industries Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
-        </is>
-      </c>
+          <t>17,369,700 Equity Shares of Anlon Healthcare Limited are subject to a Lock-Up Agreement Ending on 3-SEP-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1479,68 +1483,60 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE.NS</t>
+          <t>CUBEXTUB.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Limited</t>
+          <t>Cubex Tubings Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>532.9000244140625</v>
+        <v>74.59999847412109</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>560.5499877929688</v>
+        <v>84.90000152587891</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>529.9500122070312</v>
+        <v>74.59999847412109</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>558.4500122070312</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>530.2000122070312</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>558.4500122070312</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>5741713</v>
+        <v>244471</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE Outlook for the Week - Equitypandit</t>
+          <t>Cubex Tubings to consider raising funds via convertible debt - scanx.trade</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>HDFC Life share price rises on IRDAI commission cut report - Business Upturn</t>
+          <t>Cubex Tubings to consider raising funds via convertible debt - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>HDFC Life Share Price Today (HDFCLIFE) | Live Chart, News &amp; Stock Market - TechGraph</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>HDFC (HDFCLIFE.NS) Results Versus Estimates: The Company Publishes Its Latest Results in the Latest Reading; Latest Reaction: Shares Move 1.13% Lower in the Current Update - Strong Earnings Momentum - siam.in</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>HDFC Life Share Price Today: Fall, Valuation, Sector View - Univest</t>
-        </is>
-      </c>
+          <t>Cubex (CUBEXTUB.NS) Results at a Glance: The Company Lists Its Latest Available Figures; Market Response: Shares Close 0.62% Higher in the Latest Session - Margin Improvement Report - siam.in</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1548,68 +1544,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ICICIPRULI.NS</t>
+          <t>DEEP.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Limited</t>
+          <t>Deep Polymers Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>470</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>496.8999938964844</v>
+        <v>49</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>468.75</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>494.8999938964844</v>
+        <v>47.22999954223633</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>470</v>
+        <v>43.47000122070312</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>494.8999938964844</v>
+        <v>47.22999954223633</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1918837</v>
+        <v>56971</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5.3</v>
+        <v>8.65</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>ICICIPRULI 52 Week Low Streak: Decline, valuation, peers - Univest</t>
+          <t>PM Modi shares Zoho Chief Scientist Sridhar Vembu’s article on India’s deep-tech growth - News On AIR</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Share Price rises 2.06% - Univest</t>
+          <t>Super Micro Computer (NASDAQ: SMCI) Stock Price Trades At Deep Discount Despite Explosive Growth Forecasts - foreignpolicyjournal.com</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life ESOP Allotment of 184,265 Shares - Kalkine India</t>
+          <t>PM Modi shares article highlighting India’s rapidly evolving deep-tech capabilities - DD India</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>ICICIPRULI Outlook for the Week - Equitypandit</t>
+          <t>Deep Yellow Shares Dip Today: What's Behind the Move - Kalkine</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Ltd. (ICICIPRULI) Share Price Hits Fresh 52-Week Low - Univest</t>
+          <t>Deep Source Holdings (SEHK:990) Shares Climbed, What Is Behind The Latest Move? - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1617,68 +1613,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>REFEX.NS</t>
+          <t>GNFC.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Refex Industries Limited</t>
+          <t>Gujarat Narmada Valley Fertilizers and Chemicals Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>259.3999938964844</v>
+        <v>540</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>277</v>
+        <v>599</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>259.3999938964844</v>
+        <v>538.2000122070312</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>274.6000061035156</v>
+        <v>584.8499755859375</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>260.8999938964844</v>
+        <v>539.75</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>274.6000061035156</v>
+        <v>584.8499755859375</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>371806</v>
+        <v>8250095</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5.25</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Refex Industries promoter pledges additional shares for personal use - scanx.trade</t>
+          <t>GNFC shares jump 11% after 50th annual meeting; here’s what investors should know - Upstox</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Refex Industries to host investor meet at Anand Rathi summit - scanx.trade</t>
+          <t>GNFC shareholders approve dividend, board changes at 50th AGM - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Refex promoter pledges 35 lakh shares for margin funding - scanx.trade</t>
+          <t>GNFC appoints Sanjeev Kumar as Managing Director; stock reacts - Business Today</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Refex Industries (REFEX.NS) Gains 2.36%: Stock Approaches Key Resistance Zone Near ₹311.69 - Analyst Upgrade Stocks - siam.in</t>
+          <t>GNFC shares surge 11% ahead of ₹21 dividend payment | Tap to know more | Inshorts - Inshorts</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Stocks to watch: Hindustan Copper, TCS, Refex Industries, Lenskart, Suzlon - Business Standard</t>
+          <t>GNFC shareholders approve dividend, board changes at 50th AGM - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1686,68 +1682,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>MOSCHIP.NS</t>
+          <t>SUNSHINE.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Moschip Technologies Limited</t>
+          <t>Sunshine Pictures Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>200</v>
+        <v>365</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>212.8000030517578</v>
+        <v>400.0499877929688</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>209.4100036621094</v>
+        <v>394</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>199.1600036621094</v>
+        <v>363.7000122070312</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>209.4100036621094</v>
+        <v>394</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3833688</v>
+        <v>2869177</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5.15</v>
+        <v>8.33</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SEMICON India 2026: Syrma, Tata Tech, Tata Elxsi, MosChip shares jump up to 10%; here is why - Upstox</t>
+          <t>SUNSHINE Share Price Rises 9.05%: Price Action, Valuation - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>SEMICON India 2026: Syrma SGS, Dixon Tech, Kaynes Technology, Moschip Technologies shares rise up to 10% - Business Today</t>
+          <t>Sunshine Biopharma Authorizes Reverse Stock Split of Up to 1-for-20 - Minichart</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>SEMICON India 2026: Syrma SGS, Dixon Tech, Kaynes Technology, Moschip Technologies shares rise up to 10% - Business Today</t>
+          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Moschip Technologies Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Sunshine Pictures shares list at 10% premium over IPO price - The Economic Times</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Moschip Technologies Slips 2.23% to ₹206.69 — Testing the Middle of Its Recent Range - Gap and Go - siam.in</t>
+          <t>Average basic shares outstanding of CHERISH SUNSHINE INTL LTD. – OTC:CHSIF - TradingView</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1755,60 +1751,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SEJALLTD.NS</t>
+          <t>MOTISONS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sejal Glass Limited</t>
+          <t>Motisons Jewellers Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>681.7000122070312</v>
+        <v>16.3700008392334</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>681.7000122070312</v>
+        <v>18.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>663</v>
+        <v>16.20000076293945</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>681.7000122070312</v>
+        <v>17.94000053405762</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>649.25</v>
+        <v>16.6200008392334</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>681.7000122070312</v>
+        <v>17.94000053405762</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>11601</v>
+        <v>236059587</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5</v>
+        <v>7.94</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Sejal (SEJALLTD.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points under the Current Snapshot; After Results: Shares Finish 0.16% Up for the Current Session - Revenue Guidance Update - siam.in</t>
+          <t>Motisons Jewellers to consider redemption of 50 lakh preference shares - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sejal Glass Jun 2026 Earnings: Positive EPS of ₹0.35 on Revenue of ₹36.43 Crore; Stock Slips Marginally - Low Estimate Range - siam.in</t>
+          <t>Motisons Jewellers sets Sept 28 AGM; appoints N.K. Aswani as auditor - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Sejal Glass Jun 2026 Earnings: Positive EPS of ₹0.35 on Revenue of ₹36.43 Crore; Stock Slips Marginally - Low Estimate Range - siam.in</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Motisons Jewellers Share Price Today: Price Rise Review - Univest</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Motisons (MOTISONS.NS) Range: Finishes 1.03% Down at ₹16.29 at the Close; Market Levels: Traders Can Monitor the ₹15.48-₹17.10 Range under the Current Snapshot - Buyback Factor - siam.in</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1816,59 +1820,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM.NS</t>
+          <t>AHLADA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Limited</t>
+          <t>Ahlada Engineers Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>173</v>
+        <v>36.79000091552734</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>182.1300048828125</v>
+        <v>40</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>173</v>
+        <v>36.0099983215332</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>182.1300048828125</v>
+        <v>39.33000183105469</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>173.4600067138672</v>
+        <v>36.56000137329102</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>182.1300048828125</v>
+        <v>39.33000183105469</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2309741</v>
+        <v>41709</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5</v>
+        <v>7.58</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
+          <t>Ahlada Engineers Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Share Price rise: fundamentals and peers - Univest</t>
+          <t>Ahlada Engineers (NSE:AHLADA): Orders, Margins and Working-Capital Outlook - Kalkine India</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Share Price news with valuation context - Univest</t>
+          <t>Ahlada (AHLADA.NS) Results at a Glance: The Company Releases Its Current Earnings Data in the Reported Period; Closing Reaction: The Stock Loses 0.35% in the Latest Session - Consensus Beat Rate - siam.in</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Share Price rise: fundamentals and peers - Univest</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Ahlada Engineers Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Q2 Results FY27: Date and Expectations - Univest</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1887,7 +1895,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1993,7 +2001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2001,68 +2009,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SIGACHI.NS</t>
+          <t>DUCON.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Limited</t>
+          <t>Ducon Infratechnologies Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27.57999992370605</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.23999977111816</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>27.57999992370605</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>28.93000030517578</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31.15999984741211</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>28.93000030517578</v>
+        <v>1.269999980926514</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>9338652</v>
+        <v>20267849</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-7.16</v>
+        <v>-19.62</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Ducon Infratechnologies rights issue shares listed on exchanges - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Orchasp Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Share Price Today: key stock analysis - Univest</t>
+          <t>Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares Balance Sheet – NSE:DUCON_RE1 - TradingView</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Ducon Infratechnologies Share Price Today: Stock Declines - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+          <t>Ducon Infratechnologies Ltd. - RE1 Share Price Live Today - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2070,68 +2078,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>LALITHAA.NS</t>
+          <t>ORCHASP.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Limited</t>
+          <t>Orchasp Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>295</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>299.7000122070312</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>290.3999938964844</v>
+        <v>1.350000023841858</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>290.3999938964844</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>305.6499938964844</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>290.3999938964844</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4985001</v>
+        <v>1331074</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-4.99</v>
+        <v>-14.38</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Shares Hit 5% Lower Circuit After Weak Q1 Results; Here's What Investors Should Know - Trade Brains</t>
+          <t>Orchasp Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Q1FY27 net profit falls 40% QoQ to ₹208 crore - scanx.trade</t>
+          <t>Orchasp Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Ltd. Share Price Live Today - CNBC TV18</t>
+          <t>Orchasp Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Q1FY27 net profit falls 40% QoQ to ₹208 crore - scanx.trade</t>
+          <t>Orchasp Limited (ORCHASP.NS) Steadies at ₹1.4 as Price Consolidates Between Key Support and Resistance - Triple MA Cross - siam.in</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Stocks to Watch Today: HDFC Bank, Lalithaa Jewellery, Horizon Industrial Parks, Solar Industries,... - Moneycontrol.com</t>
+          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2139,64 +2147,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GLFL.NS</t>
+          <t>AVONMORE.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing Limited</t>
+          <t>Avonmore Capital &amp; Management Services Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.349999904632568</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5.440000057220459</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5.090000152587891</v>
+        <v>11.76000022888184</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5.099999904632568</v>
+        <v>12.02000045776367</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5.349999904632568</v>
+        <v>13.0600004196167</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.099999904632568</v>
+        <v>12.02000045776367</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3278</v>
+        <v>703372</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-4.67</v>
+        <v>-7.96</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing Slips 2.19% to ₹5.8: Stock Hovers Near Crucial Support Zone - Dividend Stock Picks - siam.in</t>
+          <t>Avonmore promoter stake rises to 33.42% after open market buy - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing Limited (NSE:GLFL): Understanding Its Operati - Kalkine India</t>
+          <t>Avonmore Capital &amp; Management Services promoter adds 0.04% stake - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Lease Financing Limited (NSE:GLFL): Understanding Its Operati - Kalkine India</t>
+          <t>Avonmore Capital &amp; Management Services promoter buys 64,000 shares - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Competent Automobiles Company Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Avonmore Capital &amp; Management Services Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Avonmore Capital Share Price Rises 8.29% Today - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2204,68 +2216,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>TNPL.NS</t>
+          <t>MOHITE.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tamil Nadu Newsprint &amp; Papers Limited</t>
+          <t>Mohite Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>147.25</v>
+        <v>2.609999895095825</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>151</v>
+        <v>2.660000085830688</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>145.1499938964844</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>145.1699981689453</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>152.0899963378906</v>
+        <v>2.609999895095825</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>145.1699981689453</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>249532</v>
+        <v>105342</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-4.55</v>
+        <v>-6.51</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>TNPL shareholders approve R Kannan and N Venkatesh as directors - scanx.trade</t>
+          <t>Mohite Industries closes trading window from July 1 till Q1FY27 results - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>TNPL shareholders approve R Kannan and N Venkatesh as directors - scanx.trade</t>
+          <t>Mohite Industries sets Sept 30 AGM; e-voting opens Sept 27 - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Tamil Nadu Newsprint and Papers (NSE:TNPL) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
+          <t>Mohite Industries sets Sept 30 AGM; e-voting opens Sept 27 - scanx.trade</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Paper PSU Stock: TNPL Growth Analysis 2026 - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>TNPL files business responsibility and sustainability report for FY26 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Mohite Industries: Announces AGM Book Closure on Sep 24-30, 2026 - InvestyWise</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2273,60 +2281,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>JETFREIGHT.NS</t>
+          <t>ANNU.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Jet Freight Logistics Limited</t>
+          <t>Annu Projects Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.98999977111816</v>
+        <v>50.43000030517578</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20.17000007629395</v>
+        <v>51.97999954223633</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16.51000022888184</v>
+        <v>46.54999923706055</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>19.01000022888184</v>
+        <v>49.27999877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19.89999961853027</v>
+        <v>52.66999816894531</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19.01000022888184</v>
+        <v>49.27999877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>582225</v>
+        <v>2866894</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-4.47</v>
+        <v>-6.44</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Jet (JETFREIGHT.NS) EPS and Revenue: The Company Reports Its Latest Available Figures in the Available Record; Share Move: Shares Move Higher 0.76% in the Latest Reading - EPS Guidance Update - siam.in</t>
+          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Jet Freight Logistics sets Sept 23 AGM; seeks approval for ₹250 crore borrowing limit - scanx.trade</t>
+          <t>Longevity doctor reveals what matters most for aging well, beyond pricey biohacks - foxnews.com</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Jet Freight Logistics sets Sept 23 AGM; seeks approval for ₹250 crore borrowing limit - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Annu Projects stock ends 21-24% below ₹99-IPO price on debut day - BusinessLine</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>ANNU PROJECTS LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2334,68 +2350,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SHIVALIK.NS</t>
+          <t>SIGACHI.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Rasayan Limited</t>
+          <t>Sigachi Industries Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>389.1499938964844</v>
+        <v>27.57999992370605</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>399.8500061035156</v>
+        <v>31.23999977111816</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>373.5499877929688</v>
+        <v>27.57999992370605</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>374.7000122070312</v>
+        <v>29.32999992370605</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>389.1499938964844</v>
+        <v>31.15999984741211</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>374.7000122070312</v>
+        <v>29.32999992370605</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>80073</v>
+        <v>12940305</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-3.71</v>
+        <v>-5.87</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Rasayan surges 62% in two months after Fair Value signal - Investing.com India</t>
+          <t>Sigachi Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Rasayan surges 62% in two months after Fair Value signal - Investing.com India</t>
+          <t>Sigachi Industries Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Rasayan Share Price: price action and valuation - Univest</t>
+          <t>Sigachi Industries Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Rasayan seeks approval for ₹33 crore preferential share and warrant issue - scanx.trade</t>
+          <t>Sigachi Industries Share Price Today: key stock analysis - Univest</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Shivalik Rasayan Ltd. Stock News - Value Research</t>
+          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2418,26 +2434,26 @@
         <v>7.579999923706055</v>
       </c>
       <c r="G8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>7.050000190734863</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>7.239999771118164</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>7.480000019073486</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.239999771118164</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>22914578</v>
+        <v>42661445</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-3.21</v>
+        <v>-5.75</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Alok Industries Ltd Share Price Today,, ALOKINDS Share Price NSE, BSE - Business Today</t>
+          <t>Mukesh Ambani's RIL-backed textile stock crash 21% in just 5 days - What's behind the plunge? Explained - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2447,24 +2463,24 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Mukesh Ambani's RIL-backed textile stock crash 21% in just 5 days - What's behind the plunge? Explained - TradingView</t>
+          <t>Alok Industries Share Price: fresh 52-week low, analysis - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Alok Industries Share Price: price action and fundamentals - Univest</t>
+          <t>RIL-backed Alok Industries shares hit fresh 52-week low; stock tumbles 53% in a year - Business Today</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Alok Industries Share Price: fresh 52-week low, analysis - Univest</t>
+          <t>Alok Industries 52 Week Low Streak Deepens On Weak Trade - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2472,68 +2488,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>POLICYBZR.NS</t>
+          <t>DNAMEDIA.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech Limited</t>
+          <t>Diligent Media Corporation Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1839</v>
+        <v>2.599999904632568</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1845</v>
+        <v>2.599999904632568</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1718.099975585938</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1772.599975585938</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1827.099975585938</v>
+        <v>2.450000047683716</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1772.599975585938</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4933749</v>
+        <v>124141</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-2.98</v>
+        <v>-5.71</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>PB (POLICYBZR.NS) Momentum: Finishes 2.75% Up at ₹1,847.70 in the Latest Session; Price Levels - siam.in</t>
+          <t>Diligent Media DNAMEDIA GST Show Cause Notice Disclosure - Kalkine India</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Raja Venkatraman recommends three stocks for 17 September - livemint.com</t>
+          <t>Diligent Media Publishes Notice on Dispatch of Revised FY25–26 Annual Report - TipRanks</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech Share Price Today: 2.93% Rise, Valuation View - Univest</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>PB Fintech Share Price Fall: Technicals, Valuation, Peers - Univest</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Raja Venkatraman recommends three stocks for 17 September - livemint.com</t>
-        </is>
-      </c>
+          <t>Diligent Media Publishes Notice on Dispatch of Revised FY25–26 Annual Report - TipRanks</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2541,68 +2549,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>HTEL.NS</t>
+          <t>TERAI.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Terai Tea Company Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>75.70999908447266</v>
+        <v>126.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>76.69999694824219</v>
+        <v>126.5299987792969</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>68.22000122070312</v>
+        <v>120</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>72.01000213623047</v>
+        <v>120</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>74.20999908447266</v>
+        <v>127.1600036621094</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>72.01000213623047</v>
+        <v>120</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2852418</v>
+        <v>1285</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-2.96</v>
+        <v>-5.63</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Free float of Terai Tea Co. Ltd. – NSE:TERAI - TradingView</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Jungle Revives Shares 2026-27 India Wildlife Safari and Golden Triangle Planning Insights - Digital Journal</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
+          <t>Terai Tea FY26 Results: Net profit surges 161% to ₹96 crore - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Free float of Hy-Tech Engineers Limited – NSE:HTEL - TradingView</t>
+          <t>Volume Gainers, August 21, 2026 at 3:00 PM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPO subscribed 131.68 times so far on Day 4: Check allotment date and steps - Upstox</t>
+          <t>Terai Tea appoints Rajendra Kanodia as WTD at 53rd AGM on Sep 30 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2610,68 +2618,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>STLSTRINF.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries Limited</t>
+          <t>Steel Strips Infrastructures Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9.439999580383301</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>9.979999542236328</v>
+        <v>27.79999923706055</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>9.310000419616699</v>
+        <v>25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.449999809265137</v>
+        <v>25.14999961853027</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>9.729999542236328</v>
+        <v>26.52000045776367</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9.449999809265137</v>
+        <v>25.14999961853027</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1207925</v>
+        <v>22406</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-2.88</v>
+        <v>-5.17</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries AGM Notice 2026: NSE:SUMEETINDS Filing - Kalkine India</t>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries Addresses NSE Queries and Defers Rights Issue Decision - TipRanks</t>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries submits Q1FY27 earnings call audio recording - scanx.trade</t>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Sumeet Industries announces ₹199.75 Cr rights issue to fund expansion - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Sumeet Industries Addresses NSE Queries and Defers Rights Issue Decision - TipRanks</t>
-        </is>
-      </c>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2679,68 +2683,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>KRN.NS</t>
+          <t>EASTWEST.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>KRN Heat Exchanger and Refrigeration Limited</t>
+          <t>East West Freight Carriers Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1430</v>
+        <v>2.349999904632568</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1453</v>
+        <v>2.349999904632568</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1386</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1400.699951171875</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1438.300048828125</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1400.699951171875</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>502213</v>
+        <v>156787</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-2.61</v>
+        <v>-5.15</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Paytm, KRN Heat Exchanger, Ather Energy, Vishal Mega Mart: Expert shares key entry levels, targets - BusinessToday - indiaipo.in</t>
+          <t>EastWest seeks P9 billion in first stock rights offer since 2015 - InsiderPH</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Paytm, KRN Heat Exchanger, Ather Energy, Vishal Mega Mart: Expert shares key entry levels, targets - BusinessToday - indiaipo.in</t>
+          <t>EastWest Bank prices P9-B stock rights offer - BusinessWorld - BusinessWorld Online</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>KRN Share Price Fall: Technical Setup and Sector Context - Univest</t>
+          <t>EastWest Bank looks to raise P9B from stock rights offering - BusinessWorld - BusinessWorld Online</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>KRN Heat Exchanger and Refrigeration Ltd leads losers in 'A' group - Business Standard</t>
+          <t>EastWest sets P9-billion capital raising push - Inquirer.net</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>KRN Heat Exchanger and Refrigeration Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>EastWest eyes P9 billion stock rights offer - Philstar.com</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2748,60 +2752,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AQYLON.NS</t>
+          <t>SHIVALIK.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus Limited</t>
+          <t>Shivalik Rasayan Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>20.45000076293945</v>
+        <v>389.1499938964844</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>20.45000076293945</v>
+        <v>399.8500061035156</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>19.13999938964844</v>
+        <v>367.2000122070312</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>19.20000076293945</v>
+        <v>369.2999877929688</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>19.70999908447266</v>
+        <v>389.1499938964844</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>19.20000076293945</v>
+        <v>369.2999877929688</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>304802</v>
+        <v>112649</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-2.59</v>
+        <v>-5.1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus promoter Kurjibhai Rupareliya sells 1.36% stake in open market - scanx.trade</t>
+          <t>Shivalik Rasayan surges 62% in two months after Fair Value signal - Investing.com India</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus promoter Kurjibhai Rupareliya sells 1.36% stake in open market - scanx.trade</t>
+          <t>Shivalik Rasayan surges 62% in two months after Fair Value signal - Investing.com India</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Aqylon Nexus Promoter Sells 34.47 Lakh Shares - whalesbook.com</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Shivalik Rasayan Share Price: price action and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Shivalik Rasayan approves preferential allotment of shares and warrants - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Shivalik Rasayan Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2809,64 +2821,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO.NS</t>
+          <t>TECHNVISN.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Limited</t>
+          <t>TechNVision Ventures Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>822.2999877929688</v>
+        <v>4362</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>828.2000122070312</v>
+        <v>4576</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>788.7999877929688</v>
+        <v>4144</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>798.5499877929688</v>
+        <v>4144</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>819.0499877929688</v>
+        <v>4362</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>798.5499877929688</v>
+        <v>4144</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>697879</v>
+        <v>378</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-2.5</v>
+        <v>-5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Share Price Falls 8.25%: Full Analysis - Univest</t>
+          <t>TechNVision Ventures Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Newly listed MV Electrosystems shares soar 10%: Stock jumps from Rs.425 IPO price to Rs.848 - what's driving the rally? - TradingView</t>
+          <t>TechNVision Ventures Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
+          <t>TechNVision (TECHNVISN.NS) Chart: Closes Nearly Flat at ₹5,082.90 in Latest Trading; Key Range: Price Remains Between ₹4,828.75 Support and ₹5,337.05 Resistance for the Current Session - Aggressive Growth Picks - siam.in</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Newly listed MV Electrosystems shares soar 10%: Stock jumps from Rs.425 IPO price to Rs.848 - what's driving the rally? - TradingView</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>TechNVision Ventures Ltd. Share Price at fresh 52-week low - Univest</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>TechNVision Ventures Share Price: one-year low analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2874,68 +2890,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>MEESHO.NS</t>
+          <t>OSWALSEEDS.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Meesho Limited</t>
+          <t>ShreeOswal Seeds And Chemicals Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>213</v>
+        <v>14.80000019073486</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>213.0700073242188</v>
+        <v>14.96000003814697</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>207.9199981689453</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>207.9799957275391</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>213.2599945068359</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>207.9799957275391</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3970259</v>
+        <v>294062</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-2.48</v>
+        <v>-5</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Meesho Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Shree Oswal Seeds and Chemicals Share Price Analysis - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Meesho - Volume Shocker: MFs added 1 crore+ shares to 8 stocks in August '26; rally up to 30% - The Economic Times</t>
+          <t>Shree Oswal Seeds and Chemicals Share Price Analysis - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Meesho promoter confirms no encumbrance on shares in FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>SoftBank sells $186M Meesho stake in block deal - Dealroom</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>CAM Advises JP Morgan On Sale Of Meesho Limited's Equity Shares - LawBeat</t>
-        </is>
-      </c>
+          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2943,51 +2951,51 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KWIL.NS</t>
+          <t>NIRAJISPAT.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (India) Limited</t>
+          <t>Niraj Ispat Industries Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41.34999847412109</v>
+        <v>300</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>41.79000091552734</v>
+        <v>300</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40.25</v>
+        <v>285</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>285</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>41.31999969482422</v>
+        <v>300</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>40.29999923706055</v>
+        <v>285</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>5862240</v>
+        <v>103</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-2.47</v>
+        <v>-5</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Kwality (KWIL.NS) Results Review: The Report Supplies Updated Headline Figures in Latest Trading; Share Response: The Stock Ends Down 2.96% in the Available Record - Revenue Per Share - siam.in</t>
+          <t>Niraj (NIRAJISPAT.NS) Price Update: Ends Down by 3.00% at ₹205.65 for the Current Session - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Kwality (KWIL.NS) Results Review: The Report Supplies Updated Headline Figures in Latest Trading; Share Response: The Stock Ends Down 2.96% in the Available Record - Revenue Per Share - siam.in</t>
+          <t>Niraj (NIRAJISPAT.NS) Session: Finishes Nearly Flat at ₹216.00; Levels: the ₹205.20 to ₹226.80 Range Remains in Focus in the Available Record - PSAR Stop - siam.in</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities, August 21, 2026 at 3:00 PM IST - HDFC Sky</t>
+          <t>Niraj (NIRAJISPAT.NS) Session: Finishes Nearly Flat at ₹216.00; Levels: the ₹205.20 to ₹226.80 Range Remains in Focus in the Available Record - PSAR Stop - siam.in</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -2996,7 +3004,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3004,68 +3012,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AFCONS.NS</t>
+          <t>MAHASTEEL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Afcons Infrastructure Limited</t>
+          <t>Mahamaya Steel Industries Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>256.6000061035156</v>
+        <v>1250</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>258.7000122070312</v>
+        <v>1250</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>243.5</v>
+        <v>1201.900024414062</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>252.1499938964844</v>
+        <v>1201.900024414062</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>258.3999938964844</v>
+        <v>1265.099975585938</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>252.1499938964844</v>
+        <v>1201.900024414062</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2072763</v>
+        <v>1144</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-2.42</v>
+        <v>-5</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>AFCONS INFRASTRUCTURE LTD Share Price - Upstox</t>
+          <t>Mahamaya Steel Industries Ltd. Lower Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Nifty Smallcap 100 extends fall for 5th day; Afcons, FSL skid up to 14% - Business Standard</t>
+          <t>Mahamaya Steel Industries Ltd. Lower Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Shapoorji Pallonji Group stocks zoom 20% as RBI asks Tata Sons to list - Business Standard</t>
+          <t>Mahamaya (MAHASTEEL.NS) Session: Rises 0.99% to ₹1,187.30 at the Close; Boundary Watch: Price Remains Between ₹1,127.93 Support and ₹1,246.66 Resistance in the Latest Reading - Cash Secured Put - siam.in</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Afcons Infra stock surges on Tata Sons listing hopes. Is a re-rating on the cards? - livemint.com</t>
+          <t>Mahamaya Steel Industries Limited Reports Sales Figures for August 2026 - EquityBulls</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Afcons Infrastructure Share Price rises 12.68%: analysis - Univest</t>
+          <t>Mahamaya Steel Industries Share Price hits 52-week high - Univest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3073,68 +3081,56 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BATLIBOI.NS</t>
+          <t>ONIXSOLAR.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Batliboi Limited</t>
+          <t>Onix Solar Energy Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>83.09999847412109</v>
+        <v>376.2000122070312</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>83.94000244140625</v>
+        <v>376.2000122070312</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>78.11000061035156</v>
+        <v>376.2000122070312</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>80.15000152587891</v>
+        <v>376.2000122070312</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>82.09999847412109</v>
+        <v>395.9500122070312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>80.15000152587891</v>
+        <v>376.2000122070312</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>67396</v>
+        <v>7550</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-2.38</v>
+        <v>-4.99</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Batliboi Ltd. Share Price Today: Price Action and Valuation - Univest</t>
+          <t>Onix Solar Energy Ltd. (ONIXSOLAR) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Vedanta Iron &amp; Steel seeks approval for ESOP 2026, related party transactions - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Batliboi (BATLIBOI.NS) Quarterly Figures: The Company Publishes Its Latest Results in the Latest Reading; After Results: Shares Move Higher 0.54% in the Latest Reading - Earnings Call Highlights - siam.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Batliboi signs MOU to sell part of Surat land and buildings - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Batliboi Consolidated June 2026 Net Sales at Rs 125.29 crore, up 80.15% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Onix Solar Energy Ltd. (ONIXSOLAR) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3142,64 +3138,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PKTEA.NS</t>
+          <t>SETL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
+          <t>Standard Engineering Technology Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>931.9500122070312</v>
+        <v>409.9500122070312</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>936.9500122070312</v>
+        <v>422</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>900.0499877929688</v>
+        <v>401.4500122070312</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>915</v>
+        <v>401.4500122070312</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>936.9500122070312</v>
+        <v>422.5499877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>915</v>
+        <v>401.4500122070312</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1646</v>
+        <v>2841516</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-2.34</v>
+        <v>-4.99</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>PKTEA Share Price Fall: Price Action, Valuation and Sector - Univest</t>
+          <t>SETL Share Price News after yearly high and valuation check - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>PKTEA Share Price Fall: Price Action, Valuation and Sector - Univest</t>
+          <t>SETL Share Price News after yearly high and valuation check - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Peria Karamalai Tea PKTEA Record Date FY26 Dividend AGM - Kalkine India</t>
-        </is>
-      </c>
+          <t>SETL Share Price at fresh 52-week high with valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3207,68 +3199,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>OIL.NS</t>
+          <t>VISACHROME.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Oil India Limited</t>
+          <t>VISA Chrome Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>485</v>
+        <v>31.86000061035156</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>491</v>
+        <v>32.29999923706055</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>477</v>
+        <v>30.27000045776367</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>477.1000061035156</v>
+        <v>30.27000045776367</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>487.6000061035156</v>
+        <v>31.86000061035156</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>477.1000061035156</v>
+        <v>30.27000045776367</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>573096</v>
+        <v>99686</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-2.15</v>
+        <v>-4.99</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Indian shares rise on bargain buying, Fed, oil cap gains - Reuters</t>
+          <t>VISA Chrome Limited Auditor Raises 'Going Concern' Doubt - marketscreener.com</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>European shares rise as oil slips, yields stall By Reuters - Investing.com</t>
+          <t>VISA Chrome returns to profitability in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Oil (USCrude) Price Forecast for Today, Tomorrow, Next Week, and Next 30 Days - LiteFinance</t>
+          <t>Al Maha Investment Fund acquires 5.41% stake in Visa Chrome - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>European shares rise as oil slips, yields stall By Reuters - Investing.com</t>
+          <t>VISA Chrome returns to profitability in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Indian shares rise on bargain buying, Fed, oil cap gains - TradingView</t>
+          <t>ACRE revises Visa Chrome stake sale to 67.6 lakh shares - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:23:03 IST</t>
+          <t>2026-09-17 20:45:48 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3276,63 +3268,59 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>GUJENERGY.NS</t>
+          <t>RADHIKAJWE.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>GUJARAT ENERGY LIMITED</t>
+          <t>Radhika Jeweltech Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>244.3999938964844</v>
+        <v>68.12000274658203</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>245.4499969482422</v>
+        <v>68.12000274658203</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>237.6100006103516</v>
+        <v>68.12000274658203</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>239.0500030517578</v>
+        <v>68.12000274658203</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>244.2400054931641</v>
+        <v>71.69999694824219</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>239.0500030517578</v>
+        <v>68.12000274658203</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>668547</v>
+        <v>132578</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-2.12</v>
+        <v>-4.99</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Gas Share Price Up 2.36%: Price, Valuation View - Univest</t>
+          <t>Does Radhika Jeweltech (NSE:RADHIKAJWE) Deserve A Spot On Your Watchlist? - simplywall.st</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Energy Limited Appoints Dhirubhai Shah &amp; Co. LLP as Statutory Auditors - PSU Connect</t>
+          <t>Does Radhika Jeweltech (NSE:RADHIKAJWE) Deserve A Spot On Your Watchlist? - simplywall.st</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Energy schedules 14th AGM for September 29, 2026 - scanx.trade</t>
+          <t>Radhika Jeweltech Dips 2.6% to ₹68.5: Support and Resistance Levels in Spotlight - Wave Equality - siam.in</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Energy EVP Yogiraj Navathe retires on August 29 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Energy Limited Appoints Dhirubhai Shah &amp; Co. LLP as Statutory Auditors - PSU Connect</t>
-        </is>
-      </c>
+          <t>Radhika Jeweltech Files Tenth Annual Report for FY 2025-26 With Stock Exchanges - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SKYWAYS.NS</t>
+          <t>SVGLOBAL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services Limited</t>
+          <t>S V Global Mill Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>126.9000015258789</v>
+        <v>127.5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>135.3500061035156</v>
+        <v>153.9100036621094</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>122.5500030517578</v>
+        <v>126.4000015258789</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>128.3899993896484</v>
+        <v>147.9199981689453</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>117.9800033569336</v>
+        <v>128.2599945068359</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>128.3899993896484</v>
+        <v>147.9199981689453</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>73762224</v>
+        <v>6683</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8.82</v>
+        <v>15.33</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services shares rally 15% as Q1 profit jumps threefold YoY; interim dividend declared - Upstox</t>
+          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services shares rally 15% as Q1 profit jumps threefold YoY; interim dividend declared - Upstox</t>
+          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services shares surge 14.5% as Q1 PAT more than doubles - Business Standard</t>
+          <t>SV Global Mill Ltd. Share Price Fall and Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services share price surges 15% after Q1 results, dividend announcements | All details here - livemint.com</t>
+          <t>SV Global Mill Share Price falls 10.07% | Price analysis - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Recently listed Skyways Air shares jump nearly 15% today; here's why - Business Today</t>
+          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HTEL.NS</t>
+          <t>SAMBHV.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Sambhv Steel Tubes Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>73.75</v>
+        <v>129.0800018310547</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>79.37999725341797</v>
+        <v>150.9900054931641</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>71.26000213623047</v>
+        <v>129.0800018310547</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>78.12999725341797</v>
+        <v>147.5700073242188</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>72.05000305175781</v>
+        <v>129.0899963378906</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>78.12999725341797</v>
+        <v>147.5700073242188</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2979210</v>
+        <v>28285913</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>8.44</v>
+        <v>14.32</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Sambhv Steel Tubes Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Sambhv Steel Tubes Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Free float of Hy-Tech Engineers Limited – NSE:HTEL - TradingView</t>
+          <t>Sambhv Steel Tubes hosts Chrys Capital for Raipur plant visit - scanx.trade</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
+          <t>Here's Why Sambhv Steel Tubes (NSE:SAMBHV) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers IPO subscribed 131.68 times so far on Day 4: Check allotment date and steps - Upstox</t>
+          <t>Sambhv Steel Tubes clarifies ₹115 issue price for 8.7m FCEWs - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -703,39 +703,39 @@
         <v>442</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>477</v>
+        <v>480.7999877929688</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>437.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>469.1000061035156</v>
+        <v>476.7000122070312</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>435.2000122070312</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>469.1000061035156</v>
+        <v>476.7000122070312</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1413097</v>
+        <v>1960823</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7.79</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>Talbros Automotive Dips 1.79% to ₹401.35: Consolidation Phase Nears Key Support - Flat Correction - siam.in</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Talbros Automotive Publishes Addendum Notice for 69th AGM - TipRanks</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>Is It Smart To Buy Talbros Automotive Components Limited (NSE:TALBROAUTO) Before It Goes Ex-Dividend? - simplywall.st</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Talbros Automotive Publishes Addendum Notice for 69th AGM - TipRanks</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Talbros Automotive TALBROAUTO Investor Meet 28 Sept 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -756,68 +756,56 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AUGMONT.NS</t>
+          <t>CEWATER.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Augmont Enterprises Limited</t>
+          <t>Concord Enviro Systems Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>815</v>
+        <v>252.8000030517578</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>872</v>
+        <v>286</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>813</v>
+        <v>252.8000030517578</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>866.6500244140625</v>
+        <v>279.25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>811.0999755859375</v>
+        <v>256.5</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>866.6500244140625</v>
+        <v>279.25</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>566928</v>
+        <v>750844</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>6.85</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Augmont Enterprises Share Price Today, Augmont Enterprises Stock Price Live NSE/BSE Updates - The Economic Times</t>
+          <t>CEWATER Share Price Today: price rise, valuation and peers - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Augmont Enterprises Ltd (AUGMONT) Share Price - Business Today</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Augmont Enterprises Ltd (AUGMONT) Share Price - Business Today</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Augmont Enterprises Share Price: fresh 52-week low analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Augmont Enterprises shares make decent market debut at 22% premium over IPO price - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>CEWATER Share Price Today: price rise, valuation and peers - Univest</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -825,68 +813,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CSM.NS</t>
+          <t>CMRGREEN.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Limited</t>
+          <t>CMR Green Technologies Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>104</v>
+        <v>214.7899932861328</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>114.9000015258789</v>
+        <v>234.5800018310547</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>101.5</v>
+        <v>214.7899932861328</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>109.5999984741211</v>
+        <v>231.8699951171875</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>102.6399993896484</v>
+        <v>213.2599945068359</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>109.5999984741211</v>
+        <v>231.8699951171875</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3658512</v>
+        <v>1840718</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6.78</v>
+        <v>8.73</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>CSM Technologies Share Price news with sector comparison - Univest</t>
+          <t>CMR Green Technologies Ltd Share Price Today,, CMRGREEN Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Morton’s Stock, Washington’s Jaegle win CSM Fall Athletes of the Week - BVM Sports</t>
+          <t>CMR Green Technologies Reschedules 21st AGM, Publishes Nationwide Notice - TipRanks</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd leads losers in 'B' group - Business Standard</t>
+          <t>4,907,198 Equity Shares of CMR Green Technologies Limited are subject to a Lock-Up Agreement Ending on 5-SEP-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>How (CSM) Movements Inform Risk Allocation Models - Stock Traders Daily</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Understanding Momentum Shifts in (CSM) - Stock Traders Daily</t>
-        </is>
-      </c>
+          <t>CMR Green Technologies Reschedules 21st AGM, Publishes Nationwide Notice - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -894,64 +878,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>PBMPOLY.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Limited</t>
+          <t>PBM Polytex Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>980.8499755859375</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1051.800048828125</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>979</v>
+        <v>60.08000183105469</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1044.25</v>
+        <v>65</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>980.8499755859375</v>
+        <v>60</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1044.25</v>
+        <v>65</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2014237</v>
+        <v>146</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6.46</v>
+        <v>8.33</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Jyoti (JYOTICNC.NS) Trading: Closes 0.09% Lower at ₹949.75 on the Day; Current Setup: the Current Price Sits Inside the Supplied Technical Range in the Latest Reading - Composite Profile - siam.in</t>
+          <t>PBM Polytex Limited Submits Q4FY26 Regulation 74(5) Certificate to BSE - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Share Price Fall and Valuation View - Univest</t>
+          <t>PBM Polytex Ltd. (PBMPOLY) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Ltd. Share Price: Price Action View - Univest</t>
+          <t>Book value per share of PBM Polytex Ltd. – NSE:PBMPOLY - tradingview.com</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Share Price Fall and Valuation View - Univest</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>PBM Polytex Ltd. (PBMPOLY) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>PBM Polytex Reports Strong Q3FY26 Results with Net Profit of ₹232.26 Lakhs - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -959,56 +947,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PWL.NS</t>
+          <t>GUJAPOLLO.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Physicswallah Limited</t>
+          <t>Gujarat Apollo Industries Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>128</v>
+        <v>333.9500122070312</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>136.1699981689453</v>
+        <v>354.9500122070312</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>135.7599945068359</v>
+        <v>350.1000061035156</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>127.8000030517578</v>
+        <v>324</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>135.7599945068359</v>
+        <v>350.1000061035156</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>10233973</v>
+        <v>36321</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.23</v>
+        <v>8.06</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>PhysicsWallah block deal: Equity worth Rs 550 crore changes hands; stock climbs - Business Today</t>
+          <t>Gujarat Apollo Industries Advances 3% to ₹347.95; Key Hurdle at ₹365.35 - Early Entry Signals - siam.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>PhysicsWallah block deal: Equity worth Rs 550 crore changes hands; stock climbs - Business Today</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Gujarat Apollo Industries (NSE: GUJAPOLLO) Business Overview - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Apollo Industries (NSE: GUJAPOLLO) Business Overview - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Apollo Industries Holds Steady at ₹337.7; Key Resistance at ₹354.58 in Sight - Momentum ETF - siam.in</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat (GUJAPOLLO.NS) Earnings Reading: The Company Releases Its Current Earnings Data on the Day; Market Response: The Market Price Declines 1.27% in the Available Record - Revenue Breakdown Analysis - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1016,68 +1016,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER.NS</t>
+          <t>SHIVAAGRO.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Skipper Limited</t>
+          <t>Shiva Global Agro Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>537</v>
+        <v>39.88999938964844</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>566.5</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>532.0999755859375</v>
+        <v>37.15999984741211</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>565.2000122070312</v>
+        <v>41.79000091552734</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>532.5499877929688</v>
+        <v>38.70999908447266</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>565.2000122070312</v>
+        <v>41.79000091552734</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>979556</v>
+        <v>861</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6.13</v>
+        <v>7.96</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Skipper receives voluntary ESG score of 60 from risk agency - scanx.trade</t>
+          <t>Shiva Global Agro (NSE:SHIVAAGRO): Fertiliser Sector Basics - Kalkine India</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Skipper receives voluntary ESG score of 60 from risk agency - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Here's Why We Think Skipper (NSE:SKIPPER) Is Well Worth Watching - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Skipper Ltd. Share Price at fresh 52-week high; stock view - Univest</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Skipper Consolidated June 2026 Net Sales at Rs 1,309.83 crore, up 4.46% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Shiva Global Agro (NSE:SHIVAAGRO): Fertiliser Sector Basics - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1085,68 +1073,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR.NS</t>
+          <t>CAPILLARY.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>GMM Pfaudler Limited</t>
+          <t>Capillary Technologies India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1370</v>
+        <v>448.9500122070312</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1470</v>
+        <v>489</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1370</v>
+        <v>443.1000061035156</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1442.099975585938</v>
+        <v>484.0499877929688</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1363.400024414062</v>
+        <v>448.9500122070312</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1442.099975585938</v>
+        <v>484.0499877929688</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>881903</v>
+        <v>532692</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5.77</v>
+        <v>7.82</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>GMM Pfaudler (GMMPFAUDLR.NS) Slips 0.77% to ₹1,309 — Support and Resistance Levels in Focus - NAAIM Exposure - siam.in</t>
+          <t>Mirae Asset sells 175,842 Capillary Technologies shares in open market - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>CRISIL Reaffirms Credit Ratings for GMM Pfaudler Limited - EquityBulls</t>
+          <t>Mirae Asset sells 175,842 Capillary Technologies shares in open market - scanx.trade</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>GMM Pfaudler share price target: Buy rating, 39% upside - Check rationale behind recommendation by InCred Equities - livemint.com</t>
+          <t>Capillary Technologies India Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>GMM Pfaudler Share Price Near 52-Week High, Valuation View - Univest</t>
+          <t>Capillary (CAPILLARY.NS) Latest: Loses 0.08% to Close at ₹501.95 in Latest Trading; Range View: the Session Ends Within the Reported Technical Boundaries - Dealer Positioning - siam.in</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>GMM Pfaudler Share Price today up 5.13% on price action - Univest</t>
+          <t>CAPILLARY 52 Week Low Streak Deepens After Repeat Trough - Univest</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1154,68 +1142,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>PRECWIRE.NS</t>
+          <t>AUGMONT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires India Limited</t>
+          <t>Augmont Enterprises Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>450</v>
+        <v>815</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>488.8999938964844</v>
+        <v>884</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>448.5499877929688</v>
+        <v>813</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>474.6499938964844</v>
+        <v>874.3499755859375</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>449.25</v>
+        <v>811.0999755859375</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>474.6499938964844</v>
+        <v>874.3499755859375</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1582709</v>
+        <v>898791</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5.65</v>
+        <v>7.8</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires India Share Price Declines on Price Action - Univest</t>
+          <t>Augmont Enterprises Share Price Today, Augmont Enterprises Stock Price Live NSE/BSE Updates - The Economic Times</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires India Gains BSE, NSE Nod for Preferential CCD Issue - TipRanks</t>
+          <t>Augmont Enterprises Ltd (AUGMONT) Share Price - Business Today</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires India Share Price Rises 5.47%: Analysis - Univest</t>
+          <t>Augmont Enterprises Share Price: fresh 52-week low analysis - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires India Share Price hits fresh 52-week high - Univest</t>
+          <t>Augmont Enterprises Ltd (AUGMONT) Share Price - Business Today</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires India Gains BSE, NSE Nod for Preferential CCD Issue - TipRanks</t>
+          <t>Augmont Enterprises shares make decent market debut at 22% premium over IPO price - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1223,68 +1211,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>URBANCO.NS</t>
+          <t>FCL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Urban Company Limited</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>163.8899993896484</v>
+        <v>53.31000137329102</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>172</v>
+        <v>57.75</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>162.5500030517578</v>
+        <v>52.90000152587891</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>171.6100006103516</v>
+        <v>57.02000045776367</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>162.8099975585938</v>
+        <v>52.9900016784668</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>171.6100006103516</v>
+        <v>57.02000045776367</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>5845563</v>
+        <v>26160940</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.41</v>
+        <v>7.61</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>URBAN COMPANY LIMITED Share Price rise with sector context - Univest</t>
+          <t>FINEOS Corporation (ASX:FCL): What Investors Need to Know About This Insurance Software Stock - Kalkine</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>URBAN COMPANY LIMITED Share Price rise with sector context - Univest</t>
+          <t>FINEOS Corporation (ASX:FCL): What Investors Need to Know About This Insurance Software Stock - Kalkine</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>URBAN COMPANY Share Price today: price action and valuation - Univest</t>
+          <t>Fineotex Chemical Ltd. (FCL) Share Price hits fresh 52-week high as FCL trades at Rs 60.98 - Univest</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>ETFs Investing in Urban Company Limited Stocks - TradingView</t>
+          <t>Fineotex (FCL.NS) Earnings Snapshot: The Company Lists Its Latest Available Figures on the Day; Market Reaction: Shares Move Lower 1.69% for the Current Session - Margin Guidance - siam.in</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>URBAN COMPANY Share Price Today: Decline in Focus - Univest</t>
+          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - Kalkine</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1292,64 +1280,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM.NS</t>
+          <t>GMMPFAUDLR.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Limited</t>
+          <t>GMM Pfaudler Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>893.4500122070312</v>
+        <v>1370</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>945</v>
+        <v>1475</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>890</v>
+        <v>1370</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>940.4000244140625</v>
+        <v>1467</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>893.5</v>
+        <v>1363.400024414062</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>940.4000244140625</v>
+        <v>1467</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>307722</v>
+        <v>1207844</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.25</v>
+        <v>7.6</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Share Price: fresh 52-week high, fundamentals - Univest</t>
+          <t>GMM Pfaudler (GMMPFAUDLR.NS) Slips 0.77% to ₹1,309 — Support and Resistance Levels in Focus - NAAIM Exposure - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Plans Virtual Investor Meet With Citi on 15 September - TipRanks</t>
+          <t>CRISIL Reaffirms Credit Ratings for GMM Pfaudler Limited - EquityBulls</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Share Price: fresh 52-week high and valuation - Univest</t>
+          <t>GMM Pfaudler share price target: Buy rating, 39% upside - Check rationale behind recommendation by InCred Equities - livemint.com</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Cyient DLM Plans Virtual Investor Meet With Citi on 15 September - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>GMM Pfaudler Share Price Near 52-Week High, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>GMM Pfaudler Share Price today up 5.13% on price action - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1357,68 +1349,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM.NS</t>
+          <t>HLEGLAS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sudarshan Chemical Industries Limited</t>
+          <t>HLE Glascoat Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1203.800048828125</v>
+        <v>415.9500122070312</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1268.900024414062</v>
+        <v>457.2000122070312</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1199.400024414062</v>
+        <v>413</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1267.800048828125</v>
+        <v>446.8999938964844</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1205.400024414062</v>
+        <v>415.6499938964844</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1267.800048828125</v>
+        <v>446.8999938964844</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>130212</v>
+        <v>1020903</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.18</v>
+        <v>7.52</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Sudarshan Chemical (SUDARSCHEM.NS) Gains 3.32% to ₹1,262.30; Resistance at ₹1,325.41 in Focus - Iron Condor Alert - siam.in</t>
+          <t>HLE Glascoat Share Price rise: price action and P/E view - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sudarshan Chemical (SUDARSCHEM.NS) Gains 3.32% to ₹1,262.30; Resistance at ₹1,325.41 in Focus - Iron Condor Alert - siam.in</t>
+          <t>HLE Glascoat promoter Nilesh Patel gifts 10% stake to son Aalap - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Sudarshan Chemical ESOP Allotment: 8,781 Shares Issued in August 2026 - Kalkine India</t>
+          <t>HLE (HLEGLAS.NS) Latest Quarter: The Company Releases Its Current Earnings Data in the Latest Reading; Share Move: Shares Fall 0.28% at the Close - Margin Expansion Trends - siam.in</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Sudarshan Chemical Industries Share Price Today Gains 5.08% - Univest</t>
+          <t>HLE (HLEGLAS.NS) EPS and Revenue: The Latest Financial Metrics Are Now Available in the Reported Period; Market Reaction: The Stock Records a 1.74% Decrease in the Latest Reading - Consensus Forecast Report - siam.in</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Sudarshan Chemical Sells VP4 Frankfurt to Celanese to Refocus on Core Pigments - TipRanks</t>
+          <t>HLE Glascoat Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,68 +1418,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PNC.NS</t>
+          <t>WSTCSTPAPR.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Pritish Nandy Communications Limited</t>
+          <t>West Coast Paper Mills Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.02000045776367</v>
+        <v>716</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>17.88999938964844</v>
+        <v>772</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>16.02000045776367</v>
+        <v>713.9500122070312</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>17.48999977111816</v>
+        <v>768.2999877929688</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>16.6299991607666</v>
+        <v>716.4500122070312</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17.48999977111816</v>
+        <v>768.2999877929688</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>89211</v>
+        <v>592182</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5.17</v>
+        <v>7.24</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Stock Crash: PNC Infratech shares tank 20%, extend losses from 52-week high on this negative development - CNBC TV18</t>
+          <t>West Coast Paper Mills 52 Week High Streak Extends Again - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Mandatory PNC redemption shifts 851 shares at AXIA Energia (AXIAY) - Stock Titan</t>
+          <t>West Coast Paper Mills Share Price today after yearly high - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>PNC Infratech stock crashes 20%, hits lower circuit after three-year NHAI, MoRTH bidding ban - Moneycontrol.com</t>
+          <t>West (WSTCSTPAPR.NS) Snapshot: Moves 3.45% Up to ₹636.25 for the Current Session; Price Setup: Support at ₹604.44 and Resistance at ₹668.06 Frame the Range - Triple Bottom - siam.in</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>NHAI extends debarment to PNC Infratech; stock hits 52-week low - BusinessLine</t>
+          <t>West Coast Paper Mills Share Price: fresh 52-week high at Rs - Univest</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>PNC Infratech shares hit 20% lower circuit as NHAI extends Awadh Expressway debarment to company; all you need to know - Upstox</t>
+          <t>West Coast Paper Mills Share Price Today Near 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1495,68 +1487,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>VENUSPIPES.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>Venus Pipes &amp; Tubes Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>603.5499877929688</v>
+        <v>2123.10009765625</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>603.5499877929688</v>
+        <v>2309.10009765625</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>585.0999755859375</v>
+        <v>2120</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>603.5499877929688</v>
+        <v>2282.89990234375</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>574.8499755859375</v>
+        <v>2131.699951171875</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>603.5499877929688</v>
+        <v>2282.89990234375</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1280342</v>
+        <v>1274312</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.99</v>
+        <v>7.09</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Jewellery Stocks In Focus: TBZ, Thangamayil, PC Jeweller, Lalithaa Jewellery, Bluestone Surge Up To 5% - NDTV Profit</t>
+          <t>Venus Pipes &amp; Tubes Share Price live: latest stock news - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Jewellery Stocks In Focus: TBZ, Thangamayil, PC Jeweller, Lalithaa Jewellery, Bluestone Surge Up To 5% - NDTV Profit</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-17 — cnbctv:df8bdb20b094b:0 - tradingview.com</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>GRT Jewellers launches ₹431 crore open offer for remaining TBZ stake - BusinessLine</t>
+          <t>If EPS Growth Is Important To You, Venus Pipes and Tubes (NSE:VENUSPIPES) Presents An Opportunity - simplywall.st</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri share price today: TBZ stock on fire again - What's driving the bull run? - livemint.com</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-17 — cnbctv:df8bdb20b094b:0 - tradingview.com</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
+          <t>Venus Pipes &amp; Tubes Share Price: Price Action at Yearly High - Univest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1564,46 +1556,46 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>WAAREEINDO.NS</t>
+          <t>PWL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Indosolar Limited</t>
+          <t>Physicswallah Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>260.1000061035156</v>
+        <v>128</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>271.7000122070312</v>
+        <v>137.5</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>253.3000030517578</v>
+        <v>128</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>271.7000122070312</v>
+        <v>136.6000061035156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>258.7999877929688</v>
+        <v>127.8000030517578</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>271.7000122070312</v>
+        <v>136.6000061035156</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>199740</v>
+        <v>20005965</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.98</v>
+        <v>6.89</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Indosolar Limited Completes Disbursement of Fractional Share Proceeds Under NCLT Resolution Plan - scanx.trade</t>
+          <t>PhysicsWallah block deal: Equity worth Rs 550 crore changes hands; stock climbs - Business Today</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Indosolar Limited Completes Disbursement of Fractional Share Proceeds Under NCLT Resolution Plan - scanx.trade</t>
+          <t>PhysicsWallah block deal: Equity worth Rs 550 crore changes hands; stock climbs - Business Today</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
@@ -1613,7 +1605,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1621,68 +1613,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>HEG.NS</t>
+          <t>JSWINFRA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>HEG Limited</t>
+          <t>JSW Infrastructure Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>226.3000030517578</v>
+        <v>329.8999938964844</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>237.0500030517578</v>
+        <v>356.9500122070312</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>226.25</v>
+        <v>326.1000061035156</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>237.0500030517578</v>
+        <v>348.25</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>225.8000030517578</v>
+        <v>326.6499938964844</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>237.0500030517578</v>
+        <v>348.25</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>366851</v>
+        <v>25470641</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.98</v>
+        <v>6.61</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>HEG promoter group stake rises to 60.72% after scheme completion - scanx.trade</t>
+          <t>1,755,920,503 Equity Shares of JSW Infrastructure Limited are subject to a Lock-Up Agreement Ending on 18-SEP-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>HEG promoter group stake rises to 60.72% after scheme completion - scanx.trade</t>
+          <t>1,755,920,503 Equity Shares of JSW Infrastructure Limited are subject to a Lock-Up Agreement Ending on 18-SEP-2026. - marketscreener.com</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>HEG Share Price Falls 5% Intraday, Down 67% Since Demerger: What's Dragging The Stock? - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Why are HEG Ltd shares showing a fall of 63% in Monday's trade? - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
-        </is>
-      </c>
+          <t>JSW Infrastructure Share Price Falls: Price, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1690,68 +1674,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS.NS</t>
+          <t>UNOMINDA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems Limited</t>
+          <t>UNO Minda Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>726</v>
+        <v>1213.199951171875</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>761</v>
+        <v>1284</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>725.1500244140625</v>
+        <v>1206.800048828125</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>758</v>
+        <v>1284</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>722.0999755859375</v>
+        <v>1205</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>758</v>
+        <v>1284</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2026018</v>
+        <v>1277954</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.97</v>
+        <v>6.56</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
+          <t>UNO (UNOMINDA.NS) Earnings Update: Available Data Shows the Latest Reported Performance for This Review; Share Response: The Stock Loses 1.28% in the Latest Session - Free Cash Flow Trends - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems Share Price: Price Action and Valuation - Univest</t>
+          <t>UNOMINDA Q2 2026 Earnings: Revenue Climbs 16.91% to ₹19,385.01 Crore, Yet Stock Slips 1.89% - Guidance Revision Trend - siam.in</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems Share Price: Price Action and Valuation - Univest</t>
+          <t>UNOMINDA Q2 2026 Earnings: Revenue Climbs 16.91% to ₹19,385.01 Crore, Yet Stock Slips 1.89% - Guidance Revision Trend - siam.in</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Why Did TD Power Systems Shares Crash 50% Today? Check the Reason - Trade Brains</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Stocks in Focus: TD Power and 4 other stocks Set to Trade Ex-Bonus and Ex-Split Next Week - Trade Brains</t>
-        </is>
-      </c>
+          <t>Uno Minda: Shareholder Reports Loss of Original Share Certificate - InvestyWise</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1759,68 +1739,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>WELCORP.NS</t>
+          <t>HTEL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2472.60009765625</v>
+        <v>73.75</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2581.89990234375</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2472.60009765625</v>
+        <v>71.26000213623047</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2580</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2460.300048828125</v>
+        <v>72.05000305175781</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2580</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1423487</v>
+        <v>3939738</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.87</v>
+        <v>6.55</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp Share Price - Live NSE: WELCORP Stock Price &amp; Chart - Upstox</t>
+          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp Share Price Today: Rs 2,479.90 and sector view - Univest</t>
+          <t>HTEL Share Price Today - HY-TECH ENGINEERS LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp Share Price Slides; Steel Peer Review - Univest</t>
+          <t>Free float of Hy-Tech Engineers Limited – NSE:HTEL - tradingview.com</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Rs 17,200 cr order! Welspun Corp shares rally 12% as fresh order equals 30% of m-cap - Business Today</t>
+          <t>Share Price Today - Hy-Tech Engineers Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Welspun Corp shares zoom 12%, hit record high after bagging largest-ever ₹17,200 crore US order - Upstox</t>
+          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1828,61 +1808,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>AZAD.NS</t>
+          <t>SKIPPER.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Azad Engineering Limited</t>
+          <t>Skipper Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2605.300048828125</v>
+        <v>537</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2747.89990234375</v>
+        <v>570</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2605.300048828125</v>
+        <v>532.0999755859375</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2730.5</v>
+        <v>566.2000122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2605.300048828125</v>
+        <v>532.5499877929688</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2730.5</v>
+        <v>566.2000122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>308696</v>
+        <v>1433300</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4.81</v>
+        <v>6.32</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Azad Engineering Share Price Today: Valuation and Peers - Univest</t>
+          <t>Skipper receives voluntary ESG score of 60 from risk agency - scanx.trade</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Azad Engineering Share Price Today: Valuation and Peers - Univest</t>
+          <t>Skipper receives voluntary ESG score of 60 from risk agency - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Sussanne Khan says mom Zarine’s death brought her closer to Hrithik Roshan’s mom, shares ‘warm’ bond with Saba Azad - The Indian Express</t>
+          <t>Here's Why We Think Skipper (NSE:SKIPPER) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Sussanne Khan Reveals She Shares A ‘Warm’ Bond With Hrithik Roshan’s Girlfriend Saba Azad, Is Super Close To - iDiva</t>
+          <t>Skipper Ltd. Share Price at fresh 52-week high; stock view - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Azad Engineering Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Skipper Consolidated June 2026 Net Sales at Rs 1,309.83 crore, up 4.46% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
@@ -1903,14 +1883,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2009,7 +1989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2017,68 +1997,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TATACHEM.NS</t>
+          <t>SBGLP.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals Limited</t>
+          <t>Suratwwala Business Group Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>729</v>
+        <v>26.52000045776367</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>741.3499755859375</v>
+        <v>26.59000015258789</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>697.9500122070312</v>
+        <v>21.32999992370605</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>698.9500122070312</v>
+        <v>22.22999954223633</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>779.2999877929688</v>
+        <v>25.78000068664551</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>698.9500122070312</v>
+        <v>22.22999954223633</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>8968481</v>
+        <v>587657</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-10.31</v>
+        <v>-13.77</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals Share Price - Live NSE: TATACHEM Stock Price &amp; Chart - Upstox</t>
+          <t>Suratwwala Business Group (SBGLP.NS) Ticks Higher: Small-Cap Holds Above ₹21 on NSE - Head and Shoulders - siam.in</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals Share Price Today: 12.44% Gain Explained - Univest</t>
+          <t>Suratwwala Business Group (SBGLP.NS) Ticks Higher: Small-Cap Holds Above ₹21 on NSE - Head and Shoulders - siam.in</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>TATACHEM Share Price Today - Tata Chemicals on NSE/BSE - scanx.trade</t>
+          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Why is Tata Chemicals' share price rising today? Soda ash deal, Tata Sons listing buzz explained - Upstox</t>
+          <t>Suratwwala Business Group Share Price Today: 11.04% Gain - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals Stock Price Forecast. Should You Buy TATACHEM.NS? - StockInvest.us</t>
+          <t>SBGLP Technical Setup After Recent Decline - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2098,25 +2078,25 @@
         <v>14.28999996185303</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>15.0600004196167</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>14.28999996185303</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>14.28999996185303</v>
+        <v>14.35999965667725</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>15.86999988555908</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14.28999996185303</v>
+        <v>14.35999965667725</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>5611195</v>
+        <v>18623657</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.960000000000001</v>
+        <v>-9.51</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -2135,19 +2115,19 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price and Daily Chart View - Kalkine India</t>
+          <t>Atal Realtech Downtrend Continues - Kalkine India</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech NSE:ATALREAL Board Meeting Outcome September 2026 - Kalkine India</t>
+          <t>Atal Realtech Lower Circuit: Chart Analysis - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2155,68 +2135,56 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SBGLP.NS</t>
+          <t>OPTIFIN.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Limited</t>
+          <t>Optimus Finance Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>26.52000045776367</v>
+        <v>14.98999977111816</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>26.59000015258789</v>
+        <v>14.98999977111816</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23.20999908447266</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23.88999938964844</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25.78000068664551</v>
+        <v>15.13000011444092</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23.88999938964844</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>354249</v>
+        <v>61040</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.33</v>
+        <v>-7.4</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group (SBGLP.NS) Ticks Higher: Small-Cap Holds Above ₹21 on NSE - Head and Shoulders - siam.in</t>
+          <t>Optimus Finance appoints Kheradia as director, new auditor - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group (SBGLP.NS) Ticks Higher: Small-Cap Holds Above ₹21 on NSE - Head and Shoulders - siam.in</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Suratwwala Business Group Share Price Today: 11.04% Gain - Univest</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>SBGLP Technical Setup After Recent Decline - Kalkine India</t>
-        </is>
-      </c>
+          <t>Optimus Finance appoints Kheradia as director, new auditor - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2224,60 +2192,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MODTHREAD.NS</t>
+          <t>RELAXO.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Modern Threads (India) Limited</t>
+          <t>Relaxo Footwears Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>49.20999908447266</v>
+        <v>314.25</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>50.34999847412109</v>
+        <v>315</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>47</v>
+        <v>289.25</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>47.0099983215332</v>
+        <v>291.25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>50.34999847412109</v>
+        <v>313.7000122070312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>47.0099983215332</v>
+        <v>291.25</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2560</v>
+        <v>2052973</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-6.63</v>
+        <v>-7.16</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Modern (MODTHREAD.NS) Financial Results: The Latest Financial Metrics Are Now Available in Latest Trading; Share Move: Shares Close 1.37% Lower in the Latest Session - EPS Growth Report - siam.in</t>
+          <t>Interested In Relaxo Footwears' (NSE:RELAXO) Upcoming ₹3.50 Dividend? You Have Three Days Left - simplywall.st</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Modern Threads India Holds Steady at ₹53.58: Consolidation Within ₹50.9–₹56.26 Range - Sell Signal Alerts - siam.in</t>
+          <t>Relaxo Footwears vs Bata India: Which Footwear Stock Has the Stronger Growth Story? - Trade Brains</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Modern Threads India Holds Steady at ₹53.58: Consolidation Within ₹50.9–₹56.26 Range - Sell Signal Alerts - siam.in</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Relaxo Footwears incorporates SPV for captive solar power - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Relaxo Footwears (RELAXO.NS) Slips 3.6% to ₹346.4; Support at ₹329.08 in Focus - Insider Sentiment - siam.in</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Anupam Rasayan, Balu Forge, Cochin Shipyard, Lux Industries, Relaxo Footwears Dividends: Last Day To Buy To Qualify - NDTV Profit</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2285,68 +2261,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RELAXO.NS</t>
+          <t>STLSTRINF.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Relaxo Footwears Limited</t>
+          <t>Steel Strips Infrastructures Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>314.25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>315</v>
+        <v>26.89999961853027</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>291.7999877929688</v>
+        <v>23.1200008392334</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>293.7999877929688</v>
+        <v>23.46999931335449</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>313.7000122070312</v>
+        <v>25.14999961853027</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>293.7999877929688</v>
+        <v>23.46999931335449</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>642512</v>
+        <v>28554</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.34</v>
+        <v>-6.68</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Interested In Relaxo Footwears' (NSE:RELAXO) Upcoming ₹3.50 Dividend? You Have Three Days Left - simplywall.st</t>
+          <t>Steel Strips Infrastructures Ltd Share Price - Business Today</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Anupam Rasayan, Balu Forge, Cochin Shipyard, Lux Industries, Relaxo Footwears Dividends: Last Day To Buy To Qualify - NDTV Profit</t>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Relaxo Footwears incorporates SPV for captive solar power - scanx.trade</t>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Relaxo Footwears (RELAXO.NS) Slips 3.6% to ₹346.4; Support at ₹329.08 in Focus - Insider Sentiment - siam.in</t>
+          <t>Steel Strips Infrastructures Ltd (STLSTRINF) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Anupam Rasayan, Balu Forge, Cochin Shipyard, Lux Industries, Relaxo Footwears Dividends: Last Day To Buy To Qualify - NDTV Profit</t>
+          <t>PRIMEURB Stock Price and Chart — BSE:PRIMEURB - tradingview.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2354,68 +2330,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SWARAJ.NS</t>
+          <t>FILATFASH.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Swaraj Suiting Limited</t>
+          <t>Filatex Fashions Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>273.0499877929688</v>
+        <v>0.1899999976158142</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>287</v>
+        <v>0.1899999976158142</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>273.0499877929688</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>273.0499877929688</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>287.3999938964844</v>
+        <v>0.1800000071525574</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>273.0499877929688</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>399263</v>
+        <v>16682906</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.56</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>If EPS Growth Is Important To You, Swaraj Suiting (NSE:SWARAJ) Presents An Opportunity - simplywall.st</t>
+          <t>Filatex Fashions Limited (NSE:FILATFASH) Shares May Have Slumped 26% But Getting In Cheap Is Still Unlikely - simplywall.st</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>ESDS Software: IPO doubled investors money, now company launches Swaraj Sethu - All about Unified DevSecOps Platform - livemint.com</t>
+          <t>Filatex Fashions Limited Submits SEBI Compliance Certificate for Quarter Ended March 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Swaraj Engines to transfer shares to IEPF on September 4 - scanx.trade</t>
+          <t>FILATEX FASHIONS LIMITED Share Price - Live NSE: FILATFASH Stock Price &amp; Chart - upstox.com</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>ESDS Software: IPO doubled investors money, now company launches Swaraj Sethu - All about Unified DevSecOps Platform - livemint.com</t>
+          <t>Filatex Fashions Limited Submits SEBI Compliance Certificate for Quarter Ended March 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Swaraj Suiting Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>FILATFASH Share Price Today - Filatex Fashions Stock Analysis - Equitypandit</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2423,68 +2399,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>RHETAN.NS</t>
+          <t>HALDER.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Limited</t>
+          <t>Halder Venture Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>286.2000122070312</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>293.1000061035156</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>277</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>280.9500122070312</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.59000015258789</v>
+        <v>297.1499938964844</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>280.9500122070312</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>449500</v>
+        <v>482</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.95</v>
+        <v>-5.45</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT sets Sept 16 AGM date; proposes ₹300 crore borrowing limit hike - scanx.trade</t>
+          <t>Tata Chemicals, TCPL, Uno Minda, Welspun Living, Bandhan Bank, E2E Networks: Expert shares outlook - BusinessToday - IndiaIPO</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT sets Sept 16 AGM date; proposes ₹300 crore borrowing limit hike - scanx.trade</t>
+          <t>Tata Chemicals, TCPL, Uno Minda, Welspun Living, Bandhan Bank, E2E Networks: Expert shares outlook - BusinessToday - IndiaIPO</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - ThePrint</t>
+          <t>Halder Venture Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock under 50 hits 10% upper circuit despite stock market crash - livemint.com</t>
+          <t>Halder Venture dispatches AGM notice and annual report for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Ltd. Share Price Action and Fundamental View - Univest</t>
+          <t>Halder Venture Share Price: Good Buy After Q1 FY27 Results? - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2492,68 +2468,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA.NS</t>
+          <t>GUJALKALI.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>eMudhra Limited</t>
+          <t>Gujarat Alkalies and Chemicals Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>633.25</v>
+        <v>661.5499877929688</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>638.0999755859375</v>
+        <v>668.7999877929688</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>601.0999755859375</v>
+        <v>631.0999755859375</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>606.0999755859375</v>
+        <v>638.7000122070312</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>633.3499755859375</v>
+        <v>673.75</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>606.0999755859375</v>
+        <v>638.7000122070312</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>821965</v>
+        <v>217900</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.3</v>
+        <v>-5.2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>eMudhra share price jumps 12% today, extends gains for second session | What's behind the rally? - livemint.com</t>
+          <t>Don't Race Out To Buy Gujarat Alkalies and Chemicals Limited (NSE:GUJALKALI) Just Because It's Going Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>eMudhra vs Nifty 50: Share Price Performance Compared - Univest</t>
+          <t>Don't Race Out To Buy Gujarat Alkalies and Chemicals Limited (NSE:GUJALKALI) Just Because It's Going Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>eMudhra shares surge 20% in early deals; here's why - Business Today</t>
+          <t>Gujarat Alkalies Eases 0.86% to ₹712.55; Stock Holds Above Key Support at ₹676.92 - Ratio Spread Trade - siam.in</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>eMudhra zooms 20% amid huge volumes in weak market; here's why - Business Standard</t>
+          <t>GUJALKALI Share Price: stock news, price action and analysis - Univest</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>eMudhra shares zoom nearly 37% in two days; here's the trigger - BusinessToday - IndiaIPO</t>
+          <t>Over ₹17 per share dividend by Gujarat-based PSU company; check record and payment date | Do you own? - livemint.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2561,64 +2537,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL.NS</t>
+          <t>CUPID.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Cupid Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>548</v>
+        <v>280.2999877929688</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>552.9000244140625</v>
+        <v>282</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>518.2999877929688</v>
+        <v>251.1000061035156</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>524.2999877929688</v>
+        <v>265</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>546.1500244140625</v>
+        <v>279.1499938964844</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>524.2999877929688</v>
+        <v>265</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>351328</v>
+        <v>27287571</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4</v>
+        <v>-5.07</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness (ZYDUSWELL.NS) Slips 3.09% to ₹548.8 as FMCG Stock Tests Mid-Range Support - BPI Reversal - siam.in</t>
+          <t>Cupid shares reclassified from BSE Group B to Group A - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness (ZYDUSWELL.NS) Slips 3.09% to ₹548.8 as FMCG Stock Tests Mid-Range Support - BPI Reversal - siam.in</t>
+          <t>4:1 Bonus Allotment: How Your 1 Cupid Stock Became 80 Shares In 2 Years; Buy Condom Maker Shares? - Goodreturns</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness Dips 1.64% to ₹526.4: Stock Hovers Between Key Support and Resistance Levels - New Highs New Lows - siam.in</t>
+          <t>4:1 Bonus Allotment: How Your 1 Cupid Stock Became 80 Shares In 2 Years; Buy Condom Maker Shares? - Goodreturns</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited Announces Appointment of Kapil Sharma as Chief Revenue Officer (India and Indian Subcontinent), Effective September 1, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Cupid, Avalon, Pine Labs, ACME Solar, Groww, Belrise: FTSE rebalancing, inflow preview - Business Today</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Cupid Co-Promoter Aditya Halwasiya Acquires 5.90 Lakh Shares, Raising Promoter Group Stake To 46.87% - Sahi</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2626,68 +2606,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>ONIXSOLAR.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>Onix Solar Energy Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>33.56000137329102</v>
+        <v>357.3999938964844</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>36.5</v>
+        <v>357.3999938964844</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>33.56000137329102</v>
+        <v>357.3999938964844</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>33.91999816894531</v>
+        <v>357.3999938964844</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>35.31999969482422</v>
+        <v>376.2000122070312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>33.91999816894531</v>
+        <v>357.3999938964844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2708173</v>
+        <v>6099</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-3.96</v>
+        <v>-5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>ONIXSOLAR Stock Price and Chart — NSE:ONIXSOLAR - tradingview.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities to Raise ₹10 Crore via Secured Non-Convertible Debentures - TipRanks</t>
+          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities to Raise ₹10 Crore via Secured Non-Convertible Debentures - TipRanks</t>
+          <t>Onix Solar Energy Limited Schedules Rights Issue Committee Meeting for May 11, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities approves issuance of NCDs up to ₹10 Crore - Business Upturn</t>
+          <t>Onix Solar Energy Limited Board Approves Rights Issue of Up to Rs. 130 Crore - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2695,68 +2675,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ASTEC.NS</t>
+          <t>SWARAJ.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Astec LifeSciences Limited</t>
+          <t>Swaraj Suiting Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>760</v>
+        <v>273.0499877929688</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>767.5999755859375</v>
+        <v>287</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>720.0499877929688</v>
+        <v>273.0499877929688</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>725.9500122070312</v>
+        <v>273.0499877929688</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>755.1500244140625</v>
+        <v>287.3999938964844</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>725.9500122070312</v>
+        <v>273.0499877929688</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>68693</v>
+        <v>404231</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-3.87</v>
+        <v>-4.99</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - TradingView</t>
+          <t>Swaraj Suiting Ltd. Lower Circuit Streak: Day 2 Price and Data - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Astec LifeSciences addresses recent surge in trading volume, confirms regulatory compliance - Business Upturn</t>
+          <t>Swaraj Suiting Ltd. Lower Circuit Streak: Day 2 Price and Data - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - livemint.com</t>
+          <t>If EPS Growth Is Important To You, Swaraj Suiting (NSE:SWARAJ) Presents An Opportunity - simplywall.st</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences Share Price Fall: Technicals, Valuation - Univest</t>
+          <t>Swaraj Engines to transfer shares to IEPF on September 4 - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Astec Industries Inc. (ASTE) Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>ESDS Software: IPO doubled investors money, now company launches Swaraj Sethu - All about Unified DevSecOps Platform - livemint.com</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2764,68 +2744,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ROUTE.NS</t>
+          <t>RHETAN.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ROUTE MOBILE LIMITED</t>
+          <t>Rhetan TMT Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>490.2999877929688</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>490.7000122070312</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>468.8500061035156</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>474</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>492.6000061035156</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>474</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>269452</v>
+        <v>614120</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-3.78</v>
+        <v>-4.95</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>OnEMI Technology shares in focus as board clears fund raising via preferential route - Business Today</t>
+          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>TCS, HCL Tech, Tata Elxsi, Route Mobile to Tech Mahindra: IT stocks dip up to 3% | Here's why - livemint.com</t>
+          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>TCS, HCL Tech, Tata Elxsi, Route Mobile to Tech Mahindra: IT stocks dip up to 3% | Here's why - livemint.com</t>
+          <t>Rhetan TMT regularizes Jhanvi Sethi as independent director - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>WTI slips below $97 as Saudi alternative route and softer US stock draw ease supply fears - VT Markets</t>
+          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - ThePrint</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>NSE shares may trade on its platform under 'permitted-to-trade' route - thehindu.com</t>
+          <t>Small-cap stock under 50 hits 10% upper circuit despite stock market crash - livemint.com</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2833,68 +2813,56 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TCC.NS</t>
+          <t>KPITTECH.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept Limited</t>
+          <t>KPIT Technologies Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>51.36000061035156</v>
+        <v>559.2999877929688</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>51.86000061035156</v>
+        <v>559.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>49.4900016784668</v>
+        <v>532</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>49.5099983215332</v>
+        <v>532</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>51.25</v>
+        <v>559.2999877929688</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>49.5099983215332</v>
+        <v>532</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>359012</v>
+        <v>3944020</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-3.4</v>
+        <v>-4.88</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>TCryptochicks Price (TCC/USD) Today | Live Price, Market Cap &amp; Chart - Binance</t>
+          <t>KPIT (KPITTECH.NS) Financial Update: The Latest Report Adds New Financial Reference Points under the Current Snapshot; Post-Earnings: Shares Fall 1.05% in the Latest Session - CEO Earnings Statement - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Taiwan Cement Corporation stock holds steady as investors eye latest earnings trend - ad-hoc-news.de</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan Cement Corporation stock holds steady as investors eye latest earnings trend - ad-hoc-news.de</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>TCC Share Price Rises 12.46%: Valuation and Sector View - Univest</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>TCC Concept Limited (NSE: TCC) Falls 5.53% as Stock Movement Draws Market Attention - Kalkine India</t>
-        </is>
-      </c>
+          <t>KPIT (KPITTECH.NS) Financial Update: The Latest Report Adds New Financial Reference Points under the Current Snapshot; Post-Earnings: Shares Fall 1.05% in the Latest Session - CEO Earnings Statement - siam.in</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2902,68 +2870,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>TMPV.NS</t>
+          <t>EMPOWER.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tata Motors Passenger Vehicles Limited</t>
+          <t>Empower India Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>309.6000061035156</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>310</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>303.25</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>304.3999938964844</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>314.5</v>
+        <v>2.5</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>304.3999938964844</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>9485747</v>
+        <v>1202346</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-3.21</v>
+        <v>-4.8</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals shares crash 7.5% amid Tata Sons listing row; TMPV, TCS down 2%: Here's why - Moneycontrol.com</t>
+          <t>Penny stock under 10 rupees hits 5% upper circuit after this acquisition update - livemint.com</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals shares crash 7.5% amid Tata Sons listing row; TMPV, TCS down 2%: Here's why - Moneycontrol.com</t>
+          <t>Empower India Ltd Upgraded to Buy on Strong Technical and Financial Performance - MarketsMojo</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Tata Sons listing: Tata Steel, Tata Motors, Tata Chemicals among stocks that could benefit; here's why - Business Today</t>
+          <t>Empower India signs non-binding term sheet to acquire 100% stake in Valiance Engineers - ET Infra</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>TMPV share price: Buy or Sell - Univest</t>
+          <t>Empower India Shares Hit 5% Upper Circuit After Acquisition Plan; Company To Buy 100% Of Valiance Engineers - Goodreturns</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Tata Motors PV Shares Fall 6% After Q1 Profit Plunges 79%; Brokerage Sees 11% Downside - Goodreturns</t>
+          <t>Taking Stock - September 16, 2026 - Fed rate decision - Empower</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2971,68 +2939,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS.NS</t>
+          <t>NIACL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom Limited</t>
+          <t>The New India Assurance Company Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>614</v>
+        <v>196.7599945068359</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>622.7000122070312</v>
+        <v>196.7599945068359</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>590.1500244140625</v>
+        <v>186</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>590.5999755859375</v>
+        <v>187.6600036621094</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>610</v>
+        <v>197.0500030517578</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>590.5999755859375</v>
+        <v>187.6600036621094</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>105626</v>
+        <v>9375719</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-3.18</v>
+        <v>-4.77</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom Share Price Today: Key Stock Analysis - Univest</t>
+          <t>New India Assurance Share Price Fall and Valuation View - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>New India Assurance Share Price Fall and Valuation View - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS.NS Q2 2026 Earnings: EPS Holds at ₹7.39 as Shares Rise 6.83% Despite Revenue Dip - Peak Earnings Alert - siam.in</t>
+          <t>NIACL, IFCI shares rise up to 9% as NSE IPO opens for subscription - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom Invests ₹5.60 Crore In Subsidiary Optiemus Unmanned Systems - Sahi</t>
+          <t>IFCI, NIACL shares jump as NSE's ₹22,569-cr IPO opens | Tap to know more | Inshorts - Inshorts</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>NIACL (NIACL.NS) Slips 0.66% to ₹184.19 as New India Assurance Tests Mid-Range Support - Charm Flow - siam.in</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3040,68 +3008,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DUCON.NS</t>
+          <t>INDIQUBE.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.220000028610229</v>
+        <v>200</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.289999961853027</v>
+        <v>202.8699951171875</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1.149999976158142</v>
+        <v>190.8999938964844</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>192.8500061035156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.269999980926514</v>
+        <v>202.4499969482422</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.230000019073486</v>
+        <v>192.8500061035156</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4768421</v>
+        <v>81977</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-3.15</v>
+        <v>-4.74</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>INDIQUBE Stock Price and Chart — NSE:INDIQUBE - tradingview.com</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies: Small Cap Q2 Preview - Univest</t>
+          <t>Indiqube Spaces Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Ltd. - RE1 Share Price Live Today - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares Balance Sheet – NSE:DUCON_RE1 - TradingView</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Ducon Infratechnologies rights issue shares listed on exchanges - scanx.trade</t>
-        </is>
-      </c>
+          <t>Indiqube Spaces Bull Case vs Bear Case for 2026 - Univest</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3109,68 +3069,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TCS.NS</t>
+          <t>MODTHREAD.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Limited</t>
+          <t>Modern Threads (India) Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2177.199951171875</v>
+        <v>49.20999908447266</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2177.300048828125</v>
+        <v>50.34999847412109</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2115.39990234375</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2121.39990234375</v>
+        <v>47.9900016784668</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2190</v>
+        <v>50.34999847412109</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2121.39990234375</v>
+        <v>47.9900016784668</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3057688</v>
+        <v>5222</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.13</v>
+        <v>-4.69</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals shares crash 7.5% amid Tata Sons listing row; TMPV, TCS down 2%: Here's why - Moneycontrol.com</t>
+          <t>Modern (MODTHREAD.NS) Financial Results: The Latest Financial Metrics Are Now Available in Latest Trading; Share Move: Shares Close 1.37% Lower in the Latest Session - EPS Growth Report - siam.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TCS Shares Fall Over 3% As Tata Sons Governance Dispute Intensifies - businessworld.in</t>
+          <t>Modern Threads India Holds Steady at ₹53.58: Consolidation Within ₹50.9–₹56.26 Range - Sell Signal Alerts - siam.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>TCS Shares Fall Over 3% As Tata Sons Governance Dispute Intensifies - businessworld.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>TCS, HCL Tech, Tata Elxsi, Route Mobile to Tech Mahindra: IT stocks dip up to 3% | Here's why - livemint.com</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Tata Group shares fall up to 8 pc amid corporate feud over N Chandrasekaran - Telangana Today</t>
-        </is>
-      </c>
+          <t>Modern Threads India Holds Steady at ₹53.58: Consolidation Within ₹50.9–₹56.26 Range - Sell Signal Alerts - siam.in</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3178,68 +3130,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>FIRSTCRY.NS</t>
+          <t>ZYDUSWELL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Brainbees Solutions Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>169.8000030517578</v>
+        <v>548</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>170</v>
+        <v>552.9000244140625</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>163.6600036621094</v>
+        <v>512</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>164.0200042724609</v>
+        <v>522.25</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>169.25</v>
+        <v>546.1500244140625</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>164.0200042724609</v>
+        <v>522.25</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2242241</v>
+        <v>723768</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.09</v>
+        <v>-4.38</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>FirstCry stock: Brainbees Solutions share price jumps 7% after 54% fall in 1 year - reason? - IndiaIPO</t>
+          <t>Zydus Wellness (ZYDUSWELL.NS) Slips 3.09% to ₹548.8 as FMCG Stock Tests Mid-Range Support - BPI Reversal - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>FirstCry, Zensar Tech, Tata Investment Corp shares surge amid spike in volumes; check full list - Upstox</t>
+          <t>Zydus Wellness (ZYDUSWELL.NS) Slips 3.09% to ₹548.8 as FMCG Stock Tests Mid-Range Support - BPI Reversal - siam.in</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>FirstCry stock: Brainbees Solutions share price jumps 7% after 54% fall in 1 year - Bigger rebound on cards? - livemint.com</t>
+          <t>Zydus Wellness Dips 1.64% to ₹526.4: Stock Hovers Between Key Support and Resistance Levels - New Highs New Lows - siam.in</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>FirstCry, Zensar Tech, Tata Investment Corp shares surge amid spike in volumes; check full list - Upstox</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>FirstCry lost its edge, then its unicorn status. Now comes the fightback - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Zydus Wellness Limited Announces Appointment of Kapil Sharma as Chief Revenue Officer (India and Indian Subcontinent), Effective September 1, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3247,68 +3195,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>GNRL.NS</t>
+          <t>GLOBALE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Natural Resources Limited</t>
+          <t>Globale Tessile Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>101.5999984741211</v>
+        <v>10.94999980926514</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>103.9899978637695</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>96.69000244140625</v>
+        <v>10.93000030517578</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>97.95999908447266</v>
+        <v>11</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>101.0500030517578</v>
+        <v>11.5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>97.95999908447266</v>
+        <v>11</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>145874</v>
+        <v>8037</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.06</v>
+        <v>-4.35</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>GNRL Shares Jump Following Resumption of Post-Monsoon Drilling - Motilal Oswal</t>
+          <t>Globale Tessile AGM rescheduled to Sep 23; FY26 loss widens - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>GNRL Shares Jump Following Resumption of Post-Monsoon Drilling - Motilal Oswal</t>
+          <t>EDP Renovaveis stock gains as Lisbon rally follows latest interim figures - AD HOC NEWS</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Gujarat (GNRL.NS) Outlook: Finishes 0.29% Lower at ₹101.60 on the Day; Key Range: Price Remains Between ₹96.52 Support and ₹106.68 Resistance in the Latest Session - Float Adjusted Cap - siam.in</t>
+          <t>Globale Tessile Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Natural Resources Share Price Rises 13.47% Today - Univest</t>
+          <t>Globale Tessile Ltd Locks at Lower Circuit With 4.87% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Dixon targets aerospace, defence, and auto sectors for major expansion - Motilal Oswal</t>
+          <t>Globale (GLOBALE.NS) Earnings Update: Available Data Shows the Latest Reported Performance under the Current Snapshot; Investor Response: Shares Close 2.72% Lower in the Available Record - Core Business Growth - siam.in</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:02:24 IST</t>
+          <t>2026-09-18 20:07:47 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3316,54 +3264,58 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO.NS</t>
+          <t>KMCSHIL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Jamna Auto Industries Limited</t>
+          <t>K M C Speciality Hospitals (India) Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>126.5999984741211</v>
+        <v>157</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>128</v>
+        <v>158.3300018310547</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>122.4000015258789</v>
+        <v>148</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>123.120002746582</v>
+        <v>150.2599945068359</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>126.9599990844727</v>
+        <v>156.7400054931641</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>123.120002746582</v>
+        <v>150.2599945068359</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1771798</v>
+        <v>467949</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.02</v>
+        <v>-4.13</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Jamna Auto Industries Limited (NSE:JAMNAAUTO) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>KMC Speciality Hospitals Share Price: price rise, valuation - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Jamna Auto Industries Limited (NSE:JAMNAAUTO) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>KMC Speciality Hospitals Share Price: Price Action and Peers - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Jamna Auto Promoter Pradeep Singh Jauhar Sells 2.49% Stake via Block Deal - Whalesbook</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
+          <t>KMC Speciality Hospitals Share Price: Price Action and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>KMC Speciality Hospitals Share Price today near 52-week peak - Univest</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -438,8 +438,8 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PROTEAN.NS</t>
+          <t>ARVEE.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov Technologies Limited</t>
+          <t>Arvee Laboratories (India) Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>493</v>
+        <v>177.5399932861328</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>588.3499755859375</v>
+        <v>208.8699951171875</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>491.5</v>
+        <v>174.9299926757812</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>588.3499755859375</v>
+        <v>208.8699951171875</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>490.2999877929688</v>
+        <v>174.0599975585938</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>588.3499755859375</v>
+        <v>208.8699951171875</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7955904</v>
+        <v>60933</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov Technologies Ltd leads gainers in 'A' group - Business Standard</t>
+          <t>Arvee Labs (ARVEE.NS) Surges 18% to ₹193.74: Key Levels to Watch - Volatility Skew - siam.in</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>PROTEAN EGOV TECH Share Price Today Up 17% - Equitymaster</t>
+          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>PROTEAN EGOV TECH Share Price Today Up 17% - Equitymaster</t>
+          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov Technologies (PROTEAN.NS) Slips 0.72% to ₹485.35, Holding Above ₹461 Support - Gap Up Stocks - siam.in</t>
+          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov Technologies Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Arvee Laboratories (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,60 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>TANAA.NS</t>
+          <t>PROTEAN.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Limited</t>
+          <t>Protean eGov Technologies Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>266.3500061035156</v>
+        <v>493</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>319.6000061035156</v>
+        <v>588.3499755859375</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>266.3500061035156</v>
+        <v>491.5</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>319.6000061035156</v>
+        <v>588.3499755859375</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>266.3500061035156</v>
+        <v>490.2999877929688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>319.6000061035156</v>
+        <v>588.3499755859375</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>211305</v>
+        <v>7996314</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.99</v>
+        <v>20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA): Niche Defence Stock Watch - Kalkine India</t>
+          <t>Protean eGov shares zoom 20% to hit upper circuit; here's what's happening - businesstoday.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+          <t>Protean eGov shares zoom 20% to hit upper circuit; here's what's happening - BusinessToday - IndiaIPO</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Protean eGov Technologies Ltd leads gainers in 'A' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Protean eGov shares zoom 20% to hit upper circuit; here's what's happening - BusinessToday - IndiaIPO</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>PROTEAN EGOV TECH Share Price Today Up 17% - Equitymaster</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +691,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>TANAA.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>Taneja Aerospace &amp; Aviation Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>177.5399932861328</v>
+        <v>266.3500061035156</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>208.8699951171875</v>
+        <v>319.6000061035156</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>174.9299926757812</v>
+        <v>266.3500061035156</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>206</v>
+        <v>319.6000061035156</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>174.0599975585938</v>
+        <v>266.3500061035156</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>206</v>
+        <v>319.6000061035156</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>47831</v>
+        <v>226450</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>18.35</v>
+        <v>19.99</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Arvee Labs (ARVEE.NS) Surges 18% to ₹193.74: Key Levels to Watch - Volatility Skew - siam.in</t>
+          <t>Taneja Aerospace &amp; Aviation (TANAA): Niche Defence Stock Watch - Kalkine India</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
+          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Arvee Laboratories (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
-        </is>
-      </c>
+          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +752,56 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CROWN.NS</t>
+          <t>INDORAMA.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Crown Lifters Limited</t>
+          <t>Indo Rama Synthetics (India) Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>108</v>
+        <v>91.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>126.7399978637695</v>
+        <v>109.2600021362305</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>108</v>
+        <v>91.08999633789062</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>124</v>
+        <v>106.5500030517578</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>108.4800033569336</v>
+        <v>91.05000305175781</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>124</v>
+        <v>106.5500030517578</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>153740</v>
+        <v>13822935</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14.31</v>
+        <v>17.02</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Crown Siem Côte d'Ivoire (SEMC) — BRVM - Dabafinance</t>
+          <t>Indo Rama Synthetics Share Price - Live NSE: INDORAMA Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Crown Castle stock gains on analyst upgrade and dividend yield - AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>JPMorgan upgrades Crown Holdings stock rating on valuation By Investing.com - Investing.com India</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>L'Oreal steals French stock market crown from LVMH - Reuters</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>L’Oréal Steals French Stock Market Crown From LVMH - The Business of Fashion</t>
-        </is>
-      </c>
+          <t>Indo Rama Synthetics Share Price - Live NSE: INDORAMA Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,56 +809,60 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>INDORAMA.NS</t>
+          <t>FEDDERSHOL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics (India) Limited</t>
+          <t>Fedders Holding Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>91.5</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>104.4899978637695</v>
+        <v>63.47999954223633</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>91.08999633789062</v>
+        <v>54</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>103.9000015258789</v>
+        <v>61.4900016784668</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>91.05000305175781</v>
+        <v>52.90000152587891</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>103.9000015258789</v>
+        <v>61.4900016784668</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6995003</v>
+        <v>35766255</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>14.11</v>
+        <v>16.24</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics Share Price - Live NSE: INDORAMA Stock Price &amp; Chart - Upstox</t>
+          <t>Fedders Holding Ltd. Share Price Today Near Yearly High - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics Share Price - Live NSE: INDORAMA Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
+          <t>Fedders Holding Ltd. Share Price Today Near Yearly High - Univest</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Fedders Holding approves NSE direct listing, appoints three new directors - scanx.trade</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -878,56 +870,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SURAJEST.NS</t>
+          <t>AHCL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate Developers Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>193.7899932861328</v>
+        <v>23.15999984741211</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>222.9600067138672</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>193</v>
+        <v>23.14999961853027</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>216.8000030517578</v>
+        <v>26.23999977111816</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>192.25</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>216.8000030517578</v>
+        <v>26.23999977111816</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2277936</v>
+        <v>130243729</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>12.77</v>
+        <v>14.59</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate Developers Share Price rises 8.72%: key data - univest.in</t>
+          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate Developers Share Price rises 8.72%: key data - univest.in</t>
+          <t>AHCL Share Price Today Near 52-Week High and Market Cap - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate Developers Slips 3.86% to ₹191.01: Key Levels to Watch for SURAJEST.NS - Bearish Pattern Stocks - siam.in</t>
+          <t>AHCL Share Price Today Near 52-Week High and Market Cap - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate Developers Alerts Shareholders on AGM Access and KYC Compliance - TipRanks</t>
+          <t>Anlon Healthcare Publishes Record Date Notice Following Postal Ballot Approval - scanx.trade</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -935,7 +927,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -943,68 +935,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN.NS</t>
+          <t>GAJA.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>KPI Green Energy Limited</t>
+          <t>Gaja Alternative Asset Management Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>284.5</v>
+        <v>143</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>324.7000122070312</v>
+        <v>168.3300018310547</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>283.8999938964844</v>
+        <v>141.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>320</v>
+        <v>162.7100067138672</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>284.4500122070312</v>
+        <v>142.5</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>320</v>
+        <v>162.7100067138672</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>13257200</v>
+        <v>18146677</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>12.5</v>
+        <v>14.18</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>KPI Global Infrastructure Share Price - Live NSE: KPIGREEN Stock Price &amp; Chart - Upstox</t>
+          <t>Gaja AAM Lists 16% Higher; Stock Ends 5% Up From Issue Price - HDFC Sky</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>KPI Global Infrastructure Share Price - Live NSE: KPIGREEN Stock Price &amp; Chart - Upstox</t>
+          <t>GAJA ALT ASSET MGT LTD Share Price at Fresh 52-Week Low - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And KPI Green Energy (NSE:KPIGREEN) Passed With Ease - simplywall.st</t>
+          <t>India's Gaja Alternative Asset valued at $251.5 million in trading debut - Reuters</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>KPI Green Energy (KPIGREEN.NS) Slips 1.91% to ₹282 as ₹267.9 Support Comes Into Focus - Growth Stock Picks - siam.in</t>
+          <t>Gaja Alternative shares make decent listing gains at 16% premium; should you buy, sell or hold? - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>KPI (KPIGREEN.NS) Sheds -1.91% — Support at ₹267.90 Now Critical 2026-09-14 - Thematic ETF Flow - siam.in</t>
+          <t>Gaja Alternative shares fall 3.5% even as total income rises 27% in Q1 to Rs 52 crore - TradingView</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1012,64 +1004,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>KPL.NS</t>
+          <t>KPIGREEN.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Kwality Pharmaceuticals Limited</t>
+          <t>KPI Green Energy Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3478.89990234375</v>
+        <v>284.5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3840</v>
+        <v>324.7000122070312</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3447.199951171875</v>
+        <v>283.8999938964844</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3815</v>
+        <v>321.3999938964844</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3471.199951171875</v>
+        <v>284.4500122070312</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3815</v>
+        <v>321.3999938964844</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>107182</v>
+        <v>18325693</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>9.9</v>
+        <v>12.99</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Kwality Pharmaceuticals Slips 1.13% to ₹3,277: Stock Consolidates Between Key Support and Resistance - Spring Pattern - siam.in</t>
+          <t>KPI Global Infrastructure Share Price - Live NSE: KPIGREEN Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Kwality Pharmaceuticals Share Price rises 8.15%: analysis - Univest</t>
+          <t>KPI Global Infrastructure Share Price - Live NSE: KPIGREEN Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Kwality Pharmaceuticals Share Price rises 8.15%: analysis - Univest</t>
+          <t>We Ran A Stock Scan For Earnings Growth And KPI Green Energy (NSE:KPIGREEN) Passed With Ease - simplywall.st</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>KPL Share Price | Kwality Pharmaceuticals Ltd Stock Analysis &amp; Recommendation - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>KPI Green Energy (KPIGREEN.NS) Slips 1.91% to ₹282 as ₹267.9 Support Comes Into Focus - Growth Stock Picks - siam.in</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>KPI Green Energy (KPIGREEN.NS) Gains 1.24% to ₹307: Renewable Play Nears Key Resistance - Scalping Stock Signals - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1077,68 +1073,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CENTUM.NS</t>
+          <t>ZOTA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Limited</t>
+          <t>Zota Health Care LImited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4351.5</v>
+        <v>1160</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4785.2998046875</v>
+        <v>1324.400024414062</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4350</v>
+        <v>1138.900024414062</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4751.60009765625</v>
+        <v>1287.800048828125</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4333.2998046875</v>
+        <v>1144.5</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4751.60009765625</v>
+        <v>1287.800048828125</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>203950</v>
+        <v>401249</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.65</v>
+        <v>12.52</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Share Price - Upstox</t>
+          <t>Zota Health Care Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Share Price - Upstox</t>
+          <t>Zota Health Care Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Ltd. Share Price Today: key stock move - Univest</t>
+          <t>Zota Health Care FY26 revenue surges 84% to ₹53,866 lakhs - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Ltd. Stock News - Value Research</t>
+          <t>Zota (ZOTA.NS) Stock Analysis: -1.12% Down — Bearish Signals to Watch 2026-09-11 - Force Index - siam.in</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics schedules virtual analyst meet on September 9 - scanx.trade</t>
+          <t>Zota Healthcare - Mukul Agrawal’s portfolio: Top 5 stock holdings and their one-month performance - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1146,68 +1142,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TEGA.NS</t>
+          <t>JAYKAY.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries Limited</t>
+          <t>Jaykay Enterprises Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1950</v>
+        <v>169.6900024414062</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2135</v>
+        <v>190.7599945068359</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1933.300048828125</v>
+        <v>169.6799926757812</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2117</v>
+        <v>187.5599975585938</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1943</v>
+        <v>167.1799926757812</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2117</v>
+        <v>187.5599975585938</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>3078505</v>
+        <v>4432715</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>12.19</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries shares surge nearly 10% on ₹126 crore Kalpataru Projects contract - CNBC TV18</t>
+          <t>Enterprise value of Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares – BSE:JAYKAY_RE1 - TradingView</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries shares surge nearly 10% on ₹126 crore Kalpataru Projects contract - CNBC TV18</t>
+          <t>Enterprise value of Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares – BSE:JAYKAY_RE1 - TradingView</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries Share Price - Live NSE: TEGA Stock Price &amp; Chart - Upstox</t>
+          <t>Jaykay Enterprises Subsidiary Neumesh Labs Receives MCA Investigation Notice - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries Share Price rises 5.01%: valuation, peers - univest.in</t>
+          <t>Jaykay Enterprises Ltd. - RE1 Share Price Live Today - CNBC TV18</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+          <t>Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares Earnings and Revenue – NSE:JAYKAY_RE1 - TradingView</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1215,68 +1211,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>JPPOWER.NS</t>
+          <t>CROWN.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Jaiprakash Power Ventures Limited</t>
+          <t>Crown Lifters Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16.04999923706055</v>
+        <v>108</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>17.48999977111816</v>
+        <v>127.9000015258789</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>16.04999923706055</v>
+        <v>108</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>16.72999954223633</v>
+        <v>121.379997253418</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.36999988555908</v>
+        <v>108.4800033569336</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16.72999954223633</v>
+        <v>121.379997253418</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>476157690</v>
+        <v>283904</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.85</v>
+        <v>11.89</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>295 percent return in 5 years: Share price of THIS company zooms 12 percent today, check key details here - India.com</t>
+          <t>Crown Lifters Share Price Today: Rs 120 and key metrics - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>295 percent return in 5 years: Share price of THIS company zooms 12 percent today, check key details here - India.com</t>
+          <t>Crown Castle stock falls after dividend cut as analysts reassess income appeal - AD HOC NEWS</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>JPPOWER Slips 1.41%: Jaiprakash Power Ventures Hovers Near Key Support Zone - Late Stage Breakouts - siam.in</t>
+          <t>JPMorgan upgrades Crown Holdings stock rating on valuation By Investing.com - Investing.com India</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Jaiprakash Power shares jumped 10% today; here's why - businesstoday.in</t>
+          <t>L'Oreal steals French stock market crown from LVMH - Reuters</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>295% return in 5 years: Jaiprakash Power Ventures share price zooms 12% today - what's driving the rally? - Livemint</t>
+          <t>L’Oréal Steals French Stock Market Crown From LVMH - The Business of Fashion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1284,68 +1280,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GLOBE.NS</t>
+          <t>RATNAVEER.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>GLOBE ENTERPRISES (INDIA) LIMITED</t>
+          <t>Ratnaveer Precision Engineering Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>302</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2.480000019073486</v>
+        <v>338</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2.029999971389771</v>
+        <v>296.8999938964844</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.25</v>
+        <v>334.5499877929688</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2.069999933242798</v>
+        <v>299.25</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.25</v>
+        <v>334.5499877929688</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>6213353</v>
+        <v>20650744</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Globe Life Inc. (GL) Edges Lower as Shares Test Mid-Range Support - Dividend Stock Picks - careplusvn.com</t>
+          <t>Ratnaveer Precision Engineering Share Price rises 9.01% - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3 Things You Need to Know Before Buying IonQ Stock - The Globe and Mail</t>
+          <t>Ratnaveer Precision Engineering Share Price rises 9.01% - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3 Things You Need to Know Before Buying IonQ Stock - The Globe and Mail</t>
+          <t>Ratnaveer Precision completes dispatch of ₹330 crore rights issue offer - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Globe Civil Projects Slips 1% to ₹46.21; Stock Hovers Between Key Support and Resistance - Volume Breakout Ideas - siam.in</t>
+          <t>Press Release Distribution India - Business Wire India</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Globe Life stock slips as analysts keep a moderate buy - AD HOC NEWS</t>
+          <t>Ratnaveer Precision Engineering share price hits 52-week high | What's behind the rally? - TradingView</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1353,56 +1349,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM.NS</t>
+          <t>TARSONS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Limited</t>
+          <t>Tarsons Products Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1067</v>
+        <v>305.8999938964844</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1161.449951171875</v>
+        <v>356.8500061035156</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1065.25</v>
+        <v>305.0499877929688</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1147.150024414062</v>
+        <v>341.2999877929688</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1055.900024414062</v>
+        <v>306.1000061035156</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1147.150024414062</v>
+        <v>341.2999877929688</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4182808</v>
+        <v>5943251</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM LIMITED Share Price - Upstox</t>
+          <t>Tarsons Products Share Price Rise: Fundamental Analysis - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM LIMITED Share Price - Upstox</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Tarsons Products Share Price Rise: Fundamental Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Tarsons (TARSONS.NS) Shares: Finishes 0.39% Down at ₹345.50 on the Day; Chart View: Support at ₹328.22 and Resistance at ₹362.78 Frame the Range for the Current Session - Outside Reversal - siam.in</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Tarsons Products Ltd Downgraded to Strong Sell Amid Weak Fundamentals and Valuation Concerns - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Tarsons Products schedules 43rd AGM for September 24, 2026 - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1410,68 +1418,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>QUINT.NS</t>
+          <t>JASH.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Limited</t>
+          <t>Jash Engineering Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>73.44999694824219</v>
+        <v>551</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>77.01999664306641</v>
+        <v>596.9000244140625</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>68.69999694824219</v>
+        <v>541</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>76</v>
+        <v>575.9000244140625</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>70.01999664306641</v>
+        <v>521.1500244140625</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>76</v>
+        <v>575.9000244140625</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>574383</v>
+        <v>14684581</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>10.51</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>QDLDW Share Price Today - Quint Digital Limited Stock Price Live NSE/BSE - univest.in</t>
+          <t>Jash Engineering Share Price Today, Jash Engineering Stock Price Live NSE/BSE Updates - The Economic Times</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>QDLDW Share Price Today - Quint Digital Limited Stock Price Live NSE/BSE - univest.in</t>
+          <t>Jash Engineering Share Price Today, Jash Engineering Stock Price Live NSE/BSE Updates - The Economic Times</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Share Price near 52-week high, valuation view - univest.in</t>
+          <t>Be Sure To Check Out Jash Engineering Limited (NSE:JASH) Before It Goes Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital Share Price Today Near Yearly High | QUINT - univest.in</t>
+          <t>Jash Engineering promoter Rohan Patel sells 10,000 equity shares - scanx.trade</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Quint Digital submits Letter of Offer for ₹908.8 lakh rights issue - scanx.trade</t>
+          <t>Jash (JASH.NS) Earnings Update: The Report Supplies Updated Headline Figures at the Close; Market Response: Shares Move Higher 2.98% on the Day - Balance Sheet Strength - siam.in</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1479,68 +1487,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KDGREEN.NS</t>
+          <t>AGI.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>KD Green Industries Limited</t>
+          <t>AGI Greenpac Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>49.52000045776367</v>
+        <v>744.0499877929688</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>54.27999877929688</v>
+        <v>824</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>48.61000061035156</v>
+        <v>744</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53.5</v>
+        <v>819.3499755859375</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>49.34999847412109</v>
+        <v>745.0499877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>53.5</v>
+        <v>819.3499755859375</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>78713</v>
+        <v>1015912</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8.41</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>KDGREEN Share Price Today - Manbro Industries Ltd. Stock Price Live NSE/BSE - univest.in</t>
+          <t>AGI Greenpac Share Price Today: Price Rise and Valuation - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>KD Green merger to create green steel and infrastructure hub - scanx.trade</t>
+          <t>AGI Infra schedules board meeting to consider QIP equity fundraising - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of KD Green Industries Ltd – NSE:KDGREEN - TradingView</t>
+          <t>AGI Inc Class A Actuals &amp; Estimates (NYSE:AGBK) - TradingView</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>KD Green merger to create green steel and infrastructure hub - scanx.trade</t>
+          <t>AGI Infra schedules board meeting to consider QIP equity fundraising - scanx.trade</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of KD Green Industries Ltd (NSE:KDGREEN) - TradingView</t>
+          <t>Alamos Gold (NYSE:AGI): A Growth-at-a-Reasonable-Price Opportunity - ChartMill</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1548,68 +1556,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>BHAGERIA.NS</t>
+          <t>SILVERTUC.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>Silver Touch Technologies Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>351.0499877929688</v>
+        <v>144.1199951171875</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>364.6499938964844</v>
+        <v>160.8999938964844</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>348</v>
+        <v>142.5200042724609</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>362</v>
+        <v>160.6999969482422</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>334.75</v>
+        <v>146.2799987792969</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>362</v>
+        <v>160.6999969482422</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>274558</v>
+        <v>1166674</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries (BHAGERIA.NS) Surges 5% to ₹318.25, Nears Key Resistance at ₹334 - Rounding Top - siam.in</t>
+          <t>Principle of Polarity at a Key Technical Zone for NSE:SILVERTUC by yatharthshah23 - TradingView</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Q2 FY27 Preview - univest.in</t>
+          <t>Silver Touch Technologies Limited Engaged by Gujarat Urja Vikas Nigam Limited to Provide Comprehensive Management and Oem-Authorised Support of Core It Infrastructure - marketscreener.com</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Silver Touch Technologies Share Price Falls 8.95% Today - Univest</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Ltd Locks at Upper Circuit With 5% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+          <t>Silver Touch Technologies Limited Engaged by Gujarat Urja Vikas Nigam Limited to Provide Comprehensive Management and Oem-Authorised Support of Core It Infrastructure - marketscreener.com</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Gets Conditional Restart Permission After MPCB Approval - scanx.trade</t>
+          <t>Silver (SILVERTUC.NS) Financial Update: The Company Reports Its Latest Available Figures for the Current Session; Price Move: The Share Price Adds 0.84% on the Day - Upward Estimate Revision - siam.in</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1617,68 +1625,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND.NS</t>
+          <t>TEGA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Raymond Limited</t>
+          <t>Tega Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>978</v>
+        <v>1950</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1066</v>
+        <v>2149</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>969.9500122070312</v>
+        <v>1933.300048828125</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1056.449951171875</v>
+        <v>2129</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>978</v>
+        <v>1943</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1056.449951171875</v>
+        <v>2129</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4707939</v>
+        <v>4580597</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8.02</v>
+        <v>9.57</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>600% gains in 5 years and still counting! Raymond stock surges 7%, what's driving the rally? - Livemint</t>
+          <t>Tega Industries shares hit 52-week high on ₹126 crore Kalpataru Projects contract - CNBC TV18 - LinkedIn</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Nykredit A S Purchases Shares of 64,520 Raymond James Financial, Inc. $RJF - MarketBeat</t>
+          <t>Tega Industries Stock Rallies 8% After Subsidiary Bags ₹126 Cr Order From Kalpataru Projects - Trade Brains</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Raymond, Welspun Living, Alok Industries shares rise up to 8%; here's why - businesstoday.in</t>
+          <t>Tega Industries shares rally 11% to hit 52-week high as subsidiary bags order worth ₹126 crore - Upstox</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Raymond shares jump 20% to hit all-time high after three days of consecutive gains; further growth tailwinds ahead? - Upstox</t>
+          <t>Tega Industries shares surge nearly 10% on ₹126 crore Kalpataru Projects contract - CNBC TV18</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Raymond surges 20% on huge volume; here's why stock rose 66% in 11 days - Business Standard</t>
+          <t>Tega Industries Hits 52-Week High on Rs 126 Cr Order - Equitypandit</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1686,68 +1694,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>FILATEX.NS</t>
+          <t>CENTUM.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Limited</t>
+          <t>Centum Electronics Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>94.69999694824219</v>
+        <v>4351.5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>102.879997253418</v>
+        <v>4805</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>92.91000366210938</v>
+        <v>4350</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>101.1999969482422</v>
+        <v>4739.2001953125</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>93.83000183105469</v>
+        <v>4333.2998046875</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>101.1999969482422</v>
+        <v>4739.2001953125</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>11384970</v>
+        <v>296060</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.85</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Top stocks to buy under ₹100: Equitas Small, Meghmani Organics, Filatex by Sumeet Bagadia; check stop-loss, target price - Livemint</t>
+          <t>Centum Electronics Share Price - Upstox</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Top stocks to buy under ₹100: Equitas Small, Meghmani Organics, Filatex by Sumeet Bagadia; check stop-loss, target price - Livemint</t>
+          <t>Centum Electronics Share Price - Upstox</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Filatex India 52 Week High Streak: Key Analysis - univest.in</t>
+          <t>Centum Electronics Ltd. Share Price Today: key stock move - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Q4 FY26 Earnings Call: EBITDA Surges 34.5%, INR 690 Crore CAPEX Underway - scanx.trade</t>
+          <t>Centum Electronics Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Filatex India Limited (NSE:FILATEX) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Centum Electronics schedules virtual analyst meet on September 9 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1755,68 +1763,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>OAL.NS</t>
+          <t>EMBDL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Limited</t>
+          <t>Embassy Developments Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>514.1500244140625</v>
+        <v>53.88000106811523</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>555</v>
+        <v>59.2599983215332</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>514.1500244140625</v>
+        <v>53.88000106811523</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>554.4000244140625</v>
+        <v>58.88999938964844</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>514.1500244140625</v>
+        <v>53.88000106811523</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>554.4000244140625</v>
+        <v>58.88999938964844</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>46361</v>
+        <v>5985106</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.83</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Share Price update: OAL gains 12.35% - univest.in</t>
+          <t>Embassy Developments opens special window for physical share transfers - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Herter's J9 - For Sale, Used - Excellent Condition - Guns.com</t>
+          <t>Embassy Developments opens special window for physical share transfers - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>OAL FY26 Net Profit Falls 90.7% on Higher Costs - scanx.trade</t>
+          <t>Embassy Developments Limited Reports Q3FY26 Losses, Management Addresses Challenges in Earnings Call - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Share Price rises 8.72%; valuation view - univest.in</t>
+          <t>Catalyst Trusteeship pledges 5,35,40,000 Embassy Developments shares - scanx.trade</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Share Price rises 9.72% on key metrics - univest.in</t>
+          <t>Embassy Developments: Pledge on 4.43 Cr Shares Released by Catalyst Trusteeship - investywise.com</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1824,61 +1832,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>KROSS.NS</t>
+          <t>RSL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Kross Limited</t>
+          <t>Rajputana Stainless Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>261.739990234375</v>
+        <v>201.6999969482422</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>237.5</v>
+        <v>180.8500061035156</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>257.3500061035156</v>
+        <v>197.8800048828125</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>239.1900024414062</v>
+        <v>181.2100067138672</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>257.3500061035156</v>
+        <v>197.8800048828125</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4233403</v>
+        <v>1078964</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7.59</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd Share Price Today Near 52-Week High and Valuation - univest.in</t>
+          <t>RAJPUTANA STAINLESS LTD Share Price - Live NSE: RSL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd. Share Price Today: 8.18% Gain and Market Cap - univest.in</t>
+          <t>RAJPUTANA STAINLESS LTD Share Price - Live NSE: RSL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Kross AGM sees 74% voter turnout; all resolutions passed - scanx.trade</t>
+          <t>RSL Q2 2026 Earnings: Revenue Climbs 8.06% YoY to ₹1,005.41 Crore, EPS at ₹7.17, Yet Shares Slip 4.46% - siam.in</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>If EPS Growth Is Important To You, Kross (NSE:KROSS) Presents An Opportunity - simplywall.st</t>
+          <t>Rajputana Stainless Limited (RSL.NS): Steady at ₹181.5 as Stock Consolidates Between Key Levels - Bear Flag - siam.in</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>RSL Textiles (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2013,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2013,68 +2021,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TERAI.NS</t>
+          <t>AZADIND.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Terai Tea Company Limited</t>
+          <t>Azad India Mobility Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>134</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>134</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>104.5</v>
+        <v>73.41000366210938</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>104.5</v>
+        <v>75.36000061035156</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>120</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>104.5</v>
+        <v>75.36000061035156</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>312</v>
+        <v>53291</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-12.92</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Terai Tea Company Submits Q4 FY26 Dematerialisation Certificate to Stock Exchanges - scanx.trade</t>
+          <t>AZADIND Stock Price and Chart — NSE:AZADIND - TradingView</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Terai Tea Company Submits Q4 FY26 Dematerialisation Certificate to Stock Exchanges - scanx.trade</t>
+          <t>Azad India Mobility Ltd. (AZADIND) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Terai Tea Co Ltd is Rated Sell by MarketsMOJO - MarketsMojo</t>
+          <t>Azad India Mobility Limited Submits SEBI Compliance Certificate for Q4FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Terai Tea appoints Rajendra Kanodia as WTD at 53rd AGM on Sep 30 - scanx.trade</t>
+          <t>Azad India Mobility Ltd. (AZADIND) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Terai Tea FY26 Results: Net profit surges 161% to ₹96 crore - scanx.trade</t>
+          <t>Azad India Mobility Limited rolls out First batch of 12 EV Luxury Buses - EquityBulls</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2082,68 +2090,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>TREL.NS</t>
+          <t>OFSS.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Transindia Real Estate Limited</t>
+          <t>Oracle Financial Services Software Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30</v>
+        <v>11787</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>30.93000030517578</v>
+        <v>11787</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>26.31999969482422</v>
+        <v>10900</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>26.79999923706055</v>
+        <v>10911</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>29.65999984741211</v>
+        <v>11896</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>26.79999923706055</v>
+        <v>10911</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>580114</v>
+        <v>565241</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.640000000000001</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>TREL Share Price Today: rise, valuation and sector view - univest.in</t>
+          <t>Why Oracle Shares are falling today? Explained - India Infoline</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>NFL Fines Cardinals Backup Cornerback Kei’Trel Clark $6,651 for Writing ‘Glory Be 2 God’ on His Eyeblack - People.com</t>
+          <t>OFSS Clarifies Oracle Data Centre Debt Rumour Impact - Kalkine India</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Transindia Real Estate completes acquisition of 48.28% stake in Comptech Solutions for ₹24 cr - scanx.trade</t>
+          <t>OFSS shares fall 6.5% as report says Oracle's $18-billion data centre debt under pressure - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Should You Think About Buying Trelleborg AB (publ) (STO:TREL B) Now? - simplywall.st</t>
+          <t>OFSS shares tumble 7%; Wipro, Coforge, Infosys shares down up to 2%. Why are IT stocks under pressure toda - The Economic Times</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Trelleborg steps up share buybacks to refine capital structure - The Globe and Mail</t>
+          <t>OFSS shares crack 7%; what's spooking Nifty IT's best-performing stock? - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2151,68 +2159,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ASTAR.NS</t>
+          <t>MACPOWER.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Asian Star Company Limited</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>814.9500122070312</v>
+        <v>2111</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>848</v>
+        <v>2175</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>725.5</v>
+        <v>1817.699951171875</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>730.4000244140625</v>
+        <v>1955.300048828125</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>807.3499755859375</v>
+        <v>2104.5</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>730.4000244140625</v>
+        <v>1955.300048828125</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>14498</v>
+        <v>221525</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.529999999999999</v>
+        <v>-7.09</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Asian Star Company Ltd. Upper Circuit Streak: Day 2 Price and Data - univest.in</t>
+          <t>Should You Be Adding Macpower CNC Machines (NSE:MACPOWER) To Your Watchlist Today? - simplywall.st</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 8 Stocks That Hit Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Astar Fi Opens Public Beta for Onchain Personal Finance Manager - TradingView</t>
+          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Asian Star Company Ltd. Upper Circuit Today: Price, Data and Peers - univest.in</t>
+          <t>Macpower CNC Machines Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Astar Price Today in Australia | ASTR to AUD Live Price &amp; Chart - Binance</t>
+          <t>Macpower CNC Machines Share Price Today after 8.91% gain - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2220,68 +2228,60 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AZADIND.NS</t>
+          <t>GEEKAYWIRE.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Limited</t>
+          <t>Geekay Wires Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>82.18000030517578</v>
+        <v>33.68999862670898</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>82.18000030517578</v>
+        <v>33.72000122070312</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>73.41000366210938</v>
+        <v>27.79999923706055</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>74.72000122070312</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>82.18000030517578</v>
+        <v>33.25</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>74.72000122070312</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>44228</v>
+        <v>1028113</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-9.08</v>
+        <v>-7.07</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Limited Submits SEBI Compliance Certificate for Q4FY26 - scanx.trade</t>
+          <t>GEEKAYWIRE Q2 2026 Earnings: EPS of ₹2.88 as Revenue Eases 3.82% Year-on-Year - Analyst Coverage Count - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Ltd. (AZADIND) Fundamental and Financial Data - Stocktwits</t>
+          <t>GEEKAYWIRE Q2 2026 Earnings: EPS of ₹2.88 as Revenue Eases 3.82% Year-on-Year - Analyst Coverage Count - siam.in</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Limited rolls out First batch of 12 EV Luxury Buses - EquityBulls</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Azad India Mobility Ltd. (AZADIND) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Azad India Mobility Limited Reports Strong Q3FY26 Results and Completes Regulatory Publication - scanx.trade</t>
-        </is>
-      </c>
+          <t>Geekay Wires Share Price rises 9.23% with valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2289,68 +2289,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SHANTI.NS</t>
+          <t>VAISHALI.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Shanti Overseas (India) Limited</t>
+          <t>Vaishali Pharma Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.190000057220459</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6.300000190734863</v>
+        <v>9.119999885559082</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.380000114440918</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5.639999866485596</v>
+        <v>8.239999771118164</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6.190000057220459</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.639999866485596</v>
+        <v>8.239999771118164</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>250027</v>
+        <v>464234</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-8.890000000000001</v>
+        <v>-6.26</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Ast spacemobile COO Shanti Gupta sells $706,680 in company stock By Investing.com - Investing.com India</t>
+          <t>Vaishali Pharma (VAISHALI.NS) Slips 3.77% to ₹8.68 as Shares Test Support Near ₹8.25 - Beta Neutral Pair - siam.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International approves rights issue up to Rs 100 crore - scanx.trade</t>
+          <t>Vaishali Pharma (VAISHALI.NS) Slips 3.77% to ₹8.68 as Shares Test Support Near ₹8.25 - Beta Neutral Pair - siam.in</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Disco Shanti’s hospital photo leaves fans worried as veteran actress shares ‘Back To Home’ update without - The Times of India</t>
+          <t>Market prediction today: Gift Nifty up; Vaishali Parekh picks three buy or sell stocks — REC, Dabur India, HUL - Livemint</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Buys 1.44 Lakh Shares In Lalithaa Jewellery Mart For ₹3.88 Crore - Sahi</t>
+          <t>Buy or sell: Gift Nifty signals flat start | Vaishali Parekh recommends three stocks to buy today - 31 August 2026 - TradingView</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International approves rights issue up to Rs 100 crore - scanx.trade</t>
+          <t>Market prediction: What Gift Nifty says for opening; Vaishali Parekh gives 3 stocks - HDFC Bank, Cochin Shipyard, Waaree - Livemint</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2358,60 +2358,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE.NS</t>
+          <t>SHIVAMAUTO.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Geekay Wires Limited</t>
+          <t>Shivam Autotech Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33.68999862670898</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>33.72000122070312</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>27.79999923706055</v>
+        <v>17.79000091552734</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>30.61000061035156</v>
+        <v>18.22999954223633</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33.25</v>
+        <v>19.42000007629395</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30.61000061035156</v>
+        <v>18.22999954223633</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>928710</v>
+        <v>778455</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-7.94</v>
+        <v>-6.13</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE Q2 2026 Earnings: EPS of ₹2.88 as Revenue Eases 3.82% Year-on-Year - Analyst Coverage Count - siam.in</t>
+          <t>Shivam Autotech Share Price Falls 8.47% on Price Action - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE Q2 2026 Earnings: EPS of ₹2.88 as Revenue Eases 3.82% Year-on-Year - Analyst Coverage Count - siam.in</t>
+          <t>Shivam Autotech Share Price Falls 8.47% on Price Action - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Geekay Wires Share Price rises 9.23% with valuation view - univest.in</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Shivam Autotech Share Price and Chart Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Shivam Autotech Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Shivam Autotech schedules 21st AGM for September 25, 2026 - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2419,68 +2427,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>OFSS.NS</t>
+          <t>ADDIND.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Limited</t>
+          <t>Addi Industries Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11787</v>
+        <v>82.65000152587891</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11787</v>
+        <v>82.65000152587891</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>11012</v>
+        <v>75</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>11057</v>
+        <v>77.73999786376953</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11896</v>
+        <v>82.65000152587891</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11057</v>
+        <v>77.73999786376953</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>421728</v>
+        <v>207</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.05</v>
+        <v>-5.94</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>OFSS shares fall 6.5% as report says Oracle's $18-billion data centre debt under pressure - Moneycontrol.com</t>
+          <t>ADDIND Stock Price and Chart — NSE:ADDIND - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>OFSS shares tumble 7%; Wipro, Coforge, Infosys shares down up to 2%. Why are IT stocks under pressure toda - The Economic Times</t>
+          <t>Addi Industries Ltd. (ADDIND) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Why Oracle Shares are falling today? Explained - India Infoline</t>
+          <t>Addi Industries Ltd. Share Price Analysis: 8.22% Increase - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>OFSS shares tumble 7%; Wipro, Coforge, Infosys shares down up to 2%. Why are IT stocks under pressure toda - The Economic Times</t>
+          <t>Addi Industries Limited Submits SEBI Compliance Certificate for Q4 FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Share Price - Live NSE: OFSS Stock Price &amp; Chart - Upstox</t>
+          <t>Addi Industries Ltd. (ADDIND) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2488,68 +2496,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER.NS</t>
+          <t>BCG.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Limited</t>
+          <t>Brightcom Group Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2111</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2175</v>
+        <v>10.46000003814697</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1817.699951171875</v>
+        <v>9.529999732971191</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1963</v>
+        <v>9.670000076293945</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2104.5</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1963</v>
+        <v>9.670000076293945</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>195567</v>
+        <v>17102834</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-6.72</v>
+        <v>-5.75</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Should You Be Adding Macpower CNC Machines (NSE:MACPOWER) To Your Watchlist Today? - simplywall.st</t>
+          <t>Brightcom Group (BCG.NS) Holds Steady at ₹9.04: Key Levels to Monitor - Spring Pattern - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
+          <t>Baltic Classifieds Group PLC (BCG.L) Stock Analysis: Assessing the 13.43% Upside Potential - DirectorsTalk Interviews</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
+          <t>Binah Capital Group (BCG) Slides 3.12% as Shares Test Support Zone - Call Resistance - careplusvn.com</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Baltic Classifieds Group PLC (BCG.L) Stock Analysis: Assessing the 13.43% Upside Potential - DirectorsTalk Interviews</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Share Price Today after 8.91% gain - univest.in</t>
+          <t>Binah Capital Group (BCG) Edges Higher: Stock Holds Above Support at $1.41 - Overnight Profile - careplusvn.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2557,60 +2565,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PACIFICI.NS</t>
+          <t>KHANDSE.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Limited</t>
+          <t>Khandwala Securities Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>140.0500030517578</v>
+        <v>17.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>140.0500030517578</v>
+        <v>17.81999969482422</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>139</v>
+        <v>16.59000015258789</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>139.1000061035156</v>
+        <v>17.14999961853027</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>147.9900054931641</v>
+        <v>18.09000015258789</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>139.1000061035156</v>
+        <v>17.14999961853027</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>243</v>
+        <v>5959</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-6.01</v>
+        <v>-5.2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Ltd (PACIFICI): Stone Processor Turnaround Watch - Kalkine India</t>
+          <t>Khandwala Securities (KHANDSE.NS) Slides 4.12% to ₹16.97, Drifting Toward ₹16.12 Support Zone - Systematic Flow - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Pacific Industries Ltd (PACIFICI): Stone Processor Turnaround Watch - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Pacific Industries Ltd - ndtvprofit.com</t>
-        </is>
-      </c>
+          <t>Khandwala Securities (KHANDSE.NS) Slides 4.12% to ₹16.97, Drifting Toward ₹16.12 Support Zone - Systematic Flow - siam.in</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2618,64 +2622,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CARYSIL.NS</t>
+          <t>TARMAT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>CARYSIL LIMITED</t>
+          <t>Tarmat Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1125.699951171875</v>
+        <v>57.7599983215332</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1139</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1060.199951171875</v>
+        <v>52.97999954223633</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1063.900024414062</v>
+        <v>54.7599983215332</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1131.300048828125</v>
+        <v>57.7599983215332</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1063.900024414062</v>
+        <v>54.7599983215332</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>96577</v>
+        <v>45062</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.96</v>
+        <v>-5.19</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Carysil Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Tarmat Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Carysil Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Tarmat sets e-voting and book closure dates for Sept 30 AGM - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Carysil schedules AGM for September 22, confirms ₹3 dividend - scanx.trade</t>
+          <t>Tarmat Ltd. Share Price rise with market cap at Rs 128.43 Cr - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Carysil files FY26 BRSR report; turnover stands at ₹504.62 crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Tarmat Stock Falls 6%: Key Levels and Results - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Dhunseri Tea &amp; Industries Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2683,60 +2691,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>THAKDEV.NS</t>
+          <t>CURAA.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Limited</t>
+          <t>Cura Technologies Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>127.5100021362305</v>
+        <v>72.19999694824219</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>127.5100021362305</v>
+        <v>72.25</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>116.75</v>
+        <v>72.19999694824219</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>120</v>
+        <v>72.19999694824219</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>127.5100021362305</v>
+        <v>76</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>120</v>
+        <v>72.19999694824219</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>120</v>
+        <v>644</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5.89</v>
+        <v>-5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Declines 5.31% to ₹142; Support at ₹134.9 in Focus - Aggressive Growth Picks - siam.in</t>
+          <t>Cura Technologies Slips 2.72%: Stock Approaches Key Support Zone on NSE - Inside Day Breakout - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Share Price Today: 9.97% Decline - univest.in</t>
+          <t>Cura Technologies Confirms EGM Notice Publication: Leadership Changes Scheduled - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Share Price Today: 9.97% Decline - univest.in</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
+          <t>Cura Technologies Confirms EGM Notice Publication: Leadership Changes Scheduled - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - The Economic Times</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2744,68 +2756,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CUPID.NS</t>
+          <t>GRAVISSHO.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Cupid Limited</t>
+          <t>Graviss Hospitality Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>266.2999877929688</v>
+        <v>36.34999847412109</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>271.2999877929688</v>
+        <v>36.34999847412109</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>248</v>
+        <v>36.34000015258789</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>249.6999969482422</v>
+        <v>36.34000015258789</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>265</v>
+        <v>38.25</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>249.6999969482422</v>
+        <v>36.34000015258789</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>32551760</v>
+        <v>817</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5.77</v>
+        <v>-4.99</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Cupid shares reclassified from BSE Group B to Group A - scanx.trade</t>
+          <t>Graviss Hospitality Share Price: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Cupid promoter declares no encumbrance of shares in FY26 - scanx.trade</t>
+          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4:1 Bonus Allotment: How Your 1 Cupid Stock Became 80 Shares In 2 Years; Buy Condom Maker Shares? - Goodreturns</t>
+          <t>Graviss Hospitality Gains 3.45% to ₹29.66; GRAVISSHO.NS Approaches Resistance at ₹31.14 - Standard Deviation - siam.in</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Rs.10,000 to Rs.6.8 lakh in 3 years: Multibagger stock delivers 6,783% return | Do you own? - TradingView</t>
+          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Cupid Share Price Falls 4.75%: Price Action Data - univest.in</t>
+          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2813,68 +2825,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ADDIND.NS</t>
+          <t>SHAHALLOYS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Limited</t>
+          <t>Shah Alloys Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>82.65000152587891</v>
+        <v>89.59999847412109</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>82.65000152587891</v>
+        <v>92.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>75</v>
+        <v>87.87999725341797</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>78</v>
+        <v>87.87999725341797</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>82.65000152587891</v>
+        <v>92.5</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>78</v>
+        <v>87.87999725341797</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>67</v>
+        <v>24631</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.63</v>
+        <v>-4.99</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>ADDIND Stock Price and Chart — NSE:ADDIND - TradingView</t>
+          <t>Shah Alloys Share Price rise: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits</t>
+          <t>Shah Alloys Files Scrutinizer’s Report and Voting Results for 36th AGM - TipRanks</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Ltd. Share Price Analysis: 8.22% Increase - univest.in</t>
+          <t>Shah Alloys Share Price Today: Valuation and Sector View - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Limited Submits SEBI Compliance Certificate for Q4 FY26 - scanx.trade</t>
+          <t>Shah Alloys Share Price News: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Ltd. (ADDIND) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>Shah Alloys SHAHALLOYS 36th AGM voting results 2026 - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2882,56 +2894,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>KANCOTEA.NS</t>
+          <t>BURNPUR.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Limited</t>
+          <t>Burnpur Cement Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>55</v>
+        <v>17.8799991607666</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>55</v>
+        <v>17.8799991607666</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>52.5</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>52.5</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>55.61999893188477</v>
+        <v>17.85000038146973</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>52.5</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>39</v>
+        <v>26077</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5.61</v>
+        <v>-4.99</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Kanco Tea &amp; Industries Ltd. (NSE:KANCOTEA) - TradingView</t>
+          <t>Burnpur Cement secures BSE approval for promoter reclassification - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Kanco Tea &amp; Industries Ltd. (NSE:KANCOTEA) - TradingView</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Burnpur Cement secures BSE approval for promoter reclassification - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Burnpur Cement BURNPUR Promoter Reclassification 2026 - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Price Band Hitters on September 7, 2026 at 12:00 PM - HDFC Sky</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2939,68 +2963,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KSR.NS</t>
+          <t>SPELS.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Limited</t>
+          <t>SPEL Semiconductor Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>43.20000076293945</v>
+        <v>131.4600067138672</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>43.20000076293945</v>
+        <v>131.4600067138672</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>41.04000091552734</v>
+        <v>131.4600067138672</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>41.04000091552734</v>
+        <v>131.4600067138672</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>43.20000076293945</v>
+        <v>138.3699951171875</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>41.04000091552734</v>
+        <v>131.4600067138672</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>12412</v>
+        <v>23177</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5</v>
+        <v>-4.99</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>SPELS Stock Price and Chart — NSE:SPELS - TradingView</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>UK shares new renderings of Kroger Field fan upgrades - On3</t>
+          <t>SPEL Semiconductor Ltd. (SPELS) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Ltd Locks at Upper Circuit With 5% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+          <t>SPEL Semiconductor Limited Schedules Board Meeting for April 15, 2026 to Review Q3FY26 Results and Corporate Actions - scanx.trade</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Share Price in Focus on Bulk Deals - univest.in</t>
+          <t>SPEL Semiconductor Limited Files SEBI SAST Compliance Declaration for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear AGM passes FY26 results; promoters vote 100% in favour - scanx.trade</t>
+          <t>SPEL Semiconductor Share Price Today - SPEL Semiconductor Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3008,68 +3032,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>LASA.NS</t>
+          <t>AKSHOPTFBR.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics Limited</t>
+          <t>Aksh Optifibre Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5.889999866485596</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5.889999866485596</v>
+        <v>7.889999866485596</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5.889999866485596</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>5.889999866485596</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6.199999809265137</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5.889999866485596</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>13388</v>
+        <v>304309</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5</v>
+        <v>-4.97</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics Bull Case vs Bear Case for 2026 - univest.in</t>
+          <t>Aksh Optifibre Share Price - Upstox</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics FY26 Results: Net loss widens 131% to ₹3,409 lakh - scanx.trade</t>
+          <t>Aksh Optifibre Share Price - Upstox</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Lasa Supergenerics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Lasa Supergenerics FY26 Results: Net loss widens 131% to ₹3,409 lakh - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Lasa (LASA.NS) Latest: Posts a 1.57% Gain to ₹7.10 on the Day; Next Test: the Supplied Trading Band Runs From ₹6.74 to ₹7.46 in the Available Record - Pre-Earnings Momentum - siam.in</t>
-        </is>
-      </c>
+          <t>AKSHOPTFBR Q2 2026 Earnings: Net Loss of ₹0.8 Per Share as Revenue Declines 2.2% YoY - Balance Sheet Strength - siam.in</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3077,68 +3093,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GRAVISSHO.NS</t>
+          <t>SEJALLTD.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Limited</t>
+          <t>Sejal Glass Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>36.34999847412109</v>
+        <v>701.1500244140625</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>36.34999847412109</v>
+        <v>710</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>36.34000015258789</v>
+        <v>678.7000122070312</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>36.34000015258789</v>
+        <v>678.9000244140625</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>38.25</v>
+        <v>714.4000244140625</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>36.34000015258789</v>
+        <v>678.9000244140625</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>816</v>
+        <v>14548</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.99</v>
+        <v>-4.97</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Share Price: price action and valuation - univest.in</t>
+          <t>Here's Why We Think Sejal Glass (NSE:SEJALLTD) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Share Price Today: price action review - univest.in</t>
+          <t>Here's Why We Think Sejal Glass (NSE:SEJALLTD) Is Well Worth Watching - simplywall.st</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Gains 3.45% to ₹29.66; GRAVISSHO.NS Approaches Resistance at ₹31.14 - Standard Deviation - siam.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Graviss Hospitality Share Price Today: price action review - univest.in</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
-        </is>
-      </c>
+          <t>Sejal Glass Jun 2026 Earnings: Positive EPS of ₹0.35 on Revenue of ₹36.43 Crore; Stock Slips Marginally - Low Estimate Range - siam.in</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3146,68 +3154,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RHETAN.NS</t>
+          <t>SELMC.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Limited</t>
+          <t>SEL Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>26.40999984741211</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>26.40999984741211</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>26.40999984741211</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>26.40999984741211</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v>27.79000091552734</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>26.40999984741211</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>463159</v>
+        <v>19744</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.96</v>
+        <v>-4.97</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - univest.in</t>
+          <t>SEL MANUFACTURING CO LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - univest.in</t>
+          <t>SEL MANUFACTURING CO LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT regularizes Jhanvi Sethi as independent director - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Rhetan TMT Ltd Forms Death Cross, Signalling Potential Bearish Trend - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - ThePrint</t>
-        </is>
-      </c>
+          <t>SELMC Q2 2026 Earnings: Revenue Tumbles 53% YoY, EPS Loss Widens to ₹50.66 - Earnings Growth Forecast - siam.in</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3215,68 +3215,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO.NS</t>
+          <t>RHETAN.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Limited</t>
+          <t>Rhetan TMT Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1295</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1298.800048828125</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1209</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1224.800048828125</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1288.300048828125</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1224.800048828125</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1331653</v>
+        <v>556175</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.93</v>
+        <v>-4.96</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO DIAGNOSTICS LTD Share Price - Upstox</t>
+          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO Share Price Today - MOLBIO DIAGNOSTICS LTD Stock Price Live NSE/BSE - univest.in</t>
+          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO Share Price Today - MOLBIO DIAGNOSTICS LTD Stock Price Live NSE/BSE - univest.in</t>
+          <t>Rhetan TMT regularizes Jhanvi Sethi as independent director - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Recently listed Molbio Diagnostics share price falls 9%: Healthcare stock loses 18.5% in 2 days after blockbuster rally - Livemint</t>
+          <t>Rhetan TMT Ltd Forms Death Cross, Signalling Potential Bearish Trend - MarketsMojo</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Q1FY27 net profit up 523% to ₹52.7 crore on deferred exports - scanx.trade</t>
+          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - ThePrint</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 13:36:46 IST</t>
+          <t>2026-09-21 22:05:01 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3284,61 +3284,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BHAGYANGR.NS</t>
+          <t>MUKESHB.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bhagyanagar India Limited</t>
+          <t>Mukesh Babu Financial Services Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>458.8999938964844</v>
+        <v>127</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>458.8999938964844</v>
+        <v>127</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>424.3999938964844</v>
+        <v>126.3499984741211</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>424.9500122070312</v>
+        <v>126.4199981689453</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>446.7000122070312</v>
+        <v>133</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>424.9500122070312</v>
+        <v>126.4199981689453</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>255405</v>
+        <v>18</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.87</v>
+        <v>-4.95</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Bhagyanagar India Share Price - Upstox</t>
+          <t>Mukesh Babu Financial Services Ltd. - Stocktwits</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bhagyanagar India Limited Announces Voting Results for NCLT-Directed Meetings - scanx.trade</t>
+          <t>Mukesh Babu Financial Services Ltd. - Stocktwits</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bhagyanagar India Limited Announces Voting Results for NCLT-Directed Meetings - scanx.trade</t>
+          <t>PIONRINV Stock Price and Chart — NSE:PIONRINV - TradingView</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Bhagyanagar (BHAGYANGR.NS) Stock: Ends Lower by 1.41% at ₹388.95 in Latest Trading; Level Watch: Traders Can Monitor the ₹369.50-₹408.40 Range in the Latest Reading - Bullish Percent Index - siam.in</t>
+          <t>Mukesh Babu Financial Services Ltd - Equitypandit</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Bhagyanagar India (NSE:BHAGYANGR) Makes An Interesting Case - simplywall.st</t>
+          <t>LKPSEC Stock Price and Chart — NSE:LKPSEC - TradingView</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>ARTEMISMED.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>Artemis Medicare Services Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>177.5399932861328</v>
+        <v>339.0499877929688</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>208.8699951171875</v>
+        <v>346.75</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>174.9299926757812</v>
+        <v>338.1499938964844</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>208.8699951171875</v>
+        <v>341.8500061035156</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>174.0599975585938</v>
+        <v>339.0499877929688</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>208.8699951171875</v>
+        <v>341.8500061035156</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>60933</v>
+        <v>198548</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>20</v>
+        <v>0.83</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Arvee Labs (ARVEE.NS) Surges 18% to ₹193.74: Key Levels to Watch - Volatility Skew - siam.in</t>
+          <t>Artemis Med Service Share Price - upstox.com</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
+          <t>Artemis Med Service Share Price - upstox.com</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Share Price Falls 9.35%: Full Analysis - Univest</t>
+          <t>Artemis Medicare Services Share Price: 52-week high update - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories Stock: Daily Chart Analysis - Kalkine India</t>
+          <t>Artemis (ARTEMISMED.NS) Quarter in Focus: The Company Reports Its Latest Available Figures in Latest Trading; Closing Move: Shares Finish 1.49% Lower in the Available Record - EPS Estimate Trend - siam.in</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>Artemis Medicare Services (NSE:ARTEMISMED): Will It Attend the Anand Rathi G-200 Summit 2026? - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>PROTEAN.NS</t>
+          <t>ORIENTPPR.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov Technologies Limited</t>
+          <t>Orient Paper &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>493</v>
+        <v>17.25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>588.3499755859375</v>
+        <v>17.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>491.5</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>588.3499755859375</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>490.2999877929688</v>
+        <v/>
       </c>
       <c r="J3" s="2" t="n">
-        <v>588.3499755859375</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>7996314</v>
+        <v>60546</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov shares zoom 20% to hit upper circuit; here's what's happening - businesstoday.in</t>
+          <t>Orient (ORIENTPPR.NS) Levels: Moves 2.10% Up to ₹17.49 at the Close; Range Check: the Session Ends Within the Reported Technical Boundaries in Latest Trading - Profitability Factor - siam.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov shares zoom 20% to hit upper circuit; here's what's happening - BusinessToday - IndiaIPO</t>
+          <t>Orient Paper launches e-voting postal ballot for shareholder approval - TipRanks</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov Technologies Ltd leads gainers in 'A' group - Business Standard</t>
+          <t>Orient Paper &amp; Industries Share Price Today: Key Update - Univest</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Protean eGov shares zoom 20% to hit upper circuit; here's what's happening - BusinessToday - IndiaIPO</t>
+          <t>Orient Paper &amp; Industries (NSE: ORIENTPPR): 4 Things to Watch - Kalkine India</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>PROTEAN EGOV TECH Share Price Today Up 17% - Equitymaster</t>
+          <t>Orient Paper launches e-voting postal ballot for shareholder approval - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,51 +691,51 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>TANAA.NS</t>
+          <t>ORIENTCER.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Limited</t>
+          <t>ORIENT CERATECH LIMITED</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>266.3500061035156</v>
+        <v>48.29000091552734</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>319.6000061035156</v>
+        <v>49.43000030517578</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>266.3500061035156</v>
+        <v>47.52999877929688</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>319.6000061035156</v>
+        <v>48.93000030517578</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>266.3500061035156</v>
+        <v/>
       </c>
       <c r="J4" s="2" t="n">
-        <v>319.6000061035156</v>
+        <v>48.93000030517578</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>226450</v>
+        <v>142603</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>19.99</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA): Niche Defence Stock Watch - Kalkine India</t>
+          <t>Orient Ceratech Slips 2.51% to ₹45.51 on NSE as ORIENTCER Tests Support at ₹43.23 - Dividend Growth Stocks - siam.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+          <t>Orient Ceratech Slips 2.51% to ₹45.51 on NSE as ORIENTCER Tests Support at ₹43.23 - Dividend Growth Stocks - siam.in</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+          <t>There's A Lot To Like About Orient Ceratech's (NSE:ORIENTCER) Upcoming ₹0.35 Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr"/>
@@ -744,7 +744,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,56 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>INDORAMA.NS</t>
+          <t>ORIENTCEM.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics (India) Limited</t>
+          <t>Orient Cement Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>91.5</v>
+        <v>125.0699996948242</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>109.2600021362305</v>
+        <v>125.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>91.08999633789062</v>
+        <v>122.5699996948242</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>106.5500030517578</v>
+        <v>123.1500015258789</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>91.05000305175781</v>
+        <v/>
       </c>
       <c r="J5" s="2" t="n">
-        <v>106.5500030517578</v>
+        <v>123.1500015258789</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>13822935</v>
+        <v>301309</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>17.02</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics Share Price - Live NSE: INDORAMA Stock Price &amp; Chart - Upstox</t>
+          <t>Orient Cement (ORIENTCEM.NS) Slips 1.07% to ₹128.16: Stock Holds Above Key Support Zone - Risk Reward Setups - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics Share Price - Live NSE: INDORAMA Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Orient Cement Clarifies CFO Name Discrepancy in KMP Disclosure - TipRanks</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Orient Cement CFO Resignation: Kajal Saxena Steps Down - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Orient Cement Clarifies CFO Name Discrepancy in KMP Disclosure - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Orient Cement provides clarification on key managerial personnel change - Business Upturn</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -809,60 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL.NS</t>
+          <t>ORIENTBELL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Fedders Holding Limited</t>
+          <t>Orient Bell Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>54</v>
+        <v>394.8999938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.47999954223633</v>
+        <v>406.7999877929688</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>54</v>
+        <v>393.0499877929688</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.4900016784668</v>
+        <v>393.5499877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>52.90000152587891</v>
+        <v/>
       </c>
       <c r="J6" s="2" t="n">
-        <v>61.4900016784668</v>
+        <v>393.5499877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>35766255</v>
+        <v>11279</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>16.24</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Fedders Holding Ltd. Share Price Today Near Yearly High - Univest</t>
+          <t>Orient (ORIENTBELL.NS) Quarter in Focus: The Company Reports Its Latest Available Figures under the Current Snapshot; Price Move: The Stock Ends Down 0.91% in the Latest Reading - Subscription Growth Report - siam.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Fedders Holding Ltd. Share Price Today Near Yearly High - Univest</t>
+          <t>Orient Bell (NSE:ORIENTBELL): What Is the Analyst Meet Scheduled for 15 September 2026? - Kalkine India</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Fedders Holding approves NSE direct listing, appoints three new directors - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Orient Bell (NSE:ORIENTBELL): What Is the Analyst Meet Scheduled for 15 September 2026? - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Orient Bell To Hold Analyst And Investor Meeting On September 10 - sahi.com</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>5 Ceramic Stocks India 2026: Strong Future Roadmaps - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -870,64 +890,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AHCL.NS</t>
+          <t>ORCHASP.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Limited</t>
+          <t>Orchasp Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23.15999984741211</v>
+        <v>1.429999947547913</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>27.47999954223633</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>23.14999961853027</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>26.23999977111816</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.89999961853027</v>
+        <v/>
       </c>
       <c r="J7" s="2" t="n">
-        <v>26.23999977111816</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>130243729</v>
+        <v>69114</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>14.59</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
+          <t>Orchasp Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>AHCL Share Price Today Near 52-Week High and Market Cap - Univest</t>
+          <t>Orchasp sets book closure for 32nd AGM on September 30 - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>AHCL Share Price Today Near 52-Week High and Market Cap - Univest</t>
+          <t>Orchasp Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Publishes Record Date Notice Following Postal Ballot Approval - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Orchasp sets book closure for 32nd AGM on September 30 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -935,68 +959,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>GAJA.NS</t>
+          <t>OPTIEMUS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management Limited</t>
+          <t>Optiemus Infracom Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>143</v>
+        <v>590</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>168.3300018310547</v>
+        <v>708.9000244140625</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>141.5</v>
+        <v>590</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>162.7100067138672</v>
+        <v>708.9000244140625</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>142.5</v>
+        <v/>
       </c>
       <c r="J8" s="2" t="n">
-        <v>162.7100067138672</v>
+        <v>708.9000244140625</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>18146677</v>
+        <v>7995347</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>14.18</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Gaja AAM Lists 16% Higher; Stock Ends 5% Up From Issue Price - HDFC Sky</t>
+          <t>Optiemus Infracom To Acquire 51.1% Stake In Joint Venture With Nothing Electronics - sahi.com</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>GAJA ALT ASSET MGT LTD Share Price at Fresh 52-Week Low - Univest</t>
+          <t>Optiemus Infracom To Acquire 51.1% Stake In Joint Venture With Nothing Electronics - sahi.com</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>India's Gaja Alternative Asset valued at $251.5 million in trading debut - Reuters</t>
+          <t>Optiemus Infracom shares surge 14% as screen protectors for smartphones brought under BIS effective April... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Gaja Alternative shares make decent listing gains at 16% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+          <t>Optiemus Infracom Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Gaja Alternative shares fall 3.5% even as total income rises 27% in Q1 to Rs 52 crore - TradingView</t>
+          <t>OPTIEMUS.NS Q2 2026 Earnings: EPS Holds at ₹7.39 as Shares Rise 6.83% Despite Revenue Dip - Peak Earnings Alert - siam.in</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1004,68 +1028,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN.NS</t>
+          <t>ONIXSOLAR.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>KPI Green Energy Limited</t>
+          <t>Onix Solar Energy Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>284.5</v>
+        <v>328</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>324.7000122070312</v>
+        <v>338</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>283.8999938964844</v>
+        <v>322.6000061035156</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>321.3999938964844</v>
+        <v>322.6000061035156</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>284.4500122070312</v>
+        <v/>
       </c>
       <c r="J9" s="2" t="n">
-        <v>321.3999938964844</v>
+        <v>322.6000061035156</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>18325693</v>
+        <v>246559</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>12.99</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>KPI Global Infrastructure Share Price - Live NSE: KPIGREEN Stock Price &amp; Chart - Upstox</t>
+          <t>ONIXSOLAR Stock Price and Chart — NSE:ONIXSOLAR - TradingView</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>KPI Global Infrastructure Share Price - Live NSE: KPIGREEN Stock Price &amp; Chart - Upstox</t>
+          <t>ONIXSOLAR Stock Price and Chart — NSE:ONIXSOLAR - TradingView</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And KPI Green Energy (NSE:KPIGREEN) Passed With Ease - simplywall.st</t>
+          <t>Onix Solar Energy Limited Schedules Rights Issue Committee Meeting for May 11, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>KPI Green Energy (KPIGREEN.NS) Slips 1.91% to ₹282 as ₹267.9 Support Comes Into Focus - Growth Stock Picks - siam.in</t>
+          <t>Onix Solar Energy Limited Board Approves Rights Issue of Up to Rs. 130 Crore - scanx.trade</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>KPI Green Energy (KPIGREEN.NS) Gains 1.24% to ₹307: Renewable Play Nears Key Resistance - Scalping Stock Signals - siam.in</t>
+          <t>Onix Solar Energy Limited Publishes Rights Issue Allotment Basis with Regulatory Compliance - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1073,68 +1097,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ZOTA.NS</t>
+          <t>ONGC.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Zota Health Care LImited</t>
+          <t>Oil &amp; Natural Gas Corporation Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1160</v>
+        <v>235.5099945068359</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1324.400024414062</v>
+        <v>236.3699951171875</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1138.900024414062</v>
+        <v>233.75</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1287.800048828125</v>
+        <v>235.6999969482422</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1144.5</v>
+        <v/>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1287.800048828125</v>
+        <v>235.6999969482422</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>401249</v>
+        <v>5071801</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>12.52</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Zota Health Care Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Stocks to watch: ONGC, Pine Labs, GRSE, Waaree, Lloyds Metals, Aarti Inds - Business Standard</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Zota Health Care Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Stocks to watch: ONGC, Pine Labs, GRSE, Waaree, Lloyds Metals, Aarti Inds - Business Standard</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Zota Health Care FY26 revenue surges 84% to ₹53,866 lakhs - scanx.trade</t>
+          <t>ONGC strikes gas at deepwater well in Mahanadi offshore Basin; what investors need to know - upstox.com</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Zota (ZOTA.NS) Stock Analysis: -1.12% Down — Bearish Signals to Watch 2026-09-11 - Force Index - siam.in</t>
+          <t>Energy dividend kings: ONGC, IOCL, BPCL, Castrol or IGL, which stock delivers the highest payout? Comparison - TradingView</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Zota Healthcare - Mukul Agrawal’s portfolio: Top 5 stock holdings and their one-month performance - The Economic Times</t>
+          <t>ONGC finds gas near Odisha coast in Mahanadi deepwater basin - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1142,68 +1166,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>JAYKAY.NS</t>
+          <t>ONEPOINT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Limited</t>
+          <t>One Point One Solutions Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>169.6900024414062</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>190.7599945068359</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>169.6799926757812</v>
+        <v>60.04999923706055</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>187.5599975585938</v>
+        <v>63.31999969482422</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>167.1799926757812</v>
+        <v/>
       </c>
       <c r="J11" s="2" t="n">
-        <v>187.5599975585938</v>
+        <v>63.31999969482422</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4432715</v>
+        <v>5843270</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>12.19</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value of Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares – BSE:JAYKAY_RE1 - TradingView</t>
+          <t>One Point One Solutions Q2 2026 Earnings: EPS of ₹1.45 and 22.24% Revenue Growth Drive 5.08% Stock Uptick - Guidance Update - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value of Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares – BSE:JAYKAY_RE1 - TradingView</t>
+          <t>One Point One Solutions to Brief Analysts and Investors in Kochi - TipRanks</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Subsidiary Neumesh Labs Receives MCA Investigation Notice - scanx.trade</t>
+          <t>One Point One Solutions to Brief Analysts and Investors in Kochi - TipRanks</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Ltd. - RE1 Share Price Live Today - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares Earnings and Revenue – NSE:JAYKAY_RE1 - TradingView</t>
-        </is>
-      </c>
+          <t>One Point One Solutions wins 'Best Use of AI in Customer Service' award at India CX Summit 2026 - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1211,68 +1231,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CROWN.NS</t>
+          <t>ONEGLOBAL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Crown Lifters Limited</t>
+          <t>One Global Service Provider Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>108</v>
+        <v>537.2999877929688</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>127.9000015258789</v>
+        <v>552</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>108</v>
+        <v>519.9500122070312</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>121.379997253418</v>
+        <v>538</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>108.4800033569336</v>
+        <v/>
       </c>
       <c r="J12" s="2" t="n">
-        <v>121.379997253418</v>
+        <v>538</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>283904</v>
+        <v>5482</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>11.89</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Crown Lifters Share Price Today: Rs 120 and key metrics - Univest</t>
+          <t>One Global Service Provider Limited Approves Revised Issue Pricing for Acquisition of Matrix Labs Entities - EquityBulls</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Crown Castle stock falls after dividend cut as analysts reassess income appeal - AD HOC NEWS</t>
+          <t>Oneglobal completes takeover of Hong Kong crypto specialist Fraction - InsuranceAsia News</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>JPMorgan upgrades Crown Holdings stock rating on valuation By Investing.com - Investing.com India</t>
+          <t>Oneglobal completes takeover of Hong Kong crypto specialist Fraction - InsuranceAsia News</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>L'Oreal steals French stock market crown from LVMH - Reuters</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>L’Oréal Steals French Stock Market Crown From LVMH - The Business of Fashion</t>
-        </is>
-      </c>
+          <t>One Global Service Provider to consider preferential equity issuance at Sep 3 board - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1280,68 +1296,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER.NS</t>
+          <t>RENUKA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Limited</t>
+          <t>Shree Renuka Sugars Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>302</v>
+        <v>22.92000007629395</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>338</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>296.8999938964844</v>
+        <v>22.90999984741211</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>334.5499877929688</v>
+        <v>23.01000022888184</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>299.25</v>
+        <v/>
       </c>
       <c r="J13" s="2" t="n">
-        <v>334.5499877929688</v>
+        <v>23.01000022888184</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>20650744</v>
+        <v>4571350</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Share Price rises 9.01% - Univest</t>
+          <t>Shree Renuka Sugars Share Price - upstox.com</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Share Price rises 9.01% - Univest</t>
+          <t>Shree Renuka Sugars Share Price - upstox.com</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision completes dispatch of ₹330 crore rights issue offer - scanx.trade</t>
+          <t>Shree Renuka Sugars (RENUKA.NS) Slips 2% to ₹23.01 as Stock Tests Lower End of Range - RVOL Spike - siam.in</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Press Release Distribution India - Business Wire India</t>
+          <t>Shree Renuka Sugars Share Price today rises to Rs 25.20 - Univest</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering share price hits 52-week high | What's behind the rally? - TradingView</t>
+          <t>Sugar stocks rebound; Balrampur, Shree Renuka, Triveni rally up to 13% - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1349,68 +1365,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TARSONS.NS</t>
+          <t>OMINFRAL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Limited</t>
+          <t>OM INFRA LIMITED</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>305.8999938964844</v>
+        <v>80.59999847412109</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>356.8500061035156</v>
+        <v>80.69000244140625</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>305.0499877929688</v>
+        <v>78.41999816894531</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>341.2999877929688</v>
+        <v>79.18000030517578</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>306.1000061035156</v>
+        <v/>
       </c>
       <c r="J14" s="2" t="n">
-        <v>341.2999877929688</v>
+        <v>79.18000030517578</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5943251</v>
+        <v>21819</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Share Price Rise: Fundamental Analysis - Univest</t>
+          <t>OM (OMINFRAL.NS) Chart: Retreats 0.44% to ₹83.38; Next Session: the Price Remains Bounded by the Supplied Support and Resistance - Scalping Stock Signals - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Share Price Rise: Fundamental Analysis - Univest</t>
+          <t>Om Infra OMINFRAL Auditor Appointment 54th AGM 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Tarsons (TARSONS.NS) Shares: Finishes 0.39% Down at ₹345.50 on the Day; Chart View: Support at ₹328.22 and Resistance at ₹362.78 Frame the Range for the Current Session - Outside Reversal - siam.in</t>
+          <t>Om Infra OMINFRAL 54th AGM outcomes September 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products Ltd Downgraded to Strong Sell Amid Weak Fundamentals and Valuation Concerns - MarketsMojo</t>
+          <t>Om Infra OMINFRAL Auditor Appointment 54th AGM 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Tarsons Products schedules 43rd AGM for September 24, 2026 - scanx.trade</t>
+          <t>Om Infra sets Sep 12 AGM; proposes ₹0.50 dividend, auditor appointment - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1418,68 +1434,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>JASH.NS</t>
+          <t>OMAXE.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Jash Engineering Limited</t>
+          <t>Omaxe Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>551</v>
+        <v>114</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>596.9000244140625</v>
+        <v>119.3399963378906</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>541</v>
+        <v>114</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>575.9000244140625</v>
+        <v>115.8000030517578</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>521.1500244140625</v>
+        <v/>
       </c>
       <c r="J15" s="2" t="n">
-        <v>575.9000244140625</v>
+        <v>115.8000030517578</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>14684581</v>
+        <v>413910</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10.51</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Jash Engineering Share Price Today, Jash Engineering Stock Price Live NSE/BSE Updates - The Economic Times</t>
+          <t>Omaxe Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Jash Engineering Share Price Today, Jash Engineering Stock Price Live NSE/BSE Updates - The Economic Times</t>
+          <t>Omaxe Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Jash Engineering Limited (NSE:JASH) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>SAT dismisses Omaxe appeal against SEBI order over financial statement irregularities - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Jash Engineering promoter Rohan Patel sells 10,000 equity shares - scanx.trade</t>
+          <t>Omaxe accepts resignation of Neeraj Arora as Vice President – PMO - scanx.trade</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Jash (JASH.NS) Earnings Update: The Report Supplies Updated Headline Figures at the Close; Market Response: Shares Move Higher 2.98% on the Day - Balance Sheet Strength - siam.in</t>
+          <t>Omaxe Ltd. Share Price Update: Rise, Fundamentals, Sector - Univest</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1487,68 +1503,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AGI.NS</t>
+          <t>OMAXAUTO.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>AGI Greenpac Limited</t>
+          <t>Omax Autos Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>744.0499877929688</v>
+        <v>191.4299926757812</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>824</v>
+        <v>197.2200012207031</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>744</v>
+        <v>187.2200012207031</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>819.3499755859375</v>
+        <v>188.9700012207031</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>745.0499877929688</v>
+        <v/>
       </c>
       <c r="J16" s="2" t="n">
-        <v>819.3499755859375</v>
+        <v>188.9700012207031</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1015912</v>
+        <v>42655</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>AGI Greenpac Share Price Today: Price Rise and Valuation - Univest</t>
+          <t>Omax Autos Eases to ₹184.48; Stock Holds Above Key Support Amid Consolidation - KAMA Signal - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>AGI Infra schedules board meeting to consider QIP equity fundraising - scanx.trade</t>
+          <t>Omax Autos Eases to ₹184.48; Stock Holds Above Key Support Amid Consolidation - KAMA Signal - siam.in</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>AGI Inc Class A Actuals &amp; Estimates (NYSE:AGBK) - TradingView</t>
+          <t>Omax (OMAXAUTO.NS) Earnings Snapshot: The Report Provides a New Financial Snapshot under the Current Snapshot; Shares Move 0.44% Down in Latest Trading - Slow Growth Warning - siam.in</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>AGI Infra schedules board meeting to consider QIP equity fundraising - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Alamos Gold (NYSE:AGI): A Growth-at-a-Reasonable-Price Opportunity - ChartMill</t>
-        </is>
-      </c>
+          <t>Omax Autos shareholders approve all AGM resolutions with 98.37% assent - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1556,68 +1568,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SILVERTUC.NS</t>
+          <t>OLECTRA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Silver Touch Technologies Limited</t>
+          <t>Olectra Greentech Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>144.1199951171875</v>
+        <v>1212</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>160.8999938964844</v>
+        <v>1256</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>142.5200042724609</v>
+        <v>1210.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>160.6999969482422</v>
+        <v>1226.400024414062</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>146.2799987792969</v>
+        <v/>
       </c>
       <c r="J17" s="2" t="n">
-        <v>160.6999969482422</v>
+        <v>1226.400024414062</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1166674</v>
+        <v>440337</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Principle of Polarity at a Key Technical Zone for NSE:SILVERTUC by yatharthshah23 - TradingView</t>
+          <t>Olectra Greentech: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Silver Touch Technologies Limited Engaged by Gujarat Urja Vikas Nigam Limited to Provide Comprehensive Management and Oem-Authorised Support of Core It Infrastructure - marketscreener.com</t>
+          <t>Olectra Greentech: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Silver Touch Technologies Share Price Falls 8.95% Today - Univest</t>
+          <t>Olectra Greentech Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Silver Touch Technologies Limited Engaged by Gujarat Urja Vikas Nigam Limited to Provide Comprehensive Management and Oem-Authorised Support of Core It Infrastructure - marketscreener.com</t>
+          <t>Olectra (OLECTRA.NS) Stock: Falls 0.69% to ₹1,288.60 at the Close; Immediate View: ₹1,224.17 and ₹1,353.03 Define the Nearby Reference Levels in Latest Trading - Fast Moving Stocks - siam.in</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Silver (SILVERTUC.NS) Financial Update: The Company Reports Its Latest Available Figures for the Current Session; Price Move: The Share Price Adds 0.84% on the Day - Upward Estimate Revision - siam.in</t>
+          <t>Olectra Greentech files FY26 sustainability report with stock exchanges - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1625,68 +1637,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TEGA.NS</t>
+          <t>OAL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries Limited</t>
+          <t>Oriental Aromatics Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1950</v>
+        <v>554.7999877929688</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2149</v>
+        <v>570</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1933.300048828125</v>
+        <v>550.0499877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2129</v>
+        <v>562.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1943</v>
+        <v/>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2129</v>
+        <v>562.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4580597</v>
+        <v>56252</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9.57</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries shares hit 52-week high on ₹126 crore Kalpataru Projects contract - CNBC TV18 - LinkedIn</t>
+          <t>Oriental Aromatics Share Price Update With Valuation View - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries Stock Rallies 8% After Subsidiary Bags ₹126 Cr Order From Kalpataru Projects - Trade Brains</t>
+          <t>Oriental Aromatics Share Price Update With Valuation View - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries shares rally 11% to hit 52-week high as subsidiary bags order worth ₹126 crore - Upstox</t>
+          <t>OAL FY26 Net Profit Falls 90.7% on Higher Costs - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries shares surge nearly 10% on ₹126 crore Kalpataru Projects contract - CNBC TV18</t>
+          <t>Oriental Aromatics Share Price update: OAL gains 12.35% - Univest</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Tega Industries Hits 52-Week High on Rs 126 Cr Order - Equitypandit</t>
+          <t>Oriental Aromatics Share Price rises 8.72%; valuation view - Univest</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1694,68 +1706,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CENTUM.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4351.5</v>
+        <v>335</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4805</v>
+        <v>337.6499938964844</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4350</v>
+        <v>330.2999877929688</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>4739.2001953125</v>
+        <v>333.2999877929688</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4333.2998046875</v>
+        <v/>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4739.2001953125</v>
+        <v>333.2999877929688</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>296060</v>
+        <v>740788</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Share Price - Upstox</t>
+          <t>Nykaa Share Price Today: Decline, Technicals, Fundamentals - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Share Price - Upstox</t>
+          <t>Nykaa Q2 FY27 Results Preview - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Ltd. Share Price Today: key stock move - Univest</t>
+          <t>Nykaa Share Price rises 2.33%: valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Ltd. Stock News - Value Research</t>
+          <t>Nykaa rally: Planning to buy fashion retailer stock after recent up move? Here's what analyst says - Business Today</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics schedules virtual analyst meet on September 9 - scanx.trade</t>
+          <t>Nykaa shares: Elara Capital hikes target price; sees 43% upside potential - Business Today</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1763,68 +1775,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EMBDL.NS</t>
+          <t>NUVOCO.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Embassy Developments Limited</t>
+          <t>Nuvoco Vistas Corporation Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>53.88000106811523</v>
+        <v>330.5499877929688</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>59.2599983215332</v>
+        <v>339.3999938964844</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>53.88000106811523</v>
+        <v>330.5499877929688</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>58.88999938964844</v>
+        <v>337.7000122070312</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>53.88000106811523</v>
+        <v/>
       </c>
       <c r="J20" s="2" t="n">
-        <v>58.88999938964844</v>
+        <v>337.7000122070312</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>5985106</v>
+        <v>115715</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Embassy Developments opens special window for physical share transfers - scanx.trade</t>
+          <t>Nuvoco Vistas to host in-person meet with Ambit Capital - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Embassy Developments opens special window for physical share transfers - scanx.trade</t>
+          <t>Nuvoco Vistas enters into Rs 300 crore option agreement for Series B CCDs - Business Upturn</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Embassy Developments Limited Reports Q3FY26 Losses, Management Addresses Challenges in Earnings Call - scanx.trade</t>
+          <t>Nuvoco Vistas AGM approves all resolutions, appoints new auditors - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Catalyst Trusteeship pledges 5,35,40,000 Embassy Developments shares - scanx.trade</t>
+          <t>Nuvoco Vistas schedules in-person investor meeting with Mirae Asset on Sep 3 - scanx.trade</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Embassy Developments: Pledge on 4.43 Cr Shares Released by Catalyst Trusteeship - investywise.com</t>
+          <t>Nuvoco Vistas discloses independent ESG rating of 67.1 for FY26 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1832,61 +1844,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RSL.NS</t>
+          <t>NUVAMA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>Nuvama Wealth Management Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>182</v>
+        <v>1689.400024414062</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>201.6999969482422</v>
+        <v>1710</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>180.8500061035156</v>
+        <v>1678</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>197.8800048828125</v>
+        <v>1684.5</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>181.2100067138672</v>
+        <v/>
       </c>
       <c r="J21" s="2" t="n">
-        <v>197.8800048828125</v>
+        <v>1684.5</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1078964</v>
+        <v>89297</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>RAJPUTANA STAINLESS LTD Share Price - Live NSE: RSL Stock Price &amp; Chart - Upstox</t>
+          <t>Dixon Tech shares: Why Nuvama raised target price, cut FY27 earnings estimate - Business Today</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>RAJPUTANA STAINLESS LTD Share Price - Live NSE: RSL Stock Price &amp; Chart - Upstox</t>
+          <t>Dixon Tech shares: Why Nuvama raised target price, cut FY27 earnings estimate - Business Today</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>RSL Q2 2026 Earnings: Revenue Climbs 8.06% YoY to ₹1,005.41 Crore, EPS at ₹7.17, Yet Shares Slip 4.46% - siam.in</t>
+          <t>Race for Nuvama Wealth: EQT, Brookfield, ChrysCapital, Axight picked for next round - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited (RSL.NS): Steady at ₹181.5 as Stock Consolidates Between Key Levels - Bear Flag - siam.in</t>
+          <t>Nuvama Wealth Management Share Price Today: Key Analysis - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>RSL Textiles (India) Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>Solar Industries shares plunge 17% in 2 days. Why Jefferies, Nuvama still see up to 46% upside - The Economic Times</t>
         </is>
       </c>
     </row>
@@ -1907,14 +1919,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2013,7 +2025,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2021,68 +2033,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AZADIND.NS</t>
+          <t>AARNAV.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Limited</t>
+          <t>Aarnav Fashions Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>82.18000030517578</v>
+        <v>31.54999923706055</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>82.18000030517578</v>
+        <v>31.92000007629395</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>73.41000366210938</v>
+        <v>31.11000061035156</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>75.36000061035156</v>
+        <v>31.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>82.18000030517578</v>
+        <v>32.56999969482422</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>75.36000061035156</v>
+        <v>31.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>53291</v>
+        <v>4416</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-3.29</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>AZADIND Stock Price and Chart — NSE:AZADIND - TradingView</t>
+          <t>Aarnav Fashions Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Ltd. (AZADIND) Fundamental and Financial Data - Stocktwits</t>
+          <t>Aarnav Fashions Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Limited Submits SEBI Compliance Certificate for Q4FY26 - scanx.trade</t>
+          <t>Aarnav Fashions Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Ltd. (AZADIND) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>Aarnav Fashions FY26 net profit rises 1.2% to ₹934.63 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Azad India Mobility Limited rolls out First batch of 12 EV Luxury Buses - EquityBulls</t>
+          <t>Aarnav Fashions Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2090,68 +2102,56 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>OFSS.NS</t>
+          <t>DISAQ.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Limited</t>
+          <t>Disa India Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11787</v>
+        <v>11905</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>11787</v>
+        <v>12117</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>10900</v>
+        <v>11905</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10911</v>
+        <v>12052</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11896</v>
+        <v>12134</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10911</v>
+        <v>12052</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>565241</v>
+        <v>23</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.279999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Why Oracle Shares are falling today? Explained - India Infoline</t>
+          <t>Disa India Ltd (DISAQ.NS) Climbs 2.42% to ₹12,008: A Test of the ₹12,608 Resistance Zone? - Stop Run - siam.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>OFSS Clarifies Oracle Data Centre Debt Rumour Impact - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>OFSS shares fall 6.5% as report says Oracle's $18-billion data centre debt under pressure - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>OFSS shares tumble 7%; Wipro, Coforge, Infosys shares down up to 2%. Why are IT stocks under pressure toda - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>OFSS shares crack 7%; what's spooking Nifty IT's best-performing stock? - Business Standard</t>
-        </is>
-      </c>
+          <t>Disa India Ltd (DISAQ.NS) Climbs 2.42% to ₹12,008: A Test of the ₹12,608 Resistance Zone? - Stop Run - siam.in</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2159,68 +2159,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER.NS</t>
+          <t>OMINFRAL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Limited</t>
+          <t>OM INFRA LIMITED</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2111</v>
+        <v>80.59999847412109</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2175</v>
+        <v>80.69000244140625</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1817.699951171875</v>
+        <v>78.41999816894531</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1955.300048828125</v>
+        <v>79.18000030517578</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2104.5</v>
+        <v/>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1955.300048828125</v>
+        <v>79.18000030517578</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>221525</v>
+        <v>21819</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.09</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Should You Be Adding Macpower CNC Machines (NSE:MACPOWER) To Your Watchlist Today? - simplywall.st</t>
+          <t>OM (OMINFRAL.NS) Chart: Retreats 0.44% to ₹83.38; Next Session: the Price Remains Bounded by the Supplied Support and Resistance - Scalping Stock Signals - siam.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
+          <t>Om Infra OMINFRAL Auditor Appointment 54th AGM 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
+          <t>Om Infra OMINFRAL 54th AGM outcomes September 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Om Infra OMINFRAL Auditor Appointment 54th AGM 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Share Price Today after 8.91% gain - Univest</t>
+          <t>Om Infra sets Sep 12 AGM; proposes ₹0.50 dividend, auditor appointment - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2228,60 +2228,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE.NS</t>
+          <t>ORIENTPPR.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Geekay Wires Limited</t>
+          <t>Orient Paper &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33.68999862670898</v>
+        <v>17.25</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>33.72000122070312</v>
+        <v>17.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>27.79999923706055</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>30.89999961853027</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33.25</v>
+        <v/>
       </c>
       <c r="J5" s="2" t="n">
-        <v>30.89999961853027</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1028113</v>
+        <v>60546</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.07</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE Q2 2026 Earnings: EPS of ₹2.88 as Revenue Eases 3.82% Year-on-Year - Analyst Coverage Count - siam.in</t>
+          <t>Orient (ORIENTPPR.NS) Levels: Moves 2.10% Up to ₹17.49 at the Close; Range Check: the Session Ends Within the Reported Technical Boundaries in Latest Trading - Profitability Factor - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE Q2 2026 Earnings: EPS of ₹2.88 as Revenue Eases 3.82% Year-on-Year - Analyst Coverage Count - siam.in</t>
+          <t>Orient Paper launches e-voting postal ballot for shareholder approval - TipRanks</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Geekay Wires Share Price rises 9.23% with valuation view - Univest</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Orient Paper &amp; Industries Share Price Today: Key Update - Univest</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Orient Paper &amp; Industries (NSE: ORIENTPPR): 4 Things to Watch - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Orient Paper launches e-voting postal ballot for shareholder approval - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2289,68 +2297,60 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>VAISHALI.NS</t>
+          <t>ORIENTCER.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Vaishali Pharma Limited</t>
+          <t>ORIENT CERATECH LIMITED</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>9.090000152587891</v>
+        <v>48.29000091552734</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>9.119999885559082</v>
+        <v>49.43000030517578</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8.159999847412109</v>
+        <v>47.52999877929688</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8.239999771118164</v>
+        <v>48.93000030517578</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8.789999961853027</v>
+        <v/>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8.239999771118164</v>
+        <v>48.93000030517578</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>464234</v>
+        <v>142603</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.26</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Vaishali Pharma (VAISHALI.NS) Slips 3.77% to ₹8.68 as Shares Test Support Near ₹8.25 - Beta Neutral Pair - siam.in</t>
+          <t>Orient Ceratech Slips 2.51% to ₹45.51 on NSE as ORIENTCER Tests Support at ₹43.23 - Dividend Growth Stocks - siam.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Vaishali Pharma (VAISHALI.NS) Slips 3.77% to ₹8.68 as Shares Test Support Near ₹8.25 - Beta Neutral Pair - siam.in</t>
+          <t>Orient Ceratech Slips 2.51% to ₹45.51 on NSE as ORIENTCER Tests Support at ₹43.23 - Dividend Growth Stocks - siam.in</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Market prediction today: Gift Nifty up; Vaishali Parekh picks three buy or sell stocks — REC, Dabur India, HUL - Livemint</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Buy or sell: Gift Nifty signals flat start | Vaishali Parekh recommends three stocks to buy today - 31 August 2026 - TradingView</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Market prediction: What Gift Nifty says for opening; Vaishali Parekh gives 3 stocks - HDFC Bank, Cochin Shipyard, Waaree - Livemint</t>
-        </is>
-      </c>
+          <t>There's A Lot To Like About Orient Ceratech's (NSE:ORIENTCER) Upcoming ₹0.35 Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2358,68 +2358,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SHIVAMAUTO.NS</t>
+          <t>ORIENTCEM.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Shivam Autotech Limited</t>
+          <t>Orient Cement Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>20.70000076293945</v>
+        <v>125.0699996948242</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>20.70000076293945</v>
+        <v>125.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>17.79000091552734</v>
+        <v>122.5699996948242</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>18.22999954223633</v>
+        <v>123.1500015258789</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19.42000007629395</v>
+        <v/>
       </c>
       <c r="J7" s="2" t="n">
-        <v>18.22999954223633</v>
+        <v>123.1500015258789</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>778455</v>
+        <v>301309</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.13</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Shivam Autotech Share Price Falls 8.47% on Price Action - Univest</t>
+          <t>Orient Cement (ORIENTCEM.NS) Slips 1.07% to ₹128.16: Stock Holds Above Key Support Zone - Risk Reward Setups - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Shivam Autotech Share Price Falls 8.47% on Price Action - Univest</t>
+          <t>Orient Cement Clarifies CFO Name Discrepancy in KMP Disclosure - TipRanks</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Shivam Autotech Share Price and Chart Analysis - Kalkine India</t>
+          <t>Orient Cement CFO Resignation: Kajal Saxena Steps Down - Kalkine India</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Shivam Autotech Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Orient Cement Clarifies CFO Name Discrepancy in KMP Disclosure - TipRanks</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Shivam Autotech schedules 21st AGM for September 25, 2026 - scanx.trade</t>
+          <t>Orient Cement provides clarification on key managerial personnel change - Business Upturn</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2427,68 +2427,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ADDIND.NS</t>
+          <t>ORIENTBELL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Limited</t>
+          <t>Orient Bell Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>82.65000152587891</v>
+        <v>394.8999938964844</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>82.65000152587891</v>
+        <v>406.7999877929688</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>75</v>
+        <v>393.0499877929688</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>77.73999786376953</v>
+        <v>393.5499877929688</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>82.65000152587891</v>
+        <v/>
       </c>
       <c r="J8" s="2" t="n">
-        <v>77.73999786376953</v>
+        <v>393.5499877929688</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>207</v>
+        <v>11279</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.94</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ADDIND Stock Price and Chart — NSE:ADDIND - TradingView</t>
+          <t>Orient (ORIENTBELL.NS) Quarter in Focus: The Company Reports Its Latest Available Figures under the Current Snapshot; Price Move: The Stock Ends Down 0.91% in the Latest Reading - Subscription Growth Report - siam.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Ltd. (ADDIND) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
+          <t>Orient Bell (NSE:ORIENTBELL): What Is the Analyst Meet Scheduled for 15 September 2026? - Kalkine India</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Ltd. Share Price Analysis: 8.22% Increase - Univest</t>
+          <t>Orient Bell (NSE:ORIENTBELL): What Is the Analyst Meet Scheduled for 15 September 2026? - Kalkine India</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Limited Submits SEBI Compliance Certificate for Q4 FY26 - scanx.trade</t>
+          <t>Orient Bell To Hold Analyst And Investor Meeting On September 10 - sahi.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Addi Industries Ltd. (ADDIND) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>5 Ceramic Stocks India 2026: Strong Future Roadmaps - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2496,68 +2496,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BCG.NS</t>
+          <t>ORCHASP.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Brightcom Group Limited</t>
+          <t>Orchasp Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10.30000019073486</v>
+        <v>1.429999947547913</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>10.46000003814697</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>9.529999732971191</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9.670000076293945</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10.26000022888184</v>
+        <v/>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9.670000076293945</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>17102834</v>
+        <v>69114</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.75</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Brightcom Group (BCG.NS) Holds Steady at ₹9.04: Key Levels to Monitor - Spring Pattern - siam.in</t>
+          <t>Orchasp Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Baltic Classifieds Group PLC (BCG.L) Stock Analysis: Assessing the 13.43% Upside Potential - DirectorsTalk Interviews</t>
+          <t>Orchasp sets book closure for 32nd AGM on September 30 - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Binah Capital Group (BCG) Slides 3.12% as Shares Test Support Zone - Call Resistance - careplusvn.com</t>
+          <t>Orchasp Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Baltic Classifieds Group PLC (BCG.L) Stock Analysis: Assessing the 13.43% Upside Potential - DirectorsTalk Interviews</t>
+          <t>Orchasp sets book closure for 32nd AGM on September 30 - scanx.trade</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Binah Capital Group (BCG) Edges Higher: Stock Holds Above Support at $1.41 - Overnight Profile - careplusvn.com</t>
+          <t>ORCHASP Consolidated June 2026 Net Sales at Rs 2.08 crore, down 73.12% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2565,56 +2565,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KHANDSE.NS</t>
+          <t>OPTIEMUS.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Khandwala Securities Limited</t>
+          <t>Optiemus Infracom Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17.5</v>
+        <v>590</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>17.81999969482422</v>
+        <v>708.9000244140625</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>16.59000015258789</v>
+        <v>590</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17.14999961853027</v>
+        <v>708.9000244140625</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>18.09000015258789</v>
+        <v/>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17.14999961853027</v>
+        <v>708.9000244140625</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5959</v>
+        <v>7995347</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Khandwala Securities (KHANDSE.NS) Slides 4.12% to ₹16.97, Drifting Toward ₹16.12 Support Zone - Systematic Flow - siam.in</t>
+          <t>Optiemus Infracom To Acquire 51.1% Stake In Joint Venture With Nothing Electronics - sahi.com</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Khandwala Securities (KHANDSE.NS) Slides 4.12% to ₹16.97, Drifting Toward ₹16.12 Support Zone - Systematic Flow - siam.in</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Optiemus Infracom To Acquire 51.1% Stake In Joint Venture With Nothing Electronics - sahi.com</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Optiemus Infracom shares surge 14% as screen protectors for smartphones brought under BIS effective April... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Optiemus Infracom Share: Bull Case vs Bear Case for 2026 - Univest</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>OPTIEMUS.NS Q2 2026 Earnings: EPS Holds at ₹7.39 as Shares Rise 6.83% Despite Revenue Dip - Peak Earnings Alert - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2622,68 +2634,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TARMAT.NS</t>
+          <t>ONIXSOLAR.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Limited</t>
+          <t>Onix Solar Energy Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>57.7599983215332</v>
+        <v>328</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>58.63000106811523</v>
+        <v>338</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>52.97999954223633</v>
+        <v>322.6000061035156</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>54.7599983215332</v>
+        <v>322.6000061035156</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>57.7599983215332</v>
+        <v/>
       </c>
       <c r="J11" s="2" t="n">
-        <v>54.7599983215332</v>
+        <v>322.6000061035156</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>45062</v>
+        <v>246559</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.19</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>ONIXSOLAR Stock Price and Chart — NSE:ONIXSOLAR - TradingView</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Tarmat sets e-voting and book closure dates for Sept 30 AGM - scanx.trade</t>
+          <t>ONIXSOLAR Stock Price and Chart — NSE:ONIXSOLAR - TradingView</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Ltd. Share Price rise with market cap at Rs 128.43 Cr - Univest</t>
+          <t>Onix Solar Energy Limited Schedules Rights Issue Committee Meeting for May 11, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Stock Falls 6%: Key Levels and Results - Kalkine India</t>
+          <t>Onix Solar Energy Limited Board Approves Rights Issue of Up to Rs. 130 Crore - scanx.trade</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Dhunseri Tea &amp; Industries Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Onix Solar Energy Limited Publishes Rights Issue Allotment Basis with Regulatory Compliance - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2691,64 +2703,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CURAA.NS</t>
+          <t>ONGC.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Cura Technologies Limited</t>
+          <t>Oil &amp; Natural Gas Corporation Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>72.19999694824219</v>
+        <v>235.5099945068359</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>72.25</v>
+        <v>236.3699951171875</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>72.19999694824219</v>
+        <v>233.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>72.19999694824219</v>
+        <v>235.6999969482422</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>76</v>
+        <v/>
       </c>
       <c r="J12" s="2" t="n">
-        <v>72.19999694824219</v>
+        <v>235.6999969482422</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>644</v>
+        <v>5071801</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Cura Technologies Slips 2.72%: Stock Approaches Key Support Zone on NSE - Inside Day Breakout - siam.in</t>
+          <t>Stocks to watch: ONGC, Pine Labs, GRSE, Waaree, Lloyds Metals, Aarti Inds - Business Standard</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Cura Technologies Confirms EGM Notice Publication: Leadership Changes Scheduled - scanx.trade</t>
+          <t>Stocks to watch: ONGC, Pine Labs, GRSE, Waaree, Lloyds Metals, Aarti Inds - Business Standard</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Cura Technologies Confirms EGM Notice Publication: Leadership Changes Scheduled - scanx.trade</t>
+          <t>ONGC strikes gas at deepwater well in Mahanadi offshore Basin; what investors need to know - upstox.com</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Energy dividend kings: ONGC, IOCL, BPCL, Castrol or IGL, which stock delivers the highest payout? Comparison - TradingView</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>ONGC finds gas near Odisha coast in Mahanadi deepwater basin - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2756,68 +2772,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GRAVISSHO.NS</t>
+          <t>ONEPOINT.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Limited</t>
+          <t>One Point One Solutions Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>36.34999847412109</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>36.34999847412109</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>36.34000015258789</v>
+        <v>60.04999923706055</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>36.34000015258789</v>
+        <v>63.31999969482422</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38.25</v>
+        <v/>
       </c>
       <c r="J13" s="2" t="n">
-        <v>36.34000015258789</v>
+        <v>63.31999969482422</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>817</v>
+        <v>5843270</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.99</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Share Price: price action and valuation - Univest</t>
+          <t>One Point One Solutions Q2 2026 Earnings: EPS of ₹1.45 and 22.24% Revenue Growth Drive 5.08% Stock Uptick - Guidance Update - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
+          <t>One Point One Solutions to Brief Analysts and Investors in Kochi - TipRanks</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Gains 3.45% to ₹29.66; GRAVISSHO.NS Approaches Resistance at ₹31.14 - Standard Deviation - siam.in</t>
+          <t>One Point One Solutions to Brief Analysts and Investors in Kochi - TipRanks</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
-        </is>
-      </c>
+          <t>One Point One Solutions wins 'Best Use of AI in Customer Service' award at India CX Summit 2026 - Business Upturn</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2825,68 +2837,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SHAHALLOYS.NS</t>
+          <t>PEARLPOLY.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Limited</t>
+          <t>Pearl Polymers Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>89.59999847412109</v>
+        <v>18.81999969482422</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>92.5</v>
+        <v>18.82999992370605</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>87.87999725341797</v>
+        <v>18.14999961853027</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>87.87999725341797</v>
+        <v>18.82999992370605</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>92.5</v>
+        <v/>
       </c>
       <c r="J14" s="2" t="n">
-        <v>87.87999725341797</v>
+        <v>18.82999992370605</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>24631</v>
+        <v>23252</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.99</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Share Price rise: price action and valuation - Univest</t>
+          <t>Pearl Polymers Limited (PEARLPOLY.NS): Modest Uptick Amid Consolidation Range - ETF Premium Discount - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Files Scrutinizer’s Report and Voting Results for 36th AGM - TipRanks</t>
+          <t>Pearl Polymers Limited (PEARLPOLY.NS): Modest Uptick Amid Consolidation Range - ETF Premium Discount - siam.in</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Share Price Today: Valuation and Sector View - Univest</t>
+          <t>Pearl Polymers Share Price Target 2026: Bull Case Rs 25.00, Bear - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys Share Price News: Price Action and Valuation - Univest</t>
+          <t>Pearl Polymers Reappoints Independent Director, Submits Revised Board Outcome - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Shah Alloys SHAHALLOYS 36th AGM voting results 2026 - Kalkine India</t>
+          <t>Here's Why Shareholders Will Not Be Complaining About Pearl Polymers Limited's (NSE:PEARLPOLY) CEO Pay Packet - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2894,68 +2906,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BURNPUR.NS</t>
+          <t>OMPOWER.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement Limited</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17.8799991607666</v>
+        <v>169.3699951171875</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>17.8799991607666</v>
+        <v>171.3000030517578</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>16.95999908447266</v>
+        <v>167</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>16.95999908447266</v>
+        <v>168.3099975585938</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>17.85000038146973</v>
+        <v/>
       </c>
       <c r="J15" s="2" t="n">
-        <v>16.95999908447266</v>
+        <v>168.3099975585938</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>26077</v>
+        <v>15960</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.99</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement secures BSE approval for promoter reclassification - scanx.trade</t>
+          <t>OMPOWER Stock Price and Chart — NSE:OMPOWER - TradingView</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement secures BSE approval for promoter reclassification - scanx.trade</t>
+          <t>Om Power Transmission promoters buy shares worth ₹74.46 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>OM POWER TRANSMISSION LTD Share Price - upstox.com</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement BURNPUR Promoter Reclassification 2026 - Kalkine India</t>
+          <t>Om Power Transmission promoters buy shares worth ₹74.46 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Price Band Hitters on September 7, 2026 at 12:00 PM - HDFC Sky</t>
+          <t>OMPOWER Share Price Today - OM POWER TRANSMISSION LTD Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2963,68 +2975,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SPELS.NS</t>
+          <t>ORISSAMINE.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SPEL Semiconductor Limited</t>
+          <t>The Orissa Minerals Development Company Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>131.4600067138672</v>
+        <v>3819</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>131.4600067138672</v>
+        <v>3884.89990234375</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>131.4600067138672</v>
+        <v>3819</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>131.4600067138672</v>
+        <v>3850</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>138.3699951171875</v>
+        <v/>
       </c>
       <c r="J16" s="2" t="n">
-        <v>131.4600067138672</v>
+        <v>3850</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>23177</v>
+        <v>3053</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.99</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>SPELS Stock Price and Chart — NSE:SPELS - TradingView</t>
+          <t>Orissa Minerals Development Closes Trading Window Ahead of Quarterly Results - TipRanks</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>SPEL Semiconductor Ltd. (SPELS) Fundamental and Financial Data - Stocktwits</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>SPEL Semiconductor Limited Schedules Board Meeting for April 15, 2026 to Review Q3FY26 Results and Corporate Actions - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>SPEL Semiconductor Limited Files SEBI SAST Compliance Declaration for FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>SPEL Semiconductor Share Price Today - SPEL Semiconductor Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
-        </is>
-      </c>
+          <t>Orissa Minerals Development Closes Trading Window Ahead of Quarterly Results - TipRanks</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3032,60 +3032,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AKSHOPTFBR.NS</t>
+          <t>OMAXE.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Aksh Optifibre Limited</t>
+          <t>Omaxe Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7.659999847412109</v>
+        <v>114</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7.889999866485596</v>
+        <v>119.3399963378906</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7.449999809265137</v>
+        <v>114</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>7.449999809265137</v>
+        <v>115.8000030517578</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7.840000152587891</v>
+        <v/>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7.449999809265137</v>
+        <v>115.8000030517578</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>304309</v>
+        <v>413910</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Aksh Optifibre Share Price - Upstox</t>
+          <t>Omaxe Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Aksh Optifibre Share Price - Upstox</t>
+          <t>Omaxe Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>AKSHOPTFBR Q2 2026 Earnings: Net Loss of ₹0.8 Per Share as Revenue Declines 2.2% YoY - Balance Sheet Strength - siam.in</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>SAT dismisses Omaxe appeal against SEBI order over financial statement irregularities - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Omaxe accepts resignation of Neeraj Arora as Vice President – PMO - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Omaxe Ltd. Share Price Update: Rise, Fundamentals, Sector - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3093,60 +3101,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SEJALLTD.NS</t>
+          <t>OMAXAUTO.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sejal Glass Limited</t>
+          <t>Omax Autos Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>701.1500244140625</v>
+        <v>191.4299926757812</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>710</v>
+        <v>197.2200012207031</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>678.7000122070312</v>
+        <v>187.2200012207031</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>678.9000244140625</v>
+        <v>188.9700012207031</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>714.4000244140625</v>
+        <v/>
       </c>
       <c r="J18" s="2" t="n">
-        <v>678.9000244140625</v>
+        <v>188.9700012207031</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>14548</v>
+        <v>42655</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Sejal Glass (NSE:SEJALLTD) Is Well Worth Watching - simplywall.st</t>
+          <t>Omax Autos Eases to ₹184.48; Stock Holds Above Key Support Amid Consolidation - KAMA Signal - siam.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Sejal Glass (NSE:SEJALLTD) Is Well Worth Watching - simplywall.st</t>
+          <t>Omax Autos Eases to ₹184.48; Stock Holds Above Key Support Amid Consolidation - KAMA Signal - siam.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Sejal Glass Jun 2026 Earnings: Positive EPS of ₹0.35 on Revenue of ₹36.43 Crore; Stock Slips Marginally - Low Estimate Range - siam.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t>Omax (OMAXAUTO.NS) Earnings Snapshot: The Report Provides a New Financial Snapshot under the Current Snapshot; Shares Move 0.44% Down in Latest Trading - Slow Growth Warning - siam.in</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Omax Autos shareholders approve all AGM resolutions with 98.37% assent - scanx.trade</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3154,60 +3166,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SELMC.NS</t>
+          <t>OLECTRA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SEL Manufacturing Company Limited</t>
+          <t>Olectra Greentech Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>26.40999984741211</v>
+        <v>1212</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>26.40999984741211</v>
+        <v>1256</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>26.40999984741211</v>
+        <v>1210.5</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>26.40999984741211</v>
+        <v>1226.400024414062</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>27.79000091552734</v>
+        <v/>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26.40999984741211</v>
+        <v>1226.400024414062</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>19744</v>
+        <v>440337</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SEL MANUFACTURING CO LTD Share Price - Upstox</t>
+          <t>Olectra Greentech: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>SEL MANUFACTURING CO LTD Share Price - Upstox</t>
+          <t>Olectra Greentech: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>SELMC Q2 2026 Earnings: Revenue Tumbles 53% YoY, EPS Loss Widens to ₹50.66 - Earnings Growth Forecast - siam.in</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Olectra Greentech Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Olectra (OLECTRA.NS) Stock: Falls 0.69% to ₹1,288.60 at the Close; Immediate View: ₹1,224.17 and ₹1,353.03 Define the Nearby Reference Levels in Latest Trading - Fast Moving Stocks - siam.in</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Olectra Greentech files FY26 sustainability report with stock exchanges - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3215,68 +3235,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RHETAN.NS</t>
+          <t>OAL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Limited</t>
+          <t>Oriental Aromatics Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>554.7999877929688</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>570</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>550.0499877929688</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>562.5</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.56999969482422</v>
+        <v/>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18.60000038146973</v>
+        <v>562.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>556175</v>
+        <v>56252</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.96</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Oriental Aromatics Share Price Update With Valuation View - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Oriental Aromatics Share Price Update With Valuation View - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT regularizes Jhanvi Sethi as independent director - scanx.trade</t>
+          <t>OAL FY26 Net Profit Falls 90.7% on Higher Costs - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Ltd Forms Death Cross, Signalling Potential Bearish Trend - MarketsMojo</t>
+          <t>Oriental Aromatics Share Price update: OAL gains 12.35% - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - ThePrint</t>
+          <t>Oriental Aromatics Share Price rises 8.72%; valuation view - Univest</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:01 IST</t>
+          <t>2026-09-22 13:21:24 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3284,61 +3304,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MUKESHB.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Mukesh Babu Financial Services Limited</t>
+          <t>FSN E-Commerce Ventures Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>127</v>
+        <v>335</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>127</v>
+        <v>337.6499938964844</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>126.3499984741211</v>
+        <v>330.2999877929688</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>126.4199981689453</v>
+        <v>333.2999877929688</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>133</v>
+        <v/>
       </c>
       <c r="J21" s="2" t="n">
-        <v>126.4199981689453</v>
+        <v>333.2999877929688</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>18</v>
+        <v>740788</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.95</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Mukesh Babu Financial Services Ltd. - Stocktwits</t>
+          <t>Nykaa Share Price Today: Decline, Technicals, Fundamentals - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Mukesh Babu Financial Services Ltd. - Stocktwits</t>
+          <t>Nykaa Q2 FY27 Results Preview - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>PIONRINV Stock Price and Chart — NSE:PIONRINV - TradingView</t>
+          <t>Nykaa Share Price rises 2.33%: valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Mukesh Babu Financial Services Ltd - Equitypandit</t>
+          <t>Nykaa rally: Planning to buy fashion retailer stock after recent up move? Here's what analyst says - Business Today</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>LKPSEC Stock Price and Chart — NSE:LKPSEC - TradingView</t>
+          <t>Nykaa shares: Elara Capital hikes target price; sees 43% upside potential - Business Today</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>JAYKAY.NS</t>
+          <t>CUBEXTUB.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Limited</t>
+          <t>Cubex Tubings Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>192.3999938964844</v>
+        <v>125.8199996948242</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>219.3500061035156</v>
+        <v>125.8199996948242</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>191.4700012207031</v>
+        <v>117</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>217.1000061035156</v>
+        <v>125.8199996948242</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>189.5</v>
+        <v>104.8499984741211</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>217.1000061035156</v>
+        <v>125.8199996948242</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7789748</v>
+        <v>1061626</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>14.56</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Inventory turnover of Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares – BSE:JAYKAY_RE1 - TradingView</t>
+          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Inventory turnover of Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares – BSE:JAYKAY_RE1 - TradingView</t>
+          <t>12 Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Subsidiary Neumesh Labs Receives MCA Investigation Notice - scanx.trade</t>
+          <t>Cubex Tubings Share Price rise: fundamentals and sector view - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Ltd. - RE1 Share Price Live Today - CNBC TV18</t>
+          <t>Cubex Tubings Limited Board Approves ₹135 Crore Fund-Raising Plan - EquityBulls</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares Earnings and Revenue – NSE:JAYKAY_RE1 - TradingView</t>
+          <t>Cubex Tubings approves ₹135 Cr raise via convertible debt, sets EGM date - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>OLAELEC.NS</t>
+          <t>PREMIERPOL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited</t>
+          <t>Premier Polyfilm Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>38.25</v>
+        <v>81.69999694824219</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>42.36000061035156</v>
+        <v>97.22000122070312</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>38.25</v>
+        <v>81.13999938964844</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>41.70999908447266</v>
+        <v>96.72000122070312</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>37.77999877929688</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>41.70999908447266</v>
+        <v>96.72000122070312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>284785800</v>
+        <v>6516805</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>10.4</v>
+        <v>19.38</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>OLA Electric Mobility Share Price rises 5.82%: analysis - Univest</t>
+          <t>Premier Polyfilm promoter raises stake to 12% via open market - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Plans On-Site Analyst Meet at Future Factory and Giga Factory - The Globe and Mail</t>
+          <t>Premier Polyfilm Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Plans On-Site Analyst Meet at Future Factory and Giga Factory - The Globe and Mail</t>
+          <t>Is It Smart To Buy Premier Polyfilm Ltd. (NSE:PREMIERPOL) Before It Goes Ex-Dividend? - simplywall.st</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Ola shares rise 6% on S1Z launch with indigenous cell tech, claims 301 km per charge - Business Today</t>
+          <t>Premier Polyfilm Share Price at Rs 97.14 near 52-week peak - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Stocks To Buy or Sell Today, August 31, 2026: Ola Electric and HDFC Bank Among Shares That May Remain in - LatestLY</t>
+          <t>Premier Polyfilm Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>OMAXAUTO.NS</t>
+          <t>MANINDS.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Omax Autos Limited</t>
+          <t>Man Industries (India) Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>193.8000030517578</v>
+        <v>875</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>209.9400024414062</v>
+        <v>1005</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>192.2100067138672</v>
+        <v>866.25</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>209.9400024414062</v>
+        <v>986.7000122070312</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>190.8600006103516</v>
+        <v>849.9000244140625</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>209.9400024414062</v>
+        <v>986.7000122070312</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>196002</v>
+        <v>10690942</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10</v>
+        <v>16.1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Omax Autos (OMAXAUTO.NS) Slips 1.12% to ₹167.10 as Traders Watch ₹158.74 Support - SuperTrend Flip - siam.in</t>
+          <t>Man Industries posts concall transcript for Q4FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Omax Autos (OMAXAUTO.NS) Slips 1.12% to ₹167.10 as Traders Watch ₹158.74 Support - SuperTrend Flip - siam.in</t>
+          <t>Man Industries posts concall transcript for Q4FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Omax Autos Eases to ₹184.48; Stock Holds Above Key Support Amid Consolidation - KAMA Signal - siam.in</t>
+          <t>Man Industries (India) Share Price: 52-Week High Update - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Omax (OMAXAUTO.NS) Earnings Snapshot: The Report Provides a New Financial Snapshot under the Current Snapshot; Shares Move 0.44% Down in Latest Trading - Slow Growth Warning - siam.in</t>
+          <t>Man Industries (India) Share Price hits fresh 52-week high - Univest</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Omax Autos shareholders approve all AGM resolutions with 98.37% assent - scanx.trade</t>
+          <t>Man Industries Share Price Fall: Technicals and Valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +760,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AASTHA.NS</t>
+          <t>SUBEXLTD.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Limited</t>
+          <t>Subex Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>83</v>
+        <v>19.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>89.77999877929688</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>83</v>
+        <v>19.47999954223633</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>89.77999877929688</v>
+        <v>22.07999992370605</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>81.62000274658203</v>
+        <v>19.3700008392334</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>89.77999877929688</v>
+        <v>22.07999992370605</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2363567</v>
+        <v>70951577</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>10</v>
+        <v>13.99</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex to allot 4.41 crore bonus shares - Moneycontrol.com</t>
+          <t>Subex Ltd Share Price Today,, SUBEXLTD Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex to allot 4.41 crore bonus shares - Moneycontrol.com</t>
+          <t>Subex Ltd. Share Price Update: Price Rise and Valuation - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex to Allot 4.41 Cr Bonus Shares; Record Date Set - Rediff MoneyWiz</t>
+          <t>Subex Ltd. Share Price rises 11.24%: valuation and sector - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex fixes Monday as record date for bonus issue - TradingView</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Aastha Spintex stock jumps 10% after bonus issue announcement | Tap to know more | Inshorts - Inshorts</t>
-        </is>
-      </c>
+          <t>Subex Ltd. Share Price Update: Price Rise and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,68 +825,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>KROSS.NS</t>
+          <t>RAYMONDREL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kross Limited</t>
+          <t>Raymond Realty Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>260.8500061035156</v>
+        <v>591</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>283</v>
+        <v>679</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>257.5</v>
+        <v>591</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>280.5</v>
+        <v>671.4500122070312</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>256.1300048828125</v>
+        <v>589.5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>280.5</v>
+        <v>671.4500122070312</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4183206</v>
+        <v>12801131</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9.51</v>
+        <v>13.9</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd Hits All-Time High of Rs 268.85 as Momentum Builds Across Timeframes - MarketsMojo</t>
+          <t>RAYMOND REALTY Share Price Today: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd Hits All-Time High of Rs 268.85 as Momentum Builds Across Timeframes - MarketsMojo</t>
+          <t>RAYMOND REALTY Share Price Today: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd. Share Price Today: KROSS Price and Valuation - Univest</t>
+          <t>Raymond Realty Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Kross Limited Promoter Anita Rai Acquires 30,000 Equity Shares Through Open Market - scanx.trade</t>
+          <t>Raymond Realty Limited announced that it expects to receive INR 1.021906756 billion in funding from J K Investors Ltd. - marketscreener.com</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>If EPS Growth Is Important To You, Kross (NSE:KROSS) Presents An Opportunity - simplywall.st</t>
+          <t>Raymond Realty to Join Jefferies 5th India Forum for Investor Meetings - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -898,64 +894,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ONEPOINT.NS</t>
+          <t>JAYKAY.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>One Point One Solutions Limited</t>
+          <t>Jaykay Enterprises Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>63.90000152587891</v>
+        <v>192.3999938964844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>70.5</v>
+        <v>219.3500061035156</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>63.59999847412109</v>
+        <v>191.4700012207031</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.16000366210938</v>
+        <v>212.7599945068359</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>63.20000076293945</v>
+        <v>189.5</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>69.16000366210938</v>
+        <v>212.7599945068359</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>17301751</v>
+        <v>9949318</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>9.43</v>
+        <v>12.27</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And One Point One Solutions (NSE:ONEPOINT) Passed With Ease - simplywall.st</t>
+          <t>Jaykay Enterprises promoter group oversubscribes rights issue by 19.45 lakh shares - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>One Point One Solutions secures INR 39.32 crore Customer Experience Centre of Excellence mandate - Business Upturn</t>
+          <t>Jaykay Enterprises promoter group oversubscribes rights issue by 19.45 lakh shares - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>One Point One Solutions wins 'Best Use of AI in Customer Service' award at India CX Summit 2026 - Business Upturn</t>
+          <t>Inventory turnover of Jaykay Enterprises Limited Rights 2026-18.09.26 For Shares – BSE:JAYKAY_RE1 - TradingView</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>One Point One Solutions secures INR 39.32 crore Customer Experience Centre of Excellence mandate - Business Upturn</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Jaykay Enterprises Subsidiary Neumesh Labs Receives MCA Investigation Notice - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Jaykay Enterprises Ltd. - RE1 Share Price Live Today - CNBC TV18</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -963,64 +963,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP.NS</t>
+          <t>NAGREEKEXP.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited</t>
+          <t>Nagreeka Exports Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>62.29999923706055</v>
+        <v>22.25</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>67.19999694824219</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.77000045776367</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.66999816894531</v>
+        <v>24.20999908447266</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>61.77000045776367</v>
+        <v>21.65999984741211</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>66.66999816894531</v>
+        <v>24.20999908447266</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>7360060</v>
+        <v>97332</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>7.93</v>
+        <v>11.77</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited (DELTACORP.NS) Climbs Over 4% to ₹58.5 as Buyers Defend Lower Support Zone - Double Bottom - siam.in</t>
+          <t>Nagreeka Exports Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited (DELTACORP.NS) Climbs Over 4% to ₹58.5 as Buyers Defend Lower Support Zone - Double Bottom - siam.in</t>
+          <t>Nagreeka Exports Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited (DELTACORP.NS) Consolidates Near ₹54 as Traders Eye Range Boundaries - Factor Timing - siam.in</t>
+          <t>Nagreeka Exports Limited (NSE: NAGREEKEXP) Falls 5.23% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP Outlook for the Week - Equitypandit</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Nagreeka Exports Ltd Share Price Today,, NAGREEKEXP Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Nagreeka Exports Holds Near ₹21.3: Consolidation Persists for NAGREEKEXP on NSE - Rounding Top - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1040,29 +1044,29 @@
         <v>12.53999996185303</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>13.19999980926514</v>
+        <v>14.28999996185303</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>12.40999984741211</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>13.11999988555908</v>
+        <v>13.52999973297119</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>12.17000007629395</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13.11999988555908</v>
+        <v>13.52999973297119</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>156741</v>
+        <v>428270</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7.81</v>
+        <v>11.18</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Adroit (ADROITINFO.NS) Earnings Snapshot: The Report Provides a New Financial Snapshot on the Day; Price Reaction: Shares Finish 2.23% Lower in the Latest Session - Profit Margin Analysis - siam.in</t>
+          <t>Adroit (ADROITINFO.NS) Earnings Snapshot: The Report Provides a New Financial Snapshot on the Day; Price Reaction: Shares Finish 2.23% Lower in the Latest Session - Margin Guidance - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1077,7 +1081,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Adroit (ADROITINFO.NS) Earnings Snapshot: The Report Provides a New Financial Snapshot on the Day; Price Reaction: Shares Finish 2.23% Lower in the Latest Session - Margin Guidance - siam.in</t>
+          <t>Adroit (ADROITINFO.NS) Earnings Snapshot: The Report Provides a New Financial Snapshot on the Day; Price Reaction: Shares Finish 2.23% Lower in the Latest Session - Earnings Cycle Report - siam.in</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1089,7 +1093,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1097,68 +1101,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>RPGLIFE.NS</t>
+          <t>DELTACORP.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>RPG Life Sciences Limited</t>
+          <t>Delta Corp Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2771.60009765625</v>
+        <v>62.29999923706055</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2944</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2727.10009765625</v>
+        <v>61.77000045776367</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2915</v>
+        <v>68.65000152587891</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2746.89990234375</v>
+        <v>61.77000045776367</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2915</v>
+        <v>68.65000152587891</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>50914</v>
+        <v>17765643</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.12</v>
+        <v>11.14</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>RPG Life Sciences Slips 1.46% to ₹2590.5: Stock Holds Key Support Amid Pharma Sector Consolidation - McClellan Summation - siam.in</t>
+          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>RPG Life Sciences (NSE: RPGLIFE) - Company Overview and Sector Context - Kalkine India</t>
+          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>RPG Life Sciences (NSE: RPGLIFE) - Company Overview and Sector Context - Kalkine India</t>
+          <t>Delta Corp Limited (DELTACORP.NS) Consolidates Near ₹54 as Traders Eye Range Boundaries - Factor Timing - siam.in</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>RPG (RPGLIFE.NS) Results Check: The Report Provides a New Financial Snapshot in the Reported Period; Closing Move: The Session Ends Near the Prior Level in the Latest Session - Guidance vs Actual - siam.in</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>RPGLIFE Q2 2026 Earnings: EPS at ₹69.64 on 8.41% Revenue Growth - Profitability Analysis - siam.in</t>
-        </is>
-      </c>
+          <t>DELTACORP Outlook for the Week - Equitypandit</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1166,68 +1166,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ROLEXRINGS.NS</t>
+          <t>MUKANDLTD.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Rolex Rings Limited</t>
+          <t>Mukand Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>173.5</v>
+        <v>141.4100036621094</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>187.6499938964844</v>
+        <v>158.8000030517578</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>173.4199981689453</v>
+        <v>141.4100036621094</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>182.8999938964844</v>
+        <v>157.1100006103516</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>172.5</v>
+        <v>141.4100036621094</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>182.8999938964844</v>
+        <v>157.1100006103516</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>5747656</v>
+        <v>2524541</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.03</v>
+        <v>11.1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>ROLEXRINGS Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>Mukand Limited (MUKANDLTD.NS) Rises 1.11% to ₹134.44: Consolidation Phase Within Established Range - Impulse Wave - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Rolex (ROLEXRINGS.NS) Market: Declines 1.33% to ₹174.70 at the Close; Chart Watch: the Current Price Sits Inside the Supplied Technical Range in Latest Trading - Virgin POC - siam.in</t>
+          <t>Mukand Ltd. Share Price News: Today’s Rise and Valuation - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Rolex Rings Limited's (NSE:ROLEXRINGS) Stock Is Going Strong: Is the Market Following Fundamentals? - simplywall.st</t>
+          <t>Mukand fixes Aug 7 record date for Rs 3 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>ROLEXRINGS.NS Jun 2026 Quarter Earnings: EPS at ₹2.21 on Revenue of ₹304 Crore; Stock Gains 3.08% - siam.in</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Rolex Rings Limited Receives Stock Exchange Approval for Promoter Group Reclassification - scanx.trade</t>
-        </is>
-      </c>
+          <t>Mukand Ltd. Share Price News: Today’s Rise and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1235,68 +1231,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>TEMPSENS.NS</t>
+          <t>ELECON.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Tempsens Instruments (India) Limited</t>
+          <t>Elecon Engineering Company Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>538</v>
+        <v>420.5499877929688</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>574.4500122070312</v>
+        <v>476.8999938964844</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>538</v>
+        <v>420.1000061035156</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>568.8499755859375</v>
+        <v>466.6000061035156</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>537.0999755859375</v>
+        <v>420.5499877929688</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>568.8499755859375</v>
+        <v>466.6000061035156</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2833719</v>
+        <v>30984922</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.91</v>
+        <v>10.95</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Tempsens Instruments Share Price Today, Tempsens Instruments Stock Price Live NSE/BSE Updates - The Economic Times</t>
+          <t>Elecon Engineering, Bikaji Foods, 360 One Wam shares surge amid spike in volumes; check full list - Upstox</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Tempsens Instruments Q1FY27 Results: Net profit up 14% to ₹15.2 crore - scanx.trade</t>
+          <t>Volumes jump at Elecon Engineering Company Ltd counter - Business Standard</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Tempsens Instruments Q1FY27 Results: Net profit up 14% to ₹15.2 crore - scanx.trade</t>
+          <t>20% Jump In Six Months: Elecon Engineering Share Price Jumps 12% In Trade - NDTV Profit</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,242,497 Equity Shares of Tempsens Instruments Limited are subject to a Lock-Up Agreement Ending on 23-SEP-2026. - marketscreener.com</t>
+          <t>This stock is one of the top gainers in Nifty 500 today - Check share price performance | Do you own it? - Livemint</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Tempsens Instruments Shares Rally on 27% Growth Guidance - Equitypandit</t>
+          <t>Volumes jump at Elecon Engineering Company Ltd counter - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1304,68 +1300,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VEDPOWER.NS</t>
+          <t>UNIDT.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Vedanta Power Limited</t>
+          <t>United Drilling Tools Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>31.29000091552734</v>
+        <v>211</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>33.43999862670898</v>
+        <v>254.8999938964844</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>31.28000068664551</v>
+        <v>211</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>32.86999893188477</v>
+        <v>235.2400054931641</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.06999969482422</v>
+        <v>212.4199981689453</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>32.86999893188477</v>
+        <v>235.2400054931641</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>19952521</v>
+        <v>330348</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.79</v>
+        <v>10.74</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>VEDPOWER Share Price Today - Vedanta Power Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>United Drilling Tools Share Price: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Vedanta Power Ltd. Share Price Today - Vedanta Power Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>20% Upper Circuit: 12 Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Vedanta Power Ltd. Share Price Today - Vedanta Power Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>United Drilling Tools Limited Secures ₹5.04 Crore Order from ONGC for Integral Blade Stabilizer Supply - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Vedanta Power Ltd. (VEDPOWER): Vedanta Power 52 Week Low Streak: Second Straight Session Near One-Year Low - Univest</t>
+          <t>United Drilling Tools Limited (NSE:UNIDT) Goes Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Vedanta Power Share Price Drops, Hits Fresh 52-Week Low - Univest</t>
+          <t>United Drilling Tools Limited Receives Order From Argentera Engenharia E Serviços De Petróleo E Gas Ltda For Supply Of Casing Pipe With UDT Connectors - marketscreener.com</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1373,68 +1369,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SAIL.NS</t>
+          <t>RPGLIFE.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Steel Authority of India Limited</t>
+          <t>RPG Life Sciences Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>174.5</v>
+        <v>2771.60009765625</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>184.7200012207031</v>
+        <v>3047.199951171875</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>174.5</v>
+        <v>2727.10009765625</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>183.3399963378906</v>
+        <v>3025.39990234375</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>174.0099945068359</v>
+        <v>2746.89990234375</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>183.3399963378906</v>
+        <v>3025.39990234375</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>28435658</v>
+        <v>143443</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.36</v>
+        <v>10.14</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>SAIL Share Price Update: Price Rise, Fundamentals, Peers - Univest</t>
+          <t>RPG Life Sciences Slips 1.46% to ₹2590.5: Stock Holds Key Support Amid Pharma Sector Consolidation - McClellan Summation - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Nifty Metal index up over 1%; SAIL, Welpsun Corp soar up to 4%; here's why - Business Standard</t>
+          <t>RPG Life Sciences (NSE: RPGLIFE) - Company Overview and Sector Context - Kalkine India</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Nifty Metal index up over 1%; SAIL, Welpsun Corp soar up to 4%; here's why - Business Standard</t>
+          <t>RPG Life Sciences (NSE: RPGLIFE) - Company Overview and Sector Context - Kalkine India</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Tata Steel vs Hindalco vs JSW vs Nalco vs SAIL vs NMDC: Which Metal Stock To Gain From Aluminium Price Shock? - Goodreturns</t>
+          <t>RPG (RPGLIFE.NS) Results Check: The Report Provides a New Financial Snapshot in the Reported Period; Closing Move: The Session Ends Near the Prior Level in the Latest Session - Guidance vs Actual - siam.in</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>SAIL Q1FY27 EBITDA surges 50% to ₹4,356 cr on better realizations - scanx.trade</t>
+          <t>RPGLIFE Q2 2026 Earnings: EPS at ₹69.64 on 8.41% Revenue Growth - Profitability Analysis - siam.in</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1442,56 +1438,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ANDREWYU.NS</t>
+          <t>DCMSIL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Company Limited</t>
+          <t>DCM Shriram International Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>26.75</v>
+        <v>70.77999877929688</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>28.98999977111816</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>26.1299991607666</v>
+        <v>70.01000213623047</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>27.88999938964844</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26.48999977111816</v>
+        <v>70.41999816894531</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>27.88999938964844</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>409121</v>
+        <v>281648</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5.29</v>
+        <v>10</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Company Ltd. Share Price Today: 10.87% gain - Univest</t>
+          <t>DCMSIL Stock Price and Chart — NSE:DCMSIL - TradingView</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Andrew Yule &amp; Company Ltd. Share Price Today: 10.87% gain - Univest</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>DCM Shriram International Ltd. Share Price: 8.19% Gain Today - Univest</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>DCMSIL Share Price Today - DCM Shriram International Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Ltd. Share Price: 8.19% Gain Today - Univest</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>DCM Shriram International (DCMSIL.NS) Gains Nearly 2% – Key Levels in Focus - Active ETF Flow - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1499,68 +1507,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AARNAV.NS</t>
+          <t>SUNFLAG.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Limited</t>
+          <t>Sunflag Iron And Steel Company Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>31.97999954223633</v>
+        <v>356.8999938964844</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>33.41999816894531</v>
+        <v>390.5499877929688</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30.75</v>
+        <v>356.5499877929688</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>33.41999816894531</v>
+        <v>390.5499877929688</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31.82999992370605</v>
+        <v>355.0499877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>33.41999816894531</v>
+        <v>390.5499877929688</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>20679</v>
+        <v>911760</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Ltd. Upper Circuit Streak: Day 2 Price and Data - Univest</t>
+          <t>Sunflag Iron &amp; Steel: Anand Kapre exits independent director role - scanx.trade</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Ltd. Upper Circuit Streak: Day 2 Price and Data - Univest</t>
+          <t>Sunflag Iron &amp; Steel Company Ltd Rallies 7.8% Surpassing Sector Gains on 23 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Sunflag Iron and Steel (NSE:SUNFLAG) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Sunflag Iron &amp; Steel holds AGM on Sep 25, recommends ₹1 dividend - scanx.trade</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions FY26 net profit rises 1.2% to ₹934.63 lakh - scanx.trade</t>
+          <t>Sunflag Iron And Steel Company Ltd. Share Price Rises 8.09% - Univest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1568,68 +1576,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK.NS</t>
+          <t>KABRAEXTRU.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>STL Networks Limited</t>
+          <t>Kabra Extrusion Technik Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>49.65000152587891</v>
+        <v>693.9500122070312</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>49.70000076293945</v>
+        <v>732.8499755859375</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>48.5</v>
+        <v>678.5499877929688</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>49.70000076293945</v>
+        <v>732.8499755859375</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>47.34000015258789</v>
+        <v>666.25</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>49.70000076293945</v>
+        <v>732.8499755859375</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2979314</v>
+        <v>402750</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.99</v>
+        <v>10</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>STL NETWORKS LIMITED Upper Circuit Streak: Day 2 Price and Data - Univest</t>
+          <t>Kabra Extrusiontechnik Share Price near 52-week high | - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>STL NETWORKS LIMITED Upper Circuit Streak: Day 2 Price and Data - Univest</t>
+          <t>Kabra Extrusiontechnik Share Price near 52-week high | - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK.NS Q2 2026 Earnings: Revenue Declines 18.61% YoY, EPS Loss of ₹2.03, Yet Stock Gains 4.98% - siam.in</t>
+          <t>Kabra Extrusiontechnik Share Price rises 9.10% to Rs 727 - Univest</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Ankit Agarwal confirms no encumbrance on STL Networks shares in FY26 - scanx.trade</t>
+          <t>Kabra Extrusiontechnik KABRAEXTRU Preferential Issue Allottee Change - Kalkine India</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>STL NETWORKS LIMITED Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Kabra Extrusiontechnik Share Price Rises 8.56% to Rs 689 - Univest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1637,60 +1645,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MCLEODRUSS.NS</t>
+          <t>AASTHA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mcleod Russel India Limited</t>
+          <t>Aastha Spintex Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45.68999862670898</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>47.20000076293945</v>
+        <v>89.77999877929688</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>44.95999908447266</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>47.20000076293945</v>
+        <v>89.76999664306641</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>44.95999908447266</v>
+        <v>81.62000274658203</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>47.20000076293945</v>
+        <v>89.76999664306641</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>123969</v>
+        <v>2984614</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.98</v>
+        <v>9.99</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>McLeod Russel schedules 28th AGM for September 30 via VC - scanx.trade</t>
+          <t>Aastha Spintex to allot 4.41 crore bonus shares - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>McLeod Russel Sets September 30 Virtual AGM, Publishes FY26 Annual Report - TipRanks</t>
+          <t>Aastha Spintex to allot 4.41 crore bonus shares - The Economic Times</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>McLeod Russel Sets September 30 Virtual AGM, Publishes FY26 Annual Report - TipRanks</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Aastha Spintex to allot 4.41 crore bonus shares - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Share Price Rise: What Today’s Move Shows - Univest</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Aastha Spintex to Allot 4.41 Cr Bonus Shares; Record Date Set - Rediff MoneyWiz</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1698,68 +1714,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>NEUEON.NS</t>
+          <t>SAKUMA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Neueon Corporation Limited</t>
+          <t>Sakuma Exports Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13.0600004196167</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>13.0600004196167</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13.0600004196167</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>13.0600004196167</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>12.4399995803833</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13.0600004196167</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>7072</v>
+        <v>2655959</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.98</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Neueon Corporation narrows Q1FY27 standalone loss to ₹82.11 lakh - scanx.trade</t>
+          <t>Sakuma Exports Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Neueon Corporation narrows Q1FY27 standalone loss to ₹82.11 lakh - scanx.trade</t>
+          <t>Sakuma Exports Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Neueon Corporation Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Sakuma Exports Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Neueon Corporation to consider fund raising and AOA amendments - scanx.trade</t>
+          <t>Sakuma Exports revenue falls 25% to ₹17,174 crore in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Neueon Corporation withdraws ₹150.79 Cr rights issue proposal - scanx.trade</t>
+          <t>Sakuma Exports Share Price Gains 9.4%: Stock News Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1767,64 +1783,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KIRIINDUS.NS</t>
+          <t>WEWIN.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries Limited</t>
+          <t>WE WIN LIMITED</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>546</v>
+        <v>43.9900016784668</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>569</v>
+        <v>47.29999923706055</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>543.5999755859375</v>
+        <v>43.04999923706055</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>565.9500122070312</v>
+        <v>46.7599983215332</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>540.5</v>
+        <v>43</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>565.9500122070312</v>
+        <v>46.7599983215332</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>687677</v>
+        <v>8968</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.71</v>
+        <v>8.74</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries Share Price today: valuation and sector view - Univest</t>
+          <t>We Win (NSE:WEWIN): Why Has the Trading Window Been Closed from 1 October 2026? - Kalkine India</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today -8 September 2026 - TradingView</t>
+          <t>We Win (NSE:WEWIN): Why Has the Trading Window Been Closed from 1 October 2026? - Kalkine India</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Breakout stocks to buy or sell: Sumeet Bagadia recommends five shares to buy today -8 September 2026 - TradingView</t>
+          <t>WEWIN Q2 2026 Earnings: EPS of ₹4.41 With Revenue Up 7.34% YoY, Shares Slip 1.23% - Margin Improvement Report - siam.in</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries Share Price Today: Price Rise and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>We Win Ltd transmits 1.70% stake to Sitaram Gupta following promoter demise - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>We Win Limited Files Annual Disclosure Confirming Non-Large Corporate Status Under SEBI - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1832,50 +1852,58 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ALUFLUOR.NS</t>
+          <t>RGL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Limited</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>538</v>
+        <v>156.7799987792969</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>577.9000244140625</v>
+        <v>173.8000030517578</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>537.9000244140625</v>
+        <v>155.9900054931641</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>567.75</v>
+        <v>170.4799957275391</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>543.3499755859375</v>
+        <v>156.7799987792969</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>567.75</v>
+        <v>170.4799957275391</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>16381</v>
+        <v>4184466</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4.49</v>
+        <v>8.74</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Share Price Rises 9.89% to Rs 540: Analysis - Univest</t>
+          <t>Renaissance Global Share Price Rises 8.04%: Valuation View - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Share Price Rises 9.89% to Rs 540: Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+          <t>Renaissance Global Share Price near 52-week high, price and - Univest</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Renaissance Global Share Price near 52-week high, price and - Univest</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>3 UK REIT Stocks Retail Investors Are Watching Before The October Budget - simplywall.st</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1895,7 +1923,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2001,7 +2029,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2009,68 +2037,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE.NS</t>
+          <t>TAALTECH.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>BlueStone Jewellery and Lifestyle Limited</t>
+          <t>Taal Tech Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>941.9500122070312</v>
+        <v>1151.400024414062</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>969.9000244140625</v>
+        <v>1174.699951171875</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>824</v>
+        <v>1080.300048828125</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>837.7000122070312</v>
+        <v>1094.800048828125</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>930.4000244140625</v>
+        <v>1185.400024414062</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>837.7000122070312</v>
+        <v>1094.800048828125</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>6141466</v>
+        <v>101515</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-9.960000000000001</v>
+        <v>-7.64</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>BlueStone Jewellery share price falls 52-week low today | What's behind the plunge? - livemint.com</t>
+          <t>TAAL Tech Limited (TAALTECH.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>BlueStone Jewellery share price falls 52-week low today | What's behind the plunge? - livemint.com</t>
+          <t>TAAL Tech Limited (TAALTECH.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - TradingView</t>
+          <t>Taal Tech Limited (TAALTECH.NS) Slips 1.12% to ₹4399.6, Holds Range-Bound Course - ADD Alert - siam.in</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Market Trading Guide: Finolex Cables among 3 stock recommendations for Wednesday - The Economic Times</t>
+          <t>1:5 stock split alert! Mukul Agrawal-portfolio stock nearing record date; delivers 400% return in 5 years | Do you own? - Livemint</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Jewellery Stocks Today: PC Jeweller, Lalithaa Jewellery, BlueStone, PNG Jewellers, Thangamayil Rise Up to 15% - India Infoline</t>
+          <t>TAAL Tech Limited (TAALTECH.BO) Stock Forum &amp; Discussion - Yahoo Finance - Yahoo! Finance Canada</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2078,60 +2106,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>OPTIFIN.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>Optimus Finance Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.89999961853027</v>
+        <v>15.88000011444092</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.79999923706055</v>
+        <v>17</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30.77000045776367</v>
+        <v>14.6899995803833</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>30.89999961853027</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>32.38000106811523</v>
+        <v>16.70000076293945</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>30.89999961853027</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2653551</v>
+        <v>1281710</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-4.57</v>
+        <v>-7.43</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Optimus Finance Ltd (NSE: OPTIFIN) Declines 7.78% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI Q2 2026 Earnings: Revenue Jumps 213.6% YoY as EPS Hits ₹5.29, Shares Slip 5.2% - Profit Guidance Range - siam.in</t>
+          <t>Optimus Finance Ltd (NSE: OPTIFIN) Declines 7.78% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI Q2 2026 Earnings: Revenue Jumps 213.6% YoY as EPS Hits ₹5.29, Shares Slip 5.2% - Profit Guidance Range - siam.in</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Optimus Finance Share Price Today: Ownership and Sector - Univest</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Optimus Finance appoints Kheradia as director, new auditor - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>12 Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2139,68 +2175,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG.NS</t>
+          <t>PFOCUS.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ather Energy Limited</t>
+          <t>Prime Focus Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1544</v>
+        <v>362.5499877929688</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1545</v>
+        <v>362.7999877929688</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1483.699951171875</v>
+        <v>333.1499938964844</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1489.099975585938</v>
+        <v>337.1499938964844</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1543.800048828125</v>
+        <v>357.4500122070312</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1489.099975585938</v>
+        <v>337.1499938964844</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>5182149</v>
+        <v>6883255</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-3.54</v>
+        <v>-5.68</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price News: Today’s Decline Explained - Univest</t>
+          <t>Prime Focus Ltd (NSE: PFOCUS) Falls 5.78% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price News: Today’s Decline Explained - Univest</t>
+          <t>Prime Focus Ltd (NSE: PFOCUS) Falls 5.78% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>When Can We Expect A Profit From Ather Energy Limited (NSE:ATHERENERG)? - simplywall.st</t>
+          <t>PFOCUS Forecast — Price Target — Prediction for 2027 - TradingView</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Ather Energy shares climb to all-time high, rising 17% above Hero MotoCorp block price - TechStock²</t>
+          <t>Prime Focus promoter confirms no share encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price: today’s move and sector context - Univest</t>
+          <t>Prime Focus Share Price rises 2.23% | PFOCUS analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2208,60 +2244,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>RACLGEAR.NS</t>
+          <t>MFML.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>RACL Geartech Limited</t>
+          <t>Mahalaxmi Fabric Mills Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1758</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1795</v>
+        <v>19.8700008392334</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1691.400024414062</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1697.800048828125</v>
+        <v>18.21999931335449</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1758</v>
+        <v>19.26000022888184</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1697.800048828125</v>
+        <v>18.21999931335449</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>24113</v>
+        <v>22464</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-3.42</v>
+        <v>-5.4</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>RACL Geartech Share Price near 52-week high, valuation view - Univest</t>
+          <t>Mahalaxmi Fabric Mills MFML 35th AGM September 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>RACL Geartech Share Price near 52-week high, valuation view - Univest</t>
+          <t>Globale Tessile AGM rescheduled to Sep 23; FY26 loss widens - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>RACL Geartech Share Price today: valuation and sector view - Univest</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t>Mahalaxmi (MFML.NS) Snapshot: Advances 2.91% to ₹19.48 at the Close; Market Levels: Price Remains Between ₹18.51 Support and ₹20.45 Resistance in the Latest Session - Iceberg Order - siam.in</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Globale Tessile AGM rescheduled to Sep 23; FY26 loss widens - scanx.trade</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2269,68 +2309,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MOBIKWIK.NS</t>
+          <t>AQYLON.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>One Mobikwik Systems Limited</t>
+          <t>Aqylon Nexus Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>208.4799957275391</v>
+        <v>20.38999938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>209.6900024414062</v>
+        <v>20.73999977111816</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>202.1199951171875</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>203.6600036621094</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>209.0200042724609</v>
+        <v>19.79999923706055</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>203.6600036621094</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>946627</v>
+        <v>649150</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-2.56</v>
+        <v>-5</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Paytm vs Pine Labs vs One MobiKwik: Analyst decodes fintech stock charts - Business Standard</t>
+          <t>Leading Leasing Finance raises Aqylon Nexus stake to 12.85% - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>MobiKwik AGM passes all resolutions, re-appoints Vineet Bansal - scanx.trade</t>
+          <t>Aqylon Nexus promoter Kurjibhai Rupareliya sells 6.99% stake - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>MobiKwik AGM passes all resolutions, re-appoints Vineet Bansal - scanx.trade</t>
+          <t>Aqylon Nexus (AQYLON.NS) Slips 3.23% to ₹21.88 as Stock Nears Key Support - Put Spread Alert - siam.in</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Paytm, MobiKwik shares fall over 2% as govt notifies UPI fee on transactions above ₹2,000 - Fortune India</t>
+          <t>Aqylon Nexus promoter Kurjibhai Rupareliya sells 6.99% stake - scanx.trade</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Paytm, One Mobikwik shares jump up to 5% after UPI MDR announcement; brokerages see revenue boost - TradingView</t>
+          <t>Aqylon Nexus Limited (AQYLON.NS) Surges 4.75% to ₹21.59; Near-Term Resistance at ₹22.67 in Focus - News Sentiment - siam.in</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2338,68 +2378,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AVTNPL.NS</t>
+          <t>VCL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products Limited</t>
+          <t>Vaxtex Cotfab Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>100</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>102</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>95.80999755859375</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>95.86000061035156</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>98.26000213623047</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>95.86000061035156</v>
+        <v>1.519999980926514</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>894329</v>
+        <v>770755</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-2.44</v>
+        <v>-5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products NSE:AVTNPL Volume Spurt Clarification - Kalkine India</t>
+          <t>Vaxtex Cotfab NSE:VCL Zeal Global SAST Disclosure - Kalkine India</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products NSE:AVTNPL Volume Spurt Clarification - Kalkine India</t>
+          <t>Vaxtex Cotfab Discloses Shareholding Change by Zeal Global Opportunities Fund - TipRanks</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products Share Price Update After 10.37% Gain - Univest</t>
+          <t>Price Band Hitters on September 8, 2026 at 12:00 PM - HDFC Sky</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural AGM voting results: all 5 resolutions pass with strong support - scanx.trade</t>
+          <t>Sebi fines Varanium Cloud, promoter Sabale and 7 others Rs 33.08 crore over fund diversion - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products Share Price: price rise and valuation - Univest</t>
+          <t>SEBI slaps ₹33 crore fine on Varanium Cloud, eight others for diversion of IPO proceeds - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2407,64 +2447,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>WINDLAS.NS</t>
+          <t>GRAVISSHO.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Limited</t>
+          <t>Graviss Hospitality Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1105</v>
+        <v>33.20000076293945</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1107.650024414062</v>
+        <v>33.20000076293945</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1071</v>
+        <v>32.81000137329102</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1078</v>
+        <v>32.81000137329102</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1102.300048828125</v>
+        <v>34.52999877929688</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1078</v>
+        <v>32.81000137329102</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>57072</v>
+        <v>5544</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-2.2</v>
+        <v>-4.98</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>Graviss Hospitality Ltd (NSE: GRAVISSHO) Declines 4.98% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>Graviss Hospitality Ltd (NSE: GRAVISSHO) Declines 4.98% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Windlas Biotech Ltd. Stock News - Value Research</t>
+          <t>Graviss Hospitality Share Price: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Volume shocker stocks: Why share price of EMS, Expleo Solutions, Windlas Biotech, AKI India, Heritage Foods are up today - livemint.com</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Graviss Hospitality Gains 3.45% to ₹29.66; GRAVISSHO.NS Approaches Resistance at ₹31.14 - Standard Deviation - siam.in</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Graviss Hospitality Share Price Today: price action review - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2472,68 +2516,64 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MIDWESTLTD.NS</t>
+          <t>EUROTEXIND.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Midwest Limited</t>
+          <t>Eurotex Industries and Exports Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1020</v>
+        <v>12.26000022888184</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1085</v>
+        <v>12.84000015258789</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>992.0999755859375</v>
+        <v>11.64999961853027</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>996.7000122070312</v>
+        <v>11.64999961853027</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1018.299987792969</v>
+        <v>12.26000022888184</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>996.7000122070312</v>
+        <v>11.64999961853027</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>18335</v>
+        <v>1092</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-2.12</v>
+        <v>-4.98</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Midwest Limited reports INR645 crore revenue in FY26 - scanx.trade</t>
+          <t>Eurotex (EUROTEXIND.NS) EPS and Revenue: Available Data Shows the Latest Reported Performance in the Current Update; Post-Report: The Stock Records a Flat Reaction in the Current Update - EPS Guidance Update - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Midwest Limited reports INR645 crore revenue in FY26 - scanx.trade</t>
+          <t>Eurotex shareholders clear all resolutions at 40th AGM, back capital and board moves - TipRanks</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Midwest (MIDWESTLTD.NS) Rallies +0.60% as Bulls Target ₹1118.78 2026-09-10 - Island Reversal - siam.in</t>
+          <t>EUROTEXIND Q2 2026 Earnings: Reported Loss of ₹0.91 Per Share as Revenue Figure Remains Undisclosed - New Analyst Coverage - siam.in</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Midwest Ltd. Share Price Near Low: Technical, Fundamental - Univest</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Midwest Ltd. Share Price: Price, Valuation, Sector View - Univest</t>
-        </is>
-      </c>
+          <t>Eurotex shareholders clear all resolutions at 40th AGM, back capital and board moves - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2556,22 +2596,22 @@
         <v>200.6999969482422</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>192.5599975585938</v>
+        <v>187.1100006103516</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>193.4100036621094</v>
+        <v>188.3000030517578</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>197.5800018310547</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>193.4100036621094</v>
+        <v>188.3000030517578</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>19639692</v>
+        <v>37093046</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-2.11</v>
+        <v>-4.7</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -2590,7 +2630,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs share price jumps 13%: Fintech stock rises sharply as trading volume explodes - livemint.com</t>
+          <t>Pine Labs share price jumps 13%: Fintech stock rises sharply as trading volume explodes - Livemint</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2610,68 +2650,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EMMVEE.NS</t>
+          <t>GRADIENTE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Emmvee Photovoltaic Power Limited</t>
+          <t>Gradiente Infotainment Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>340.7999877929688</v>
+        <v>2.359999895095825</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>341.8999938964844</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>327.1000061035156</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>332.6499938964844</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>339.75</v>
+        <v>2.369999885559082</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>332.6499938964844</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2189620</v>
+        <v>375585</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-2.09</v>
+        <v>-4.64</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Here's why Emmvee Photovoltaic shares jumped over 8% on Monday - CNBC TV18 - linkedin.com</t>
+          <t>Gradiente Infotainment launches Abhaya trailer and music videos - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Emmvee Photovoltaic appoints Murugesh C as company secretary - scanx.trade</t>
+          <t>Gradiente Infotainment (NSE:GRADIENTE): What Does the Release of Music Video "DEVA" Mean for the Company? - Kalkine India</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>EMMVEE Share Price Rises 7.65%: Price Action and Valuation - Univest</t>
+          <t>GRADIENTE.NS Q2 2023 Earnings: Marginal Profit of ₹0.06 Per Share as Stock Slides 4.88% - Revenue Per Share - siam.in</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-09-21 — cnbctv:c0a25f30e094b:0 - TradingView</t>
+          <t>Gradiente Infotainment (NSE:GRADIENTE): What Does the Release of Music Video "DEVA" Mean for the Company? - Kalkine India</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Emmvee Photovoltaic appoints Murugesh C as company secretary - scanx.trade</t>
+          <t>Momentum Stocks: PNB Housing Finance, Divis Labs, Ipca Labs, Paytm hit 52-week high - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2679,68 +2719,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AGI.NS</t>
+          <t>EMPOWER.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>AGI Greenpac Limited</t>
+          <t>Empower India Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>847</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>850.4000244140625</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>825.5999755859375</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>828.2999877929688</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>845.7000122070312</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>828.2999877929688</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>114423</v>
+        <v>1642208</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-2.06</v>
+        <v>-4.63</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Alamos Gold Inc (AGI) Stock Up 3.1% and Still Undervalued -- GF Score: 83/100 - GuruFocus</t>
+          <t>Penny stock under 10 rupees hits 5% upper circuit after this acquisition update - Livemint</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Alamos Gold Inc. $AGI Shares Bought by Andra AP fonden - marketbeat.com</t>
+          <t>Dangote to empower two million women with refinery IPO shares - PM News Nigeria</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>AGI Greenpac Share Price Today: Price Rise and Valuation - Univest</t>
+          <t>What employees should know before their company goes public - Empower</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Multibagger Stock Alert! AGI Infra Down 4.2%, Delivers 661% Returns In 3 Yrs | What's Next For Investors? - Goodreturns</t>
+          <t>Empower India Shares Hit 5% Upper Circuit After Acquisition Plan; Company To Buy 100% Of Valiance Engineers - Goodreturns</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>AGI Inc Class A Actuals &amp; Estimates (NYSE:AGBK) - TradingView</t>
+          <t>Empower India Ltd Upgraded to Buy on Strong Technical and Financial Performance - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2748,68 +2788,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CENTRUM.NS</t>
+          <t>RVTH.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Centrum Capital Limited</t>
+          <t>Revathi Equipment India Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>21.85000038146973</v>
+        <v>718.75</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>21.85000038146973</v>
+        <v>719</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20.90999984741211</v>
+        <v>620</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>21</v>
+        <v>641.1500244140625</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>21.43000030517578</v>
+        <v>671.5499877929688</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21</v>
+        <v>641.1500244140625</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>193820</v>
+        <v>1229</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-2.01</v>
+        <v>-4.53</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Centrum Capital Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Revathi Equipment India Share Price Today Down 11.67% - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Centrum Holding Prepares London IPO with Citi and JPMorgan - UzDaily</t>
+          <t>Revathi Equipment India Share Price Today: Market Cap, Peers - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Centrum Capital Ltd. Stock News - Value Research</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Centrum Capital Share Price: Good Buy After Q1 FY27 Results? - Univest</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Centrum Holding Prepares London IPO with Citi and JPMorgan - UzDaily</t>
-        </is>
-      </c>
+          <t>Revathi Equipment India Share Price Today: Market Cap, Peers - Univest</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2817,68 +2849,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SUNDARMFIN.NS</t>
+          <t>AURUS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Finance Limited</t>
+          <t>AURUS GEM CORPORATION LIMITED</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4729.2001953125</v>
+        <v>4.909999847412109</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4741.5</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4640</v>
+        <v>4.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4657.10009765625</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4751.89990234375</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4657.10009765625</v>
+        <v>4.670000076293945</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>33922</v>
+        <v>124281</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-1.99</v>
+        <v>-4.5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Finance Share Price News With Valuation Update - Univest</t>
+          <t>Modi shares ride with Putin in armoured Aurus Senat - The Tribune</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Two Trades for Today: A mid-cap private bank for a 6.3% upmove, an NBFC stock for an almost 7% gain - The Economic Times</t>
+          <t>Modi shares ride with Putin in armoured Aurus Senat - The Tribune</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Should You Be Adding Sundaram Finance (NSE:SUNDARMFIN) To Your Watchlist Today? - simplywall.st</t>
+          <t>Aurus Gem publishes newspaper notice for September 29 AGM - scanx.trade</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Finance Holds Its Ground: SUNDARMFIN.NS Edges Higher at ₹4539.6 - Dividend ETF - siam.in</t>
+          <t>Putin arrives in Aurus Senat, Xi Jinping's Hongqi N701, coming to Delhi: Inside the 'moving bunkers' at BRICS Summit | Key features - ET Now</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Sundaram Finance Share Price Rise: Valuation And Sector - Univest</t>
+          <t>BRICS Summit 2026: Putin’s Aurus vs Xi Jinping’s Hongqi L5 – which car is more powerful? Features, price and security - Zee News</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2886,68 +2918,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT.NS</t>
+          <t>SHILGRAVQ.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Persistent Systems Limited</t>
+          <t>Shilp Gravures Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5400</v>
+        <v>154.5700073242188</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5413</v>
+        <v>160</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5249</v>
+        <v>144</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>5260.5</v>
+        <v>147.6699981689453</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5366</v>
+        <v>154.5700073242188</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5260.5</v>
+        <v>147.6699981689453</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>239392</v>
+        <v>32843</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-1.97</v>
+        <v>-4.46</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Stock Picks Today: HDFC Bank, Persistent Systems, Dixon Tech, Hindalco, Voltas, And More On Brokerages' Radar - NDTV Profit</t>
+          <t>Shilp Gravures Share Price Falls 10.82%: Valuation View - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>GIFT Nifty down 45 pts; Adani shares, Hero Motors, Persistent, IRB Infra, among top stocks in focus - Business Today</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Stocks to Watch Today: Hero Motors, RHI Magnesita, Persistent Systems, IRB Infrastructure, Jindal Supreme,... - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Persistent Systems Secures 83.25% Nagarro Ownership, Extends Acceptance to October 6 - Sahi</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Persistent Systems picks additional 61% stake in German-based firm Nagarro; check details - Upstox</t>
-        </is>
-      </c>
+          <t>Shilp Gravures Share Price Falls 10.82%: Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2955,68 +2975,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>TREJHARA.NS</t>
+          <t>GOCLCORP.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>TREJHARA SOLUTIONS LIMITED</t>
+          <t>GOCL Corporation Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>136.9700012207031</v>
+        <v>407.75</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>138.9700012207031</v>
+        <v>413.7999877929688</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>132.1000061035156</v>
+        <v>389.1499938964844</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>133.5200042724609</v>
+        <v>392.75</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>136.2100067138672</v>
+        <v>411.0499877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>133.5200042724609</v>
+        <v>392.75</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>7569</v>
+        <v>281372</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-1.97</v>
+        <v>-4.45</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Trejhara Solutions approves FY26 financials at 9th AGM - scanx.trade</t>
+          <t>GOCL Corporation Ltd. Share Price and Sector Comparison - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Trejhara Solutions approves FY26 financials at 9th AGM - scanx.trade</t>
+          <t>GOCL Corporation Ltd. Share Price and Sector Comparison - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>TREJHARA (TREJHARA.NS) Stock: Slides -1.64%, Support at ₹138.06 2026-09-10 - Breadth Thrust - siam.in</t>
+          <t>GOCL (GOCLCORP.NS) Results at a Glance: The Report Supplies Updated Headline Figures in the Reported Period; Price Reaction: The Stock Ends Up 0.43% in Latest Trading - SaaS Earnings Trends - siam.in</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Trejhara Solutions Targets Steady Long-Term Growth Via Strategic Market Expansion - Sahi</t>
+          <t>1500% dividend stock alert! Check amount per share, record date, payment timeline and performance - TradingView</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Trejhara Solutions Expands Global Logistics Focus With Growth Strategy - Kalkine India</t>
+          <t>GOCL Corporation schedules 65th AGM for September 29, 2026 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3024,68 +3044,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>NILASPACES.NS</t>
+          <t>PAR.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces Limited</t>
+          <t>Par Drugs And Chemicals Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12.27000045776367</v>
+        <v>136.7899932861328</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>12.27000045776367</v>
+        <v>136.7899932861328</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>11.67000007629395</v>
+        <v>131.3000030517578</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>11.80000019073486</v>
+        <v>131.9199981689453</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12.02000045776367</v>
+        <v>137.8200073242188</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>11.80000019073486</v>
+        <v>131.9199981689453</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1302370</v>
+        <v>15475</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-1.83</v>
+        <v>-4.28</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces (NILASPACES.NS) Edges Higher to ₹12.55; ₹13.18 Resistance in Focus - Gamma Flip Level - siam.in</t>
+          <t>Apimeds Pharmaceuticals completes 1-for-10 reverse stock split and reduces par value - Investing.com India</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces promoter Kiran B Vadodaria cuts stake by 0.25% - scanx.trade</t>
+          <t>Apimeds Pharmaceuticals completes 1-for-10 reverse stock split and reduces par value - Investing.com India</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces opens remote e-voting for key resolutions - scanx.trade</t>
+          <t>Manika Plastech shares debut at par with issue price; drop 5% later - BusinessLine</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>NILASPACES.NS Q2 2026 Earnings: Revenue Jumps 36.25% YoY, EPS at ₹0.73 - EBITDA Analysis - siam.in</t>
+          <t>Manika Plastech shares list at par with IPO issue price on NSE, BSE - Upstox</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Nila Spaces promoter Kiran B Vadodaria cuts stake by 0.25% - scanx.trade</t>
+          <t>Manika Plastech shares make flat market debut, list at par with IPO price - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3093,68 +3113,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SWIGGY.NS</t>
+          <t>MONEYBOXX.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Swiggy Limited</t>
+          <t>Moneyboxx Finance Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>284.2999877929688</v>
+        <v>57.40000152587891</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>289.6499938964844</v>
+        <v>58.40000152587891</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>278.1499938964844</v>
+        <v>54.52999877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>278.8500061035156</v>
+        <v>54.95999908447266</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>284.0499877929688</v>
+        <v>57.40000152587891</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>278.8500061035156</v>
+        <v>54.95999908447266</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>11627947</v>
+        <v>70288</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-1.83</v>
+        <v>-4.25</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Top breakout stocks to buy today: Swiggy, Welspun, Finolex, Vishal Mega Mart, Carborundum by Sumeet Bagadia | Targets - livemint.com</t>
+          <t>Moneyboxx Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Top breakout stocks to buy today: Swiggy, Welspun, Finolex, Vishal Mega Mart, Carborundum by Sumeet Bagadia | Targets - livemint.com</t>
+          <t>Moneyboxx Finance to host analyst meet on Sep 28, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Swiggy shares drop 4%, market value down Rs 5,000 crore in 2 days. Here’s why - The Economic Times</t>
+          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Swiggy Shares in Focus After Major MSCI Index Move: What Triggered the Decision? - Outlook Money</t>
+          <t>Moneyboxx Finance FY26 net profit rises 7.4% to ₹1.34 crore - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>India's Swiggy pares gains as its shares exit MSCI indexes - Reuters</t>
+          <t>Moneyboxx Finance Share Price Rises 9.99% on Valuation View - Univest</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3162,68 +3182,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ISHANCH.NS</t>
+          <t>TERASOFT.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Limited</t>
+          <t>Tera Software Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>51.15000152587891</v>
+        <v>240.3000030517578</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>51.97999954223633</v>
+        <v>246.9499969482422</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>48.45000076293945</v>
+        <v>228.6000061035156</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>49.88000106811523</v>
+        <v>230.8000030517578</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>50.77999877929688</v>
+        <v>240.8000030517578</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>49.88000106811523</v>
+        <v>230.8000030517578</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>16720</v>
+        <v>37055</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-1.77</v>
+        <v>-4.15</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>ISHANCH Q2 2026 Earnings: ₹3.0 Loss Per Share and a 27.6% Revenue Decline, Yet the Stock Gains 7.75% - Return On Equity - siam.in</t>
+          <t>Tera Software (TERASOFT.NS) Slips 2% to ₹248.4 as Stock Tests Support Zone - Arms Index - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Share Price Today After 10.74% Gain - Univest</t>
+          <t>TVS Supply Chain Solutions initiates arbitration to recover ₹3.69 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Share Price Today: key metrics - Univest</t>
+          <t>Tera Software Ltd 52 Week Low Streak And Valuation View - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Share Price Today After 10.74% Gain - Univest</t>
+          <t>Do Tera Software's (NSE:TERASOFT) Earnings Warrant Your Attention? - simplywall.st</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Ishan Dyes and Chemicals Share Price Today After 11.7% Rise - Univest</t>
+          <t>Tera Software Share Price Near Yearly Low, Valuation View - Univest</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3231,68 +3251,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>XTRANET.NS</t>
+          <t>TANAA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Limited</t>
+          <t>Taneja Aerospace &amp; Aviation Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>336.3500061035156</v>
+        <v>366.7000122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>337.7000122070312</v>
+        <v>375</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>319</v>
+        <v>347.1000061035156</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>328.4700012207031</v>
+        <v>352.4500122070312</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>334.3599853515625</v>
+        <v>367.0499877929688</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>328.4700012207031</v>
+        <v>352.4500122070312</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>624046</v>
+        <v>183253</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-1.76</v>
+        <v>-3.98</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+          <t>Taneja Aerospace &amp; Aviation Ltd (NSE: TANAA) Gains 15.68% as Stock Sees Renewed Market Interest - Kalkine India</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+          <t>Taneja Aerospace &amp; Aviation Ltd (NSE: TANAA) Gains 15.68% as Stock Sees Renewed Market Interest - Kalkine India</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>XTRANET Share Price Today Near Yearly High, Rs 1,632 Cr Cap - Univest</t>
+          <t>Taneja Aerospace &amp; Aviation (TANAA): Niche Defence Stock Watch - Kalkine India</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>XTRANET Share Price Update: 8.26% Gain and Fundamentals - Univest</t>
+          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies to host analyst meet on September 24 - scanx.trade</t>
+          <t>Taneja Aerospace &amp; Aviation Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:24:28 IST</t>
+          <t>2026-09-23 20:41:43 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3300,55 +3320,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MASFIN.NS</t>
+          <t>MEDICO.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MAS Financial Services Limited</t>
+          <t>Medico Remedies Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>289.5</v>
+        <v>34.15000152587891</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>290.0499877929688</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>283.6000061035156</v>
+        <v>31.81999969482422</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>284.3999938964844</v>
+        <v>32.65000152587891</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>289.3500061035156</v>
+        <v>33.95999908447266</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>284.3999938964844</v>
+        <v>32.65000152587891</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>71040</v>
+        <v>583854</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-1.71</v>
+        <v>-3.86</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>MAS Financial Services Ltd. Stock News - Value Research</t>
+          <t>Medico Remedies Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAS Financial Services Receives Voluntary ESG Rating of 71 from SES - TipRanks</t>
+          <t>Medico Remedies Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>MAS Financial Services Receives Voluntary ESG Rating of 71 from SES - TipRanks</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Medico Remedies shareholders approve FY26 accounts, director reappointments - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Medico Remedies price fall: valuation and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Prism Medico and Pharmacy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,12 +439,12 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UNIDT.NS</t>
+          <t>INDIAGLYCO.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Limited</t>
+          <t>India Glycols Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>231</v>
+        <v>256.8999938964844</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>272</v>
+        <v>309.2000122070312</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>231</v>
+        <v>255.3999938964844</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>269.5</v>
+        <v>306</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>235.2400054931641</v>
+        <v>257.7000122070312</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>269.5</v>
+        <v>306</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>520738</v>
+        <v>4840415</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>14.56</v>
+        <v>18.74</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Share Price: price rise and valuation - Univest</t>
+          <t>Did India Glycols shares crash 80%? Here’s why the plunge is not real - Fortune India</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 12 Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+          <t>India Glycols Share Price Today up 9.62%: key stock analysis - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Limited Secures ₹5.04 Crore Order from ONGC for Integral Blade Stabilizer Supply - scanx.trade</t>
+          <t>India Glycols demerged into three entities - India Glycols, IGL Spirits, and Ennature Bio Pharma - Indian Chemical News</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Limited (NSE:UNIDT) Goes Ex-Dividend Soon - simplywall.st</t>
+          <t>India Glycols shares: Why this multibagger stock is showing 80% crash in some trading apps today - Business Today</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Limited Receives Order From Argentera Engenharia E Serviços De Petróleo E Gas Ltda For Supply Of Casing Pipe With UDT Connectors - marketscreener.com</t>
+          <t>Demerger news: 3 new separate entities formed - Check benefits, shareholding pattern and what stock investors got - livemint.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>REMSONSIND.NS</t>
+          <t>DCI.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Remsons Industries Limited</t>
+          <t>Dc Infotech And Communication Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>102.5</v>
+        <v>265</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>113.3899993896484</v>
+        <v>318.8999938964844</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>101.5199966430664</v>
+        <v>264.2999877929688</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>111.0400009155273</v>
+        <v>302.3999938964844</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>99.87000274658203</v>
+        <v>268.6000061035156</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>111.0400009155273</v>
+        <v>302.3999938964844</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1198779</v>
+        <v>1477225</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>11.18</v>
+        <v>12.58</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Remsons Industries Limited (NSE:REMSONSIND) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Donaldson Company, Inc. (DCI) Stock Forecasts - Yahoo Finance</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Remsons UK Subsidiary Wins ₹30 Crore Hood Rod Contract - scanx.trade</t>
+          <t>Donaldson Company, Inc. (DCI) Stock Forecasts - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Remsons Industries Share Price news: Rs 94.4 and 8.52% rise - Univest</t>
+          <t>Donaldson Co. CEO Tod Carpenter sells $2.9 million in DCI stock - Investing.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Remsons Industries Ltd (REMSONSIND): Export Story in Focus - Kalkine India</t>
+          <t>DCI Share Price Rise: Fundamentals, Peers and Market Cap - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Remsons Industries Share Price Today up 9.93% | Rs 88.55 - Univest</t>
+          <t>Why (DCI) Price Action Is Critical for Tactical Trading - Stock Traders Daily</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,60 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>FRONTSP.NS</t>
+          <t>REMSONSIND.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Frontier Springs Limited</t>
+          <t>Remsons Industries Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1451.800048828125</v>
+        <v>102.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1569.800048828125</v>
+        <v>113.3899993896484</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1451.800048828125</v>
+        <v>101.5199966430664</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1540.800048828125</v>
+        <v>111.120002746582</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1394.599975585938</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1540.800048828125</v>
+        <v>111.120002746582</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1303275</v>
+        <v>1519376</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10.48</v>
+        <v>11.26</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Frontier Springs shares permitted to trade on NSE from April 20 - scanx.trade</t>
+          <t>Be Sure To Check Out Remsons Industries Limited (NSE:REMSONSIND) Before It Goes Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Frontier Springs Ltd (FRONTSP): Rail Capex Play Under the Lens - Kalkine India</t>
+          <t>Remsons UK Subsidiary Wins ₹30 Crore Hood Rod Contract - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Frontier Springs Ltd (FRONTSP): Rail Capex Play Under the Lens - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Remsons Industries Share Price news: Rs 94.4 and 8.52% rise - Univest</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Remsons Industries Ltd (REMSONSIND): Export Story in Focus - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Remsons Industries Share Price Today up 9.93% | Rs 88.55 - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VIKRAN.NS</t>
+          <t>KSCL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering Limited</t>
+          <t>Kaveri Seed Company Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>58.5</v>
+        <v>712.8499755859375</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>62.61999893188477</v>
+        <v>819.9500122070312</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>57.52999877929688</v>
+        <v>704.4000244140625</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.52999877929688</v>
+        <v>783.8499755859375</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>56.13999938964844</v>
+        <v>710.7000122070312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>61.52999877929688</v>
+        <v>783.8499755859375</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>27516784</v>
+        <v>19331957</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>9.6</v>
+        <v>10.29</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
+          <t>KSCL Share Price: near 52-week low with mixed fundamentals - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering hosts investor meet at Anand Rathi conference on Sep 21 - scanx.trade</t>
+          <t>Kaveri Seed Closes Trading Window Ahead of Q2 FY2026 Results - TipRanks</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Vikran (VIKRAN.NS) Quarterly Figures: The Report Provides a New Financial Snapshot at the Close; After Earnings: The Stock Ends Down 0.25% in the Latest Reading - Cash Flow Report - siam.in</t>
+          <t>Kaveri (KSCL.NS) Market: Declines 0.74% to ₹781.05 in the Latest Session; Next Test: the Price Remains Bounded by the Supplied Support and Resistance in Latest Trading - Dividend ETF - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering shareholders approve ₹1,000 crore NCD facility - scanx.trade</t>
+          <t>Kaveri (KSCL.NS) Update: Records a 0.08% Decrease to ₹786.20 in the Current Update; Price Setup: the ₹746.89 to ₹825.51 Range Remains in Focus - Parabolic SAR - siam.in</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering hosts investor meet at Anand Rathi conference on Sep 21 - scanx.trade</t>
+          <t>Kaveri Seed Company Share Price: fresh 52-week low analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,64 +829,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA.NS</t>
+          <t>DANGEE.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>H.G. Infra Engineering Limited</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>448.8500061035156</v>
+        <v>2.75</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>488.8500061035156</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>445.4500122070312</v>
+        <v>2.740000009536743</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>482.7000122070312</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>450.7000122070312</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>482.7000122070312</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>251066</v>
+        <v>7561092</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA.NS Q2 2026 Earnings: EPS of ₹50.69 With Modest 2.96% Revenue Growth as Shares Slip 0.67% - Earnings Sentiment Score - siam.in</t>
+          <t>Volume Gainers, September 24, 2026 at 3:30 PM IST: Kaveri Seed Leads Volume Jump - HDFC Sky</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>HG Infra Engineering Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+          <t>Volume Gainers, September 24, 2026 at 3:30 PM IST: Kaveri Seed Leads Volume Jump - HDFC Sky</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>HG Infra Engineering Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+          <t>Dangee Dums Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>H.G. Infra Engineering confirms Aug 19 AGM date, e-voting window - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Volume Gainers, September 24, 2026 at 12:00 PM IST: Dangee Dums Leads Volume Jump - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>The Dangee Dums Bull Case - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,56 +898,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO.NS</t>
+          <t>KABRAEXTRU.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Jamna Auto Industries Limited</t>
+          <t>Kabra Extrusion Technik Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>129</v>
+        <v>739.7999877929688</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>138.6699981689453</v>
+        <v>806.0999755859375</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>128.3200073242188</v>
+        <v>737</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>138.5899963378906</v>
+        <v>806.0999755859375</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>129.5500030517578</v>
+        <v>732.8499755859375</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>138.5899963378906</v>
+        <v>806.0999755859375</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5060192</v>
+        <v>520788</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6.98</v>
+        <v>10</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Jamna Auto Industries Limited (NSE:JAMNAAUTO) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Kabra Extrusiontechnik Share Price near 52-week high | - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Jamna Auto Industries Limited (NSE:JAMNAAUTO) Before It Goes Ex-Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Kabra Extrusiontechnik Share Price near 52-week high | - Univest</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Kabra Extrusion Technik (KABRAEXTRU.NS) Rises 2.47% to ₹725, Holding Above Key Support - siam.in</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Kabra Extrusiontechnik Share Price rises 9.10% to Rs 727 - Univest</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Kabra Extrusiontechnik KABRAEXTRU Preferential Issue Allottee Change - Kalkine India</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -943,64 +967,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT.NS</t>
+          <t>CUBEXTUB.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Greaves Cotton Limited</t>
+          <t>Cubex Tubings Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>206.1699981689453</v>
+        <v>138.3999938964844</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>220</v>
+        <v>138.3999938964844</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>202.2200012207031</v>
+        <v>125.8199996948242</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>219.4100036621094</v>
+        <v>138.3999938964844</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>206.0099945068359</v>
+        <v>125.8199996948242</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>219.4100036621094</v>
+        <v>138.3999938964844</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4385126</v>
+        <v>805254</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Elpro International increases stake in Greaves Cotton with ₹5 crore investment - scanx.trade</t>
+          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Elpro International increases stake in Greaves Cotton with ₹5 crore investment - scanx.trade</t>
+          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Greaves Cotton (GREAVESCOT.NS) Holds Near ₹194.78 as Market Weighs E-Mobility Transition - Break of Structure - siam.in</t>
+          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Greaves Cotton takes full control of Excel Controllinkage as acquisition completes - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Cubex Tubings Share Price rise: fundamentals and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Cubex Tubings Limited Board Approves ₹135 Crore Fund-Raising Plan - EquityBulls</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1008,68 +1036,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP.NS</t>
+          <t>DCMSIL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited</t>
+          <t>DCM Shriram International Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>68.84999847412109</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>74.80000305175781</v>
+        <v>85.19999694824219</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>68.84999847412109</v>
+        <v>74.09999847412109</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>72.76999664306641</v>
+        <v>85.19999694824219</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>68.65000152587891</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>72.76999664306641</v>
+        <v>85.19999694824219</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>22811188</v>
+        <v>396593</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6</v>
+        <v>9.99</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
+          <t>DCM Shriram International Share Price and Sector Analysis - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
+          <t>DCM Shriram International Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited (DELTACORP.NS) Consolidates Near ₹54 as Traders Eye Range Boundaries - Factor Timing - siam.in</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>DELTACORP Outlook for the Week - Equitypandit</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Delta Corp sets Sept 10 AGM; details TDS rules for ₹0.50 dividend - scanx.trade</t>
-        </is>
-      </c>
+          <t>DCM Shriram International Ltd. Upper Circuit: Price and Key Data - Univest</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1077,68 +1097,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>FILATFASH.NS</t>
+          <t>BOHRAIND.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions Limited</t>
+          <t>Bohra Industries Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1899999976158142</v>
+        <v>13.10999965667725</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.1899999976158142</v>
+        <v>15</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.1800000071525574</v>
+        <v>13.10999965667725</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.1899999976158142</v>
+        <v>14.93000030517578</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.1800000071525574</v>
+        <v>13.64000034332275</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1899999976158142</v>
+        <v>14.93000030517578</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>35987703</v>
+        <v>36086</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5.56</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions Limited (NSE:FILATFASH) Shares May Have Slumped 26% But Getting In Cheap Is Still Unlikely - simplywall.st</t>
+          <t>Bohra Industries (BOHRAIND.NS) Ticks Up 1.38% to ₹13.18 as Stock Holds Above Key ₹12.52 Support - Factor Valuation - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Filatex Fashions resolves preferential allotment dispute through conciliation - ETLegalWorld.com</t>
+          <t>Bohra Industries (BOHRAIND.NS) Ticks Up 1.38% to ₹13.18 as Stock Holds Above Key ₹12.52 Support - Factor Valuation - siam.in</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>FILATEX FASHIONS LIMITED Share Price - Live NSE: FILATFASH Stock Price &amp; Chart - Upstox</t>
+          <t>Bohra Industries Trades Lower at ₹12.35: Key Support Holds as Downside Pressure Persists - Anchored VWAP - siam.in</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Have Filatex Fashions Insiders Been Selling Stock? - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>FILATFASH Stock Price and Chart — NSE:FILATFASH - TradingView</t>
-        </is>
-      </c>
+          <t>BOHRAIND Q2 2026 Earnings: Zero Revenue and ₹-1.4 EPS Highlight Dormant Quarter - EPS Guidance Update - siam.in</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1146,64 +1162,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDREL.NS</t>
+          <t>VIKRAN.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Raymond Realty Limited</t>
+          <t>Vikran Engineering Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>664.5999755859375</v>
+        <v>58.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>717</v>
+        <v>62.61999893188477</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>662.5</v>
+        <v>57.52999877929688</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>707.0999755859375</v>
+        <v>60.9900016784668</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>671.4500122070312</v>
+        <v>56.13999938964844</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>707.0999755859375</v>
+        <v>60.9900016784668</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>14860538</v>
+        <v>34846412</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5.31</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND REALTY Share Price Today: price rise and valuation - Univest</t>
+          <t>Vikran Engineering shares rally nearly 12% on securing ₹154 crore order from Power Grid - Upstox</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND REALTY Share Price Today: price rise and valuation - Univest</t>
+          <t>Vikran Engineering shares rally nearly 12% on securing ₹154 crore order from Power Grid - Upstox</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Raymond Realty Limited announced that it expects to receive INR 1.021906756 billion in funding from J K Investors Ltd. - marketscreener.com</t>
+          <t>Vikran Engineering Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Raymond Realty to Join Jefferies 5th India Forum for Investor Meetings - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Vikran (VIKRAN.NS) Quarterly Figures: The Report Provides a New Financial Snapshot at the Close; After Earnings: The Stock Ends Down 0.25% in the Latest Reading - Cash Flow Report - siam.in</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Vikran Engineering shareholders approve ₹1,000 crore NCD facility - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1211,60 +1231,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK.NS</t>
+          <t>ABDL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>The South Indian Bank Limited</t>
+          <t>Allied Blenders and Distillers Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>47</v>
+        <v>660</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>49.86000061035156</v>
+        <v>722</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46.72000122070312</v>
+        <v>650</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>49.56999969482422</v>
+        <v>712.1500244140625</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>47.08000183105469</v>
+        <v>656.4000244140625</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>49.56999969482422</v>
+        <v>712.1500244140625</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>36985873</v>
+        <v>6588934</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.29</v>
+        <v>8.49</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>South Indian Bank (NSE:SOUTHBANK) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
+          <t>ABDL Share Price rises 5.37%: price action and fundamentals - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>South Indian Bank (NSE:SOUTHBANK) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
+          <t>Allied Blenders stock surges 6% as promoter offloads 55 lakh shares to meet MPS norms - BusinessLine</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Russell Howard shares a devastatingly raw update on the loss of his baby son, Felix - primetimer.com</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Allied Blenders stock surges 6% as promoter offloads 55 lakh shares to meet MPS norms - BusinessLine</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Allied Blenders shares surge over 5% after SBI Mutual Fund, Abu Dhabi Investment Authority buy stake - Upstox</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>India Sugar Import Shock Puts Allied Blenders And Globus Spirits In Focus - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1272,68 +1300,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY.NS</t>
+          <t>JAGSNPHARM.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Capillary Technologies India Limited</t>
+          <t>Jagsonpal Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>544.4500122070312</v>
+        <v>227.8999938964844</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>574.9000244140625</v>
+        <v>249.8399963378906</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>523.1500244140625</v>
+        <v>226.7599945068359</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>573.5</v>
+        <v>243.9700012207031</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>545.5499877929688</v>
+        <v>225.6300048828125</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>573.5</v>
+        <v>243.9700012207031</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>582800</v>
+        <v>9252323</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.12</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Capillary Technologies Completes Strategic Acquisition of Session M Companies - scanx.trade</t>
+          <t>Jagsonpal Pharmaceuticals Limited (NSE:JAGSNPHARM) Passed Our Checks, And It's About To Pay A ₹4.00 Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Capillary Technologies Completes Strategic Acquisition of Session M Companies - scanx.trade</t>
+          <t>Jagsonpal Pharmaceuticals Ltd (NSE: JAGSNPHARM) Acquires Wellness Portfolio for ₹46.7 Crore - Kalkine India</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Capillary Technologies India Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Jagsonpal Pharmaceuticals Ltd (NSE: JAGSNPHARM) Acquires Wellness Portfolio for ₹46.7 Crore - Kalkine India</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Mirae Asset sells 53,335 Capillary Technologies shares on Sep 18 - scanx.trade</t>
+          <t>Jagsonpal Pharmaceuticals releases Q1 FY27 earnings call recording online - scanx.trade</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY 52 Week Low Streak Deepens After Repeat Trough - Univest</t>
+          <t>Jagsonpal Pharmaceuticals acquires Wellness Portfolio for up to ₹46.7 crore - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1341,64 +1369,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>KANORICHEM.NS</t>
+          <t>GREAVESCOT.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kanoria Chemicals &amp; Industries Limited</t>
+          <t>Greaves Cotton Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>182.5</v>
+        <v>206.1699981689453</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>191.3500061035156</v>
+        <v>223.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>178.5899963378906</v>
+        <v>202.2200012207031</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>191.3500061035156</v>
+        <v>221.8300018310547</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>182.2400054931641</v>
+        <v>206.0099945068359</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>191.3500061035156</v>
+        <v>221.8300018310547</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>71500</v>
+        <v>15909049</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5</v>
+        <v>7.68</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Kanoria Chemicals &amp; Industries Ltd. Upper Circuit: Price and Key Data - Univest</t>
+          <t>Greaves Cotton (GREAVESCOT.NS) Holds Near ₹194.78 as Market Weighs E-Mobility Transition - Break of Structure - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Kanoria Chemicals &amp; Industries Ltd. Upper Circuit: Price and Key Data - Univest</t>
+          <t>Greaves Cotton takes full control of Excel Controllinkage as acquisition completes - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>KANORICHEM Share Price Today - Kanoria Chemicals &amp; Industries Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Kanoria Chemicals KANORICHEM Trading Window Closure Oct 2026 - Kalkine India</t>
-        </is>
-      </c>
+          <t>Greaves Cotton takes full control of Excel Controllinkage as acquisition completes - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1406,64 +1430,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>PRAENG.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>Prajay Engineers Syndicate Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>30.79999923706055</v>
+        <v>21</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>32.29999923706055</v>
+        <v>24.1299991607666</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30.11000061035156</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>32.29999923706055</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.77000045776367</v>
+        <v>21.3799991607666</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>32.29999923706055</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1651239</v>
+        <v>127589</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4.97</v>
+        <v>6.92</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Prajay Engineers Syndicate Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Share Price update on fundamentals - Univest</t>
+          <t>PRAENG Q2 2026 Earnings: Loss Per Share of ₹2.69 as Revenue Falls 33.12% Year-on-Year - Analyst Drop Coverage - siam.in</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI Q2 2026 Earnings: Revenue Jumps 213.6% YoY as EPS Hits ₹5.29, Shares Slip 5.2% - Profit Guidance Range - siam.in</t>
+          <t>Prajay Engineers Syndicate files FY26 annual report and AGM notice - scanx.trade</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Share Price update on fundamentals - Univest</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>PRAENG Q2 2026 Earnings: Loss Per Share of ₹2.69 as Revenue Falls 33.12% Year-on-Year - Analyst Drop Coverage - siam.in</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>PRAENG.NS Q2 2026 Earnings: Revenue Drops 33% YoY, Reports Loss of ₹2.69 Per Share - Analyst Drop Coverage - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1471,68 +1499,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GNA.NS</t>
+          <t>AVANTEL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GNA Axles Limited</t>
+          <t>Avantel Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>601.5</v>
+        <v>153</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>648</v>
+        <v>160</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>590</v>
+        <v>151.3800048828125</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>624.5</v>
+        <v>155.3399963378906</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>596.6500244140625</v>
+        <v>146.1699981689453</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>624.5</v>
+        <v>155.3399963378906</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>5757102</v>
+        <v>19464519</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.67</v>
+        <v>6.27</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>GNA Axles Share Price near 52-week high: price, valuation - Univest</t>
+          <t>Avantel shares rise 9% after Rs 177 crore satellite communication order from Zetwerk - The Economic Times</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>GNA Axles Ltd. Surges 7.32% to Day's High of Rs 641.75 — Outperforms Sector by 6.92 Percentage Points - MarketsMojo</t>
+          <t>Avantel shares rise 9% after Rs 177 crore satellite communication order from Zetwerk - The Economic Times</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>GNA Axles Limited (GNA.NS) Slips to ₹549.0 as Stock Tests Mid-Range Support - ETF Creation Redemption - siam.in</t>
+          <t>Price Action: Avantel shares surge 8% on order win; Macquarie initiates ‘Neutral’ on Angel One - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>GNA Axles Share Price: Is It a Good Buy After Q1 FY27 Results? - Univest</t>
+          <t>27% Jump In Six Months: Avantel Share Price Surges Over 9% In Trade Today. Here's Why - NDTV Profit</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>GNA Axles (GNA.NS) Slips 1.37% to ₹532.45: Key Levels to Watch as Stock Holds Above Support - Retail Driven Moves - siam.in</t>
+          <t>Avantel shares jump 9% on bagging order worth over ₹177 crore from Zetwerk Manufacturing - Upstox</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1540,68 +1568,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CELLO.NS</t>
+          <t>ZFSTEERING.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Cello World Limited</t>
+          <t>ZF Steering Gear (India) Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>324</v>
+        <v>710</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>344</v>
+        <v>760</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>320.1499938964844</v>
+        <v>709.8499755859375</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>338.4500122070312</v>
+        <v>746.0999755859375</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>324.1000061035156</v>
+        <v>703.6500244140625</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>338.4500122070312</v>
+        <v>746.0999755859375</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1653129</v>
+        <v>11028</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.43</v>
+        <v>6.03</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>After 29 years, TransUnion’s CFO will step down - Stock Titan</t>
+          <t>ZF (ZFSTEERING.NS) Earnings Reading: The Company Releases Its Current Earnings Data on the Day; Closing Move - siam.in</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>After 29 years, TransUnion’s CFO will step down - Stock Titan</t>
+          <t>ZF Steering Gear (India) Share Price Rise: Key Analysis - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Cello World Ltd Dividend History, Yield &amp; Record Date - indmoney.com</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Cello World Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - valueresearchonline.com</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Cello World Ltd. Share Price: 52-Week Low, Valuation View - Univest</t>
-        </is>
-      </c>
+          <t>ZF Steering Gear (India) Share Price Rise: Key Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1609,60 +1629,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE.NS</t>
+          <t>BLUSPRING.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
+          <t>Bluspring Enterprises Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>81.90000152587891</v>
+        <v>132.5899963378906</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>86.45999908447266</v>
+        <v>142.75</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>79</v>
+        <v>131.3200073242188</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>85.80000305175781</v>
+        <v>140.5599975585938</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>82.34999847412109</v>
+        <v>132.5899963378906</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>85.80000305175781</v>
+        <v>140.5599975585938</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>412926</v>
+        <v>1597809</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.19</v>
+        <v>6.01</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence Share Price Today: Sector and Peer View - Univest</t>
+          <t>BLUSPRING Share Price update after 8.92% rise in early trade - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence Share Price Today: Sector and Peer View - Univest</t>
+          <t>Bluspring Enterprises subsidiary secures ₹2,049.8 crore power plant O&amp;M contract - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence &amp; Wireless Technologies (KAVDEFENCE) Share Price Falls 8.66% Today - Univest</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Bluspring Enterprises Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>BLUSPRING ENTERPRISES Share Price Today: Down 9.99% - Univest</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Bluspring Enterprises Share: Bull Case vs Bear Case for 2026 - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1670,68 +1698,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM.NS</t>
+          <t>DELTACORP.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Limited</t>
+          <t>Delta Corp Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1245</v>
+        <v>68.84999847412109</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1314</v>
+        <v>74.80000305175781</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1233.849975585938</v>
+        <v>68.84999847412109</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1304.199951171875</v>
+        <v>72.68000030517578</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1251.900024414062</v>
+        <v>68.65000152587891</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1304.199951171875</v>
+        <v>72.68000030517578</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1315873</v>
+        <v>28298356</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.18</v>
+        <v>5.87</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM LIMITED Share Price - Live NSE: INDOMIM Stock Price &amp; Chart - Upstox</t>
+          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Upstox</t>
+          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM Share Price Today - INDO-MIM LIMITED Stock Price Live NSE/BSE - Univest</t>
+          <t>Delta Corp Limited (DELTACORP.NS) Consolidates Near ₹54 as Traders Eye Range Boundaries - Factor Timing - siam.in</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>IndoMIM Share Price Today - Indo-MIM Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+          <t>DELTACORP Outlook for the Week - Equitypandit</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Free float of INDO-MIM Limited – NSE:INDOMIM - TradingView</t>
+          <t>Delta Corp sets Sept 10 AGM; details TDS rules for ₹0.50 dividend - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1739,68 +1767,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KANPRPLA.NS</t>
+          <t>LAL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Limited</t>
+          <t>Lorenzini Apparels Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>256.4500122070312</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>274.9500122070312</v>
+        <v>9.489999771118164</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>256.2999877929688</v>
+        <v>8.470000267028809</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>267</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>257.0499877929688</v>
+        <v>8.569999694824219</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>267</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>21640</v>
+        <v>163991</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3.87</v>
+        <v>5.83</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Investors Shouldn't Be Too Comfortable With Kanpur Plastipack's (NSE:KANPRPLA) Earnings - simplywall.st</t>
+          <t>Dr. Lal PathLabs Stock Signals to Watch This Week - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Kanpur (KANPRPLA.NS) Financial Update: Available Data Shows the Latest Reported Performance under the Current Snapshot; Closing Reaction: The Share Price Sheds 4.13% in the Latest Reading - Earnings Trend Analysis - siam.in</t>
+          <t>ISOC promoter Shanti Lal Jain gifts 1.09% stake; holding falls to nil - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Limited (NSE: KANPRPLA) Stock Advances to Lead Mid-Cap Movers - Kalkine India</t>
+          <t>ISOC promoter Shanti Lal Jain gifts 1.09% stake; holding falls to nil - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Limited (KANPRPLA) Gains Momentum: Key Levels and Technical Outlook - MFI Oversold - siam.in</t>
+          <t>Dixon Tech, Bharat Dynamics, Chaman Lal Setia, Manyavar, Dividends: Last Day To Buy Shares To Qualify - NDTV Profit</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Kanpur Plastipack Share Price Today With Valuation View - Univest</t>
+          <t>Newly listed Shiprocket, Behari Lal Engineering post Q1 results; here’s how shares reacted - Fortune India</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1808,63 +1836,51 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL.NS</t>
+          <t>CRAVATEX.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Raymond Lifestyle Limited</t>
+          <t>Cravatex Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>674.0499877929688</v>
+        <v>341.7000122070312</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>720</v>
+        <v>410</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>670.75</v>
+        <v>340.9500122070312</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>703.4000244140625</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>677.4500122070312</v>
+        <v>341.7000122070312</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>703.4000244140625</v>
+        <v>361.4500122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>650370</v>
+        <v>14407</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>3.83</v>
+        <v>5.78</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Raymond Lifestyle Limited (NSE:RAYMONDLSL) Investor Conference Participation Update - Kalkine India</t>
+          <t>Cravatex Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Raymond Lifestyle Limited (NSE:RAYMONDLSL) Investor Conference Participation Update - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Raymond Lifestyle Share Price at fresh 52-week low, analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Raymond Lifestyle to host investor conference on Sep 3 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Raymond Lifestyle to host investor meet at PL Capital conference - scanx.trade</t>
-        </is>
-      </c>
+          <t>Cravatex Ltd. Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1989,7 +2005,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1997,68 +2013,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>POLICYBZR.NS</t>
+          <t>MFSL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech Limited</t>
+          <t>Max Financial Services Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1697.699951171875</v>
+        <v>1406.699951171875</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1697.699951171875</v>
+        <v>1429.800048828125</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1320.099975585938</v>
+        <v>1360.099975585938</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1320.099975585938</v>
+        <v>1410</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1886.300048828125</v>
+        <v>1562.900024414062</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1320.099975585938</v>
+        <v>1410</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2696626</v>
+        <v>11421538</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-30.02</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech (POLICYBZR.NS) Ticks Up 0.67% to ₹1805.0, Holding Above Key Support - Descending Triangle - siam.in</t>
+          <t>Max Financial Services Ltd (NSE: MFSL) Declines 9.46% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech Schedules Urgent Virtual Analyst Call - TipRanks</t>
+          <t>Max Financial Services Ltd (NSE: MFSL) Declines 9.46% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech (POLICYBZR) Holds Near ₹1,870 After Mild Upside: Support and Resistance in Focus - Bullish Sentiment - siam.in</t>
+          <t>Max Financial Services Share Price Today: key market context - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech Ltd. Share Price today: valuation and peer view - Univest</t>
+          <t>Max Financial Services Share Price and valuation update - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>PB (POLICYBZR.NS) Momentum: Finishes 2.75% Up at ₹1,847.70 in the Latest Session; Price Levels - siam.in</t>
+          <t>Max Financial Services Share Price Live: Latest Market Move - Univest</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2066,68 +2082,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AASTHA.NS</t>
+          <t>LTF.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Limited</t>
+          <t>L&amp;T Finance Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>96</v>
+        <v>279</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>96</v>
+        <v>290.6000061035156</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>80.80000305175781</v>
+        <v>279</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>80.80000305175781</v>
+        <v>282</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>89.76999664306641</v>
+        <v>310</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>80.80000305175781</v>
+        <v>282</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3605508</v>
+        <v>36068873</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.99</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Shares Hit 10% UC After Board Fixes September 28 Record Date for 1:1 Bonus Issue - Trade Brains</t>
+          <t>L&amp;T Finance Drops 2.36% to ₹314.3: Stock Holds Above Support Amid NBFC Sector Volatility - Revenue Growth Stocks - siam.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Secures ₹25 Crore Fabric Orders; Shares Fall 9.99% - HDFC Sky</t>
+          <t>PB Fintech shares fall 23%; Bajaj Finance, L&amp;T Finance also take hit; here's why - Business Today</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Secures ₹25 Crore Fabric Orders; Shares Fall 9.99% - HDFC Sky</t>
+          <t>Green LTF Holdings II LP director sells $126.1m in Life Time Group stock - Investing.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Ltd Upgraded to Hold as Technicals Improve Amid Mixed Financials - MarketsMojo</t>
+          <t>L&amp;T Finance Share Price Falls 2.30%: Price Action Review - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex approves 1:1 bonus, dividend, and fabric expansion - scanx.trade</t>
+          <t>PB Fintech shares fall 23%; Bajaj Finance, L&amp;T Finance also take hit; here's why - Business Today</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2135,68 +2151,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>LTF.NS</t>
+          <t>SGRL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Limited</t>
+          <t>Shree Ganesh Remedies Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>279</v>
+        <v>731.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>290.6000061035156</v>
+        <v>739.4500122070312</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>279</v>
+        <v>654</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>283.8500061035156</v>
+        <v>677.1500244140625</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>310</v>
+        <v>735.5499877929688</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>283.8500061035156</v>
+        <v>677.1500244140625</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>25771393</v>
+        <v>45846</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-8.44</v>
+        <v>-7.94</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Drops 2.36% to ₹314.3: Stock Holds Above Support Amid NBFC Sector Volatility - Revenue Growth Stocks - siam.in</t>
+          <t>Shree Ganesh Remedies Share Price rises 17.45%: analysis - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech shares fall 23%; Bajaj Finance, L&amp;T Finance also take hit; here's why - Business Today</t>
+          <t>Shree Ganesh Remedies Ltd. Share Price News and Analysis - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Green LTF Holdings II LP director sells $126.1m in Life Time Group stock - Investing.com</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>L&amp;T Finance Share Price Falls 2.30%: Price Action Review - Univest</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>PB Fintech shares fall 23%; Bajaj Finance, L&amp;T Finance also take hit; here's why - Business Today</t>
-        </is>
-      </c>
+          <t>Shree Ganesh Remedies Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2204,68 +2212,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HIKAL.NS</t>
+          <t>NOCIL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hikal Limited</t>
+          <t>NOCIL Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>230.4499969482422</v>
+        <v>204.9100036621094</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>233.1000061035156</v>
+        <v>204.9100036621094</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>216.1000061035156</v>
+        <v>187</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>216.2299957275391</v>
+        <v>191.3999938964844</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>232.4299926757812</v>
+        <v>206.3000030517578</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>216.2299957275391</v>
+        <v>191.3999938964844</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>966786</v>
+        <v>4915030</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-6.97</v>
+        <v>-7.22</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+          <t>Nocil Share Price Falls as Chemical Stock Stays in Focus - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd Downgraded to Sell Amid Weak Fundamentals and Mixed Technical Signals - MarketsMojo</t>
+          <t>NOCIL Ltd Hits Intraday Low Amid Price Pressure on 24 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd. Share Price News: Rs 247.80 and Market Cap View - Univest</t>
+          <t>NOCIL Ltd Hits Intraday Low Amid Price Pressure on 24 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd Downgraded to Sell Amid Weak Fundamentals and Mixed Technical Signals - MarketsMojo</t>
+          <t>NOCIL Stock Signals to Watch This Week - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd hosts analyst meet in Pune on September 4 - scanx.trade</t>
+          <t>NOCIL to discuss Q1FY27 performance on Aug 4 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2273,68 +2281,60 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NOCIL.NS</t>
+          <t>OSWALSEEDS.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Limited</t>
+          <t>ShreeOswal Seeds And Chemicals Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>204.9100036621094</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>204.9100036621094</v>
+        <v>13.75</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>187</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>192.1499938964844</v>
+        <v>12.68000030517578</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>206.3000030517578</v>
+        <v>13.56999969482422</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>192.1499938964844</v>
+        <v>12.68000030517578</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4051048</v>
+        <v>445150</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.86</v>
+        <v>-6.56</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Stock Signals to Watch This Week - Univest</t>
+          <t>ShreeOswal Seeds Share Price and Technical View - Kalkine India</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Stock Signals to Watch This Week - Univest</t>
+          <t>ShreeOswal Seeds Share Price and Technical View - Kalkine India</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Ltd Share Price Today,, NOCIL Share Price NSE, BSE - Business Today</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>NOCIL to discuss Q1FY27 performance on Aug 4 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Nocil Share Price rises 8.20%: valuation and sector view - Univest</t>
-        </is>
-      </c>
+          <t>Shree Oswal Seeds and Chemicals Share Price Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2342,68 +2342,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ISFT.NS</t>
+          <t>HALDER.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Intrasoft Technologies Limited</t>
+          <t>Halder Venture Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>105.3199996948242</v>
+        <v>263.8999938964844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>106.6999969482422</v>
+        <v>285</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>98.59999847412109</v>
+        <v>244</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>100.6999969482422</v>
+        <v>248.75</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>107.629997253418</v>
+        <v>266.1499938964844</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>100.6999969482422</v>
+        <v>248.75</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>145156</v>
+        <v>51353</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.44</v>
+        <v>-6.54</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Does IntraSoft Technologies (NSE:ISFT) Deserve A Spot On Your Watchlist? - simplywall.st</t>
+          <t>Halder Venture Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>IntraSoft Technologies NSE:ISFT Clarifies Price Movement - Kalkine India</t>
+          <t>Halder Venture Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>IntraSoft Technologies NSE:ISFT Clarifies Price Movement - Kalkine India</t>
+          <t>Halder Venture Share Price rises 9.85%: valuation check - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Intrasoft Technologies Share Price Today: Rs 104 update - Univest</t>
+          <t>Tata Chemicals, TCPL, Uno Minda, Welspun Living, Bandhan Bank, E2E Networks: Expert shares outlook - BusinessToday - IndiaIPO</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>ISFT.NS Q2 2026 Earnings: EPS of ₹8.14 With Revenue Up 5.33% YoY, Shares Slip 3.59% - Pre-Earnings Drift - siam.in</t>
+          <t>Halder Venture Ltd. Stock News - Value Research</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2411,68 +2411,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD.NS</t>
+          <t>SUBEXLTD.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Limited</t>
+          <t>Subex Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>51.77999877929688</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>51.77999877929688</v>
+        <v>22.21999931335449</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>48.59999847412109</v>
+        <v>20.30999946594238</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>48.88999938964844</v>
+        <v>20.70999908447266</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>52.20000076293945</v>
+        <v>22.07999992370605</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>48.88999938964844</v>
+        <v>20.70999908447266</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4202838</v>
+        <v>19504211</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-6.34</v>
+        <v>-6.2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide (JINDWORLD.NS) Edges Higher at ₹38.31; Key Support and Resistance in Focus - Dividend Growth Stocks - siam.in</t>
+          <t>Subex Ltd. Share Price rises 11.24%: valuation and sector - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Limited(BSE: 531543) dropped from S&amp;P Global BMI Index - marketscreener.com</t>
+          <t>Subex Ltd. Share Price Update: Price Rise and Valuation - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Share Price Falls in Second Session - Univest</t>
+          <t>Subex Ltd. Share Price Update: Price Rise and Valuation - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
+          <t>Subex seeks shareholder nod for new ESOP scheme, trust loan - scanx.trade</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Share Price Falls; Valuation Check - Univest</t>
+          <t>Subex shareholders approve all resolutions at 32nd AGM with 98% support - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2480,68 +2480,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SUBEXLTD.NS</t>
+          <t>SAICAPI.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Subex Limited</t>
+          <t>Sai Capital Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>21.89999961853027</v>
+        <v>157.25</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>22.21999931335449</v>
+        <v>157.25</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20.61000061035156</v>
+        <v>142.1499938964844</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>20.79000091552734</v>
+        <v>146.0299987792969</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.07999992370605</v>
+        <v>155.6900024414062</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20.79000091552734</v>
+        <v>146.0299987792969</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>12999858</v>
+        <v>488</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.84</v>
+        <v>-6.2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price rises 11.24%: valuation and sector - Univest</t>
+          <t>Technical Analysis of Sai Capital Ltd. (NSE:SAICAPI) - TradingView</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Update: Price Rise and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Subex Ltd. Share Price Update: Price Rise and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Subex shareholders approve all resolutions at 32nd AGM with 98% support - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Subex shareholders approve new ESOP scheme and trust authorization - scanx.trade</t>
-        </is>
-      </c>
+          <t>Technical Analysis of Sai Capital Ltd. (NSE:SAICAPI) - TradingView</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2549,64 +2537,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TANAA.NS</t>
+          <t>LAHOTIOV.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Limited</t>
+          <t>Lahoti Overseas Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>349.5</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>349.6000061035156</v>
+        <v>41</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>332.5</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>334.0499877929688</v>
+        <v>38.27999877929688</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>352.4500122070312</v>
+        <v>40.77000045776367</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>334.0499877929688</v>
+        <v>38.27999877929688</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>48044</v>
+        <v>14264</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.22</v>
+        <v>-6.11</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Ltd (NSE: TANAA) Gains 15.68% as Stock Sees Renewed Market Interest - Kalkine India</t>
+          <t>Lahoti Overseas Share Price today: valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Ltd (NSE: TANAA) Gains 15.68% as Stock Sees Renewed Market Interest - Kalkine India</t>
+          <t>Lahoti Overseas Limited Announces Resignation of Mahesh Mishra from Chief Financial Officer, Effective September 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation (TANAA) Share Price Falls 9.58% Today to Rs 246.25 - Univest</t>
+          <t>Lahoti Overseas Limited Announces Resignation of Mahesh Mishra from Chief Financial Officer, Effective September 09, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Ltd. Upper Circuit: Price and Key Data - Univest</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>LAHOTIOV June 2026 Quarter Earnings: EPS at ₹1.06 on ₹88.41 Crore Revenue; Stock Declines 5.95% - Share Repurchase Impact - siam.in</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>LAHOTIOV Jun 2026 Earnings: Steady ₹1.06 EPS on ₹88.41 Crore Revenue Keeps the Stock Flat - CEO Earnings Statement - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2614,68 +2606,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE.NS</t>
+          <t>MVELECTRO.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>BlueStone Jewellery and Lifestyle Limited</t>
+          <t>MV Electrosystems Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>862.4500122070312</v>
+        <v>867</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>862.5499877929688</v>
+        <v>867</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>812</v>
+        <v>811.5499877929688</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>812.0999755859375</v>
+        <v>818.5</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>855.5</v>
+        <v>871.5999755859375</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>812.0999755859375</v>
+        <v>818.5</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>5165054</v>
+        <v>903056</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.07</v>
+        <v>-6.09</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>BlueStone shares worth ₹513 crore change hands in block deal; stock in focus - CNBC TV18</t>
+          <t>MVELECTRO Share Price Today - MV Electrosystems Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>BlueStone shares worth ₹513 crore change hands in block deal; stock in focus - CNBC TV18</t>
+          <t>MVELECTRO Share Price Today - MV Electrosystems Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>BlueStone Jewellery share price falls 9% today | What's behind the plunge? - Livemint</t>
+          <t>MV Electrosystems Share Price today: Rs 800 and market cap - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Bluestone Jewellery &amp; Lifestyle Ltd leads losers in 'A' group - Business Standard</t>
+          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Market Trading Guide: Finolex Cables among 3 stock recommendations for Wednesday - The Economic Times</t>
+          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2683,60 +2675,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>BAJFINANCE.NS</t>
+          <t>MEGASTAR.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Finance Limited</t>
+          <t>Megastar Foods Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1005</v>
+        <v>277.5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1015</v>
+        <v>277.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>976</v>
+        <v>254.5500030517578</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>991.5</v>
+        <v>260.8999938964844</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1043.199951171875</v>
+        <v>277.6000061035156</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>991.5</v>
+        <v>260.8999938964844</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>8593006</v>
+        <v>8557</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.96</v>
+        <v>-6.02</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Finance Share Price Today declines 2.01%: key facts - Univest</t>
+          <t>Megastar Foods Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Emami promoters pledge and release shares with Bajaj Finance, DBS Bank - scanx.trade</t>
+          <t>Megastar Foods Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Emami promoters pledge and release shares with Bajaj Finance, DBS Bank - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
+          <t>Megastar Foods schedules 15th AGM for September 23, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Megastar Chiranjeevi's Kaka Team Shares Exciting Shooting Update - The Hans India</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2744,56 +2740,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>LASERPOWER.NS</t>
+          <t>ADROITINFO.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Laser Power &amp; Infra Limited</t>
+          <t>Adroit Infotech Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>284.75</v>
+        <v>13.88000011444092</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>285.3999938964844</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>272.8500061035156</v>
+        <v>12.60999965667725</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>273.5</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>287.3999938964844</v>
+        <v>13.52999973297119</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>273.5</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>388816</v>
+        <v>170767</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.84</v>
+        <v>-5.91</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Laser Power &amp; Infra Ltd Share Price Today,, LASERPOWER Share Price NSE, BSE - Business Today</t>
+          <t>Adroit Infotech Eases 1.44% to ₹10.25, Holds Above Key ₹9.74 Support - Fear Greed Index - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Laser Power &amp; Infra Ltd Share Price Today,, LASERPOWER Share Price NSE, BSE - Business Today</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
+          <t>Adroit Infotech Corrects XBRL-PDF Mismatch in FY26 Results - TipRanks</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Adroit Infotech Corrects XBRL-PDF Mismatch in FY26 Results - TipRanks</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2801,56 +2801,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>BLEL.NS</t>
+          <t>BAJFINANCE.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering Limited</t>
+          <t>Bajaj Finance Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>464</v>
+        <v>1005</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>464.3500061035156</v>
+        <v>1015</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>442.2000122070312</v>
+        <v>974</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>447.0499877929688</v>
+        <v>982</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>469.6000061035156</v>
+        <v>1043.199951171875</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>447.0499877929688</v>
+        <v>982</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>395492</v>
+        <v>13383127</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.8</v>
+        <v>-5.87</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,587,471 Equity Shares of Behari Lal Engineering Limited are subject to a Lock-Up Agreement Ending on 15-SEP-2026. - marketscreener.com</t>
+          <t>Bajaj Finance Share Price Today declines 2.01%: key facts - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,587,471 Equity Shares of Behari Lal Engineering Limited are subject to a Lock-Up Agreement Ending on 15-SEP-2026. - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>Emami promoters pledge and release shares with Bajaj Finance, DBS Bank - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Emami promoters pledge and release shares with Bajaj Finance, DBS Bank - scanx.trade</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2858,68 +2862,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>WHIRLPOOL.NS</t>
+          <t>SBGLP.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool of India Limited</t>
+          <t>Suratwwala Business Group Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>810</v>
+        <v>23.63999938964844</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>853.75</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>810</v>
+        <v>22.10000038146973</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>826.7000122070312</v>
+        <v>22.88999938964844</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>865.25</v>
+        <v>24.30999946594238</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>826.7000122070312</v>
+        <v>22.88999938964844</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5582985</v>
+        <v>202878</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.46</v>
+        <v>-5.84</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool Shares Spike 20% On Report Of Promoter Stake Sale Plan - NDTV Profit</t>
+          <t>Suratwwala Business Group (SBGLP.NS) Ticks Higher: Small-Cap Holds Above ₹21 on NSE - Head and Shoulders - siam.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Here's what the Whirlpool India management said on the promoter stake sale plans; Stock down 4% - CNBC TV18</t>
+          <t>Suratwwala Business Group Share Price Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool of India shares surge 20% as promoter Whirlpool Mauritius eyes full exit: Sources - CNBC TV18</t>
+          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool of India promoter set to sell entire stake, reports CNBC-Awaaz; shares hit 20% upper circuit - Moneycontrol.com</t>
+          <t>Suratwwala Business Group Share Price Today: 11.04% Gain - Univest</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Whirlpool of India stock soars 20% to hit upper circuit on promoter stake sale buzz - The Economic Times</t>
+          <t>Suratwwala Business Group Share Price Analysis - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2927,68 +2931,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NAGREEKCAP.NS</t>
+          <t>VGL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure Limited</t>
+          <t>VARVEE GLOBAL LIMITED</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>29.79999923706055</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>29.79999923706055</v>
+        <v>70.05999755859375</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.20999908447266</v>
+        <v>66.22000122070312</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>28.86000061035156</v>
+        <v>66.51999664306641</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>30.20000076293945</v>
+        <v>70.62999725341797</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28.86000061035156</v>
+        <v>66.51999664306641</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>14248</v>
+        <v>117073</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.44</v>
+        <v>-5.82</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure (NAGREEKCAP.NS) Gains 1.86% – Key Levels to Watch - Price Target - siam.in</t>
+          <t>Fisher Funds Trims Vista Group Stake but Retains Strong Holding - The Globe and Mail</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure (NAGREEKCAP.NS) Gains 1.86% – Key Levels to Watch - Price Target - siam.in</t>
+          <t>Fisher Funds Trims Vista Group Stake but Retains Strong Holding - The Globe and Mail</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Investors Aren't Entirely Convinced By Nagreeka Capital &amp; Infrastructure Ltd.'s (NSE:NAGREEKCAP) Earnings - simplywall.st</t>
+          <t>Vista Group International (ASX:VGL): Is This Cinema Tech Stock Is Worth Watching After Raising Revenue Guidance - kalkine.com.au</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>SITAENT Stock Price and Chart — BSE:SITAENT - TradingView</t>
+          <t>Aarvee Denims &amp; Exports Share Price today after sharp gain - Univest</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure Announces Board Changes and AGM Proceedings - scanx.trade</t>
+          <t>Vista Group International Number of Employees 2026 | Employee Count &amp; Headcount Data - Revelio Labs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2996,68 +3000,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>JINDWORLD.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>IFCI Limited</t>
+          <t>Jindal Worldwide Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>78.38999938964844</v>
+        <v>51.77999877929688</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>78.86000061035156</v>
+        <v>51.77999877929688</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>75.70999908447266</v>
+        <v>48.40999984741211</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>76.04000091552734</v>
+        <v>49.16999816894531</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>79.48999786376953</v>
+        <v>52.20000076293945</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>76.04000091552734</v>
+        <v>49.16999816894531</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>45567752</v>
+        <v>5922292</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.34</v>
+        <v>-5.8</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>NSE Share Price Rises 3.45%: IFCI, New India Assurance, GIC Re in Focus After NSE IPO Listing - India Infoline</t>
+          <t>Jindal Worldwide (JINDWORLD.NS) Edges Higher at ₹38.31; Key Support and Resistance in Focus - Dividend Growth Stocks - siam.in</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>NSE Share Price Rises 3.45%: IFCI, New India Assurance, GIC Re in Focus After NSE IPO Listing - India Infoline</t>
+          <t>Jindal Worldwide Limited(BSE: 531543) dropped from S&amp;P Global BMI Index - marketscreener.com</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>IFCI, NIACL witness a 2-month roller-coaster ride amid NSE IPO; what next? - Business Standard</t>
+          <t>Jindal Worldwide Share Price Falls in Second Session - Univest</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>NSE stock rises 5% on market debut: How shares of IFCI, SBI, Bank of Baroda, GIC Re are trading today - Business Today</t>
+          <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>IFCI, New India Assurance, other stocks drop up to 3% as NSE makes a muted market debut. What to expect? - The Economic Times</t>
+          <t>Jindal Worldwide Share Price Falls; Valuation Check - Univest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3065,56 +3069,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT.NS</t>
+          <t>MARINE.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>California Software Company Limited</t>
+          <t>Marine Electricals (India) Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>39.59999847412109</v>
+        <v>415</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>39.9900016784668</v>
+        <v>421.1000061035156</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>38.02000045776367</v>
+        <v>396</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>38.29999923706055</v>
+        <v>401.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>40.02000045776367</v>
+        <v>425.7999877929688</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>38.29999923706055</v>
+        <v>401.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>128273</v>
+        <v>2131350</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.3</v>
+        <v>-5.71</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>Knowledge Marine shares jump 5% then drop 2% despite this work order update - What next? Tech experts decode - TradingView</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Tokio Marine Holdings stock falls 3.27 percent in Tokyo - AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Marine Electricals shares rise 7% as company expands operational capacity with launch of new plant in Goa - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Marine Electricals shares jump 8% on capacity expansion update; stock up 92% YTD - Upstox</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge Marine shares jump 5% then drop 2% despite this work order update - What next? Tech experts decode - livemint.com</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3122,68 +3138,56 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK.NS</t>
+          <t>GTECJAINX.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DCB Bank Limited</t>
+          <t>G-TEC JAINX EDUCATION LIMITED</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>218.3999938964844</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>218.9900054931641</v>
+        <v>27.98999977111816</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>206.6900024414062</v>
+        <v>26.11000061035156</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>214.1399993896484</v>
+        <v>26.47999954223633</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>223.6900024414062</v>
+        <v>28.06999969482422</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>214.1399993896484</v>
+        <v>26.47999954223633</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2386707</v>
+        <v>5666</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.27</v>
+        <v>-5.66</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>DCB Bank (NSE:DCBBANK): Why Did It Publish a Special Window Notice for Physical Share Transfer? - Kalkine India</t>
+          <t>G-TEC Jainx Education (GTECJAINX.NS) Slips 5.80% to ₹27.61, Testing ₹26.23 Support Zone - Gap and Reverse - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>DCB Bank (NSE:DCBBANK): Why Did It Publish a Special Window Notice for Physical Share Transfer? - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>DCB Bank Share Price hits fresh 52-week high on price action - Univest</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>DCB Bank DCBBANK PE Capital Infusion Rumour Clarification - Kalkine India</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>DCB Bank Ltd. (DCBBANK) Share Price hits fresh 52-week high after Rs 218.30 close - Univest</t>
-        </is>
-      </c>
+          <t>G-TEC Jainx Education (GTECJAINX.NS) Slips 5.80% to ₹27.61, Testing ₹26.23 Support Zone - Gap and Reverse - siam.in</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3191,68 +3195,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SHIPROCKET.NS</t>
+          <t>BLUESTONE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Shiprocket Limited</t>
+          <t>BlueStone Jewellery and Lifestyle Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>126</v>
+        <v>862.4500122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>126.8000030517578</v>
+        <v>862.5499877929688</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>121.8300018310547</v>
+        <v>790.0499877929688</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>121.9000015258789</v>
+        <v>807.1500244140625</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>127.2300033569336</v>
+        <v>855.5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>121.9000015258789</v>
+        <v>807.1500244140625</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1461388</v>
+        <v>6798083</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.19</v>
+        <v>-5.65</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Shiprocket Ltd Share Price Today,, SHIPROCKET Share Price NSE, BSE - Business Today</t>
+          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - TradingView</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Shiprocket Ltd Share Price Today,, SHIPROCKET Share Price NSE, BSE - Business Today</t>
+          <t>BlueStone shares worth ₹513 crore change hands in block deal; stock in focus - CNBC TV18</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Shiprocket shares jump over 4% ahead of Q1 earnings release; what investors should know - Upstox</t>
+          <t>BlueStone shares worth ₹513 crore change hands in block deal; stock in focus - CNBC TV18</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Newly listed Shiprocket, Behari Lal Engineering post Q1 results; here’s how shares reacted - Fortune India</t>
+          <t>BlueStone Jewellery share price falls 9% today | What's behind the plunge? - livemint.com</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Shiprocket narrows Q1 loss to Rs 13.7 Cr; revenue jumps 34% post IPO - Entrackr</t>
+          <t>Bluestone Jewellery &amp; Lifestyle Ltd leads losers in 'A' group - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:13:38 IST</t>
+          <t>2026-09-24 20:58:06 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3260,61 +3264,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MANALIPETC.NS</t>
+          <t>RACE.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Manali Petrochemicals Limited</t>
+          <t>Race Eco Chain Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>87.09999847412109</v>
+        <v>120.1999969482422</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>87.09999847412109</v>
+        <v>122.8899993896484</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>84.09999847412109</v>
+        <v>114</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>84.15000152587891</v>
+        <v>115.9800033569336</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>87.69000244140625</v>
+        <v>122.9100036621094</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>84.15000152587891</v>
+        <v>115.9800033569336</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>643303</v>
+        <v>76249</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.04</v>
+        <v>-5.64</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Income Investors Should Know That Manali Petrochemicals Limited (NSE:MANALIPETC) Goes Ex-Dividend Soon - webull.com</t>
+          <t>Nine European Drugmakers Warn the Continent Risks Losing the Pharma Investment Race: Report - PharmExec.com</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Income Investors Should Know That Manali Petrochemicals Limited (NSE:MANALIPETC) Goes Ex-Dividend Soon - webull.com</t>
+          <t>Meta VR Stock Dips 0.4% as Vision Pro Race Heats Up [2026] - tech-insider.org</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Manali Petrochemicals (MANALIPETC.NS) Eases 1.12% to ₹85.3 as Investors Watch ₹81.03 Support Zone - Mutual Fund Flow - siam.in</t>
+          <t>Meta VR Stock Dips 0.4% as Vision Pro Race Heats Up [2026] - tech-insider.org</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Manali Petrochemicals Share Price update: Rs 89.95, up 8.64% - Univest</t>
+          <t>Snap Stock Rises as It Joins the AI Assistant Race - Barron's</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Manali Petrochemicals Share Price Today: price action view - Univest</t>
+          <t>Ferrari has used €558 million to buy its own shares in 2026 - Stock Titan</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>India Glycols Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>256.8999938964844</v>
+        <v>55.97999954223633</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>309.2000122070312</v>
+        <v>62.43999862670898</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>255.3999938964844</v>
+        <v>54.70999908447266</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>306</v>
+        <v>62.09999847412109</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>257.7000122070312</v>
+        <v>55.77000045776367</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>306</v>
+        <v>62.09999847412109</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4840415</v>
+        <v>2430221</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>18.74</v>
+        <v>11.35</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Did India Glycols shares crash 80%? Here’s why the plunge is not real - Fortune India</t>
+          <t>The Ugar Sugar Works Share Price - Upstox</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>India Glycols Share Price Today up 9.62%: key stock analysis - Univest</t>
+          <t>The Ugar Sugar Works Share Price - Upstox</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>India Glycols demerged into three entities - India Glycols, IGL Spirits, and Ennature Bio Pharma - Indian Chemical News</t>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - kalkine.co.in</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>India Glycols shares: Why this multibagger stock is showing 80% crash in some trading apps today - Business Today</t>
+          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - univest.in</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Demerger news: 3 new separate entities formed - Check benefits, shareholding pattern and what stock investors got - livemint.com</t>
+          <t>Ugar Sugar Works Plant Operational Despite KSPCB Order; Shares Rise - HDFC Sky</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DCI.NS</t>
+          <t>SHANTIGOLD.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Dc Infotech And Communication Limited</t>
+          <t>Shanti Gold International Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>265</v>
+        <v>289.7999877929688</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>318.8999938964844</v>
+        <v>322</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>264.2999877929688</v>
+        <v>288.989990234375</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>302.3999938964844</v>
+        <v>315.7000122070312</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>268.6000061035156</v>
+        <v>283.6199951171875</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>302.3999938964844</v>
+        <v>315.7000122070312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1477225</v>
+        <v>21620457</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>12.58</v>
+        <v>11.31</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Donaldson Company, Inc. (DCI) Stock Forecasts - Yahoo Finance</t>
+          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Donaldson Company, Inc. (DCI) Stock Forecasts - Yahoo! Finance Canada</t>
+          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Donaldson Co. CEO Tod Carpenter sells $2.9 million in DCI stock - Investing.com</t>
+          <t>Shanti Gold International (SHANTIGOLD) Share Price Falls 8.03% Today - univest.in</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>DCI Share Price Rise: Fundamentals, Peers and Market Cap - Univest</t>
+          <t>Shanti Gold International SHANTIGOLD Q1 FY27 Results Clarification - kalkine.co.in</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Why (DCI) Price Action Is Critical for Tactical Trading - Stock Traders Daily</t>
+          <t>Shanti Gold International Share Price rises 9.58% today - univest.in</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>REMSONSIND.NS</t>
+          <t>AVADHSUGAR.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Remsons Industries Limited</t>
+          <t>Avadh Sugar &amp; Energy Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>102.5</v>
+        <v>724.0999755859375</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>113.3899993896484</v>
+        <v>796.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>101.5199966430664</v>
+        <v>720.6500244140625</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>111.120002746582</v>
+        <v>796.5</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>99.87000274658203</v>
+        <v>724.0999755859375</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>111.120002746582</v>
+        <v>796.5</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1519376</v>
+        <v>461445</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>11.26</v>
+        <v>10</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Remsons Industries Limited (NSE:REMSONSIND) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Avadh Sugar &amp; Energy Holds Steady Near ₹733 as Traders Eye Range Boundaries - Volume Spike Alerts - siam.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Remsons UK Subsidiary Wins ₹30 Crore Hood Rod Contract - scanx.trade</t>
+          <t>Avadh Sugar &amp; Energy turns profitable in Q1FY27 with ₹0.24 Cr net profit - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Remsons Industries Share Price news: Rs 94.4 and 8.52% rise - Univest</t>
+          <t>AVADHSUGAR Q2 2026 Earnings: Revenue Edges Up 2.36% as EPS Comes in at ₹28.63 - EPS Miss Report - siam.in</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Remsons Industries Ltd (REMSONSIND): Export Story in Focus - Kalkine India</t>
+          <t>Sugar stocks: Why Balrampur Chini, Bajaj Hindusthan, Dwarikesh Sugar, others are falling today - Business Today</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Remsons Industries Share Price Today up 9.93% | Rs 88.55 - Univest</t>
+          <t>Avadh Sugar &amp; Energy turns profitable in Q1FY27 with ₹0.24 Cr net profit - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KSCL.NS</t>
+          <t>ANTELOPUS.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Kaveri Seed Company Limited</t>
+          <t>Antelopus Selan Energy Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>712.8499755859375</v>
+        <v>1135</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>819.9500122070312</v>
+        <v>1260</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>704.4000244140625</v>
+        <v>1094.400024414062</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>783.8499755859375</v>
+        <v>1241.75</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>710.7000122070312</v>
+        <v>1130.949951171875</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>783.8499755859375</v>
+        <v>1241.75</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>19331957</v>
+        <v>4478800</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>10.29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>KSCL Share Price: near 52-week low with mixed fundamentals - Univest</t>
+          <t>Antelopus Selan Energy: Best Stock in Its Sector? Key Metrics - univest.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Kaveri Seed Closes Trading Window Ahead of Q2 FY2026 Results - TipRanks</t>
+          <t>Antelopus Selan Energy: Best Stock in Its Sector? Key Metrics - univest.in</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Kaveri (KSCL.NS) Market: Declines 0.74% to ₹781.05 in the Latest Session; Next Test: the Price Remains Bounded by the Supplied Support and Resistance in Latest Trading - Dividend ETF - siam.in</t>
+          <t>Antelopus Selan Energy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Kaveri (KSCL.NS) Update: Records a 0.08% Decrease to ₹786.20 in the Current Update; Price Setup: the ₹746.89 to ₹825.51 Range Remains in Focus - Parabolic SAR - siam.in</t>
+          <t>Antelopus Selan Energy ESOP Allotment September 2026 - kalkine.co.in</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Kaveri Seed Company Share Price: fresh 52-week low analysis - Univest</t>
+          <t>Antelopus Selan Energy (ANTELOPUS.NS) Slides 7.16% to ₹1057.8 as Stock Nears Key Support - Low Beta Factor - siam.in</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,68 +829,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DANGEE.NS</t>
+          <t>DAVANGERE.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>Davangere Sugar Company Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.75</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.970000028610229</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.740000009536743</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.970000028610229</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2.700000047683716</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.970000028610229</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>7561092</v>
+        <v>26001785</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>10</v>
+        <v>9.59</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Volume Gainers, September 24, 2026 at 3:30 PM IST: Kaveri Seed Leads Volume Jump - HDFC Sky</t>
+          <t>Sugar stock under ₹5 Davangere Sugar Company jumps over 7% | What's fueling the stock - Livemint</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Volume Gainers, September 24, 2026 at 3:30 PM IST: Kaveri Seed Leads Volume Jump - HDFC Sky</t>
+          <t>Davangere Sugar FY26 net profit falls to ₹850.66 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Dangee Dums Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
+          <t>Davangere Sugar FY26 net profit falls to ₹850.66 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Volume Gainers, September 24, 2026 at 12:00 PM IST: Dangee Dums Leads Volume Jump - HDFC Sky</t>
+          <t>Davangere Sugar Stock Jumps 6%: What’s Driving This Sugar Stock Rally As Ethanol Expansion Plans Gather Pace? - Goodreturns</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>The Dangee Dums Bull Case - Univest</t>
+          <t>Davangere Sugar Company Share Price Update and Analysis - univest.in</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -898,68 +898,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU.NS</t>
+          <t>TCI.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Limited</t>
+          <t>Transport Corporation of India Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>739.7999877929688</v>
+        <v>877</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>806.0999755859375</v>
+        <v>955</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>737</v>
+        <v>863.1500244140625</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>806.0999755859375</v>
+        <v>912.3499755859375</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>732.8499755859375</v>
+        <v>833.4500122070312</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>806.0999755859375</v>
+        <v>912.3499755859375</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>520788</v>
+        <v>4932104</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusiontechnik Share Price near 52-week high | - Univest</t>
+          <t>TCI Express Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusiontechnik Share Price near 52-week high | - Univest</t>
+          <t>TCI Express Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik (KABRAEXTRU.NS) Rises 2.47% to ₹725, Holding Above Key Support - siam.in</t>
+          <t>Transcontinental Realty Investors (TCI) Ticks Up 1.31% to $40.35, Holding Above Key Support - PCR Divergence - siam.in</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusiontechnik Share Price rises 9.10% to Rs 727 - Univest</t>
+          <t>TCI Share Price: Fresh 52-Week Low, Valuation View - univest.in</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusiontechnik KABRAEXTRU Preferential Issue Allottee Change - Kalkine India</t>
+          <t>Transcontinental Realty Investors stock holds its value on September 22, 2026 - AD HOC NEWS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -967,68 +967,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB.NS</t>
+          <t>ARTEMISMED.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Limited</t>
+          <t>Artemis Medicare Services Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>138.3999938964844</v>
+        <v>346</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>138.3999938964844</v>
+        <v>378.7999877929688</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>125.8199996948242</v>
+        <v>346</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>138.3999938964844</v>
+        <v>358.8999938964844</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>125.8199996948242</v>
+        <v>332.7000122070312</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>138.3999938964844</v>
+        <v>358.8999938964844</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>805254</v>
+        <v>16749605</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10</v>
+        <v>7.87</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
+          <t>Artemis Medicare Services Share Price rises 6.45% today - univest.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
+          <t>Artemis Medicare Services Share Price rises 6.45% today - univest.in</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
+          <t>Artemis Med Service Share Price - Upstox</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Share Price rise: fundamentals and sector view - Univest</t>
+          <t>Artemis Medicare Slips Marginally to ₹342.05; ARTEMISMED Tests Crucial Support Zone - Runaway Gap - siam.in</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Limited Board Approves ₹135 Crore Fund-Raising Plan - EquityBulls</t>
+          <t>Artemis Medicare Services Share Price: 52-week high update - univest.in</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1036,51 +1036,51 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DCMSIL.NS</t>
+          <t>LLOYDSENGG.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram International Limited</t>
+          <t>LLOYDS ENGINEERING WORKS LIMITED</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>79.44999694824219</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>85.19999694824219</v>
+        <v>98.90000152587891</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>74.09999847412109</v>
+        <v>89.05999755859375</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>85.19999694824219</v>
+        <v>97.86000061035156</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>77.45999908447266</v>
+        <v>90.91000366210938</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>85.19999694824219</v>
+        <v>97.86000061035156</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>396593</v>
+        <v>39218627</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>9.99</v>
+        <v>7.64</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram International Share Price and Sector Analysis - Univest</t>
+          <t>Lloyds Engineering Calls NCLT-Ordered Creditor Meet on Merger Scheme - The Globe and Mail</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram International Ltd. Upper Circuit: Price and Key Data - Univest</t>
+          <t>Lloyds Engineering Calls NCLT-Ordered Creditor Meet on Merger Scheme - The Globe and Mail</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>DCM Shriram International Ltd. Upper Circuit: Price and Key Data - Univest</t>
+          <t>Should You Be Adding Lloyds Engineering Works (NSE:LLOYDSENGG) To Your Watchlist Today? - simplywall.st</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1097,64 +1097,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>BOHRAIND.NS</t>
+          <t>LLOYDSENT.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Bohra Industries Limited</t>
+          <t>Lloyds Enterprises Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13.10999965667725</v>
+        <v>75.58000183105469</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>15</v>
+        <v>81.40000152587891</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13.10999965667725</v>
+        <v>74.48999786376953</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>14.93000030517578</v>
+        <v>79.70999908447266</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13.64000034332275</v>
+        <v>75.58000183105469</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14.93000030517578</v>
+        <v>79.70999908447266</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>36086</v>
+        <v>9324042</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>5.46</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Bohra Industries (BOHRAIND.NS) Ticks Up 1.38% to ₹13.18 as Stock Holds Above Key ₹12.52 Support - Factor Valuation - siam.in</t>
+          <t>Lloyds Enterprises Limited (NSE:LLOYDSENT) Stock Has Shown Weakness Lately But Financials Look Strong: Should Prospective Shareholders Make The Leap? - simplywall.st</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Bohra Industries (BOHRAIND.NS) Ticks Up 1.38% to ₹13.18 as Stock Holds Above Key ₹12.52 Support - Factor Valuation - siam.in</t>
+          <t>Lloyds enterprises limited Q1 FY27 Results Preview - univest.in</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Bohra Industries Trades Lower at ₹12.35: Key Support Holds as Downside Pressure Persists - Anchored VWAP - siam.in</t>
+          <t>Lloyds enterprises limited Q1 FY27 Results Preview - univest.in</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>BOHRAIND Q2 2026 Earnings: Zero Revenue and ₹-1.4 EPS Highlight Dormant Quarter - EPS Guidance Update - siam.in</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Lloyds Enterprises Limited Submits Q4FY26 Certificate Under SEBI Depositories Regulations - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Lloyds Enterprises Limited (NSE:LLOYDPP) Shares May Have Slumped 25% But Getting In Cheap Is Still Unlikely - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1162,68 +1166,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VIKRAN.NS</t>
+          <t>KRONOX.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering Limited</t>
+          <t>Kronox Lab Sciences Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>58.5</v>
+        <v>205</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>62.61999893188477</v>
+        <v>206.5800018310547</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>57.52999877929688</v>
+        <v>198.0099945068359</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.9900016784668</v>
+        <v>206.5800018310547</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>56.13999938964844</v>
+        <v>196.75</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>60.9900016784668</v>
+        <v>206.5800018310547</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>34846412</v>
+        <v>136343</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering shares rally nearly 12% on securing ₹154 crore order from Power Grid - Upstox</t>
+          <t>Indo Borax secures ₹225 crore funding to acquire Kronox Lab Sciences - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering shares rally nearly 12% on securing ₹154 crore order from Power Grid - Upstox</t>
+          <t>Indo Borax secures ₹225 crore funding to acquire Kronox Lab Sciences - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Kronox Lab Sciences (KRONOX.NS) Holds Near ₹184.69: Stock Gains 0.72% as Range-Bound Trend Persists - Put Spread Alert - siam.in</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Vikran (VIKRAN.NS) Quarterly Figures: The Report Provides a New Financial Snapshot at the Close; After Earnings: The Stock Ends Down 0.25% in the Latest Reading - Cash Flow Report - siam.in</t>
+          <t>Kronox Lab Sciences Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering shareholders approve ₹1,000 crore NCD facility - scanx.trade</t>
+          <t>KRONOX Lab Sciences Limited Publishes Unaudited Financial Results for Q3 FY26 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1231,68 +1235,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ABDL.NS</t>
+          <t>STLNETWORK.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Allied Blenders and Distillers Limited</t>
+          <t>STL Networks Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>660</v>
+        <v>54.5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>722</v>
+        <v>54.61000061035156</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>650</v>
+        <v>52.40000152587891</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>712.1500244140625</v>
+        <v>54.61000061035156</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>656.4000244140625</v>
+        <v>52.0099983215332</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>712.1500244140625</v>
+        <v>54.61000061035156</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>6588934</v>
+        <v>8896179</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.49</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>ABDL Share Price rises 5.37%: price action and fundamentals - Univest</t>
+          <t>Free float of STL Networks Limited – NSE:STLNETWORK - TradingView</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Allied Blenders stock surges 6% as promoter offloads 55 lakh shares to meet MPS norms - BusinessLine</t>
+          <t>Anil Agarwal confirms no encumbrance on STL Networks shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Allied Blenders stock surges 6% as promoter offloads 55 lakh shares to meet MPS norms - BusinessLine</t>
+          <t>Anil Agarwal confirms no encumbrance on STL Networks shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Allied Blenders shares surge over 5% after SBI Mutual Fund, Abu Dhabi Investment Authority buy stake - Upstox</t>
+          <t>STLNETWORK.NS Q2 2026 Earnings: Revenue Declines 18.61% YoY, EPS Loss of ₹2.03, Yet Stock Gains 4.98% - siam.in</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>India Sugar Import Shock Puts Allied Blenders And Globus Spirits In Focus - simplywall.st</t>
+          <t>STLNETWORK Stock Price and Chart — NSE:STLNETWORK - TradingView</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1300,68 +1304,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>JAGSNPHARM.NS</t>
+          <t>BIRLACABLE.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Jagsonpal Pharmaceuticals Limited</t>
+          <t>Birla Cable Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>227.8999938964844</v>
+        <v>350.8999938964844</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>249.8399963378906</v>
+        <v>362.4500122070312</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>226.7599945068359</v>
+        <v>331</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>243.9700012207031</v>
+        <v>362.4500122070312</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>225.6300048828125</v>
+        <v>345.2000122070312</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>243.9700012207031</v>
+        <v>362.4500122070312</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>9252323</v>
+        <v>475860</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Jagsonpal Pharmaceuticals Limited (NSE:JAGSNPHARM) Passed Our Checks, And It's About To Pay A ₹4.00 Dividend - simplywall.st</t>
+          <t>Birla Cable Ltd. Lower Circuit Today: Price, Data and Peers - univest.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Jagsonpal Pharmaceuticals Ltd (NSE: JAGSNPHARM) Acquires Wellness Portfolio for ₹46.7 Crore - Kalkine India</t>
+          <t>Birla Cable Ltd. Lower Circuit Today: Price, Data and Peers - univest.in</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Jagsonpal Pharmaceuticals Ltd (NSE: JAGSNPHARM) Acquires Wellness Portfolio for ₹46.7 Crore - Kalkine India</t>
+          <t>Birla Cable FY26 Net Profit Jumps 235%; Dividend Declared - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Jagsonpal Pharmaceuticals releases Q1 FY27 earnings call recording online - scanx.trade</t>
+          <t>Birla Cable Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Jagsonpal Pharmaceuticals acquires Wellness Portfolio for up to ₹46.7 crore - scanx.trade</t>
+          <t>Universal Cables Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1369,60 +1373,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT.NS</t>
+          <t>NRAIL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Greaves Cotton Limited</t>
+          <t>N R Agarwal Industries Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>206.1699981689453</v>
+        <v>650</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>223.5</v>
+        <v>673</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>202.2200012207031</v>
+        <v>631.2000122070312</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>221.8300018310547</v>
+        <v>666.9000244140625</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>206.0099945068359</v>
+        <v>637.75</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>221.8300018310547</v>
+        <v>666.9000244140625</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>15909049</v>
+        <v>12411</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>7.68</v>
+        <v>4.57</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Greaves Cotton (GREAVESCOT.NS) Holds Near ₹194.78 as Market Weighs E-Mobility Transition - Break of Structure - siam.in</t>
+          <t>N R Agarwal Industries (NRAIL.NS) Slips 2.60% to ₹595.30 as Paper Stock Holds Mid-Range - Ending Diagonal - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Greaves Cotton takes full control of Excel Controllinkage as acquisition completes - scanx.trade</t>
+          <t>N R Agarwal Industries NRAIL Trading Window Closure Q2 FY27 - kalkine.co.in</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Greaves Cotton takes full control of Excel Controllinkage as acquisition completes - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>NR Agarwal Industries Share Price today: key market update - univest.in</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>NRAIL Q2 2026 Earnings: Revenue Climbs 30.1% YoY as EPS Prints at ₹25.68 - Earnings Beat Streak - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1430,68 +1442,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PRAENG.NS</t>
+          <t>BAJAJHIND.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Prajay Engineers Syndicate Limited</t>
+          <t>Bajaj Hindusthan Sugar Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21</v>
+        <v>20.04999923706055</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>24.1299991607666</v>
+        <v>20.76000022888184</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20.70000076293945</v>
+        <v>19.80999946594238</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>22.86000061035156</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.3799991607666</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22.86000061035156</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>127589</v>
+        <v>18061171</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>6.92</v>
+        <v>3.32</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Prajay Engineers Syndicate Ltd. Stock News - Value Research</t>
+          <t>Bajaj Hindusthan Sugar Share Price Today: 5.39% Decline - univest.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>PRAENG Q2 2026 Earnings: Loss Per Share of ₹2.69 as Revenue Falls 33.12% Year-on-Year - Analyst Drop Coverage - siam.in</t>
+          <t>Bajaj Hindusthan Sugar Share Price Today: 5.39% Decline - univest.in</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Prajay Engineers Syndicate files FY26 annual report and AGM notice - scanx.trade</t>
+          <t>Bajaj Hindusthan Sugar Share Price Update, Sector Context - univest.in</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>PRAENG Q2 2026 Earnings: Loss Per Share of ₹2.69 as Revenue Falls 33.12% Year-on-Year - Analyst Drop Coverage - siam.in</t>
+          <t>Bajaj Hindusthan Sugar Share Price update after 5.67% gain - univest.in</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>PRAENG.NS Q2 2026 Earnings: Revenue Drops 33% YoY, Reports Loss of ₹2.69 Per Share - Analyst Drop Coverage - siam.in</t>
+          <t>Bajaj Hindusthan Sugar Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1499,68 +1511,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AVANTEL.NS</t>
+          <t>HBLENGINE.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Avantel Limited</t>
+          <t>HBL Engineering Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>153</v>
+        <v>779</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>160</v>
+        <v>809</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>151.3800048828125</v>
+        <v>765.9500122070312</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>155.3399963378906</v>
+        <v>801</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>146.1699981689453</v>
+        <v>775.2999877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>155.3399963378906</v>
+        <v>801</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>19464519</v>
+        <v>4077839</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>6.27</v>
+        <v>3.31</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Avantel shares rise 9% after Rs 177 crore satellite communication order from Zetwerk - The Economic Times</t>
+          <t>Should You Buy HBL Engineering Limited (NSE:HBLENGINE) For Its Upcoming Dividend? - simplywall.st</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Avantel shares rise 9% after Rs 177 crore satellite communication order from Zetwerk - The Economic Times</t>
+          <t>HBL Engineering Share Price Today: Rs 785.1 After 2.39% Rise - univest.in</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Price Action: Avantel shares surge 8% on order win; Macquarie initiates ‘Neutral’ on Angel One - Moneycontrol.com</t>
+          <t>Should You Be Adding HBL Engineering (NSE:HBLENGINE) To Your Watchlist Today? - simplywall.st</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27% Jump In Six Months: Avantel Share Price Surges Over 9% In Trade Today. Here's Why - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Avantel shares jump 9% on bagging order worth over ₹177 crore from Zetwerk Manufacturing - Upstox</t>
-        </is>
-      </c>
+          <t>HBL Engineering Share Price Today: Rs 785.1 After 2.39% Rise - univest.in</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1568,60 +1576,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ZFSTEERING.NS</t>
+          <t>DYNAMATECH.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ZF Steering Gear (India) Limited</t>
+          <t>Dynamatic Technologies Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>710</v>
+        <v>12541</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>760</v>
+        <v>13287</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>709.8499755859375</v>
+        <v>12490</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>746.0999755859375</v>
+        <v>12965</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>703.6500244140625</v>
+        <v>12551</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>746.0999755859375</v>
+        <v>12965</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>11028</v>
+        <v>27272</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6.03</v>
+        <v>3.3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>ZF (ZFSTEERING.NS) Earnings Reading: The Company Releases Its Current Earnings Data on the Day; Closing Move - siam.in</t>
+          <t>Dynamatic Technologies Share Price Today: Key Price Action - univest.in</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>ZF Steering Gear (India) Share Price Rise: Key Analysis - Univest</t>
+          <t>DYNAMATECH Q2 2026 Earnings: EPS of ₹47.73 and 15.11% Revenue Growth Met a Muted Market Reception - GAAP Earnings Report - siam.in</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ZF Steering Gear (India) Share Price Rise: Key Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t>Dynamatic Technologies Share Price Rise: Valuation View - univest.in</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>DYNAMATECH Q2 2026 Earnings: EPS of ₹47.73 and 15.11% Revenue Growth Met a Muted Market Reception - GAAP Earnings Report - siam.in</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1629,68 +1641,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING.NS</t>
+          <t>RATNAVEER.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Bluspring Enterprises Limited</t>
+          <t>Ratnaveer Precision Engineering Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>132.5899963378906</v>
+        <v>324.8999938964844</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>142.75</v>
+        <v>341.6499938964844</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>131.3200073242188</v>
+        <v>323</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>140.5599975585938</v>
+        <v>334.1499938964844</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>132.5899963378906</v>
+        <v>323.9500122070312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>140.5599975585938</v>
+        <v>334.1499938964844</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1597809</v>
+        <v>5171380</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6.01</v>
+        <v>3.15</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING Share Price update after 8.92% rise in early trade - Univest</t>
+          <t>Ratnaveer Precision Engineering Share Price rises 9.01% - univest.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bluspring Enterprises subsidiary secures ₹2,049.8 crore power plant O&amp;M contract - scanx.trade</t>
+          <t>Ratnaveer Precision Engineering Advances CCL Project; Order Bookings Expected to Begin From October 31 - BizzBuzz</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bluspring Enterprises Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Press Release Distribution India - Business Wire India</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING ENTERPRISES Share Price Today: Down 9.99% - Univest</t>
+          <t>Ratnaveer Precision Engineering share price hits 52-week high | What's behind the rally? - Livemint</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Bluspring Enterprises Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Ratnaveer Precision Engineering’s ₹330-crore rights issue fully subscribed - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1698,68 +1710,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP.NS</t>
+          <t>PARAGMILK.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited</t>
+          <t>Parag Milk Foods Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>68.84999847412109</v>
+        <v>262</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>74.80000305175781</v>
+        <v>269.3999938964844</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>68.84999847412109</v>
+        <v>256.25</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>72.68000030517578</v>
+        <v>266.3999938964844</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>68.65000152587891</v>
+        <v>258.3999938964844</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>72.68000030517578</v>
+        <v>266.3999938964844</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>28298356</v>
+        <v>1405372</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5.87</v>
+        <v>3.1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
+          <t>Parag Milk Foods Share Price Today: Rs 256.5 after rise - univest.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-21 — cnbctv:a6f5fee85094b:0 - TradingView</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited (DELTACORP.NS) Consolidates Near ₹54 as Traders Eye Range Boundaries - Factor Timing - siam.in</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>DELTACORP Outlook for the Week - Equitypandit</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Delta Corp sets Sept 10 AGM; details TDS rules for ₹0.50 dividend - scanx.trade</t>
-        </is>
-      </c>
+          <t>News by CNBC TV18 on TradingView, 2026-09-21 — cnbctv:a6f5fee85094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1767,68 +1771,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>LAL.NS</t>
+          <t>SAKAR.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Lorenzini Apparels Limited</t>
+          <t>Sakar Healthcare Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8.720000267028809</v>
+        <v>1125.099975585938</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9.489999771118164</v>
+        <v>1189.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>8.470000267028809</v>
+        <v>1125.099975585938</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.069999694824219</v>
+        <v>1161.949951171875</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>8.569999694824219</v>
+        <v>1128.550048828125</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9.069999694824219</v>
+        <v>1161.949951171875</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>163991</v>
+        <v>62605</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5.83</v>
+        <v>2.96</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Dr. Lal PathLabs Stock Signals to Watch This Week - Univest</t>
+          <t>Sakar Healthcare Share Price Update: Sector and Peer View - univest.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ISOC promoter Shanti Lal Jain gifts 1.09% stake; holding falls to nil - scanx.trade</t>
+          <t>Sakar Healthcare Share: Bull Case vs Bear Case for 2026 - univest.in</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ISOC promoter Shanti Lal Jain gifts 1.09% stake; holding falls to nil - scanx.trade</t>
+          <t>Sakar Healthcare Ltd. Share Price Rise Streak: Key update - univest.in</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Dixon Tech, Bharat Dynamics, Chaman Lal Setia, Manyavar, Dividends: Last Day To Buy Shares To Qualify - NDTV Profit</t>
+          <t>Sakar Healthcare Share: Bull Case vs Bear Case for 2026 - univest.in</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Newly listed Shiprocket, Behari Lal Engineering post Q1 results; here’s how shares reacted - Fortune India</t>
+          <t>Sakar Healthcare Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1836,51 +1840,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CRAVATEX.NS</t>
+          <t>PGIL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Cravatex Limited</t>
+          <t>Pearl Global Industries Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>341.7000122070312</v>
+        <v>1281.800048828125</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>410</v>
+        <v>1355</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>340.9500122070312</v>
+        <v>1274.800048828125</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>361.4500122070312</v>
+        <v>1311</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>341.7000122070312</v>
+        <v>1273.599975585938</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>361.4500122070312</v>
+        <v>1311</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>14407</v>
+        <v>362070</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5.78</v>
+        <v>2.94</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Cravatex Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>PGIL 52 Week High Streak: Price, Sector, Valuation View - univest.in</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Cravatex Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Buy Pearl Global Industries; target of Rs 1400: Emkay Global Financial - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Pearl Global Industries Share Price Today: PGIL up 6.44% - univest.in</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Pearl Global Industries Share Price Rise in Textile Sector - univest.in</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Pearl Global Industries Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1899,14 +1915,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2005,7 +2021,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2013,68 +2029,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MFSL.NS</t>
+          <t>TURTLEMINT.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Max Financial Services Limited</t>
+          <t>Turtlemint Fintech Solutions Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1406.699951171875</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1429.800048828125</v>
+        <v>97.76999664306641</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1360.099975585938</v>
+        <v>87.23999786376953</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1410</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1562.900024414062</v>
+        <v>109.0400009155273</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1410</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>11421538</v>
+        <v>16797656</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-9.779999999999999</v>
+        <v>-19.11</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd (NSE: MFSL) Declines 9.46% as Stock Draws Market Attention - Kalkine India</t>
+          <t>PB Fintech, Turtlemint Shares Extend Slump as Outlook Worsens - Bloomberg.com</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd (NSE: MFSL) Declines 9.46% as Stock Draws Market Attention - Kalkine India</t>
+          <t>PB Fintech, Turtlemint Shares Extend Slump as Outlook Worsens - Bloomberg.com</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Max Financial Services Share Price Today: key market context - Univest</t>
+          <t>Not just PB Fintech, this smallcap stock fell 36% in two days on IRDAI proposals - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Max Financial Services Share Price and valuation update - Univest</t>
+          <t>Turtlemint Fintech Solutions Extends Decline On Second Day, Share Price Hits 20% Lower Circuit - ndtvprofit.com</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Max Financial Services Share Price Live: Latest Market Move - Univest</t>
+          <t>Insurance stocks crash: PB Fintech, Turtlemint shares fall up to 28% on IRDAI draft - Is this a buying opportu - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2082,68 +2098,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>LTF.NS</t>
+          <t>AASTHA.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Limited</t>
+          <t>Aastha Spintex Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>290.6000061035156</v>
+        <v>79</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>279</v>
+        <v>72.72000122070312</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>282</v>
+        <v>72.72000122070312</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>310</v>
+        <v>80.80000305175781</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>282</v>
+        <v>72.72000122070312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>36068873</v>
+        <v>3926117</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Drops 2.36% to ₹314.3: Stock Holds Above Support Amid NBFC Sector Volatility - Revenue Growth Stocks - siam.in</t>
+          <t>Bonus issue record date today: Last chance to buy Aastha Spintex shares as deadline approaches-Check stock performance - Livemint</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech shares fall 23%; Bajaj Finance, L&amp;T Finance also take hit; here's why - Business Today</t>
+          <t>Aastha Spintex Ltd (NSE: AASTHA) Declines 10.00% as Stock Draws Market Attention - kalkine.co.in</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Green LTF Holdings II LP director sells $126.1m in Life Time Group stock - Investing.com</t>
+          <t>Aastha Spintex Ltd (NSE: AASTHA) Declines 10.00% as Stock Draws Market Attention - kalkine.co.in</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Share Price Falls 2.30%: Price Action Review - Univest</t>
+          <t>Aastha Spintex Share Price Fall: Price and Valuation - univest.in</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech shares fall 23%; Bajaj Finance, L&amp;T Finance also take hit; here's why - Business Today</t>
+          <t>Aastha Spintex Secures ₹25 Crore Fabric Orders; Shares Fall 9.99% - HDFC Sky</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2151,60 +2167,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SGRL.NS</t>
+          <t>MANUGRAPH.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Shree Ganesh Remedies Limited</t>
+          <t>Manugraph India Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>731.5</v>
+        <v>23</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>739.4500122070312</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>654</v>
+        <v>19.81999969482422</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>677.1500244140625</v>
+        <v>19.81999969482422</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>735.5499877929688</v>
+        <v>22.02000045776367</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>677.1500244140625</v>
+        <v>19.81999969482422</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>45846</v>
+        <v>177954</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.94</v>
+        <v>-9.99</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Shree Ganesh Remedies Share Price rises 17.45%: analysis - Univest</t>
+          <t>Manugraph India (MANUGRAPH.NS) Edges Higher to ₹15.19 as Stock Pivots Near Key Resistance - Fibonacci Retracement - siam.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Shree Ganesh Remedies Ltd. Share Price News and Analysis - Univest</t>
+          <t>Cubex Tubings Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Shree Ganesh Remedies Ltd. Share Price News and Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Manugraph India Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Manugraph India Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Manugraph India Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2212,68 +2236,60 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>NOCIL.NS</t>
+          <t>OLAELEC.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Limited</t>
+          <t>Ola Electric Mobility Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>204.9100036621094</v>
+        <v>42.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>204.9100036621094</v>
+        <v>42.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>187</v>
+        <v>38.56999969482422</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>191.3999938964844</v>
+        <v>38.63000106811523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>206.3000030517578</v>
+        <v>42.52000045776367</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>191.3999938964844</v>
+        <v>38.63000106811523</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4915030</v>
+        <v>132452739</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.22</v>
+        <v>-9.15</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Nocil Share Price Falls as Chemical Stock Stays in Focus - Univest</t>
+          <t>Ola Electric Plans On-Site Analyst Meet at Future Factory and Giga Factory - The Globe and Mail</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Ltd Hits Intraday Low Amid Price Pressure on 24 Sep 2026 - MarketsMojo</t>
+          <t>Ola Electric Plans On-Site Analyst Meet at Future Factory and Giga Factory - The Globe and Mail</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Ltd Hits Intraday Low Amid Price Pressure on 24 Sep 2026 - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>NOCIL Stock Signals to Watch This Week - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>NOCIL to discuss Q1FY27 performance on Aug 4 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Ola shares rise 6% on S1Z launch with indigenous cell tech, claims 301 km per charge - Business Today</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2281,60 +2297,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS.NS</t>
+          <t>MEESHO.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal Seeds And Chemicals Limited</t>
+          <t>Meesho Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13.39999961853027</v>
+        <v>228.9299926757812</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>13.75</v>
+        <v>229.5800018310547</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12.55000019073486</v>
+        <v>218</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>12.68000030517578</v>
+        <v>218.8600006103516</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13.56999969482422</v>
+        <v>232.8399963378906</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12.68000030517578</v>
+        <v>218.8600006103516</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>445150</v>
+        <v>21263015</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.56</v>
+        <v>-6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal Seeds Share Price and Technical View - Kalkine India</t>
+          <t>Meesho shares can fall 28%, warns Nomura after initiating coverage with Reduce call. Here is why - The Economic Times</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal Seeds Share Price and Technical View - Kalkine India</t>
+          <t>Meesho shares fall 6% as Nomura warns of premium valuation, initiates 'Reduce' with Rs 167 TP - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Shree Oswal Seeds and Chemicals Share Price Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Meesho shares fall 6% as Nomura warns of premium valuation, initiates 'Reduce' with Rs 167 TP - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Shares Trading At Significant Premium, Says Nomura; Assigns 'Reduce' Rating, Sees Over 28% Downside - ndtvprofit.com</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Meesho's valuation woes prompt Nomura to assign 'Reduce' tag; stock down 5% - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2342,68 +2366,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HALDER.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Halder Venture Limited</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>263.8999938964844</v>
+        <v>61.93999862670898</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>285</v>
+        <v>63.4900016784668</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>244</v>
+        <v>61.93999862670898</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>248.75</v>
+        <v>61.93999862670898</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>266.1499938964844</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>248.75</v>
+        <v>61.93999862670898</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>51353</v>
+        <v>2394236</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.54</v>
+        <v>-5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Halder Venture Ltd is Rated Sell - MarketsMojo</t>
+          <t>PVP Ventures slumps after CEO, COO resign - Business Standard</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Halder Venture Ltd is Rated Sell - MarketsMojo</t>
+          <t>PVP Ventures slumps after CEO, COO resign - Business Standard</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Halder Venture Share Price rises 9.85%: valuation check - Univest</t>
+          <t>PVP Ventures accepts resignation of Executive Director and COO - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Tata Chemicals, TCPL, Uno Minda, Welspun Living, Bandhan Bank, E2E Networks: Expert shares outlook - BusinessToday - IndiaIPO</t>
+          <t>PVP Ventures Ltd. Upper Circuit Streak: Day 2 Price and Data - univest.in</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Halder Venture Ltd. Stock News - Value Research</t>
+          <t>PVP Ventures (PVP.NS) Slips 1.82% to ₹64.9 as Stock Drifts Toward ₹61.66 Support - Weekly Profile - siam.in</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2411,68 +2435,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SUBEXLTD.NS</t>
+          <t>EMPOWER.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Subex Limited</t>
+          <t>Empower India Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21.89999961853027</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>22.21999931335449</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20.30999946594238</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20.70999908447266</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.07999992370605</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20.70999908447266</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>19504211</v>
+        <v>4455082</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-6.2</v>
+        <v>-4.59</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price rises 11.24%: valuation and sector - Univest</t>
+          <t>Penny stock under 10 rupees hits 5% upper circuit after this acquisition update - Livemint</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Update: Price Rise and Valuation - Univest</t>
+          <t>Dangote to empower two million women with refinery IPO shares - PM News Nigeria</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Subex Ltd. Share Price Update: Price Rise and Valuation - Univest</t>
+          <t>What employees should know before their company goes public - Empower</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Subex seeks shareholder nod for new ESOP scheme, trust loan - scanx.trade</t>
+          <t>Empower India Share Price Rises 4% Penny Stock Eyes India's Growing AI and Data Centre Infrastructure Boom - Goodreturns</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Subex shareholders approve all resolutions at 32nd AGM with 98% support - scanx.trade</t>
+          <t>Good time to reset AI stock positioning, says Empower's Marta Norton - CNBC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2480,56 +2504,64 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SAICAPI.NS</t>
+          <t>INDOTHAI.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Limited</t>
+          <t>Indo Thai Securities Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>157.25</v>
+        <v>32.29000091552734</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>157.25</v>
+        <v>32.79999923706055</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>142.1499938964844</v>
+        <v>30.68000030517578</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>146.0299987792969</v>
+        <v>30.85000038146973</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>155.6900024414062</v>
+        <v>32.29000091552734</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>146.0299987792969</v>
+        <v>30.85000038146973</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>488</v>
+        <v>875526</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-6.2</v>
+        <v>-4.46</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Sai Capital Ltd. (NSE:SAICAPI) - TradingView</t>
+          <t>Indo Thai Securities Share Price update on fundamentals - univest.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Sai Capital Ltd. (NSE:SAICAPI) - TradingView</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+          <t>Indo Thai Securities Share Price update on fundamentals - univest.in</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>INDOTHAI Q2 2026 Earnings: Revenue Jumps 213.6% YoY as EPS Hits ₹5.29, Shares Slip 5.2% - Profit Guidance Range - siam.in</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2537,68 +2569,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>LAHOTIOV.NS</t>
+          <t>TFCILTD.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lahoti Overseas Limited</t>
+          <t>Tourism Finance Corporation of India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>37</v>
+        <v>135.4900054931641</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>38.27999877929688</v>
+        <v>137.7299957275391</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>40.77000045776367</v>
+        <v>143.4600067138672</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>38.27999877929688</v>
+        <v>137.7299957275391</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>14264</v>
+        <v>19601760</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-6.11</v>
+        <v>-3.99</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Lahoti Overseas Share Price today: valuation and sector view - Univest</t>
+          <t>TFCILTD Share Price: Yearly High, Valuation and Sector View - univest.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Lahoti Overseas Limited Announces Resignation of Mahesh Mishra from Chief Financial Officer, Effective September 09, 2026 - marketscreener.com</t>
+          <t>TFCILTD Share Price: Yearly High, Valuation and Sector View - univest.in</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Lahoti Overseas Limited Announces Resignation of Mahesh Mishra from Chief Financial Officer, Effective September 09, 2026 - marketscreener.com</t>
+          <t>TFCILTD Share Price Hits Fresh 52-Week High: Price Action - univest.in</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>LAHOTIOV June 2026 Quarter Earnings: EPS at ₹1.06 on ₹88.41 Crore Revenue; Stock Declines 5.95% - Share Repurchase Impact - siam.in</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>LAHOTIOV Jun 2026 Earnings: Steady ₹1.06 EPS on ₹88.41 Crore Revenue Keeps the Stock Flat - CEO Earnings Statement - siam.in</t>
-        </is>
-      </c>
+          <t>Tourism Finance Corporation (TFCILTD.NS) Slips to ₹140.54 — Key Support and Resistance Levels in Spotlight - Volatility Surface - siam.in</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2606,68 +2634,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO.NS</t>
+          <t>RML.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Limited</t>
+          <t>Rane (Madras) Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>867</v>
+        <v>1369.599975585938</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>867</v>
+        <v>1379.199951171875</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>811.5499877929688</v>
+        <v>1305.900024414062</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>818.5</v>
+        <v>1310.099975585938</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>871.5999755859375</v>
+        <v>1362.800048828125</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>818.5</v>
+        <v>1310.099975585938</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>903056</v>
+        <v>31844</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-6.09</v>
+        <v>-3.87</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO Share Price Today - MV Electrosystems Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>Rane (Madras) Limited (RML.NS) Rallies 3.80% to ₹1330.5 as Auto Ancillary Counter Nears Upper Resistance - Insider Selling Alerts - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO Share Price Today - MV Electrosystems Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>Rane (Madras) Limited (RML.NS) Rallies 3.80% to ₹1330.5 as Auto Ancillary Counter Nears Upper Resistance - Insider Selling Alerts - siam.in</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Share Price today: Rs 800 and market cap - Univest</t>
+          <t>Rane (RML.NS) Up +3.80% — 3 Reasons the Rally Could Continue 2026-09-20 - Synthetic Long - siam.in</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
+          <t>symbol__ Stock Quote Price and Forecast - CNN</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
+          <t>Resolution Minerals (RML) Stock Price, News &amp; Analysis $RML - MarketBeat</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2675,64 +2703,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MEGASTAR.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Megastar Foods Limited</t>
+          <t>One 97 Communications Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>277.5</v>
+        <v>1732.5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>277.5</v>
+        <v>1747.199951171875</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>254.5500030517578</v>
+        <v>1665</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>260.8999938964844</v>
+        <v>1668.5</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>277.6000061035156</v>
+        <v>1735.5</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>260.8999938964844</v>
+        <v>1668.5</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>8557</v>
+        <v>2973840</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.02</v>
+        <v>-3.86</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Megastar Foods Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Paytm Stock And 2 Indian Founder Led Stocks To Watch - simplywall.st</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Megastar Foods Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>NSE rises 5% after listing: Paytm crashed 27%, Coal India soared 40%; how India’s mega IPOs debuted - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Megastar Foods schedules 15th AGM for September 23, 2026 - scanx.trade</t>
+          <t>Paytm is looking beyond payments. What it means for the stock - TradingView</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Megastar Chiranjeevi's Kaka Team Shares Exciting Shooting Update - The Hans India</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Ferro alloy maker Maithan bets ₹62 crore on Paytm and ESDS shares - Dealroom</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>PAYTM Share Price today near yearly high with valuation - univest.in</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2740,60 +2772,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ADROITINFO.NS</t>
+          <t>MEGASTAR.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Adroit Infotech Limited</t>
+          <t>Megastar Foods Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13.88000011444092</v>
+        <v>270</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>13.90999984741211</v>
+        <v>270</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>12.60999965667725</v>
+        <v>251.3999938964844</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>12.72999954223633</v>
+        <v>251.3999938964844</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13.52999973297119</v>
+        <v>260.8999938964844</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12.72999954223633</v>
+        <v>251.3999938964844</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>170767</v>
+        <v>3081</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5.91</v>
+        <v>-3.64</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Adroit Infotech Eases 1.44% to ₹10.25, Holds Above Key ₹9.74 Support - Fear Greed Index - siam.in</t>
+          <t>Megastar Foods Share: Bull Case vs Bear Case for 2026 - univest.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Adroit Infotech Corrects XBRL-PDF Mismatch in FY26 Results - TipRanks</t>
+          <t>Megastar Foods Share: Bull Case vs Bear Case for 2026 - univest.in</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Adroit Infotech Corrects XBRL-PDF Mismatch in FY26 Results - TipRanks</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t>Megastar Foods schedules 15th AGM for September 23, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Megastar Chiranjeevi's Kaka Team Shares Exciting Shooting Update - The Hans India</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2801,60 +2837,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>BAJFINANCE.NS</t>
+          <t>GLOBAL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Finance Limited</t>
+          <t>Global Education Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1005</v>
+        <v>142.3500061035156</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1015</v>
+        <v>142.4900054931641</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>974</v>
+        <v>135.1999969482422</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>982</v>
+        <v>136</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1043.199951171875</v>
+        <v>141</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>982</v>
+        <v>136</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>13383127</v>
+        <v>154741</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.87</v>
+        <v>-3.55</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Finance Share Price Today declines 2.01%: key facts - Univest</t>
+          <t>Global shares, bonds bounce as oil skid offers inflation relief - DD News</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Emami promoters pledge and release shares with Bajaj Finance, DBS Bank - scanx.trade</t>
+          <t>Aussie Dollar Slides: Why It Could Boost Your SMSF's Global Shares - Kalkine Media</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Emami promoters pledge and release shares with Bajaj Finance, DBS Bank - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Liberty Global stock hits 52-week low at 9.42 USD - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Bond Selloff Worsens, Dinging Stocks - WSJ</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>A US diesel export ban would trigger global stock drawdowns, cut US refinery utilisation and risk driving gasoline prices higher - Wood Mackenzie</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2862,68 +2906,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SBGLP.NS</t>
+          <t>OPTIEMUS.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Limited</t>
+          <t>Optiemus Infracom Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>23.63999938964844</v>
+        <v>775.5</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>25.45000076293945</v>
+        <v>787.2999877929688</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>22.10000038146973</v>
+        <v>752.0499877929688</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>22.88999938964844</v>
+        <v>754.6500244140625</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.30999946594238</v>
+        <v>781.5</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22.88999938964844</v>
+        <v>754.6500244140625</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>202878</v>
+        <v>358203</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5.84</v>
+        <v>-3.44</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group (SBGLP.NS) Ticks Higher: Small-Cap Holds Above ₹21 on NSE - Head and Shoulders - siam.in</t>
+          <t>Optiemus Infracom To Acquire 51.1% Stake In Joint Venture With Nothing Electronics - Sahi</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Share Price Analysis - Kalkine India</t>
+          <t>Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom — Ask Profit - ndtvprofit.com</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
+          <t>Optiemus Infracom shares extend two-day rally to 33%: Here are two reasons - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Share Price Today: 11.04% Gain - Univest</t>
+          <t>Optiemus Infracom shares surge nearly 45% in three sessions, hit fresh 52-week high; here is why - Upstox</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Share Price Analysis - Kalkine India</t>
+          <t>Optiemus eyes ₹2,000 crore FY28 revenue from screen protectors, stock up 20% for second day - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2931,68 +2975,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VGL.NS</t>
+          <t>COASTCORP.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>VARVEE GLOBAL LIMITED</t>
+          <t>Coastal Corporation Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>69</v>
+        <v>38.47000122070312</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>70.05999755859375</v>
+        <v>38.47000122070312</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>66.22000122070312</v>
+        <v>35.65999984741211</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>66.51999664306641</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>70.62999725341797</v>
+        <v>37.68000030517578</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>66.51999664306641</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>117073</v>
+        <v>91490</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.82</v>
+        <v>-3.4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Fisher Funds Trims Vista Group Stake but Retains Strong Holding - The Globe and Mail</t>
+          <t>Coastal Corporation Share Price today: key market analysis - univest.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Fisher Funds Trims Vista Group Stake but Retains Strong Holding - The Globe and Mail</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Vista Group International (ASX:VGL): Is This Cinema Tech Stock Is Worth Watching After Raising Revenue Guidance - kalkine.com.au</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Aarvee Denims &amp; Exports Share Price today after sharp gain - Univest</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Vista Group International Number of Employees 2026 | Employee Count &amp; Headcount Data - Revelio Labs</t>
-        </is>
-      </c>
+          <t>Coastal Corporation Share Price today: key market analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3000,68 +3032,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD.NS</t>
+          <t>VIKRAN.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Limited</t>
+          <t>Vikran Engineering Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>51.77999877929688</v>
+        <v>60.5</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>51.77999877929688</v>
+        <v>60.97999954223633</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>48.40999984741211</v>
+        <v>58.52999877929688</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>49.16999816894531</v>
+        <v>59.04999923706055</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>52.20000076293945</v>
+        <v>60.9900016784668</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>49.16999816894531</v>
+        <v>59.04999923706055</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>5922292</v>
+        <v>1905408</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.8</v>
+        <v>-3.18</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide (JINDWORLD.NS) Edges Higher at ₹38.31; Key Support and Resistance in Focus - Dividend Growth Stocks - siam.in</t>
+          <t>Intraday Stocks for Today: 3 Setups From Vikran, Divi's Labs and Olectra - univest.in</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Limited(BSE: 531543) dropped from S&amp;P Global BMI Index - marketscreener.com</t>
+          <t>Intraday Stocks for Today: 3 Setups From Vikran, Divi's Labs and Olectra - univest.in</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Share Price Falls in Second Session - Univest</t>
+          <t>Vikran Engineering shares rally nearly 12% on securing ₹154 crore order from Power Grid - Upstox</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
+          <t>Vikran Engineering Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Share Price Falls; Valuation Check - Univest</t>
+          <t>Vikran Engineering shareholders approve ₹1,000 crore NCD facility - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3069,68 +3101,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MARINE.NS</t>
+          <t>GODREJAGRO.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Marine Electricals (India) Limited</t>
+          <t>Godrej Agrovet Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>415</v>
+        <v>676</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>421.1000061035156</v>
+        <v>679.9500122070312</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>396</v>
+        <v>653.3499755859375</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>401.5</v>
+        <v>654.8499755859375</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>425.7999877929688</v>
+        <v>676.0499877929688</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>401.5</v>
+        <v>654.8499755859375</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2131350</v>
+        <v>75911</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.71</v>
+        <v>-3.14</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Knowledge Marine shares jump 5% then drop 2% despite this work order update - What next? Tech experts decode - TradingView</t>
+          <t>Godrej Agrovet ESGS 2018 Stock Option Grant and Lapse - kalkine.co.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Tokio Marine Holdings stock falls 3.27 percent in Tokyo - AD HOC NEWS</t>
+          <t>Top stocks to buy today: Stock market recommendations for September 25, 2026 - check list - The Times of India</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Marine Electricals shares rise 7% as company expands operational capacity with launch of new plant in Goa - Moneycontrol.com</t>
+          <t>Godrej Agrovet FY26: Revenue ₹10,233 Cr, ₹11 Dividend &amp; Call Recording - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Marine Electricals shares jump 8% on capacity expansion update; stock up 92% YTD - Upstox</t>
+          <t>Godrej Agrovet Share Price Rises; Price, Valuation View - univest.in</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Knowledge Marine shares jump 5% then drop 2% despite this work order update - What next? Tech experts decode - livemint.com</t>
+          <t>Top stocks to buy today: Stock market recommendations for September 25, 2026 - check list - The Times of India</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3138,56 +3170,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>GTECJAINX.NS</t>
+          <t>INDOMIM.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>G-TEC JAINX EDUCATION LIMITED</t>
+          <t>INDO-MIM Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>27.18000030517578</v>
+        <v>1349</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>27.98999977111816</v>
+        <v>1349</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>26.11000061035156</v>
+        <v>1270</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>26.47999954223633</v>
+        <v>1272</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.06999969482422</v>
+        <v>1311.150024414062</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26.47999954223633</v>
+        <v>1272</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>5666</v>
+        <v>1117294</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.66</v>
+        <v>-2.99</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>G-TEC Jainx Education (GTECJAINX.NS) Slips 5.80% to ₹27.61, Testing ₹26.23 Support Zone - Gap and Reverse - siam.in</t>
+          <t>INDO-MIM LIMITED Share Price - Live NSE: INDOMIM Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>G-TEC Jainx Education (GTECJAINX.NS) Slips 5.80% to ₹27.61, Testing ₹26.23 Support Zone - Gap and Reverse - siam.in</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Upstox</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>INDOMIM Share Price Today - INDO-MIM LIMITED Stock Price Live NSE/BSE - univest.in</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>IndoMIM Share Price Today - Indo-MIM Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Free float of INDO-MIM Limited – NSE:INDOMIM - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3195,68 +3239,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE.NS</t>
+          <t>ORCHPHARMA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>BlueStone Jewellery and Lifestyle Limited</t>
+          <t>Orchid Pharma Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>862.4500122070312</v>
+        <v>1102.599975585938</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>862.5499877929688</v>
+        <v>1116</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>790.0499877929688</v>
+        <v>1061.099975585938</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>807.1500244140625</v>
+        <v>1063.900024414062</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>855.5</v>
+        <v>1096.150024414062</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>807.1500244140625</v>
+        <v>1063.900024414062</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>6798083</v>
+        <v>44771</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.65</v>
+        <v>-2.94</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE Stock Price and Chart — NSE:BLUESTONE - TradingView</t>
+          <t>Orchid Pharma (NSE: ORCHPHARMA) Property Acquisition and Merger Share Listing Update - kalkine.co.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>BlueStone shares worth ₹513 crore change hands in block deal; stock in focus - CNBC TV18</t>
+          <t>Orchid Pharma: Equity Shares Listed Post Amalgamation Approval - InvestyWise</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>BlueStone shares worth ₹513 crore change hands in block deal; stock in focus - CNBC TV18</t>
+          <t>Orchid Pharma Surges 6% to ₹1,024.85, Breaks Past Key Resistance Zone - Volume Rate Change - siam.in</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>BlueStone Jewellery share price falls 9% today | What's behind the plunge? - livemint.com</t>
+          <t>Orchid Pharma Share Price Today: Price Rise and Fundamentals - univest.in</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Bluestone Jewellery &amp; Lifestyle Ltd leads losers in 'A' group - Business Standard</t>
+          <t>Orchid Pharma announces listing of 4,45,86,052 equity shares following amalgamation - Business Upturn</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:58:06 IST</t>
+          <t>2026-09-25 13:31:05 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3264,61 +3308,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RACE.NS</t>
+          <t>MANIPALHOS.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Race Eco Chain Limited</t>
+          <t>Manipal Health Enterprises Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>120.1999969482422</v>
+        <v>739</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>122.8899993896484</v>
+        <v>746.5499877929688</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>114</v>
+        <v>719.0999755859375</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>115.9800033569336</v>
+        <v>720.7000122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>122.9100036621094</v>
+        <v>742.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>115.9800033569336</v>
+        <v>720.7000122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>76249</v>
+        <v>296848</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.64</v>
+        <v>-2.94</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Nine European Drugmakers Warn the Continent Risks Losing the Pharma Investment Race: Report - PharmExec.com</t>
+          <t>Manipal Health Enterprises Ltd Share Price Today,, MANIPALHOS Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Meta VR Stock Dips 0.4% as Vision Pro Race Heats Up [2026] - tech-insider.org</t>
+          <t>MANIPAL HEALTH ENTERPRI L (MANIPALHOS) Share Price Falls 2.29% Today - univest.in</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Meta VR Stock Dips 0.4% as Vision Pro Race Heats Up [2026] - tech-insider.org</t>
+          <t>MANIPAL HEALTH ENTERPRI L Share Price Rise and Valuation - univest.in</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Snap Stock Rises as It Joins the AI Assistant Race - Barron's</t>
+          <t>MANIPALHOS Share Price: Fresh 52-Week High and Valuation - univest.in</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Ferrari has used €558 million to buy its own shares in 2026 - Stock Titan</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-10 — cnbctv:fa79b73ec094b:0 - TradingView</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>ADSL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>Allied Digital Services Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>55.97999954223633</v>
+        <v>97.98000335693359</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>62.43999862670898</v>
+        <v>115.5199966430664</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>54.70999908447266</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>62.09999847412109</v>
+        <v>115.5199966430664</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>55.77000045776367</v>
+        <v>96.26999664306641</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62.09999847412109</v>
+        <v>115.5199966430664</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2430221</v>
+        <v>2244051</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>11.35</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price - Upstox</t>
+          <t>Allied Digital Services Share Price rises 14.29% to Rs 110 - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price - Upstox</t>
+          <t>Allied Digital Services Share Price rises 14.29% to Rs 110 - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - kalkine.co.in</t>
+          <t>ADSL Holdings Inc. (AMNNF) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - univest.in</t>
+          <t>Coya Therapeutics (COYA) Rises Modestly as Shares Hold Above $4.41 Support - Momentum Factor - siam.in</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works Plant Operational Despite KSPCB Order; Shares Rise - HDFC Sky</t>
+          <t>Stocks in news: Canara Bank, Vodafone Idea, Premier Energies and ACME Solar - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGOLD.NS</t>
+          <t>RETAIL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Limited</t>
+          <t>JHS Svendgaard Retail Ventures Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>289.7999877929688</v>
+        <v>17.97999954223633</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>322</v>
+        <v>20.05999946594238</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>288.989990234375</v>
+        <v>16.36000061035156</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>315.7000122070312</v>
+        <v>20.05999946594238</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>283.6199951171875</v>
+        <v>16.71999931335449</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>315.7000122070312</v>
+        <v>20.05999946594238</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>21620457</v>
+        <v>111518</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>11.31</v>
+        <v>19.98</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>SS Retail Share Price: Stock debuts at 47%, gains 14% more after listing - India Infoline</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>What Instacart Stock's Retail Expansion Means For Shareholders - simplywall.st</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International (SHANTIGOLD) Share Price Falls 8.03% Today - univest.in</t>
+          <t>SS Retail shares list at 51% premium over IPO price on BSE; should you buy, sell or hold? - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International SHANTIGOLD Q1 FY27 Results Clarification - kalkine.co.in</t>
+          <t>Spencer's Retail Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Share Price rises 9.58% today - univest.in</t>
+          <t>SS Retail shares make strong D-Street debut, list at 51% premium over IPO price - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,56 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AVADHSUGAR.NS</t>
+          <t>LANDSMILL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Avadh Sugar &amp; Energy Limited</t>
+          <t>Landsmill Green Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>724.0999755859375</v>
+        <v>0.5299999713897705</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>796.5</v>
+        <v>0.6200000047683716</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>720.6500244140625</v>
+        <v>0.5199999809265137</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>796.5</v>
+        <v>0.6200000047683716</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>724.0999755859375</v>
+        <v>0.5199999809265137</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>796.5</v>
+        <v>0.6200000047683716</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>461445</v>
+        <v>6935351</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10</v>
+        <v>19.23</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Avadh Sugar &amp; Energy Holds Steady Near ₹733 as Traders Eye Range Boundaries - Volume Spike Alerts - siam.in</t>
+          <t>Landsmill Green board approves promoter reclassification to public category - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Avadh Sugar &amp; Energy turns profitable in Q1FY27 with ₹0.24 Cr net profit - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>AVADHSUGAR Q2 2026 Earnings: Revenue Edges Up 2.36% as EPS Comes in at ₹28.63 - EPS Miss Report - siam.in</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Sugar stocks: Why Balrampur Chini, Bajaj Hindusthan, Dwarikesh Sugar, others are falling today - Business Today</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Avadh Sugar &amp; Energy turns profitable in Q1FY27 with ₹0.24 Cr net profit - scanx.trade</t>
-        </is>
-      </c>
+          <t>Landsmill Green board approves promoter reclassification to public category - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +748,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ANTELOPUS.NS</t>
+          <t>SHANTIGOLD.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy Limited</t>
+          <t>Shanti Gold International Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1135</v>
+        <v>289.7999877929688</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1260</v>
+        <v>333.0899963378906</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1094.400024414062</v>
+        <v>288.989990234375</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1241.75</v>
+        <v>325.6799926757812</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1130.949951171875</v>
+        <v>283.6199951171875</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1241.75</v>
+        <v>325.6799926757812</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4478800</v>
+        <v>36403975</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>14.83</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy: Best Stock in Its Sector? Key Metrics - univest.in</t>
+          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy: Best Stock in Its Sector? Key Metrics - univest.in</t>
+          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Shanti Gold International (SHANTIGOLD) Share Price Falls 8.03% Today - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy ESOP Allotment September 2026 - kalkine.co.in</t>
+          <t>Shanti Gold International SHANTIGOLD Q1 FY27 Results Clarification - kalkine.co.in</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy (ANTELOPUS.NS) Slides 7.16% to ₹1057.8 as Stock Nears Key Support - Low Beta Factor - siam.in</t>
+          <t>Shanti Gold International Share Price rises 9.58% today - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,68 +817,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DAVANGERE.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar Company Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.190000057220459</v>
+        <v>55.97999954223633</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.400000095367432</v>
+        <v>66.66000366210938</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.150000095367432</v>
+        <v>54.70999908447266</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.400000095367432</v>
+        <v>64.02999877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2.190000057220459</v>
+        <v>55.77000045776367</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.400000095367432</v>
+        <v>64.02999877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>26001785</v>
+        <v>13696602</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9.59</v>
+        <v>14.81</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Sugar stock under ₹5 Davangere Sugar Company jumps over 7% | What's fueling the stock - Livemint</t>
+          <t>UGARSUGAR Share Price Today: 8.51% Rise, Valuation View - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar FY26 net profit falls to ₹850.66 lakh - scanx.trade</t>
+          <t>UGARSUGAR Share Price Today: 8.51% Rise, Valuation View - Univest</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar FY26 net profit falls to ₹850.66 lakh - scanx.trade</t>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - kalkine.co.in</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar Stock Jumps 6%: What’s Driving This Sugar Stock Rally As Ethanol Expansion Plans Gather Pace? - Goodreturns</t>
+          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - Univest</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar Company Share Price Update and Analysis - univest.in</t>
+          <t>Ugar Sugar Works Plant Operational Despite KSPCB Order; Shares Rise - hdfcsky.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -898,68 +886,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TCI.NS</t>
+          <t>TGVSL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Transport Corporation of India Limited</t>
+          <t>TGV Sraac Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>877</v>
+        <v>110.1100006103516</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>955</v>
+        <v>127.7399978637695</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>863.1500244140625</v>
+        <v>110.1100006103516</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>912.3499755859375</v>
+        <v>124.7799987792969</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>833.4500122070312</v>
+        <v>109.3099975585938</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>912.3499755859375</v>
+        <v>124.7799987792969</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4932104</v>
+        <v>10384035</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>14.15</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>TCI Express Ltd is Rated Sell - MarketsMojo</t>
+          <t>TGV SRAAC Ltd (TGVSL): Chlor-Alkali Recovery and Outlook - kalkine.co.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>TCI Express Ltd is Rated Sell - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Transcontinental Realty Investors (TCI) Ticks Up 1.31% to $40.35, Holding Above Key Support - PCR Divergence - siam.in</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>TCI Share Price: Fresh 52-Week Low, Valuation View - univest.in</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Transcontinental Realty Investors stock holds its value on September 22, 2026 - AD HOC NEWS</t>
-        </is>
-      </c>
+          <t>TGV SRAAC Ltd (TGVSL): Chlor-Alkali Recovery and Outlook - kalkine.co.in</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -967,68 +943,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ARTEMISMED.NS</t>
+          <t>UTTAMSUGAR.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Artemis Medicare Services Limited</t>
+          <t>Uttam Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>346</v>
+        <v>261.7999877929688</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>378.7999877929688</v>
+        <v>304.8999938964844</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>346</v>
+        <v>260</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>358.8999938964844</v>
+        <v>293.1499938964844</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>332.7000122070312</v>
+        <v>260</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>358.8999938964844</v>
+        <v>293.1499938964844</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>16749605</v>
+        <v>2804540</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>7.87</v>
+        <v>12.75</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Artemis Medicare Services Share Price rises 6.45% today - univest.in</t>
+          <t>Uttam Sugar Mills Share Price Fall: Price Action Review - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Artemis Medicare Services Share Price rises 6.45% today - univest.in</t>
+          <t>Uttam Sugar Mills (NSE:UTTAMSUGAR) Names Harish Kumar Dhingra as CFO - kalkine.co.in</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Artemis Med Service Share Price - Upstox</t>
+          <t>Uttam Sugar Mills Limited Announces Appointment of Harish Kumar Dhingra to Chief Financial Officer, Effective September 18, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Artemis Medicare Slips Marginally to ₹342.05; ARTEMISMED Tests Crucial Support Zone - Runaway Gap - siam.in</t>
+          <t>Uttam Sugar Mills UTTAMSUGAR Regulation 30 KMP Authorisation - kalkine.co.in</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Artemis Medicare Services Share Price: 52-week high update - univest.in</t>
+          <t>Uttam Sugar Mills (NSE: UTTAMSUGAR) — Integrated Sugar Business Explained - kalkine.co.in</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1036,60 +1012,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG.NS</t>
+          <t>KMSUGAR.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>LLOYDS ENGINEERING WORKS LIMITED</t>
+          <t>K.M.Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>91.23000335693359</v>
+        <v>29.20000076293945</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>98.90000152587891</v>
+        <v>33.02000045776367</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>89.05999755859375</v>
+        <v>29.20000076293945</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>97.86000061035156</v>
+        <v>32.45999908447266</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>90.91000366210938</v>
+        <v>29.05999946594238</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>97.86000061035156</v>
+        <v>32.45999908447266</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>39218627</v>
+        <v>1179803</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7.64</v>
+        <v>11.7</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Lloyds Engineering Calls NCLT-Ordered Creditor Meet on Merger Scheme - The Globe and Mail</t>
+          <t>K.M. Sugar Mills Share Price Today: Rs 31.70 and 8.75% Rise - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Lloyds Engineering Calls NCLT-Ordered Creditor Meet on Merger Scheme - The Globe and Mail</t>
+          <t>K.M. Sugar Mills Share Price Today: Rs 31.70 and 8.75% Rise - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Should You Be Adding Lloyds Engineering Works (NSE:LLOYDSENGG) To Your Watchlist Today? - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>KMSUGAR Demerger Effective Date and Record Date October 2026 - kalkine.co.in</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>KM Sugar Mills KMSUGAR promoter share transmission SAST 2026 - kalkine.co.in</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>K.M. Sugar Mills Share Price Today: Price Action Review - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1097,68 +1081,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT.NS</t>
+          <t>DWARKESH.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lloyds Enterprises Limited</t>
+          <t>Dwarikesh Sugar Industries Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>75.58000183105469</v>
+        <v>40.72000122070312</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>81.40000152587891</v>
+        <v>45.61999893188477</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>74.48999786376953</v>
+        <v>40.70000076293945</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>79.70999908447266</v>
+        <v>45.0099983215332</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>75.58000183105469</v>
+        <v>40.7400016784668</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>79.70999908447266</v>
+        <v>45.0099983215332</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>9324042</v>
+        <v>9510474</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5.46</v>
+        <v>10.48</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Lloyds Enterprises Limited (NSE:LLOYDSENT) Stock Has Shown Weakness Lately But Financials Look Strong: Should Prospective Shareholders Make The Leap? - simplywall.st</t>
+          <t>Dwarikesh Sugar DWARKESH Trading Window Closure Oct 2026 - kalkine.co.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Lloyds enterprises limited Q1 FY27 Results Preview - univest.in</t>
+          <t>Dwarikesh Sugar DWARKESH Trading Window Closure Oct 2026 - kalkine.co.in</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Lloyds enterprises limited Q1 FY27 Results Preview - univest.in</t>
+          <t>Dwarikesh Sugar FY26 Net Profit Rises 32% to ₹3,083.80 Lakh - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Lloyds Enterprises Limited Submits Q4FY26 Certificate Under SEBI Depositories Regulations - scanx.trade</t>
+          <t>Warren Buffett-Style Cash Flow Stocks Could Face Heavy Downside in OpenAI Era, Warns Dwarkesh Patel - Yahoo Finance</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Lloyds Enterprises Limited (NSE:LLOYDPP) Shares May Have Slumped 25% But Getting In Cheap Is Still Unlikely - simplywall.st</t>
+          <t>OpenAI-Hugging Face controversy deepens as experts debate Dwarkesh Patel's 'AI civilisation' claims - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1166,68 +1150,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>KRONOX.NS</t>
+          <t>BLUECLOUDS.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Limited</t>
+          <t>Blue Cloud Softech Solutions Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>205</v>
+        <v>20.85000038146973</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>206.5800018310547</v>
+        <v>23.56999969482422</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>198.0099945068359</v>
+        <v>20.67000007629395</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>206.5800018310547</v>
+        <v>22.15999984741211</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>196.75</v>
+        <v>20.05999946594238</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>206.5800018310547</v>
+        <v>22.15999984741211</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>136343</v>
+        <v>69595946</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>10.47</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax secures ₹225 crore funding to acquire Kronox Lab Sciences - scanx.trade</t>
+          <t>BLUECLOUDS wins AI infra deal of USD 15.5M from IBM Cloud Inc. - Business Standard</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax secures ₹225 crore funding to acquire Kronox Lab Sciences - scanx.trade</t>
+          <t>BLUECLOUDS wins AI infra deal of USD 15.5M from IBM Cloud Inc. - Business Standard</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences (KRONOX.NS) Holds Near ₹184.69: Stock Gains 0.72% as Range-Bound Trend Persists - Put Spread Alert - siam.in</t>
+          <t>Total common shares outstanding of Blue Cloud Softech Solutions Ltd. – NSE:BLUECLOUDS - TradingView</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>Blueclouds launches GMB Life - a preventive screening and wellness app - Business Standard</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>KRONOX Lab Sciences Limited Publishes Unaudited Financial Results for Q3 FY26 - scanx.trade</t>
+          <t>ConnectM (CNTM) pursues $5M deal backed by most of its assets - Stock Titan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1235,68 +1219,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK.NS</t>
+          <t>SBC.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>STL Networks Limited</t>
+          <t>SBC Exports Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>54.5</v>
+        <v>48.13999938964844</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>54.61000061035156</v>
+        <v>53.7400016784668</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>52.40000152587891</v>
+        <v>48.04999923706055</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>54.61000061035156</v>
+        <v>53.02000045776367</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>52.0099983215332</v>
+        <v>48.0099983215332</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>54.61000061035156</v>
+        <v>53.02000045776367</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>8896179</v>
+        <v>23812681</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5</v>
+        <v>10.44</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Free float of STL Networks Limited – NSE:STLNETWORK - TradingView</t>
+          <t>In October, SBC Medical plans online and New York meetings with investors. - Stock Titan</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Anil Agarwal confirms no encumbrance on STL Networks shares in FY26 - scanx.trade</t>
+          <t>In October, SBC Medical plans online and New York meetings with investors. - Stock Titan</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Anil Agarwal confirms no encumbrance on STL Networks shares in FY26 - scanx.trade</t>
+          <t>SBC Exports (SBC.NS) Gains 1.83% to ₹42.81, Holds Above Support at ₹40.67 - Continuation Pattern Picks - siam.in</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK.NS Q2 2026 Earnings: Revenue Declines 18.61% YoY, EPS Loss of ₹2.03, Yet Stock Gains 4.98% - siam.in</t>
+          <t>SBC Exports dispatches FY26 annual report web link to shareholders - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK Stock Price and Chart — NSE:STLNETWORK - TradingView</t>
+          <t>SBC Options Chain — NASDAQ:SBC - TradingView</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1304,68 +1288,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE.NS</t>
+          <t>CUBEXTUB.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Limited</t>
+          <t>Cubex Tubings Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>350.8999938964844</v>
+        <v>147.8999938964844</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>362.4500122070312</v>
+        <v>152.2400054931641</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>331</v>
+        <v>130.0500030517578</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>362.4500122070312</v>
+        <v>152.2400054931641</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>345.2000122070312</v>
+        <v>138.3999938964844</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>362.4500122070312</v>
+        <v>152.2400054931641</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>475860</v>
+        <v>2579589</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Ltd. Lower Circuit Today: Price, Data and Peers - univest.in</t>
+          <t>Cubex Tubings Share Price today: price action and value - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Ltd. Lower Circuit Today: Price, Data and Peers - univest.in</t>
+          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable FY26 Net Profit Jumps 235%; Dividend Declared - scanx.trade</t>
+          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - kalkine.co.in</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Universal Cables Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1373,68 +1357,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>NRAIL.NS</t>
+          <t>SHOPERSTOP.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries Limited</t>
+          <t>Shoppers Stop Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>650</v>
+        <v>382.5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>673</v>
+        <v>439.7999877929688</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>631.2000122070312</v>
+        <v>382.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>666.9000244140625</v>
+        <v>423.5499877929688</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>637.75</v>
+        <v>385.0499877929688</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>666.9000244140625</v>
+        <v>423.5499877929688</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>12411</v>
+        <v>3588097</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4.57</v>
+        <v>10</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries (NRAIL.NS) Slips 2.60% to ₹595.30 as Paper Stock Holds Mid-Range - Ending Diagonal - siam.in</t>
+          <t>Shoppers Stop NSE:SHOPERSTOP Trading Window Closure Oct 2026 - kalkine.co.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries NRAIL Trading Window Closure Q2 FY27 - kalkine.co.in</t>
+          <t>Shoppers Stop Share Price Rises 11.83% Today - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries NRAIL Price Movement Clarification - kalkine.co.in</t>
+          <t>Shoppers Stop Share Price Rises 11.83% Today - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>NR Agarwal Industries Share Price today: key market update - univest.in</t>
+          <t>Shoppers Stop Reports FY26 Net Loss, Approves Rs 40 Crore Beauty Subsidiary Investment - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>NRAIL Q2 2026 Earnings: Revenue Climbs 30.1% YoY as EPS Prints at ₹25.68 - Earnings Beat Streak - siam.in</t>
+          <t>Volume Gainers, September 15, 2026 at 12:00 PM IST - hdfcsky.com</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1442,68 +1426,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHIND.NS</t>
+          <t>FCSSOFT.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Limited</t>
+          <t>FCS Software Solutions Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>20.04999923706055</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>20.76000022888184</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>19.80999946594238</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>20.55999946594238</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>19.89999961853027</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20.55999946594238</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>18061171</v>
+        <v>3497158</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3.32</v>
+        <v>9.77</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Share Price Today: 5.39% Decline - univest.in</t>
+          <t>FCS Softwares Share Price - Upstox</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bajaj Hindusthan Sugar Share Price Today: 5.39% Decline - univest.in</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Bajaj Hindusthan Sugar Share Price Update, Sector Context - univest.in</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Bajaj Hindusthan Sugar Share Price update after 5.67% gain - univest.in</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Bajaj Hindusthan Sugar Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
-        </is>
-      </c>
+          <t>FCS Softwares Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1511,64 +1483,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>HBLENGINE.NS</t>
+          <t>DANGEE.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>HBL Engineering Limited</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>779</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>809</v>
+        <v>3.259999990463257</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>765.9500122070312</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>801</v>
+        <v>3.259999990463257</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>775.2999877929688</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>801</v>
+        <v>3.259999990463257</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4077839</v>
+        <v>909887</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3.31</v>
+        <v>9.76</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Should You Buy HBL Engineering Limited (NSE:HBLENGINE) For Its Upcoming Dividend? - simplywall.st</t>
+          <t>Dangee Dums Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>HBL Engineering Share Price Today: Rs 785.1 After 2.39% Rise - univest.in</t>
+          <t>Volume Gainers, September 24, 2026 at 3:30 PM IST: Kaveri Seed Leads Volume Jump - hdfcsky.com</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Should You Be Adding HBL Engineering (NSE:HBLENGINE) To Your Watchlist Today? - simplywall.st</t>
+          <t>Volume Gainers, September 24, 2026 at 12:00 PM IST: Dangee Dums Leads Volume Jump - hdfcsky.com</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>HBL Engineering Share Price Today: Rs 785.1 After 2.39% Rise - univest.in</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>The Dangee Dums Bull Case - Univest</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Dangee Dums Ltd. Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1576,64 +1552,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH.NS</t>
+          <t>QUADFUTURE.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Dynamatic Technologies Limited</t>
+          <t>Quadrant Future Tek Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12541</v>
+        <v>502.8500061035156</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>13287</v>
+        <v>559.7000122070312</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>12490</v>
+        <v>492.6000061035156</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12965</v>
+        <v>547.5</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12551</v>
+        <v>500.3999938964844</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>12965</v>
+        <v>547.5</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>27272</v>
+        <v>1949531</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3.3</v>
+        <v>9.41</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Dynamatic Technologies Share Price Today: Key Price Action - univest.in</t>
+          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH Q2 2026 Earnings: EPS of ₹47.73 and 15.11% Revenue Growth Met a Muted Market Reception - GAAP Earnings Report - siam.in</t>
+          <t>QUADRANT FUTURE TEK Share Price Today: Rs 543 after rise - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Dynamatic Technologies Share Price Rise: Valuation View - univest.in</t>
+          <t>Quadrant Future Tek Holds Above Support Near ₹440 Despite Mild Dip - Momentum Surge Alerts - siam.in</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH Q2 2026 Earnings: EPS of ₹47.73 and 15.11% Revenue Growth Met a Muted Market Reception - GAAP Earnings Report - siam.in</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Quadrant Future Tek (NSE:QUADFUTURE): Why Has the Trading Window Been Closed? - kalkine.co.in</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>QUADRANT FUTURE TEK LTD 52 Week High Streak: Consecutive High Analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1641,68 +1621,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER.NS</t>
+          <t>STARTECK.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Limited</t>
+          <t>Starteck Finance Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>324.8999938964844</v>
+        <v>242.0500030517578</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>341.6499938964844</v>
+        <v>262.7000122070312</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>323</v>
+        <v>242.0500030517578</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>334.1499938964844</v>
+        <v>262.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>323.9500122070312</v>
+        <v>240.3999938964844</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>334.1499938964844</v>
+        <v>262.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5171380</v>
+        <v>211</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3.15</v>
+        <v>9.19</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Share Price rises 9.01% - univest.in</t>
+          <t>Starteck Finance Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Advances CCL Project; Order Bookings Expected to Begin From October 31 - BizzBuzz</t>
+          <t>Starteck Finance Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Press Release Distribution India - Business Wire India</t>
+          <t>Starteck Finance approves ₹0.25 dividend, fund raising at 41st AGM - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering share price hits 52-week high | What's behind the rally? - Livemint</t>
+          <t>Starteck Finance Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering’s ₹330-crore rights issue fully subscribed - Moneycontrol.com</t>
+          <t>Starteck Finance Ltd (STARTECK): An Earnings Quality Question - kalkine.co.in</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1710,60 +1690,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PARAGMILK.NS</t>
+          <t>HERANBA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Parag Milk Foods Limited</t>
+          <t>Heranba Industries Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>262</v>
+        <v>173.9499969482422</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>269.3999938964844</v>
+        <v>198.8999938964844</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>256.25</v>
+        <v>171.0099945068359</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>266.3999938964844</v>
+        <v>187.6000061035156</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>258.3999938964844</v>
+        <v>172.2700042724609</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>266.3999938964844</v>
+        <v>187.6000061035156</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1405372</v>
+        <v>3333259</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>3.1</v>
+        <v>8.9</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Parag Milk Foods Share Price Today: Rs 256.5 after rise - univest.in</t>
+          <t>Heranba Industries Share Price Today With Sector Context - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-09-21 — cnbctv:a6f5fee85094b:0 - TradingView</t>
+          <t>Heranba Industries Share Price Today With Sector Context - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-09-21 — cnbctv:a6f5fee85094b:0 - TradingView</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Heranba promoters confirm no share encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Heranba Industries Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Heranba Industries Bull Case vs Bear Case for 2026 - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1771,68 +1759,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SAKAR.NS</t>
+          <t>DBOL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare Limited</t>
+          <t>Dhampur Bio Organics Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1125.099975585938</v>
+        <v>112.5100021362305</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1189.5</v>
+        <v>123</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1125.099975585938</v>
+        <v>112.5100021362305</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1161.949951171875</v>
+        <v>122.25</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1128.550048828125</v>
+        <v>113.1999969482422</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1161.949951171875</v>
+        <v>122.25</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>62605</v>
+        <v>352605</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2.96</v>
+        <v>7.99</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare Share Price Update: Sector and Peer View - univest.in</t>
+          <t>Dhampur Bio Organics shareholders approve dividend, CEO redesignation at AGM - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare Share: Bull Case vs Bear Case for 2026 - univest.in</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Sakar Healthcare Ltd. Share Price Rise Streak: Key update - univest.in</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Sakar Healthcare Share: Bull Case vs Bear Case for 2026 - univest.in</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Sakar Healthcare Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
+          <t>Dhampur Bio Organics shareholders approve dividend, CEO redesignation at AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1840,61 +1816,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PGIL.NS</t>
+          <t>FCL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Limited</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1281.800048828125</v>
+        <v>56.5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1355</v>
+        <v>61.04999923706055</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1274.800048828125</v>
+        <v>55.75</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1311</v>
+        <v>60.47999954223633</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1273.599975585938</v>
+        <v>56.06999969482422</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1311</v>
+        <v>60.47999954223633</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>362070</v>
+        <v>47011140</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2.94</v>
+        <v>7.87</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>PGIL 52 Week High Streak: Price, Sector, Valuation View - univest.in</t>
+          <t>FCL-X Fire &amp; Safety Inc. (FCLX.V) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Buy Pearl Global Industries; target of Rs 1400: Emkay Global Financial - Moneycontrol.com</t>
+          <t>FCL-X Fire &amp; Safety Inc. (FCLX.V) Stock Forum &amp; Discussion - Yahoo Finance - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Share Price Today: PGIL up 6.44% - univest.in</t>
+          <t>Fineotex Chemical Ltd. (FCL) Share Price hits fresh 52-week high as FCL trades at Rs 60.98 - Univest</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Share Price Rise in Textile Sector - univest.in</t>
+          <t>FINEOS Corporation (ASX:FCL): What Investors Need to Know About This Insurance Software Stock - kalkine.com.au</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Ltd Dividend History, Yield &amp; Record Date - INDmoney</t>
+          <t>FCL-X Fire &amp; Safety Inc. (FCLX.V) Stock Forum &amp; Discussion - Yahoo Finance - Yahoo! Finance Canada</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1891,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2021,7 +1997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2029,68 +2005,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TURTLEMINT.NS</t>
+          <t>MEDICO.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Turtlemint Fintech Solutions Limited</t>
+          <t>Medico Remedies Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>90.65000152587891</v>
+        <v>33.15000152587891</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>97.76999664306641</v>
+        <v>33.15999984741211</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>87.23999786376953</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>88.19999694824219</v>
+        <v>26</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>109.0400009155273</v>
+        <v>32.5</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>88.19999694824219</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>16797656</v>
+        <v>3536256</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-19.11</v>
+        <v>-20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech, Turtlemint Shares Extend Slump as Outlook Worsens - Bloomberg.com</t>
+          <t>Medico Remedies Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>PB Fintech, Turtlemint Shares Extend Slump as Outlook Worsens - Bloomberg.com</t>
+          <t>Medico Remedies Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Not just PB Fintech, this smallcap stock fell 36% in two days on IRDAI proposals - Moneycontrol.com</t>
+          <t>Medico Remedies Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Turtlemint Fintech Solutions Extends Decline On Second Day, Share Price Hits 20% Lower Circuit - ndtvprofit.com</t>
+          <t>Medico Remedies Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Insurance stocks crash: PB Fintech, Turtlemint shares fall up to 28% on IRDAI draft - Is this a buying opportu - CNBC TV18</t>
+          <t>Prism Medico and Pharmacy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2098,68 +2074,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AASTHA.NS</t>
+          <t>OLAELEC.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Limited</t>
+          <t>Ola Electric Mobility Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>79</v>
+        <v>42.5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>79</v>
+        <v>42.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>72.72000122070312</v>
+        <v>38.0099983215332</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>72.72000122070312</v>
+        <v>38.47999954223633</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>80.80000305175781</v>
+        <v>42.52000045776367</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>72.72000122070312</v>
+        <v>38.47999954223633</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3926117</v>
+        <v>194452956</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Bonus issue record date today: Last chance to buy Aastha Spintex shares as deadline approaches-Check stock performance - Livemint</t>
+          <t>Ola Electric (NSE: OLAELEC) Shares Fall 9%: Brokerage Views and Key Risks - kalkine.co.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Ltd (NSE: AASTHA) Declines 10.00% as Stock Draws Market Attention - kalkine.co.in</t>
+          <t>Ola Electric (NSE: OLAELEC) Shares Fall 9%: Brokerage Views and Key Risks - kalkine.co.in</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Ltd (NSE: AASTHA) Declines 10.00% as Stock Draws Market Attention - kalkine.co.in</t>
+          <t>Ola Electric Share Price - Live NSE: OLAELEC Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Share Price Fall: Price and Valuation - univest.in</t>
+          <t>Ola Electric Mobility Ltd (NSE: OLAELEC) Declines 7.86% as Stock Draws Market Attention - kalkine.co.in</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Secures ₹25 Crore Fabric Orders; Shares Fall 9.99% - HDFC Sky</t>
+          <t>Ola Electric Plans On-Site Analyst Meet at Future Factory and Giga Factory - The Globe and Mail</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2167,68 +2143,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MANUGRAPH.NS</t>
+          <t>SGL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Manugraph India Limited</t>
+          <t>STL Global Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>23</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>23</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>19.81999969482422</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19.81999969482422</v>
+        <v>9.029999732971191</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>22.02000045776367</v>
+        <v>9.810000419616699</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.81999969482422</v>
+        <v>9.029999732971191</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>177954</v>
+        <v>64142</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.99</v>
+        <v>-7.95</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Manugraph India (MANUGRAPH.NS) Edges Higher to ₹15.19 as Stock Pivots Near Key Resistance - Fibonacci Retracement - siam.in</t>
+          <t>STL Global SGL Trading Window Closure October 2026 - kalkine.co.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>STL Global SGL Trading Window Closure October 2026 - kalkine.co.in</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Manugraph India Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>SGL stock gains 9.68 percent as shares reach MYR 0.17 - AD HOC NEWS</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Manugraph India Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
+          <t>STL Global (SGL.NS) Rises 2.03% to ₹10.07; Key Resistance at ₹10.57 in Focus - Fade Trade - siam.in</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Manugraph India Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
+          <t>SGL Resources Ltd is Rated Strong Sell - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2236,51 +2212,51 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>OLAELEC.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>42.5</v>
+        <v>15.01000022888184</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>42.5</v>
+        <v>15.01000022888184</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>38.56999969482422</v>
+        <v>13.14000034332275</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>38.63000106811523</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>42.52000045776367</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>38.63000106811523</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>132452739</v>
+        <v>7859410</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-9.15</v>
+        <v>-7.4</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Plans On-Site Analyst Meet at Future Factory and Giga Factory - The Globe and Mail</t>
+          <t>Atal Realtech Ltd (NSE: ATALREAL) Falls 5.48% as Stock Draws Market Attention - kalkine.co.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Plans On-Site Analyst Meet at Future Factory and Giga Factory - The Globe and Mail</t>
+          <t>Atal Realtech Ltd (NSE: ATALREAL) Falls 5.48% as Stock Draws Market Attention - kalkine.co.in</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ola shares rise 6% on S1Z launch with indigenous cell tech, claims 301 km per charge - Business Today</t>
+          <t>Atal Realtech Share Price Today: Price Fall and Valuation - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
@@ -2289,7 +2265,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2297,68 +2273,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MEESHO.NS</t>
+          <t>RRECL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Meesho Limited</t>
+          <t>RDB Real Estate Constructions Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>228.9299926757812</v>
+        <v>132.9499969482422</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>229.5800018310547</v>
+        <v>132.9499969482422</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>218</v>
+        <v>121.0299987792969</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>218.8600006103516</v>
+        <v>123.4000015258789</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>232.8399963378906</v>
+        <v>133.1199951171875</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>218.8600006103516</v>
+        <v>123.4000015258789</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>21263015</v>
+        <v>343</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6</v>
+        <v>-7.3</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Meesho shares can fall 28%, warns Nomura after initiating coverage with Reduce call. Here is why - The Economic Times</t>
+          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Meesho shares fall 6% as Nomura warns of premium valuation, initiates 'Reduce' with Rs 167 TP - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Meesho shares fall 6% as Nomura warns of premium valuation, initiates 'Reduce' with Rs 167 TP - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Meesho Shares Trading At Significant Premium, Says Nomura; Assigns 'Reduce' Rating, Sees Over 28% Downside - ndtvprofit.com</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Meesho's valuation woes prompt Nomura to assign 'Reduce' tag; stock down 5% - Business Standard</t>
-        </is>
-      </c>
+          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2366,68 +2330,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>UNIDT.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Limited</t>
+          <t>United Drilling Tools Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>61.93999862670898</v>
+        <v>257.7300109863281</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>63.4900016784668</v>
+        <v>260.8200073242188</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>61.93999862670898</v>
+        <v>238.2400054931641</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.93999862670898</v>
+        <v>241.7100067138672</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>65.19999694824219</v>
+        <v>259.760009765625</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>61.93999862670898</v>
+        <v>241.7100067138672</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2394236</v>
+        <v>139219</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5</v>
+        <v>-6.95</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures slumps after CEO, COO resign - Business Standard</t>
+          <t>United Drilling Tools Share Price: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures slumps after CEO, COO resign - Business Standard</t>
+          <t>20% Upper Circuit: 12 Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures accepts resignation of Executive Director and COO - scanx.trade</t>
+          <t>United Drilling Tools Limited Secures ₹5.04 Crore Order from ONGC for Integral Blade Stabilizer Supply - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Upper Circuit Streak: Day 2 Price and Data - univest.in</t>
+          <t>United Drilling Tools Limited (NSE:UNIDT) Goes Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures (PVP.NS) Slips 1.82% to ₹64.9 as Stock Drifts Toward ₹61.66 Support - Weekly Profile - siam.in</t>
+          <t>United Drilling Tools Slips 1.62% to ₹230.36 — Support and Resistance Levels in Focus - Insider Sentiment - siam.in</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2435,68 +2399,56 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER.NS</t>
+          <t>PBMPOLY.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Empower India Limited</t>
+          <t>PBM Polytex Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.870000004768372</v>
+        <v>60.59999847412109</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1.870000004768372</v>
+        <v>67.47000122070312</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.870000004768372</v>
+        <v>57.97000122070312</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.870000004768372</v>
+        <v>59.90999984741211</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.960000038146973</v>
+        <v>63.68000030517578</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.870000004768372</v>
+        <v>59.90999984741211</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4455082</v>
+        <v>464</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.59</v>
+        <v>-5.92</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Penny stock under 10 rupees hits 5% upper circuit after this acquisition update - Livemint</t>
+          <t>PBM Polytex Ltd. (NSE: PBMPOLY) Business Overview and Growth Factors - kalkine.co.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Dangote to empower two million women with refinery IPO shares - PM News Nigeria</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>What employees should know before their company goes public - Empower</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Empower India Share Price Rises 4% Penny Stock Eyes India's Growing AI and Data Centre Infrastructure Boom - Goodreturns</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Good time to reset AI stock positioning, says Empower's Marta Norton - CNBC</t>
-        </is>
-      </c>
+          <t>PBM Polytex Ltd. (NSE: PBMPOLY) Business Overview and Growth Factors - kalkine.co.in</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2504,64 +2456,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI.NS</t>
+          <t>PREMIERPOL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Limited</t>
+          <t>Premier Polyfilm Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32.29000091552734</v>
+        <v>102</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>32.79999923706055</v>
+        <v>102.6699981689453</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30.68000030517578</v>
+        <v>94.19999694824219</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>30.85000038146973</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>32.29000091552734</v>
+        <v>100.5100021362305</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>30.85000038146973</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>875526</v>
+        <v>783831</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.46</v>
+        <v>-5.08</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Share Price update on fundamentals - univest.in</t>
+          <t>Premier Polyfilm (PREMIERPOL) Sheds Nearly 1% Amid Range-Bound Trading - Turnaround Stocks - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Indo Thai Securities Share Price update on fundamentals - univest.in</t>
+          <t>Premier Polyfilm insider Manvi Goenka sells 2.07 lakh shares - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Indo Thai Securities (NSE:INDOTHAI) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Is It Smart To Buy Premier Polyfilm Ltd. (NSE:PREMIERPOL) Before It Goes Ex-Dividend? - simplywall.st</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>INDOTHAI Q2 2026 Earnings: Revenue Jumps 213.6% YoY as EPS Hits ₹5.29, Shares Slip 5.2% - Profit Guidance Range - siam.in</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Premier Polyfilm Share Price at Rs 97.14 near 52-week peak - Univest</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Premier Polyfilm Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2569,64 +2525,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TFCILTD.NS</t>
+          <t>NAGREEKCAP.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Tourism Finance Corporation of India Limited</t>
+          <t>Nagreeka Capital &amp; Infrastructure Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>142</v>
+        <v>30.75</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>144</v>
+        <v>31.35000038146973</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>135.4900054931641</v>
+        <v>27.17000007629395</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>137.7299957275391</v>
+        <v>28.05999946594238</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>143.4600067138672</v>
+        <v>29.54999923706055</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>137.7299957275391</v>
+        <v>28.05999946594238</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>19601760</v>
+        <v>138167</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-3.99</v>
+        <v>-5.04</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>TFCILTD Share Price: Yearly High, Valuation and Sector View - univest.in</t>
+          <t>Nagreeka Capital &amp; Infrastructure (NAGREEKCAP.NS) Slips 1.59% to ₹22.87, Hovers Near Support Zone - Fibonacci Entry Signals - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>TFCILTD Share Price: Yearly High, Valuation and Sector View - univest.in</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>TFCILTD Share Price Hits Fresh 52-Week High: Price Action - univest.in</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Tourism Finance Corporation (TFCILTD.NS) Slips to ₹140.54 — Key Support and Resistance Levels in Spotlight - Volatility Surface - siam.in</t>
-        </is>
-      </c>
+          <t>Nagreeka Capital &amp; Infrastructure (NAGREEKCAP.NS) Slips 1.59% to ₹22.87, Hovers Near Support Zone - Fibonacci Entry Signals - siam.in</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2634,68 +2582,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RML.NS</t>
+          <t>CALSOFT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Rane (Madras) Limited</t>
+          <t>California Software Company Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1369.599975585938</v>
+        <v>37.77999877929688</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1379.199951171875</v>
+        <v>37.90000152587891</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1305.900024414062</v>
+        <v>36.11999893188477</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1310.099975585938</v>
+        <v>36.11999893188477</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1362.800048828125</v>
+        <v>38.02000045776367</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1310.099975585938</v>
+        <v>36.11999893188477</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>31844</v>
+        <v>227209</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-3.87</v>
+        <v>-5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Rane (Madras) Limited (RML.NS) Rallies 3.80% to ₹1330.5 as Auto Ancillary Counter Nears Upper Resistance - Insider Selling Alerts - siam.in</t>
+          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Rane (Madras) Limited (RML.NS) Rallies 3.80% to ₹1330.5 as Auto Ancillary Counter Nears Upper Resistance - Insider Selling Alerts - siam.in</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Rane (RML.NS) Up +3.80% — 3 Reasons the Rally Could Continue 2026-09-20 - Synthetic Long - siam.in</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>symbol__ Stock Quote Price and Forecast - CNN</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Resolution Minerals (RML) Stock Price, News &amp; Analysis $RML - MarketBeat</t>
-        </is>
-      </c>
+          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2703,68 +2639,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>PVP.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>One 97 Communications Limited</t>
+          <t>PVP Ventures Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1732.5</v>
+        <v>61.93999862670898</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1747.199951171875</v>
+        <v>63.4900016784668</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1665</v>
+        <v>61.93999862670898</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1668.5</v>
+        <v>61.93999862670898</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1735.5</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1668.5</v>
+        <v>61.93999862670898</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2973840</v>
+        <v>2454235</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-3.86</v>
+        <v>-5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Paytm Stock And 2 Indian Founder Led Stocks To Watch - simplywall.st</t>
+          <t>PVP Ventures slumps after CEO, COO resign - Business Standard</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>NSE rises 5% after listing: Paytm crashed 27%, Coal India soared 40%; how India’s mega IPOs debuted - Moneycontrol.com</t>
+          <t>PVP Ventures slumps after CEO, COO resign - Business Standard</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Paytm is looking beyond payments. What it means for the stock - TradingView</t>
+          <t>PVP Ventures Ltd. Upper Circuit Streak: Day 2 Price and Data - Univest</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Ferro alloy maker Maithan bets ₹62 crore on Paytm and ESDS shares - Dealroom</t>
+          <t>PVP Ventures accepts Dr. Ellen Jane Feehan resignation as CEO - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>PAYTM Share Price today near yearly high with valuation - univest.in</t>
+          <t>PVP Ventures (PVP.NS) Slips 1.82% to ₹64.9 as Stock Drifts Toward ₹61.66 Support - Weekly Profile - siam.in</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2772,64 +2708,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MEGASTAR.NS</t>
+          <t>MOTISONS.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Megastar Foods Limited</t>
+          <t>Motisons Jewellers Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>270</v>
+        <v>18.88999938964844</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>270</v>
+        <v>19.47999954223633</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>251.3999938964844</v>
+        <v>17.6200008392334</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>251.3999938964844</v>
+        <v>17.85000038146973</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>260.8999938964844</v>
+        <v>18.79000091552734</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>251.3999938964844</v>
+        <v>17.85000038146973</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3081</v>
+        <v>119044859</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-3.64</v>
+        <v>-5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Megastar Foods Share: Bull Case vs Bear Case for 2026 - univest.in</t>
+          <t>Motisons Jewellers to consider redemption of 50 lakh preference shares - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Megastar Foods Share: Bull Case vs Bear Case for 2026 - univest.in</t>
+          <t>Motisons Jewellers (NSE:MOTISONS): What Does the Redemption of 50 Lakh Preference Shares Mean? - kalkine.co.in</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Megastar Foods schedules 15th AGM for September 23, 2026 - scanx.trade</t>
+          <t>Motisons Jewellers (NSE:MOTISONS): What Does the Redemption of 50 Lakh Preference Shares Mean? - kalkine.co.in</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Megastar Chiranjeevi's Kaka Team Shares Exciting Shooting Update - The Hans India</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Motisons Jewellers sets Sept 28 AGM; appoints N.K. Aswani as auditor - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers Share Price Today: Price Rise Review - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2837,68 +2777,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>GLOBAL.NS</t>
+          <t>SIMPLXREA.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Global Education Limited</t>
+          <t>Simplex Realty Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>142.3500061035156</v>
+        <v>131.9900054931641</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>142.4900054931641</v>
+        <v>138.5700073242188</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>135.1999969482422</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>136</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>141</v>
+        <v>131.9900054931641</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>136</v>
+        <v>125.4000015258789</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>154741</v>
+        <v>717</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-3.55</v>
+        <v>-4.99</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Global shares, bonds bounce as oil skid offers inflation relief - DD News</t>
+          <t>GUJTLRM Stock Price and Chart — BSE:GUJTLRM - TradingView</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Aussie Dollar Slides: Why It Could Boost Your SMSF's Global Shares - Kalkine Media</t>
+          <t>GUJTLRM Stock Price and Chart — BSE:GUJTLRM - TradingView</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Liberty Global stock hits 52-week low at 9.42 USD - Investing.com India</t>
+          <t>SATCH Stock Price and Chart — BSE:SATCH - TradingView</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Bond Selloff Worsens, Dinging Stocks - WSJ</t>
+          <t>ARTNIRMAN Stock Price and Chart — NSE:ARTNIRMAN - TradingView</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>A US diesel export ban would trigger global stock drawdowns, cut US refinery utilisation and risk driving gasoline prices higher - Wood Mackenzie</t>
+          <t>PRAENG Stock Price and Chart — NSE:PRAENG - TradingView</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2906,68 +2846,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS.NS</t>
+          <t>SEMAC.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom Limited</t>
+          <t>Semac Construction Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>775.5</v>
+        <v>268.3999938964844</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>787.2999877929688</v>
+        <v>268.3999938964844</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>752.0499877929688</v>
+        <v>255</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>754.6500244140625</v>
+        <v>255</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>781.5</v>
+        <v>268.3999938964844</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>754.6500244140625</v>
+        <v>255</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>358203</v>
+        <v>1613</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-3.44</v>
+        <v>-4.99</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom To Acquire 51.1% Stake In Joint Venture With Nothing Electronics - Sahi</t>
+          <t>Semac Construction shares FY26 annual report web link ahead of AGM - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Buy, Sell Or Hold: NSE vs BSE, Ola Electric, Laurus Labs, GE Shipping, Optiemus Infracom — Ask Profit - ndtvprofit.com</t>
+          <t>Semac Construction to hold 49th AGM on September 25 via video conference - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom shares extend two-day rally to 33%: Here are two reasons - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Optiemus Infracom shares surge nearly 45% in three sessions, hit fresh 52-week high; here is why - Upstox</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Optiemus eyes ₹2,000 crore FY28 revenue from screen protectors, stock up 20% for second day - CNBC TV18</t>
-        </is>
-      </c>
+          <t>Semac Construction to hold 49th AGM on September 25 via video conference - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2975,56 +2907,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COASTCORP.NS</t>
+          <t>MONEYBOXX.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Coastal Corporation Limited</t>
+          <t>Moneyboxx Finance Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>38.47000122070312</v>
+        <v>55.29999923706055</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>38.47000122070312</v>
+        <v>55.29999923706055</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>35.65999984741211</v>
+        <v>51.20999908447266</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>51.20999908447266</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>37.68000030517578</v>
+        <v>53.90000152587891</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>51.20999908447266</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>91490</v>
+        <v>26962</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-3.4</v>
+        <v>-4.99</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Coastal Corporation Share Price today: key market analysis - univest.in</t>
+          <t>Moneyboxx Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Coastal Corporation Share Price today: key market analysis - univest.in</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Moneyboxx Finance allots ₹60 crore NCDs at 10.75% coupon - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance FY26 net profit rises 7.4% to ₹1.34 crore - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3032,68 +2976,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIKRAN.NS</t>
+          <t>SRGHFL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering Limited</t>
+          <t>SRG Housing Finance Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>60.5</v>
+        <v>155.25</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>60.97999954223633</v>
+        <v>155.25</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>58.52999877929688</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.04999923706055</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>60.9900016784668</v>
+        <v>154.5</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>59.04999923706055</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1905408</v>
+        <v>15491</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-3.18</v>
+        <v>-4.98</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Intraday Stocks for Today: 3 Setups From Vikran, Divi's Labs and Olectra - univest.in</t>
+          <t>SRGHFL Share Price Near 52-Week Low: Price Action Update - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Intraday Stocks for Today: 3 Setups From Vikran, Divi's Labs and Olectra - univest.in</t>
+          <t>SRG Housing Finance SRGHFL Trading Window Closure Q2 FY27 - kalkine.co.in</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering shares rally nearly 12% on securing ₹154 crore order from Power Grid - Upstox</t>
+          <t>SRG Housing Finance Share Price Fall: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>SRG Housing Finance SRGHFL Trading Window Closure Q2 FY27 - kalkine.co.in</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Vikran Engineering shareholders approve ₹1,000 crore NCD facility - scanx.trade</t>
+          <t>SRG Housing Finance Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3101,68 +3045,56 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO.NS</t>
+          <t>VISACHROME.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Godrej Agrovet Limited</t>
+          <t>VISA Chrome Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>676</v>
+        <v>35.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>679.9500122070312</v>
+        <v>37.95000076293945</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>653.3499755859375</v>
+        <v>34.52999877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>654.8499755859375</v>
+        <v>34.54000091552734</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>676.0499877929688</v>
+        <v>36.34000015258789</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>654.8499755859375</v>
+        <v>34.54000091552734</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>75911</v>
+        <v>20791</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.14</v>
+        <v>-4.95</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Godrej Agrovet ESGS 2018 Stock Option Grant and Lapse - kalkine.co.in</t>
+          <t>ACRE revises Visa Chrome stake sale to 67.6 lakh shares - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Top stocks to buy today: Stock market recommendations for September 25, 2026 - check list - The Times of India</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Godrej Agrovet FY26: Revenue ₹10,233 Cr, ₹11 Dividend &amp; Call Recording - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Godrej Agrovet Share Price Rises; Price, Valuation View - univest.in</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Top stocks to buy today: Stock market recommendations for September 25, 2026 - check list - The Times of India</t>
-        </is>
-      </c>
+          <t>ACRE revises Visa Chrome stake sale to 67.6 lakh shares - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3170,68 +3102,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM.NS</t>
+          <t>RHETAN.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM Limited</t>
+          <t>Rhetan TMT Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1349</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1349</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1270</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1272</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1311.150024414062</v>
+        <v>15.96000003814697</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1272</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1117294</v>
+        <v>803050</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-2.99</v>
+        <v>-4.95</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>INDO-MIM LIMITED Share Price - Live NSE: INDOMIM Stock Price &amp; Chart - Upstox</t>
+          <t>Rhetan TMT Ltd (NSE: RHETAN) Declines 4.98% as Stock Draws Market Attention - kalkine.co.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Indo-MIM shares decline ahead of Q1 results; here's how the stock is performing vs issue price - Upstox</t>
+          <t>Rhetan TMT Ltd (NSE: RHETAN) Declines 4.98% as Stock Draws Market Attention - kalkine.co.in</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>INDOMIM Share Price Today - INDO-MIM LIMITED Stock Price Live NSE/BSE - univest.in</t>
+          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>IndoMIM Share Price Today - Indo-MIM Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+          <t>250% Return In 3 Years: Iron &amp; Steel Stock Hits Fresh 52-Week High After Key Business Update - goodreturns.in</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Free float of INDO-MIM Limited – NSE:INDOMIM - TradingView</t>
+          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3239,68 +3171,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ORCHPHARMA.NS</t>
+          <t>KSHITIJPOL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Orchid Pharma Limited</t>
+          <t>Kshitij Polyline Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1102.599975585938</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1116</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1061.099975585938</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1063.900024414062</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1096.150024414062</v>
+        <v>5.059999942779541</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1063.900024414062</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>44771</v>
+        <v>497047</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-2.94</v>
+        <v>-4.94</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Orchid Pharma (NSE: ORCHPHARMA) Property Acquisition and Merger Share Listing Update - kalkine.co.in</t>
+          <t>Kshitij Polyline Slips Nearly 5% to ₹3.44 — Support at ₹3.27 Becomes Key - Adaptive Moving Average - siam.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Orchid Pharma: Equity Shares Listed Post Amalgamation Approval - InvestyWise</t>
+          <t>Kshitij Polyline Uses Rights Issue Proceeds to Cut Debt - TipRanks</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Orchid Pharma Surges 6% to ₹1,024.85, Breaks Past Key Resistance Zone - Volume Rate Change - siam.in</t>
+          <t>Kshitij Polyline KSHITIJPOL Rights Issue Allotment Details - kalkine.co.in</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Orchid Pharma Share Price Today: Price Rise and Fundamentals - univest.in</t>
+          <t>Kshitij Polyline KSHITIJPOL Rights Issue Corrigendum August 2026 - kalkine.co.in</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Orchid Pharma announces listing of 4,45,86,052 equity shares following amalgamation - Business Upturn</t>
+          <t>Kshitij Polyline KSHITIJPOL AGM E-Voting Date Corrected - kalkine.co.in</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:31:05 IST</t>
+          <t>2026-09-25 21:00:14 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3308,61 +3240,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MANIPALHOS.NS</t>
+          <t>ARVEE.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises Limited</t>
+          <t>Arvee Laboratories (India) Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>739</v>
+        <v>225.5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>746.5499877929688</v>
+        <v>226</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>719.0999755859375</v>
+        <v>210.1999969482422</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>720.7000122070312</v>
+        <v>213.1900024414062</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>742.5</v>
+        <v>224.25</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>720.7000122070312</v>
+        <v>213.1900024414062</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>296848</v>
+        <v>9323</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-2.94</v>
+        <v>-4.93</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Manipal Health Enterprises Ltd Share Price Today,, MANIPALHOS Share Price NSE, BSE - Business Today</t>
+          <t>Arvee Laboratories (ARVEE.NS) Rises 3.13% to ₹243.47, Positioned Midway Between Key Support and Resistance - Stop Hunt - siam.in</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MANIPAL HEALTH ENTERPRI L (MANIPALHOS) Share Price Falls 2.29% Today - univest.in</t>
+          <t>Arvee Laboratories India: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>MANIPAL HEALTH ENTERPRI L Share Price Rise and Valuation - univest.in</t>
+          <t>Arvee Laboratories India: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>MANIPALHOS Share Price: Fresh 52-Week High and Valuation - univest.in</t>
+          <t>Indian Stocks Open Higher Despite Rise in Crude Oil Prices - Investing.com India</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-09-10 — cnbctv:fa79b73ec094b:0 - TradingView</t>
+          <t>Arvee Laboratories Stock: Daily Chart Analysis - kalkine.co.in</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ADSL.NS</t>
+          <t>RETAIL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Allied Digital Services Limited</t>
+          <t>JHS Svendgaard Retail Ventures Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>97.98000335693359</v>
+        <v>23</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>115.5199966430664</v>
+        <v>24.06999969482422</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>97</v>
+        <v>22.1299991607666</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>115.5199966430664</v>
+        <v>24.06999969482422</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>96.26999664306641</v>
+        <v>20.05999946594238</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>115.5199966430664</v>
+        <v>24.06999969482422</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2244051</v>
+        <v>125255</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>20</v>
+        <v>19.99</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Allied Digital Services Share Price rises 14.29% to Rs 110 - Univest</t>
+          <t>SS Retail share price jumps 7% amid stock market fall | Do you own? - TradingView</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Allied Digital Services Share Price rises 14.29% to Rs 110 - Univest</t>
+          <t>SS Retail share price jumps 7% amid stock market fall | Do you own? - TradingView</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ADSL Holdings Inc. (AMNNF) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+          <t>SS Retail share price jumps 7% amid stock market fall | Do you own? - Livemint</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Coya Therapeutics (COYA) Rises Modestly as Shares Hold Above $4.41 Support - Momentum Factor - siam.in</t>
+          <t>Patel Retail Opens 54th Store; Shares Fall 1.43% - HDFC Sky</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Stocks in news: Canara Bank, Vodafone Idea, Premier Energies and ACME Solar - The Economic Times</t>
+          <t>SS Retail Share Price: Stock debuts at 47%, gains 14% more after listing - India Infoline</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,60 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RETAIL.NS</t>
+          <t>LANDSMILL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>JHS Svendgaard Retail Ventures Limited</t>
+          <t>Landsmill Green Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17.97999954223633</v>
+        <v>0.7200000286102295</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>20.05999946594238</v>
+        <v>0.7400000095367432</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>16.36000061035156</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>20.05999946594238</v>
+        <v>0.7400000095367432</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16.71999931335449</v>
+        <v>0.6200000047683716</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>20.05999946594238</v>
+        <v>0.7400000095367432</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>111518</v>
+        <v>15857667</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.98</v>
+        <v>19.35</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>SS Retail Share Price: Stock debuts at 47%, gains 14% more after listing - India Infoline</t>
+          <t>EXCEL REALTY N INFRA Share Price - Live NSE: LANDSMILL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>What Instacart Stock's Retail Expansion Means For Shareholders - simplywall.st</t>
+          <t>EXCEL REALTY N INFRA Share Price - Live NSE: LANDSMILL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>SS Retail shares list at 51% premium over IPO price on BSE; should you buy, sell or hold? - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Spencer's Retail Share: Bull Case vs Bear Case for 2026 - Univest</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>SS Retail shares make strong D-Street debut, list at 51% premium over IPO price - The Economic Times</t>
-        </is>
-      </c>
+          <t>Landsmill Green board approves promoter reclassification to public category - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,56 +683,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>LANDSMILL.NS</t>
+          <t>REPRO.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green Limited</t>
+          <t>Repro India Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.5299999713897705</v>
+        <v>301</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6200000047683716</v>
+        <v>345.8999938964844</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.5199999809265137</v>
+        <v>301</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6200000047683716</v>
+        <v>338.2999877929688</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.5199999809265137</v>
+        <v>288.25</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.6200000047683716</v>
+        <v>338.2999877929688</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>6935351</v>
+        <v>341458</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>19.23</v>
+        <v>17.36</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green board approves promoter reclassification to public category - scanx.trade</t>
+          <t>REPRO Share Price Near Low: Technical and Fundamental View - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green board approves promoter reclassification to public category - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Repro India Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Repro India Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>REPRO.NS Jun 2026 Earnings: EPS of ₹90.03 Drives 7.35% Stock Advance - Margin Guidance - siam.in</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Repro India Share: Bull Case vs Bear Case for 2026 - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -748,68 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGOLD.NS</t>
+          <t>IWP.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Limited</t>
+          <t>The Indian Wood Products Company Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>289.7999877929688</v>
+        <v>34.31000137329102</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>333.0899963378906</v>
+        <v>40.47999954223633</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>288.989990234375</v>
+        <v>34.31000137329102</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>325.6799926757812</v>
+        <v>39.7599983215332</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>283.6199951171875</v>
+        <v>34.97000122070312</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>325.6799926757812</v>
+        <v>39.7599983215332</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36403975</v>
+        <v>450122</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14.83</v>
+        <v>13.7</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Technical Reactions to IWP Trends in Macro Strategies - news.stocktradersdaily.com</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>IWP: Limping Into Q4, A Sell For Now (NYSEARCA:IWP) - Seeking Alpha</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International (SHANTIGOLD) Share Price Falls 8.03% Today - Univest</t>
+          <t>IWP Capital urges FedEx to report on risks of s... - Pluang</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International SHANTIGOLD Q1 FY27 Results Clarification - kalkine.co.in</t>
+          <t>IWP: Quality Issues, Unconvincing Returns, A Hold At Best (NYSEARCA:IWP) - Seeking Alpha</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Share Price rises 9.58% today - Univest</t>
+          <t>IWP Capital to Vote "FOR" FedEx Proposal 6 on Abortion-Drug Distribution Risk - Finansavisen</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -817,68 +821,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>BPLPHARMA.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>Bharat Parenterals Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>55.97999954223633</v>
+        <v>2093</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>66.66000366210938</v>
+        <v>2277.60009765625</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>54.70999908447266</v>
+        <v>2050</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>64.02999877929688</v>
+        <v>2116.89990234375</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>55.77000045776367</v>
+        <v>1898</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>64.02999877929688</v>
+        <v>2116.89990234375</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>13696602</v>
+        <v>120603</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>14.81</v>
+        <v>11.53</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price Today: 8.51% Rise, Valuation View - Univest</t>
+          <t>Bharat Parenterals shares rally 25% in three sessions; Here is why stock is rising - Upstox</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR Share Price Today: 8.51% Rise, Valuation View - Univest</t>
+          <t>Bharat Parenterals shares rally 25% in three sessions; Here is why stock is rising - Upstox</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - kalkine.co.in</t>
+          <t>Bharat Parenterals Board Meeting to Review Preferential Issue Proposal - Kalkine India</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Ugar Sugar Works Plant Operational Despite KSPCB Order; Shares Rise - hdfcsky.com</t>
-        </is>
-      </c>
+          <t>Bharat Parenterals schedules board meet for Sept 29 to consider preferential issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,56 +886,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TGVSL.NS</t>
+          <t>PRIMO.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>TGV Sraac Limited</t>
+          <t>Primo Chemicals Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>110.1100006103516</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>127.7399978637695</v>
+        <v>29.79999923706055</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>110.1100006103516</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>124.7799987792969</v>
+        <v>28.18000030517578</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>109.3099975585938</v>
+        <v>25.28000068664551</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>124.7799987792969</v>
+        <v>28.18000030517578</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>10384035</v>
+        <v>3649335</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>14.15</v>
+        <v>11.47</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>TGV SRAAC Ltd (TGVSL): Chlor-Alkali Recovery and Outlook - kalkine.co.in</t>
+          <t>Primo Chemicals Share Price: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>TGV SRAAC Ltd (TGVSL): Chlor-Alkali Recovery and Outlook - kalkine.co.in</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Primo Chemicals Share Price: Price Action and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Primo Brands (PRMB) Stock May Be Undervalued On Earnings Power - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Primo Chemicals approves merger with subsidiary Flow Tech - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>how InvestingPro’s Primo Chemicals overvaluation call saved investors 51% By Investing.com - Investing.com India</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -943,68 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR.NS</t>
+          <t>DAMCAPITAL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Limited</t>
+          <t>Dam Capital Advisors Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>261.7999877929688</v>
+        <v>139.8999938964844</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>304.8999938964844</v>
+        <v>155</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>260</v>
+        <v>137.7100067138672</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>293.1499938964844</v>
+        <v>152.2899932861328</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>260</v>
+        <v>138.1799926757812</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>293.1499938964844</v>
+        <v>152.2899932861328</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2804540</v>
+        <v>11407500</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>12.75</v>
+        <v>10.21</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price Fall: Price Action Review - Univest</t>
+          <t>DAM Capital Advisors Trading Window Closure Q2 FY27 - Kalkine India</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills (NSE:UTTAMSUGAR) Names Harish Kumar Dhingra as CFO - kalkine.co.in</t>
+          <t>DAM Capital Advisors Trading Window Closure Q2 FY27 - Kalkine India</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Limited Announces Appointment of Harish Kumar Dhingra to Chief Financial Officer, Effective September 18, 2026 - marketscreener.com</t>
+          <t>Dam Capital Advisors Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills UTTAMSUGAR Regulation 30 KMP Authorisation - kalkine.co.in</t>
+          <t>DAM Capital Advisors Ltd Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills (NSE: UTTAMSUGAR) — Integrated Sugar Business Explained - kalkine.co.in</t>
+          <t>PVR Inox board approves share buyback worth up to ₹300 crore; all you need to know - Dailyhunt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1012,68 +1024,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>KMSUGAR.NS</t>
+          <t>ARVEE.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>K.M.Sugar Mills Limited</t>
+          <t>Arvee Laboratories (India) Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>29.20000076293945</v>
+        <v>213.1900024414062</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>33.02000045776367</v>
+        <v>234.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>29.20000076293945</v>
+        <v>213.1900024414062</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>32.45999908447266</v>
+        <v>234.5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>29.05999946594238</v>
+        <v>213.1900024414062</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32.45999908447266</v>
+        <v>234.5</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1179803</v>
+        <v>31561</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Share Price Today: Rs 31.70 and 8.75% Rise - Univest</t>
+          <t>Arvee Laboratories (ARVEE.NS) Rises 3.13% to ₹243.47, Positioned Midway Between Key Support and Resistance - Stop Hunt - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Share Price Today: Rs 31.70 and 8.75% Rise - Univest</t>
+          <t>Arvee Laboratories India: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>KMSUGAR Demerger Effective Date and Record Date October 2026 - kalkine.co.in</t>
+          <t>Arvee Laboratories India: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>KM Sugar Mills KMSUGAR promoter share transmission SAST 2026 - kalkine.co.in</t>
+          <t>Arvee Laboratories (India) Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>K.M. Sugar Mills Share Price Today: Price Action Review - Univest</t>
+          <t>Indian Stocks Open Higher Despite Rise in Crude Oil Prices - Investing.com India</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1081,68 +1093,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH.NS</t>
+          <t>HINDCON.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Limited</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>40.72000122070312</v>
+        <v>30.29000091552734</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45.61999893188477</v>
+        <v>30.36000061035156</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40.70000076293945</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45.0099983215332</v>
+        <v>30.36000061035156</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>40.7400016784668</v>
+        <v>27.60000038146973</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>45.0099983215332</v>
+        <v>30.36000061035156</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>9510474</v>
+        <v>155579</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10.48</v>
+        <v>10</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar DWARKESH Trading Window Closure Oct 2026 - kalkine.co.in</t>
+          <t>Hindcon Chemicals Share Price Today with Valuation View - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar DWARKESH Trading Window Closure Oct 2026 - kalkine.co.in</t>
+          <t>Hindcon Chemicals vs Nifty 50: Share Price Performance Compared - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar FY26 Net Profit Rises 32% to ₹3,083.80 Lakh - scanx.trade</t>
+          <t>Hindcon Chemicals (HINDCON.NS) Slips 1.45% to ₹23.74, Holds Midpoint of Trading Range - Rounding Bottom - siam.in</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Warren Buffett-Style Cash Flow Stocks Could Face Heavy Downside in OpenAI Era, Warns Dwarkesh Patel - Yahoo Finance</t>
+          <t>Hindcon Chemicals Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>OpenAI-Hugging Face controversy deepens as experts debate Dwarkesh Patel's 'AI civilisation' claims - Moneycontrol.com</t>
+          <t>Hindcon Chemicals Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1150,68 +1162,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>BLUECLOUDS.NS</t>
+          <t>CUBEXTUB.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Blue Cloud Softech Solutions Limited</t>
+          <t>Cubex Tubings Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>20.85000038146973</v>
+        <v>154.8000030517578</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>23.56999969482422</v>
+        <v>167.4600067138672</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20.67000007629395</v>
+        <v>151</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>22.15999984741211</v>
+        <v>167.4600067138672</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.05999946594238</v>
+        <v>152.2400054931641</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22.15999984741211</v>
+        <v>167.4600067138672</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>69595946</v>
+        <v>1061016</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10.47</v>
+        <v>10</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>BLUECLOUDS wins AI infra deal of USD 15.5M from IBM Cloud Inc. - Business Standard</t>
+          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>BLUECLOUDS wins AI infra deal of USD 15.5M from IBM Cloud Inc. - Business Standard</t>
+          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Total common shares outstanding of Blue Cloud Softech Solutions Ltd. – NSE:BLUECLOUDS - TradingView</t>
+          <t>Cubex Tubings Share Price today: price action and value - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Blueclouds launches GMB Life - a preventive screening and wellness app - Business Standard</t>
+          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>ConnectM (CNTM) pursues $5M deal backed by most of its assets - Stock Titan</t>
+          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1219,68 +1231,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SBC.NS</t>
+          <t>AASTHA.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>SBC Exports Limited</t>
+          <t>Aastha Spintex Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>48.13999938964844</v>
+        <v>37.02999877929688</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>53.7400016784668</v>
+        <v>39.95000076293945</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>48.04999923706055</v>
+        <v>37.02999877929688</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>53.02000045776367</v>
+        <v>39.68999862670898</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>48.0099983215332</v>
+        <v>36.36000061035156</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>53.02000045776367</v>
+        <v>39.68999862670898</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>23812681</v>
+        <v>1704531</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.44</v>
+        <v>9.16</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>In October, SBC Medical plans online and New York meetings with investors. - Stock Titan</t>
+          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18 - LinkedIn</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>In October, SBC Medical plans online and New York meetings with investors. - Stock Titan</t>
+          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18 - LinkedIn</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>SBC Exports (SBC.NS) Gains 1.83% to ₹42.81, Holds Above Support at ₹40.67 - Continuation Pattern Picks - siam.in</t>
+          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>SBC Exports dispatches FY26 annual report web link to shareholders - scanx.trade</t>
+          <t>Aastha Spintex Secures ₹25 Crore Fabric Orders; Shares Fall 9.99% - HDFC Sky</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>SBC Options Chain — NASDAQ:SBC - TradingView</t>
+          <t>1 Free Shares On 1, 10 Shares On 10, 100 Shares On 100; Why Textile Stock Crashed 50% On 1:1 Bonus Record Date - Goodreturns</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1288,68 +1300,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB.NS</t>
+          <t>SUNFLAG.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Limited</t>
+          <t>Sunflag Iron And Steel Company Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>147.8999938964844</v>
+        <v>415.7999877929688</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>152.2400054931641</v>
+        <v>451.7000122070312</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>130.0500030517578</v>
+        <v>412.3500061035156</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>152.2400054931641</v>
+        <v>445.6000061035156</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>138.3999938964844</v>
+        <v>410.6499938964844</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>152.2400054931641</v>
+        <v>445.6000061035156</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2579589</v>
+        <v>4042085</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10</v>
+        <v>8.51</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Share Price today: price action and value - Univest</t>
+          <t>Sunflag Iron and Steel Share Price - Upstox</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
+          <t>Sunflag Iron &amp; Steel approves ₹1 per share dividend for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
+          <t>Sunflag Iron And Steel Company Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - kalkine.co.in</t>
+          <t>Sunflag Iron and Steel (NSE:SUNFLAG) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
+          <t>Sunflag Iron &amp; Steel: Anand Kapre exits independent director role - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1357,68 +1369,56 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SHOPERSTOP.NS</t>
+          <t>INDOBORAX.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Shoppers Stop Limited</t>
+          <t>Indo Borax &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>382.5</v>
+        <v>441.0499877929688</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>439.7999877929688</v>
+        <v>508.7000122070312</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>382.5</v>
+        <v>435</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>423.5499877929688</v>
+        <v>486.6499938964844</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>385.0499877929688</v>
+        <v>449.9500122070312</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>423.5499877929688</v>
+        <v>486.6499938964844</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3588097</v>
+        <v>6660637</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>10</v>
+        <v>8.16</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Shoppers Stop NSE:SHOPERSTOP Trading Window Closure Oct 2026 - kalkine.co.in</t>
+          <t>Indo Borax &amp; Chemicals (INDOBORAX.NS) Holds Firm at ₹470.2 as Traders Eye ₹493.71 Resistance - Growth ETF - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Shoppers Stop Share Price Rises 11.83% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Shoppers Stop Share Price Rises 11.83% Today - Univest</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Shoppers Stop Reports FY26 Net Loss, Approves Rs 40 Crore Beauty Subsidiary Investment - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Volume Gainers, September 15, 2026 at 12:00 PM IST - hdfcsky.com</t>
-        </is>
-      </c>
+          <t>Indo Borax &amp; Chemicals (INDOBORAX.NS) Holds Firm at ₹470.2 as Traders Eye ₹493.71 Resistance - Growth ETF - siam.in</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,56 +1426,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>FCSSOFT.NS</t>
+          <t>PRITIKAUTO.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>FCS Software Solutions Limited</t>
+          <t>Pritika Auto Industries Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.340000033378601</v>
+        <v>18</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.460000038146973</v>
+        <v>18.97999954223633</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1.340000033378601</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.460000038146973</v>
+        <v>18.48999977111816</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.330000042915344</v>
+        <v>17.15999984741211</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.460000038146973</v>
+        <v>18.48999977111816</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3497158</v>
+        <v>749440</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>9.77</v>
+        <v>7.75</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>FCS Softwares Share Price - Upstox</t>
+          <t>Earnings Working Against Pritika Auto Industries Limited's (NSE:PRITIKAUTO) Share Price - simplywall.st</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>FCS Softwares Share Price - Upstox</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Pritika Auto Industries PRITIKAUTO Board Meeting August 2026 - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Pritika Auto Industries Limited Files Q4FY26 Demat Certificate and Annual SEBI Disclosure - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>PRITIKAUTO Stock Price and Chart — NSE:PRITIKAUTO - TradingView</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Pritika Auto Industries demerger: NCLT gives approval for value unlocking. Details here - Livemint</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1483,68 +1495,60 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DANGEE.NS</t>
+          <t>THAKDEV.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>Thakkers Developers Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3.160000085830688</v>
+        <v>134.9900054931641</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3.259999990463257</v>
+        <v>145</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2.980000019073486</v>
+        <v>134.9900054931641</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3.259999990463257</v>
+        <v>145</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2.970000028610229</v>
+        <v>134.9900054931641</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.259999990463257</v>
+        <v>145</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>909887</v>
+        <v>1310</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.76</v>
+        <v>7.42</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Dangee Dums Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
+          <t>Thakkers Developers Declines 5.31% to ₹142; Support at ₹134.9 in Focus - Aggressive Growth Picks - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Volume Gainers, September 24, 2026 at 3:30 PM IST: Kaveri Seed Leads Volume Jump - hdfcsky.com</t>
+          <t>Thakkers Developers Share Price Today: 9.97% Decline - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Volume Gainers, September 24, 2026 at 12:00 PM IST: Dangee Dums Leads Volume Jump - hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>The Dangee Dums Bull Case - Univest</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Dangee Dums Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
+          <t>Thakkers Developers Share Price Today: 9.97% Decline - Univest</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1552,68 +1556,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE.NS</t>
+          <t>HAVISHA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited</t>
+          <t>Sri Havisha Hospitality and Infrastructure Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>502.8500061035156</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>559.7000122070312</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>492.6000061035156</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>547.5</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>500.3999938964844</v>
+        <v>1.379999995231628</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>547.5</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1949531</v>
+        <v>46485</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.41</v>
+        <v>7.25</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE Share Price rises 12.58%; fundamentals, peers - Univest</t>
+          <t>Sri Havisha Hospitality Edges Higher: HAVISHA.NS Holds Above ₹1.40, Resistance Eyed at ₹1.48 - Opening Range Breakout - siam.in</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK Share Price Today: Rs 543 after rise - Univest</t>
+          <t>Compare with SHRI SHAKTI - Equitymaster</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Holds Above Support Near ₹440 Despite Mild Dip - Momentum Surge Alerts - siam.in</t>
+          <t>Sri Havisha Hospitality and Infrastructure Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek (NSE:QUADFUTURE): Why Has the Trading Window Been Closed? - kalkine.co.in</t>
+          <t>Sri Havisha Hospitality sets Sep 26 AGM for sweat equity, RPT approvals - scanx.trade</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>QUADRANT FUTURE TEK LTD 52 Week High Streak: Consecutive High Analysis - Univest</t>
+          <t>Sri Havisha Hospitality and Infrastructure Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1621,68 +1625,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>STARTECK.NS</t>
+          <t>ALUFLUOR.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Starteck Finance Limited</t>
+          <t>Alufluoride Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>242.0500030517578</v>
+        <v>565.4000244140625</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>262.7000122070312</v>
+        <v>644.4000244140625</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>242.0500030517578</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>262.5</v>
+        <v>605.4000244140625</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>240.3999938964844</v>
+        <v>565.4000244140625</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>262.5</v>
+        <v>605.4000244140625</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>211</v>
+        <v>59177</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9.19</v>
+        <v>7.07</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Starteck Finance Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Alufluoride Share Price Rises 9.89% to Rs 540: Analysis - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Starteck Finance Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Alufluoride Q1 Results: Net profit drops 9.6% YoY to ₹287 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Starteck Finance approves ₹0.25 dividend, fund raising at 41st AGM - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Starteck Finance Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Starteck Finance Ltd (STARTECK): An Earnings Quality Question - kalkine.co.in</t>
-        </is>
-      </c>
+          <t>Alufluoride Q1 Results: Net profit drops 9.6% YoY to ₹287 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1690,68 +1686,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>HERANBA.NS</t>
+          <t>SUMEDHA.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Heranba Industries Limited</t>
+          <t>Sumedha Fiscal Services Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>173.9499969482422</v>
+        <v>42.75</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>198.8999938964844</v>
+        <v>45.9900016784668</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>171.0099945068359</v>
+        <v>40.09999847412109</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>187.6000061035156</v>
+        <v>45.93999862670898</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>172.2700042724609</v>
+        <v>42.95000076293945</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>187.6000061035156</v>
+        <v>45.93999862670898</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3333259</v>
+        <v>3675</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8.9</v>
+        <v>6.96</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Heranba Industries Share Price Today With Sector Context - Univest</t>
+          <t>US Infotech buys 250 Sumedha Fiscal shares, holds 13.42% - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Heranba Industries Share Price Today With Sector Context - Univest</t>
+          <t>Compare with SUMEDHA FISC - Equitymaster</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Heranba promoters confirm no share encumbrance in FY26 - scanx.trade</t>
+          <t>Sumedha Fiscal promoter group buys 45,000 shares in two days - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Heranba Industries Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Sumedha Fiscal Services Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Heranba Industries Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Sumedha Fiscal promoter group buys 10,530 shares voluntarily under SAST - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1759,56 +1755,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DBOL.NS</t>
+          <t>EMKAY.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Bio Organics Limited</t>
+          <t>Emkay Global Financial Services Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>112.5100021362305</v>
+        <v>273.2000122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>123</v>
+        <v>292.8999938964844</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>112.5100021362305</v>
+        <v>273.2000122070312</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>122.25</v>
+        <v>287.3999938964844</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>113.1999969482422</v>
+        <v>270.3500061035156</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>122.25</v>
+        <v>287.3999938964844</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>352605</v>
+        <v>243425</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.99</v>
+        <v>6.31</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Bio Organics shareholders approve dividend, CEO redesignation at AGM - scanx.trade</t>
+          <t>Is Emkay Global Financial Services the Best Stock in Its Sector? A Look at the Numbers - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Bio Organics shareholders approve dividend, CEO redesignation at AGM - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Gas PSU stock to buy: After 26% returns in 6 months, Emkay Global sees further 16% upside | Target, stop-loss, rationale - Livemint</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Buy National Stock Exchange; target of Rs 2050: Emkay Global Financial - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Gas PSU stock to buy: After 26% returns in 6 months, Emkay Global sees further 16% upside | Target, stop-loss, rationale - Livemint</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>GAIL shares: Emkay upgrades stock, sees 16% upside; check target price - Business Today</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1816,61 +1824,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>FCL.NS</t>
+          <t>3BBLACKBIO.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Fineotex Chemical Limited</t>
+          <t>3B Blackbio Dx Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>56.5</v>
+        <v>1502.900024414062</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>61.04999923706055</v>
+        <v>1587.599975585938</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>55.75</v>
+        <v>1475.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.47999954223633</v>
+        <v>1548</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>56.06999969482422</v>
+        <v>1456.199951171875</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>60.47999954223633</v>
+        <v>1548</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>47011140</v>
+        <v>51064</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7.87</v>
+        <v>6.3</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>FCL-X Fire &amp; Safety Inc. (FCLX.V) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+          <t>3B (3BBLACKBIO.NS) Results Check: The Latest Report Adds New Financial Reference Points in the Current Update; Market Response: Shares Finish 1.36% Lower for the Current Session - Annual Earnings Summary - siam.in</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>FCL-X Fire &amp; Safety Inc. (FCLX.V) Stock Forum &amp; Discussion - Yahoo Finance - Yahoo! Finance Canada</t>
+          <t>3B (3BBLACKBIO.NS) Results Check: The Latest Report Adds New Financial Reference Points in the Current Update; Market Response: Shares Finish 1.36% Lower for the Current Session - Annual Earnings Summary - siam.in</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Fineotex Chemical Ltd. (FCL) Share Price hits fresh 52-week high as FCL trades at Rs 60.98 - Univest</t>
+          <t>3BBLACKBIO Share Price Today - 3B Blackbio DX Stock Analysis - Equitypandit</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>FINEOS Corporation (ASX:FCL): What Investors Need to Know About This Insurance Software Stock - kalkine.com.au</t>
+          <t>3B BlackBio Dx Limited Promoters Declare No Share Encumbrance for FY2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>FCL-X Fire &amp; Safety Inc. (FCLX.V) Stock Forum &amp; Discussion - Yahoo Finance - Yahoo! Finance Canada</t>
+          <t>3B Blackbio Dx Holds Steady Near Key Support Levels Amid Mild Decline - Counter Trend Trade - siam.in</t>
         </is>
       </c>
     </row>
@@ -1891,14 +1899,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -1997,7 +2005,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2005,68 +2013,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MEDICO.NS</t>
+          <t>PAISALO.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Limited</t>
+          <t>Paisalo Digital Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.15000152587891</v>
+        <v>87.01000213623047</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>33.15999984741211</v>
+        <v>88.70999908447266</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>26</v>
+        <v>73.41999816894531</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26</v>
+        <v>74.84999847412109</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>32.5</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>26</v>
+        <v>74.84999847412109</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3536256</v>
+        <v>28362633</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-20</v>
+        <v>-15.92</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Paisalo Digital to host virtual investor conference on September 29, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Paisalo Digital to host virtual investor conference on September 29, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Paisalo Digital (PAISALO.NS) Holds Near ₹84.59 as Stock Consolidates Between ₹80.36 and ₹88.82 - Scalping Stock Signals - siam.in</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Ltd is Rated Sell - MarketsMojo</t>
+          <t>Paisalo Digital: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Prism Medico and Pharmacy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Paisalo Digital Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2074,68 +2082,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>OLAELEC.NS</t>
+          <t>MEDICO.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited</t>
+          <t>Medico Remedies Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>42.5</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>42.5</v>
+        <v>26.20999908447266</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>38.0099983215332</v>
+        <v>20.88999938964844</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>38.47999954223633</v>
+        <v>22.35000038146973</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>42.52000045776367</v>
+        <v>26</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>38.47999954223633</v>
+        <v>22.35000038146973</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>194452956</v>
+        <v>3070528</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.5</v>
+        <v>-14.04</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric (NSE: OLAELEC) Shares Fall 9%: Brokerage Views and Key Risks - kalkine.co.in</t>
+          <t>Medico Remedies Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric (NSE: OLAELEC) Shares Fall 9%: Brokerage Views and Key Risks - kalkine.co.in</t>
+          <t>Prism Medico sets AGM for Sept 19; seeks approval for ₹23 cr Infuze Well stake - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Share Price - Live NSE: OLAELEC Stock Price &amp; Chart - Upstox</t>
+          <t>Medico Remedies Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Ltd (NSE: OLAELEC) Declines 7.86% as Stock Draws Market Attention - kalkine.co.in</t>
+          <t>Prism Medico and Pharmacy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Plans On-Site Analyst Meet at Future Factory and Giga Factory - The Globe and Mail</t>
+          <t>Prism Medico AGM resolutions pass with 99.99% shareholder approval - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2143,68 +2151,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SGL.NS</t>
+          <t>SAICAPI.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>STL Global Limited</t>
+          <t>Sai Capital Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10.18000030517578</v>
+        <v>156.9499969482422</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10.18000030517578</v>
+        <v>156.9499969482422</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8.899999618530273</v>
+        <v>136</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.029999732971191</v>
+        <v>136</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9.810000419616699</v>
+        <v>156.9900054931641</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.029999732971191</v>
+        <v>136</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>64142</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.95</v>
+        <v>-13.37</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>STL Global SGL Trading Window Closure October 2026 - kalkine.co.in</t>
+          <t>Sai Capital Limited Submits Annual Secretarial Compliance Report for Financial Year Ended March 31, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>STL Global SGL Trading Window Closure October 2026 - kalkine.co.in</t>
+          <t>Sai Capital Ltd. (SAICAPI) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>SGL stock gains 9.68 percent as shares reach MYR 0.17 - AD HOC NEWS</t>
+          <t>Sai Capital Ltd. (SAICAPI) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>STL Global (SGL.NS) Rises 2.03% to ₹10.07; Key Resistance at ₹10.57 in Focus - Fade Trade - siam.in</t>
+          <t>Sai Capital consolidated net profit rises 16% to ₹1,255.69 Lacs in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>SGL Resources Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Sai Capital Ltd. (SAICAPI) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2212,60 +2220,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>KOTYARK.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Limited</t>
+          <t>Kotyark Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15.01000022888184</v>
+        <v>31.69000053405762</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>15.01000022888184</v>
+        <v>31.69000053405762</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.14000034332275</v>
+        <v>24.95999908447266</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>13.52000045776367</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14.60000038146973</v>
+        <v>31.20000076293945</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.52000045776367</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>7859410</v>
+        <v>1493708</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.4</v>
+        <v>-12.34</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Ltd (NSE: ATALREAL) Falls 5.48% as Stock Draws Market Attention - kalkine.co.in</t>
+          <t>Kotyark Industries allots 10.2 crore bonus shares in 10:1 ratio - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Ltd (NSE: ATALREAL) Falls 5.48% as Stock Draws Market Attention - kalkine.co.in</t>
+          <t>Kotyark Industries promoter reduces stake to 5.47% - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price Today: Price Fall and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Kotyark Industries promoter reduces stake to 5.47% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Kotyark Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Kotyark Industries Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2273,56 +2289,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RRECL.NS</t>
+          <t>EKI.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate Constructions Limited</t>
+          <t>EKI Energy Services Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>132.9499969482422</v>
+        <v>102.7900009155273</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>132.9499969482422</v>
+        <v>106</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>121.0299987792969</v>
+        <v>90.90000152587891</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>123.4000015258789</v>
+        <v>90.90000152587891</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>133.1199951171875</v>
+        <v>100.9899978637695</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>123.4000015258789</v>
+        <v>90.90000152587891</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>343</v>
+        <v>126639</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-7.3</v>
+        <v>-9.99</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
+          <t>EKI Energy Services Ltd (NSE: EKI) Gains 19.99% as Stock Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>RDB Real Estate schedules 8th AGM for September 28, 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>EKI Energy Services Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>EKI Energy Services Share Price rise with sector comparison - Univest</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>EKI Energy Services Ltd is Rated Strong Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>EKI Energy Services Share Price today: Rs 80 after rise - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2330,68 +2358,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>UNIDT.NS</t>
+          <t>ARMANFIN.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Limited</t>
+          <t>Arman Financial Services Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>257.7300109863281</v>
+        <v>1830.199951171875</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>260.8200073242188</v>
+        <v>1835.900024414062</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>238.2400054931641</v>
+        <v>1666.199951171875</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>241.7100067138672</v>
+        <v>1704</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>259.760009765625</v>
+        <v>1885.599975585938</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>241.7100067138672</v>
+        <v>1704</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>139219</v>
+        <v>195143</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.95</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Share Price: price rise and valuation - Univest</t>
+          <t>Arman Financial Services (ARMANFIN.NS) Slips 4.63% to ₹1918.1 as Stock Retreats From Resistance - Linear Regression - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: 12 Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+          <t>Arman Financial Services ARMANFIN Trading Window Closure - Kalkine India</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Limited Secures ₹5.04 Crore Order from ONGC for Integral Blade Stabilizer Supply - scanx.trade</t>
+          <t>Arman Financial Services ESOP Allotment September 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Limited (NSE:UNIDT) Goes Ex-Dividend Soon - simplywall.st</t>
+          <t>Arman Financial Services Schedules Virtual Analyst Meeting For September 29 At 1 PM - Sahi</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>United Drilling Tools Slips 1.62% to ₹230.36 — Support and Resistance Levels in Focus - Insider Sentiment - siam.in</t>
+          <t>ARMANFIN Q2 2026 Earnings: EPS at ₹53.57 as Revenue Slips 4.96% Year-on-Year - Margin Guidance - siam.in</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2399,56 +2427,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PBMPOLY.NS</t>
+          <t>ANTELOPUS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PBM Polytex Limited</t>
+          <t>Antelopus Selan Energy Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60.59999847412109</v>
+        <v>1260</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>67.47000122070312</v>
+        <v>1260</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>57.97000122070312</v>
+        <v>1143.849975585938</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.90999984741211</v>
+        <v>1145.900024414062</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>63.68000030517578</v>
+        <v>1261.699951171875</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>59.90999984741211</v>
+        <v>1145.900024414062</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>464</v>
+        <v>885207</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.92</v>
+        <v>-9.18</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>PBM Polytex Ltd. (NSE: PBMPOLY) Business Overview and Growth Factors - kalkine.co.in</t>
+          <t>ANTELOPUS SELAN ENERGY LTD Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>PBM Polytex Ltd. (NSE: PBMPOLY) Business Overview and Growth Factors - kalkine.co.in</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>ANTELOPUS SELAN ENERGY LTD Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy: Best Stock in Its Sector? Key Metrics - Univest</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>176% return in 2026 so far! Antelopus Selan Energy falls 3% after massive rally | What’s spooking investors? - Livemint</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2456,68 +2496,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PREMIERPOL.NS</t>
+          <t>NPST.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Premier Polyfilm Limited</t>
+          <t>Network People Services Technologies Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>102</v>
+        <v>1812.599975585938</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>102.6699981689453</v>
+        <v>1813</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>94.19999694824219</v>
+        <v>1640.300048828125</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>95.40000152587891</v>
+        <v>1648.300048828125</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>100.5100021362305</v>
+        <v>1796.300048828125</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>95.40000152587891</v>
+        <v>1648.300048828125</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>783831</v>
+        <v>83010</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.08</v>
+        <v>-8.24</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Premier Polyfilm (PREMIERPOL) Sheds Nearly 1% Amid Range-Bound Trading - Turnaround Stocks - siam.in</t>
+          <t>NETWORK PEOPLE SRV TECH L Share Price - Live NSE: NPST Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Premier Polyfilm insider Manvi Goenka sells 2.07 lakh shares - scanx.trade</t>
+          <t>NETWORK PEOPLE SRV TECH L Share Price - Live NSE: NPST Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Is It Smart To Buy Premier Polyfilm Ltd. (NSE:PREMIERPOL) Before It Goes Ex-Dividend? - simplywall.st</t>
+          <t>NPST Share Price rises 10.36%: price action and analysis - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Premier Polyfilm Share Price at Rs 97.14 near 52-week peak - Univest</t>
+          <t>NPST to host analyst meeting with SBI Mutual Funds on Sep 29, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Premier Polyfilm Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2525,56 +2565,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>NAGREEKCAP.NS</t>
+          <t>DELTACORP.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure Limited</t>
+          <t>Delta Corp Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30.75</v>
+        <v>80.79000091552734</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>31.35000038146973</v>
+        <v>81</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>27.17000007629395</v>
+        <v>71.27999877929688</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>28.05999946594238</v>
+        <v>71.51000213623047</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>29.54999923706055</v>
+        <v>76.83999633789062</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28.05999946594238</v>
+        <v>71.51000213623047</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>138167</v>
+        <v>10643698</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.04</v>
+        <v>-6.94</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure (NAGREEKCAP.NS) Slips 1.59% to ₹22.87, Hovers Near Support Zone - Fibonacci Entry Signals - siam.in</t>
+          <t>Delta Corp Share Price - Live NSE: DELTACORP Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Capital &amp; Infrastructure (NAGREEKCAP.NS) Slips 1.59% to ₹22.87, Hovers Near Support Zone - Fibonacci Entry Signals - siam.in</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Delta Corp Share Price - Live NSE: DELTACORP Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Delta Corp Limited (DELTACORP.NS) Consolidates Near ₹54 as Traders Eye Range Boundaries - Factor Timing - siam.in</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>DELTACORP Outlook for the Week (September 28, 2026 – October 02, 2026) - Equitypandit</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2582,56 +2634,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT.NS</t>
+          <t>JSFB.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>California Software Company Limited</t>
+          <t>Jana Small Finance Bank Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37.77999877929688</v>
+        <v>537</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>37.90000152587891</v>
+        <v>541.0999755859375</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>36.11999893188477</v>
+        <v>498</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>36.11999893188477</v>
+        <v>501.8999938964844</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>38.02000045776367</v>
+        <v>535.25</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>36.11999893188477</v>
+        <v>501.8999938964844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>227209</v>
+        <v>984248</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5</v>
+        <v>-6.23</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>Jana Small Finance Bank Limited (JSFB.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CALSOF Share Price Today - California Software Company Ltd. Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Jana Small Finance Bank Limited (JSFB.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>JANA SMALL FIN BANK LTD Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>JSFB Share Price today: price rise, valuation and peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Jana Small Finance Bank Trades Lower at ₹537.5; Support and Resistance Levels in Focus - Ichimoku Cloud - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2639,68 +2703,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PVP.NS</t>
+          <t>MERCANTILE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Limited</t>
+          <t>Mercantile Ventures Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>61.93999862670898</v>
+        <v>22.27000045776367</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>63.4900016784668</v>
+        <v>22.27000045776367</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>61.93999862670898</v>
+        <v>21.30999946594238</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.93999862670898</v>
+        <v>21.30999946594238</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>65.19999694824219</v>
+        <v>22.71999931335449</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>61.93999862670898</v>
+        <v>21.30999946594238</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2454235</v>
+        <v>4</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5</v>
+        <v>-6.21</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures slumps after CEO, COO resign - Business Standard</t>
+          <t>Surat Trade and Mercantile Lim Share Price - Live SURATRAML Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures slumps after CEO, COO resign - Business Standard</t>
+          <t>Vivid Mercantile holds 32nd AGM, appoints new statutory auditors - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures Ltd. Upper Circuit Streak: Day 2 Price and Data - Univest</t>
+          <t>Vivid Mercantile holds 32nd AGM, appoints new statutory auditors - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures accepts Dr. Ellen Jane Feehan resignation as CEO - scanx.trade</t>
+          <t>REG - Mercantile Inv Tst - Dividend Declaration - TradingView</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>PVP Ventures (PVP.NS) Slips 1.82% to ₹64.9 as Stock Drifts Toward ₹61.66 Support - Weekly Profile - siam.in</t>
+          <t>Mercantile Ventures Share Price gains in latest market move - Univest</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2708,68 +2772,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MOTISONS.NS</t>
+          <t>NILE.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers Limited</t>
+          <t>Nile Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18.88999938964844</v>
+        <v>1369.5</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>19.47999954223633</v>
+        <v>1369.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>17.6200008392334</v>
+        <v>1271.099975585938</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>17.85000038146973</v>
+        <v>1286</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.79000091552734</v>
+        <v>1369.699951171875</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17.85000038146973</v>
+        <v>1286</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>119044859</v>
+        <v>5837</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5</v>
+        <v>-6.11</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers to consider redemption of 50 lakh preference shares - scanx.trade</t>
+          <t>Nile Limited (NILE.NS) Trades at ₹1448.0, Down 0.62%: Range-Bound Action Keeps Support and Resistance in Focus - Passive Flow - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers (NSE:MOTISONS): What Does the Redemption of 50 Lakh Preference Shares Mean? - kalkine.co.in</t>
+          <t>LA County sees highest number of West Nile virus cases in nearly a decade - abcnews.com</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers (NSE:MOTISONS): What Does the Redemption of 50 Lakh Preference Shares Mean? - kalkine.co.in</t>
+          <t>Nile Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers sets Sept 28 AGM; appoints N.K. Aswani as auditor - scanx.trade</t>
+          <t>Nile Limited (NILE): Lead Recycling Compounder in Focus - Kalkine India</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers Share Price Today: Price Rise Review - Univest</t>
+          <t>Nile Limited (NILE.NS) Holds Ground Near ₹1,471.5; Key Support and Resistance Levels in Focus - Quality ETF - siam.in</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2777,68 +2841,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SIMPLXREA.NS</t>
+          <t>SENCO.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Simplex Realty Limited</t>
+          <t>Senco Gold Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>131.9900054931641</v>
+        <v>331.1000061035156</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>138.5700073242188</v>
+        <v>331.1000061035156</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>125.4000015258789</v>
+        <v>310.4500122070312</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>125.4000015258789</v>
+        <v>311.6499938964844</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>131.9900054931641</v>
+        <v>331.1000061035156</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>125.4000015258789</v>
+        <v>311.6499938964844</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>717</v>
+        <v>1671874</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.87</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>GUJTLRM Stock Price and Chart — BSE:GUJTLRM - TradingView</t>
+          <t>Senco Gold clarifies sustainable EBITDA margin at 7.5-7.8% post Q1FY27 surge - scanx.trade</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>GUJTLRM Stock Price and Chart — BSE:GUJTLRM - TradingView</t>
+          <t>Senco Gold clarifies sustainable EBITDA margin at 7.5-7.8% post Q1FY27 surge - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>SATCH Stock Price and Chart — BSE:SATCH - TradingView</t>
+          <t>Senco Gold Share Price - Upstox</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>ARTNIRMAN Stock Price and Chart — NSE:ARTNIRMAN - TradingView</t>
+          <t>Kalyan Jewellers vs Senco Gold vs Rajesh Exports: Comparison - Univest</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>PRAENG Stock Price and Chart — NSE:PRAENG - TradingView</t>
+          <t>Senco Gold (SENCO.NS) Eases 0.84% to ₹346.95 as Traders Watch ₹329.6 Support - Wave Extension - siam.in</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2846,60 +2910,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SEMAC.NS</t>
+          <t>NOCIL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Semac Construction Limited</t>
+          <t>NOCIL Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>268.3999938964844</v>
+        <v>188.0500030517578</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>268.3999938964844</v>
+        <v>188.0500030517578</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>255</v>
+        <v>175.3600006103516</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>255</v>
+        <v>177.3999938964844</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>268.3999938964844</v>
+        <v>188.4100036621094</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>255</v>
+        <v>177.3999938964844</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1613</v>
+        <v>1062860</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.84</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Semac Construction shares FY26 annual report web link ahead of AGM - scanx.trade</t>
+          <t>Nocil Share Price - Upstox</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Semac Construction to hold 49th AGM on September 25 via video conference - scanx.trade</t>
+          <t>Nocil Share Price - Upstox</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Semac Construction to hold 49th AGM on September 25 via video conference - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>NOCIL Stock Signals to Watch This Week - Univest</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Nocil Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Nocil Share Price Falls as Chemical Stock Stays in Focus - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2907,68 +2979,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX.NS</t>
+          <t>MANAPPURAM.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Limited</t>
+          <t>Manappuram Finance Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>55.29999923706055</v>
+        <v>328</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>55.29999923706055</v>
+        <v>330.6499938964844</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>51.20999908447266</v>
+        <v>312.1499938964844</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.20999908447266</v>
+        <v>315.1499938964844</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>53.90000152587891</v>
+        <v>334</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>51.20999908447266</v>
+        <v>315.1499938964844</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>26962</v>
+        <v>6694363</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.64</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Stock to buy today: Manappuram Finance (₹334) - BusinessLine</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance allots ₹60 crore NCDs at 10.75% coupon - scanx.trade</t>
+          <t>Stock to buy today: Manappuram Finance (₹334) - BusinessLine</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd. Stock News - Value Research</t>
+          <t>Manappuram Finance Share Price today: price rise, valuation - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Gold Duty Hike Triggers Rally In Gold Loan Stocks: Manappuram Finance &amp; Muthoot Finance Shares Surge 8% - Goodreturns</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance FY26 net profit rises 7.4% to ₹1.34 crore - scanx.trade</t>
+          <t>Manappuram Finance Open Offer Launched for 26% Stake Acquisition by BC Asia - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2976,68 +3048,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SRGHFL.NS</t>
+          <t>SIS.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Limited</t>
+          <t>SIS LIMITED</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>155.25</v>
+        <v>418.3999938964844</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>155.25</v>
+        <v>418.3999938964844</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>146.8000030517578</v>
+        <v>378.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>146.8000030517578</v>
+        <v>394.8500061035156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>154.5</v>
+        <v>418.3999938964844</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>146.8000030517578</v>
+        <v>394.8500061035156</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>15491</v>
+        <v>1589711</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.98</v>
+        <v>-5.63</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>SRGHFL Share Price Near 52-Week Low: Price Action Update - Univest</t>
+          <t>Savaria Corporation (SIS.TO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance SRGHFL Trading Window Closure Q2 FY27 - kalkine.co.in</t>
+          <t>Savaria Corporation (SIS.TO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Share Price Fall: Stock Analysis - Univest</t>
+          <t>SIS buys back 25,000 shares at avg ₹422.55 on Sept 25 - scanx.trade</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance SRGHFL Trading Window Closure Q2 FY27 - kalkine.co.in</t>
+          <t>SIS Limited (SIS.NS) Steadies Near ₹416 as Stock Consolidates Below Key Resistance - Fundamental Weighted - siam.in</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
+          <t>SIS buys additional 1.51% stake in Updater Services; Taurus MF sells over 1% stake in Advit Jewels - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3045,56 +3117,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VISACHROME.NS</t>
+          <t>SHANTIGOLD.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>VISA Chrome Limited</t>
+          <t>Shanti Gold International Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>35.5</v>
+        <v>315</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>37.95000076293945</v>
+        <v>316.1900024414062</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>34.52999877929688</v>
+        <v>302.4100036621094</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>34.54000091552734</v>
+        <v>307.4200134277344</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.34000015258789</v>
+        <v>325.6799926757812</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>34.54000091552734</v>
+        <v>307.4200134277344</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>20791</v>
+        <v>6531722</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.95</v>
+        <v>-5.61</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>ACRE revises Visa Chrome stake sale to 67.6 lakh shares - scanx.trade</t>
+          <t>Shanti Gold International (SHANTIGOLD.NS) Climbs 3.28% to ₹250.4, Presses Toward ₹263 Resistance - Double Bottom - siam.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>ACRE revises Visa Chrome stake sale to 67.6 lakh shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Shanti Gold International approves rights issue up to Rs 100 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Share Price rises 9.58% today - Univest</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Shanti Gold International approves rights issue up to Rs 100 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3102,68 +3186,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RHETAN.NS</t>
+          <t>KIRANVYPAR.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Limited</t>
+          <t>Kiran Vyapar Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15.17000007629395</v>
+        <v>195</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>15.17000007629395</v>
+        <v>195</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15.17000007629395</v>
+        <v>180.5500030517578</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>15.17000007629395</v>
+        <v>189.9900054931641</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15.96000003814697</v>
+        <v>201.1499938964844</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15.17000007629395</v>
+        <v>189.9900054931641</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>803050</v>
+        <v>9787</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.95</v>
+        <v>-5.55</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Ltd (NSE: RHETAN) Declines 4.98% as Stock Draws Market Attention - kalkine.co.in</t>
+          <t>Kiran (KIRANVYPAR.NS) Stock Screener: -1.36% Decline on Elevated Volume 2026-08-30 - Weekly Profile - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Ltd (NSE: RHETAN) Declines 4.98% as Stock Draws Market Attention - kalkine.co.in</t>
+          <t>Kiran Vyapar shareholders approve FY26 financials and final dividend - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Kiran Vyapar Share Price Today: Market Cap And Valuation - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>250% Return In 3 Years: Iron &amp; Steel Stock Hits Fresh 52-Week High After Key Business Update - goodreturns.in</t>
+          <t>MSUM Acquires 33.86% Stake in Kiran Vyapar Through NCLT-Approved Amalgamation - scanx.trade</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - Business Standard</t>
+          <t>Kiran Vyapar shareholders approve FY26 financials and final dividend - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3171,68 +3255,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL.NS</t>
+          <t>TALBROAUTO.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline Limited</t>
+          <t>Talbros Automotive Components Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4.809999942779541</v>
+        <v>457.3500061035156</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4.809999942779541</v>
+        <v>463.7999877929688</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.809999942779541</v>
+        <v>426.6000061035156</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>4.809999942779541</v>
+        <v>431.9500122070312</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5.059999942779541</v>
+        <v>457.3500061035156</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4.809999942779541</v>
+        <v>431.9500122070312</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>497047</v>
+        <v>385325</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.94</v>
+        <v>-5.55</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline Slips Nearly 5% to ₹3.44 — Support at ₹3.27 Becomes Key - Adaptive Moving Average - siam.in</t>
+          <t>Talbros Automotive Components Limited Approves Appointment of Mr. Rahul Bhutoria as an Independent Director, Effective 16 September, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline Uses Rights Issue Proceeds to Cut Debt - TipRanks</t>
+          <t>Talbros Automotive Publishes Addendum Notice for 69th AGM - TipRanks</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline KSHITIJPOL Rights Issue Allotment Details - kalkine.co.in</t>
+          <t>Talbros Automotive Components Ltd. (TALBROAUTO) Share Price Near 52-Week High on Strong Price Action - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline KSHITIJPOL Rights Issue Corrigendum August 2026 - kalkine.co.in</t>
+          <t>Is It Smart To Buy Talbros Automotive Components Limited (NSE:TALBROAUTO) Before It Goes Ex-Dividend? - simplywall.st</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline KSHITIJPOL AGM E-Voting Date Corrected - kalkine.co.in</t>
+          <t>Talbros Automotive Components Share Price Hits Fresh 52-Week High at Rs 485: Key Reasons Behind the Rally - Univest</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:14 IST</t>
+          <t>2026-09-28 14:20:40 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3240,63 +3324,59 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>TRIGYN.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>Trigyn Technologies Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>225.5</v>
+        <v>56.61999893188477</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>226</v>
+        <v>58</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>210.1999969482422</v>
+        <v>52.79999923706055</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>213.1900024414062</v>
+        <v>53.58000183105469</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>224.25</v>
+        <v>56.61999893188477</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>213.1900024414062</v>
+        <v>53.58000183105469</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>9323</v>
+        <v>100381</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.93</v>
+        <v>-5.37</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (ARVEE.NS) Rises 3.13% to ₹243.47, Positioned Midway Between Key Support and Resistance - Stop Hunt - siam.in</t>
+          <t>Trigyn Technologies Share Price Fall and Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories India: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>Trigyn Technologies schedules 40th AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories India: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>Trigyn Technologies schedules 40th AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Indian Stocks Open Higher Despite Rise in Crude Oil Prices - Investing.com India</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Arvee Laboratories Stock: Daily Chart Analysis - kalkine.co.in</t>
-        </is>
-      </c>
+          <t>Trigyn Technologies Slips 3.4% to ₹59.36: Stock Nears Key Support After Downward Move - Conversion Trade - siam.in</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="53" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,56 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RETAIL.NS</t>
+          <t>TNTELE.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>JHS Svendgaard Retail Ventures Limited</t>
+          <t>Tamilnadu Telecommunication Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>23</v>
+        <v>9.989999771118164</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>24.06999969482422</v>
+        <v>11.89000034332275</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22.1299991607666</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>24.06999969482422</v>
+        <v>11.89000034332275</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.05999946594238</v>
+        <v>9.909999847412109</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>24.06999969482422</v>
+        <v>11.89000034332275</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>125255</v>
+        <v>172414</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.99</v>
+        <v>19.98</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>SS Retail share price jumps 7% amid stock market fall | Do you own? - TradingView</t>
+          <t>Tamilnadu Telecommunications Secures Shareholder Nod on All AGM Resolutions - TipRanks</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>SS Retail share price jumps 7% amid stock market fall | Do you own? - TradingView</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>SS Retail share price jumps 7% amid stock market fall | Do you own? - Livemint</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Patel Retail Opens 54th Store; Shares Fall 1.43% - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>SS Retail Share Price: Stock debuts at 47%, gains 14% more after listing - India Infoline</t>
-        </is>
-      </c>
+          <t>Tamilnadu Telecommunications Secures Shareholder Nod on All AGM Resolutions - TipRanks</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -649,7 +637,7 @@
         <v>0.7400000095367432</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>15857667</v>
+        <v>15982595</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>19.35</v>
@@ -675,7 +663,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +671,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>REPRO.NS</t>
+          <t>RSYSTEMS.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Repro India Limited</t>
+          <t>R Systems International Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345.8999938964844</v>
+        <v>282.739990234375</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>301</v>
+        <v>245.4499969482422</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>338.2999877929688</v>
+        <v>275.2099914550781</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>288.25</v>
+        <v>235.6199951171875</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>338.2999877929688</v>
+        <v>275.2099914550781</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>341458</v>
+        <v>61310945</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>17.36</v>
+        <v>16.8</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>REPRO Share Price Near Low: Technical and Fundamental View - Univest</t>
+          <t>Here's What We Like About R Systems International's (NSE:RSYSTEMS) Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Repro India Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>R Systems International Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Repro India Ltd. Stock News - Value Research</t>
+          <t>800% dividend stock: This Blackstone-backed IT share zooms 14% after fixing record date; check amount per share - TradingView</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>REPRO.NS Jun 2026 Earnings: EPS of ₹90.03 Drives 7.35% Stock Advance - Margin Guidance - siam.in</t>
+          <t>3 AI Safety Software Stocks Investors May Be Missing Right Now - simplywall.st</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Repro India Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>R Systems International Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +740,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IWP.NS</t>
+          <t>PRIMO.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The Indian Wood Products Company Limited</t>
+          <t>Primo Chemicals Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34.31000137329102</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40.47999954223633</v>
+        <v>29.79999923706055</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>34.31000137329102</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>39.7599983215332</v>
+        <v>28.1299991607666</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.97000122070312</v>
+        <v>25.28000068664551</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>39.7599983215332</v>
+        <v>28.1299991607666</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>450122</v>
+        <v>4154850</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>13.7</v>
+        <v>11.27</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Technical Reactions to IWP Trends in Macro Strategies - news.stocktradersdaily.com</t>
+          <t>Primo Chemicals Share Price: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>IWP: Limping Into Q4, A Sell For Now (NYSEARCA:IWP) - Seeking Alpha</t>
+          <t>Primo Chemicals Share Price: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>IWP Capital urges FedEx to report on risks of s... - Pluang</t>
+          <t>Primo Brands (PRMB) Stock May Be Undervalued On Earnings Power - Yahoo Finance</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>IWP: Quality Issues, Unconvincing Returns, A Hold At Best (NYSEARCA:IWP) - Seeking Alpha</t>
+          <t>Primo Chemicals approves merger with subsidiary Flow Tech - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>IWP Capital to Vote "FOR" FedEx Proposal 6 on Abortion-Drug Distribution Risk - Finansavisen</t>
+          <t>how InvestingPro’s Primo Chemicals overvaluation call saved investors 51% By Investing.com - Investing.com India</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,64 +809,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BPLPHARMA.NS</t>
+          <t>SYNCOMF.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bharat Parenterals Limited</t>
+          <t>Syncom Formulations (India) Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2093</v>
+        <v>20.17000007629395</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2277.60009765625</v>
+        <v>23.42000007629395</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2050</v>
+        <v>20.17000007629395</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2116.89990234375</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1898</v>
+        <v>20.04999923706055</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2116.89990234375</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>120603</v>
+        <v>82428576</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>11.53</v>
+        <v>10.72</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Bharat Parenterals shares rally 25% in three sessions; Here is why stock is rising - Upstox</t>
+          <t>With EPS Growth And More, Syncom Formulations (India) (NSE:SYNCOMF) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Bharat Parenterals shares rally 25% in three sessions; Here is why stock is rising - Upstox</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Bharat Parenterals Board Meeting to Review Preferential Issue Proposal - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Bharat Parenterals schedules board meet for Sept 29 to consider preferential issue - scanx.trade</t>
-        </is>
-      </c>
+          <t>With EPS Growth And More, Syncom Formulations (India) (NSE:SYNCOMF) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,68 +866,60 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PRIMO.NS</t>
+          <t>AHCL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26</v>
+        <v>32.25</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>29.79999923706055</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.79999923706055</v>
+        <v>32.2400016784668</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>28.18000030517578</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25.28000068664551</v>
+        <v>31.51000022888184</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>28.18000030517578</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3649335</v>
+        <v>23572264</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>11.47</v>
+        <v>10</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals Share Price: Price Action and Valuation - Univest</t>
+          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals Share Price: Price Action and Valuation - Univest</t>
+          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Primo Brands (PRMB) Stock May Be Undervalued On Earnings Power - Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Primo Chemicals approves merger with subsidiary Flow Tech - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>how InvestingPro’s Primo Chemicals overvaluation call saved investors 51% By Investing.com - Investing.com India</t>
-        </is>
-      </c>
+          <t>Anlon Healthcare Limited Seeks Shareholder Approval for Stock Split and Bonus Issue Through Postal Ballot - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,68 +927,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DAMCAPITAL.NS</t>
+          <t>CUBEXTUB.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Dam Capital Advisors Limited</t>
+          <t>Cubex Tubings Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>139.8999938964844</v>
+        <v>154.8000030517578</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>155</v>
+        <v>167.4600067138672</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>137.7100067138672</v>
+        <v>151</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>152.2899932861328</v>
+        <v>167.4600067138672</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>138.1799926757812</v>
+        <v>152.2400054931641</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>152.2899932861328</v>
+        <v>167.4600067138672</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>11407500</v>
+        <v>1078393</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10.21</v>
+        <v>10</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>DAM Capital Advisors Trading Window Closure Q2 FY27 - Kalkine India</t>
+          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>DAM Capital Advisors Trading Window Closure Q2 FY27 - Kalkine India</t>
+          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Dam Capital Advisors Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
+          <t>Cubex Tubings Share Price today: price action and value - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>DAM Capital Advisors Ltd Peer Comparison – Compare with Others - Value Research</t>
+          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>PVR Inox board approves share buyback worth up to ₹300 crore; all you need to know - Dailyhunt</t>
+          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1024,68 +996,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>PRITIKAUTO.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>Pritika Auto Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>213.1900024414062</v>
+        <v>18</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>234.5</v>
+        <v>18.97999954223633</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>213.1900024414062</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>234.5</v>
+        <v>18.8700008392334</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>213.1900024414062</v>
+        <v>17.15999984741211</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>234.5</v>
+        <v>18.8700008392334</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>31561</v>
+        <v>1141258</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (ARVEE.NS) Rises 3.13% to ₹243.47, Positioned Midway Between Key Support and Resistance - Stop Hunt - siam.in</t>
+          <t>Earnings Working Against Pritika Auto Industries Limited's (NSE:PRITIKAUTO) Share Price - simplywall.st</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories India: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>Pritika Auto Industries PRITIKAUTO Board Meeting August 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories India: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>Pritika Auto Industries Limited Files Q4FY26 Demat Certificate and Annual SEBI Disclosure - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>PRITIKAUTO Stock Price and Chart — NSE:PRITIKAUTO - TradingView</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Indian Stocks Open Higher Despite Rise in Crude Oil Prices - Investing.com India</t>
+          <t>Pritika Auto Industries demerger: NCLT gives approval for value unlocking. Details here - Livemint</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1093,68 +1065,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>HINDCON.NS</t>
+          <t>POLYSPIN.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>Polyspin Exports Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30.29000091552734</v>
+        <v>32</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>30.36000061035156</v>
+        <v>32</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>29.04999923706055</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>30.36000061035156</v>
+        <v>31.78000068664551</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>27.60000038146973</v>
+        <v>28.97999954223633</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>30.36000061035156</v>
+        <v>31.78000068664551</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>155579</v>
+        <v>373</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10</v>
+        <v>9.66</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Share Price Today with Valuation View - Univest</t>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals vs Nifty 50: Share Price Performance Compared - Univest</t>
+          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals (HINDCON.NS) Slips 1.45% to ₹23.74, Holds Midpoint of Trading Range - Rounding Bottom - siam.in</t>
+          <t>Polyspin Exports Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Polyspin Exports Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1162,68 +1134,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB.NS</t>
+          <t>SUNFLAG.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Limited</t>
+          <t>Sunflag Iron And Steel Company Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>154.8000030517578</v>
+        <v>415.7999877929688</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>167.4600067138672</v>
+        <v>451.7000122070312</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>151</v>
+        <v>412.3500061035156</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>167.4600067138672</v>
+        <v>449.2000122070312</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>152.2400054931641</v>
+        <v>410.6499938964844</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>167.4600067138672</v>
+        <v>449.2000122070312</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1061016</v>
+        <v>4466773</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
+          <t>Sunflag Iron and Steel Stock Signals to Watch This Week - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
+          <t>Sunflag Iron &amp; Steel approves ₹1 per share dividend for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Share Price today: price action and value - Univest</t>
+          <t>Sunflag Iron and Steel Share Price - Upstox</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
+          <t>Sunflag Iron and Steel (NSE:SUNFLAG) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
+          <t>Sunflag Iron And Steel Company Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1231,68 +1203,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AASTHA.NS</t>
+          <t>3BBLACKBIO.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Limited</t>
+          <t>3B Blackbio Dx Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>37.02999877929688</v>
+        <v>1502.900024414062</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>39.95000076293945</v>
+        <v>1599</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>37.02999877929688</v>
+        <v>1475.5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>39.68999862670898</v>
+        <v>1584.800048828125</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.36000061035156</v>
+        <v>1456.199951171875</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>39.68999862670898</v>
+        <v>1584.800048828125</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1704531</v>
+        <v>84309</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>9.16</v>
+        <v>8.83</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18 - LinkedIn</t>
+          <t>3B BlackBio Dx concludes investor meeting with Capri Global Holdings - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18 - LinkedIn</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Aastha Spintex Secures ₹25 Crore Fabric Orders; Shares Fall 9.99% - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1 Free Shares On 1, 10 Shares On 10, 100 Shares On 100; Why Textile Stock Crashed 50% On 1:1 Bonus Record Date - Goodreturns</t>
-        </is>
-      </c>
+          <t>3B BlackBio Dx concludes investor meeting with Capri Global Holdings - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1300,68 +1260,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG.NS</t>
+          <t>SDBL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron And Steel Company Limited</t>
+          <t>Som Distilleries &amp; Breweries Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>415.7999877929688</v>
+        <v>81.91999816894531</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>451.7000122070312</v>
+        <v>83.80000305175781</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>412.3500061035156</v>
+        <v>78.11000061035156</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>445.6000061035156</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>410.6499938964844</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>445.6000061035156</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4042085</v>
+        <v>19487108</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.51</v>
+        <v>8.42</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron and Steel Share Price - Upstox</t>
+          <t>Som Distilleries &amp; Brew Share Price - Live NSE: SDBL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron &amp; Steel approves ₹1 per share dividend for FY26 - scanx.trade</t>
+          <t>Why is Som Distilleries stock rising today? Ace investor Prashant Jain-backed liquor share jumps 7% on this key update - Livemint</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron And Steel Company Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Som Distilleries &amp; Breweries Falls 1.23% to ₹67.29 as SDBL Holds Above Key Support - High Volume Node - siam.in</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron and Steel (NSE:SUNFLAG) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
+          <t>SDBL submits FY26 BRSR: beer drives 84.7% of turnover - scanx.trade</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron &amp; Steel: Anand Kapre exits independent director role - scanx.trade</t>
+          <t>SDBL Board Meets On September 5 To Consider Convertible Warrant Issue - Sahi</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1369,46 +1329,46 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX.NS</t>
+          <t>SILLYMONKS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals Limited</t>
+          <t>Silly Monks Entertainment Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>441.0499877929688</v>
+        <v>22.79000091552734</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>508.7000122070312</v>
+        <v>24.22999954223633</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>435</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>486.6499938964844</v>
+        <v>23.82999992370605</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>449.9500122070312</v>
+        <v>22.03000068664551</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>486.6499938964844</v>
+        <v>23.82999992370605</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>6660637</v>
+        <v>146873</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.16</v>
+        <v>8.17</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals (INDOBORAX.NS) Holds Firm at ₹470.2 as Traders Eye ₹493.71 Resistance - Growth ETF - siam.in</t>
+          <t>Cresto Techno Ltd. Share Price Today - Cresto Techno Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals (INDOBORAX.NS) Holds Firm at ₹470.2 as Traders Eye ₹493.71 Resistance - Growth ETF - siam.in</t>
+          <t>Cresto Techno Ltd. Share Price Today - Cresto Techno Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -1418,7 +1378,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,68 +1386,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PRITIKAUTO.NS</t>
+          <t>DCI.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Pritika Auto Industries Limited</t>
+          <t>Dc Infotech And Communication Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>18</v>
+        <v>304.8999938964844</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>18.97999954223633</v>
+        <v>336.6000061035156</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>17.35000038146973</v>
+        <v>301.2000122070312</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>18.48999977111816</v>
+        <v>326.6499938964844</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>17.15999984741211</v>
+        <v>302</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>18.48999977111816</v>
+        <v>326.6499938964844</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>749440</v>
+        <v>448649</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>7.75</v>
+        <v>8.16</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Earnings Working Against Pritika Auto Industries Limited's (NSE:PRITIKAUTO) Share Price - simplywall.st</t>
+          <t>DCI Share Price Rise as Industry Benchmarks Are Reviewed - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Pritika Auto Industries PRITIKAUTO Board Meeting August 2026 - Kalkine India</t>
+          <t>DCI Share Price Rise as Industry Benchmarks Are Reviewed - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Pritika Auto Industries Limited Files Q4FY26 Demat Certificate and Annual SEBI Disclosure - scanx.trade</t>
+          <t>Donaldson (DCI) Stock Could Be 16% Undervalued On Durable Cash Flow - Yahoo Finance</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>PRITIKAUTO Stock Price and Chart — NSE:PRITIKAUTO - TradingView</t>
+          <t>How Investors May Respond To Donaldson Stock After An Earnings Beat - simplywall.st</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Pritika Auto Industries demerger: NCLT gives approval for value unlocking. Details here - Livemint</t>
+          <t>Donaldson Co. CEO Tod Carpenter sells $2.9 million in DCI stock - Investing.com</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1495,60 +1455,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>THAKDEV.NS</t>
+          <t>AASTHA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Limited</t>
+          <t>Aastha Spintex Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>134.9900054931641</v>
+        <v>37.02999877929688</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>145</v>
+        <v>39.95000076293945</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>134.9900054931641</v>
+        <v>37.02999877929688</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>145</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>134.9900054931641</v>
+        <v>36.36000061035156</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>145</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1310</v>
+        <v>2200221</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7.42</v>
+        <v>8.09</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Declines 5.31% to ₹142; Support at ₹134.9 in Focus - Aggressive Growth Picks - siam.in</t>
+          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18 - LinkedIn</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Share Price Today: 9.97% Decline - Univest</t>
+          <t>Aastha Spintex shares rise 9% after adjusting for 1:1 bonus issue - TradingView</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Thakkers Developers Share Price Today: 9.97% Decline - Univest</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Aastha Spintex shares rise 9% after adjusting for 1:1 bonus issue - TradingView</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Aastha Spintex Share Price today: stock rises to Rs 39.49 - Univest</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1556,68 +1524,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>HAVISHA.NS</t>
+          <t>ALUFLUOR.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sri Havisha Hospitality and Infrastructure Limited</t>
+          <t>Alufluoride Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.399999976158142</v>
+        <v>565.4000244140625</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.590000033378601</v>
+        <v>644.4000244140625</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1.399999976158142</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.480000019073486</v>
+        <v>604.7000122070312</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.379999995231628</v>
+        <v>565.4000244140625</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.480000019073486</v>
+        <v>604.7000122070312</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>46485</v>
+        <v>66544</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Sri Havisha Hospitality Edges Higher: HAVISHA.NS Holds Above ₹1.40, Resistance Eyed at ₹1.48 - Opening Range Breakout - siam.in</t>
+          <t>Alufluoride Share Price Rises 9.89% to Rs 540: Analysis - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Compare with SHRI SHAKTI - Equitymaster</t>
+          <t>Alufluoride Q1 Results: Net profit drops 9.6% YoY to ₹287 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Sri Havisha Hospitality and Infrastructure Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Sri Havisha Hospitality sets Sep 26 AGM for sweat equity, RPT approvals - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Sri Havisha Hospitality and Infrastructure Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
+          <t>Alufluoride Q1 Results: Net profit drops 9.6% YoY to ₹287 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1625,60 +1585,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ALUFLUOR.NS</t>
+          <t>OPTIEMUS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Limited</t>
+          <t>Optiemus Infracom Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>565.4000244140625</v>
+        <v>761.2999877929688</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>644.4000244140625</v>
+        <v>828.9000244140625</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>562.5999755859375</v>
+        <v>754</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>605.4000244140625</v>
+        <v>809.9500122070312</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>565.4000244140625</v>
+        <v>758.5499877929688</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>605.4000244140625</v>
+        <v>809.9500122070312</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>59177</v>
+        <v>3027104</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.07</v>
+        <v>6.78</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Share Price Rises 9.89% to Rs 540: Analysis - Univest</t>
+          <t>Optiemus Infracom shares extend two-day rally to 33%: Here are two reasons - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Q1 Results: Net profit drops 9.6% YoY to ₹287 lakh - scanx.trade</t>
+          <t>Optiemus Electronics partners with Quectel to manufacture wireless modules in India - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Q1 Results: Net profit drops 9.6% YoY to ₹287 lakh - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Optiemus Infracom To Acquire 51.1% Stake In Joint Venture With Nothing Electronics - Sahi</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Optiemus Infracom shares surge nearly 45% in three sessions, hit fresh 52-week high; here is why - Upstox</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Optiemus Infracom Hits 20% Upper Circuit As CMF Deepens India Partnership - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1686,68 +1654,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SUMEDHA.NS</t>
+          <t>MACPOWER.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sumedha Fiscal Services Limited</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42.75</v>
+        <v>2170</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45.9900016784668</v>
+        <v>2226</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>40.09999847412109</v>
+        <v>2116</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45.93999862670898</v>
+        <v>2194.60009765625</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>42.95000076293945</v>
+        <v>2062.5</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>45.93999862670898</v>
+        <v>2194.60009765625</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3675</v>
+        <v>148082</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6.96</v>
+        <v>6.4</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>US Infotech buys 250 Sumedha Fiscal shares, holds 13.42% - scanx.trade</t>
+          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Compare with SUMEDHA FISC - Equitymaster</t>
+          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Sumedha Fiscal promoter group buys 45,000 shares in two days - scanx.trade</t>
+          <t>Macpower CNC Machines Share Price News on Capital Goods - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Sumedha Fiscal Services Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Should You Be Adding Macpower CNC Machines (NSE:MACPOWER) To Your Watchlist Today? - simplywall.st</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Sumedha Fiscal promoter group buys 10,530 shares voluntarily under SAST - scanx.trade</t>
+          <t>Macpower CNC Machines Ltd is Rated Hold - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1755,68 +1723,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EMKAY.NS</t>
+          <t>SHUKRAPHAR.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Emkay Global Financial Services Limited</t>
+          <t>Shukra Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>273.2000122070312</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>292.8999938964844</v>
+        <v>60.4900016784668</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>273.2000122070312</v>
+        <v>56</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>287.3999938964844</v>
+        <v>59.43000030517578</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>270.3500061035156</v>
+        <v>55.93000030517578</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>287.3999938964844</v>
+        <v>59.43000030517578</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>243425</v>
+        <v>15637756</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6.31</v>
+        <v>6.26</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Is Emkay Global Financial Services the Best Stock in Its Sector? A Look at the Numbers - Univest</t>
+          <t>SHUKRA PHARMA RG (SHUKRAPHAR) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Gas PSU stock to buy: After 26% returns in 6 months, Emkay Global sees further 16% upside | Target, stop-loss, rationale - Livemint</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Buy National Stock Exchange; target of Rs 2050: Emkay Global Financial - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Gas PSU stock to buy: After 26% returns in 6 months, Emkay Global sees further 16% upside | Target, stop-loss, rationale - Livemint</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>GAIL shares: Emkay upgrades stock, sees 16% upside; check target price - Business Today</t>
-        </is>
-      </c>
+          <t>SHUKRA PHARMA RG (SHUKRAPHAR) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1824,63 +1780,51 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3BBLACKBIO.NS</t>
+          <t>INDOBORAX.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3B Blackbio Dx Limited</t>
+          <t>Indo Borax &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1502.900024414062</v>
+        <v>441.0499877929688</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1587.599975585938</v>
+        <v>508.7000122070312</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1475.5</v>
+        <v>435</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1548</v>
+        <v>477.5499877929688</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1456.199951171875</v>
+        <v>449.9500122070312</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1548</v>
+        <v>477.5499877929688</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>51064</v>
+        <v>8225574</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6.3</v>
+        <v>6.13</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3B (3BBLACKBIO.NS) Results Check: The Latest Report Adds New Financial Reference Points in the Current Update; Market Response: Shares Finish 1.36% Lower for the Current Session - Annual Earnings Summary - siam.in</t>
+          <t>Indo Borax &amp; Chemicals (INDOBORAX.NS) Holds Firm at ₹470.2 as Traders Eye ₹493.71 Resistance - Growth ETF - siam.in</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3B (3BBLACKBIO.NS) Results Check: The Latest Report Adds New Financial Reference Points in the Current Update; Market Response: Shares Finish 1.36% Lower for the Current Session - Annual Earnings Summary - siam.in</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>3BBLACKBIO Share Price Today - 3B Blackbio DX Stock Analysis - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>3B BlackBio Dx Limited Promoters Declare No Share Encumbrance for FY2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>3B Blackbio Dx Holds Steady Near Key Support Levels Amid Mild Decline - Counter Trend Trade - siam.in</t>
-        </is>
-      </c>
+          <t>Indo Borax &amp; Chemicals (INDOBORAX.NS) Holds Firm at ₹470.2 as Traders Eye ₹493.71 Resistance - Growth ETF - siam.in</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2005,7 +1949,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2013,68 +1957,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PAISALO.NS</t>
+          <t>KOTYARK.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital Limited</t>
+          <t>Kotyark Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>87.01000213623047</v>
+        <v>31.69000053405762</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>88.70999908447266</v>
+        <v>31.69000053405762</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>73.41999816894531</v>
+        <v>24.95999908447266</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>74.84999847412109</v>
+        <v>26.46999931335449</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>89.01999664306641</v>
+        <v>31.20000076293945</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>74.84999847412109</v>
+        <v>26.46999931335449</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>28362633</v>
+        <v>1861015</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-15.92</v>
+        <v>-15.16</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital to host virtual investor conference on September 29, 2026 - scanx.trade</t>
+          <t>Kotyark Industries closes trading window from Oct 1 for Q2FY27 results - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital to host virtual investor conference on September 29, 2026 - scanx.trade</t>
+          <t>Kotyark Industries closes trading window from Oct 1 for Q2FY27 results - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital (PAISALO.NS) Holds Near ₹84.59 as Stock Consolidates Between ₹80.36 and ₹88.82 - Scalping Stock Signals - siam.in</t>
+          <t>Kotyark Industries allots 10.2 crore bonus shares in 10:1 ratio - scanx.trade</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>Kotyark Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Kotyark Industries Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2082,68 +2026,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MEDICO.NS</t>
+          <t>PAISALO.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Limited</t>
+          <t>Paisalo Digital Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26.20000076293945</v>
+        <v>87.01000213623047</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>26.20999908447266</v>
+        <v>88.70999908447266</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20.88999938964844</v>
+        <v>73.41999816894531</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>22.35000038146973</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22.35000038146973</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3070528</v>
+        <v>37592752</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-14.04</v>
+        <v>-10.58</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Paisalo Digital Ltd leads losers in 'A' group - Business Standard</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Prism Medico sets AGM for Sept 19; seeks approval for ₹23 cr Infuze Well stake - scanx.trade</t>
+          <t>Paisalo Digital Ltd leads losers in 'A' group - Business Standard</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Paisalo Digital (PAISALO.NS) Holds Near ₹84.59 as Stock Consolidates Between ₹80.36 and ₹88.82 - Scalping Stock Signals - siam.in</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Prism Medico and Pharmacy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Paisalo Digital to host virtual investor conference on September 29, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Prism Medico AGM resolutions pass with 99.99% shareholder approval - scanx.trade</t>
+          <t>Paisalo Digital: Best Stock in Its Sector? Key Metrics - Univest</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2151,68 +2095,56 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SAICAPI.NS</t>
+          <t>NOIDATOLL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Limited</t>
+          <t>Noida Toll Bridge Company Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>156.9499969482422</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>156.9499969482422</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>136</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>136</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>156.9900054931641</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>136</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>324907</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-13.37</v>
+        <v>-9.6</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Limited Submits Annual Secretarial Compliance Report for Financial Year Ended March 31, 2026 - scanx.trade</t>
+          <t>Noida Toll Bridge Company Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Ltd. (SAICAPI) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Sai Capital Ltd. (SAICAPI) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Sai Capital consolidated net profit rises 16% to ₹1,255.69 Lacs in FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Sai Capital Ltd. (SAICAPI) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
+          <t>Noida Toll Bridge Company Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2220,68 +2152,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KOTYARK.NS</t>
+          <t>NPST.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries Limited</t>
+          <t>Network People Services Technologies Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>31.69000053405762</v>
+        <v>1812.599975585938</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>31.69000053405762</v>
+        <v>1813</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.95999908447266</v>
+        <v>1625.099975585938</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>27.35000038146973</v>
+        <v>1635</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31.20000076293945</v>
+        <v>1796.300048828125</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27.35000038146973</v>
+        <v>1635</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1493708</v>
+        <v>110140</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-12.34</v>
+        <v>-8.98</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries allots 10.2 crore bonus shares in 10:1 ratio - scanx.trade</t>
+          <t>NETWORK PEOPLE SRV TECH L Share Price - Live NSE: NPST Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries promoter reduces stake to 5.47% - scanx.trade</t>
+          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries promoter reduces stake to 5.47% - scanx.trade</t>
+          <t>NPST Share Price rises 10.36%: price action and analysis - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>NPST to host analyst meeting with SBI Mutual Funds on Sep 29, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2289,68 +2221,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EKI.NS</t>
+          <t>RSL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>EKI Energy Services Limited</t>
+          <t>Rajputana Stainless Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>102.7900009155273</v>
+        <v>182.4100036621094</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>106</v>
+        <v>182.4100036621094</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>90.90000152587891</v>
+        <v>165.9199981689453</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>90.90000152587891</v>
+        <v>167.4100036621094</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>100.9899978637695</v>
+        <v>183.4600067138672</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>90.90000152587891</v>
+        <v>167.4100036621094</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>126639</v>
+        <v>799141</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-9.99</v>
+        <v>-8.75</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>EKI Energy Services Ltd (NSE: EKI) Gains 19.99% as Stock Draws Market Attention - Kalkine India</t>
+          <t>RAJPUTANA STAINLESS LTD Share Price - Live NSE: RSL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>EKI Energy Services Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Sergi Solans scores 2 goals, RSL beats Revolution 3-0 to snap 13-game winless skid - FOX Sports</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>EKI Energy Services Share Price rise with sector comparison - Univest</t>
+          <t>Rajputana Stainless Limited (RSL.NS): Steady at ₹181.5 as Stock Consolidates Between Key Levels - Bear Flag - siam.in</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>EKI Energy Services Ltd is Rated Strong Sell - MarketsMojo</t>
+          <t>Rajasthan Securities approves ₹40 crore guarantee for subsidiary RSL Securities - scanx.trade</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>EKI Energy Services Share Price today: Rs 80 after rise - Univest</t>
+          <t>Sergi Solans scores 2 goals, RSL beats Revolution 3-0 to snap 13-game winless skid - FOX Sports</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2358,68 +2290,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ARMANFIN.NS</t>
+          <t>VTMLTD.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Arman Financial Services Limited</t>
+          <t>VTM Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1830.199951171875</v>
+        <v>42.43999862670898</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1835.900024414062</v>
+        <v>43.11000061035156</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1666.199951171875</v>
+        <v>37.45000076293945</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1704</v>
+        <v>38.06999969482422</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1885.599975585938</v>
+        <v>41.52999877929688</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1704</v>
+        <v>38.06999969482422</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>195143</v>
+        <v>348087</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-9.630000000000001</v>
+        <v>-8.33</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Arman Financial Services (ARMANFIN.NS) Slips 4.63% to ₹1918.1 as Stock Retreats From Resistance - Linear Regression - siam.in</t>
+          <t>VTM Ltd net profit falls 58% to ₹193 lakh as costs outpace revenue - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Arman Financial Services ARMANFIN Trading Window Closure - Kalkine India</t>
+          <t>VTM Ltd net profit falls 58% to ₹193 lakh as costs outpace revenue - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Arman Financial Services ESOP Allotment September 2026 - Kalkine India</t>
+          <t>VTM Limited Share Price Falls as Technical Setup Shifts - Kalkine India</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Arman Financial Services Schedules Virtual Analyst Meeting For September 29 At 1 PM - Sahi</t>
+          <t>VTM Ltd. Share Price rises 13.42%: valuation view - Univest</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>ARMANFIN Q2 2026 Earnings: EPS at ₹53.57 as Revenue Slips 4.96% Year-on-Year - Margin Guidance - siam.in</t>
+          <t>VTM Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2427,68 +2359,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ANTELOPUS.NS</t>
+          <t>KIRANVYPAR.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy Limited</t>
+          <t>Kiran Vyapar Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1260</v>
+        <v>195</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1260</v>
+        <v>195</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1143.849975585938</v>
+        <v>180.5500030517578</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1145.900024414062</v>
+        <v>185.1699981689453</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1261.699951171875</v>
+        <v>201.1499938964844</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1145.900024414062</v>
+        <v>185.1699981689453</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>885207</v>
+        <v>12146</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-9.18</v>
+        <v>-7.94</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ANTELOPUS SELAN ENERGY LTD Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
+          <t>Kiran (KIRANVYPAR.NS) Stock Screener: -1.36% Decline on Elevated Volume 2026-08-30 - Weekly Profile - siam.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ANTELOPUS SELAN ENERGY LTD Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
+          <t>Kiran Vyapar shareholders approve FY26 financials and final dividend - scanx.trade</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>Kiran Vyapar Share Price Today: Market Cap And Valuation - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>MSUM Acquires 33.86% Stake in Kiran Vyapar Through NCLT-Approved Amalgamation - scanx.trade</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>176% return in 2026 so far! Antelopus Selan Energy falls 3% after massive rally | What’s spooking investors? - Livemint</t>
+          <t>Kiran Vyapar shareholders approve FY26 financials and final dividend - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2496,68 +2428,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>NPST.NS</t>
+          <t>ELECTHERM.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Network People Services Technologies Limited</t>
+          <t>Electrotherm (India) Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1812.599975585938</v>
+        <v>850</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1813</v>
+        <v>870</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1640.300048828125</v>
+        <v>786.0499877929688</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1648.300048828125</v>
+        <v>806.6500244140625</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1796.300048828125</v>
+        <v>873.3499755859375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1648.300048828125</v>
+        <v>806.6500244140625</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>83010</v>
+        <v>69913</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-8.24</v>
+        <v>-7.64</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SRV TECH L Share Price - Live NSE: NPST Stock Price &amp; Chart - Upstox</t>
+          <t>Electrotherm (India) Share Price Fall: Key Market Update - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SRV TECH L Share Price - Live NSE: NPST Stock Price &amp; Chart - Upstox</t>
+          <t>Electrotherm holds 40th AGM, approves director appointments and financials - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>NPST Share Price rises 10.36%: price action and analysis - Univest</t>
+          <t>Electrotherm India ELECTHERM 40th AGM Resolutions September 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>NPST to host analyst meeting with SBI Mutual Funds on Sep 29, 2026 - scanx.trade</t>
+          <t>Electrotherm holds 40th AGM, approves director appointments and financials - scanx.trade</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
+          <t>Electrotherm India (ELECTHERM.NS) Slips 1.15% to ₹945.35, Holding Mid-Range Between Key Levels - Put Flow Alert - siam.in</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2565,68 +2497,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DELTACORP.NS</t>
+          <t>CREATIVEYE.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Limited</t>
+          <t>Creative Eye Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>80.79000091552734</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>81</v>
+        <v>6.239999771118164</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>71.27999877929688</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>71.51000213623047</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>76.83999633789062</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>71.51000213623047</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>10643698</v>
+        <v>20647</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-6.94</v>
+        <v>-7.59</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Share Price - Live NSE: DELTACORP Stock Price &amp; Chart - Upstox</t>
+          <t>Creative Eye AGM adopts FY26 financials, appoints STDJ &amp; Co as auditor - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Delta Corp Share Price - Live NSE: DELTACORP Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Delta Corp Ltd. Share Price Update: Fundamentals, Peer View - Univest</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Delta Corp Limited (DELTACORP.NS) Consolidates Near ₹54 as Traders Eye Range Boundaries - Factor Timing - siam.in</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>DELTACORP Outlook for the Week (September 28, 2026 – October 02, 2026) - Equitypandit</t>
-        </is>
-      </c>
+          <t>Creative Eye AGM adopts FY26 financials, appoints STDJ &amp; Co as auditor - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2634,68 +2554,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>JSFB.NS</t>
+          <t>RAMBHAJO.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Jana Small Finance Bank Limited</t>
+          <t>Advit Jewels Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>537</v>
+        <v>282.4400024414062</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>541.0999755859375</v>
+        <v>282.4400024414062</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>498</v>
+        <v>263</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>501.8999938964844</v>
+        <v>265.0299987792969</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>535.25</v>
+        <v>286.2300109863281</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>501.8999938964844</v>
+        <v>265.0299987792969</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>984248</v>
+        <v>860767</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-6.23</v>
+        <v>-7.41</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Jana Small Finance Bank Limited (JSFB.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Jana Small Finance Bank Limited (JSFB.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>JANA SMALL FIN BANK LTD Share Price - Upstox</t>
+          <t>ADVIT JEWELS LIMITED Share Price news: valuation and peers - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>JSFB Share Price today: price rise, valuation and peers - Univest</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Jana Small Finance Bank Trades Lower at ₹537.5; Support and Resistance Levels in Focus - Ichimoku Cloud - siam.in</t>
-        </is>
-      </c>
+          <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2703,68 +2619,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>MERCANTILE.NS</t>
+          <t>NOCIL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mercantile Ventures Limited</t>
+          <t>NOCIL Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>22.27000045776367</v>
+        <v>188.0500030517578</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>22.27000045776367</v>
+        <v>188.0500030517578</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>21.30999946594238</v>
+        <v>174</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>21.30999946594238</v>
+        <v>175.1699981689453</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.71999931335449</v>
+        <v>188.4100036621094</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21.30999946594238</v>
+        <v>175.1699981689453</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>4</v>
+        <v>1512312</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-6.21</v>
+        <v>-7.03</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Surat Trade and Mercantile Lim Share Price - Live SURATRAML Stock Price &amp; Chart - Upstox</t>
+          <t>NOCIL Stock Signals to Watch This Week - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Vivid Mercantile holds 32nd AGM, appoints new statutory auditors - scanx.trade</t>
+          <t>Nocil Share Price Falls as Chemical Stock Stays in Focus - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Vivid Mercantile holds 32nd AGM, appoints new statutory auditors - scanx.trade</t>
+          <t>Nocil Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>REG - Mercantile Inv Tst - Dividend Declaration - TradingView</t>
+          <t>Nocil Share Price Falls as Chemical Stock Stays in Focus - Univest</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Mercantile Ventures Share Price gains in latest market move - Univest</t>
+          <t>NOCIL sets ₹1.50 dividend for FY26, details TDS rules - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2772,68 +2688,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NILE.NS</t>
+          <t>OMAXE.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Nile Limited</t>
+          <t>Omaxe Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1369.5</v>
+        <v>110</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1369.5</v>
+        <v>116.0400009155273</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1271.099975585938</v>
+        <v>108.0100021362305</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1286</v>
+        <v>110.2699966430664</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1369.699951171875</v>
+        <v>118.5299987792969</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1286</v>
+        <v>110.2699966430664</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5837</v>
+        <v>1131149</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.11</v>
+        <v>-6.97</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Nile Limited (NILE.NS) Trades at ₹1448.0, Down 0.62%: Range-Bound Action Keeps Support and Resistance in Focus - Passive Flow - siam.in</t>
+          <t>Omaxe Stock Signals to Watch This Week - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>LA County sees highest number of West Nile virus cases in nearly a decade - abcnews.com</t>
+          <t>Omaxe shares fall 4% after SEBI bars company from securities market for three months - Business Upturn</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Nile Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>SEBI finds Omaxe, promoter-linked entities breached MPS norms through 2013 OFS, imposes restraint and... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Nile Limited (NILE): Lead Recycling Compounder in Focus - Kalkine India</t>
+          <t>Sebi Bans Omaxe, Others for Artificial Public Shareholding - Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Nile Limited (NILE.NS) Holds Ground Near ₹1,471.5; Key Support and Resistance Levels in Focus - Quality ETF - siam.in</t>
+          <t>SEBI Bars Omaxe for 3 Months, Promoters for 1 Year, Imposes ₹1.92 Crore Penalty Over MPS Violation - Moneylife</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2841,68 +2757,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SENCO.NS</t>
+          <t>KDGREEN.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Senco Gold Limited</t>
+          <t>KD Green Industries Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>331.1000061035156</v>
+        <v>49.5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331.1000061035156</v>
+        <v>51</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>310.4500122070312</v>
+        <v>46.06000137329102</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>311.6499938964844</v>
+        <v>46.7599983215332</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>331.1000061035156</v>
+        <v>50.09999847412109</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>311.6499938964844</v>
+        <v>46.7599983215332</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1671874</v>
+        <v>56641</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.87</v>
+        <v>-6.67</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Senco Gold clarifies sustainable EBITDA margin at 7.5-7.8% post Q1FY27 surge - scanx.trade</t>
+          <t>KDGREEN Share Price Today - Manbro Industries Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Senco Gold clarifies sustainable EBITDA margin at 7.5-7.8% post Q1FY27 surge - scanx.trade</t>
+          <t>KD Green merger to create green steel and infrastructure hub - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Senco Gold Share Price - Upstox</t>
+          <t>KD Green Industries Ltd - equitypandit.com</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Kalyan Jewellers vs Senco Gold vs Rajesh Exports: Comparison - Univest</t>
+          <t>Technical Analysis of KD Green Industries Ltd (NSE:KDGREEN) - TradingView</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Senco Gold (SENCO.NS) Eases 0.84% to ₹346.95 as Traders Watch ₹329.6 Support - Wave Extension - siam.in</t>
+          <t>KD Green merger to create green steel and infrastructure hub - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2910,68 +2826,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>NOCIL.NS</t>
+          <t>MANINDS.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Limited</t>
+          <t>Man Industries (India) Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>188.0500030517578</v>
+        <v>1020</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>188.0500030517578</v>
+        <v>1030.900024414062</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>175.3600006103516</v>
+        <v>943.7000122070312</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>177.3999938964844</v>
+        <v>953.3499755859375</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>188.4100036621094</v>
+        <v>1020.349975585938</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>177.3999938964844</v>
+        <v>953.3499755859375</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1062860</v>
+        <v>1294525</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5.84</v>
+        <v>-6.57</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Nocil Share Price - Upstox</t>
+          <t>Here's Why Man Industries (India) (NSE:MANINDS) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Nocil Share Price - Upstox</t>
+          <t>Here's Why Man Industries (India) (NSE:MANINDS) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Stock Signals to Watch This Week - Univest</t>
+          <t>Man Industries Drops 3.55% to ₹792.55; Support at ₹752.92 Becomes Key - Jelly Roll Trade - siam.in</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Nocil Ltd. Stock News - Value Research</t>
+          <t>Man Industries (India) Share Price: 52-Week High Update - Univest</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Nocil Share Price Falls as Chemical Stock Stays in Focus - Univest</t>
+          <t>Man Industries Share Price Fall: Technicals and Valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2979,68 +2895,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MANAPPURAM.NS</t>
+          <t>LAMBODHARA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Manappuram Finance Limited</t>
+          <t>Lambodhara Textiles Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>328</v>
+        <v>141</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>330.6499938964844</v>
+        <v>141</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>312.1499938964844</v>
+        <v>131.8600006103516</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>315.1499938964844</v>
+        <v>135.1900024414062</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>334</v>
+        <v>144.5700073242188</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>315.1499938964844</v>
+        <v>135.1900024414062</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>6694363</v>
+        <v>37259</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.64</v>
+        <v>-6.49</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Stock to buy today: Manappuram Finance (₹334) - BusinessLine</t>
+          <t>Lambodhara Textiles Share Price today: key valuation view - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Stock to buy today: Manappuram Finance (₹334) - BusinessLine</t>
+          <t>Lambodhara Textiles Trading Window Closure Q2 FY27 - Kalkine India</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Manappuram Finance Share Price today: price rise, valuation - Univest</t>
+          <t>Lambodhara Textiles Trading Window Closure Q2 FY27 - Kalkine India</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Gold Duty Hike Triggers Rally In Gold Loan Stocks: Manappuram Finance &amp; Muthoot Finance Shares Surge 8% - Goodreturns</t>
+          <t>Is It Smart To Buy Lambodhara Textiles Limited (NSE:LAMBODHARA) Before It Goes Ex-Dividend? - simplywall.st</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Manappuram Finance Open Offer Launched for 26% Stake Acquisition by BC Asia - scanx.trade</t>
+          <t>Lambodhara Textiles Share Price Fall: Price Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3048,68 +2964,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SIS.NS</t>
+          <t>AVTNPL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>SIS LIMITED</t>
+          <t>AVT Natural Products Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>418.3999938964844</v>
+        <v>92.5</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>418.3999938964844</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>378.5</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>394.8500061035156</v>
+        <v>86.61000061035156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>418.3999938964844</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>394.8500061035156</v>
+        <v>86.61000061035156</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1589711</v>
+        <v>493697</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.63</v>
+        <v>-6.45</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Savaria Corporation (SIS.TO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+          <t>AVT Natural Products Ltd Share Price Today,, AVTNPL Share Price NSE, BSE - Business Today</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Savaria Corporation (SIS.TO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+          <t>AVT Natural AGM voting results: all 5 resolutions pass with strong support - scanx.trade</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>SIS buys back 25,000 shares at avg ₹422.55 on Sept 25 - scanx.trade</t>
+          <t>AVT Natural AGM voting results: all 5 resolutions pass with strong support - scanx.trade</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>SIS Limited (SIS.NS) Steadies Near ₹416 as Stock Consolidates Below Key Resistance - Fundamental Weighted - siam.in</t>
+          <t>AVT Natural Products Share Price: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>SIS buys additional 1.51% stake in Updater Services; Taurus MF sells over 1% stake in Advit Jewels - Moneycontrol.com</t>
+          <t>AVT Natural Products Share Price rises 8.28% on valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3117,68 +3033,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGOLD.NS</t>
+          <t>STERTOOLS.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Limited</t>
+          <t>Sterling Tools Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>316.1900024414062</v>
+        <v>240.6499938964844</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>302.4100036621094</v>
+        <v>223.5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>307.4200134277344</v>
+        <v>224.1300048828125</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>325.6799926757812</v>
+        <v>239.4600067138672</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>307.4200134277344</v>
+        <v>224.1300048828125</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>6531722</v>
+        <v>50109</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5.61</v>
+        <v>-6.4</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International (SHANTIGOLD.NS) Climbs 3.28% to ₹250.4, Presses Toward ₹263 Resistance - Double Bottom - siam.in</t>
+          <t>Sterling Tools Share Price - Upstox</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International approves rights issue up to Rs 100 crore - scanx.trade</t>
+          <t>Sterling Tools Share Price - Upstox</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Share Price rises 9.58% today - Univest</t>
+          <t>Sterling Tools Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International approves rights issue up to Rs 100 crore - scanx.trade</t>
+          <t>STERTOOLS Q2 2026 Earnings: EPS of ₹8.02 as Revenue Slips 20.79% Year-on-Year - Earnings Weakness Phase - siam.in</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Here's Why We Think Shanti Gold International (NSE:SHANTIGOLD) Might Deserve Your Attention Today - simplywall.st</t>
+          <t>Sterling Tools opens e-voting for Whole Time Director appointment - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3186,68 +3102,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>KIRANVYPAR.NS</t>
+          <t>ACL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Kiran Vyapar Limited</t>
+          <t>Andhra Cements Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>195</v>
+        <v>42.93999862670898</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>195</v>
+        <v>42.93999862670898</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>180.5500030517578</v>
+        <v>39.5099983215332</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>189.9900054931641</v>
+        <v>39.93999862670898</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>201.1499938964844</v>
+        <v>42.63000106811523</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>189.9900054931641</v>
+        <v>39.93999862670898</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>9787</v>
+        <v>67312</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.55</v>
+        <v>-6.31</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Kiran (KIRANVYPAR.NS) Stock Screener: -1.36% Decline on Elevated Volume 2026-08-30 - Weekly Profile - siam.in</t>
+          <t>ANDHRA CEMENTS LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Kiran Vyapar shareholders approve FY26 financials and final dividend - scanx.trade</t>
+          <t>ANDHRA CEMENTS LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Kiran Vyapar Share Price Today: Market Cap And Valuation - Univest</t>
+          <t>A.C.L. Construction Ltd. (ACL) To Issue 1.95M Shares To Settle $234K Debt - TradingView</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>MSUM Acquires 33.86% Stake in Kiran Vyapar Through NCLT-Approved Amalgamation - scanx.trade</t>
+          <t>A.C.L. Construction Ltd. Announces Shares for Debt Settlement - TradingView</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Kiran Vyapar shareholders approve FY26 financials and final dividend - scanx.trade</t>
+          <t>A.C.L. Construction Ltd. Resolves $234,495 Debt via Share Issuance to Company Insiders - Kalkine Media</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3255,68 +3171,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>TALBROAUTO.NS</t>
+          <t>AERONEU.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Talbros Automotive Components Limited</t>
+          <t>Aeroflex Neu Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>457.3500061035156</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>463.7999877929688</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>426.6000061035156</v>
+        <v>73</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>431.9500122070312</v>
+        <v>75.18000030517578</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>457.3500061035156</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>431.9500122070312</v>
+        <v>75.18000030517578</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>385325</v>
+        <v>30144</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.55</v>
+        <v>-6.28</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Talbros Automotive Components Limited Approves Appointment of Mr. Rahul Bhutoria as an Independent Director, Effective 16 September, 2026 - marketscreener.com</t>
+          <t>Sah Polymers Share Price - Upstox</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Talbros Automotive Publishes Addendum Notice for 69th AGM - TipRanks</t>
+          <t>Sah Polymers Share Price Today: Price Fall and Valuation - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Talbros Automotive Components Ltd. (TALBROAUTO) Share Price Near 52-Week High on Strong Price Action - Univest</t>
+          <t>Sah Polymers Share Price Today: Price Fall and Valuation - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Is It Smart To Buy Talbros Automotive Components Limited (NSE:TALBROAUTO) Before It Goes Ex-Dividend? - simplywall.st</t>
+          <t>Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Talbros Automotive Components Share Price Hits Fresh 52-Week High at Rs 485: Key Reasons Behind the Rally - Univest</t>
+          <t>Aeroflex Neu Limited (AERONEU.NS) Slips 1.76% to ₹65.91, Holds Above Key Support - Box Spread - siam.in</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:20:40 IST</t>
+          <t>2026-09-28 23:46:12 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3324,59 +3240,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TRIGYN.NS</t>
+          <t>MANAKSIA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies Limited</t>
+          <t>Manaksia Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>56.61999893188477</v>
+        <v>63.90000152587891</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>58</v>
+        <v>64.69999694824219</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>52.79999923706055</v>
+        <v>58.25</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.58000183105469</v>
+        <v>60.18999862670898</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>56.61999893188477</v>
+        <v>64.11000061035156</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>53.58000183105469</v>
+        <v>60.18999862670898</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>100381</v>
+        <v>52826</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.37</v>
+        <v>-6.11</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies Share Price Fall and Stock Analysis - Univest</t>
+          <t>Manaksia Share Price - Upstox</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies schedules 40th AGM for September 30, 2026 - scanx.trade</t>
+          <t>Manaksia Coated Metals hosts virtual analyst meet on Sep 28 - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies schedules 40th AGM for September 30, 2026 - scanx.trade</t>
+          <t>Manaksia Coated Metals hosts virtual analyst meet on Sep 28 - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies Slips 3.4% to ₹59.36: Stock Nears Key Support After Downward Move - Conversion Trade - siam.in</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>MANAKSIA. Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Manaksia Share Price rises 8.4%: valuation view - Univest</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -562,28 +562,28 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9.989999771118164</v>
+        <v>13.5</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>14.26000022888184</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>13.10999965667725</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>14.26000022888184</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>11.89000034332275</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>9.600000381469727</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>11.89000034332275</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>9.909999847412109</v>
-      </c>
       <c r="J2" s="2" t="n">
-        <v>11.89000034332275</v>
+        <v>14.26000022888184</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>172414</v>
+        <v>507741</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.98</v>
+        <v>19.93</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -610,60 +610,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>LANDSMILL.NS</t>
+          <t>AXISCADES.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green Limited</t>
+          <t>AXISCADES Technologies Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7200000286102295</v>
+        <v>2034</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.7400000095367432</v>
+        <v>2067.39990234375</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.6600000262260437</v>
+        <v>1970.800048828125</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.7400000095367432</v>
+        <v>2067.39990234375</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.6200000047683716</v>
+        <v>1879.5</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.7400000095367432</v>
+        <v>2067.39990234375</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>15982595</v>
+        <v>774119</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.35</v>
+        <v>10</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL REALTY N INFRA Share Price - Live NSE: LANDSMILL Stock Price &amp; Chart - Upstox</t>
+          <t>Axiscades Tech shares gain 10% after equity worth ₹741 crore changes hands in block deal window - CNBC TV18</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL REALTY N INFRA Share Price - Live NSE: LANDSMILL Stock Price &amp; Chart - Upstox</t>
+          <t>Jupiter Capital sells 10.86% stake in Axiscades Technologies - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green board approves promoter reclassification to public category - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Axiscades Tech shares hit 10% upper circuit on block deal in defence firm - Business Standard</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Axiscades Tech share price locked in 10% upper circuit | What’s driving the stock and what lies ahead? - Livemint</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Jupiter Capital sells 10.86% stake in Axiscades Technologies - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -671,68 +679,56 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>RSYSTEMS.NS</t>
+          <t>EUROTEXIND.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>R Systems International Limited</t>
+          <t>Eurotex Industries and Exports Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>250</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>282.739990234375</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>245.4499969482422</v>
+        <v>12.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>275.2099914550781</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>235.6199951171875</v>
+        <v>12.92000007629395</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>275.2099914550781</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>61310945</v>
+        <v>1869</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>16.8</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Here's What We Like About R Systems International's (NSE:RSYSTEMS) Upcoming Dividend - simplywall.st</t>
+          <t>Eurotex shareholders clear all resolutions at 40th AGM, back capital and board moves - TipRanks</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>R Systems International Ltd. Upper Circuit: Price and Key Data - Univest</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>800% dividend stock: This Blackstone-backed IT share zooms 14% after fixing record date; check amount per share - TradingView</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3 AI Safety Software Stocks Investors May Be Missing Right Now - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>R Systems International Ltd. Upper Circuit: Price and Key Data - Univest</t>
-        </is>
-      </c>
+          <t>Eurotex shareholders clear all resolutions at 40th AGM, back capital and board moves - TipRanks</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -740,68 +736,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PRIMO.NS</t>
+          <t>INDOCO.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals Limited</t>
+          <t>Indoco Remedies Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>26</v>
+        <v>249.8000030517578</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>29.79999923706055</v>
+        <v>284.7699890136719</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>25.79999923706055</v>
+        <v>249.1999969482422</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>28.1299991607666</v>
+        <v>270.7999877929688</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.28000068664551</v>
+        <v>249.0599975585938</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28.1299991607666</v>
+        <v>270.7999877929688</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4154850</v>
+        <v>13977717</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>11.27</v>
+        <v>8.73</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals Share Price: Price Action and Valuation - Univest</t>
+          <t>Indoco Remedies incorporates wholly owned subsidiary Warren Lifesciences - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals Share Price: Price Action and Valuation - Univest</t>
+          <t>Indoco Remedies incorporates wholly owned subsidiary Warren Lifesciences - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Primo Brands (PRMB) Stock May Be Undervalued On Earnings Power - Yahoo Finance</t>
+          <t>Indoco Remedies (INDOCO.NS) Slips 8.22% to ₹241.39 as Stock Tests Key Support Zone - Ending Diagonal - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Primo Chemicals approves merger with subsidiary Flow Tech - scanx.trade</t>
+          <t>Indoco Remedies Share Price Drops; Technicals in Focus - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>how InvestingPro’s Primo Chemicals overvaluation call saved investors 51% By Investing.com - Investing.com India</t>
+          <t>Indoco Remedies shares jump 7% after 5-day fall; UK regulator clears Goa plant inspection - Business Today</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -809,56 +805,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SYNCOMF.NS</t>
+          <t>VESUVIUS.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Syncom Formulations (India) Limited</t>
+          <t>Vesuvius India Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.17000007629395</v>
+        <v>386.5499877929688</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>23.42000007629395</v>
+        <v>433.7999877929688</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20.17000007629395</v>
+        <v>385.6000061035156</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>22.20000076293945</v>
+        <v>418.25</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.04999923706055</v>
+        <v>385.3999938964844</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22.20000076293945</v>
+        <v>418.25</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>82428576</v>
+        <v>1659733</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>10.72</v>
+        <v>8.52</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Syncom Formulations (India) (NSE:SYNCOMF) Makes An Interesting Case - simplywall.st</t>
+          <t>Why is Vesuvius stock surging today? - Investing.com India</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Syncom Formulations (India) (NSE:SYNCOMF) Makes An Interesting Case - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Why is Vesuvius stock surging today? - Investing.com India</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>REG - Vesuvius plc RHI Magnesita N.V. - Response to Media Speculation - TradingView</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Vesuvius Shares Surge After Board Confirms RHI Magnesita Takeover Approaches - asktraders.com</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Vesuvius stock trades below its 200 day moving average - AD HOC NEWS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -866,60 +874,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AHCL.NS</t>
+          <t>ORBTEXP.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Limited</t>
+          <t>Orbit Exports Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>32.25</v>
+        <v>233.6000061035156</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>34.65999984741211</v>
+        <v>245</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>32.2400016784668</v>
+        <v>225.1100006103516</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>34.65999984741211</v>
+        <v>243.9499969482422</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>31.51000022888184</v>
+        <v>227.1499938964844</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>34.65999984741211</v>
+        <v>243.9499969482422</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>23572264</v>
+        <v>35556</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
+          <t>ORBTEXP Q2 2026 Earnings: Revenue Climbs 6.07% YoY to ₹226.67 Crore as EPS Prints at ₹12.29 - Earnings Quality Score - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>ANLON HEALTHCARE LIMITED Share Price - Upstox</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Anlon Healthcare Limited Seeks Shareholder Approval for Stock Split and Bonus Issue Through Postal Ballot - scanx.trade</t>
-        </is>
-      </c>
+          <t>ORBTEXP Q2 2026 Earnings: Revenue Climbs 6.07% YoY to ₹226.67 Crore as EPS Prints at ₹12.29 - Earnings Quality Score - siam.in</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -927,68 +931,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CUBEXTUB.NS</t>
+          <t>RSYSTEMS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Limited</t>
+          <t>R Systems International Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>154.8000030517578</v>
+        <v>290</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>167.4600067138672</v>
+        <v>302.989990234375</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>151</v>
+        <v>285.2000122070312</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>167.4600067138672</v>
+        <v>294.7799987792969</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>152.2400054931641</v>
+        <v>275.2099914550781</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>167.4600067138672</v>
+        <v>294.7799987792969</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1078393</v>
+        <v>51098274</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10</v>
+        <v>7.11</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Ltd (NSE: CUBEXTUB) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
+          <t>Here's What We Like About R Systems International's (NSE:RSYSTEMS) Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
+          <t>Why are R Systems International shares up 28% in 2 days despite weak trends on Dalal Street? Reason, next target price - TradingView</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings Share Price today: price action and value - Univest</t>
+          <t>R Systems International Reports 800% Dividend, Shares Jump 14% - Kalkine India</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Four-day upper circuit streak drives this small-cap stock up 74%; here's the key trigger behind the jump - TradingView</t>
+          <t>800% dividend stock: This Blackstone-backed IT share zooms 14% after fixing record date; check amount per share - TradingView</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Cubex Tubings (NSE:CUBEXTUB) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
+          <t>Why are R Systems International shares up 28% in 2 days despite weak trends on Dalal Street? Reason, next target price - TradingView</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -996,68 +1000,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PRITIKAUTO.NS</t>
+          <t>VIKRAN.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Pritika Auto Industries Limited</t>
+          <t>Vikran Engineering Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>18</v>
+        <v>57.25</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>18.97999954223633</v>
+        <v>63</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>17.35000038146973</v>
+        <v>56.5</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>18.8700008392334</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>17.15999984741211</v>
+        <v>57.2599983215332</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>18.8700008392334</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1141258</v>
+        <v>5787584</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Earnings Working Against Pritika Auto Industries Limited's (NSE:PRITIKAUTO) Share Price - simplywall.st</t>
+          <t>Vikran Engineering shares rally nearly 12% on securing ₹154 crore order from Power Grid - Upstox</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Pritika Auto Industries PRITIKAUTO Board Meeting August 2026 - Kalkine India</t>
+          <t>Intraday Stocks for Today: 3 Setups From Vikran, Divi's Labs and Olectra - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Pritika Auto Industries Limited Files Q4FY26 Demat Certificate and Annual SEBI Disclosure - scanx.trade</t>
+          <t>Intraday Stocks for Today: 3 Setups From Vikran, Divi's Labs and Olectra - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>PRITIKAUTO Stock Price and Chart — NSE:PRITIKAUTO - TradingView</t>
+          <t>Vikran Engineering shareholders approve ₹1,000 crore NCD facility - scanx.trade</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Pritika Auto Industries demerger: NCLT gives approval for value unlocking. Details here - Livemint</t>
+          <t>Vikran Engineering hosts investor meet at Anand Rathi conference on Sep 21 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1065,68 +1069,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>POLYSPIN.NS</t>
+          <t>RESPONIND.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Polyspin Exports Limited</t>
+          <t>Responsive Industries Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>32</v>
+        <v>162.3999938964844</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>32</v>
+        <v>172.6900024414062</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>29.04999923706055</v>
+        <v>160.2200012207031</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>31.78000068664551</v>
+        <v>172.0700073242188</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.97999954223633</v>
+        <v>161.6000061035156</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>31.78000068664551</v>
+        <v>172.0700073242188</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>373</v>
+        <v>1011596</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.66</v>
+        <v>6.48</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+          <t>Responsive Industries Share Price rises 13.72%: key view - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Polyspin Exports appoints Durga Ramji as MD at 41st AGM - scanx.trade</t>
+          <t>Responsive Ind shares drop 5% as board shelves buyback proposal - Business Today</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Polyspin Exports Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Ltd leads gainers in 'B' group - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Polyspin Exports Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
+          <t>Responsive Ind shares drop 5% as board shelves buyback proposal - Business Today</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1134,68 +1130,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG.NS</t>
+          <t>ATLASCYCLE.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron And Steel Company Limited</t>
+          <t>Atlas Cycles (Haryana) Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>415.7999877929688</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>451.7000122070312</v>
+        <v>100</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>412.3500061035156</v>
+        <v>91.66000366210938</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>449.2000122070312</v>
+        <v>97.23000335693359</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>410.6499938964844</v>
+        <v>91.43000030517578</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>449.2000122070312</v>
+        <v>97.23000335693359</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4466773</v>
+        <v>38262</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>6.34</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron and Steel Stock Signals to Watch This Week - Univest</t>
+          <t>Atlas Cycles ATLASCYCLE Trading Window Closed Q2 FY27 - Kalkine India</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Sunflag Iron &amp; Steel approves ₹1 per share dividend for FY26 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Sunflag Iron and Steel Share Price - Upstox</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Sunflag Iron and Steel (NSE:SUNFLAG) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Sunflag Iron And Steel Company Share: Bull Case vs Bear Case for 2026 - Univest</t>
-        </is>
-      </c>
+          <t>Atlas Cycles ATLASCYCLE Trading Window Closed Q2 FY27 - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1203,56 +1187,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3BBLACKBIO.NS</t>
+          <t>AZAD.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3B Blackbio Dx Limited</t>
+          <t>Azad Engineering Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1502.900024414062</v>
+        <v>2779</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1599</v>
+        <v>2998</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1475.5</v>
+        <v>2751.10009765625</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1584.800048828125</v>
+        <v>2893.39990234375</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1456.199951171875</v>
+        <v>2723.199951171875</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1584.800048828125</v>
+        <v>2893.39990234375</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>84309</v>
+        <v>4409962</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8.83</v>
+        <v>6.25</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3B BlackBio Dx concludes investor meeting with Capri Global Holdings - scanx.trade</t>
+          <t>Azad Engineering shares extend 2026 gains to 82% after Goldman Sachs thumbs-up - CNBC TV18</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3B BlackBio Dx concludes investor meeting with Capri Global Holdings - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Azad Engineering shares jump 10% as company expands GE Vernova's manufacturing footprint - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Stock Picks Today: Sun Pharma, Azad Engineering, Marico, NTPC, And More On Brokerages' Radar - ndtvprofit.com</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Azad Engineering Share Price and Valuation After New High - Univest</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>97% rally in two years! Azad Engineering share price jumps 5% today - Check target, stop loss, performance - Livemint</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1260,68 +1256,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SDBL.NS</t>
+          <t>ABLBL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Som Distilleries &amp; Breweries Limited</t>
+          <t>Aditya Birla Lifestyle Brands Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>81.91999816894531</v>
+        <v>77.12999725341797</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>83.80000305175781</v>
+        <v>84.43000030517578</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>78.11000061035156</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>80.62000274658203</v>
+        <v>81.97000122070312</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>74.36000061035156</v>
+        <v>77.16999816894531</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>80.62000274658203</v>
+        <v>81.97000122070312</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>19487108</v>
+        <v>18738517</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.42</v>
+        <v>6.22</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Som Distilleries &amp; Brew Share Price - Live NSE: SDBL Stock Price &amp; Chart - Upstox</t>
+          <t>ABLBL Share Price: fresh 52-week low, valuation check - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Why is Som Distilleries stock rising today? Ace investor Prashant Jain-backed liquor share jumps 7% on this key update - Livemint</t>
+          <t>ABLBL Share Price: fresh 52-week low, valuation check - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Som Distilleries &amp; Breweries Falls 1.23% to ₹67.29 as SDBL Holds Above Key Support - High Volume Node - siam.in</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>SDBL submits FY26 BRSR: beer drives 84.7% of turnover - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>SDBL Board Meets On September 5 To Consider Convertible Warrant Issue - Sahi</t>
-        </is>
-      </c>
+          <t>ABLBL Share Price Today: fresh 52-week low and ratio check - Univest</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1329,46 +1317,46 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SILLYMONKS.NS</t>
+          <t>ADROITINFO.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Silly Monks Entertainment Limited</t>
+          <t>Adroit Infotech Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>22.79000091552734</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>24.22999954223633</v>
+        <v>14.97000026702881</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>22.29999923706055</v>
+        <v>13.25</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>23.82999992370605</v>
+        <v>14.34000015258789</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.03000068664551</v>
+        <v>13.51000022888184</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>23.82999992370605</v>
+        <v>14.34000015258789</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>146873</v>
+        <v>611941</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.17</v>
+        <v>6.14</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Cresto Techno Ltd. Share Price Today - Cresto Techno Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Adroit Infotech Eases 1.44% to ₹10.25, Holds Above Key ₹9.74 Support - Fear Greed Index - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Cresto Techno Ltd. Share Price Today - Cresto Techno Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Adroit Infotech Eases 1.44% to ₹10.25, Holds Above Key ₹9.74 Support - Fear Greed Index - siam.in</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -1378,7 +1366,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1386,68 +1374,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DCI.NS</t>
+          <t>ELECTCAST.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Dc Infotech And Communication Limited</t>
+          <t>Electrosteel Castings Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>304.8999938964844</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>336.6000061035156</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>301.2000122070312</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>326.6499938964844</v>
+        <v>76.75</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>302</v>
+        <v>72.34999847412109</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>326.6499938964844</v>
+        <v>76.75</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>448649</v>
+        <v>23260255</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>8.16</v>
+        <v>6.08</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>DCI Share Price Rise as Industry Benchmarks Are Reviewed - Univest</t>
+          <t>Electrosteel Castings (ELECTCAST.NS) Edges Up 1.69% to ₹74.11, Nearing Resistance Zone - New Highs New Lows - siam.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>DCI Share Price Rise as Industry Benchmarks Are Reviewed - Univest</t>
+          <t>Electrosteel Castings accepts retirement of two senior vice presidents - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Donaldson (DCI) Stock Could Be 16% Undervalued On Durable Cash Flow - Yahoo Finance</t>
+          <t>Electrosteel Thermal Coal Makes Additional Share Purchase Worth Rs 4.54 Crore - scanx.trade</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>How Investors May Respond To Donaldson Stock After An Earnings Beat - simplywall.st</t>
+          <t>Electrosteel Castings Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Donaldson Co. CEO Tod Carpenter sells $2.9 million in DCI stock - Investing.com</t>
+          <t>Electrosteel Castings ELECTCAST Trading Window Closure Oct 2026 - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1455,68 +1443,60 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AASTHA.NS</t>
+          <t>MVELECTRO.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex Limited</t>
+          <t>MV Electrosystems Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>37.02999877929688</v>
+        <v>789.9000244140625</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>39.95000076293945</v>
+        <v>838</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>37.02999877929688</v>
+        <v>781.2999877929688</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>39.29999923706055</v>
+        <v>834</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>36.36000061035156</v>
+        <v>786.3499755859375</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>39.29999923706055</v>
+        <v>834</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2200221</v>
+        <v>1050659</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8.09</v>
+        <v>6.06</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18 - LinkedIn</t>
+          <t>MVELECTRO Share Price Today - MV Electrosystems Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex shares rise 9% after adjusting for 1:1 bonus issue - TradingView</t>
+          <t>MVELECTRO Share Price Today - MV Electrosystems Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Aastha Spintex shares rise 9% after adjusting for 1:1 bonus issue - TradingView</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Aastha Spintex Share Price today: stock rises to Rs 39.49 - Univest</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18</t>
-        </is>
-      </c>
+          <t>MV Electrosystems Share Price today: Rs 800 and market cap - Univest</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1524,60 +1504,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ALUFLUOR.NS</t>
+          <t>PRECWIRE.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Limited</t>
+          <t>Precision Wires India Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>565.4000244140625</v>
+        <v>480</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>644.4000244140625</v>
+        <v>513.7000122070312</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>562.5999755859375</v>
+        <v>476.5499877929688</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>604.7000122070312</v>
+        <v>509.6499938964844</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>565.4000244140625</v>
+        <v>480.6499938964844</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>604.7000122070312</v>
+        <v>509.6499938964844</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>66544</v>
+        <v>1056783</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6.95</v>
+        <v>6.03</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Share Price Rises 9.89% to Rs 540: Analysis - Univest</t>
+          <t>Precision Wires India Slips 2.86% to ₹483.1; PRECWIRE.NS Approaches Key Support - Negative Gamma - siam.in</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Q1 Results: Net profit drops 9.6% YoY to ₹287 lakh - scanx.trade</t>
+          <t>Precision Wires India Share Price rise and valuation view - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Alufluoride Q1 Results: Net profit drops 9.6% YoY to ₹287 lakh - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Precision Wires India Share Price Rises 5.47%: Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Precision Wires India Share Price rise and valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Precision Wires India PRECWIRE CCD Preferential Issue Approval - Kalkine India</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1585,68 +1573,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS.NS</t>
+          <t>UNICHEMLAB.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom Limited</t>
+          <t>Unichem Laboratories Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>761.2999877929688</v>
+        <v>537</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>828.9000244140625</v>
+        <v>608</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>754</v>
+        <v>530</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>809.9500122070312</v>
+        <v>568</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>758.5499877929688</v>
+        <v>536.4000244140625</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>809.9500122070312</v>
+        <v>568</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3027104</v>
+        <v>3856142</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6.78</v>
+        <v>5.89</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom shares extend two-day rally to 33%: Here are two reasons - Moneycontrol.com</t>
+          <t>Unichem Laboratories Share Price - Live NSE: UNICHEMLAB Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Electronics partners with Quectel to manufacture wireless modules in India - scanx.trade</t>
+          <t>Unichem Laboratories Limited (NSE:UNICHEMLAB) Gets Five Observations at Goa Formulation Facility - Kalkine India</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom To Acquire 51.1% Stake In Joint Venture With Nothing Electronics - Sahi</t>
+          <t>Buzzing Stocks: Prestige Estates falls as subsidiary withdraws DRHP; Zydus Life hits 52-week high on zero observations - TradingView</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Optiemus Infracom shares surge nearly 45% in three sessions, hit fresh 52-week high; here is why - Upstox</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Optiemus Infracom Hits 20% Upper Circuit As CMF Deepens India Partnership - TradingView</t>
-        </is>
-      </c>
+          <t>Unichem Laboratories Limited (NSE:UNICHEMLAB) Gets Five Observations at Goa Formulation Facility - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1654,68 +1638,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER.NS</t>
+          <t>SAMBHV.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Limited</t>
+          <t>Sambhv Steel Tubes Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2170</v>
+        <v>154</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2226</v>
+        <v>163.8000030517578</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2116</v>
+        <v>152.5</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2194.60009765625</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2062.5</v>
+        <v>154</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2194.60009765625</v>
+        <v>162</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>148082</v>
+        <v>7343081</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6.4</v>
+        <v>5.19</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
+          <t>Sambhv Steel Tubes Corrects Vajra Alloys Net Worth in Revised Filing - scanx.trade</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC targets 28-30% revenue growth in FY27 - scanx.trade</t>
+          <t>Sambhv Steel Tubes Corrects Vajra Alloys Net Worth in Revised Filing - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Share Price News on Capital Goods - Univest</t>
+          <t>Sambhv Steel Tubes shares jump 8%, extend two-day surge to 24% on heavy volumes; expansion plans in focus - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Should You Be Adding Macpower CNC Machines (NSE:MACPOWER) To Your Watchlist Today? - simplywall.st</t>
+          <t>SAMBHV 52 Week High Streak Keeps Stock Near Yearly Peak - Univest</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd is Rated Hold - MarketsMojo</t>
+          <t>Sambhv Steel Tubes to host virtual analyst meet on September 29 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1723,56 +1707,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR.NS</t>
+          <t>SENORES.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Shukra Pharmaceuticals Limited</t>
+          <t>Senores Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>56.70000076293945</v>
+        <v>1352.5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>60.4900016784668</v>
+        <v>1422</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>56</v>
+        <v>1352.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.43000030517578</v>
+        <v>1421</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>55.93000030517578</v>
+        <v>1351.800048828125</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>59.43000030517578</v>
+        <v>1421</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>15637756</v>
+        <v>308428</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6.26</v>
+        <v>5.12</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>SHUKRA PHARMA RG (SHUKRAPHAR) Fundamental and Financial Data - Stocktwits</t>
+          <t>Senores Pharmaceuticals AGM passes all resolutions; public dissent on ESOP - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>SHUKRA PHARMA RG (SHUKRAPHAR) Fundamental and Financial Data - Stocktwits</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+          <t>Senores Pharmaceuticals AGM passes all resolutions; public dissent on ESOP - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>SENORES Share Price Rises 5.04% | Market Cap Rs 6,572 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Senores Pharmaceuticals Ltd is Rated Hold - MarketsMojo</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1780,51 +1772,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>INDOBORAX.NS</t>
+          <t>WEALTH.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals Limited</t>
+          <t>Wealth First Portfolio Managers Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>441.0499877929688</v>
+        <v>846.75</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>508.7000122070312</v>
+        <v>918</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>435</v>
+        <v>837.7999877929688</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>477.5499877929688</v>
+        <v>875.2000122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>449.9500122070312</v>
+        <v>832.7999877929688</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>477.5499877929688</v>
+        <v>875.2000122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>8225574</v>
+        <v>4585</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6.13</v>
+        <v>5.09</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals (INDOBORAX.NS) Holds Firm at ₹470.2 as Traders Eye ₹493.71 Resistance - Growth ETF - siam.in</t>
+          <t>Meta Shares Slide 4%, Shaving Billions from Zuckerberg’s Paper Wealth - Yahoo Finance</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Indo Borax &amp; Chemicals (INDOBORAX.NS) Holds Firm at ₹470.2 as Traders Eye ₹493.71 Resistance - Growth ETF - siam.in</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Northwestern Mutual Wealth Management Co. Purchases 22,489 Shares of Amazon.com, Inc. $AMZN - MarketBeat</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Meta Shares Slide 4%, Shaving Billions from Zuckerberg’s Paper Wealth - gadgetreview.com</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>China Tries to Cool Taiwan’s Hot Stock Market - Cabot Wealth Network</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Earnings Momentum Faster Than Stock Prices, Says ASK Private Wealth's Vinay Jaising - ndtvprofit.com</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1843,7 +1847,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1949,7 +1953,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1957,68 +1961,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KOTYARK.NS</t>
+          <t>IWP.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries Limited</t>
+          <t>The Indian Wood Products Company Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.69000053405762</v>
+        <v>39.95000076293945</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31.69000053405762</v>
+        <v>42.40000152587891</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24.95999908447266</v>
+        <v>37.75</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26.46999931335449</v>
+        <v>38.54000091552734</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31.20000076293945</v>
+        <v>40.95999908447266</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>26.46999931335449</v>
+        <v>38.54000091552734</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1861015</v>
+        <v>313398</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-15.16</v>
+        <v>-5.91</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries closes trading window from Oct 1 for Q2FY27 results - scanx.trade</t>
+          <t>IWP Files Revised Disclosure for Mohta's Resignation Under SEBI Norms - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries closes trading window from Oct 1 for Q2FY27 results - scanx.trade</t>
+          <t>IWP Files Revised Disclosure for Mohta's Resignation Under SEBI Norms - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries allots 10.2 crore bonus shares in 10:1 ratio - scanx.trade</t>
+          <t>Technical Reactions to IWP Trends in Macro Strategies - Stock Traders Daily</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>IWP Capital urges FedEx to report on risks of s... - Pluang</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Kotyark Industries Ltd is Rated Hold by MarketsMOJO - MarketsMojo</t>
+          <t>IWP Capital to Vote "FOR" FedEx Proposal 6 on Abortion-Drug Distribution Risk - Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2026,68 +2030,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>PAISALO.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>87.01000213623047</v>
+        <v>62</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>88.70999908447266</v>
+        <v>62.40999984741211</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>73.41999816894531</v>
+        <v>58.15999984741211</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>79.59999847412109</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>89.01999664306641</v>
+        <v>62.29000091552734</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>79.59999847412109</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37592752</v>
+        <v>827230</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-10.58</v>
+        <v>-5.88</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital Ltd leads losers in 'A' group - Business Standard</t>
+          <t>UGARSUGAR Share Price Today: 8.51% Rise, Valuation View - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital Ltd leads losers in 'A' group - Business Standard</t>
+          <t>UGARSUGAR Share Price Today: 8.51% Rise, Valuation View - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital (PAISALO.NS) Holds Near ₹84.59 as Stock Consolidates Between ₹80.36 and ₹88.82 - Scalping Stock Signals - siam.in</t>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital to host virtual investor conference on September 29, 2026 - scanx.trade</t>
+          <t>The Ugar Sugar Works Limited Receives Closure Directions From Karnataka State Pollution Control Board - marketscreener.com</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital: Best Stock in Its Sector? Key Metrics - Univest</t>
+          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2095,56 +2099,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NOIDATOLL.NS</t>
+          <t>ADSL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Noida Toll Bridge Company Limited</t>
+          <t>Allied Digital Services Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.970000028610229</v>
+        <v>114</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4</v>
+        <v>114.3000030517578</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3.569999933242798</v>
+        <v>108.2699966430664</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3.579999923706055</v>
+        <v>110.2600021362305</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3.960000038146973</v>
+        <v>116.6600036621094</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.579999923706055</v>
+        <v>110.2600021362305</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>324907</v>
+        <v>504653</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.6</v>
+        <v>-5.49</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Noida Toll Bridge Company Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
+          <t>Allied Digital Serv Share Price - Live NSE: ADSL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Noida Toll Bridge Company Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Allied Digital reports record revenue of ₹968 crore in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Allied Digital Services Share Price rises 14.29% to Rs 110 - Univest</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>ADSL Holdings Inc. (AMNNF) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Allied Digital Services Ltd. Upper Circuit: Price and Key Data - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2152,68 +2168,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>NPST.NS</t>
+          <t>PRSMJOHNSN.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Network People Services Technologies Limited</t>
+          <t>Prism Johnson Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1812.599975585938</v>
+        <v>115.0899963378906</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1813</v>
+        <v>115.1500015258789</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1625.099975585938</v>
+        <v>108.5699996948242</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1635</v>
+        <v>109.120002746582</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1796.300048828125</v>
+        <v>115.1500015258789</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1635</v>
+        <v>109.120002746582</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>110140</v>
+        <v>663261</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-8.98</v>
+        <v>-5.24</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SRV TECH L Share Price - Live NSE: NPST Stock Price &amp; Chart - Upstox</t>
+          <t>Prism Johnson Share Price - Upstox</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>NPST confirms dispatch of 13th AGM notice scheduled for September 28 - scanx.trade</t>
+          <t>Prism Johnson Completes Postal Ballot Notice Publication for ₹324 Crore Divestment - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>NPST Share Price rises 10.36%: price action and analysis - Univest</t>
+          <t>Prism Johnson (PRSMJOHNSN.NS) Holds Near ₹111.12; Range-Bound Action with Support at ₹105.56 and Resistance at ₹116.68 - Keltner Channel - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>NPST to host analyst meeting with SBI Mutual Funds on Sep 29, 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>NPST Surges 4.22% to ₹1,708: Network People Services Technologies Approaches Key Resistance - Fundamentals - siam.in</t>
-        </is>
-      </c>
+          <t>Prism Johnson Completes Postal Ballot Notice Publication for ₹324 Crore Divestment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2221,68 +2233,60 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RSL.NS</t>
+          <t>PREMIERENE.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>Premier Energies Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>182.4100036621094</v>
+        <v>906</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>182.4100036621094</v>
+        <v>917.5999755859375</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>165.9199981689453</v>
+        <v>857.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>167.4100036621094</v>
+        <v>860</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>183.4600067138672</v>
+        <v>906</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>167.4100036621094</v>
+        <v>860</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>799141</v>
+        <v>2064786</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-8.75</v>
+        <v>-5.08</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>RAJPUTANA STAINLESS LTD Share Price - Live NSE: RSL Stock Price &amp; Chart - Upstox</t>
+          <t>Premier Energies Share Price News: market cap and ratios - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sergi Solans scores 2 goals, RSL beats Revolution 3-0 to snap 13-game winless skid - FOX Sports</t>
+          <t>Premier Energies seeks nod for RPTs worth ₹76,890 million - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited (RSL.NS): Steady at ₹181.5 as Stock Consolidates Between Key Levels - Bear Flag - siam.in</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Rajasthan Securities approves ₹40 crore guarantee for subsidiary RSL Securities - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Sergi Solans scores 2 goals, RSL beats Revolution 3-0 to snap 13-game winless skid - FOX Sports</t>
-        </is>
-      </c>
+          <t>Premier Energies seeks nod for RPTs worth ₹76,890 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2290,68 +2294,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>VTMLTD.NS</t>
+          <t>SHANTIGEAR.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>VTM Limited</t>
+          <t>Shanthi Gears Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>42.43999862670898</v>
+        <v>625</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43.11000061035156</v>
+        <v>625</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>37.45000076293945</v>
+        <v>601.6500244140625</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>38.06999969482422</v>
+        <v>601.6500244140625</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>41.52999877929688</v>
+        <v>633.2999877929688</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>38.06999969482422</v>
+        <v>601.6500244140625</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>348087</v>
+        <v>78420</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-8.33</v>
+        <v>-5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>VTM Ltd net profit falls 58% to ₹193 lakh as costs outpace revenue - scanx.trade</t>
+          <t>Shanthi Gears Q2 2026 Earnings: Revenue Slips 14.4% YoY as Stock Dips 2% - Earnings Seasonality - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>VTM Ltd net profit falls 58% to ₹193 lakh as costs outpace revenue - scanx.trade</t>
+          <t>Tube Investments schedules analyst meetings in September - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>VTM Limited Share Price Falls as Technical Setup Shifts - Kalkine India</t>
+          <t>Shanthi Gears Share Price news: yearly high and valuation - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>VTM Ltd. Share Price rises 13.42%: valuation view - Univest</t>
+          <t>Price Action: WeWork India rises 3% on solar plant approval; Shanthi Gears jumps 5% after CFO appointment - TradingView</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>VTM Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Shanthi Gears Limited (NSE:SHANTIGEAR): A Simple Guide to Its Business and Sector Position - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2359,68 +2363,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KIRANVYPAR.NS</t>
+          <t>STLNETWORK.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kiran Vyapar Limited</t>
+          <t>STL Networks Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>195</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>195</v>
+        <v>51.09000015258789</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>180.5500030517578</v>
+        <v>49.45999908447266</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>185.1699981689453</v>
+        <v>49.45999908447266</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>201.1499938964844</v>
+        <v>52.06000137329102</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>185.1699981689453</v>
+        <v>49.45999908447266</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>12146</v>
+        <v>16561133</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.94</v>
+        <v>-4.99</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Kiran (KIRANVYPAR.NS) Stock Screener: -1.36% Decline on Elevated Volume 2026-08-30 - Weekly Profile - siam.in</t>
+          <t>STL NETWORKS LIMITED Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Kiran Vyapar shareholders approve FY26 financials and final dividend - scanx.trade</t>
+          <t>STL NETWORKS LIMITED Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Kiran Vyapar Share Price Today: Market Cap And Valuation - Univest</t>
+          <t>STLNETWORK Stock Price and Chart — NSE:STLNETWORK - TradingView</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>MSUM Acquires 33.86% Stake in Kiran Vyapar Through NCLT-Approved Amalgamation - scanx.trade</t>
+          <t>STLNETWORK.NS Q2 2026 Earnings: Revenue Declines 18.61% YoY, EPS Loss of ₹2.03, Yet Stock Gains 4.98% - siam.in</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Kiran Vyapar shareholders approve FY26 financials and final dividend - scanx.trade</t>
+          <t>Anil Agarwal confirms no encumbrance on STL Networks shares in FY26 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2428,68 +2432,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ELECTHERM.NS</t>
+          <t>CHEMBONDCH.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Electrotherm (India) Limited</t>
+          <t>Chembond Chemicals Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>850</v>
+        <v>246.8000030517578</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>870</v>
+        <v>246.8000030517578</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>786.0499877929688</v>
+        <v>230.3000030517578</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>806.6500244140625</v>
+        <v>230.3000030517578</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>873.3499755859375</v>
+        <v>242.3999938964844</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>806.6500244140625</v>
+        <v>230.3000030517578</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>69913</v>
+        <v>9686</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-7.64</v>
+        <v>-4.99</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Electrotherm (India) Share Price Fall: Key Market Update - Univest</t>
+          <t>Chembond Chemical Specialties Ltd. Lower Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Electrotherm holds 40th AGM, approves director appointments and financials - scanx.trade</t>
+          <t>Chembond Chemical Specialties Ltd. Lower Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Electrotherm India ELECTHERM 40th AGM Resolutions September 2026 - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Electrotherm holds 40th AGM, approves director appointments and financials - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Electrotherm India (ELECTHERM.NS) Slips 1.15% to ₹945.35, Holding Mid-Range Between Key Levels - Put Flow Alert - siam.in</t>
-        </is>
-      </c>
+          <t>Chembond Chemicals CHEMBONDCH Trading Window Closure - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2497,56 +2493,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CREATIVEYE.NS</t>
+          <t>MANUGRAPH.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Creative Eye Limited</t>
+          <t>Manugraph India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6</v>
+        <v>17.88999938964844</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>6.239999771118164</v>
+        <v>17.88999938964844</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5.650000095367432</v>
+        <v>17.88999938964844</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5.71999979019165</v>
+        <v>17.88999938964844</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6.190000057220459</v>
+        <v>18.82999992370605</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5.71999979019165</v>
+        <v>17.88999938964844</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>20647</v>
+        <v>12977</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-7.59</v>
+        <v>-4.99</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Creative Eye AGM adopts FY26 financials, appoints STDJ &amp; Co as auditor - scanx.trade</t>
+          <t>Manugraph India (MANUGRAPH.NS) Edges Higher to ₹15.19 as Stock Pivots Near Key Resistance - Fibonacci Retracement - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Creative Eye AGM adopts FY26 financials, appoints STDJ &amp; Co as auditor - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Manugraph India Ltd is Rated Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Manugraph India Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Manugraph India Ltd is Rated Sell - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Manugraph India Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2554,64 +2562,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RAMBHAJO.NS</t>
+          <t>ELITECON.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Limited</t>
+          <t>Elitecon International Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>282.4400024414062</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>282.4400024414062</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>263</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>265.0299987792969</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>286.2300109863281</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>265.0299987792969</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>860767</v>
+        <v>3376528</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-7.41</v>
+        <v>-4.98</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Elitecon International Signs Export Pact With South Africa Firm; Shares Fall 2.64% - hdfcsky.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Ltd. Share Price Today - Advit Jewels Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Elitecon International signs $60 million tobacco supply deal - BusinessLine</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ADVIT JEWELS LIMITED Share Price news: valuation and peers - Univest</t>
+          <t>Elitecon International signs $60 million tobacco supply deal - BusinessLine</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Elitecon International surges 5% with ₹202 Cr export order, expands into Africa - Alice Blue</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Tobacco Stock Elitecon International In Focus: Company Signs Up To Rs 574 Crore South Africa Supply Pact - Goodreturns</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2619,68 +2631,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>NOCIL.NS</t>
+          <t>NEUEON.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Limited</t>
+          <t>Neueon Corporation Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>188.0500030517578</v>
+        <v>15.85000038146973</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>188.0500030517578</v>
+        <v>15.85000038146973</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>174</v>
+        <v>14.35000038146973</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>175.1699981689453</v>
+        <v>14.35000038146973</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>188.4100036621094</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>175.1699981689453</v>
+        <v>14.35000038146973</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1512312</v>
+        <v>36804</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-7.03</v>
+        <v>-4.97</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>NOCIL Stock Signals to Watch This Week - Univest</t>
+          <t>Neueon Corporation Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Nocil Share Price Falls as Chemical Stock Stays in Focus - Univest</t>
+          <t>Neueon board approves ₹300 crore fund raise and AOA amendments - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Nocil Ltd. Stock News - Value Research</t>
+          <t>Neueon board approves ₹300 crore fund raise and AOA amendments - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Nocil Share Price Falls as Chemical Stock Stays in Focus - Univest</t>
+          <t>Neueon Corporation withdraws ₹150.79 Cr rights issue proposal - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>NOCIL sets ₹1.50 dividend for FY26, details TDS rules - scanx.trade</t>
+          <t>Neueon Towers Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2688,68 +2700,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>OMAXE.NS</t>
+          <t>KABRAEXTRU.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Omaxe Limited</t>
+          <t>Kabra Extrusion Technik Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>110</v>
+        <v>831.0999755859375</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>116.0400009155273</v>
+        <v>841.9000244140625</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>108.0100021362305</v>
+        <v>820</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>110.2699966430664</v>
+        <v>820.25</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>118.5299987792969</v>
+        <v>863.1500244140625</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>110.2699966430664</v>
+        <v>820.25</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1131149</v>
+        <v>283662</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-6.97</v>
+        <v>-4.97</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Omaxe Stock Signals to Watch This Week - Univest</t>
+          <t>Why Kabra (KABRAEXTRU.NS) Just Dropped -3.50% — What to Watch 2026-09-16 - Inverse ETF Flow - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Omaxe shares fall 4% after SEBI bars company from securities market for three months - Business Upturn</t>
+          <t>Kabra Extrusiontechnik (NSE:KABRAEXTRU): What Does the Preferential Issue Approval Mean? - Kalkine India</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>SEBI finds Omaxe, promoter-linked entities breached MPS norms through 2013 OFS, imposes restraint and... - Moneycontrol.com</t>
+          <t>Kabra Extrusiontechnik (NSE:KABRAEXTRU): What Does the Preferential Issue Approval Mean? - Kalkine India</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Sebi Bans Omaxe, Others for Artificial Public Shareholding - Rediff MoneyWiz</t>
+          <t>Kabra Extrusiontechnik Share Price near 52-week high | - Univest</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>SEBI Bars Omaxe for 3 Months, Promoters for 1 Year, Imposes ₹1.92 Crore Penalty Over MPS Violation - Moneylife</t>
+          <t>Kabra Extrusiontechnik Share Price: 52-Week High, Valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2757,68 +2769,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>KDGREEN.NS</t>
+          <t>DISHTV.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>KD Green Industries Limited</t>
+          <t>Dish TV India Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>49.5</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>51</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46.06000137329102</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46.7599983215332</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>50.09999847412109</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46.7599983215332</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>56641</v>
+        <v>2306401</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-6.67</v>
+        <v>-4.87</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>KDGREEN Share Price Today - Manbro Industries Ltd. Stock Price Live NSE/BSE - Univest</t>
+          <t>Dish TV India Limited Auditor Raises 'Going Concern' Doubt - marketscreener.com</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>KD Green merger to create green steel and infrastructure hub - scanx.trade</t>
+          <t>Dish TV India Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>KD Green Industries Ltd - equitypandit.com</t>
+          <t>Dish TV India Ltd. Lower Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of KD Green Industries Ltd (NSE:KDGREEN) - TradingView</t>
+          <t>Dish TV India Limited(BSE: 532839) dropped from S&amp;P Global BMI Index - marketscreener.com</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>KD Green merger to create green steel and infrastructure hub - scanx.trade</t>
+          <t>Dish TV schedules 38th AGM for September 29, 2026 via video conferencing - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2826,68 +2838,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>MANINDS.NS</t>
+          <t>AASTHA.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Man Industries (India) Limited</t>
+          <t>Aastha Spintex Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1020</v>
+        <v>38.70999908447266</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1030.900024414062</v>
+        <v>38.70999908447266</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>943.7000122070312</v>
+        <v>36.61000061035156</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>953.3499755859375</v>
+        <v>37.40000152587891</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1020.349975585938</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>953.3499755859375</v>
+        <v>37.40000152587891</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1294525</v>
+        <v>594555</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-6.57</v>
+        <v>-4.83</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Man Industries (India) (NSE:MANINDS) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>Aastha Spintex allots 4.41 crore bonus shares in 1:1 ratio - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Man Industries (India) (NSE:MANINDS) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>Aastha Spintex allots 4.41 crore bonus shares in 1:1 ratio - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Man Industries Drops 3.55% to ₹792.55; Support at ₹752.92 Becomes Key - Jelly Roll Trade - siam.in</t>
+          <t>Aastha Spintex shares jump 7% after adjusting for 1:1 bonus - All you need to know - CNBC TV18 - LinkedIn</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Man Industries (India) Share Price: 52-Week High Update - Univest</t>
+          <t>Aastha Spintex Secures ₹25 Crore Fabric Orders; Shares Fall 9.99% - hdfcsky.com</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Man Industries Share Price Fall: Technicals and Valuation - Univest</t>
+          <t>Aastha Spintex shares rise 9% after adjusting for 1:1 bonus issue - TradingView</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2895,68 +2907,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>LAMBODHARA.NS</t>
+          <t>TVVISION.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Limited</t>
+          <t>TV Vision Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>141</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>141</v>
+        <v>3.049999952316284</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>131.8600006103516</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>135.1900024414062</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>144.5700073242188</v>
+        <v>2.960000038146973</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>135.1900024414062</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>37259</v>
+        <v>62959</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-6.49</v>
+        <v>-4.73</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Share Price today: key valuation view - Univest</t>
+          <t>NCLT dismisses IBC petition filed by Swami Films against TV Vision - scanx.trade</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Trading Window Closure Q2 FY27 - Kalkine India</t>
+          <t>NCLT dismisses IBC petition filed by Swami Films against TV Vision - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Trading Window Closure Q2 FY27 - Kalkine India</t>
+          <t>TV Vision faces ₹53.93 Cr GST demand over alleged ITC excess availment - scanx.trade</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Is It Smart To Buy Lambodhara Textiles Limited (NSE:LAMBODHARA) Before It Goes Ex-Dividend? - simplywall.st</t>
+          <t>TV Vision Ltd. Share Price Today - TV Vision Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Lambodhara Textiles Share Price Fall: Price Analysis - Univest</t>
+          <t>TVVISION Historical Data - Equitypandit</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2964,68 +2976,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AVTNPL.NS</t>
+          <t>ALMONDZ.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products Limited</t>
+          <t>Almondz Global Securities Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>92.5</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>92.59999847412109</v>
+        <v>20.61000061035156</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>86.01999664306641</v>
+        <v>20.04000091552734</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>86.61000061035156</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>92.58000183105469</v>
+        <v>21.09000015258789</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>86.61000061035156</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>493697</v>
+        <v>238996</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-6.45</v>
+        <v>-4.69</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products Ltd Share Price Today,, AVTNPL Share Price NSE, BSE - Business Today</t>
+          <t>Almondz promoter buys 2.41 lakh shares, holding hits 1% - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural AGM voting results: all 5 resolutions pass with strong support - scanx.trade</t>
+          <t>Almondz promoter buys 2.41 lakh shares, holding hits 1% - scanx.trade</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural AGM voting results: all 5 resolutions pass with strong support - scanx.trade</t>
+          <t>Almondz Global Sec Share Price - Upstox</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products Share Price: price rise and valuation - Univest</t>
+          <t>Avonmore Capital &amp; Management Services Ltd Share Price Today NSE/BSE Charts - Alice Blue</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>AVT Natural Products Share Price rises 8.28% on valuation - Univest</t>
+          <t>Almondz Global Securities Share Price: 12% Fall Analysis - Univest</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3033,68 +3045,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>STERTOOLS.NS</t>
+          <t>CORDSCABLE.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sterling Tools Limited</t>
+          <t>Cords Cable Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>240</v>
+        <v>315.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>240.6499938964844</v>
+        <v>335</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>223.5</v>
+        <v>314.8500061035156</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>224.1300048828125</v>
+        <v>316</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>239.4600067138672</v>
+        <v>331.3999938964844</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>224.1300048828125</v>
+        <v>316</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>50109</v>
+        <v>64580</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-6.4</v>
+        <v>-4.65</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Sterling Tools Share Price - Upstox</t>
+          <t>Cords Cable Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sterling Tools Share Price - Upstox</t>
+          <t>Cords Cable Industries Trading Window Closure October 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Sterling Tools Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>STERTOOLS Q2 2026 Earnings: EPS of ₹8.02 as Revenue Slips 20.79% Year-on-Year - Earnings Weakness Phase - siam.in</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Sterling Tools opens e-voting for Whole Time Director appointment - scanx.trade</t>
-        </is>
-      </c>
+          <t>Cords Cable Industries Trading Window Closure October 2026 - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3102,68 +3110,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ACL.NS</t>
+          <t>PATANJALI.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Andhra Cements Limited</t>
+          <t>Patanjali Foods Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42.93999862670898</v>
+        <v>390</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>42.93999862670898</v>
+        <v>391.6000061035156</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>39.5099983215332</v>
+        <v>368.8999938964844</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>39.93999862670898</v>
+        <v>373.25</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>42.63000106811523</v>
+        <v>390.7999877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>39.93999862670898</v>
+        <v>373.25</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>67312</v>
+        <v>3196250</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-6.31</v>
+        <v>-4.49</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>ANDHRA CEMENTS LIMITED Share Price - Upstox</t>
+          <t>Patanjali Foods shares extend rally, jump 6% as management backs FY27 growth targets - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>ANDHRA CEMENTS LIMITED Share Price - Upstox</t>
+          <t>KRBL vs Bikaji Foods International vs Patanjali Foods: Comparison - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>A.C.L. Construction Ltd. (ACL) To Issue 1.95M Shares To Settle $234K Debt - TradingView</t>
+          <t>KRBL vs Bikaji Foods International vs Patanjali Foods: Comparison - Univest</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>A.C.L. Construction Ltd. Announces Shares for Debt Settlement - TradingView</t>
+          <t>Patanjali Foods share price rises 5% today. What is driving the rally in the FMCG stock? - Livemint</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>A.C.L. Construction Ltd. Resolves $234,495 Debt via Share Issuance to Company Insiders - Kalkine Media</t>
+          <t>Here's why Patanjali Foods, AWL Agri and Godrej Agrovet shares will be in focus today - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3171,68 +3179,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>AERONEU.NS</t>
+          <t>TURTLEMINT.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Neu Limited</t>
+          <t>Turtlemint Fintech Solutions Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>80.01000213623047</v>
+        <v>84</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>80.01000213623047</v>
+        <v>84.05000305175781</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>73</v>
+        <v>78.80000305175781</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>75.18000030517578</v>
+        <v>79.55999755859375</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>80.22000122070312</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>75.18000030517578</v>
+        <v>79.55999755859375</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>30144</v>
+        <v>2046580</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-6.28</v>
+        <v>-4.48</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Sah Polymers Share Price - Upstox</t>
+          <t>PB Fintech, Turtlemint Fintech tank up to 43% in 4 days; hit 52-week lows - Business Standard</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sah Polymers Share Price Today: Price Fall and Valuation - Univest</t>
+          <t>PB Fintech, Turtlemint Fintech tank up to 43% in 4 days; hit 52-week lows - Business Standard</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Sah Polymers Share Price Today: Price Fall and Valuation - Univest</t>
+          <t>Turtlemint Fintech Solutions Ltd (TURTLEMINT) Share Price - Business Today</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Neu Ltd (NSE: AERONEU) Gains 20.00% as Stock Sees Renewed Market Interest - Kalkine India</t>
+          <t>Insurance stocks crash: PB Fintech, Turtlemint shares fall up to 28% on IRDAI draft - Is this a buying opportu - CNBC TV18</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Neu Limited (AERONEU.NS) Slips 1.76% to ₹65.91, Holds Above Key Support - Box Spread - siam.in</t>
+          <t>PB Fintech, Turtlemint Shares Extend Slump as Outlook Worsens - Bloomberg.com</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:46:12 IST</t>
+          <t>2026-09-29 14:17:25 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3240,61 +3248,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MANAKSIA.NS</t>
+          <t>NESCO.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Limited</t>
+          <t>Nesco Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>63.90000152587891</v>
+        <v>1082.300048828125</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>64.69999694824219</v>
+        <v>1082.300048828125</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>58.25</v>
+        <v>1036.900024414062</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.18999862670898</v>
+        <v>1038.400024414062</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>64.11000061035156</v>
+        <v>1086.400024414062</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>60.18999862670898</v>
+        <v>1038.400024414062</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>52826</v>
+        <v>89314</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-6.11</v>
+        <v>-4.42</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Share Price - Upstox</t>
+          <t>Nesco Stock Signals to Watch This Week - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Coated Metals hosts virtual analyst meet on Sep 28 - scanx.trade</t>
+          <t>Nesco Stock Signals to Watch This Week - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Coated Metals hosts virtual analyst meet on Sep 28 - scanx.trade</t>
+          <t>NESCO Share Price - Upstox</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>MANAKSIA. Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
+          <t>Nesco Limited (NESCO.NS) Slips 1.32% to ₹1,087.7 as Stock Holds Above Key Support Zone - Put Call Ratio - siam.in</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Manaksia Share Price rises 8.4%: valuation view - Univest</t>
+          <t>Nesco share analysis: prime land, but a long wait for growth - Value Research</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:17:25 IST</t>
+          <t>2026-09-29 22:08:34 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,56 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TNTELE.NS</t>
+          <t>DPABHUSHAN.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tamilnadu Telecommunication Limited</t>
+          <t>D. P. Abhushan Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13.5</v>
+        <v>1384</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.26000022888184</v>
+        <v>1665.800048828125</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>13.10999965667725</v>
+        <v>1376.400024414062</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>14.26000022888184</v>
+        <v>1665.800048828125</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>11.89000034332275</v>
+        <v>1388.199951171875</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14.26000022888184</v>
+        <v>1665.800048828125</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>507741</v>
+        <v>975157</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.93</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Tamilnadu Telecommunications Secures Shareholder Nod on All AGM Resolutions - TipRanks</t>
+          <t>D.P. Abhushan Share Price Update with Fundamental Analysis - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Tamilnadu Telecommunications Secures Shareholder Nod on All AGM Resolutions - TipRanks</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>D.P. Abhushan board to consider fund raise via preferential issue on Oct 5 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>D.P. Abhushan board to consider fund raise via preferential issue on Oct 5 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, D. P. Abhushan (NSE:DPABHUSHAN) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>D. P. Abhushan (DPABHUSHAN.NS) Declines 3.22% to ₹1370.4 — Key Levels to Track - Fibonacci Arc - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:17:25 IST</t>
+          <t>2026-09-29 22:08:34 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -610,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES.NS</t>
+          <t>RETAIL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES Technologies Limited</t>
+          <t>JHS Svendgaard Retail Ventures Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2034</v>
+        <v>28.8799991607666</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2067.39990234375</v>
+        <v>28.8799991607666</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1970.800048828125</v>
+        <v>28.79999923706055</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2067.39990234375</v>
+        <v>28.8799991607666</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1879.5</v>
+        <v>24.06999969482422</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2067.39990234375</v>
+        <v>28.8799991607666</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>774119</v>
+        <v>117004</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>10</v>
+        <v>19.98</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Axiscades Tech shares gain 10% after equity worth ₹741 crore changes hands in block deal window - CNBC TV18</t>
+          <t>REG - Smarter Web Company - Launch of Retail Offer of "MORE" Preferred Shares - TradingView</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Jupiter Capital sells 10.86% stake in Axiscades Technologies - scanx.trade</t>
+          <t>B&amp;M Retail stock gains 1.07 percent as BofA lifts target - AD HOC NEWS</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Axiscades Tech shares hit 10% upper circuit on block deal in defence firm - Business Standard</t>
+          <t>7NR RETAIL Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Axiscades Tech share price locked in 10% upper circuit | What’s driving the stock and what lies ahead? - Livemint</t>
+          <t>Is Itochu (ITOCY) Stock Outpacing Its Retail-Wholesale Peers This Year? - finance.yahoo.com</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Jupiter Capital sells 10.86% stake in Axiscades Technologies - scanx.trade</t>
+          <t>SS Retail share price jumps 7% amid stock market fall | Do you own? - Livemint</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:17:25 IST</t>
+          <t>2026-09-29 22:08:34 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -679,56 +691,60 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EUROTEXIND.NS</t>
+          <t>LANDSMILL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Eurotex Industries and Exports Limited</t>
+          <t>Landsmill Green Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13.10000038146973</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>14.10000038146973</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>12.5</v>
+        <v>0.7599999904632568</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14.10000038146973</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.92000007629395</v>
+        <v>0.7400000095367432</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.10000038146973</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1869</v>
+        <v>18968233</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>18.92</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Eurotex shareholders clear all resolutions at 40th AGM, back capital and board moves - TipRanks</t>
+          <t>EXCEL REALTY N INFRA Share Price - Live NSE: LANDSMILL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Eurotex shareholders clear all resolutions at 40th AGM, back capital and board moves - TipRanks</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>Landsmill Green holds 24th AGM to adopt FY26 financials - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Landsmill Green holds 24th AGM to adopt FY26 financ